--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90ED481D-9573-42B7-B038-6CD8A49715FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AADE7B9-31E2-4D05-99FF-CDC28D12A908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -5,18 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\副業\LINE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AADE7B9-31E2-4D05-99FF-CDC28D12A908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823291FA-2F15-4108-B624-A9D156C8DF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="リスト" sheetId="1" r:id="rId1"/>
+    <sheet name="進捗表" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$3:$AA$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">リスト!$A$3:$AA$230</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,6 +26,24 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={05AA67FA-12A1-434A-9C6D-CDE6FF0D4BC8}</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{05AA67FA-12A1-434A-9C6D-CDE6FF0D4BC8}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    個数分絵を作成して割り振りを決める</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
@@ -80,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="243">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -449,53 +468,53 @@
     <rPh sb="7" eb="9">
       <t>シヨウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>リスト</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>推し</t>
     <rPh sb="0" eb="1">
       <t>オ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>お相撲さん</t>
     <rPh sb="1" eb="3">
       <t>スモウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>お姫様</t>
     <rPh sb="1" eb="3">
       <t>ヒメサマ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>幽霊</t>
     <rPh sb="0" eb="2">
       <t>ユウレイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>宇宙人</t>
     <rPh sb="0" eb="3">
       <t>ウチュウジン</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>画家</t>
     <rPh sb="0" eb="2">
       <t>ガカ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>世界の人の笑顔</t>
@@ -508,209 +527,209 @@
     <rPh sb="5" eb="7">
       <t>エガオ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>カップ麺</t>
     <rPh sb="3" eb="4">
       <t>メン</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>植物</t>
     <rPh sb="0" eb="2">
       <t>ショクブツ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>文豪</t>
     <rPh sb="0" eb="2">
       <t>ブンゴウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>光源氏</t>
     <rPh sb="0" eb="3">
       <t>ヒカルゲンジ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>気象状況</t>
     <rPh sb="0" eb="4">
       <t>キショウジョウキョウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>猫</t>
     <rPh sb="0" eb="1">
       <t>ネコ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>犬</t>
     <rPh sb="0" eb="1">
       <t>イヌ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ふわふわ</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>馬</t>
     <rPh sb="0" eb="1">
       <t>ウマ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>鯛</t>
     <rPh sb="0" eb="1">
       <t>タイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>仕事中</t>
     <rPh sb="0" eb="3">
       <t>シゴトチュウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>うまくいきますように</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>うまいぞ</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>御利益　御利益</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>早いぞ早いぞ</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>汗だくだく</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>風が気持ちいいな</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>走ります</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>食べたい、、、　　　（人参前にして）</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>頑張ったよ　　　　　（一等賞で）</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>歩いていくよ</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ひーひっひ</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>話が上手い</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ウルウル　　　　　　（瞳に涙を溜めて）</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>今年も頑張ろうね</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>素晴らしい年になったね</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>横になるわ　　　　　（横たわったイラスト）</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>綺麗でしょ</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>無言、、、</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>〇</t>
   </si>
   <si>
     <t>神！</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>サイコー</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>輝いている</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>キラキラッ</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ス・テ・キ</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>推し愛してる</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>好きだよー</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ほーっ</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>眩しい！</t>
     <rPh sb="0" eb="1">
       <t>マブ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>応援しているよ</t>
     <rPh sb="0" eb="2">
       <t>オウエン</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>元気になるよ</t>
     <rPh sb="0" eb="2">
       <t>ゲンキ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>振り返り</t>
@@ -720,30 +739,30 @@
     <rPh sb="2" eb="3">
       <t>カエ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>鴨</t>
     <rPh sb="0" eb="1">
       <t>カモ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ちらっ</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>おはよう</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>おつかれ</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>おやすみ</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>今向かってる</t>
@@ -753,58 +772,58 @@
     <rPh sb="1" eb="2">
       <t>ム</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>あとで</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>どうする？</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>嬉しい</t>
     <rPh sb="0" eb="1">
       <t>ウレ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ドン引き</t>
     <rPh sb="2" eb="3">
       <t>ビ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>困った</t>
     <rPh sb="0" eb="1">
       <t>コマ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>笑</t>
     <rPh sb="0" eb="1">
       <t>ワラ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>いいなぁ</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>寝てた</t>
     <rPh sb="0" eb="1">
       <t>ネ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>楽しんでる？</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ただいまパソコン使用中</t>
@@ -814,14 +833,14 @@
     <rPh sb="10" eb="11">
       <t>チュウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ただいま出張中</t>
     <rPh sb="4" eb="7">
       <t>シュッチョウチュウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>今帰宅中</t>
@@ -831,7 +850,7 @@
     <rPh sb="1" eb="4">
       <t>キタクチュウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>今通勤中</t>
@@ -841,7 +860,7 @@
     <rPh sb="1" eb="4">
       <t>ツウキンチュウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>外回り中です</t>
@@ -851,242 +870,357 @@
     <rPh sb="3" eb="4">
       <t>チュウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ZOOM会議中</t>
     <rPh sb="4" eb="7">
       <t>カイギチュウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>痩せたい</t>
     <rPh sb="0" eb="1">
       <t>ヤ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>会いたい</t>
     <rPh sb="0" eb="1">
       <t>ア</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>話したい</t>
     <rPh sb="0" eb="1">
       <t>ハナ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>見たい</t>
     <rPh sb="0" eb="1">
       <t>ミ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>聞きたい</t>
     <rPh sb="0" eb="1">
       <t>キ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>読みたい</t>
     <rPh sb="0" eb="1">
       <t>ヨ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ありがたい</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>おめでたい</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>歌いたい</t>
     <rPh sb="0" eb="1">
       <t>ウタ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>眠たい</t>
     <rPh sb="0" eb="1">
       <t>ネム</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>休みたい</t>
     <rPh sb="0" eb="1">
       <t>ヤス</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ゆっくりしたい</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>考えたい</t>
     <rPh sb="0" eb="1">
       <t>カンガ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>座りたい</t>
     <rPh sb="0" eb="1">
       <t>スワ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>働きたい</t>
     <rPh sb="0" eb="1">
       <t>ハタラ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>休憩したい</t>
     <rPh sb="0" eb="2">
       <t>キュウケイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>挑戦したい</t>
     <rPh sb="0" eb="2">
       <t>チョウセン</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>旅したい</t>
     <rPh sb="0" eb="1">
       <t>タビ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>参加したい</t>
     <rPh sb="0" eb="2">
       <t>サンカ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>運動したい</t>
     <rPh sb="0" eb="2">
       <t>ウンドウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>応援したい</t>
     <rPh sb="0" eb="2">
       <t>オウエン</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>守りたい</t>
     <rPh sb="0" eb="1">
       <t>マモ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>手伝いたい</t>
     <rPh sb="0" eb="2">
       <t>テツダ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>寒い</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>大変だ</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>何処にいるの？</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>急いでいきます</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>やったぜ</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>がんばりましょう</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ルンルンルン</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>これあげる</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>うーん悩む</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>暑い</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>大丈夫？</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>はしゃいでしまった</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>超絶ごめんなさい</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ありがとう</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>また会おう</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>楽しい時間をありがと</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ひな祭り</t>
+    <rPh sb="2" eb="3">
+      <t>マツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>基本の絵作成</t>
+    <rPh sb="0" eb="2">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>担当割り振り作成</t>
+    <rPh sb="0" eb="2">
+      <t>タントウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>文字入れ【和】</t>
+    <rPh sb="0" eb="2">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>文字入れ【知】</t>
+    <rPh sb="0" eb="2">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>チ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>MAIN、TAB作成</t>
+    <rPh sb="8" eb="10">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>申請中</t>
+    <rPh sb="0" eb="2">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>販売中</t>
+    <rPh sb="0" eb="2">
+      <t>ハンバイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>ひな祭り</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>神様</t>
+    <rPh sb="0" eb="2">
+      <t>カミサマ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>神様</t>
+    <rPh sb="0" eb="2">
+      <t>カミサマ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1149,8 +1283,22 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="MS P ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1178,6 +1326,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1247,60 +1401,60 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1312,12 +1466,34 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{19A992FB-2484-415A-9E43-77DE60BD213C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1330,6 +1506,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="知恵 山下" id="{DD5EADF8-B504-43B2-BB0E-C2E7C3FF5FAA}" userId="cd9976f2c19ed1e4" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1672,148 +1854,170 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C2" dT="2026-01-31T04:40:30.76" personId="{DD5EADF8-B504-43B2-BB0E-C2E7C3FF5FAA}" id="{05AA67FA-12A1-434A-9C6D-CDE6FF0D4BC8}">
+    <text>個数分絵を作成して割り振りを決める</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA230"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:AB230"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
-    <col min="1" max="1" width="3.4140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.4375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="3.58203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.58203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="21" width="3.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="3.5625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.5625" bestFit="1" customWidth="1"/>
+    <col min="10" max="28" width="3.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="22.5">
-      <c r="A1" s="18"/>
-      <c r="B1" s="15" t="s">
+    <row r="1" spans="1:28" ht="22.9">
+      <c r="A1" s="17"/>
+      <c r="B1" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="21"/>
-      <c r="U1" s="21"/>
-      <c r="V1" s="21"/>
-      <c r="W1" s="21"/>
-    </row>
-    <row r="2" spans="1:27" ht="22.5">
-      <c r="A2" s="19"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="e" vm="1">
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+    </row>
+    <row r="2" spans="1:28" ht="22.9">
+      <c r="A2" s="18"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6" t="e" vm="2">
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6" t="e" vm="3">
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="S2" s="6" t="e" vm="4">
+      <c r="S2" s="5" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-    </row>
-    <row r="3" spans="1:27" s="14" customFormat="1" ht="92.5" thickBot="1">
-      <c r="A3" s="20"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="12" t="s">
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+    </row>
+    <row r="3" spans="1:28" s="13" customFormat="1" ht="90.4" thickBot="1">
+      <c r="A3" s="19"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="N3" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="O3" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="P3" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="R3" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="S3" s="12" t="s">
+      <c r="S3" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="T3" s="12" t="s">
+      <c r="T3" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="U3" s="12" t="s">
+      <c r="U3" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="V3" s="12"/>
-      <c r="W3" s="12"/>
-    </row>
-    <row r="4" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1" thickTop="1">
+      <c r="V3" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="11"/>
+      <c r="Z3" s="11"/>
+      <c r="AA3" s="11"/>
+      <c r="AB3" s="11"/>
+    </row>
+    <row r="4" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>228</v>
       </c>
       <c r="C4" s="1"/>
@@ -1843,12 +2047,17 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
-    </row>
-    <row r="5" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+    </row>
+    <row r="5" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>229</v>
       </c>
       <c r="C5" s="1"/>
@@ -1880,8 +2089,13 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
-    </row>
-    <row r="6" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+    </row>
+    <row r="6" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -1911,8 +2125,13 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
-    </row>
-    <row r="7" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+    </row>
+    <row r="7" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -1940,11 +2159,13 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
-      <c r="Y7" s="5"/>
-      <c r="Z7" s="5"/>
-      <c r="AA7" s="5"/>
-    </row>
-    <row r="8" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+    </row>
+    <row r="8" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -1972,11 +2193,13 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
-      <c r="Y8" s="5"/>
-      <c r="Z8" s="5"/>
-      <c r="AA8" s="5"/>
-    </row>
-    <row r="9" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="1"/>
+    </row>
+    <row r="9" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -2004,11 +2227,13 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
-      <c r="Y9" s="5"/>
-      <c r="Z9" s="5"/>
-      <c r="AA9" s="5"/>
-    </row>
-    <row r="10" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+    </row>
+    <row r="10" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -2036,11 +2261,13 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
-      <c r="Y10" s="5"/>
-      <c r="Z10" s="5"/>
-      <c r="AA10" s="5"/>
-    </row>
-    <row r="11" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
+    </row>
+    <row r="11" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -2070,11 +2297,13 @@
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
-      <c r="Y11" s="5"/>
-      <c r="Z11" s="5"/>
-      <c r="AA11" s="5"/>
-    </row>
-    <row r="12" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+    </row>
+    <row r="12" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -2102,11 +2331,13 @@
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="5"/>
-      <c r="AA12" s="5"/>
-    </row>
-    <row r="13" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1"/>
+    </row>
+    <row r="13" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -2134,8 +2365,13 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
-    </row>
-    <row r="14" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="1"/>
+    </row>
+    <row r="14" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -2163,8 +2399,13 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
-    </row>
-    <row r="15" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1"/>
+    </row>
+    <row r="15" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -2192,8 +2433,13 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
-    </row>
-    <row r="16" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="1"/>
+    </row>
+    <row r="16" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -2221,8 +2467,13 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
-    </row>
-    <row r="17" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X16" s="1"/>
+      <c r="Y16" s="1"/>
+      <c r="Z16" s="1"/>
+      <c r="AA16" s="1"/>
+      <c r="AB16" s="1"/>
+    </row>
+    <row r="17" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -2250,8 +2501,13 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
-    </row>
-    <row r="18" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X17" s="1"/>
+      <c r="Y17" s="1"/>
+      <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
+      <c r="AB17" s="1"/>
+    </row>
+    <row r="18" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -2279,8 +2535,13 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
-    </row>
-    <row r="19" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1"/>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1"/>
+    </row>
+    <row r="19" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -2308,8 +2569,13 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
-    </row>
-    <row r="20" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="1"/>
+    </row>
+    <row r="20" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -2337,8 +2603,13 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
-    </row>
-    <row r="21" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1"/>
+      <c r="AA20" s="1"/>
+      <c r="AB20" s="1"/>
+    </row>
+    <row r="21" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -2366,8 +2637,13 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
-    </row>
-    <row r="22" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X21" s="1"/>
+      <c r="Y21" s="1"/>
+      <c r="Z21" s="1"/>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="1"/>
+    </row>
+    <row r="22" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -2397,8 +2673,13 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
-    </row>
-    <row r="23" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X22" s="1"/>
+      <c r="Y22" s="1"/>
+      <c r="Z22" s="1"/>
+      <c r="AA22" s="1"/>
+      <c r="AB22" s="1"/>
+    </row>
+    <row r="23" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -2426,8 +2707,13 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
-    </row>
-    <row r="24" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X23" s="1"/>
+      <c r="Y23" s="1"/>
+      <c r="Z23" s="1"/>
+      <c r="AA23" s="1"/>
+      <c r="AB23" s="1"/>
+    </row>
+    <row r="24" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -2455,8 +2741,13 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
-    </row>
-    <row r="25" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X24" s="1"/>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
+    </row>
+    <row r="25" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -2484,8 +2775,13 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
-    </row>
-    <row r="26" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
+      <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1"/>
+    </row>
+    <row r="26" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -2513,8 +2809,13 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
-    </row>
-    <row r="27" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
+    </row>
+    <row r="27" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -2544,8 +2845,13 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
-    </row>
-    <row r="28" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X27" s="1"/>
+      <c r="Y27" s="1"/>
+      <c r="Z27" s="1"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1"/>
+    </row>
+    <row r="28" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -2573,8 +2879,13 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
-    </row>
-    <row r="29" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
+    </row>
+    <row r="29" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -2602,8 +2913,13 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
-    </row>
-    <row r="30" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X29" s="1"/>
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
+    </row>
+    <row r="30" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -2631,8 +2947,13 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
-    </row>
-    <row r="31" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1"/>
+      <c r="AA30" s="1"/>
+      <c r="AB30" s="1"/>
+    </row>
+    <row r="31" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -2666,8 +2987,13 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
-    </row>
-    <row r="32" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+    </row>
+    <row r="32" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -2697,8 +3023,13 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
-    </row>
-    <row r="33" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
+      <c r="AB32" s="1"/>
+    </row>
+    <row r="33" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -2726,8 +3057,13 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
-    </row>
-    <row r="34" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
+      <c r="AB33" s="1"/>
+    </row>
+    <row r="34" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -2755,8 +3091,13 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
-    </row>
-    <row r="35" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1"/>
+      <c r="Z34" s="1"/>
+      <c r="AA34" s="1"/>
+      <c r="AB34" s="1"/>
+    </row>
+    <row r="35" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -2784,8 +3125,13 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
-    </row>
-    <row r="36" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X35" s="1"/>
+      <c r="Y35" s="1"/>
+      <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
+      <c r="AB35" s="1"/>
+    </row>
+    <row r="36" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -2813,8 +3159,13 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
-    </row>
-    <row r="37" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
+      <c r="AB36" s="1"/>
+    </row>
+    <row r="37" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -2842,8 +3193,13 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
-    </row>
-    <row r="38" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X37" s="1"/>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="1"/>
+      <c r="AA37" s="1"/>
+      <c r="AB37" s="1"/>
+    </row>
+    <row r="38" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -2871,8 +3227,13 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
-    </row>
-    <row r="39" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1"/>
+      <c r="Z38" s="1"/>
+      <c r="AA38" s="1"/>
+      <c r="AB38" s="1"/>
+    </row>
+    <row r="39" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -2900,8 +3261,13 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
-    </row>
-    <row r="40" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1"/>
+      <c r="AA39" s="1"/>
+      <c r="AB39" s="1"/>
+    </row>
+    <row r="40" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -2929,8 +3295,13 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
-    </row>
-    <row r="41" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1"/>
+      <c r="Z40" s="1"/>
+      <c r="AA40" s="1"/>
+      <c r="AB40" s="1"/>
+    </row>
+    <row r="41" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -2958,8 +3329,13 @@
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
-    </row>
-    <row r="42" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X41" s="1"/>
+      <c r="Y41" s="1"/>
+      <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
+      <c r="AB41" s="1"/>
+    </row>
+    <row r="42" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -2987,8 +3363,13 @@
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
-    </row>
-    <row r="43" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1"/>
+      <c r="Z42" s="1"/>
+      <c r="AA42" s="1"/>
+      <c r="AB42" s="1"/>
+    </row>
+    <row r="43" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -3016,8 +3397,13 @@
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
-    </row>
-    <row r="44" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X43" s="1"/>
+      <c r="Y43" s="1"/>
+      <c r="Z43" s="1"/>
+      <c r="AA43" s="1"/>
+      <c r="AB43" s="1"/>
+    </row>
+    <row r="44" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -3045,8 +3431,13 @@
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
-    </row>
-    <row r="45" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X44" s="1"/>
+      <c r="Y44" s="1"/>
+      <c r="Z44" s="1"/>
+      <c r="AA44" s="1"/>
+      <c r="AB44" s="1"/>
+    </row>
+    <row r="45" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -3074,8 +3465,13 @@
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
-    </row>
-    <row r="46" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X45" s="1"/>
+      <c r="Y45" s="1"/>
+      <c r="Z45" s="1"/>
+      <c r="AA45" s="1"/>
+      <c r="AB45" s="1"/>
+    </row>
+    <row r="46" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -3103,8 +3499,13 @@
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
       <c r="W46" s="1"/>
-    </row>
-    <row r="47" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X46" s="1"/>
+      <c r="Y46" s="1"/>
+      <c r="Z46" s="1"/>
+      <c r="AA46" s="1"/>
+      <c r="AB46" s="1"/>
+    </row>
+    <row r="47" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -3132,8 +3533,13 @@
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
       <c r="W47" s="1"/>
-    </row>
-    <row r="48" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X47" s="1"/>
+      <c r="Y47" s="1"/>
+      <c r="Z47" s="1"/>
+      <c r="AA47" s="1"/>
+      <c r="AB47" s="1"/>
+    </row>
+    <row r="48" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -3161,8 +3567,13 @@
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
-    </row>
-    <row r="49" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X48" s="1"/>
+      <c r="Y48" s="1"/>
+      <c r="Z48" s="1"/>
+      <c r="AA48" s="1"/>
+      <c r="AB48" s="1"/>
+    </row>
+    <row r="49" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -3190,8 +3601,13 @@
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
       <c r="W49" s="1"/>
-    </row>
-    <row r="50" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X49" s="1"/>
+      <c r="Y49" s="1"/>
+      <c r="Z49" s="1"/>
+      <c r="AA49" s="1"/>
+      <c r="AB49" s="1"/>
+    </row>
+    <row r="50" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -3219,8 +3635,13 @@
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
-    </row>
-    <row r="51" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X50" s="1"/>
+      <c r="Y50" s="1"/>
+      <c r="Z50" s="1"/>
+      <c r="AA50" s="1"/>
+      <c r="AB50" s="1"/>
+    </row>
+    <row r="51" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -3248,8 +3669,13 @@
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
       <c r="W51" s="1"/>
-    </row>
-    <row r="52" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1"/>
+      <c r="Z51" s="1"/>
+      <c r="AA51" s="1"/>
+      <c r="AB51" s="1"/>
+    </row>
+    <row r="52" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -3277,8 +3703,13 @@
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
       <c r="W52" s="1"/>
-    </row>
-    <row r="53" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X52" s="1"/>
+      <c r="Y52" s="1"/>
+      <c r="Z52" s="1"/>
+      <c r="AA52" s="1"/>
+      <c r="AB52" s="1"/>
+    </row>
+    <row r="53" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -3306,8 +3737,13 @@
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
       <c r="W53" s="1"/>
-    </row>
-    <row r="54" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X53" s="1"/>
+      <c r="Y53" s="1"/>
+      <c r="Z53" s="1"/>
+      <c r="AA53" s="1"/>
+      <c r="AB53" s="1"/>
+    </row>
+    <row r="54" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A54" s="3">
         <v>51</v>
       </c>
@@ -3335,8 +3771,13 @@
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
-    </row>
-    <row r="55" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X54" s="1"/>
+      <c r="Y54" s="1"/>
+      <c r="Z54" s="1"/>
+      <c r="AA54" s="1"/>
+      <c r="AB54" s="1"/>
+    </row>
+    <row r="55" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -3364,8 +3805,13 @@
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
       <c r="W55" s="1"/>
-    </row>
-    <row r="56" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X55" s="1"/>
+      <c r="Y55" s="1"/>
+      <c r="Z55" s="1"/>
+      <c r="AA55" s="1"/>
+      <c r="AB55" s="1"/>
+    </row>
+    <row r="56" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -3393,8 +3839,13 @@
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
       <c r="W56" s="1"/>
-    </row>
-    <row r="57" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X56" s="1"/>
+      <c r="Y56" s="1"/>
+      <c r="Z56" s="1"/>
+      <c r="AA56" s="1"/>
+      <c r="AB56" s="1"/>
+    </row>
+    <row r="57" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -3422,8 +3873,13 @@
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
       <c r="W57" s="1"/>
-    </row>
-    <row r="58" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X57" s="1"/>
+      <c r="Y57" s="1"/>
+      <c r="Z57" s="1"/>
+      <c r="AA57" s="1"/>
+      <c r="AB57" s="1"/>
+    </row>
+    <row r="58" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -3451,8 +3907,13 @@
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
       <c r="W58" s="1"/>
-    </row>
-    <row r="59" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X58" s="1"/>
+      <c r="Y58" s="1"/>
+      <c r="Z58" s="1"/>
+      <c r="AA58" s="1"/>
+      <c r="AB58" s="1"/>
+    </row>
+    <row r="59" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -3480,8 +3941,13 @@
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
       <c r="W59" s="1"/>
-    </row>
-    <row r="60" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X59" s="1"/>
+      <c r="Y59" s="1"/>
+      <c r="Z59" s="1"/>
+      <c r="AA59" s="1"/>
+      <c r="AB59" s="1"/>
+    </row>
+    <row r="60" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -3509,8 +3975,13 @@
       <c r="U60" s="1"/>
       <c r="V60" s="1"/>
       <c r="W60" s="1"/>
-    </row>
-    <row r="61" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X60" s="1"/>
+      <c r="Y60" s="1"/>
+      <c r="Z60" s="1"/>
+      <c r="AA60" s="1"/>
+      <c r="AB60" s="1"/>
+    </row>
+    <row r="61" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -3538,8 +4009,13 @@
       <c r="U61" s="1"/>
       <c r="V61" s="1"/>
       <c r="W61" s="1"/>
-    </row>
-    <row r="62" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X61" s="1"/>
+      <c r="Y61" s="1"/>
+      <c r="Z61" s="1"/>
+      <c r="AA61" s="1"/>
+      <c r="AB61" s="1"/>
+    </row>
+    <row r="62" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -3567,8 +4043,13 @@
       <c r="U62" s="1"/>
       <c r="V62" s="1"/>
       <c r="W62" s="1"/>
-    </row>
-    <row r="63" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X62" s="1"/>
+      <c r="Y62" s="1"/>
+      <c r="Z62" s="1"/>
+      <c r="AA62" s="1"/>
+      <c r="AB62" s="1"/>
+    </row>
+    <row r="63" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A63" s="3">
         <v>60</v>
       </c>
@@ -3598,8 +4079,13 @@
       <c r="U63" s="1"/>
       <c r="V63" s="1"/>
       <c r="W63" s="1"/>
-    </row>
-    <row r="64" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X63" s="1"/>
+      <c r="Y63" s="1"/>
+      <c r="Z63" s="1"/>
+      <c r="AA63" s="1"/>
+      <c r="AB63" s="1"/>
+    </row>
+    <row r="64" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A64" s="3">
         <v>61</v>
       </c>
@@ -3629,8 +4115,13 @@
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
       <c r="W64" s="1"/>
-    </row>
-    <row r="65" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X64" s="1"/>
+      <c r="Y64" s="1"/>
+      <c r="Z64" s="1"/>
+      <c r="AA64" s="1"/>
+      <c r="AB64" s="1"/>
+    </row>
+    <row r="65" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A65" s="3">
         <v>62</v>
       </c>
@@ -3658,8 +4149,13 @@
       <c r="U65" s="1"/>
       <c r="V65" s="1"/>
       <c r="W65" s="1"/>
-    </row>
-    <row r="66" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X65" s="1"/>
+      <c r="Y65" s="1"/>
+      <c r="Z65" s="1"/>
+      <c r="AA65" s="1"/>
+      <c r="AB65" s="1"/>
+    </row>
+    <row r="66" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A66" s="3">
         <v>63</v>
       </c>
@@ -3687,8 +4183,13 @@
       <c r="U66" s="1"/>
       <c r="V66" s="1"/>
       <c r="W66" s="1"/>
-    </row>
-    <row r="67" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X66" s="1"/>
+      <c r="Y66" s="1"/>
+      <c r="Z66" s="1"/>
+      <c r="AA66" s="1"/>
+      <c r="AB66" s="1"/>
+    </row>
+    <row r="67" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A67" s="3">
         <v>64</v>
       </c>
@@ -3718,8 +4219,13 @@
       <c r="U67" s="1"/>
       <c r="V67" s="1"/>
       <c r="W67" s="1"/>
-    </row>
-    <row r="68" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X67" s="1"/>
+      <c r="Y67" s="1"/>
+      <c r="Z67" s="1"/>
+      <c r="AA67" s="1"/>
+      <c r="AB67" s="1"/>
+    </row>
+    <row r="68" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A68" s="3">
         <v>65</v>
       </c>
@@ -3749,8 +4255,13 @@
       <c r="U68" s="1"/>
       <c r="V68" s="1"/>
       <c r="W68" s="1"/>
-    </row>
-    <row r="69" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X68" s="1"/>
+      <c r="Y68" s="1"/>
+      <c r="Z68" s="1"/>
+      <c r="AA68" s="1"/>
+      <c r="AB68" s="1"/>
+    </row>
+    <row r="69" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A69" s="3">
         <v>66</v>
       </c>
@@ -3780,8 +4291,13 @@
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
       <c r="W69" s="1"/>
-    </row>
-    <row r="70" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X69" s="1"/>
+      <c r="Y69" s="1"/>
+      <c r="Z69" s="1"/>
+      <c r="AA69" s="1"/>
+      <c r="AB69" s="1"/>
+    </row>
+    <row r="70" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A70" s="3">
         <v>67</v>
       </c>
@@ -3811,8 +4327,13 @@
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
       <c r="W70" s="1"/>
-    </row>
-    <row r="71" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X70" s="1"/>
+      <c r="Y70" s="1"/>
+      <c r="Z70" s="1"/>
+      <c r="AA70" s="1"/>
+      <c r="AB70" s="1"/>
+    </row>
+    <row r="71" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A71" s="3">
         <v>68</v>
       </c>
@@ -3842,8 +4363,13 @@
       <c r="U71" s="1"/>
       <c r="V71" s="1"/>
       <c r="W71" s="1"/>
-    </row>
-    <row r="72" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X71" s="1"/>
+      <c r="Y71" s="1"/>
+      <c r="Z71" s="1"/>
+      <c r="AA71" s="1"/>
+      <c r="AB71" s="1"/>
+    </row>
+    <row r="72" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A72" s="3">
         <v>69</v>
       </c>
@@ -3871,8 +4397,13 @@
       <c r="U72" s="1"/>
       <c r="V72" s="1"/>
       <c r="W72" s="1"/>
-    </row>
-    <row r="73" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X72" s="1"/>
+      <c r="Y72" s="1"/>
+      <c r="Z72" s="1"/>
+      <c r="AA72" s="1"/>
+      <c r="AB72" s="1"/>
+    </row>
+    <row r="73" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A73" s="3">
         <v>70</v>
       </c>
@@ -3900,8 +4431,13 @@
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
       <c r="W73" s="1"/>
-    </row>
-    <row r="74" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X73" s="1"/>
+      <c r="Y73" s="1"/>
+      <c r="Z73" s="1"/>
+      <c r="AA73" s="1"/>
+      <c r="AB73" s="1"/>
+    </row>
+    <row r="74" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A74" s="3">
         <v>71</v>
       </c>
@@ -3929,8 +4465,13 @@
       <c r="U74" s="1"/>
       <c r="V74" s="1"/>
       <c r="W74" s="1"/>
-    </row>
-    <row r="75" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X74" s="1"/>
+      <c r="Y74" s="1"/>
+      <c r="Z74" s="1"/>
+      <c r="AA74" s="1"/>
+      <c r="AB74" s="1"/>
+    </row>
+    <row r="75" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A75" s="3">
         <v>72</v>
       </c>
@@ -3958,8 +4499,13 @@
       <c r="U75" s="1"/>
       <c r="V75" s="1"/>
       <c r="W75" s="1"/>
-    </row>
-    <row r="76" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X75" s="1"/>
+      <c r="Y75" s="1"/>
+      <c r="Z75" s="1"/>
+      <c r="AA75" s="1"/>
+      <c r="AB75" s="1"/>
+    </row>
+    <row r="76" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A76" s="3">
         <v>73</v>
       </c>
@@ -3991,8 +4537,13 @@
       <c r="U76" s="1"/>
       <c r="V76" s="1"/>
       <c r="W76" s="1"/>
-    </row>
-    <row r="77" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X76" s="1"/>
+      <c r="Y76" s="1"/>
+      <c r="Z76" s="1"/>
+      <c r="AA76" s="1"/>
+      <c r="AB76" s="1"/>
+    </row>
+    <row r="77" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A77" s="3">
         <v>74</v>
       </c>
@@ -4022,8 +4573,13 @@
       <c r="U77" s="1"/>
       <c r="V77" s="1"/>
       <c r="W77" s="1"/>
-    </row>
-    <row r="78" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X77" s="1"/>
+      <c r="Y77" s="1"/>
+      <c r="Z77" s="1"/>
+      <c r="AA77" s="1"/>
+      <c r="AB77" s="1"/>
+    </row>
+    <row r="78" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A78" s="3">
         <v>75</v>
       </c>
@@ -4053,8 +4609,13 @@
       <c r="U78" s="1"/>
       <c r="V78" s="1"/>
       <c r="W78" s="1"/>
-    </row>
-    <row r="79" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X78" s="1"/>
+      <c r="Y78" s="1"/>
+      <c r="Z78" s="1"/>
+      <c r="AA78" s="1"/>
+      <c r="AB78" s="1"/>
+    </row>
+    <row r="79" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A79" s="3">
         <v>76</v>
       </c>
@@ -4084,8 +4645,13 @@
       <c r="U79" s="1"/>
       <c r="V79" s="1"/>
       <c r="W79" s="1"/>
-    </row>
-    <row r="80" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X79" s="1"/>
+      <c r="Y79" s="1"/>
+      <c r="Z79" s="1"/>
+      <c r="AA79" s="1"/>
+      <c r="AB79" s="1"/>
+    </row>
+    <row r="80" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A80" s="3">
         <v>77</v>
       </c>
@@ -4115,8 +4681,13 @@
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
       <c r="W80" s="1"/>
-    </row>
-    <row r="81" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X80" s="1"/>
+      <c r="Y80" s="1"/>
+      <c r="Z80" s="1"/>
+      <c r="AA80" s="1"/>
+      <c r="AB80" s="1"/>
+    </row>
+    <row r="81" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A81" s="3">
         <v>78</v>
       </c>
@@ -4148,8 +4719,13 @@
       <c r="U81" s="1"/>
       <c r="V81" s="1"/>
       <c r="W81" s="1"/>
-    </row>
-    <row r="82" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X81" s="1"/>
+      <c r="Y81" s="1"/>
+      <c r="Z81" s="1"/>
+      <c r="AA81" s="1"/>
+      <c r="AB81" s="1"/>
+    </row>
+    <row r="82" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A82" s="3">
         <v>79</v>
       </c>
@@ -4181,8 +4757,13 @@
       <c r="U82" s="1"/>
       <c r="V82" s="1"/>
       <c r="W82" s="1"/>
-    </row>
-    <row r="83" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X82" s="1"/>
+      <c r="Y82" s="1"/>
+      <c r="Z82" s="1"/>
+      <c r="AA82" s="1"/>
+      <c r="AB82" s="1"/>
+    </row>
+    <row r="83" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A83" s="3">
         <v>80</v>
       </c>
@@ -4214,8 +4795,13 @@
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
       <c r="W83" s="1"/>
-    </row>
-    <row r="84" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X83" s="1"/>
+      <c r="Y83" s="1"/>
+      <c r="Z83" s="1"/>
+      <c r="AA83" s="1"/>
+      <c r="AB83" s="1"/>
+    </row>
+    <row r="84" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A84" s="3">
         <v>81</v>
       </c>
@@ -4245,8 +4831,13 @@
       <c r="U84" s="1"/>
       <c r="V84" s="1"/>
       <c r="W84" s="1"/>
-    </row>
-    <row r="85" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X84" s="1"/>
+      <c r="Y84" s="1"/>
+      <c r="Z84" s="1"/>
+      <c r="AA84" s="1"/>
+      <c r="AB84" s="1"/>
+    </row>
+    <row r="85" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A85" s="3">
         <v>82</v>
       </c>
@@ -4274,8 +4865,13 @@
       <c r="U85" s="1"/>
       <c r="V85" s="1"/>
       <c r="W85" s="1"/>
-    </row>
-    <row r="86" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X85" s="1"/>
+      <c r="Y85" s="1"/>
+      <c r="Z85" s="1"/>
+      <c r="AA85" s="1"/>
+      <c r="AB85" s="1"/>
+    </row>
+    <row r="86" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A86" s="3">
         <v>83</v>
       </c>
@@ -4303,8 +4899,13 @@
       <c r="U86" s="1"/>
       <c r="V86" s="1"/>
       <c r="W86" s="1"/>
-    </row>
-    <row r="87" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X86" s="1"/>
+      <c r="Y86" s="1"/>
+      <c r="Z86" s="1"/>
+      <c r="AA86" s="1"/>
+      <c r="AB86" s="1"/>
+    </row>
+    <row r="87" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A87" s="3">
         <v>84</v>
       </c>
@@ -4332,8 +4933,13 @@
       <c r="U87" s="1"/>
       <c r="V87" s="1"/>
       <c r="W87" s="1"/>
-    </row>
-    <row r="88" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X87" s="1"/>
+      <c r="Y87" s="1"/>
+      <c r="Z87" s="1"/>
+      <c r="AA87" s="1"/>
+      <c r="AB87" s="1"/>
+    </row>
+    <row r="88" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A88" s="3">
         <v>85</v>
       </c>
@@ -4363,8 +4969,13 @@
       <c r="U88" s="1"/>
       <c r="V88" s="1"/>
       <c r="W88" s="1"/>
-    </row>
-    <row r="89" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X88" s="1"/>
+      <c r="Y88" s="1"/>
+      <c r="Z88" s="1"/>
+      <c r="AA88" s="1"/>
+      <c r="AB88" s="1"/>
+    </row>
+    <row r="89" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A89" s="3">
         <v>86</v>
       </c>
@@ -4392,8 +5003,13 @@
       <c r="U89" s="1"/>
       <c r="V89" s="1"/>
       <c r="W89" s="1"/>
-    </row>
-    <row r="90" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X89" s="1"/>
+      <c r="Y89" s="1"/>
+      <c r="Z89" s="1"/>
+      <c r="AA89" s="1"/>
+      <c r="AB89" s="1"/>
+    </row>
+    <row r="90" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A90" s="3">
         <v>87</v>
       </c>
@@ -4421,8 +5037,13 @@
       <c r="U90" s="1"/>
       <c r="V90" s="1"/>
       <c r="W90" s="1"/>
-    </row>
-    <row r="91" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X90" s="1"/>
+      <c r="Y90" s="1"/>
+      <c r="Z90" s="1"/>
+      <c r="AA90" s="1"/>
+      <c r="AB90" s="1"/>
+    </row>
+    <row r="91" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A91" s="3">
         <v>88</v>
       </c>
@@ -4452,8 +5073,13 @@
       <c r="U91" s="1"/>
       <c r="V91" s="1"/>
       <c r="W91" s="1"/>
-    </row>
-    <row r="92" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X91" s="1"/>
+      <c r="Y91" s="1"/>
+      <c r="Z91" s="1"/>
+      <c r="AA91" s="1"/>
+      <c r="AB91" s="1"/>
+    </row>
+    <row r="92" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A92" s="3">
         <v>89</v>
       </c>
@@ -4483,8 +5109,13 @@
       <c r="U92" s="1"/>
       <c r="V92" s="1"/>
       <c r="W92" s="1"/>
-    </row>
-    <row r="93" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X92" s="1"/>
+      <c r="Y92" s="1"/>
+      <c r="Z92" s="1"/>
+      <c r="AA92" s="1"/>
+      <c r="AB92" s="1"/>
+    </row>
+    <row r="93" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A93" s="3">
         <v>90</v>
       </c>
@@ -4512,8 +5143,13 @@
       <c r="U93" s="1"/>
       <c r="V93" s="1"/>
       <c r="W93" s="1"/>
-    </row>
-    <row r="94" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X93" s="1"/>
+      <c r="Y93" s="1"/>
+      <c r="Z93" s="1"/>
+      <c r="AA93" s="1"/>
+      <c r="AB93" s="1"/>
+    </row>
+    <row r="94" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A94" s="3">
         <v>91</v>
       </c>
@@ -4541,8 +5177,13 @@
       <c r="U94" s="1"/>
       <c r="V94" s="1"/>
       <c r="W94" s="1"/>
-    </row>
-    <row r="95" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X94" s="1"/>
+      <c r="Y94" s="1"/>
+      <c r="Z94" s="1"/>
+      <c r="AA94" s="1"/>
+      <c r="AB94" s="1"/>
+    </row>
+    <row r="95" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A95" s="3">
         <v>92</v>
       </c>
@@ -4570,8 +5211,13 @@
       <c r="U95" s="1"/>
       <c r="V95" s="1"/>
       <c r="W95" s="1"/>
-    </row>
-    <row r="96" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X95" s="1"/>
+      <c r="Y95" s="1"/>
+      <c r="Z95" s="1"/>
+      <c r="AA95" s="1"/>
+      <c r="AB95" s="1"/>
+    </row>
+    <row r="96" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A96" s="3">
         <v>93</v>
       </c>
@@ -4599,8 +5245,13 @@
       <c r="U96" s="1"/>
       <c r="V96" s="1"/>
       <c r="W96" s="1"/>
-    </row>
-    <row r="97" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X96" s="1"/>
+      <c r="Y96" s="1"/>
+      <c r="Z96" s="1"/>
+      <c r="AA96" s="1"/>
+      <c r="AB96" s="1"/>
+    </row>
+    <row r="97" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A97" s="3">
         <v>94</v>
       </c>
@@ -4628,8 +5279,13 @@
       <c r="U97" s="1"/>
       <c r="V97" s="1"/>
       <c r="W97" s="1"/>
-    </row>
-    <row r="98" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X97" s="1"/>
+      <c r="Y97" s="1"/>
+      <c r="Z97" s="1"/>
+      <c r="AA97" s="1"/>
+      <c r="AB97" s="1"/>
+    </row>
+    <row r="98" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A98" s="3">
         <v>95</v>
       </c>
@@ -4659,8 +5315,13 @@
       <c r="U98" s="1"/>
       <c r="V98" s="1"/>
       <c r="W98" s="1"/>
-    </row>
-    <row r="99" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X98" s="1"/>
+      <c r="Y98" s="1"/>
+      <c r="Z98" s="1"/>
+      <c r="AA98" s="1"/>
+      <c r="AB98" s="1"/>
+    </row>
+    <row r="99" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A99" s="3">
         <v>96</v>
       </c>
@@ -4688,8 +5349,13 @@
       <c r="U99" s="1"/>
       <c r="V99" s="1"/>
       <c r="W99" s="1"/>
-    </row>
-    <row r="100" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X99" s="1"/>
+      <c r="Y99" s="1"/>
+      <c r="Z99" s="1"/>
+      <c r="AA99" s="1"/>
+      <c r="AB99" s="1"/>
+    </row>
+    <row r="100" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A100" s="3">
         <v>97</v>
       </c>
@@ -4717,8 +5383,13 @@
       <c r="U100" s="1"/>
       <c r="V100" s="1"/>
       <c r="W100" s="1"/>
-    </row>
-    <row r="101" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X100" s="1"/>
+      <c r="Y100" s="1"/>
+      <c r="Z100" s="1"/>
+      <c r="AA100" s="1"/>
+      <c r="AB100" s="1"/>
+    </row>
+    <row r="101" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A101" s="3">
         <v>98</v>
       </c>
@@ -4746,8 +5417,13 @@
       <c r="U101" s="1"/>
       <c r="V101" s="1"/>
       <c r="W101" s="1"/>
-    </row>
-    <row r="102" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X101" s="1"/>
+      <c r="Y101" s="1"/>
+      <c r="Z101" s="1"/>
+      <c r="AA101" s="1"/>
+      <c r="AB101" s="1"/>
+    </row>
+    <row r="102" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A102" s="3">
         <v>99</v>
       </c>
@@ -4775,8 +5451,13 @@
       <c r="U102" s="1"/>
       <c r="V102" s="1"/>
       <c r="W102" s="1"/>
-    </row>
-    <row r="103" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X102" s="1"/>
+      <c r="Y102" s="1"/>
+      <c r="Z102" s="1"/>
+      <c r="AA102" s="1"/>
+      <c r="AB102" s="1"/>
+    </row>
+    <row r="103" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A103" s="3">
         <v>100</v>
       </c>
@@ -4804,8 +5485,13 @@
       <c r="U103" s="1"/>
       <c r="V103" s="1"/>
       <c r="W103" s="1"/>
-    </row>
-    <row r="104" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X103" s="1"/>
+      <c r="Y103" s="1"/>
+      <c r="Z103" s="1"/>
+      <c r="AA103" s="1"/>
+      <c r="AB103" s="1"/>
+    </row>
+    <row r="104" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A104" s="3">
         <v>101</v>
       </c>
@@ -4833,8 +5519,13 @@
       <c r="U104" s="1"/>
       <c r="V104" s="1"/>
       <c r="W104" s="1"/>
-    </row>
-    <row r="105" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X104" s="1"/>
+      <c r="Y104" s="1"/>
+      <c r="Z104" s="1"/>
+      <c r="AA104" s="1"/>
+      <c r="AB104" s="1"/>
+    </row>
+    <row r="105" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A105" s="3">
         <v>102</v>
       </c>
@@ -4862,8 +5553,13 @@
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
       <c r="W105" s="1"/>
-    </row>
-    <row r="106" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X105" s="1"/>
+      <c r="Y105" s="1"/>
+      <c r="Z105" s="1"/>
+      <c r="AA105" s="1"/>
+      <c r="AB105" s="1"/>
+    </row>
+    <row r="106" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A106" s="3">
         <v>103</v>
       </c>
@@ -4891,8 +5587,13 @@
       <c r="U106" s="1"/>
       <c r="V106" s="1"/>
       <c r="W106" s="1"/>
-    </row>
-    <row r="107" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X106" s="1"/>
+      <c r="Y106" s="1"/>
+      <c r="Z106" s="1"/>
+      <c r="AA106" s="1"/>
+      <c r="AB106" s="1"/>
+    </row>
+    <row r="107" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A107" s="3">
         <v>104</v>
       </c>
@@ -4920,8 +5621,13 @@
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
       <c r="W107" s="1"/>
-    </row>
-    <row r="108" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X107" s="1"/>
+      <c r="Y107" s="1"/>
+      <c r="Z107" s="1"/>
+      <c r="AA107" s="1"/>
+      <c r="AB107" s="1"/>
+    </row>
+    <row r="108" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A108" s="3">
         <v>105</v>
       </c>
@@ -4949,8 +5655,13 @@
       <c r="U108" s="1"/>
       <c r="V108" s="1"/>
       <c r="W108" s="1"/>
-    </row>
-    <row r="109" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X108" s="1"/>
+      <c r="Y108" s="1"/>
+      <c r="Z108" s="1"/>
+      <c r="AA108" s="1"/>
+      <c r="AB108" s="1"/>
+    </row>
+    <row r="109" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A109" s="3">
         <v>106</v>
       </c>
@@ -4978,8 +5689,13 @@
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
       <c r="W109" s="1"/>
-    </row>
-    <row r="110" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X109" s="1"/>
+      <c r="Y109" s="1"/>
+      <c r="Z109" s="1"/>
+      <c r="AA109" s="1"/>
+      <c r="AB109" s="1"/>
+    </row>
+    <row r="110" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A110" s="3">
         <v>107</v>
       </c>
@@ -5007,8 +5723,13 @@
       <c r="U110" s="1"/>
       <c r="V110" s="1"/>
       <c r="W110" s="1"/>
-    </row>
-    <row r="111" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X110" s="1"/>
+      <c r="Y110" s="1"/>
+      <c r="Z110" s="1"/>
+      <c r="AA110" s="1"/>
+      <c r="AB110" s="1"/>
+    </row>
+    <row r="111" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A111" s="3">
         <v>108</v>
       </c>
@@ -5036,8 +5757,13 @@
       <c r="U111" s="1"/>
       <c r="V111" s="1"/>
       <c r="W111" s="1"/>
-    </row>
-    <row r="112" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X111" s="1"/>
+      <c r="Y111" s="1"/>
+      <c r="Z111" s="1"/>
+      <c r="AA111" s="1"/>
+      <c r="AB111" s="1"/>
+    </row>
+    <row r="112" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A112" s="3">
         <v>109</v>
       </c>
@@ -5069,8 +5795,13 @@
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
       <c r="W112" s="1"/>
-    </row>
-    <row r="113" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X112" s="1"/>
+      <c r="Y112" s="1"/>
+      <c r="Z112" s="1"/>
+      <c r="AA112" s="1"/>
+      <c r="AB112" s="1"/>
+    </row>
+    <row r="113" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A113" s="3">
         <v>110</v>
       </c>
@@ -5100,8 +5831,13 @@
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
       <c r="W113" s="1"/>
-    </row>
-    <row r="114" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X113" s="1"/>
+      <c r="Y113" s="1"/>
+      <c r="Z113" s="1"/>
+      <c r="AA113" s="1"/>
+      <c r="AB113" s="1"/>
+    </row>
+    <row r="114" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A114" s="3">
         <v>111</v>
       </c>
@@ -5129,8 +5865,13 @@
       <c r="U114" s="1"/>
       <c r="V114" s="1"/>
       <c r="W114" s="1"/>
-    </row>
-    <row r="115" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X114" s="1"/>
+      <c r="Y114" s="1"/>
+      <c r="Z114" s="1"/>
+      <c r="AA114" s="1"/>
+      <c r="AB114" s="1"/>
+    </row>
+    <row r="115" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A115" s="3">
         <v>112</v>
       </c>
@@ -5160,8 +5901,13 @@
       <c r="U115" s="1"/>
       <c r="V115" s="1"/>
       <c r="W115" s="1"/>
-    </row>
-    <row r="116" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X115" s="1"/>
+      <c r="Y115" s="1"/>
+      <c r="Z115" s="1"/>
+      <c r="AA115" s="1"/>
+      <c r="AB115" s="1"/>
+    </row>
+    <row r="116" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A116" s="3">
         <v>113</v>
       </c>
@@ -5189,8 +5935,13 @@
       <c r="U116" s="1"/>
       <c r="V116" s="1"/>
       <c r="W116" s="1"/>
-    </row>
-    <row r="117" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X116" s="1"/>
+      <c r="Y116" s="1"/>
+      <c r="Z116" s="1"/>
+      <c r="AA116" s="1"/>
+      <c r="AB116" s="1"/>
+    </row>
+    <row r="117" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A117" s="3">
         <v>114</v>
       </c>
@@ -5218,8 +5969,13 @@
       <c r="U117" s="1"/>
       <c r="V117" s="1"/>
       <c r="W117" s="1"/>
-    </row>
-    <row r="118" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X117" s="1"/>
+      <c r="Y117" s="1"/>
+      <c r="Z117" s="1"/>
+      <c r="AA117" s="1"/>
+      <c r="AB117" s="1"/>
+    </row>
+    <row r="118" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A118" s="3">
         <v>115</v>
       </c>
@@ -5247,8 +6003,13 @@
       <c r="U118" s="1"/>
       <c r="V118" s="1"/>
       <c r="W118" s="1"/>
-    </row>
-    <row r="119" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X118" s="1"/>
+      <c r="Y118" s="1"/>
+      <c r="Z118" s="1"/>
+      <c r="AA118" s="1"/>
+      <c r="AB118" s="1"/>
+    </row>
+    <row r="119" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A119" s="3">
         <v>116</v>
       </c>
@@ -5276,8 +6037,13 @@
       <c r="U119" s="1"/>
       <c r="V119" s="1"/>
       <c r="W119" s="1"/>
-    </row>
-    <row r="120" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X119" s="1"/>
+      <c r="Y119" s="1"/>
+      <c r="Z119" s="1"/>
+      <c r="AA119" s="1"/>
+      <c r="AB119" s="1"/>
+    </row>
+    <row r="120" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A120" s="3">
         <v>117</v>
       </c>
@@ -5305,8 +6071,13 @@
       <c r="U120" s="1"/>
       <c r="V120" s="1"/>
       <c r="W120" s="1"/>
-    </row>
-    <row r="121" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X120" s="1"/>
+      <c r="Y120" s="1"/>
+      <c r="Z120" s="1"/>
+      <c r="AA120" s="1"/>
+      <c r="AB120" s="1"/>
+    </row>
+    <row r="121" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A121" s="3">
         <v>118</v>
       </c>
@@ -5334,8 +6105,13 @@
       <c r="U121" s="1"/>
       <c r="V121" s="1"/>
       <c r="W121" s="1"/>
-    </row>
-    <row r="122" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X121" s="1"/>
+      <c r="Y121" s="1"/>
+      <c r="Z121" s="1"/>
+      <c r="AA121" s="1"/>
+      <c r="AB121" s="1"/>
+    </row>
+    <row r="122" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A122" s="3">
         <v>119</v>
       </c>
@@ -5363,8 +6139,13 @@
       <c r="U122" s="1"/>
       <c r="V122" s="1"/>
       <c r="W122" s="1"/>
-    </row>
-    <row r="123" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X122" s="1"/>
+      <c r="Y122" s="1"/>
+      <c r="Z122" s="1"/>
+      <c r="AA122" s="1"/>
+      <c r="AB122" s="1"/>
+    </row>
+    <row r="123" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A123" s="3">
         <v>120</v>
       </c>
@@ -5392,8 +6173,13 @@
       <c r="U123" s="1"/>
       <c r="V123" s="1"/>
       <c r="W123" s="1"/>
-    </row>
-    <row r="124" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X123" s="1"/>
+      <c r="Y123" s="1"/>
+      <c r="Z123" s="1"/>
+      <c r="AA123" s="1"/>
+      <c r="AB123" s="1"/>
+    </row>
+    <row r="124" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A124" s="3">
         <v>121</v>
       </c>
@@ -5421,8 +6207,13 @@
       <c r="U124" s="1"/>
       <c r="V124" s="1"/>
       <c r="W124" s="1"/>
-    </row>
-    <row r="125" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X124" s="1"/>
+      <c r="Y124" s="1"/>
+      <c r="Z124" s="1"/>
+      <c r="AA124" s="1"/>
+      <c r="AB124" s="1"/>
+    </row>
+    <row r="125" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A125" s="3">
         <v>122</v>
       </c>
@@ -5450,8 +6241,13 @@
       <c r="U125" s="1"/>
       <c r="V125" s="1"/>
       <c r="W125" s="1"/>
-    </row>
-    <row r="126" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X125" s="1"/>
+      <c r="Y125" s="1"/>
+      <c r="Z125" s="1"/>
+      <c r="AA125" s="1"/>
+      <c r="AB125" s="1"/>
+    </row>
+    <row r="126" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A126" s="3">
         <v>123</v>
       </c>
@@ -5481,8 +6277,13 @@
       <c r="U126" s="1"/>
       <c r="V126" s="1"/>
       <c r="W126" s="1"/>
-    </row>
-    <row r="127" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X126" s="1"/>
+      <c r="Y126" s="1"/>
+      <c r="Z126" s="1"/>
+      <c r="AA126" s="1"/>
+      <c r="AB126" s="1"/>
+    </row>
+    <row r="127" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A127" s="3">
         <v>124</v>
       </c>
@@ -5510,8 +6311,13 @@
       <c r="U127" s="1"/>
       <c r="V127" s="1"/>
       <c r="W127" s="1"/>
-    </row>
-    <row r="128" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X127" s="1"/>
+      <c r="Y127" s="1"/>
+      <c r="Z127" s="1"/>
+      <c r="AA127" s="1"/>
+      <c r="AB127" s="1"/>
+    </row>
+    <row r="128" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A128" s="3">
         <v>125</v>
       </c>
@@ -5541,8 +6347,13 @@
       <c r="U128" s="1"/>
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
-    </row>
-    <row r="129" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X128" s="1"/>
+      <c r="Y128" s="1"/>
+      <c r="Z128" s="1"/>
+      <c r="AA128" s="1"/>
+      <c r="AB128" s="1"/>
+    </row>
+    <row r="129" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A129" s="3">
         <v>126</v>
       </c>
@@ -5570,8 +6381,13 @@
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
       <c r="W129" s="1"/>
-    </row>
-    <row r="130" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X129" s="1"/>
+      <c r="Y129" s="1"/>
+      <c r="Z129" s="1"/>
+      <c r="AA129" s="1"/>
+      <c r="AB129" s="1"/>
+    </row>
+    <row r="130" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A130" s="3">
         <v>127</v>
       </c>
@@ -5601,8 +6417,13 @@
       <c r="U130" s="1"/>
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
-    </row>
-    <row r="131" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X130" s="1"/>
+      <c r="Y130" s="1"/>
+      <c r="Z130" s="1"/>
+      <c r="AA130" s="1"/>
+      <c r="AB130" s="1"/>
+    </row>
+    <row r="131" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A131" s="3">
         <v>128</v>
       </c>
@@ -5630,8 +6451,13 @@
       <c r="U131" s="1"/>
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
-    </row>
-    <row r="132" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X131" s="1"/>
+      <c r="Y131" s="1"/>
+      <c r="Z131" s="1"/>
+      <c r="AA131" s="1"/>
+      <c r="AB131" s="1"/>
+    </row>
+    <row r="132" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A132" s="3">
         <v>129</v>
       </c>
@@ -5659,8 +6485,13 @@
       <c r="U132" s="1"/>
       <c r="V132" s="1"/>
       <c r="W132" s="1"/>
-    </row>
-    <row r="133" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X132" s="1"/>
+      <c r="Y132" s="1"/>
+      <c r="Z132" s="1"/>
+      <c r="AA132" s="1"/>
+      <c r="AB132" s="1"/>
+    </row>
+    <row r="133" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A133" s="3">
         <v>130</v>
       </c>
@@ -5688,8 +6519,13 @@
       <c r="U133" s="1"/>
       <c r="V133" s="1"/>
       <c r="W133" s="1"/>
-    </row>
-    <row r="134" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X133" s="1"/>
+      <c r="Y133" s="1"/>
+      <c r="Z133" s="1"/>
+      <c r="AA133" s="1"/>
+      <c r="AB133" s="1"/>
+    </row>
+    <row r="134" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A134" s="3">
         <v>131</v>
       </c>
@@ -5717,8 +6553,13 @@
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
       <c r="W134" s="1"/>
-    </row>
-    <row r="135" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X134" s="1"/>
+      <c r="Y134" s="1"/>
+      <c r="Z134" s="1"/>
+      <c r="AA134" s="1"/>
+      <c r="AB134" s="1"/>
+    </row>
+    <row r="135" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A135" s="3">
         <v>132</v>
       </c>
@@ -5746,8 +6587,13 @@
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
       <c r="W135" s="1"/>
-    </row>
-    <row r="136" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X135" s="1"/>
+      <c r="Y135" s="1"/>
+      <c r="Z135" s="1"/>
+      <c r="AA135" s="1"/>
+      <c r="AB135" s="1"/>
+    </row>
+    <row r="136" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A136" s="3">
         <v>133</v>
       </c>
@@ -5775,8 +6621,13 @@
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
       <c r="W136" s="1"/>
-    </row>
-    <row r="137" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X136" s="1"/>
+      <c r="Y136" s="1"/>
+      <c r="Z136" s="1"/>
+      <c r="AA136" s="1"/>
+      <c r="AB136" s="1"/>
+    </row>
+    <row r="137" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A137" s="3">
         <v>134</v>
       </c>
@@ -5804,8 +6655,13 @@
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
       <c r="W137" s="1"/>
-    </row>
-    <row r="138" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X137" s="1"/>
+      <c r="Y137" s="1"/>
+      <c r="Z137" s="1"/>
+      <c r="AA137" s="1"/>
+      <c r="AB137" s="1"/>
+    </row>
+    <row r="138" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A138" s="3">
         <v>135</v>
       </c>
@@ -5833,8 +6689,13 @@
       <c r="U138" s="1"/>
       <c r="V138" s="1"/>
       <c r="W138" s="1"/>
-    </row>
-    <row r="139" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X138" s="1"/>
+      <c r="Y138" s="1"/>
+      <c r="Z138" s="1"/>
+      <c r="AA138" s="1"/>
+      <c r="AB138" s="1"/>
+    </row>
+    <row r="139" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A139" s="3">
         <v>136</v>
       </c>
@@ -5862,8 +6723,13 @@
       <c r="U139" s="1"/>
       <c r="V139" s="1"/>
       <c r="W139" s="1"/>
-    </row>
-    <row r="140" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X139" s="1"/>
+      <c r="Y139" s="1"/>
+      <c r="Z139" s="1"/>
+      <c r="AA139" s="1"/>
+      <c r="AB139" s="1"/>
+    </row>
+    <row r="140" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A140" s="3">
         <v>137</v>
       </c>
@@ -5891,8 +6757,13 @@
       <c r="U140" s="1"/>
       <c r="V140" s="1"/>
       <c r="W140" s="1"/>
-    </row>
-    <row r="141" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X140" s="1"/>
+      <c r="Y140" s="1"/>
+      <c r="Z140" s="1"/>
+      <c r="AA140" s="1"/>
+      <c r="AB140" s="1"/>
+    </row>
+    <row r="141" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A141" s="3">
         <v>138</v>
       </c>
@@ -5920,8 +6791,13 @@
       <c r="U141" s="1"/>
       <c r="V141" s="1"/>
       <c r="W141" s="1"/>
-    </row>
-    <row r="142" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X141" s="1"/>
+      <c r="Y141" s="1"/>
+      <c r="Z141" s="1"/>
+      <c r="AA141" s="1"/>
+      <c r="AB141" s="1"/>
+    </row>
+    <row r="142" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A142" s="3">
         <v>139</v>
       </c>
@@ -5949,8 +6825,13 @@
       <c r="U142" s="1"/>
       <c r="V142" s="1"/>
       <c r="W142" s="1"/>
-    </row>
-    <row r="143" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X142" s="1"/>
+      <c r="Y142" s="1"/>
+      <c r="Z142" s="1"/>
+      <c r="AA142" s="1"/>
+      <c r="AB142" s="1"/>
+    </row>
+    <row r="143" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A143" s="3">
         <v>140</v>
       </c>
@@ -5978,8 +6859,13 @@
       <c r="U143" s="1"/>
       <c r="V143" s="1"/>
       <c r="W143" s="1"/>
-    </row>
-    <row r="144" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X143" s="1"/>
+      <c r="Y143" s="1"/>
+      <c r="Z143" s="1"/>
+      <c r="AA143" s="1"/>
+      <c r="AB143" s="1"/>
+    </row>
+    <row r="144" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A144" s="3">
         <v>141</v>
       </c>
@@ -6007,8 +6893,13 @@
       <c r="U144" s="1"/>
       <c r="V144" s="1"/>
       <c r="W144" s="1"/>
-    </row>
-    <row r="145" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X144" s="1"/>
+      <c r="Y144" s="1"/>
+      <c r="Z144" s="1"/>
+      <c r="AA144" s="1"/>
+      <c r="AB144" s="1"/>
+    </row>
+    <row r="145" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A145" s="3">
         <v>142</v>
       </c>
@@ -6036,8 +6927,13 @@
       <c r="U145" s="1"/>
       <c r="V145" s="1"/>
       <c r="W145" s="1"/>
-    </row>
-    <row r="146" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X145" s="1"/>
+      <c r="Y145" s="1"/>
+      <c r="Z145" s="1"/>
+      <c r="AA145" s="1"/>
+      <c r="AB145" s="1"/>
+    </row>
+    <row r="146" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A146" s="3">
         <v>143</v>
       </c>
@@ -6065,8 +6961,13 @@
       <c r="U146" s="1"/>
       <c r="V146" s="1"/>
       <c r="W146" s="1"/>
-    </row>
-    <row r="147" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X146" s="1"/>
+      <c r="Y146" s="1"/>
+      <c r="Z146" s="1"/>
+      <c r="AA146" s="1"/>
+      <c r="AB146" s="1"/>
+    </row>
+    <row r="147" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A147" s="3">
         <v>144</v>
       </c>
@@ -6094,8 +6995,13 @@
       <c r="U147" s="1"/>
       <c r="V147" s="1"/>
       <c r="W147" s="1"/>
-    </row>
-    <row r="148" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X147" s="1"/>
+      <c r="Y147" s="1"/>
+      <c r="Z147" s="1"/>
+      <c r="AA147" s="1"/>
+      <c r="AB147" s="1"/>
+    </row>
+    <row r="148" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A148" s="3">
         <v>145</v>
       </c>
@@ -6125,8 +7031,13 @@
       <c r="U148" s="1"/>
       <c r="V148" s="1"/>
       <c r="W148" s="1"/>
-    </row>
-    <row r="149" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X148" s="1"/>
+      <c r="Y148" s="1"/>
+      <c r="Z148" s="1"/>
+      <c r="AA148" s="1"/>
+      <c r="AB148" s="1"/>
+    </row>
+    <row r="149" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A149" s="3">
         <v>146</v>
       </c>
@@ -6154,8 +7065,13 @@
       <c r="U149" s="1"/>
       <c r="V149" s="1"/>
       <c r="W149" s="1"/>
-    </row>
-    <row r="150" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X149" s="1"/>
+      <c r="Y149" s="1"/>
+      <c r="Z149" s="1"/>
+      <c r="AA149" s="1"/>
+      <c r="AB149" s="1"/>
+    </row>
+    <row r="150" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A150" s="3">
         <v>147</v>
       </c>
@@ -6183,8 +7099,13 @@
       <c r="U150" s="1"/>
       <c r="V150" s="1"/>
       <c r="W150" s="1"/>
-    </row>
-    <row r="151" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X150" s="1"/>
+      <c r="Y150" s="1"/>
+      <c r="Z150" s="1"/>
+      <c r="AA150" s="1"/>
+      <c r="AB150" s="1"/>
+    </row>
+    <row r="151" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A151" s="3">
         <v>148</v>
       </c>
@@ -6212,8 +7133,13 @@
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
-    </row>
-    <row r="152" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X151" s="1"/>
+      <c r="Y151" s="1"/>
+      <c r="Z151" s="1"/>
+      <c r="AA151" s="1"/>
+      <c r="AB151" s="1"/>
+    </row>
+    <row r="152" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A152" s="3">
         <v>149</v>
       </c>
@@ -6241,8 +7167,13 @@
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
-    </row>
-    <row r="153" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X152" s="1"/>
+      <c r="Y152" s="1"/>
+      <c r="Z152" s="1"/>
+      <c r="AA152" s="1"/>
+      <c r="AB152" s="1"/>
+    </row>
+    <row r="153" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A153" s="3">
         <v>150</v>
       </c>
@@ -6272,8 +7203,13 @@
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
       <c r="W153" s="1"/>
-    </row>
-    <row r="154" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X153" s="1"/>
+      <c r="Y153" s="1"/>
+      <c r="Z153" s="1"/>
+      <c r="AA153" s="1"/>
+      <c r="AB153" s="1"/>
+    </row>
+    <row r="154" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A154" s="3">
         <v>151</v>
       </c>
@@ -6303,8 +7239,13 @@
       <c r="U154" s="1"/>
       <c r="V154" s="1"/>
       <c r="W154" s="1"/>
-    </row>
-    <row r="155" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X154" s="1"/>
+      <c r="Y154" s="1"/>
+      <c r="Z154" s="1"/>
+      <c r="AA154" s="1"/>
+      <c r="AB154" s="1"/>
+    </row>
+    <row r="155" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A155" s="3">
         <v>152</v>
       </c>
@@ -6336,8 +7277,13 @@
       <c r="U155" s="1"/>
       <c r="V155" s="1"/>
       <c r="W155" s="1"/>
-    </row>
-    <row r="156" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X155" s="1"/>
+      <c r="Y155" s="1"/>
+      <c r="Z155" s="1"/>
+      <c r="AA155" s="1"/>
+      <c r="AB155" s="1"/>
+    </row>
+    <row r="156" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A156" s="3">
         <v>153</v>
       </c>
@@ -6345,7 +7291,7 @@
         <v>162</v>
       </c>
       <c r="C156" s="1"/>
-      <c r="D156" s="10" t="s">
+      <c r="D156" s="9" t="s">
         <v>159</v>
       </c>
       <c r="E156" s="1"/>
@@ -6367,8 +7313,13 @@
       <c r="U156" s="1"/>
       <c r="V156" s="1"/>
       <c r="W156" s="1"/>
-    </row>
-    <row r="157" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X156" s="1"/>
+      <c r="Y156" s="1"/>
+      <c r="Z156" s="1"/>
+      <c r="AA156" s="1"/>
+      <c r="AB156" s="1"/>
+    </row>
+    <row r="157" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A157" s="3">
         <v>154</v>
       </c>
@@ -6376,7 +7327,7 @@
         <v>163</v>
       </c>
       <c r="C157" s="1"/>
-      <c r="D157" s="10" t="s">
+      <c r="D157" s="9" t="s">
         <v>159</v>
       </c>
       <c r="E157" s="1"/>
@@ -6398,8 +7349,13 @@
       <c r="U157" s="1"/>
       <c r="V157" s="1"/>
       <c r="W157" s="1"/>
-    </row>
-    <row r="158" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X157" s="1"/>
+      <c r="Y157" s="1"/>
+      <c r="Z157" s="1"/>
+      <c r="AA157" s="1"/>
+      <c r="AB157" s="1"/>
+    </row>
+    <row r="158" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A158" s="3">
         <v>155</v>
       </c>
@@ -6431,8 +7387,13 @@
       <c r="U158" s="1"/>
       <c r="V158" s="1"/>
       <c r="W158" s="1"/>
-    </row>
-    <row r="159" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X158" s="1"/>
+      <c r="Y158" s="1"/>
+      <c r="Z158" s="1"/>
+      <c r="AA158" s="1"/>
+      <c r="AB158" s="1"/>
+    </row>
+    <row r="159" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A159" s="3">
         <v>156</v>
       </c>
@@ -6440,7 +7401,7 @@
         <v>166</v>
       </c>
       <c r="C159" s="1"/>
-      <c r="D159" s="11" t="s">
+      <c r="D159" s="10" t="s">
         <v>159</v>
       </c>
       <c r="E159" s="1"/>
@@ -6462,8 +7423,13 @@
       <c r="U159" s="1"/>
       <c r="V159" s="1"/>
       <c r="W159" s="1"/>
-    </row>
-    <row r="160" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X159" s="1"/>
+      <c r="Y159" s="1"/>
+      <c r="Z159" s="1"/>
+      <c r="AA159" s="1"/>
+      <c r="AB159" s="1"/>
+    </row>
+    <row r="160" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A160" s="3">
         <v>157</v>
       </c>
@@ -6471,7 +7437,7 @@
         <v>167</v>
       </c>
       <c r="C160" s="1"/>
-      <c r="D160" s="10" t="s">
+      <c r="D160" s="9" t="s">
         <v>159</v>
       </c>
       <c r="E160" s="1"/>
@@ -6493,8 +7459,13 @@
       <c r="U160" s="1"/>
       <c r="V160" s="1"/>
       <c r="W160" s="1"/>
-    </row>
-    <row r="161" spans="1:23" ht="15" customHeight="1">
+      <c r="X160" s="1"/>
+      <c r="Y160" s="1"/>
+      <c r="Z160" s="1"/>
+      <c r="AA160" s="1"/>
+      <c r="AB160" s="1"/>
+    </row>
+    <row r="161" spans="1:28" ht="15" customHeight="1">
       <c r="A161" s="3">
         <v>158</v>
       </c>
@@ -6502,7 +7473,7 @@
         <v>168</v>
       </c>
       <c r="C161" s="1"/>
-      <c r="D161" s="10" t="s">
+      <c r="D161" s="9" t="s">
         <v>159</v>
       </c>
       <c r="E161" s="1"/>
@@ -6524,8 +7495,13 @@
       <c r="U161" s="1"/>
       <c r="V161" s="1"/>
       <c r="W161" s="1"/>
-    </row>
-    <row r="162" spans="1:23" ht="15" customHeight="1">
+      <c r="X161" s="1"/>
+      <c r="Y161" s="1"/>
+      <c r="Z161" s="1"/>
+      <c r="AA161" s="1"/>
+      <c r="AB161" s="1"/>
+    </row>
+    <row r="162" spans="1:28" ht="15" customHeight="1">
       <c r="A162" s="3">
         <v>159</v>
       </c>
@@ -6533,7 +7509,7 @@
         <v>169</v>
       </c>
       <c r="C162" s="1"/>
-      <c r="D162" s="11" t="s">
+      <c r="D162" s="10" t="s">
         <v>159</v>
       </c>
       <c r="E162" s="1"/>
@@ -6555,8 +7531,13 @@
       <c r="U162" s="1"/>
       <c r="V162" s="1"/>
       <c r="W162" s="1"/>
-    </row>
-    <row r="163" spans="1:23" ht="15" customHeight="1">
+      <c r="X162" s="1"/>
+      <c r="Y162" s="1"/>
+      <c r="Z162" s="1"/>
+      <c r="AA162" s="1"/>
+      <c r="AB162" s="1"/>
+    </row>
+    <row r="163" spans="1:28" ht="15" customHeight="1">
       <c r="A163" s="3">
         <v>160</v>
       </c>
@@ -6564,7 +7545,7 @@
         <v>170</v>
       </c>
       <c r="C163" s="1"/>
-      <c r="D163" s="10" t="s">
+      <c r="D163" s="9" t="s">
         <v>159</v>
       </c>
       <c r="E163" s="1"/>
@@ -6588,8 +7569,13 @@
       <c r="U163" s="1"/>
       <c r="V163" s="1"/>
       <c r="W163" s="1"/>
-    </row>
-    <row r="164" spans="1:23" ht="15" customHeight="1">
+      <c r="X163" s="1"/>
+      <c r="Y163" s="1"/>
+      <c r="Z163" s="1"/>
+      <c r="AA163" s="1"/>
+      <c r="AB163" s="1"/>
+    </row>
+    <row r="164" spans="1:28" ht="15" customHeight="1">
       <c r="A164" s="3">
         <v>161</v>
       </c>
@@ -6597,7 +7583,7 @@
         <v>171</v>
       </c>
       <c r="C164" s="3"/>
-      <c r="D164" s="9"/>
+      <c r="D164" s="8"/>
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
       <c r="G164" s="3"/>
@@ -6619,8 +7605,13 @@
       <c r="U164" s="3"/>
       <c r="V164" s="3"/>
       <c r="W164" s="3"/>
-    </row>
-    <row r="165" spans="1:23" ht="15" customHeight="1">
+      <c r="X164" s="3"/>
+      <c r="Y164" s="3"/>
+      <c r="Z164" s="3"/>
+      <c r="AA164" s="3"/>
+      <c r="AB164" s="3"/>
+    </row>
+    <row r="165" spans="1:28" ht="15" customHeight="1">
       <c r="A165" s="3">
         <v>162</v>
       </c>
@@ -6628,7 +7619,7 @@
         <v>173</v>
       </c>
       <c r="C165" s="3"/>
-      <c r="D165" s="9"/>
+      <c r="D165" s="8"/>
       <c r="E165" s="3"/>
       <c r="F165" s="3"/>
       <c r="G165" s="3"/>
@@ -6648,8 +7639,13 @@
       <c r="U165" s="3"/>
       <c r="V165" s="3"/>
       <c r="W165" s="3"/>
-    </row>
-    <row r="166" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X165" s="3"/>
+      <c r="Y165" s="3"/>
+      <c r="Z165" s="3"/>
+      <c r="AA165" s="3"/>
+      <c r="AB165" s="3"/>
+    </row>
+    <row r="166" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A166" s="3">
         <v>163</v>
       </c>
@@ -6657,7 +7653,7 @@
         <v>116</v>
       </c>
       <c r="C166" s="1"/>
-      <c r="D166" s="9"/>
+      <c r="D166" s="8"/>
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
       <c r="G166" s="1"/>
@@ -6677,8 +7673,13 @@
       <c r="U166" s="1"/>
       <c r="V166" s="1"/>
       <c r="W166" s="1"/>
-    </row>
-    <row r="167" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X166" s="1"/>
+      <c r="Y166" s="1"/>
+      <c r="Z166" s="1"/>
+      <c r="AA166" s="1"/>
+      <c r="AB166" s="1"/>
+    </row>
+    <row r="167" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A167" s="3">
         <v>164</v>
       </c>
@@ -6686,7 +7687,7 @@
         <v>165</v>
       </c>
       <c r="C167" s="1"/>
-      <c r="D167" s="9"/>
+      <c r="D167" s="8"/>
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
       <c r="G167" s="1"/>
@@ -6706,8 +7707,13 @@
       <c r="U167" s="1"/>
       <c r="V167" s="1"/>
       <c r="W167" s="1"/>
-    </row>
-    <row r="168" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X167" s="1"/>
+      <c r="Y167" s="1"/>
+      <c r="Z167" s="1"/>
+      <c r="AA167" s="1"/>
+      <c r="AB167" s="1"/>
+    </row>
+    <row r="168" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A168" s="3">
         <v>165</v>
       </c>
@@ -6715,7 +7721,7 @@
         <v>117</v>
       </c>
       <c r="C168" s="1"/>
-      <c r="D168" s="9"/>
+      <c r="D168" s="8"/>
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
       <c r="G168" s="1"/>
@@ -6735,8 +7741,13 @@
       <c r="U168" s="1"/>
       <c r="V168" s="1"/>
       <c r="W168" s="1"/>
-    </row>
-    <row r="169" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X168" s="1"/>
+      <c r="Y168" s="1"/>
+      <c r="Z168" s="1"/>
+      <c r="AA168" s="1"/>
+      <c r="AB168" s="1"/>
+    </row>
+    <row r="169" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A169" s="3">
         <v>166</v>
       </c>
@@ -6744,7 +7755,7 @@
         <v>118</v>
       </c>
       <c r="C169" s="1"/>
-      <c r="D169" s="9"/>
+      <c r="D169" s="8"/>
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
       <c r="G169" s="1"/>
@@ -6764,8 +7775,13 @@
       <c r="U169" s="1"/>
       <c r="V169" s="1"/>
       <c r="W169" s="1"/>
-    </row>
-    <row r="170" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X169" s="1"/>
+      <c r="Y169" s="1"/>
+      <c r="Z169" s="1"/>
+      <c r="AA169" s="1"/>
+      <c r="AB169" s="1"/>
+    </row>
+    <row r="170" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A170" s="3">
         <v>167</v>
       </c>
@@ -6773,7 +7789,7 @@
         <v>119</v>
       </c>
       <c r="C170" s="1"/>
-      <c r="D170" s="9"/>
+      <c r="D170" s="8"/>
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
       <c r="G170" s="1"/>
@@ -6793,8 +7809,13 @@
       <c r="U170" s="1"/>
       <c r="V170" s="1"/>
       <c r="W170" s="1"/>
-    </row>
-    <row r="171" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X170" s="1"/>
+      <c r="Y170" s="1"/>
+      <c r="Z170" s="1"/>
+      <c r="AA170" s="1"/>
+      <c r="AB170" s="1"/>
+    </row>
+    <row r="171" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A171" s="3">
         <v>168</v>
       </c>
@@ -6802,7 +7823,7 @@
         <v>120</v>
       </c>
       <c r="C171" s="1"/>
-      <c r="D171" s="9"/>
+      <c r="D171" s="8"/>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
       <c r="G171" s="1"/>
@@ -6822,8 +7843,13 @@
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
       <c r="W171" s="1"/>
-    </row>
-    <row r="172" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X171" s="1"/>
+      <c r="Y171" s="1"/>
+      <c r="Z171" s="1"/>
+      <c r="AA171" s="1"/>
+      <c r="AB171" s="1"/>
+    </row>
+    <row r="172" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A172" s="3">
         <v>169</v>
       </c>
@@ -6831,7 +7857,7 @@
         <v>217</v>
       </c>
       <c r="C172" s="1"/>
-      <c r="D172" s="9"/>
+      <c r="D172" s="8"/>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
       <c r="G172" s="1"/>
@@ -6853,8 +7879,13 @@
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
       <c r="W172" s="1"/>
-    </row>
-    <row r="173" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X172" s="1"/>
+      <c r="Y172" s="1"/>
+      <c r="Z172" s="1"/>
+      <c r="AA172" s="1"/>
+      <c r="AB172" s="1"/>
+    </row>
+    <row r="173" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A173" s="3">
         <v>170</v>
       </c>
@@ -6862,7 +7893,7 @@
         <v>115</v>
       </c>
       <c r="C173" s="1"/>
-      <c r="D173" s="9"/>
+      <c r="D173" s="8"/>
       <c r="E173" s="1"/>
       <c r="F173" s="1"/>
       <c r="G173" s="1"/>
@@ -6882,16 +7913,21 @@
       <c r="U173" s="1"/>
       <c r="V173" s="1"/>
       <c r="W173" s="1"/>
-    </row>
-    <row r="174" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X173" s="1"/>
+      <c r="Y173" s="1"/>
+      <c r="Z173" s="1"/>
+      <c r="AA173" s="1"/>
+      <c r="AB173" s="1"/>
+    </row>
+    <row r="174" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A174" s="3">
         <v>171</v>
       </c>
-      <c r="B174" s="7" t="s">
+      <c r="B174" s="6" t="s">
         <v>174</v>
       </c>
       <c r="C174" s="1"/>
-      <c r="D174" s="9"/>
+      <c r="D174" s="8"/>
       <c r="E174" s="1" t="s">
         <v>159</v>
       </c>
@@ -6917,16 +7953,21 @@
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
       <c r="W174" s="1"/>
-    </row>
-    <row r="175" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X174" s="1"/>
+      <c r="Y174" s="1"/>
+      <c r="Z174" s="1"/>
+      <c r="AA174" s="1"/>
+      <c r="AB174" s="1"/>
+    </row>
+    <row r="175" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A175" s="3">
         <v>172</v>
       </c>
-      <c r="B175" s="7" t="s">
+      <c r="B175" s="6" t="s">
         <v>175</v>
       </c>
       <c r="C175" s="1"/>
-      <c r="D175" s="9"/>
+      <c r="D175" s="8"/>
       <c r="E175" s="1" t="s">
         <v>159</v>
       </c>
@@ -6948,16 +7989,21 @@
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
       <c r="W175" s="1"/>
-    </row>
-    <row r="176" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X175" s="1"/>
+      <c r="Y175" s="1"/>
+      <c r="Z175" s="1"/>
+      <c r="AA175" s="1"/>
+      <c r="AB175" s="1"/>
+    </row>
+    <row r="176" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A176" s="3">
         <v>173</v>
       </c>
-      <c r="B176" s="7" t="s">
+      <c r="B176" s="6" t="s">
         <v>176</v>
       </c>
       <c r="C176" s="1"/>
-      <c r="D176" s="9"/>
+      <c r="D176" s="8"/>
       <c r="E176" s="1" t="s">
         <v>159</v>
       </c>
@@ -6983,16 +8029,21 @@
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
       <c r="W176" s="1"/>
-    </row>
-    <row r="177" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X176" s="1"/>
+      <c r="Y176" s="1"/>
+      <c r="Z176" s="1"/>
+      <c r="AA176" s="1"/>
+      <c r="AB176" s="1"/>
+    </row>
+    <row r="177" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A177" s="3">
         <v>174</v>
       </c>
-      <c r="B177" s="7" t="s">
+      <c r="B177" s="6" t="s">
         <v>177</v>
       </c>
       <c r="C177" s="1"/>
-      <c r="D177" s="9"/>
+      <c r="D177" s="8"/>
       <c r="E177" s="1"/>
       <c r="F177" s="1"/>
       <c r="G177" s="1"/>
@@ -7012,16 +8063,21 @@
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
       <c r="W177" s="1"/>
-    </row>
-    <row r="178" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X177" s="1"/>
+      <c r="Y177" s="1"/>
+      <c r="Z177" s="1"/>
+      <c r="AA177" s="1"/>
+      <c r="AB177" s="1"/>
+    </row>
+    <row r="178" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A178" s="3">
         <v>175</v>
       </c>
-      <c r="B178" s="7" t="s">
+      <c r="B178" s="6" t="s">
         <v>178</v>
       </c>
       <c r="C178" s="1"/>
-      <c r="D178" s="9"/>
+      <c r="D178" s="8"/>
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
       <c r="G178" s="1"/>
@@ -7041,16 +8097,21 @@
       <c r="U178" s="1"/>
       <c r="V178" s="1"/>
       <c r="W178" s="1"/>
-    </row>
-    <row r="179" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X178" s="1"/>
+      <c r="Y178" s="1"/>
+      <c r="Z178" s="1"/>
+      <c r="AA178" s="1"/>
+      <c r="AB178" s="1"/>
+    </row>
+    <row r="179" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A179" s="3">
         <v>176</v>
       </c>
-      <c r="B179" s="7" t="s">
+      <c r="B179" s="6" t="s">
         <v>179</v>
       </c>
       <c r="C179" s="1"/>
-      <c r="D179" s="9"/>
+      <c r="D179" s="8"/>
       <c r="E179" s="1"/>
       <c r="F179" s="1"/>
       <c r="G179" s="1"/>
@@ -7070,16 +8131,21 @@
       <c r="U179" s="1"/>
       <c r="V179" s="1"/>
       <c r="W179" s="1"/>
-    </row>
-    <row r="180" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X179" s="1"/>
+      <c r="Y179" s="1"/>
+      <c r="Z179" s="1"/>
+      <c r="AA179" s="1"/>
+      <c r="AB179" s="1"/>
+    </row>
+    <row r="180" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A180" s="3">
         <v>177</v>
       </c>
-      <c r="B180" s="7" t="s">
+      <c r="B180" s="6" t="s">
         <v>180</v>
       </c>
       <c r="C180" s="1"/>
-      <c r="D180" s="9"/>
+      <c r="D180" s="8"/>
       <c r="E180" s="1"/>
       <c r="F180" s="1"/>
       <c r="G180" s="1"/>
@@ -7101,12 +8167,17 @@
       <c r="U180" s="1"/>
       <c r="V180" s="1"/>
       <c r="W180" s="1"/>
-    </row>
-    <row r="181" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X180" s="1"/>
+      <c r="Y180" s="1"/>
+      <c r="Z180" s="1"/>
+      <c r="AA180" s="1"/>
+      <c r="AB180" s="1"/>
+    </row>
+    <row r="181" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A181" s="3">
         <v>178</v>
       </c>
-      <c r="B181" s="7" t="s">
+      <c r="B181" s="6" t="s">
         <v>181</v>
       </c>
       <c r="C181" s="1"/>
@@ -7130,12 +8201,17 @@
       <c r="U181" s="1"/>
       <c r="V181" s="1"/>
       <c r="W181" s="1"/>
-    </row>
-    <row r="182" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X181" s="1"/>
+      <c r="Y181" s="1"/>
+      <c r="Z181" s="1"/>
+      <c r="AA181" s="1"/>
+      <c r="AB181" s="1"/>
+    </row>
+    <row r="182" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A182" s="3">
         <v>179</v>
       </c>
-      <c r="B182" s="7" t="s">
+      <c r="B182" s="6" t="s">
         <v>182</v>
       </c>
       <c r="C182" s="1"/>
@@ -7159,12 +8235,17 @@
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
       <c r="W182" s="1"/>
-    </row>
-    <row r="183" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X182" s="1"/>
+      <c r="Y182" s="1"/>
+      <c r="Z182" s="1"/>
+      <c r="AA182" s="1"/>
+      <c r="AB182" s="1"/>
+    </row>
+    <row r="183" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A183" s="3">
         <v>180</v>
       </c>
-      <c r="B183" s="7" t="s">
+      <c r="B183" s="6" t="s">
         <v>183</v>
       </c>
       <c r="C183" s="1"/>
@@ -7190,12 +8271,17 @@
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
       <c r="W183" s="1"/>
-    </row>
-    <row r="184" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X183" s="1"/>
+      <c r="Y183" s="1"/>
+      <c r="Z183" s="1"/>
+      <c r="AA183" s="1"/>
+      <c r="AB183" s="1"/>
+    </row>
+    <row r="184" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A184" s="3">
         <v>181</v>
       </c>
-      <c r="B184" s="7" t="s">
+      <c r="B184" s="6" t="s">
         <v>184</v>
       </c>
       <c r="C184" s="1"/>
@@ -7221,12 +8307,17 @@
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
       <c r="W184" s="1"/>
-    </row>
-    <row r="185" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X184" s="1"/>
+      <c r="Y184" s="1"/>
+      <c r="Z184" s="1"/>
+      <c r="AA184" s="1"/>
+      <c r="AB184" s="1"/>
+    </row>
+    <row r="185" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A185" s="3">
         <v>182</v>
       </c>
-      <c r="B185" s="7" t="s">
+      <c r="B185" s="6" t="s">
         <v>185</v>
       </c>
       <c r="C185" s="1"/>
@@ -7252,8 +8343,13 @@
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
       <c r="W185" s="1"/>
-    </row>
-    <row r="186" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X185" s="1"/>
+      <c r="Y185" s="1"/>
+      <c r="Z185" s="1"/>
+      <c r="AA185" s="1"/>
+      <c r="AB185" s="1"/>
+    </row>
+    <row r="186" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A186" s="3">
         <v>183</v>
       </c>
@@ -7281,10 +8377,29 @@
       <c r="U186" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="V186" s="1"/>
-      <c r="W186" s="1"/>
-    </row>
-    <row r="187" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="V186" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="W186" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="X186" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y186" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z186" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA186" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB186" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="187" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A187" s="3">
         <v>184</v>
       </c>
@@ -7312,10 +8427,29 @@
       <c r="U187" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="V187" s="1"/>
-      <c r="W187" s="1"/>
-    </row>
-    <row r="188" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="V187" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="W187" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="X187" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y187" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z187" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA187" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB187" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="188" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A188" s="3">
         <v>185</v>
       </c>
@@ -7345,10 +8479,29 @@
       <c r="U188" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="V188" s="1"/>
-      <c r="W188" s="1"/>
-    </row>
-    <row r="189" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="V188" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="W188" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="X188" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y188" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z188" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA188" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB188" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="189" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A189" s="3">
         <v>186</v>
       </c>
@@ -7376,10 +8529,29 @@
       <c r="U189" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="V189" s="1"/>
-      <c r="W189" s="1"/>
-    </row>
-    <row r="190" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="V189" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="W189" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="X189" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y189" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z189" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA189" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB189" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="190" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A190" s="3">
         <v>187</v>
       </c>
@@ -7407,10 +8579,29 @@
       <c r="U190" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="V190" s="1"/>
-      <c r="W190" s="1"/>
-    </row>
-    <row r="191" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="V190" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="W190" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="X190" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y190" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z190" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA190" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB190" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="191" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A191" s="3">
         <v>188</v>
       </c>
@@ -7438,10 +8629,29 @@
       <c r="U191" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="V191" s="1"/>
-      <c r="W191" s="1"/>
-    </row>
-    <row r="192" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="V191" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="W191" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="X191" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y191" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z191" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA191" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB191" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="192" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A192" s="3">
         <v>189</v>
       </c>
@@ -7471,8 +8681,13 @@
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
       <c r="W192" s="1"/>
-    </row>
-    <row r="193" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X192" s="1"/>
+      <c r="Y192" s="1"/>
+      <c r="Z192" s="1"/>
+      <c r="AA192" s="1"/>
+      <c r="AB192" s="1"/>
+    </row>
+    <row r="193" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A193" s="3">
         <v>190</v>
       </c>
@@ -7504,8 +8719,13 @@
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
       <c r="W193" s="1"/>
-    </row>
-    <row r="194" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X193" s="1"/>
+      <c r="Y193" s="1"/>
+      <c r="Z193" s="1"/>
+      <c r="AA193" s="1"/>
+      <c r="AB193" s="1"/>
+    </row>
+    <row r="194" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A194" s="3">
         <v>191</v>
       </c>
@@ -7535,8 +8755,13 @@
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
       <c r="W194" s="1"/>
-    </row>
-    <row r="195" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X194" s="1"/>
+      <c r="Y194" s="1"/>
+      <c r="Z194" s="1"/>
+      <c r="AA194" s="1"/>
+      <c r="AB194" s="1"/>
+    </row>
+    <row r="195" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A195" s="3">
         <v>192</v>
       </c>
@@ -7566,8 +8791,13 @@
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
       <c r="W195" s="1"/>
-    </row>
-    <row r="196" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X195" s="1"/>
+      <c r="Y195" s="1"/>
+      <c r="Z195" s="1"/>
+      <c r="AA195" s="1"/>
+      <c r="AB195" s="1"/>
+    </row>
+    <row r="196" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A196" s="3">
         <v>193</v>
       </c>
@@ -7597,8 +8827,13 @@
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
       <c r="W196" s="1"/>
-    </row>
-    <row r="197" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X196" s="1"/>
+      <c r="Y196" s="1"/>
+      <c r="Z196" s="1"/>
+      <c r="AA196" s="1"/>
+      <c r="AB196" s="1"/>
+    </row>
+    <row r="197" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A197" s="3">
         <v>194</v>
       </c>
@@ -7628,8 +8863,13 @@
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
       <c r="W197" s="1"/>
-    </row>
-    <row r="198" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X197" s="1"/>
+      <c r="Y197" s="1"/>
+      <c r="Z197" s="1"/>
+      <c r="AA197" s="1"/>
+      <c r="AB197" s="1"/>
+    </row>
+    <row r="198" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A198" s="3">
         <v>195</v>
       </c>
@@ -7659,8 +8899,13 @@
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
       <c r="W198" s="1"/>
-    </row>
-    <row r="199" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X198" s="1"/>
+      <c r="Y198" s="1"/>
+      <c r="Z198" s="1"/>
+      <c r="AA198" s="1"/>
+      <c r="AB198" s="1"/>
+    </row>
+    <row r="199" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A199" s="3">
         <v>196</v>
       </c>
@@ -7690,8 +8935,13 @@
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
       <c r="W199" s="1"/>
-    </row>
-    <row r="200" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X199" s="1"/>
+      <c r="Y199" s="1"/>
+      <c r="Z199" s="1"/>
+      <c r="AA199" s="1"/>
+      <c r="AB199" s="1"/>
+    </row>
+    <row r="200" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A200" s="3">
         <v>197</v>
       </c>
@@ -7721,8 +8971,13 @@
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
       <c r="W200" s="1"/>
-    </row>
-    <row r="201" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X200" s="1"/>
+      <c r="Y200" s="1"/>
+      <c r="Z200" s="1"/>
+      <c r="AA200" s="1"/>
+      <c r="AB200" s="1"/>
+    </row>
+    <row r="201" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A201" s="3">
         <v>198</v>
       </c>
@@ -7752,8 +9007,13 @@
       <c r="U201" s="1"/>
       <c r="V201" s="1"/>
       <c r="W201" s="1"/>
-    </row>
-    <row r="202" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X201" s="1"/>
+      <c r="Y201" s="1"/>
+      <c r="Z201" s="1"/>
+      <c r="AA201" s="1"/>
+      <c r="AB201" s="1"/>
+    </row>
+    <row r="202" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A202" s="3">
         <v>199</v>
       </c>
@@ -7783,8 +9043,13 @@
       <c r="U202" s="1"/>
       <c r="V202" s="1"/>
       <c r="W202" s="1"/>
-    </row>
-    <row r="203" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X202" s="1"/>
+      <c r="Y202" s="1"/>
+      <c r="Z202" s="1"/>
+      <c r="AA202" s="1"/>
+      <c r="AB202" s="1"/>
+    </row>
+    <row r="203" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A203" s="3">
         <v>200</v>
       </c>
@@ -7816,8 +9081,13 @@
       <c r="U203" s="1"/>
       <c r="V203" s="1"/>
       <c r="W203" s="1"/>
-    </row>
-    <row r="204" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X203" s="1"/>
+      <c r="Y203" s="1"/>
+      <c r="Z203" s="1"/>
+      <c r="AA203" s="1"/>
+      <c r="AB203" s="1"/>
+    </row>
+    <row r="204" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A204" s="3">
         <v>201</v>
       </c>
@@ -7847,8 +9117,13 @@
       <c r="U204" s="1"/>
       <c r="V204" s="1"/>
       <c r="W204" s="1"/>
-    </row>
-    <row r="205" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X204" s="1"/>
+      <c r="Y204" s="1"/>
+      <c r="Z204" s="1"/>
+      <c r="AA204" s="1"/>
+      <c r="AB204" s="1"/>
+    </row>
+    <row r="205" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A205" s="3">
         <v>202</v>
       </c>
@@ -7878,8 +9153,13 @@
       <c r="U205" s="1"/>
       <c r="V205" s="1"/>
       <c r="W205" s="1"/>
-    </row>
-    <row r="206" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X205" s="1"/>
+      <c r="Y205" s="1"/>
+      <c r="Z205" s="1"/>
+      <c r="AA205" s="1"/>
+      <c r="AB205" s="1"/>
+    </row>
+    <row r="206" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A206" s="3">
         <v>203</v>
       </c>
@@ -7909,8 +9189,13 @@
       <c r="U206" s="1"/>
       <c r="V206" s="1"/>
       <c r="W206" s="1"/>
-    </row>
-    <row r="207" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X206" s="1"/>
+      <c r="Y206" s="1"/>
+      <c r="Z206" s="1"/>
+      <c r="AA206" s="1"/>
+      <c r="AB206" s="1"/>
+    </row>
+    <row r="207" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A207" s="3">
         <v>204</v>
       </c>
@@ -7942,8 +9227,13 @@
       <c r="U207" s="1"/>
       <c r="V207" s="1"/>
       <c r="W207" s="1"/>
-    </row>
-    <row r="208" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X207" s="1"/>
+      <c r="Y207" s="1"/>
+      <c r="Z207" s="1"/>
+      <c r="AA207" s="1"/>
+      <c r="AB207" s="1"/>
+    </row>
+    <row r="208" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A208" s="3">
         <v>205</v>
       </c>
@@ -7973,8 +9263,13 @@
       <c r="U208" s="1"/>
       <c r="V208" s="1"/>
       <c r="W208" s="1"/>
-    </row>
-    <row r="209" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X208" s="1"/>
+      <c r="Y208" s="1"/>
+      <c r="Z208" s="1"/>
+      <c r="AA208" s="1"/>
+      <c r="AB208" s="1"/>
+    </row>
+    <row r="209" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A209" s="3">
         <v>206</v>
       </c>
@@ -8004,8 +9299,13 @@
       <c r="U209" s="1"/>
       <c r="V209" s="1"/>
       <c r="W209" s="1"/>
-    </row>
-    <row r="210" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X209" s="1"/>
+      <c r="Y209" s="1"/>
+      <c r="Z209" s="1"/>
+      <c r="AA209" s="1"/>
+      <c r="AB209" s="1"/>
+    </row>
+    <row r="210" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A210" s="3">
         <v>207</v>
       </c>
@@ -8035,8 +9335,13 @@
       <c r="U210" s="1"/>
       <c r="V210" s="1"/>
       <c r="W210" s="1"/>
-    </row>
-    <row r="211" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X210" s="1"/>
+      <c r="Y210" s="1"/>
+      <c r="Z210" s="1"/>
+      <c r="AA210" s="1"/>
+      <c r="AB210" s="1"/>
+    </row>
+    <row r="211" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A211" s="3">
         <v>208</v>
       </c>
@@ -8066,8 +9371,13 @@
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
       <c r="W211" s="1"/>
-    </row>
-    <row r="212" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X211" s="1"/>
+      <c r="Y211" s="1"/>
+      <c r="Z211" s="1"/>
+      <c r="AA211" s="1"/>
+      <c r="AB211" s="1"/>
+    </row>
+    <row r="212" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A212" s="3">
         <v>209</v>
       </c>
@@ -8097,8 +9407,13 @@
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
       <c r="W212" s="1"/>
-    </row>
-    <row r="213" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X212" s="1"/>
+      <c r="Y212" s="1"/>
+      <c r="Z212" s="1"/>
+      <c r="AA212" s="1"/>
+      <c r="AB212" s="1"/>
+    </row>
+    <row r="213" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A213" s="3">
         <v>210</v>
       </c>
@@ -8128,8 +9443,13 @@
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
       <c r="W213" s="1"/>
-    </row>
-    <row r="214" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X213" s="1"/>
+      <c r="Y213" s="1"/>
+      <c r="Z213" s="1"/>
+      <c r="AA213" s="1"/>
+      <c r="AB213" s="1"/>
+    </row>
+    <row r="214" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A214" s="3">
         <v>211</v>
       </c>
@@ -8159,8 +9479,13 @@
       <c r="U214" s="1"/>
       <c r="V214" s="1"/>
       <c r="W214" s="1"/>
-    </row>
-    <row r="215" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X214" s="1"/>
+      <c r="Y214" s="1"/>
+      <c r="Z214" s="1"/>
+      <c r="AA214" s="1"/>
+      <c r="AB214" s="1"/>
+    </row>
+    <row r="215" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A215" s="3">
         <v>212</v>
       </c>
@@ -8190,8 +9515,13 @@
       <c r="U215" s="1"/>
       <c r="V215" s="1"/>
       <c r="W215" s="1"/>
-    </row>
-    <row r="216" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X215" s="1"/>
+      <c r="Y215" s="1"/>
+      <c r="Z215" s="1"/>
+      <c r="AA215" s="1"/>
+      <c r="AB215" s="1"/>
+    </row>
+    <row r="216" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A216" s="3">
         <v>213</v>
       </c>
@@ -8217,8 +9547,13 @@
       <c r="U216" s="1"/>
       <c r="V216" s="1"/>
       <c r="W216" s="1"/>
-    </row>
-    <row r="217" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X216" s="1"/>
+      <c r="Y216" s="1"/>
+      <c r="Z216" s="1"/>
+      <c r="AA216" s="1"/>
+      <c r="AB216" s="1"/>
+    </row>
+    <row r="217" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A217" s="3">
         <v>214</v>
       </c>
@@ -8244,8 +9579,13 @@
       <c r="U217" s="1"/>
       <c r="V217" s="1"/>
       <c r="W217" s="1"/>
-    </row>
-    <row r="218" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X217" s="1"/>
+      <c r="Y217" s="1"/>
+      <c r="Z217" s="1"/>
+      <c r="AA217" s="1"/>
+      <c r="AB217" s="1"/>
+    </row>
+    <row r="218" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A218" s="3">
         <v>215</v>
       </c>
@@ -8271,8 +9611,13 @@
       <c r="U218" s="1"/>
       <c r="V218" s="1"/>
       <c r="W218" s="1"/>
-    </row>
-    <row r="219" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X218" s="1"/>
+      <c r="Y218" s="1"/>
+      <c r="Z218" s="1"/>
+      <c r="AA218" s="1"/>
+      <c r="AB218" s="1"/>
+    </row>
+    <row r="219" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A219" s="3">
         <v>216</v>
       </c>
@@ -8298,8 +9643,13 @@
       <c r="U219" s="1"/>
       <c r="V219" s="1"/>
       <c r="W219" s="1"/>
-    </row>
-    <row r="220" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X219" s="1"/>
+      <c r="Y219" s="1"/>
+      <c r="Z219" s="1"/>
+      <c r="AA219" s="1"/>
+      <c r="AB219" s="1"/>
+    </row>
+    <row r="220" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A220" s="3">
         <v>217</v>
       </c>
@@ -8325,8 +9675,13 @@
       <c r="U220" s="1"/>
       <c r="V220" s="1"/>
       <c r="W220" s="1"/>
-    </row>
-    <row r="221" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X220" s="1"/>
+      <c r="Y220" s="1"/>
+      <c r="Z220" s="1"/>
+      <c r="AA220" s="1"/>
+      <c r="AB220" s="1"/>
+    </row>
+    <row r="221" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A221" s="3">
         <v>218</v>
       </c>
@@ -8352,8 +9707,13 @@
       <c r="U221" s="1"/>
       <c r="V221" s="1"/>
       <c r="W221" s="1"/>
-    </row>
-    <row r="222" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X221" s="1"/>
+      <c r="Y221" s="1"/>
+      <c r="Z221" s="1"/>
+      <c r="AA221" s="1"/>
+      <c r="AB221" s="1"/>
+    </row>
+    <row r="222" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A222" s="3">
         <v>219</v>
       </c>
@@ -8379,8 +9739,13 @@
       <c r="U222" s="1"/>
       <c r="V222" s="1"/>
       <c r="W222" s="1"/>
-    </row>
-    <row r="223" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X222" s="1"/>
+      <c r="Y222" s="1"/>
+      <c r="Z222" s="1"/>
+      <c r="AA222" s="1"/>
+      <c r="AB222" s="1"/>
+    </row>
+    <row r="223" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A223" s="3">
         <v>220</v>
       </c>
@@ -8406,8 +9771,13 @@
       <c r="U223" s="1"/>
       <c r="V223" s="1"/>
       <c r="W223" s="1"/>
-    </row>
-    <row r="224" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X223" s="1"/>
+      <c r="Y223" s="1"/>
+      <c r="Z223" s="1"/>
+      <c r="AA223" s="1"/>
+      <c r="AB223" s="1"/>
+    </row>
+    <row r="224" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A224" s="3">
         <v>221</v>
       </c>
@@ -8433,8 +9803,13 @@
       <c r="U224" s="1"/>
       <c r="V224" s="1"/>
       <c r="W224" s="1"/>
-    </row>
-    <row r="225" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X224" s="1"/>
+      <c r="Y224" s="1"/>
+      <c r="Z224" s="1"/>
+      <c r="AA224" s="1"/>
+      <c r="AB224" s="1"/>
+    </row>
+    <row r="225" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A225" s="3">
         <v>222</v>
       </c>
@@ -8460,8 +9835,13 @@
       <c r="U225" s="1"/>
       <c r="V225" s="1"/>
       <c r="W225" s="1"/>
-    </row>
-    <row r="226" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X225" s="1"/>
+      <c r="Y225" s="1"/>
+      <c r="Z225" s="1"/>
+      <c r="AA225" s="1"/>
+      <c r="AB225" s="1"/>
+    </row>
+    <row r="226" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A226" s="3">
         <v>223</v>
       </c>
@@ -8487,8 +9867,13 @@
       <c r="U226" s="1"/>
       <c r="V226" s="1"/>
       <c r="W226" s="1"/>
-    </row>
-    <row r="227" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X226" s="1"/>
+      <c r="Y226" s="1"/>
+      <c r="Z226" s="1"/>
+      <c r="AA226" s="1"/>
+      <c r="AB226" s="1"/>
+    </row>
+    <row r="227" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A227" s="3">
         <v>224</v>
       </c>
@@ -8514,8 +9899,13 @@
       <c r="U227" s="1"/>
       <c r="V227" s="1"/>
       <c r="W227" s="1"/>
-    </row>
-    <row r="228" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X227" s="1"/>
+      <c r="Y227" s="1"/>
+      <c r="Z227" s="1"/>
+      <c r="AA227" s="1"/>
+      <c r="AB227" s="1"/>
+    </row>
+    <row r="228" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A228" s="3">
         <v>225</v>
       </c>
@@ -8541,8 +9931,13 @@
       <c r="U228" s="1"/>
       <c r="V228" s="1"/>
       <c r="W228" s="1"/>
-    </row>
-    <row r="229" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X228" s="1"/>
+      <c r="Y228" s="1"/>
+      <c r="Z228" s="1"/>
+      <c r="AA228" s="1"/>
+      <c r="AB228" s="1"/>
+    </row>
+    <row r="229" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A229" s="3">
         <v>226</v>
       </c>
@@ -8568,8 +9963,13 @@
       <c r="U229" s="1"/>
       <c r="V229" s="1"/>
       <c r="W229" s="1"/>
-    </row>
-    <row r="230" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="X229" s="1"/>
+      <c r="Y229" s="1"/>
+      <c r="Z229" s="1"/>
+      <c r="AA229" s="1"/>
+      <c r="AB229" s="1"/>
+    </row>
+    <row r="230" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A230" s="3">
         <v>227</v>
       </c>
@@ -8595,6 +9995,11 @@
       <c r="U230" s="1"/>
       <c r="V230" s="1"/>
       <c r="W230" s="1"/>
+      <c r="X230" s="1"/>
+      <c r="Y230" s="1"/>
+      <c r="Z230" s="1"/>
+      <c r="AA230" s="1"/>
+      <c r="AB230" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AA230" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -8603,9 +10008,9 @@
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="C1:W1"/>
   </mergeCells>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C230 D4:D163 D181:D230 E4:W230" xr:uid="{C452CDD0-B3A9-419A-AD4E-0E5CE327C346}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C230 D4:D163 D181:D230 E4:AB230" xr:uid="{C452CDD0-B3A9-419A-AD4E-0E5CE327C346}">
       <formula1>"〇,×,△"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D164:D180" xr:uid="{E47C5A29-770A-4FF4-AE4B-E53AB5761727}">
@@ -8614,4 +10019,1813 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8513D353-BD33-4F18-8682-09CF4EA59EE5}">
+  <dimension ref="A2:H170"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <cols>
+    <col min="1" max="1" width="10.1875" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.8125" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.0625" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.9375" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="6.5625" style="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="23"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8">
+      <c r="A2" s="21"/>
+      <c r="B2" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="H4" s="25"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="H18" s="25"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="G19" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="H19" s="25"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="26"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="26"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="26"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="26"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="26"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="26"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="26"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="26"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="26"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="26"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="26"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="26"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="26"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="26"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="26"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="25"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="26"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="26"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="26"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="26"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="26"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="25"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="26"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="25"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="26"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="25"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="26"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="25"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="26"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="26"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="25"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="26"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="25"/>
+      <c r="H49" s="25"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="26"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="25"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="26"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="25"/>
+      <c r="H51" s="25"/>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="26"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="25"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="25"/>
+      <c r="H52" s="25"/>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="26"/>
+      <c r="B53" s="25"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="25"/>
+      <c r="H53" s="25"/>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="26"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="25"/>
+      <c r="H54" s="25"/>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="26"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="25"/>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="26"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25"/>
+      <c r="H56" s="25"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="26"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
+      <c r="H57" s="25"/>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="26"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="25"/>
+      <c r="H58" s="25"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="26"/>
+      <c r="B59" s="25"/>
+      <c r="C59" s="25"/>
+      <c r="D59" s="25"/>
+      <c r="E59" s="25"/>
+      <c r="F59" s="25"/>
+      <c r="G59" s="25"/>
+      <c r="H59" s="25"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="26"/>
+      <c r="B60" s="25"/>
+      <c r="C60" s="25"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="25"/>
+      <c r="H60" s="25"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="26"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="26"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="25"/>
+      <c r="D62" s="25"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
+      <c r="H62" s="25"/>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="26"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25"/>
+      <c r="G63" s="25"/>
+      <c r="H63" s="25"/>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="26"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="25"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="25"/>
+      <c r="F64" s="25"/>
+      <c r="G64" s="25"/>
+      <c r="H64" s="25"/>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="26"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="25"/>
+      <c r="F65" s="25"/>
+      <c r="G65" s="25"/>
+      <c r="H65" s="25"/>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="26"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="25"/>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="26"/>
+      <c r="B67" s="25"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="25"/>
+      <c r="E67" s="25"/>
+      <c r="F67" s="25"/>
+      <c r="G67" s="25"/>
+      <c r="H67" s="25"/>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="26"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+      <c r="D68" s="25"/>
+      <c r="E68" s="25"/>
+      <c r="F68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="25"/>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="26"/>
+      <c r="B69" s="25"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="25"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="26"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="25"/>
+      <c r="E70" s="25"/>
+      <c r="F70" s="25"/>
+      <c r="G70" s="25"/>
+      <c r="H70" s="25"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="26"/>
+      <c r="B71" s="25"/>
+      <c r="C71" s="25"/>
+      <c r="D71" s="25"/>
+      <c r="E71" s="25"/>
+      <c r="F71" s="25"/>
+      <c r="G71" s="25"/>
+      <c r="H71" s="25"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="26"/>
+      <c r="B72" s="25"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="25"/>
+      <c r="F72" s="25"/>
+      <c r="G72" s="25"/>
+      <c r="H72" s="25"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="26"/>
+      <c r="B73" s="25"/>
+      <c r="C73" s="25"/>
+      <c r="D73" s="25"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
+      <c r="H73" s="25"/>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="26"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="25"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
+      <c r="H74" s="25"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="26"/>
+      <c r="B75" s="25"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="25"/>
+      <c r="F75" s="25"/>
+      <c r="G75" s="25"/>
+      <c r="H75" s="25"/>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="26"/>
+      <c r="B76" s="25"/>
+      <c r="C76" s="25"/>
+      <c r="D76" s="25"/>
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
+      <c r="H76" s="25"/>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="26"/>
+      <c r="B77" s="25"/>
+      <c r="C77" s="25"/>
+      <c r="D77" s="25"/>
+      <c r="E77" s="25"/>
+      <c r="F77" s="25"/>
+      <c r="G77" s="25"/>
+      <c r="H77" s="25"/>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="26"/>
+      <c r="B78" s="25"/>
+      <c r="C78" s="25"/>
+      <c r="D78" s="25"/>
+      <c r="E78" s="25"/>
+      <c r="F78" s="25"/>
+      <c r="G78" s="25"/>
+      <c r="H78" s="25"/>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="26"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="25"/>
+      <c r="D79" s="25"/>
+      <c r="E79" s="25"/>
+      <c r="F79" s="25"/>
+      <c r="G79" s="25"/>
+      <c r="H79" s="25"/>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="26"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+      <c r="D80" s="25"/>
+      <c r="E80" s="25"/>
+      <c r="F80" s="25"/>
+      <c r="G80" s="25"/>
+      <c r="H80" s="25"/>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="26"/>
+      <c r="B81" s="25"/>
+      <c r="C81" s="25"/>
+      <c r="D81" s="25"/>
+      <c r="E81" s="25"/>
+      <c r="F81" s="25"/>
+      <c r="G81" s="25"/>
+      <c r="H81" s="25"/>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="26"/>
+      <c r="B82" s="25"/>
+      <c r="C82" s="25"/>
+      <c r="D82" s="25"/>
+      <c r="E82" s="25"/>
+      <c r="F82" s="25"/>
+      <c r="G82" s="25"/>
+      <c r="H82" s="25"/>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="26"/>
+      <c r="B83" s="25"/>
+      <c r="C83" s="25"/>
+      <c r="D83" s="25"/>
+      <c r="E83" s="25"/>
+      <c r="F83" s="25"/>
+      <c r="G83" s="25"/>
+      <c r="H83" s="25"/>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="26"/>
+      <c r="B84" s="25"/>
+      <c r="C84" s="25"/>
+      <c r="D84" s="25"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="25"/>
+      <c r="G84" s="25"/>
+      <c r="H84" s="25"/>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="26"/>
+      <c r="B85" s="25"/>
+      <c r="C85" s="25"/>
+      <c r="D85" s="25"/>
+      <c r="E85" s="25"/>
+      <c r="F85" s="25"/>
+      <c r="G85" s="25"/>
+      <c r="H85" s="25"/>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="26"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="25"/>
+      <c r="D86" s="25"/>
+      <c r="E86" s="25"/>
+      <c r="F86" s="25"/>
+      <c r="G86" s="25"/>
+      <c r="H86" s="25"/>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="26"/>
+      <c r="B87" s="25"/>
+      <c r="C87" s="25"/>
+      <c r="D87" s="25"/>
+      <c r="E87" s="25"/>
+      <c r="F87" s="25"/>
+      <c r="G87" s="25"/>
+      <c r="H87" s="25"/>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="26"/>
+      <c r="B88" s="25"/>
+      <c r="C88" s="25"/>
+      <c r="D88" s="25"/>
+      <c r="E88" s="25"/>
+      <c r="F88" s="25"/>
+      <c r="G88" s="25"/>
+      <c r="H88" s="25"/>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" s="26"/>
+      <c r="B89" s="25"/>
+      <c r="C89" s="25"/>
+      <c r="D89" s="25"/>
+      <c r="E89" s="25"/>
+      <c r="F89" s="25"/>
+      <c r="G89" s="25"/>
+      <c r="H89" s="25"/>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="26"/>
+      <c r="B90" s="25"/>
+      <c r="C90" s="25"/>
+      <c r="D90" s="25"/>
+      <c r="E90" s="25"/>
+      <c r="F90" s="25"/>
+      <c r="G90" s="25"/>
+      <c r="H90" s="25"/>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="26"/>
+      <c r="B91" s="25"/>
+      <c r="C91" s="25"/>
+      <c r="D91" s="25"/>
+      <c r="E91" s="25"/>
+      <c r="F91" s="25"/>
+      <c r="G91" s="25"/>
+      <c r="H91" s="25"/>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="26"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="25"/>
+      <c r="D92" s="25"/>
+      <c r="E92" s="25"/>
+      <c r="F92" s="25"/>
+      <c r="G92" s="25"/>
+      <c r="H92" s="25"/>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="26"/>
+      <c r="B93" s="25"/>
+      <c r="C93" s="25"/>
+      <c r="D93" s="25"/>
+      <c r="E93" s="25"/>
+      <c r="F93" s="25"/>
+      <c r="G93" s="25"/>
+      <c r="H93" s="25"/>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="26"/>
+      <c r="B94" s="25"/>
+      <c r="C94" s="25"/>
+      <c r="D94" s="25"/>
+      <c r="E94" s="25"/>
+      <c r="F94" s="25"/>
+      <c r="G94" s="25"/>
+      <c r="H94" s="25"/>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="26"/>
+      <c r="B95" s="25"/>
+      <c r="C95" s="25"/>
+      <c r="D95" s="25"/>
+      <c r="E95" s="25"/>
+      <c r="F95" s="25"/>
+      <c r="G95" s="25"/>
+      <c r="H95" s="25"/>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" s="26"/>
+      <c r="B96" s="25"/>
+      <c r="C96" s="25"/>
+      <c r="D96" s="25"/>
+      <c r="E96" s="25"/>
+      <c r="F96" s="25"/>
+      <c r="G96" s="25"/>
+      <c r="H96" s="25"/>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="26"/>
+      <c r="B97" s="25"/>
+      <c r="C97" s="25"/>
+      <c r="D97" s="25"/>
+      <c r="E97" s="25"/>
+      <c r="F97" s="25"/>
+      <c r="G97" s="25"/>
+      <c r="H97" s="25"/>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="26"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="25"/>
+      <c r="D98" s="25"/>
+      <c r="E98" s="25"/>
+      <c r="F98" s="25"/>
+      <c r="G98" s="25"/>
+      <c r="H98" s="25"/>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="26"/>
+      <c r="B99" s="25"/>
+      <c r="C99" s="25"/>
+      <c r="D99" s="25"/>
+      <c r="E99" s="25"/>
+      <c r="F99" s="25"/>
+      <c r="G99" s="25"/>
+      <c r="H99" s="25"/>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="26"/>
+      <c r="B100" s="25"/>
+      <c r="C100" s="25"/>
+      <c r="D100" s="25"/>
+      <c r="E100" s="25"/>
+      <c r="F100" s="25"/>
+      <c r="G100" s="25"/>
+      <c r="H100" s="25"/>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="26"/>
+      <c r="B101" s="25"/>
+      <c r="C101" s="25"/>
+      <c r="D101" s="25"/>
+      <c r="E101" s="25"/>
+      <c r="F101" s="25"/>
+      <c r="G101" s="25"/>
+      <c r="H101" s="25"/>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" s="26"/>
+      <c r="B102" s="25"/>
+      <c r="C102" s="25"/>
+      <c r="D102" s="25"/>
+      <c r="E102" s="25"/>
+      <c r="F102" s="25"/>
+      <c r="G102" s="25"/>
+      <c r="H102" s="25"/>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" s="26"/>
+      <c r="B103" s="25"/>
+      <c r="C103" s="25"/>
+      <c r="D103" s="25"/>
+      <c r="E103" s="25"/>
+      <c r="F103" s="25"/>
+      <c r="G103" s="25"/>
+      <c r="H103" s="25"/>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" s="26"/>
+      <c r="B104" s="25"/>
+      <c r="C104" s="25"/>
+      <c r="D104" s="25"/>
+      <c r="E104" s="25"/>
+      <c r="F104" s="25"/>
+      <c r="G104" s="25"/>
+      <c r="H104" s="25"/>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" s="26"/>
+      <c r="B105" s="25"/>
+      <c r="C105" s="25"/>
+      <c r="D105" s="25"/>
+      <c r="E105" s="25"/>
+      <c r="F105" s="25"/>
+      <c r="G105" s="25"/>
+      <c r="H105" s="25"/>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" s="26"/>
+      <c r="B106" s="25"/>
+      <c r="C106" s="25"/>
+      <c r="D106" s="25"/>
+      <c r="E106" s="25"/>
+      <c r="F106" s="25"/>
+      <c r="G106" s="25"/>
+      <c r="H106" s="25"/>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" s="26"/>
+      <c r="B107" s="25"/>
+      <c r="C107" s="25"/>
+      <c r="D107" s="25"/>
+      <c r="E107" s="25"/>
+      <c r="F107" s="25"/>
+      <c r="G107" s="25"/>
+      <c r="H107" s="25"/>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" s="26"/>
+      <c r="B108" s="25"/>
+      <c r="C108" s="25"/>
+      <c r="D108" s="25"/>
+      <c r="E108" s="25"/>
+      <c r="F108" s="25"/>
+      <c r="G108" s="25"/>
+      <c r="H108" s="25"/>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" s="26"/>
+      <c r="B109" s="25"/>
+      <c r="C109" s="25"/>
+      <c r="D109" s="25"/>
+      <c r="E109" s="25"/>
+      <c r="F109" s="25"/>
+      <c r="G109" s="25"/>
+      <c r="H109" s="25"/>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" s="26"/>
+      <c r="B110" s="25"/>
+      <c r="C110" s="25"/>
+      <c r="D110" s="25"/>
+      <c r="E110" s="25"/>
+      <c r="F110" s="25"/>
+      <c r="G110" s="25"/>
+      <c r="H110" s="25"/>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" s="26"/>
+      <c r="B111" s="25"/>
+      <c r="C111" s="25"/>
+      <c r="D111" s="25"/>
+      <c r="E111" s="25"/>
+      <c r="F111" s="25"/>
+      <c r="G111" s="25"/>
+      <c r="H111" s="25"/>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" s="26"/>
+      <c r="B112" s="25"/>
+      <c r="C112" s="25"/>
+      <c r="D112" s="25"/>
+      <c r="E112" s="25"/>
+      <c r="F112" s="25"/>
+      <c r="G112" s="25"/>
+      <c r="H112" s="25"/>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" s="26"/>
+      <c r="B113" s="25"/>
+      <c r="C113" s="25"/>
+      <c r="D113" s="25"/>
+      <c r="E113" s="25"/>
+      <c r="F113" s="25"/>
+      <c r="G113" s="25"/>
+      <c r="H113" s="25"/>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" s="26"/>
+      <c r="B114" s="25"/>
+      <c r="C114" s="25"/>
+      <c r="D114" s="25"/>
+      <c r="E114" s="25"/>
+      <c r="F114" s="25"/>
+      <c r="G114" s="25"/>
+      <c r="H114" s="25"/>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" s="26"/>
+      <c r="B115" s="25"/>
+      <c r="C115" s="25"/>
+      <c r="D115" s="25"/>
+      <c r="E115" s="25"/>
+      <c r="F115" s="25"/>
+      <c r="G115" s="25"/>
+      <c r="H115" s="25"/>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" s="26"/>
+      <c r="B116" s="25"/>
+      <c r="C116" s="25"/>
+      <c r="D116" s="25"/>
+      <c r="E116" s="25"/>
+      <c r="F116" s="25"/>
+      <c r="G116" s="25"/>
+      <c r="H116" s="25"/>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" s="26"/>
+      <c r="B117" s="25"/>
+      <c r="C117" s="25"/>
+      <c r="D117" s="25"/>
+      <c r="E117" s="25"/>
+      <c r="F117" s="25"/>
+      <c r="G117" s="25"/>
+      <c r="H117" s="25"/>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" s="26"/>
+      <c r="B118" s="25"/>
+      <c r="C118" s="25"/>
+      <c r="D118" s="25"/>
+      <c r="E118" s="25"/>
+      <c r="F118" s="25"/>
+      <c r="G118" s="25"/>
+      <c r="H118" s="25"/>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" s="26"/>
+      <c r="B119" s="25"/>
+      <c r="C119" s="25"/>
+      <c r="D119" s="25"/>
+      <c r="E119" s="25"/>
+      <c r="F119" s="25"/>
+      <c r="G119" s="25"/>
+      <c r="H119" s="25"/>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" s="26"/>
+      <c r="B120" s="25"/>
+      <c r="C120" s="25"/>
+      <c r="D120" s="25"/>
+      <c r="E120" s="25"/>
+      <c r="F120" s="25"/>
+      <c r="G120" s="25"/>
+      <c r="H120" s="25"/>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" s="26"/>
+      <c r="B121" s="25"/>
+      <c r="C121" s="25"/>
+      <c r="D121" s="25"/>
+      <c r="E121" s="25"/>
+      <c r="F121" s="25"/>
+      <c r="G121" s="25"/>
+      <c r="H121" s="25"/>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" s="26"/>
+      <c r="B122" s="25"/>
+      <c r="C122" s="25"/>
+      <c r="D122" s="25"/>
+      <c r="E122" s="25"/>
+      <c r="F122" s="25"/>
+      <c r="G122" s="25"/>
+      <c r="H122" s="25"/>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" s="26"/>
+      <c r="B123" s="25"/>
+      <c r="C123" s="25"/>
+      <c r="D123" s="25"/>
+      <c r="E123" s="25"/>
+      <c r="F123" s="25"/>
+      <c r="G123" s="25"/>
+      <c r="H123" s="25"/>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" s="26"/>
+      <c r="B124" s="25"/>
+      <c r="C124" s="25"/>
+      <c r="D124" s="25"/>
+      <c r="E124" s="25"/>
+      <c r="F124" s="25"/>
+      <c r="G124" s="25"/>
+      <c r="H124" s="25"/>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="26"/>
+      <c r="B125" s="25"/>
+      <c r="C125" s="25"/>
+      <c r="D125" s="25"/>
+      <c r="E125" s="25"/>
+      <c r="F125" s="25"/>
+      <c r="G125" s="25"/>
+      <c r="H125" s="25"/>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" s="26"/>
+      <c r="B126" s="25"/>
+      <c r="C126" s="25"/>
+      <c r="D126" s="25"/>
+      <c r="E126" s="25"/>
+      <c r="F126" s="25"/>
+      <c r="G126" s="25"/>
+      <c r="H126" s="25"/>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" s="26"/>
+      <c r="B127" s="25"/>
+      <c r="C127" s="25"/>
+      <c r="D127" s="25"/>
+      <c r="E127" s="25"/>
+      <c r="F127" s="25"/>
+      <c r="G127" s="25"/>
+      <c r="H127" s="25"/>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" s="26"/>
+      <c r="B128" s="25"/>
+      <c r="C128" s="25"/>
+      <c r="D128" s="25"/>
+      <c r="E128" s="25"/>
+      <c r="F128" s="25"/>
+      <c r="G128" s="25"/>
+      <c r="H128" s="25"/>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" s="26"/>
+      <c r="B129" s="25"/>
+      <c r="C129" s="25"/>
+      <c r="D129" s="25"/>
+      <c r="E129" s="25"/>
+      <c r="F129" s="25"/>
+      <c r="G129" s="25"/>
+      <c r="H129" s="25"/>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" s="26"/>
+      <c r="B130" s="25"/>
+      <c r="C130" s="25"/>
+      <c r="D130" s="25"/>
+      <c r="E130" s="25"/>
+      <c r="F130" s="25"/>
+      <c r="G130" s="25"/>
+      <c r="H130" s="25"/>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" s="26"/>
+      <c r="B131" s="25"/>
+      <c r="C131" s="25"/>
+      <c r="D131" s="25"/>
+      <c r="E131" s="25"/>
+      <c r="F131" s="25"/>
+      <c r="G131" s="25"/>
+      <c r="H131" s="25"/>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" s="26"/>
+      <c r="B132" s="25"/>
+      <c r="C132" s="25"/>
+      <c r="D132" s="25"/>
+      <c r="E132" s="25"/>
+      <c r="F132" s="25"/>
+      <c r="G132" s="25"/>
+      <c r="H132" s="25"/>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" s="26"/>
+      <c r="B133" s="25"/>
+      <c r="C133" s="25"/>
+      <c r="D133" s="25"/>
+      <c r="E133" s="25"/>
+      <c r="F133" s="25"/>
+      <c r="G133" s="25"/>
+      <c r="H133" s="25"/>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" s="26"/>
+      <c r="B134" s="25"/>
+      <c r="C134" s="25"/>
+      <c r="D134" s="25"/>
+      <c r="E134" s="25"/>
+      <c r="F134" s="25"/>
+      <c r="G134" s="25"/>
+      <c r="H134" s="25"/>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" s="26"/>
+      <c r="B135" s="25"/>
+      <c r="C135" s="25"/>
+      <c r="D135" s="25"/>
+      <c r="E135" s="25"/>
+      <c r="F135" s="25"/>
+      <c r="G135" s="25"/>
+      <c r="H135" s="25"/>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" s="26"/>
+      <c r="B136" s="25"/>
+      <c r="C136" s="25"/>
+      <c r="D136" s="25"/>
+      <c r="E136" s="25"/>
+      <c r="F136" s="25"/>
+      <c r="G136" s="25"/>
+      <c r="H136" s="25"/>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" s="26"/>
+      <c r="B137" s="25"/>
+      <c r="C137" s="25"/>
+      <c r="D137" s="25"/>
+      <c r="E137" s="25"/>
+      <c r="F137" s="25"/>
+      <c r="G137" s="25"/>
+      <c r="H137" s="25"/>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" s="26"/>
+      <c r="B138" s="25"/>
+      <c r="C138" s="25"/>
+      <c r="D138" s="25"/>
+      <c r="E138" s="25"/>
+      <c r="F138" s="25"/>
+      <c r="G138" s="25"/>
+      <c r="H138" s="25"/>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" s="26"/>
+      <c r="B139" s="25"/>
+      <c r="C139" s="25"/>
+      <c r="D139" s="25"/>
+      <c r="E139" s="25"/>
+      <c r="F139" s="25"/>
+      <c r="G139" s="25"/>
+      <c r="H139" s="25"/>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" s="26"/>
+      <c r="B140" s="25"/>
+      <c r="C140" s="25"/>
+      <c r="D140" s="25"/>
+      <c r="E140" s="25"/>
+      <c r="F140" s="25"/>
+      <c r="G140" s="25"/>
+      <c r="H140" s="25"/>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" s="26"/>
+      <c r="B141" s="25"/>
+      <c r="C141" s="25"/>
+      <c r="D141" s="25"/>
+      <c r="E141" s="25"/>
+      <c r="F141" s="25"/>
+      <c r="G141" s="25"/>
+      <c r="H141" s="25"/>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" s="26"/>
+      <c r="B142" s="25"/>
+      <c r="C142" s="25"/>
+      <c r="D142" s="25"/>
+      <c r="E142" s="25"/>
+      <c r="F142" s="25"/>
+      <c r="G142" s="25"/>
+      <c r="H142" s="25"/>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" s="26"/>
+      <c r="B143" s="25"/>
+      <c r="C143" s="25"/>
+      <c r="D143" s="25"/>
+      <c r="E143" s="25"/>
+      <c r="F143" s="25"/>
+      <c r="G143" s="25"/>
+      <c r="H143" s="25"/>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" s="26"/>
+      <c r="B144" s="25"/>
+      <c r="C144" s="25"/>
+      <c r="D144" s="25"/>
+      <c r="E144" s="25"/>
+      <c r="F144" s="25"/>
+      <c r="G144" s="25"/>
+      <c r="H144" s="25"/>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" s="26"/>
+      <c r="B145" s="25"/>
+      <c r="C145" s="25"/>
+      <c r="D145" s="25"/>
+      <c r="E145" s="25"/>
+      <c r="F145" s="25"/>
+      <c r="G145" s="25"/>
+      <c r="H145" s="25"/>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" s="26"/>
+      <c r="B146" s="25"/>
+      <c r="C146" s="25"/>
+      <c r="D146" s="25"/>
+      <c r="E146" s="25"/>
+      <c r="F146" s="25"/>
+      <c r="G146" s="25"/>
+      <c r="H146" s="25"/>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" s="26"/>
+      <c r="B147" s="25"/>
+      <c r="C147" s="25"/>
+      <c r="D147" s="25"/>
+      <c r="E147" s="25"/>
+      <c r="F147" s="25"/>
+      <c r="G147" s="25"/>
+      <c r="H147" s="25"/>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" s="26"/>
+      <c r="B148" s="25"/>
+      <c r="C148" s="25"/>
+      <c r="D148" s="25"/>
+      <c r="E148" s="25"/>
+      <c r="F148" s="25"/>
+      <c r="G148" s="25"/>
+      <c r="H148" s="25"/>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" s="26"/>
+      <c r="B149" s="25"/>
+      <c r="C149" s="25"/>
+      <c r="D149" s="25"/>
+      <c r="E149" s="25"/>
+      <c r="F149" s="25"/>
+      <c r="G149" s="25"/>
+      <c r="H149" s="25"/>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" s="26"/>
+      <c r="B150" s="25"/>
+      <c r="C150" s="25"/>
+      <c r="D150" s="25"/>
+      <c r="E150" s="25"/>
+      <c r="F150" s="25"/>
+      <c r="G150" s="25"/>
+      <c r="H150" s="25"/>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" s="26"/>
+      <c r="B151" s="25"/>
+      <c r="C151" s="25"/>
+      <c r="D151" s="25"/>
+      <c r="E151" s="25"/>
+      <c r="F151" s="25"/>
+      <c r="G151" s="25"/>
+      <c r="H151" s="25"/>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" s="26"/>
+      <c r="B152" s="25"/>
+      <c r="C152" s="25"/>
+      <c r="D152" s="25"/>
+      <c r="E152" s="25"/>
+      <c r="F152" s="25"/>
+      <c r="G152" s="25"/>
+      <c r="H152" s="25"/>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" s="26"/>
+      <c r="B153" s="25"/>
+      <c r="C153" s="25"/>
+      <c r="D153" s="25"/>
+      <c r="E153" s="25"/>
+      <c r="F153" s="25"/>
+      <c r="G153" s="25"/>
+      <c r="H153" s="25"/>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" s="26"/>
+      <c r="B154" s="25"/>
+      <c r="C154" s="25"/>
+      <c r="D154" s="25"/>
+      <c r="E154" s="25"/>
+      <c r="F154" s="25"/>
+      <c r="G154" s="25"/>
+      <c r="H154" s="25"/>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" s="26"/>
+      <c r="B155" s="25"/>
+      <c r="C155" s="25"/>
+      <c r="D155" s="25"/>
+      <c r="E155" s="25"/>
+      <c r="F155" s="25"/>
+      <c r="G155" s="25"/>
+      <c r="H155" s="25"/>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" s="26"/>
+      <c r="B156" s="25"/>
+      <c r="C156" s="25"/>
+      <c r="D156" s="25"/>
+      <c r="E156" s="25"/>
+      <c r="F156" s="25"/>
+      <c r="G156" s="25"/>
+      <c r="H156" s="25"/>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" s="26"/>
+      <c r="B157" s="25"/>
+      <c r="C157" s="25"/>
+      <c r="D157" s="25"/>
+      <c r="E157" s="25"/>
+      <c r="F157" s="25"/>
+      <c r="G157" s="25"/>
+      <c r="H157" s="25"/>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" s="26"/>
+      <c r="B158" s="25"/>
+      <c r="C158" s="25"/>
+      <c r="D158" s="25"/>
+      <c r="E158" s="25"/>
+      <c r="F158" s="25"/>
+      <c r="G158" s="25"/>
+      <c r="H158" s="25"/>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" s="26"/>
+      <c r="B159" s="25"/>
+      <c r="C159" s="25"/>
+      <c r="D159" s="25"/>
+      <c r="E159" s="25"/>
+      <c r="F159" s="25"/>
+      <c r="G159" s="25"/>
+      <c r="H159" s="25"/>
+    </row>
+    <row r="160" spans="1:8">
+      <c r="A160" s="26"/>
+      <c r="B160" s="25"/>
+      <c r="C160" s="25"/>
+      <c r="D160" s="25"/>
+      <c r="E160" s="25"/>
+      <c r="F160" s="25"/>
+      <c r="G160" s="25"/>
+      <c r="H160" s="25"/>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" s="26"/>
+      <c r="B161" s="25"/>
+      <c r="C161" s="25"/>
+      <c r="D161" s="25"/>
+      <c r="E161" s="25"/>
+      <c r="F161" s="25"/>
+      <c r="G161" s="25"/>
+      <c r="H161" s="25"/>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" s="26"/>
+      <c r="B162" s="25"/>
+      <c r="C162" s="25"/>
+      <c r="D162" s="25"/>
+      <c r="E162" s="25"/>
+      <c r="F162" s="25"/>
+      <c r="G162" s="25"/>
+      <c r="H162" s="25"/>
+    </row>
+    <row r="163" spans="1:8">
+      <c r="A163" s="26"/>
+      <c r="B163" s="25"/>
+      <c r="C163" s="25"/>
+      <c r="D163" s="25"/>
+      <c r="E163" s="25"/>
+      <c r="F163" s="25"/>
+      <c r="G163" s="25"/>
+      <c r="H163" s="25"/>
+    </row>
+    <row r="164" spans="1:8">
+      <c r="A164" s="26"/>
+      <c r="B164" s="25"/>
+      <c r="C164" s="25"/>
+      <c r="D164" s="25"/>
+      <c r="E164" s="25"/>
+      <c r="F164" s="25"/>
+      <c r="G164" s="25"/>
+      <c r="H164" s="25"/>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165" s="26"/>
+      <c r="B165" s="25"/>
+      <c r="C165" s="25"/>
+      <c r="D165" s="25"/>
+      <c r="E165" s="25"/>
+      <c r="F165" s="25"/>
+      <c r="G165" s="25"/>
+      <c r="H165" s="25"/>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" s="26"/>
+      <c r="B166" s="25"/>
+      <c r="C166" s="25"/>
+      <c r="D166" s="25"/>
+      <c r="E166" s="25"/>
+      <c r="F166" s="25"/>
+      <c r="G166" s="25"/>
+      <c r="H166" s="25"/>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" s="26"/>
+      <c r="B167" s="25"/>
+      <c r="C167" s="25"/>
+      <c r="D167" s="25"/>
+      <c r="E167" s="25"/>
+      <c r="F167" s="25"/>
+      <c r="G167" s="25"/>
+      <c r="H167" s="25"/>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" s="26"/>
+      <c r="B168" s="25"/>
+      <c r="C168" s="25"/>
+      <c r="D168" s="25"/>
+      <c r="E168" s="25"/>
+      <c r="F168" s="25"/>
+      <c r="G168" s="25"/>
+      <c r="H168" s="25"/>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" s="26"/>
+      <c r="B169" s="25"/>
+      <c r="C169" s="25"/>
+      <c r="D169" s="25"/>
+      <c r="E169" s="25"/>
+      <c r="F169" s="25"/>
+      <c r="G169" s="25"/>
+      <c r="H169" s="25"/>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170" s="26"/>
+      <c r="B170" s="25"/>
+      <c r="C170" s="25"/>
+      <c r="D170" s="25"/>
+      <c r="E170" s="25"/>
+      <c r="F170" s="25"/>
+      <c r="G170" s="25"/>
+      <c r="H170" s="25"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:H170" xr:uid="{4997AC82-12EC-4AE6-8FAD-17E499A10CEB}">
+      <formula1>"〇,×,△"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823291FA-2F15-4108-B624-A9D156C8DF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5154E2D6-763D-4519-8AAF-F4FB9E513174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="243">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -1207,7 +1207,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1289,13 +1289,6 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="MS P ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1448,6 +1441,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1468,27 +1482,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1875,37 +1868,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="22.9">
-      <c r="A1" s="17"/>
-      <c r="B1" s="14" t="s">
+      <c r="A1" s="24"/>
+      <c r="B1" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
     </row>
     <row r="2" spans="1:28" ht="22.9">
-      <c r="A2" s="18"/>
-      <c r="B2" s="15"/>
+      <c r="A2" s="25"/>
+      <c r="B2" s="22"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="e" vm="1">
         <v>#VALUE!</v>
@@ -1942,8 +1935,8 @@
       <c r="AB2" s="5"/>
     </row>
     <row r="3" spans="1:28" s="13" customFormat="1" ht="90.4" thickBot="1">
-      <c r="A3" s="19"/>
-      <c r="B3" s="16"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="23"/>
       <c r="C3" s="11" t="s">
         <v>124</v>
       </c>
@@ -10026,1796 +10019,1810 @@
   <dimension ref="A2:H170"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
-    <col min="1" max="1" width="10.1875" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.8125" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.0625" style="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.9375" style="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="6.5625" style="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="23"/>
+    <col min="1" max="1" width="10.1875" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.8125" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.0625" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.9375" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="6.5625" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="16"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8">
-      <c r="A2" s="21"/>
-      <c r="B2" s="22" t="s">
+      <c r="A2" s="14"/>
+      <c r="B2" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="15" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="H4" s="25"/>
+      <c r="B4" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="H4" s="18"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
+      <c r="B6" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
+      <c r="B7" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
+      <c r="B11" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
+      <c r="B15" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
+      <c r="B16" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="B18" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="H18" s="25"/>
+      <c r="B18" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="B19" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="G19" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="H19" s="25"/>
+      <c r="B19" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="26"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="26"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="26"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="26"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="26"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="26"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="26"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="26"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="26"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="26"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="26"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="26"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
+      <c r="A35" s="19"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="26"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
+      <c r="A36" s="19"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="26"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
+      <c r="A37" s="19"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="26"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
+      <c r="A38" s="19"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="26"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
+      <c r="A39" s="19"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="26"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
+      <c r="A40" s="19"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="26"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
+      <c r="A41" s="19"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="26"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
+      <c r="A42" s="19"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="26"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="25"/>
+      <c r="A43" s="19"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="26"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="25"/>
+      <c r="A44" s="19"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="26"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="25"/>
+      <c r="A45" s="19"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="26"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="25"/>
+      <c r="A46" s="19"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="26"/>
-      <c r="B47" s="25"/>
-      <c r="C47" s="25"/>
-      <c r="D47" s="25"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="25"/>
+      <c r="A47" s="19"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="26"/>
-      <c r="B48" s="25"/>
-      <c r="C48" s="25"/>
-      <c r="D48" s="25"/>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25"/>
-      <c r="H48" s="25"/>
+      <c r="A48" s="19"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="26"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="25"/>
-      <c r="G49" s="25"/>
-      <c r="H49" s="25"/>
+      <c r="A49" s="19"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="26"/>
-      <c r="B50" s="25"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="25"/>
-      <c r="E50" s="25"/>
-      <c r="F50" s="25"/>
-      <c r="G50" s="25"/>
-      <c r="H50" s="25"/>
+      <c r="A50" s="19"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="26"/>
-      <c r="B51" s="25"/>
-      <c r="C51" s="25"/>
-      <c r="D51" s="25"/>
-      <c r="E51" s="25"/>
-      <c r="F51" s="25"/>
-      <c r="G51" s="25"/>
-      <c r="H51" s="25"/>
+      <c r="A51" s="19"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="26"/>
-      <c r="B52" s="25"/>
-      <c r="C52" s="25"/>
-      <c r="D52" s="25"/>
-      <c r="E52" s="25"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="25"/>
-      <c r="H52" s="25"/>
+      <c r="A52" s="19"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="26"/>
-      <c r="B53" s="25"/>
-      <c r="C53" s="25"/>
-      <c r="D53" s="25"/>
-      <c r="E53" s="25"/>
-      <c r="F53" s="25"/>
-      <c r="G53" s="25"/>
-      <c r="H53" s="25"/>
+      <c r="A53" s="19"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="26"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="25"/>
-      <c r="D54" s="25"/>
-      <c r="E54" s="25"/>
-      <c r="F54" s="25"/>
-      <c r="G54" s="25"/>
-      <c r="H54" s="25"/>
+      <c r="A54" s="19"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="26"/>
-      <c r="B55" s="25"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
+      <c r="A55" s="19"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="26"/>
-      <c r="B56" s="25"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
-      <c r="H56" s="25"/>
+      <c r="A56" s="19"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="26"/>
-      <c r="B57" s="25"/>
-      <c r="C57" s="25"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="25"/>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25"/>
-      <c r="H57" s="25"/>
+      <c r="A57" s="19"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="18"/>
+      <c r="H57" s="18"/>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="26"/>
-      <c r="B58" s="25"/>
-      <c r="C58" s="25"/>
-      <c r="D58" s="25"/>
-      <c r="E58" s="25"/>
-      <c r="F58" s="25"/>
-      <c r="G58" s="25"/>
-      <c r="H58" s="25"/>
+      <c r="A58" s="19"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="18"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="26"/>
-      <c r="B59" s="25"/>
-      <c r="C59" s="25"/>
-      <c r="D59" s="25"/>
-      <c r="E59" s="25"/>
-      <c r="F59" s="25"/>
-      <c r="G59" s="25"/>
-      <c r="H59" s="25"/>
+      <c r="A59" s="19"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="18"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="26"/>
-      <c r="B60" s="25"/>
-      <c r="C60" s="25"/>
-      <c r="D60" s="25"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="25"/>
-      <c r="H60" s="25"/>
+      <c r="A60" s="19"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="26"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="25"/>
-      <c r="H61" s="25"/>
+      <c r="A61" s="19"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="18"/>
+      <c r="H61" s="18"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="26"/>
-      <c r="B62" s="25"/>
-      <c r="C62" s="25"/>
-      <c r="D62" s="25"/>
-      <c r="E62" s="25"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
-      <c r="H62" s="25"/>
+      <c r="A62" s="19"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="18"/>
+      <c r="H62" s="18"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="26"/>
-      <c r="B63" s="25"/>
-      <c r="C63" s="25"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
-      <c r="H63" s="25"/>
+      <c r="A63" s="19"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="18"/>
+      <c r="H63" s="18"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="26"/>
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="25"/>
-      <c r="G64" s="25"/>
-      <c r="H64" s="25"/>
+      <c r="A64" s="19"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="18"/>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="26"/>
-      <c r="B65" s="25"/>
-      <c r="C65" s="25"/>
-      <c r="D65" s="25"/>
-      <c r="E65" s="25"/>
-      <c r="F65" s="25"/>
-      <c r="G65" s="25"/>
-      <c r="H65" s="25"/>
+      <c r="A65" s="19"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="18"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="26"/>
-      <c r="B66" s="25"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="25"/>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="25"/>
+      <c r="A66" s="19"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="18"/>
+      <c r="H66" s="18"/>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="26"/>
-      <c r="B67" s="25"/>
-      <c r="C67" s="25"/>
-      <c r="D67" s="25"/>
-      <c r="E67" s="25"/>
-      <c r="F67" s="25"/>
-      <c r="G67" s="25"/>
-      <c r="H67" s="25"/>
+      <c r="A67" s="19"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="18"/>
+      <c r="H67" s="18"/>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="26"/>
-      <c r="B68" s="25"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="25"/>
-      <c r="E68" s="25"/>
-      <c r="F68" s="25"/>
-      <c r="G68" s="25"/>
-      <c r="H68" s="25"/>
+      <c r="A68" s="19"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="18"/>
+      <c r="H68" s="18"/>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="26"/>
-      <c r="B69" s="25"/>
-      <c r="C69" s="25"/>
-      <c r="D69" s="25"/>
-      <c r="E69" s="25"/>
-      <c r="F69" s="25"/>
-      <c r="G69" s="25"/>
-      <c r="H69" s="25"/>
+      <c r="A69" s="19"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="18"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="18"/>
+      <c r="H69" s="18"/>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="26"/>
-      <c r="B70" s="25"/>
-      <c r="C70" s="25"/>
-      <c r="D70" s="25"/>
-      <c r="E70" s="25"/>
-      <c r="F70" s="25"/>
-      <c r="G70" s="25"/>
-      <c r="H70" s="25"/>
+      <c r="A70" s="19"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="26"/>
-      <c r="B71" s="25"/>
-      <c r="C71" s="25"/>
-      <c r="D71" s="25"/>
-      <c r="E71" s="25"/>
-      <c r="F71" s="25"/>
-      <c r="G71" s="25"/>
-      <c r="H71" s="25"/>
+      <c r="A71" s="19"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18"/>
+      <c r="E71" s="18"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18"/>
+      <c r="H71" s="18"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="26"/>
-      <c r="B72" s="25"/>
-      <c r="C72" s="25"/>
-      <c r="D72" s="25"/>
-      <c r="E72" s="25"/>
-      <c r="F72" s="25"/>
-      <c r="G72" s="25"/>
-      <c r="H72" s="25"/>
+      <c r="A72" s="19"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="18"/>
+      <c r="H72" s="18"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="26"/>
-      <c r="B73" s="25"/>
-      <c r="C73" s="25"/>
-      <c r="D73" s="25"/>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="25"/>
-      <c r="H73" s="25"/>
+      <c r="A73" s="19"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="18"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="26"/>
-      <c r="B74" s="25"/>
-      <c r="C74" s="25"/>
-      <c r="D74" s="25"/>
-      <c r="E74" s="25"/>
-      <c r="F74" s="25"/>
-      <c r="G74" s="25"/>
-      <c r="H74" s="25"/>
+      <c r="A74" s="19"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="18"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="18"/>
+      <c r="H74" s="18"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="26"/>
-      <c r="B75" s="25"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="25"/>
-      <c r="E75" s="25"/>
-      <c r="F75" s="25"/>
-      <c r="G75" s="25"/>
-      <c r="H75" s="25"/>
+      <c r="A75" s="19"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="18"/>
+      <c r="H75" s="18"/>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="26"/>
-      <c r="B76" s="25"/>
-      <c r="C76" s="25"/>
-      <c r="D76" s="25"/>
-      <c r="E76" s="25"/>
-      <c r="F76" s="25"/>
-      <c r="G76" s="25"/>
-      <c r="H76" s="25"/>
+      <c r="A76" s="19"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="18"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="18"/>
+      <c r="H76" s="18"/>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="26"/>
-      <c r="B77" s="25"/>
-      <c r="C77" s="25"/>
-      <c r="D77" s="25"/>
-      <c r="E77" s="25"/>
-      <c r="F77" s="25"/>
-      <c r="G77" s="25"/>
-      <c r="H77" s="25"/>
+      <c r="A77" s="19"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
+      <c r="F77" s="18"/>
+      <c r="G77" s="18"/>
+      <c r="H77" s="18"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="26"/>
-      <c r="B78" s="25"/>
-      <c r="C78" s="25"/>
-      <c r="D78" s="25"/>
-      <c r="E78" s="25"/>
-      <c r="F78" s="25"/>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25"/>
+      <c r="A78" s="19"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="18"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="18"/>
+      <c r="H78" s="18"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="26"/>
-      <c r="B79" s="25"/>
-      <c r="C79" s="25"/>
-      <c r="D79" s="25"/>
-      <c r="E79" s="25"/>
-      <c r="F79" s="25"/>
-      <c r="G79" s="25"/>
-      <c r="H79" s="25"/>
+      <c r="A79" s="19"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="18"/>
+      <c r="E79" s="18"/>
+      <c r="F79" s="18"/>
+      <c r="G79" s="18"/>
+      <c r="H79" s="18"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="26"/>
-      <c r="B80" s="25"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="25"/>
-      <c r="E80" s="25"/>
-      <c r="F80" s="25"/>
-      <c r="G80" s="25"/>
-      <c r="H80" s="25"/>
+      <c r="A80" s="19"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="18"/>
+      <c r="D80" s="18"/>
+      <c r="E80" s="18"/>
+      <c r="F80" s="18"/>
+      <c r="G80" s="18"/>
+      <c r="H80" s="18"/>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="26"/>
-      <c r="B81" s="25"/>
-      <c r="C81" s="25"/>
-      <c r="D81" s="25"/>
-      <c r="E81" s="25"/>
-      <c r="F81" s="25"/>
-      <c r="G81" s="25"/>
-      <c r="H81" s="25"/>
+      <c r="A81" s="19"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="18"/>
+      <c r="D81" s="18"/>
+      <c r="E81" s="18"/>
+      <c r="F81" s="18"/>
+      <c r="G81" s="18"/>
+      <c r="H81" s="18"/>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="26"/>
-      <c r="B82" s="25"/>
-      <c r="C82" s="25"/>
-      <c r="D82" s="25"/>
-      <c r="E82" s="25"/>
-      <c r="F82" s="25"/>
-      <c r="G82" s="25"/>
-      <c r="H82" s="25"/>
+      <c r="A82" s="19"/>
+      <c r="B82" s="18"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18"/>
+      <c r="G82" s="18"/>
+      <c r="H82" s="18"/>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="26"/>
-      <c r="B83" s="25"/>
-      <c r="C83" s="25"/>
-      <c r="D83" s="25"/>
-      <c r="E83" s="25"/>
-      <c r="F83" s="25"/>
-      <c r="G83" s="25"/>
-      <c r="H83" s="25"/>
+      <c r="A83" s="19"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="18"/>
+      <c r="F83" s="18"/>
+      <c r="G83" s="18"/>
+      <c r="H83" s="18"/>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="26"/>
-      <c r="B84" s="25"/>
-      <c r="C84" s="25"/>
-      <c r="D84" s="25"/>
-      <c r="E84" s="25"/>
-      <c r="F84" s="25"/>
-      <c r="G84" s="25"/>
-      <c r="H84" s="25"/>
+      <c r="A84" s="19"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="18"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="18"/>
+      <c r="H84" s="18"/>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="26"/>
-      <c r="B85" s="25"/>
-      <c r="C85" s="25"/>
-      <c r="D85" s="25"/>
-      <c r="E85" s="25"/>
-      <c r="F85" s="25"/>
-      <c r="G85" s="25"/>
-      <c r="H85" s="25"/>
+      <c r="A85" s="19"/>
+      <c r="B85" s="18"/>
+      <c r="C85" s="18"/>
+      <c r="D85" s="18"/>
+      <c r="E85" s="18"/>
+      <c r="F85" s="18"/>
+      <c r="G85" s="18"/>
+      <c r="H85" s="18"/>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="26"/>
-      <c r="B86" s="25"/>
-      <c r="C86" s="25"/>
-      <c r="D86" s="25"/>
-      <c r="E86" s="25"/>
-      <c r="F86" s="25"/>
-      <c r="G86" s="25"/>
-      <c r="H86" s="25"/>
+      <c r="A86" s="19"/>
+      <c r="B86" s="18"/>
+      <c r="C86" s="18"/>
+      <c r="D86" s="18"/>
+      <c r="E86" s="18"/>
+      <c r="F86" s="18"/>
+      <c r="G86" s="18"/>
+      <c r="H86" s="18"/>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="26"/>
-      <c r="B87" s="25"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="25"/>
-      <c r="E87" s="25"/>
-      <c r="F87" s="25"/>
-      <c r="G87" s="25"/>
-      <c r="H87" s="25"/>
+      <c r="A87" s="19"/>
+      <c r="B87" s="18"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="18"/>
+      <c r="E87" s="18"/>
+      <c r="F87" s="18"/>
+      <c r="G87" s="18"/>
+      <c r="H87" s="18"/>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="26"/>
-      <c r="B88" s="25"/>
-      <c r="C88" s="25"/>
-      <c r="D88" s="25"/>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25"/>
-      <c r="H88" s="25"/>
+      <c r="A88" s="19"/>
+      <c r="B88" s="18"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="18"/>
+      <c r="E88" s="18"/>
+      <c r="F88" s="18"/>
+      <c r="G88" s="18"/>
+      <c r="H88" s="18"/>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="26"/>
-      <c r="B89" s="25"/>
-      <c r="C89" s="25"/>
-      <c r="D89" s="25"/>
-      <c r="E89" s="25"/>
-      <c r="F89" s="25"/>
-      <c r="G89" s="25"/>
-      <c r="H89" s="25"/>
+      <c r="A89" s="19"/>
+      <c r="B89" s="18"/>
+      <c r="C89" s="18"/>
+      <c r="D89" s="18"/>
+      <c r="E89" s="18"/>
+      <c r="F89" s="18"/>
+      <c r="G89" s="18"/>
+      <c r="H89" s="18"/>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="26"/>
-      <c r="B90" s="25"/>
-      <c r="C90" s="25"/>
-      <c r="D90" s="25"/>
-      <c r="E90" s="25"/>
-      <c r="F90" s="25"/>
-      <c r="G90" s="25"/>
-      <c r="H90" s="25"/>
+      <c r="A90" s="19"/>
+      <c r="B90" s="18"/>
+      <c r="C90" s="18"/>
+      <c r="D90" s="18"/>
+      <c r="E90" s="18"/>
+      <c r="F90" s="18"/>
+      <c r="G90" s="18"/>
+      <c r="H90" s="18"/>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="26"/>
-      <c r="B91" s="25"/>
-      <c r="C91" s="25"/>
-      <c r="D91" s="25"/>
-      <c r="E91" s="25"/>
-      <c r="F91" s="25"/>
-      <c r="G91" s="25"/>
-      <c r="H91" s="25"/>
+      <c r="A91" s="19"/>
+      <c r="B91" s="18"/>
+      <c r="C91" s="18"/>
+      <c r="D91" s="18"/>
+      <c r="E91" s="18"/>
+      <c r="F91" s="18"/>
+      <c r="G91" s="18"/>
+      <c r="H91" s="18"/>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="26"/>
-      <c r="B92" s="25"/>
-      <c r="C92" s="25"/>
-      <c r="D92" s="25"/>
-      <c r="E92" s="25"/>
-      <c r="F92" s="25"/>
-      <c r="G92" s="25"/>
-      <c r="H92" s="25"/>
+      <c r="A92" s="19"/>
+      <c r="B92" s="18"/>
+      <c r="C92" s="18"/>
+      <c r="D92" s="18"/>
+      <c r="E92" s="18"/>
+      <c r="F92" s="18"/>
+      <c r="G92" s="18"/>
+      <c r="H92" s="18"/>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="26"/>
-      <c r="B93" s="25"/>
-      <c r="C93" s="25"/>
-      <c r="D93" s="25"/>
-      <c r="E93" s="25"/>
-      <c r="F93" s="25"/>
-      <c r="G93" s="25"/>
-      <c r="H93" s="25"/>
+      <c r="A93" s="19"/>
+      <c r="B93" s="18"/>
+      <c r="C93" s="18"/>
+      <c r="D93" s="18"/>
+      <c r="E93" s="18"/>
+      <c r="F93" s="18"/>
+      <c r="G93" s="18"/>
+      <c r="H93" s="18"/>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="26"/>
-      <c r="B94" s="25"/>
-      <c r="C94" s="25"/>
-      <c r="D94" s="25"/>
-      <c r="E94" s="25"/>
-      <c r="F94" s="25"/>
-      <c r="G94" s="25"/>
-      <c r="H94" s="25"/>
+      <c r="A94" s="19"/>
+      <c r="B94" s="18"/>
+      <c r="C94" s="18"/>
+      <c r="D94" s="18"/>
+      <c r="E94" s="18"/>
+      <c r="F94" s="18"/>
+      <c r="G94" s="18"/>
+      <c r="H94" s="18"/>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="26"/>
-      <c r="B95" s="25"/>
-      <c r="C95" s="25"/>
-      <c r="D95" s="25"/>
-      <c r="E95" s="25"/>
-      <c r="F95" s="25"/>
-      <c r="G95" s="25"/>
-      <c r="H95" s="25"/>
+      <c r="A95" s="19"/>
+      <c r="B95" s="18"/>
+      <c r="C95" s="18"/>
+      <c r="D95" s="18"/>
+      <c r="E95" s="18"/>
+      <c r="F95" s="18"/>
+      <c r="G95" s="18"/>
+      <c r="H95" s="18"/>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="26"/>
-      <c r="B96" s="25"/>
-      <c r="C96" s="25"/>
-      <c r="D96" s="25"/>
-      <c r="E96" s="25"/>
-      <c r="F96" s="25"/>
-      <c r="G96" s="25"/>
-      <c r="H96" s="25"/>
+      <c r="A96" s="19"/>
+      <c r="B96" s="18"/>
+      <c r="C96" s="18"/>
+      <c r="D96" s="18"/>
+      <c r="E96" s="18"/>
+      <c r="F96" s="18"/>
+      <c r="G96" s="18"/>
+      <c r="H96" s="18"/>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="26"/>
-      <c r="B97" s="25"/>
-      <c r="C97" s="25"/>
-      <c r="D97" s="25"/>
-      <c r="E97" s="25"/>
-      <c r="F97" s="25"/>
-      <c r="G97" s="25"/>
-      <c r="H97" s="25"/>
+      <c r="A97" s="19"/>
+      <c r="B97" s="18"/>
+      <c r="C97" s="18"/>
+      <c r="D97" s="18"/>
+      <c r="E97" s="18"/>
+      <c r="F97" s="18"/>
+      <c r="G97" s="18"/>
+      <c r="H97" s="18"/>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="26"/>
-      <c r="B98" s="25"/>
-      <c r="C98" s="25"/>
-      <c r="D98" s="25"/>
-      <c r="E98" s="25"/>
-      <c r="F98" s="25"/>
-      <c r="G98" s="25"/>
-      <c r="H98" s="25"/>
+      <c r="A98" s="19"/>
+      <c r="B98" s="18"/>
+      <c r="C98" s="18"/>
+      <c r="D98" s="18"/>
+      <c r="E98" s="18"/>
+      <c r="F98" s="18"/>
+      <c r="G98" s="18"/>
+      <c r="H98" s="18"/>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="26"/>
-      <c r="B99" s="25"/>
-      <c r="C99" s="25"/>
-      <c r="D99" s="25"/>
-      <c r="E99" s="25"/>
-      <c r="F99" s="25"/>
-      <c r="G99" s="25"/>
-      <c r="H99" s="25"/>
+      <c r="A99" s="19"/>
+      <c r="B99" s="18"/>
+      <c r="C99" s="18"/>
+      <c r="D99" s="18"/>
+      <c r="E99" s="18"/>
+      <c r="F99" s="18"/>
+      <c r="G99" s="18"/>
+      <c r="H99" s="18"/>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="26"/>
-      <c r="B100" s="25"/>
-      <c r="C100" s="25"/>
-      <c r="D100" s="25"/>
-      <c r="E100" s="25"/>
-      <c r="F100" s="25"/>
-      <c r="G100" s="25"/>
-      <c r="H100" s="25"/>
+      <c r="A100" s="19"/>
+      <c r="B100" s="18"/>
+      <c r="C100" s="18"/>
+      <c r="D100" s="18"/>
+      <c r="E100" s="18"/>
+      <c r="F100" s="18"/>
+      <c r="G100" s="18"/>
+      <c r="H100" s="18"/>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="26"/>
-      <c r="B101" s="25"/>
-      <c r="C101" s="25"/>
-      <c r="D101" s="25"/>
-      <c r="E101" s="25"/>
-      <c r="F101" s="25"/>
-      <c r="G101" s="25"/>
-      <c r="H101" s="25"/>
+      <c r="A101" s="19"/>
+      <c r="B101" s="18"/>
+      <c r="C101" s="18"/>
+      <c r="D101" s="18"/>
+      <c r="E101" s="18"/>
+      <c r="F101" s="18"/>
+      <c r="G101" s="18"/>
+      <c r="H101" s="18"/>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="26"/>
-      <c r="B102" s="25"/>
-      <c r="C102" s="25"/>
-      <c r="D102" s="25"/>
-      <c r="E102" s="25"/>
-      <c r="F102" s="25"/>
-      <c r="G102" s="25"/>
-      <c r="H102" s="25"/>
+      <c r="A102" s="19"/>
+      <c r="B102" s="18"/>
+      <c r="C102" s="18"/>
+      <c r="D102" s="18"/>
+      <c r="E102" s="18"/>
+      <c r="F102" s="18"/>
+      <c r="G102" s="18"/>
+      <c r="H102" s="18"/>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="26"/>
-      <c r="B103" s="25"/>
-      <c r="C103" s="25"/>
-      <c r="D103" s="25"/>
-      <c r="E103" s="25"/>
-      <c r="F103" s="25"/>
-      <c r="G103" s="25"/>
-      <c r="H103" s="25"/>
+      <c r="A103" s="19"/>
+      <c r="B103" s="18"/>
+      <c r="C103" s="18"/>
+      <c r="D103" s="18"/>
+      <c r="E103" s="18"/>
+      <c r="F103" s="18"/>
+      <c r="G103" s="18"/>
+      <c r="H103" s="18"/>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="26"/>
-      <c r="B104" s="25"/>
-      <c r="C104" s="25"/>
-      <c r="D104" s="25"/>
-      <c r="E104" s="25"/>
-      <c r="F104" s="25"/>
-      <c r="G104" s="25"/>
-      <c r="H104" s="25"/>
+      <c r="A104" s="19"/>
+      <c r="B104" s="18"/>
+      <c r="C104" s="18"/>
+      <c r="D104" s="18"/>
+      <c r="E104" s="18"/>
+      <c r="F104" s="18"/>
+      <c r="G104" s="18"/>
+      <c r="H104" s="18"/>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="26"/>
-      <c r="B105" s="25"/>
-      <c r="C105" s="25"/>
-      <c r="D105" s="25"/>
-      <c r="E105" s="25"/>
-      <c r="F105" s="25"/>
-      <c r="G105" s="25"/>
-      <c r="H105" s="25"/>
+      <c r="A105" s="19"/>
+      <c r="B105" s="18"/>
+      <c r="C105" s="18"/>
+      <c r="D105" s="18"/>
+      <c r="E105" s="18"/>
+      <c r="F105" s="18"/>
+      <c r="G105" s="18"/>
+      <c r="H105" s="18"/>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="26"/>
-      <c r="B106" s="25"/>
-      <c r="C106" s="25"/>
-      <c r="D106" s="25"/>
-      <c r="E106" s="25"/>
-      <c r="F106" s="25"/>
-      <c r="G106" s="25"/>
-      <c r="H106" s="25"/>
+      <c r="A106" s="19"/>
+      <c r="B106" s="18"/>
+      <c r="C106" s="18"/>
+      <c r="D106" s="18"/>
+      <c r="E106" s="18"/>
+      <c r="F106" s="18"/>
+      <c r="G106" s="18"/>
+      <c r="H106" s="18"/>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="26"/>
-      <c r="B107" s="25"/>
-      <c r="C107" s="25"/>
-      <c r="D107" s="25"/>
-      <c r="E107" s="25"/>
-      <c r="F107" s="25"/>
-      <c r="G107" s="25"/>
-      <c r="H107" s="25"/>
+      <c r="A107" s="19"/>
+      <c r="B107" s="18"/>
+      <c r="C107" s="18"/>
+      <c r="D107" s="18"/>
+      <c r="E107" s="18"/>
+      <c r="F107" s="18"/>
+      <c r="G107" s="18"/>
+      <c r="H107" s="18"/>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="26"/>
-      <c r="B108" s="25"/>
-      <c r="C108" s="25"/>
-      <c r="D108" s="25"/>
-      <c r="E108" s="25"/>
-      <c r="F108" s="25"/>
-      <c r="G108" s="25"/>
-      <c r="H108" s="25"/>
+      <c r="A108" s="19"/>
+      <c r="B108" s="18"/>
+      <c r="C108" s="18"/>
+      <c r="D108" s="18"/>
+      <c r="E108" s="18"/>
+      <c r="F108" s="18"/>
+      <c r="G108" s="18"/>
+      <c r="H108" s="18"/>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="26"/>
-      <c r="B109" s="25"/>
-      <c r="C109" s="25"/>
-      <c r="D109" s="25"/>
-      <c r="E109" s="25"/>
-      <c r="F109" s="25"/>
-      <c r="G109" s="25"/>
-      <c r="H109" s="25"/>
+      <c r="A109" s="19"/>
+      <c r="B109" s="18"/>
+      <c r="C109" s="18"/>
+      <c r="D109" s="18"/>
+      <c r="E109" s="18"/>
+      <c r="F109" s="18"/>
+      <c r="G109" s="18"/>
+      <c r="H109" s="18"/>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="26"/>
-      <c r="B110" s="25"/>
-      <c r="C110" s="25"/>
-      <c r="D110" s="25"/>
-      <c r="E110" s="25"/>
-      <c r="F110" s="25"/>
-      <c r="G110" s="25"/>
-      <c r="H110" s="25"/>
+      <c r="A110" s="19"/>
+      <c r="B110" s="18"/>
+      <c r="C110" s="18"/>
+      <c r="D110" s="18"/>
+      <c r="E110" s="18"/>
+      <c r="F110" s="18"/>
+      <c r="G110" s="18"/>
+      <c r="H110" s="18"/>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="26"/>
-      <c r="B111" s="25"/>
-      <c r="C111" s="25"/>
-      <c r="D111" s="25"/>
-      <c r="E111" s="25"/>
-      <c r="F111" s="25"/>
-      <c r="G111" s="25"/>
-      <c r="H111" s="25"/>
+      <c r="A111" s="19"/>
+      <c r="B111" s="18"/>
+      <c r="C111" s="18"/>
+      <c r="D111" s="18"/>
+      <c r="E111" s="18"/>
+      <c r="F111" s="18"/>
+      <c r="G111" s="18"/>
+      <c r="H111" s="18"/>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="26"/>
-      <c r="B112" s="25"/>
-      <c r="C112" s="25"/>
-      <c r="D112" s="25"/>
-      <c r="E112" s="25"/>
-      <c r="F112" s="25"/>
-      <c r="G112" s="25"/>
-      <c r="H112" s="25"/>
+      <c r="A112" s="19"/>
+      <c r="B112" s="18"/>
+      <c r="C112" s="18"/>
+      <c r="D112" s="18"/>
+      <c r="E112" s="18"/>
+      <c r="F112" s="18"/>
+      <c r="G112" s="18"/>
+      <c r="H112" s="18"/>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="26"/>
-      <c r="B113" s="25"/>
-      <c r="C113" s="25"/>
-      <c r="D113" s="25"/>
-      <c r="E113" s="25"/>
-      <c r="F113" s="25"/>
-      <c r="G113" s="25"/>
-      <c r="H113" s="25"/>
+      <c r="A113" s="19"/>
+      <c r="B113" s="18"/>
+      <c r="C113" s="18"/>
+      <c r="D113" s="18"/>
+      <c r="E113" s="18"/>
+      <c r="F113" s="18"/>
+      <c r="G113" s="18"/>
+      <c r="H113" s="18"/>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="26"/>
-      <c r="B114" s="25"/>
-      <c r="C114" s="25"/>
-      <c r="D114" s="25"/>
-      <c r="E114" s="25"/>
-      <c r="F114" s="25"/>
-      <c r="G114" s="25"/>
-      <c r="H114" s="25"/>
+      <c r="A114" s="19"/>
+      <c r="B114" s="18"/>
+      <c r="C114" s="18"/>
+      <c r="D114" s="18"/>
+      <c r="E114" s="18"/>
+      <c r="F114" s="18"/>
+      <c r="G114" s="18"/>
+      <c r="H114" s="18"/>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="26"/>
-      <c r="B115" s="25"/>
-      <c r="C115" s="25"/>
-      <c r="D115" s="25"/>
-      <c r="E115" s="25"/>
-      <c r="F115" s="25"/>
-      <c r="G115" s="25"/>
-      <c r="H115" s="25"/>
+      <c r="A115" s="19"/>
+      <c r="B115" s="18"/>
+      <c r="C115" s="18"/>
+      <c r="D115" s="18"/>
+      <c r="E115" s="18"/>
+      <c r="F115" s="18"/>
+      <c r="G115" s="18"/>
+      <c r="H115" s="18"/>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="26"/>
-      <c r="B116" s="25"/>
-      <c r="C116" s="25"/>
-      <c r="D116" s="25"/>
-      <c r="E116" s="25"/>
-      <c r="F116" s="25"/>
-      <c r="G116" s="25"/>
-      <c r="H116" s="25"/>
+      <c r="A116" s="19"/>
+      <c r="B116" s="18"/>
+      <c r="C116" s="18"/>
+      <c r="D116" s="18"/>
+      <c r="E116" s="18"/>
+      <c r="F116" s="18"/>
+      <c r="G116" s="18"/>
+      <c r="H116" s="18"/>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="26"/>
-      <c r="B117" s="25"/>
-      <c r="C117" s="25"/>
-      <c r="D117" s="25"/>
-      <c r="E117" s="25"/>
-      <c r="F117" s="25"/>
-      <c r="G117" s="25"/>
-      <c r="H117" s="25"/>
+      <c r="A117" s="19"/>
+      <c r="B117" s="18"/>
+      <c r="C117" s="18"/>
+      <c r="D117" s="18"/>
+      <c r="E117" s="18"/>
+      <c r="F117" s="18"/>
+      <c r="G117" s="18"/>
+      <c r="H117" s="18"/>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="26"/>
-      <c r="B118" s="25"/>
-      <c r="C118" s="25"/>
-      <c r="D118" s="25"/>
-      <c r="E118" s="25"/>
-      <c r="F118" s="25"/>
-      <c r="G118" s="25"/>
-      <c r="H118" s="25"/>
+      <c r="A118" s="19"/>
+      <c r="B118" s="18"/>
+      <c r="C118" s="18"/>
+      <c r="D118" s="18"/>
+      <c r="E118" s="18"/>
+      <c r="F118" s="18"/>
+      <c r="G118" s="18"/>
+      <c r="H118" s="18"/>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="26"/>
-      <c r="B119" s="25"/>
-      <c r="C119" s="25"/>
-      <c r="D119" s="25"/>
-      <c r="E119" s="25"/>
-      <c r="F119" s="25"/>
-      <c r="G119" s="25"/>
-      <c r="H119" s="25"/>
+      <c r="A119" s="19"/>
+      <c r="B119" s="18"/>
+      <c r="C119" s="18"/>
+      <c r="D119" s="18"/>
+      <c r="E119" s="18"/>
+      <c r="F119" s="18"/>
+      <c r="G119" s="18"/>
+      <c r="H119" s="18"/>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="26"/>
-      <c r="B120" s="25"/>
-      <c r="C120" s="25"/>
-      <c r="D120" s="25"/>
-      <c r="E120" s="25"/>
-      <c r="F120" s="25"/>
-      <c r="G120" s="25"/>
-      <c r="H120" s="25"/>
+      <c r="A120" s="19"/>
+      <c r="B120" s="18"/>
+      <c r="C120" s="18"/>
+      <c r="D120" s="18"/>
+      <c r="E120" s="18"/>
+      <c r="F120" s="18"/>
+      <c r="G120" s="18"/>
+      <c r="H120" s="18"/>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" s="26"/>
-      <c r="B121" s="25"/>
-      <c r="C121" s="25"/>
-      <c r="D121" s="25"/>
-      <c r="E121" s="25"/>
-      <c r="F121" s="25"/>
-      <c r="G121" s="25"/>
-      <c r="H121" s="25"/>
+      <c r="A121" s="19"/>
+      <c r="B121" s="18"/>
+      <c r="C121" s="18"/>
+      <c r="D121" s="18"/>
+      <c r="E121" s="18"/>
+      <c r="F121" s="18"/>
+      <c r="G121" s="18"/>
+      <c r="H121" s="18"/>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="26"/>
-      <c r="B122" s="25"/>
-      <c r="C122" s="25"/>
-      <c r="D122" s="25"/>
-      <c r="E122" s="25"/>
-      <c r="F122" s="25"/>
-      <c r="G122" s="25"/>
-      <c r="H122" s="25"/>
+      <c r="A122" s="19"/>
+      <c r="B122" s="18"/>
+      <c r="C122" s="18"/>
+      <c r="D122" s="18"/>
+      <c r="E122" s="18"/>
+      <c r="F122" s="18"/>
+      <c r="G122" s="18"/>
+      <c r="H122" s="18"/>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="26"/>
-      <c r="B123" s="25"/>
-      <c r="C123" s="25"/>
-      <c r="D123" s="25"/>
-      <c r="E123" s="25"/>
-      <c r="F123" s="25"/>
-      <c r="G123" s="25"/>
-      <c r="H123" s="25"/>
+      <c r="A123" s="19"/>
+      <c r="B123" s="18"/>
+      <c r="C123" s="18"/>
+      <c r="D123" s="18"/>
+      <c r="E123" s="18"/>
+      <c r="F123" s="18"/>
+      <c r="G123" s="18"/>
+      <c r="H123" s="18"/>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" s="26"/>
-      <c r="B124" s="25"/>
-      <c r="C124" s="25"/>
-      <c r="D124" s="25"/>
-      <c r="E124" s="25"/>
-      <c r="F124" s="25"/>
-      <c r="G124" s="25"/>
-      <c r="H124" s="25"/>
+      <c r="A124" s="19"/>
+      <c r="B124" s="18"/>
+      <c r="C124" s="18"/>
+      <c r="D124" s="18"/>
+      <c r="E124" s="18"/>
+      <c r="F124" s="18"/>
+      <c r="G124" s="18"/>
+      <c r="H124" s="18"/>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="26"/>
-      <c r="B125" s="25"/>
-      <c r="C125" s="25"/>
-      <c r="D125" s="25"/>
-      <c r="E125" s="25"/>
-      <c r="F125" s="25"/>
-      <c r="G125" s="25"/>
-      <c r="H125" s="25"/>
+      <c r="A125" s="19"/>
+      <c r="B125" s="18"/>
+      <c r="C125" s="18"/>
+      <c r="D125" s="18"/>
+      <c r="E125" s="18"/>
+      <c r="F125" s="18"/>
+      <c r="G125" s="18"/>
+      <c r="H125" s="18"/>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="26"/>
-      <c r="B126" s="25"/>
-      <c r="C126" s="25"/>
-      <c r="D126" s="25"/>
-      <c r="E126" s="25"/>
-      <c r="F126" s="25"/>
-      <c r="G126" s="25"/>
-      <c r="H126" s="25"/>
+      <c r="A126" s="19"/>
+      <c r="B126" s="18"/>
+      <c r="C126" s="18"/>
+      <c r="D126" s="18"/>
+      <c r="E126" s="18"/>
+      <c r="F126" s="18"/>
+      <c r="G126" s="18"/>
+      <c r="H126" s="18"/>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" s="26"/>
-      <c r="B127" s="25"/>
-      <c r="C127" s="25"/>
-      <c r="D127" s="25"/>
-      <c r="E127" s="25"/>
-      <c r="F127" s="25"/>
-      <c r="G127" s="25"/>
-      <c r="H127" s="25"/>
+      <c r="A127" s="19"/>
+      <c r="B127" s="18"/>
+      <c r="C127" s="18"/>
+      <c r="D127" s="18"/>
+      <c r="E127" s="18"/>
+      <c r="F127" s="18"/>
+      <c r="G127" s="18"/>
+      <c r="H127" s="18"/>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="26"/>
-      <c r="B128" s="25"/>
-      <c r="C128" s="25"/>
-      <c r="D128" s="25"/>
-      <c r="E128" s="25"/>
-      <c r="F128" s="25"/>
-      <c r="G128" s="25"/>
-      <c r="H128" s="25"/>
+      <c r="A128" s="19"/>
+      <c r="B128" s="18"/>
+      <c r="C128" s="18"/>
+      <c r="D128" s="18"/>
+      <c r="E128" s="18"/>
+      <c r="F128" s="18"/>
+      <c r="G128" s="18"/>
+      <c r="H128" s="18"/>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="26"/>
-      <c r="B129" s="25"/>
-      <c r="C129" s="25"/>
-      <c r="D129" s="25"/>
-      <c r="E129" s="25"/>
-      <c r="F129" s="25"/>
-      <c r="G129" s="25"/>
-      <c r="H129" s="25"/>
+      <c r="A129" s="19"/>
+      <c r="B129" s="18"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="18"/>
+      <c r="E129" s="18"/>
+      <c r="F129" s="18"/>
+      <c r="G129" s="18"/>
+      <c r="H129" s="18"/>
     </row>
     <row r="130" spans="1:8">
-      <c r="A130" s="26"/>
-      <c r="B130" s="25"/>
-      <c r="C130" s="25"/>
-      <c r="D130" s="25"/>
-      <c r="E130" s="25"/>
-      <c r="F130" s="25"/>
-      <c r="G130" s="25"/>
-      <c r="H130" s="25"/>
+      <c r="A130" s="19"/>
+      <c r="B130" s="18"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="18"/>
+      <c r="E130" s="18"/>
+      <c r="F130" s="18"/>
+      <c r="G130" s="18"/>
+      <c r="H130" s="18"/>
     </row>
     <row r="131" spans="1:8">
-      <c r="A131" s="26"/>
-      <c r="B131" s="25"/>
-      <c r="C131" s="25"/>
-      <c r="D131" s="25"/>
-      <c r="E131" s="25"/>
-      <c r="F131" s="25"/>
-      <c r="G131" s="25"/>
-      <c r="H131" s="25"/>
+      <c r="A131" s="19"/>
+      <c r="B131" s="18"/>
+      <c r="C131" s="18"/>
+      <c r="D131" s="18"/>
+      <c r="E131" s="18"/>
+      <c r="F131" s="18"/>
+      <c r="G131" s="18"/>
+      <c r="H131" s="18"/>
     </row>
     <row r="132" spans="1:8">
-      <c r="A132" s="26"/>
-      <c r="B132" s="25"/>
-      <c r="C132" s="25"/>
-      <c r="D132" s="25"/>
-      <c r="E132" s="25"/>
-      <c r="F132" s="25"/>
-      <c r="G132" s="25"/>
-      <c r="H132" s="25"/>
+      <c r="A132" s="19"/>
+      <c r="B132" s="18"/>
+      <c r="C132" s="18"/>
+      <c r="D132" s="18"/>
+      <c r="E132" s="18"/>
+      <c r="F132" s="18"/>
+      <c r="G132" s="18"/>
+      <c r="H132" s="18"/>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="26"/>
-      <c r="B133" s="25"/>
-      <c r="C133" s="25"/>
-      <c r="D133" s="25"/>
-      <c r="E133" s="25"/>
-      <c r="F133" s="25"/>
-      <c r="G133" s="25"/>
-      <c r="H133" s="25"/>
+      <c r="A133" s="19"/>
+      <c r="B133" s="18"/>
+      <c r="C133" s="18"/>
+      <c r="D133" s="18"/>
+      <c r="E133" s="18"/>
+      <c r="F133" s="18"/>
+      <c r="G133" s="18"/>
+      <c r="H133" s="18"/>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" s="26"/>
-      <c r="B134" s="25"/>
-      <c r="C134" s="25"/>
-      <c r="D134" s="25"/>
-      <c r="E134" s="25"/>
-      <c r="F134" s="25"/>
-      <c r="G134" s="25"/>
-      <c r="H134" s="25"/>
+      <c r="A134" s="19"/>
+      <c r="B134" s="18"/>
+      <c r="C134" s="18"/>
+      <c r="D134" s="18"/>
+      <c r="E134" s="18"/>
+      <c r="F134" s="18"/>
+      <c r="G134" s="18"/>
+      <c r="H134" s="18"/>
     </row>
     <row r="135" spans="1:8">
-      <c r="A135" s="26"/>
-      <c r="B135" s="25"/>
-      <c r="C135" s="25"/>
-      <c r="D135" s="25"/>
-      <c r="E135" s="25"/>
-      <c r="F135" s="25"/>
-      <c r="G135" s="25"/>
-      <c r="H135" s="25"/>
+      <c r="A135" s="19"/>
+      <c r="B135" s="18"/>
+      <c r="C135" s="18"/>
+      <c r="D135" s="18"/>
+      <c r="E135" s="18"/>
+      <c r="F135" s="18"/>
+      <c r="G135" s="18"/>
+      <c r="H135" s="18"/>
     </row>
     <row r="136" spans="1:8">
-      <c r="A136" s="26"/>
-      <c r="B136" s="25"/>
-      <c r="C136" s="25"/>
-      <c r="D136" s="25"/>
-      <c r="E136" s="25"/>
-      <c r="F136" s="25"/>
-      <c r="G136" s="25"/>
-      <c r="H136" s="25"/>
+      <c r="A136" s="19"/>
+      <c r="B136" s="18"/>
+      <c r="C136" s="18"/>
+      <c r="D136" s="18"/>
+      <c r="E136" s="18"/>
+      <c r="F136" s="18"/>
+      <c r="G136" s="18"/>
+      <c r="H136" s="18"/>
     </row>
     <row r="137" spans="1:8">
-      <c r="A137" s="26"/>
-      <c r="B137" s="25"/>
-      <c r="C137" s="25"/>
-      <c r="D137" s="25"/>
-      <c r="E137" s="25"/>
-      <c r="F137" s="25"/>
-      <c r="G137" s="25"/>
-      <c r="H137" s="25"/>
+      <c r="A137" s="19"/>
+      <c r="B137" s="18"/>
+      <c r="C137" s="18"/>
+      <c r="D137" s="18"/>
+      <c r="E137" s="18"/>
+      <c r="F137" s="18"/>
+      <c r="G137" s="18"/>
+      <c r="H137" s="18"/>
     </row>
     <row r="138" spans="1:8">
-      <c r="A138" s="26"/>
-      <c r="B138" s="25"/>
-      <c r="C138" s="25"/>
-      <c r="D138" s="25"/>
-      <c r="E138" s="25"/>
-      <c r="F138" s="25"/>
-      <c r="G138" s="25"/>
-      <c r="H138" s="25"/>
+      <c r="A138" s="19"/>
+      <c r="B138" s="18"/>
+      <c r="C138" s="18"/>
+      <c r="D138" s="18"/>
+      <c r="E138" s="18"/>
+      <c r="F138" s="18"/>
+      <c r="G138" s="18"/>
+      <c r="H138" s="18"/>
     </row>
     <row r="139" spans="1:8">
-      <c r="A139" s="26"/>
-      <c r="B139" s="25"/>
-      <c r="C139" s="25"/>
-      <c r="D139" s="25"/>
-      <c r="E139" s="25"/>
-      <c r="F139" s="25"/>
-      <c r="G139" s="25"/>
-      <c r="H139" s="25"/>
+      <c r="A139" s="19"/>
+      <c r="B139" s="18"/>
+      <c r="C139" s="18"/>
+      <c r="D139" s="18"/>
+      <c r="E139" s="18"/>
+      <c r="F139" s="18"/>
+      <c r="G139" s="18"/>
+      <c r="H139" s="18"/>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="26"/>
-      <c r="B140" s="25"/>
-      <c r="C140" s="25"/>
-      <c r="D140" s="25"/>
-      <c r="E140" s="25"/>
-      <c r="F140" s="25"/>
-      <c r="G140" s="25"/>
-      <c r="H140" s="25"/>
+      <c r="A140" s="19"/>
+      <c r="B140" s="18"/>
+      <c r="C140" s="18"/>
+      <c r="D140" s="18"/>
+      <c r="E140" s="18"/>
+      <c r="F140" s="18"/>
+      <c r="G140" s="18"/>
+      <c r="H140" s="18"/>
     </row>
     <row r="141" spans="1:8">
-      <c r="A141" s="26"/>
-      <c r="B141" s="25"/>
-      <c r="C141" s="25"/>
-      <c r="D141" s="25"/>
-      <c r="E141" s="25"/>
-      <c r="F141" s="25"/>
-      <c r="G141" s="25"/>
-      <c r="H141" s="25"/>
+      <c r="A141" s="19"/>
+      <c r="B141" s="18"/>
+      <c r="C141" s="18"/>
+      <c r="D141" s="18"/>
+      <c r="E141" s="18"/>
+      <c r="F141" s="18"/>
+      <c r="G141" s="18"/>
+      <c r="H141" s="18"/>
     </row>
     <row r="142" spans="1:8">
-      <c r="A142" s="26"/>
-      <c r="B142" s="25"/>
-      <c r="C142" s="25"/>
-      <c r="D142" s="25"/>
-      <c r="E142" s="25"/>
-      <c r="F142" s="25"/>
-      <c r="G142" s="25"/>
-      <c r="H142" s="25"/>
+      <c r="A142" s="19"/>
+      <c r="B142" s="18"/>
+      <c r="C142" s="18"/>
+      <c r="D142" s="18"/>
+      <c r="E142" s="18"/>
+      <c r="F142" s="18"/>
+      <c r="G142" s="18"/>
+      <c r="H142" s="18"/>
     </row>
     <row r="143" spans="1:8">
-      <c r="A143" s="26"/>
-      <c r="B143" s="25"/>
-      <c r="C143" s="25"/>
-      <c r="D143" s="25"/>
-      <c r="E143" s="25"/>
-      <c r="F143" s="25"/>
-      <c r="G143" s="25"/>
-      <c r="H143" s="25"/>
+      <c r="A143" s="19"/>
+      <c r="B143" s="18"/>
+      <c r="C143" s="18"/>
+      <c r="D143" s="18"/>
+      <c r="E143" s="18"/>
+      <c r="F143" s="18"/>
+      <c r="G143" s="18"/>
+      <c r="H143" s="18"/>
     </row>
     <row r="144" spans="1:8">
-      <c r="A144" s="26"/>
-      <c r="B144" s="25"/>
-      <c r="C144" s="25"/>
-      <c r="D144" s="25"/>
-      <c r="E144" s="25"/>
-      <c r="F144" s="25"/>
-      <c r="G144" s="25"/>
-      <c r="H144" s="25"/>
+      <c r="A144" s="19"/>
+      <c r="B144" s="18"/>
+      <c r="C144" s="18"/>
+      <c r="D144" s="18"/>
+      <c r="E144" s="18"/>
+      <c r="F144" s="18"/>
+      <c r="G144" s="18"/>
+      <c r="H144" s="18"/>
     </row>
     <row r="145" spans="1:8">
-      <c r="A145" s="26"/>
-      <c r="B145" s="25"/>
-      <c r="C145" s="25"/>
-      <c r="D145" s="25"/>
-      <c r="E145" s="25"/>
-      <c r="F145" s="25"/>
-      <c r="G145" s="25"/>
-      <c r="H145" s="25"/>
+      <c r="A145" s="19"/>
+      <c r="B145" s="18"/>
+      <c r="C145" s="18"/>
+      <c r="D145" s="18"/>
+      <c r="E145" s="18"/>
+      <c r="F145" s="18"/>
+      <c r="G145" s="18"/>
+      <c r="H145" s="18"/>
     </row>
     <row r="146" spans="1:8">
-      <c r="A146" s="26"/>
-      <c r="B146" s="25"/>
-      <c r="C146" s="25"/>
-      <c r="D146" s="25"/>
-      <c r="E146" s="25"/>
-      <c r="F146" s="25"/>
-      <c r="G146" s="25"/>
-      <c r="H146" s="25"/>
+      <c r="A146" s="19"/>
+      <c r="B146" s="18"/>
+      <c r="C146" s="18"/>
+      <c r="D146" s="18"/>
+      <c r="E146" s="18"/>
+      <c r="F146" s="18"/>
+      <c r="G146" s="18"/>
+      <c r="H146" s="18"/>
     </row>
     <row r="147" spans="1:8">
-      <c r="A147" s="26"/>
-      <c r="B147" s="25"/>
-      <c r="C147" s="25"/>
-      <c r="D147" s="25"/>
-      <c r="E147" s="25"/>
-      <c r="F147" s="25"/>
-      <c r="G147" s="25"/>
-      <c r="H147" s="25"/>
+      <c r="A147" s="19"/>
+      <c r="B147" s="18"/>
+      <c r="C147" s="18"/>
+      <c r="D147" s="18"/>
+      <c r="E147" s="18"/>
+      <c r="F147" s="18"/>
+      <c r="G147" s="18"/>
+      <c r="H147" s="18"/>
     </row>
     <row r="148" spans="1:8">
-      <c r="A148" s="26"/>
-      <c r="B148" s="25"/>
-      <c r="C148" s="25"/>
-      <c r="D148" s="25"/>
-      <c r="E148" s="25"/>
-      <c r="F148" s="25"/>
-      <c r="G148" s="25"/>
-      <c r="H148" s="25"/>
+      <c r="A148" s="19"/>
+      <c r="B148" s="18"/>
+      <c r="C148" s="18"/>
+      <c r="D148" s="18"/>
+      <c r="E148" s="18"/>
+      <c r="F148" s="18"/>
+      <c r="G148" s="18"/>
+      <c r="H148" s="18"/>
     </row>
     <row r="149" spans="1:8">
-      <c r="A149" s="26"/>
-      <c r="B149" s="25"/>
-      <c r="C149" s="25"/>
-      <c r="D149" s="25"/>
-      <c r="E149" s="25"/>
-      <c r="F149" s="25"/>
-      <c r="G149" s="25"/>
-      <c r="H149" s="25"/>
+      <c r="A149" s="19"/>
+      <c r="B149" s="18"/>
+      <c r="C149" s="18"/>
+      <c r="D149" s="18"/>
+      <c r="E149" s="18"/>
+      <c r="F149" s="18"/>
+      <c r="G149" s="18"/>
+      <c r="H149" s="18"/>
     </row>
     <row r="150" spans="1:8">
-      <c r="A150" s="26"/>
-      <c r="B150" s="25"/>
-      <c r="C150" s="25"/>
-      <c r="D150" s="25"/>
-      <c r="E150" s="25"/>
-      <c r="F150" s="25"/>
-      <c r="G150" s="25"/>
-      <c r="H150" s="25"/>
+      <c r="A150" s="19"/>
+      <c r="B150" s="18"/>
+      <c r="C150" s="18"/>
+      <c r="D150" s="18"/>
+      <c r="E150" s="18"/>
+      <c r="F150" s="18"/>
+      <c r="G150" s="18"/>
+      <c r="H150" s="18"/>
     </row>
     <row r="151" spans="1:8">
-      <c r="A151" s="26"/>
-      <c r="B151" s="25"/>
-      <c r="C151" s="25"/>
-      <c r="D151" s="25"/>
-      <c r="E151" s="25"/>
-      <c r="F151" s="25"/>
-      <c r="G151" s="25"/>
-      <c r="H151" s="25"/>
+      <c r="A151" s="19"/>
+      <c r="B151" s="18"/>
+      <c r="C151" s="18"/>
+      <c r="D151" s="18"/>
+      <c r="E151" s="18"/>
+      <c r="F151" s="18"/>
+      <c r="G151" s="18"/>
+      <c r="H151" s="18"/>
     </row>
     <row r="152" spans="1:8">
-      <c r="A152" s="26"/>
-      <c r="B152" s="25"/>
-      <c r="C152" s="25"/>
-      <c r="D152" s="25"/>
-      <c r="E152" s="25"/>
-      <c r="F152" s="25"/>
-      <c r="G152" s="25"/>
-      <c r="H152" s="25"/>
+      <c r="A152" s="19"/>
+      <c r="B152" s="18"/>
+      <c r="C152" s="18"/>
+      <c r="D152" s="18"/>
+      <c r="E152" s="18"/>
+      <c r="F152" s="18"/>
+      <c r="G152" s="18"/>
+      <c r="H152" s="18"/>
     </row>
     <row r="153" spans="1:8">
-      <c r="A153" s="26"/>
-      <c r="B153" s="25"/>
-      <c r="C153" s="25"/>
-      <c r="D153" s="25"/>
-      <c r="E153" s="25"/>
-      <c r="F153" s="25"/>
-      <c r="G153" s="25"/>
-      <c r="H153" s="25"/>
+      <c r="A153" s="19"/>
+      <c r="B153" s="18"/>
+      <c r="C153" s="18"/>
+      <c r="D153" s="18"/>
+      <c r="E153" s="18"/>
+      <c r="F153" s="18"/>
+      <c r="G153" s="18"/>
+      <c r="H153" s="18"/>
     </row>
     <row r="154" spans="1:8">
-      <c r="A154" s="26"/>
-      <c r="B154" s="25"/>
-      <c r="C154" s="25"/>
-      <c r="D154" s="25"/>
-      <c r="E154" s="25"/>
-      <c r="F154" s="25"/>
-      <c r="G154" s="25"/>
-      <c r="H154" s="25"/>
+      <c r="A154" s="19"/>
+      <c r="B154" s="18"/>
+      <c r="C154" s="18"/>
+      <c r="D154" s="18"/>
+      <c r="E154" s="18"/>
+      <c r="F154" s="18"/>
+      <c r="G154" s="18"/>
+      <c r="H154" s="18"/>
     </row>
     <row r="155" spans="1:8">
-      <c r="A155" s="26"/>
-      <c r="B155" s="25"/>
-      <c r="C155" s="25"/>
-      <c r="D155" s="25"/>
-      <c r="E155" s="25"/>
-      <c r="F155" s="25"/>
-      <c r="G155" s="25"/>
-      <c r="H155" s="25"/>
+      <c r="A155" s="19"/>
+      <c r="B155" s="18"/>
+      <c r="C155" s="18"/>
+      <c r="D155" s="18"/>
+      <c r="E155" s="18"/>
+      <c r="F155" s="18"/>
+      <c r="G155" s="18"/>
+      <c r="H155" s="18"/>
     </row>
     <row r="156" spans="1:8">
-      <c r="A156" s="26"/>
-      <c r="B156" s="25"/>
-      <c r="C156" s="25"/>
-      <c r="D156" s="25"/>
-      <c r="E156" s="25"/>
-      <c r="F156" s="25"/>
-      <c r="G156" s="25"/>
-      <c r="H156" s="25"/>
+      <c r="A156" s="19"/>
+      <c r="B156" s="18"/>
+      <c r="C156" s="18"/>
+      <c r="D156" s="18"/>
+      <c r="E156" s="18"/>
+      <c r="F156" s="18"/>
+      <c r="G156" s="18"/>
+      <c r="H156" s="18"/>
     </row>
     <row r="157" spans="1:8">
-      <c r="A157" s="26"/>
-      <c r="B157" s="25"/>
-      <c r="C157" s="25"/>
-      <c r="D157" s="25"/>
-      <c r="E157" s="25"/>
-      <c r="F157" s="25"/>
-      <c r="G157" s="25"/>
-      <c r="H157" s="25"/>
+      <c r="A157" s="19"/>
+      <c r="B157" s="18"/>
+      <c r="C157" s="18"/>
+      <c r="D157" s="18"/>
+      <c r="E157" s="18"/>
+      <c r="F157" s="18"/>
+      <c r="G157" s="18"/>
+      <c r="H157" s="18"/>
     </row>
     <row r="158" spans="1:8">
-      <c r="A158" s="26"/>
-      <c r="B158" s="25"/>
-      <c r="C158" s="25"/>
-      <c r="D158" s="25"/>
-      <c r="E158" s="25"/>
-      <c r="F158" s="25"/>
-      <c r="G158" s="25"/>
-      <c r="H158" s="25"/>
+      <c r="A158" s="19"/>
+      <c r="B158" s="18"/>
+      <c r="C158" s="18"/>
+      <c r="D158" s="18"/>
+      <c r="E158" s="18"/>
+      <c r="F158" s="18"/>
+      <c r="G158" s="18"/>
+      <c r="H158" s="18"/>
     </row>
     <row r="159" spans="1:8">
-      <c r="A159" s="26"/>
-      <c r="B159" s="25"/>
-      <c r="C159" s="25"/>
-      <c r="D159" s="25"/>
-      <c r="E159" s="25"/>
-      <c r="F159" s="25"/>
-      <c r="G159" s="25"/>
-      <c r="H159" s="25"/>
+      <c r="A159" s="19"/>
+      <c r="B159" s="18"/>
+      <c r="C159" s="18"/>
+      <c r="D159" s="18"/>
+      <c r="E159" s="18"/>
+      <c r="F159" s="18"/>
+      <c r="G159" s="18"/>
+      <c r="H159" s="18"/>
     </row>
     <row r="160" spans="1:8">
-      <c r="A160" s="26"/>
-      <c r="B160" s="25"/>
-      <c r="C160" s="25"/>
-      <c r="D160" s="25"/>
-      <c r="E160" s="25"/>
-      <c r="F160" s="25"/>
-      <c r="G160" s="25"/>
-      <c r="H160" s="25"/>
+      <c r="A160" s="19"/>
+      <c r="B160" s="18"/>
+      <c r="C160" s="18"/>
+      <c r="D160" s="18"/>
+      <c r="E160" s="18"/>
+      <c r="F160" s="18"/>
+      <c r="G160" s="18"/>
+      <c r="H160" s="18"/>
     </row>
     <row r="161" spans="1:8">
-      <c r="A161" s="26"/>
-      <c r="B161" s="25"/>
-      <c r="C161" s="25"/>
-      <c r="D161" s="25"/>
-      <c r="E161" s="25"/>
-      <c r="F161" s="25"/>
-      <c r="G161" s="25"/>
-      <c r="H161" s="25"/>
+      <c r="A161" s="19"/>
+      <c r="B161" s="18"/>
+      <c r="C161" s="18"/>
+      <c r="D161" s="18"/>
+      <c r="E161" s="18"/>
+      <c r="F161" s="18"/>
+      <c r="G161" s="18"/>
+      <c r="H161" s="18"/>
     </row>
     <row r="162" spans="1:8">
-      <c r="A162" s="26"/>
-      <c r="B162" s="25"/>
-      <c r="C162" s="25"/>
-      <c r="D162" s="25"/>
-      <c r="E162" s="25"/>
-      <c r="F162" s="25"/>
-      <c r="G162" s="25"/>
-      <c r="H162" s="25"/>
+      <c r="A162" s="19"/>
+      <c r="B162" s="18"/>
+      <c r="C162" s="18"/>
+      <c r="D162" s="18"/>
+      <c r="E162" s="18"/>
+      <c r="F162" s="18"/>
+      <c r="G162" s="18"/>
+      <c r="H162" s="18"/>
     </row>
     <row r="163" spans="1:8">
-      <c r="A163" s="26"/>
-      <c r="B163" s="25"/>
-      <c r="C163" s="25"/>
-      <c r="D163" s="25"/>
-      <c r="E163" s="25"/>
-      <c r="F163" s="25"/>
-      <c r="G163" s="25"/>
-      <c r="H163" s="25"/>
+      <c r="A163" s="19"/>
+      <c r="B163" s="18"/>
+      <c r="C163" s="18"/>
+      <c r="D163" s="18"/>
+      <c r="E163" s="18"/>
+      <c r="F163" s="18"/>
+      <c r="G163" s="18"/>
+      <c r="H163" s="18"/>
     </row>
     <row r="164" spans="1:8">
-      <c r="A164" s="26"/>
-      <c r="B164" s="25"/>
-      <c r="C164" s="25"/>
-      <c r="D164" s="25"/>
-      <c r="E164" s="25"/>
-      <c r="F164" s="25"/>
-      <c r="G164" s="25"/>
-      <c r="H164" s="25"/>
+      <c r="A164" s="19"/>
+      <c r="B164" s="18"/>
+      <c r="C164" s="18"/>
+      <c r="D164" s="18"/>
+      <c r="E164" s="18"/>
+      <c r="F164" s="18"/>
+      <c r="G164" s="18"/>
+      <c r="H164" s="18"/>
     </row>
     <row r="165" spans="1:8">
-      <c r="A165" s="26"/>
-      <c r="B165" s="25"/>
-      <c r="C165" s="25"/>
-      <c r="D165" s="25"/>
-      <c r="E165" s="25"/>
-      <c r="F165" s="25"/>
-      <c r="G165" s="25"/>
-      <c r="H165" s="25"/>
+      <c r="A165" s="19"/>
+      <c r="B165" s="18"/>
+      <c r="C165" s="18"/>
+      <c r="D165" s="18"/>
+      <c r="E165" s="18"/>
+      <c r="F165" s="18"/>
+      <c r="G165" s="18"/>
+      <c r="H165" s="18"/>
     </row>
     <row r="166" spans="1:8">
-      <c r="A166" s="26"/>
-      <c r="B166" s="25"/>
-      <c r="C166" s="25"/>
-      <c r="D166" s="25"/>
-      <c r="E166" s="25"/>
-      <c r="F166" s="25"/>
-      <c r="G166" s="25"/>
-      <c r="H166" s="25"/>
+      <c r="A166" s="19"/>
+      <c r="B166" s="18"/>
+      <c r="C166" s="18"/>
+      <c r="D166" s="18"/>
+      <c r="E166" s="18"/>
+      <c r="F166" s="18"/>
+      <c r="G166" s="18"/>
+      <c r="H166" s="18"/>
     </row>
     <row r="167" spans="1:8">
-      <c r="A167" s="26"/>
-      <c r="B167" s="25"/>
-      <c r="C167" s="25"/>
-      <c r="D167" s="25"/>
-      <c r="E167" s="25"/>
-      <c r="F167" s="25"/>
-      <c r="G167" s="25"/>
-      <c r="H167" s="25"/>
+      <c r="A167" s="19"/>
+      <c r="B167" s="18"/>
+      <c r="C167" s="18"/>
+      <c r="D167" s="18"/>
+      <c r="E167" s="18"/>
+      <c r="F167" s="18"/>
+      <c r="G167" s="18"/>
+      <c r="H167" s="18"/>
     </row>
     <row r="168" spans="1:8">
-      <c r="A168" s="26"/>
-      <c r="B168" s="25"/>
-      <c r="C168" s="25"/>
-      <c r="D168" s="25"/>
-      <c r="E168" s="25"/>
-      <c r="F168" s="25"/>
-      <c r="G168" s="25"/>
-      <c r="H168" s="25"/>
+      <c r="A168" s="19"/>
+      <c r="B168" s="18"/>
+      <c r="C168" s="18"/>
+      <c r="D168" s="18"/>
+      <c r="E168" s="18"/>
+      <c r="F168" s="18"/>
+      <c r="G168" s="18"/>
+      <c r="H168" s="18"/>
     </row>
     <row r="169" spans="1:8">
-      <c r="A169" s="26"/>
-      <c r="B169" s="25"/>
-      <c r="C169" s="25"/>
-      <c r="D169" s="25"/>
-      <c r="E169" s="25"/>
-      <c r="F169" s="25"/>
-      <c r="G169" s="25"/>
-      <c r="H169" s="25"/>
+      <c r="A169" s="19"/>
+      <c r="B169" s="18"/>
+      <c r="C169" s="18"/>
+      <c r="D169" s="18"/>
+      <c r="E169" s="18"/>
+      <c r="F169" s="18"/>
+      <c r="G169" s="18"/>
+      <c r="H169" s="18"/>
     </row>
     <row r="170" spans="1:8">
-      <c r="A170" s="26"/>
-      <c r="B170" s="25"/>
-      <c r="C170" s="25"/>
-      <c r="D170" s="25"/>
-      <c r="E170" s="25"/>
-      <c r="F170" s="25"/>
-      <c r="G170" s="25"/>
-      <c r="H170" s="25"/>
+      <c r="A170" s="19"/>
+      <c r="B170" s="18"/>
+      <c r="C170" s="18"/>
+      <c r="D170" s="18"/>
+      <c r="E170" s="18"/>
+      <c r="F170" s="18"/>
+      <c r="G170" s="18"/>
+      <c r="H170" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5154E2D6-763D-4519-8AAF-F4FB9E513174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CFD4556-EE53-435C-8FD5-6B20099E8699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="リスト" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="271">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -1199,6 +1199,160 @@
     <t>神様</t>
     <rPh sb="0" eb="2">
       <t>カミサマ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>がんばれ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>わかった</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>はーい</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>聞きますね</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>頑張る</t>
+    <rPh sb="0" eb="2">
+      <t>ガンバ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ん？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>はぁい</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>向かっているよ</t>
+    <rPh sb="0" eb="1">
+      <t>ム</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>また明日</t>
+    <rPh sb="2" eb="4">
+      <t>アシタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>久しぶり</t>
+    <rPh sb="0" eb="1">
+      <t>ヒサ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ご無沙汰しております</t>
+    <rPh sb="1" eb="4">
+      <t>ブサタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>まるっ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>らじゃー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ええやん</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>そうなんや</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ええよ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>大丈夫</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>そう</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>それわかる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>怒るで</t>
+    <rPh sb="0" eb="1">
+      <t>オコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>まだ？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>まだ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>電車乗ってる</t>
+    <rPh sb="0" eb="2">
+      <t>デンシャ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>覚えてない</t>
+    <rPh sb="0" eb="1">
+      <t>オボ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>着いてる</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>何がいい？</t>
+    <rPh sb="0" eb="1">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>小人</t>
+    <rPh sb="0" eb="2">
+      <t>コビト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>妖精</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウセイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1400,7 +1554,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1483,6 +1637,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1857,17 +2013,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB230"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <dimension ref="A1:AB280"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="3.4375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.4140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="3.5625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.5625" bestFit="1" customWidth="1"/>
-    <col min="10" max="28" width="3.5625" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="3.58203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.58203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="28" width="3.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="22.9">
+    <row r="1" spans="1:28" ht="22.5">
       <c r="A1" s="24"/>
       <c r="B1" s="21" t="s">
         <v>122</v>
@@ -1896,7 +2052,7 @@
       <c r="V1" s="27"/>
       <c r="W1" s="27"/>
     </row>
-    <row r="2" spans="1:28" ht="22.9">
+    <row r="2" spans="1:28" ht="22.5">
       <c r="A2" s="25"/>
       <c r="B2" s="22"/>
       <c r="C2" s="5"/>
@@ -1934,7 +2090,7 @@
       <c r="AA2" s="5"/>
       <c r="AB2" s="5"/>
     </row>
-    <row r="3" spans="1:28" s="13" customFormat="1" ht="90.4" thickBot="1">
+    <row r="3" spans="1:28" s="13" customFormat="1" ht="92.5" thickBot="1">
       <c r="A3" s="26"/>
       <c r="B3" s="23"/>
       <c r="C3" s="11" t="s">
@@ -2000,8 +2156,12 @@
       <c r="W3" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="11"/>
+      <c r="X3" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>270</v>
+      </c>
       <c r="Z3" s="11"/>
       <c r="AA3" s="11"/>
       <c r="AB3" s="11"/>
@@ -9518,7 +9678,9 @@
       <c r="A216" s="3">
         <v>213</v>
       </c>
-      <c r="B216" s="4"/>
+      <c r="B216" s="6" t="s">
+        <v>243</v>
+      </c>
       <c r="C216" s="1"/>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
@@ -9550,7 +9712,9 @@
       <c r="A217" s="3">
         <v>214</v>
       </c>
-      <c r="B217" s="4"/>
+      <c r="B217" s="6" t="s">
+        <v>244</v>
+      </c>
       <c r="C217" s="1"/>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
@@ -9582,7 +9746,9 @@
       <c r="A218" s="3">
         <v>215</v>
       </c>
-      <c r="B218" s="4"/>
+      <c r="B218" s="6" t="s">
+        <v>245</v>
+      </c>
       <c r="C218" s="1"/>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
@@ -9614,7 +9780,9 @@
       <c r="A219" s="3">
         <v>216</v>
       </c>
-      <c r="B219" s="4"/>
+      <c r="B219" s="4" t="s">
+        <v>246</v>
+      </c>
       <c r="C219" s="1"/>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
@@ -9646,7 +9814,9 @@
       <c r="A220" s="3">
         <v>217</v>
       </c>
-      <c r="B220" s="4"/>
+      <c r="B220" s="4" t="s">
+        <v>247</v>
+      </c>
       <c r="C220" s="1"/>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
@@ -9678,7 +9848,9 @@
       <c r="A221" s="3">
         <v>218</v>
       </c>
-      <c r="B221" s="4"/>
+      <c r="B221" s="4" t="s">
+        <v>248</v>
+      </c>
       <c r="C221" s="1"/>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
@@ -9710,7 +9882,9 @@
       <c r="A222" s="3">
         <v>219</v>
       </c>
-      <c r="B222" s="4"/>
+      <c r="B222" s="6" t="s">
+        <v>249</v>
+      </c>
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
@@ -9742,7 +9916,9 @@
       <c r="A223" s="3">
         <v>220</v>
       </c>
-      <c r="B223" s="4"/>
+      <c r="B223" s="4" t="s">
+        <v>250</v>
+      </c>
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
@@ -9774,7 +9950,9 @@
       <c r="A224" s="3">
         <v>221</v>
       </c>
-      <c r="B224" s="4"/>
+      <c r="B224" s="4" t="s">
+        <v>251</v>
+      </c>
       <c r="C224" s="1"/>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
@@ -9806,7 +9984,9 @@
       <c r="A225" s="3">
         <v>222</v>
       </c>
-      <c r="B225" s="4"/>
+      <c r="B225" s="4" t="s">
+        <v>252</v>
+      </c>
       <c r="C225" s="1"/>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
@@ -9838,7 +10018,9 @@
       <c r="A226" s="3">
         <v>223</v>
       </c>
-      <c r="B226" s="4"/>
+      <c r="B226" s="4" t="s">
+        <v>253</v>
+      </c>
       <c r="C226" s="1"/>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
@@ -9870,7 +10052,9 @@
       <c r="A227" s="3">
         <v>224</v>
       </c>
-      <c r="B227" s="4"/>
+      <c r="B227" s="4" t="s">
+        <v>254</v>
+      </c>
       <c r="C227" s="1"/>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
@@ -9902,7 +10086,9 @@
       <c r="A228" s="3">
         <v>225</v>
       </c>
-      <c r="B228" s="4"/>
+      <c r="B228" s="4" t="s">
+        <v>255</v>
+      </c>
       <c r="C228" s="1"/>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
@@ -9934,7 +10120,9 @@
       <c r="A229" s="3">
         <v>226</v>
       </c>
-      <c r="B229" s="4"/>
+      <c r="B229" s="4" t="s">
+        <v>256</v>
+      </c>
       <c r="C229" s="1"/>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
@@ -9966,7 +10154,9 @@
       <c r="A230" s="3">
         <v>227</v>
       </c>
-      <c r="B230" s="4"/>
+      <c r="B230" s="4" t="s">
+        <v>257</v>
+      </c>
       <c r="C230" s="1"/>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
@@ -9994,6 +10184,1630 @@
       <c r="AA230" s="1"/>
       <c r="AB230" s="1"/>
     </row>
+    <row r="231" spans="1:28">
+      <c r="A231" s="3">
+        <v>228</v>
+      </c>
+      <c r="B231" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="C231" s="1"/>
+      <c r="D231" s="1"/>
+      <c r="E231" s="1"/>
+      <c r="F231" s="1"/>
+      <c r="G231" s="1"/>
+      <c r="H231" s="1"/>
+      <c r="I231" s="1"/>
+      <c r="J231" s="1"/>
+      <c r="K231" s="1"/>
+      <c r="L231" s="1"/>
+      <c r="M231" s="1"/>
+      <c r="N231" s="1"/>
+      <c r="O231" s="1"/>
+      <c r="P231" s="1"/>
+      <c r="Q231" s="1"/>
+      <c r="R231" s="1"/>
+      <c r="S231" s="1"/>
+      <c r="T231" s="1"/>
+      <c r="U231" s="1"/>
+      <c r="V231" s="1"/>
+      <c r="W231" s="1"/>
+      <c r="X231" s="1"/>
+      <c r="Y231" s="1"/>
+      <c r="Z231" s="1"/>
+      <c r="AA231" s="1"/>
+      <c r="AB231" s="1"/>
+    </row>
+    <row r="232" spans="1:28">
+      <c r="A232" s="3">
+        <v>229</v>
+      </c>
+      <c r="B232" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="C232" s="1"/>
+      <c r="D232" s="1"/>
+      <c r="E232" s="1"/>
+      <c r="F232" s="1"/>
+      <c r="G232" s="1"/>
+      <c r="H232" s="1"/>
+      <c r="I232" s="1"/>
+      <c r="J232" s="1"/>
+      <c r="K232" s="1"/>
+      <c r="L232" s="1"/>
+      <c r="M232" s="1"/>
+      <c r="N232" s="1"/>
+      <c r="O232" s="1"/>
+      <c r="P232" s="1"/>
+      <c r="Q232" s="1"/>
+      <c r="R232" s="1"/>
+      <c r="S232" s="1"/>
+      <c r="T232" s="1"/>
+      <c r="U232" s="1"/>
+      <c r="V232" s="1"/>
+      <c r="W232" s="1"/>
+      <c r="X232" s="1"/>
+      <c r="Y232" s="1"/>
+      <c r="Z232" s="1"/>
+      <c r="AA232" s="1"/>
+      <c r="AB232" s="1"/>
+    </row>
+    <row r="233" spans="1:28">
+      <c r="A233" s="3">
+        <v>230</v>
+      </c>
+      <c r="B233" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="C233" s="1"/>
+      <c r="D233" s="1"/>
+      <c r="E233" s="1"/>
+      <c r="F233" s="1"/>
+      <c r="G233" s="1"/>
+      <c r="H233" s="1"/>
+      <c r="I233" s="1"/>
+      <c r="J233" s="1"/>
+      <c r="K233" s="1"/>
+      <c r="L233" s="1"/>
+      <c r="M233" s="1"/>
+      <c r="N233" s="1"/>
+      <c r="O233" s="1"/>
+      <c r="P233" s="1"/>
+      <c r="Q233" s="1"/>
+      <c r="R233" s="1"/>
+      <c r="S233" s="1"/>
+      <c r="T233" s="1"/>
+      <c r="U233" s="1"/>
+      <c r="V233" s="1"/>
+      <c r="W233" s="1"/>
+      <c r="X233" s="1"/>
+      <c r="Y233" s="1"/>
+      <c r="Z233" s="1"/>
+      <c r="AA233" s="1"/>
+      <c r="AB233" s="1"/>
+    </row>
+    <row r="234" spans="1:28">
+      <c r="A234" s="3">
+        <v>231</v>
+      </c>
+      <c r="B234" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="C234" s="1"/>
+      <c r="D234" s="1"/>
+      <c r="E234" s="1"/>
+      <c r="F234" s="1"/>
+      <c r="G234" s="1"/>
+      <c r="H234" s="1"/>
+      <c r="I234" s="1"/>
+      <c r="J234" s="1"/>
+      <c r="K234" s="1"/>
+      <c r="L234" s="1"/>
+      <c r="M234" s="1"/>
+      <c r="N234" s="1"/>
+      <c r="O234" s="1"/>
+      <c r="P234" s="1"/>
+      <c r="Q234" s="1"/>
+      <c r="R234" s="1"/>
+      <c r="S234" s="1"/>
+      <c r="T234" s="1"/>
+      <c r="U234" s="1"/>
+      <c r="V234" s="1"/>
+      <c r="W234" s="1"/>
+      <c r="X234" s="1"/>
+      <c r="Y234" s="1"/>
+      <c r="Z234" s="1"/>
+      <c r="AA234" s="1"/>
+      <c r="AB234" s="1"/>
+    </row>
+    <row r="235" spans="1:28">
+      <c r="A235" s="3">
+        <v>232</v>
+      </c>
+      <c r="B235" s="28" t="s">
+        <v>261</v>
+      </c>
+      <c r="C235" s="1"/>
+      <c r="D235" s="1"/>
+      <c r="E235" s="1"/>
+      <c r="F235" s="1"/>
+      <c r="G235" s="1"/>
+      <c r="H235" s="1"/>
+      <c r="I235" s="1"/>
+      <c r="J235" s="1"/>
+      <c r="K235" s="1"/>
+      <c r="L235" s="1"/>
+      <c r="M235" s="1"/>
+      <c r="N235" s="1"/>
+      <c r="O235" s="1"/>
+      <c r="P235" s="1"/>
+      <c r="Q235" s="1"/>
+      <c r="R235" s="1"/>
+      <c r="S235" s="1"/>
+      <c r="T235" s="1"/>
+      <c r="U235" s="1"/>
+      <c r="V235" s="1"/>
+      <c r="W235" s="1"/>
+      <c r="X235" s="1"/>
+      <c r="Y235" s="1"/>
+      <c r="Z235" s="1"/>
+      <c r="AA235" s="1"/>
+      <c r="AB235" s="1"/>
+    </row>
+    <row r="236" spans="1:28">
+      <c r="A236" s="3">
+        <v>233</v>
+      </c>
+      <c r="B236" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="C236" s="1"/>
+      <c r="D236" s="1"/>
+      <c r="E236" s="1"/>
+      <c r="F236" s="1"/>
+      <c r="G236" s="1"/>
+      <c r="H236" s="1"/>
+      <c r="I236" s="1"/>
+      <c r="J236" s="1"/>
+      <c r="K236" s="1"/>
+      <c r="L236" s="1"/>
+      <c r="M236" s="1"/>
+      <c r="N236" s="1"/>
+      <c r="O236" s="1"/>
+      <c r="P236" s="1"/>
+      <c r="Q236" s="1"/>
+      <c r="R236" s="1"/>
+      <c r="S236" s="1"/>
+      <c r="T236" s="1"/>
+      <c r="U236" s="1"/>
+      <c r="V236" s="1"/>
+      <c r="W236" s="1"/>
+      <c r="X236" s="1"/>
+      <c r="Y236" s="1"/>
+      <c r="Z236" s="1"/>
+      <c r="AA236" s="1"/>
+      <c r="AB236" s="1"/>
+    </row>
+    <row r="237" spans="1:28">
+      <c r="A237" s="3">
+        <v>234</v>
+      </c>
+      <c r="B237" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="C237" s="1"/>
+      <c r="D237" s="1"/>
+      <c r="E237" s="1"/>
+      <c r="F237" s="1"/>
+      <c r="G237" s="1"/>
+      <c r="H237" s="1"/>
+      <c r="I237" s="1"/>
+      <c r="J237" s="1"/>
+      <c r="K237" s="1"/>
+      <c r="L237" s="1"/>
+      <c r="M237" s="1"/>
+      <c r="N237" s="1"/>
+      <c r="O237" s="1"/>
+      <c r="P237" s="1"/>
+      <c r="Q237" s="1"/>
+      <c r="R237" s="1"/>
+      <c r="S237" s="1"/>
+      <c r="T237" s="1"/>
+      <c r="U237" s="1"/>
+      <c r="V237" s="1"/>
+      <c r="W237" s="1"/>
+      <c r="X237" s="1"/>
+      <c r="Y237" s="1"/>
+      <c r="Z237" s="1"/>
+      <c r="AA237" s="1"/>
+      <c r="AB237" s="1"/>
+    </row>
+    <row r="238" spans="1:28">
+      <c r="A238" s="3">
+        <v>235</v>
+      </c>
+      <c r="B238" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="C238" s="1"/>
+      <c r="D238" s="1"/>
+      <c r="E238" s="1"/>
+      <c r="F238" s="1"/>
+      <c r="G238" s="1"/>
+      <c r="H238" s="1"/>
+      <c r="I238" s="1"/>
+      <c r="J238" s="1"/>
+      <c r="K238" s="1"/>
+      <c r="L238" s="1"/>
+      <c r="M238" s="1"/>
+      <c r="N238" s="1"/>
+      <c r="O238" s="1"/>
+      <c r="P238" s="1"/>
+      <c r="Q238" s="1"/>
+      <c r="R238" s="1"/>
+      <c r="S238" s="1"/>
+      <c r="T238" s="1"/>
+      <c r="U238" s="1"/>
+      <c r="V238" s="1"/>
+      <c r="W238" s="1"/>
+      <c r="X238" s="1"/>
+      <c r="Y238" s="1"/>
+      <c r="Z238" s="1"/>
+      <c r="AA238" s="1"/>
+      <c r="AB238" s="1"/>
+    </row>
+    <row r="239" spans="1:28">
+      <c r="A239" s="3">
+        <v>236</v>
+      </c>
+      <c r="B239" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C239" s="1"/>
+      <c r="D239" s="1"/>
+      <c r="E239" s="1"/>
+      <c r="F239" s="1"/>
+      <c r="G239" s="1"/>
+      <c r="H239" s="1"/>
+      <c r="I239" s="1"/>
+      <c r="J239" s="1"/>
+      <c r="K239" s="1"/>
+      <c r="L239" s="1"/>
+      <c r="M239" s="1"/>
+      <c r="N239" s="1"/>
+      <c r="O239" s="1"/>
+      <c r="P239" s="1"/>
+      <c r="Q239" s="1"/>
+      <c r="R239" s="1"/>
+      <c r="S239" s="1"/>
+      <c r="T239" s="1"/>
+      <c r="U239" s="1"/>
+      <c r="V239" s="1"/>
+      <c r="W239" s="1"/>
+      <c r="X239" s="1"/>
+      <c r="Y239" s="1"/>
+      <c r="Z239" s="1"/>
+      <c r="AA239" s="1"/>
+      <c r="AB239" s="1"/>
+    </row>
+    <row r="240" spans="1:28">
+      <c r="A240" s="3">
+        <v>237</v>
+      </c>
+      <c r="B240" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="C240" s="1"/>
+      <c r="D240" s="1"/>
+      <c r="E240" s="1"/>
+      <c r="F240" s="1"/>
+      <c r="G240" s="1"/>
+      <c r="H240" s="1"/>
+      <c r="I240" s="1"/>
+      <c r="J240" s="1"/>
+      <c r="K240" s="1"/>
+      <c r="L240" s="1"/>
+      <c r="M240" s="1"/>
+      <c r="N240" s="1"/>
+      <c r="O240" s="1"/>
+      <c r="P240" s="1"/>
+      <c r="Q240" s="1"/>
+      <c r="R240" s="1"/>
+      <c r="S240" s="1"/>
+      <c r="T240" s="1"/>
+      <c r="U240" s="1"/>
+      <c r="V240" s="1"/>
+      <c r="W240" s="1"/>
+      <c r="X240" s="1"/>
+      <c r="Y240" s="1"/>
+      <c r="Z240" s="1"/>
+      <c r="AA240" s="1"/>
+      <c r="AB240" s="1"/>
+    </row>
+    <row r="241" spans="1:28">
+      <c r="A241" s="3">
+        <v>238</v>
+      </c>
+      <c r="B241" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="C241" s="1"/>
+      <c r="D241" s="1"/>
+      <c r="E241" s="1"/>
+      <c r="F241" s="1"/>
+      <c r="G241" s="1"/>
+      <c r="H241" s="1"/>
+      <c r="I241" s="1"/>
+      <c r="J241" s="1"/>
+      <c r="K241" s="1"/>
+      <c r="L241" s="1"/>
+      <c r="M241" s="1"/>
+      <c r="N241" s="1"/>
+      <c r="O241" s="1"/>
+      <c r="P241" s="1"/>
+      <c r="Q241" s="1"/>
+      <c r="R241" s="1"/>
+      <c r="S241" s="1"/>
+      <c r="T241" s="1"/>
+      <c r="U241" s="1"/>
+      <c r="V241" s="1"/>
+      <c r="W241" s="1"/>
+      <c r="X241" s="1"/>
+      <c r="Y241" s="1"/>
+      <c r="Z241" s="1"/>
+      <c r="AA241" s="1"/>
+      <c r="AB241" s="1"/>
+    </row>
+    <row r="242" spans="1:28">
+      <c r="A242" s="3">
+        <v>239</v>
+      </c>
+      <c r="B242" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="C242" s="1"/>
+      <c r="D242" s="1"/>
+      <c r="E242" s="1"/>
+      <c r="F242" s="1"/>
+      <c r="G242" s="1"/>
+      <c r="H242" s="1"/>
+      <c r="I242" s="1"/>
+      <c r="J242" s="1"/>
+      <c r="K242" s="1"/>
+      <c r="L242" s="1"/>
+      <c r="M242" s="1"/>
+      <c r="N242" s="1"/>
+      <c r="O242" s="1"/>
+      <c r="P242" s="1"/>
+      <c r="Q242" s="1"/>
+      <c r="R242" s="1"/>
+      <c r="S242" s="1"/>
+      <c r="T242" s="1"/>
+      <c r="U242" s="1"/>
+      <c r="V242" s="1"/>
+      <c r="W242" s="1"/>
+      <c r="X242" s="1"/>
+      <c r="Y242" s="1"/>
+      <c r="Z242" s="1"/>
+      <c r="AA242" s="1"/>
+      <c r="AB242" s="1"/>
+    </row>
+    <row r="243" spans="1:28">
+      <c r="A243" s="3">
+        <v>240</v>
+      </c>
+      <c r="B243" s="28"/>
+      <c r="C243" s="1"/>
+      <c r="D243" s="1"/>
+      <c r="E243" s="1"/>
+      <c r="F243" s="1"/>
+      <c r="G243" s="1"/>
+      <c r="H243" s="1"/>
+      <c r="I243" s="1"/>
+      <c r="J243" s="1"/>
+      <c r="K243" s="1"/>
+      <c r="L243" s="1"/>
+      <c r="M243" s="1"/>
+      <c r="N243" s="1"/>
+      <c r="O243" s="1"/>
+      <c r="P243" s="1"/>
+      <c r="Q243" s="1"/>
+      <c r="R243" s="1"/>
+      <c r="S243" s="1"/>
+      <c r="T243" s="1"/>
+      <c r="U243" s="1"/>
+      <c r="V243" s="1"/>
+      <c r="W243" s="1"/>
+      <c r="X243" s="1"/>
+      <c r="Y243" s="1"/>
+      <c r="Z243" s="1"/>
+      <c r="AA243" s="1"/>
+      <c r="AB243" s="1"/>
+    </row>
+    <row r="244" spans="1:28">
+      <c r="A244" s="3">
+        <v>241</v>
+      </c>
+      <c r="B244" s="28"/>
+      <c r="C244" s="1"/>
+      <c r="D244" s="1"/>
+      <c r="E244" s="1"/>
+      <c r="F244" s="1"/>
+      <c r="G244" s="1"/>
+      <c r="H244" s="1"/>
+      <c r="I244" s="1"/>
+      <c r="J244" s="1"/>
+      <c r="K244" s="1"/>
+      <c r="L244" s="1"/>
+      <c r="M244" s="1"/>
+      <c r="N244" s="1"/>
+      <c r="O244" s="1"/>
+      <c r="P244" s="1"/>
+      <c r="Q244" s="1"/>
+      <c r="R244" s="1"/>
+      <c r="S244" s="1"/>
+      <c r="T244" s="1"/>
+      <c r="U244" s="1"/>
+      <c r="V244" s="1"/>
+      <c r="W244" s="1"/>
+      <c r="X244" s="1"/>
+      <c r="Y244" s="1"/>
+      <c r="Z244" s="1"/>
+      <c r="AA244" s="1"/>
+      <c r="AB244" s="1"/>
+    </row>
+    <row r="245" spans="1:28">
+      <c r="A245" s="3">
+        <v>242</v>
+      </c>
+      <c r="B245" s="28"/>
+      <c r="C245" s="1"/>
+      <c r="D245" s="1"/>
+      <c r="E245" s="1"/>
+      <c r="F245" s="1"/>
+      <c r="G245" s="1"/>
+      <c r="H245" s="1"/>
+      <c r="I245" s="1"/>
+      <c r="J245" s="1"/>
+      <c r="K245" s="1"/>
+      <c r="L245" s="1"/>
+      <c r="M245" s="1"/>
+      <c r="N245" s="1"/>
+      <c r="O245" s="1"/>
+      <c r="P245" s="1"/>
+      <c r="Q245" s="1"/>
+      <c r="R245" s="1"/>
+      <c r="S245" s="1"/>
+      <c r="T245" s="1"/>
+      <c r="U245" s="1"/>
+      <c r="V245" s="1"/>
+      <c r="W245" s="1"/>
+      <c r="X245" s="1"/>
+      <c r="Y245" s="1"/>
+      <c r="Z245" s="1"/>
+      <c r="AA245" s="1"/>
+      <c r="AB245" s="1"/>
+    </row>
+    <row r="246" spans="1:28">
+      <c r="A246" s="3">
+        <v>243</v>
+      </c>
+      <c r="B246" s="28"/>
+      <c r="C246" s="1"/>
+      <c r="D246" s="1"/>
+      <c r="E246" s="1"/>
+      <c r="F246" s="1"/>
+      <c r="G246" s="1"/>
+      <c r="H246" s="1"/>
+      <c r="I246" s="1"/>
+      <c r="J246" s="1"/>
+      <c r="K246" s="1"/>
+      <c r="L246" s="1"/>
+      <c r="M246" s="1"/>
+      <c r="N246" s="1"/>
+      <c r="O246" s="1"/>
+      <c r="P246" s="1"/>
+      <c r="Q246" s="1"/>
+      <c r="R246" s="1"/>
+      <c r="S246" s="1"/>
+      <c r="T246" s="1"/>
+      <c r="U246" s="1"/>
+      <c r="V246" s="1"/>
+      <c r="W246" s="1"/>
+      <c r="X246" s="1"/>
+      <c r="Y246" s="1"/>
+      <c r="Z246" s="1"/>
+      <c r="AA246" s="1"/>
+      <c r="AB246" s="1"/>
+    </row>
+    <row r="247" spans="1:28">
+      <c r="A247" s="3">
+        <v>244</v>
+      </c>
+      <c r="B247" s="28"/>
+      <c r="C247" s="1"/>
+      <c r="D247" s="1"/>
+      <c r="E247" s="1"/>
+      <c r="F247" s="1"/>
+      <c r="G247" s="1"/>
+      <c r="H247" s="1"/>
+      <c r="I247" s="1"/>
+      <c r="J247" s="1"/>
+      <c r="K247" s="1"/>
+      <c r="L247" s="1"/>
+      <c r="M247" s="1"/>
+      <c r="N247" s="1"/>
+      <c r="O247" s="1"/>
+      <c r="P247" s="1"/>
+      <c r="Q247" s="1"/>
+      <c r="R247" s="1"/>
+      <c r="S247" s="1"/>
+      <c r="T247" s="1"/>
+      <c r="U247" s="1"/>
+      <c r="V247" s="1"/>
+      <c r="W247" s="1"/>
+      <c r="X247" s="1"/>
+      <c r="Y247" s="1"/>
+      <c r="Z247" s="1"/>
+      <c r="AA247" s="1"/>
+      <c r="AB247" s="1"/>
+    </row>
+    <row r="248" spans="1:28">
+      <c r="A248" s="3">
+        <v>245</v>
+      </c>
+      <c r="B248" s="28"/>
+      <c r="C248" s="1"/>
+      <c r="D248" s="1"/>
+      <c r="E248" s="1"/>
+      <c r="F248" s="1"/>
+      <c r="G248" s="1"/>
+      <c r="H248" s="1"/>
+      <c r="I248" s="1"/>
+      <c r="J248" s="1"/>
+      <c r="K248" s="1"/>
+      <c r="L248" s="1"/>
+      <c r="M248" s="1"/>
+      <c r="N248" s="1"/>
+      <c r="O248" s="1"/>
+      <c r="P248" s="1"/>
+      <c r="Q248" s="1"/>
+      <c r="R248" s="1"/>
+      <c r="S248" s="1"/>
+      <c r="T248" s="1"/>
+      <c r="U248" s="1"/>
+      <c r="V248" s="1"/>
+      <c r="W248" s="1"/>
+      <c r="X248" s="1"/>
+      <c r="Y248" s="1"/>
+      <c r="Z248" s="1"/>
+      <c r="AA248" s="1"/>
+      <c r="AB248" s="1"/>
+    </row>
+    <row r="249" spans="1:28">
+      <c r="A249" s="3">
+        <v>246</v>
+      </c>
+      <c r="B249" s="28"/>
+      <c r="C249" s="1"/>
+      <c r="D249" s="1"/>
+      <c r="E249" s="1"/>
+      <c r="F249" s="1"/>
+      <c r="G249" s="1"/>
+      <c r="H249" s="1"/>
+      <c r="I249" s="1"/>
+      <c r="J249" s="1"/>
+      <c r="K249" s="1"/>
+      <c r="L249" s="1"/>
+      <c r="M249" s="1"/>
+      <c r="N249" s="1"/>
+      <c r="O249" s="1"/>
+      <c r="P249" s="1"/>
+      <c r="Q249" s="1"/>
+      <c r="R249" s="1"/>
+      <c r="S249" s="1"/>
+      <c r="T249" s="1"/>
+      <c r="U249" s="1"/>
+      <c r="V249" s="1"/>
+      <c r="W249" s="1"/>
+      <c r="X249" s="1"/>
+      <c r="Y249" s="1"/>
+      <c r="Z249" s="1"/>
+      <c r="AA249" s="1"/>
+      <c r="AB249" s="1"/>
+    </row>
+    <row r="250" spans="1:28">
+      <c r="A250" s="3">
+        <v>247</v>
+      </c>
+      <c r="B250" s="28"/>
+      <c r="C250" s="1"/>
+      <c r="D250" s="1"/>
+      <c r="E250" s="1"/>
+      <c r="F250" s="1"/>
+      <c r="G250" s="1"/>
+      <c r="H250" s="1"/>
+      <c r="I250" s="1"/>
+      <c r="J250" s="1"/>
+      <c r="K250" s="1"/>
+      <c r="L250" s="1"/>
+      <c r="M250" s="1"/>
+      <c r="N250" s="1"/>
+      <c r="O250" s="1"/>
+      <c r="P250" s="1"/>
+      <c r="Q250" s="1"/>
+      <c r="R250" s="1"/>
+      <c r="S250" s="1"/>
+      <c r="T250" s="1"/>
+      <c r="U250" s="1"/>
+      <c r="V250" s="1"/>
+      <c r="W250" s="1"/>
+      <c r="X250" s="1"/>
+      <c r="Y250" s="1"/>
+      <c r="Z250" s="1"/>
+      <c r="AA250" s="1"/>
+      <c r="AB250" s="1"/>
+    </row>
+    <row r="251" spans="1:28">
+      <c r="A251" s="3">
+        <v>248</v>
+      </c>
+      <c r="B251" s="28"/>
+      <c r="C251" s="1"/>
+      <c r="D251" s="1"/>
+      <c r="E251" s="1"/>
+      <c r="F251" s="1"/>
+      <c r="G251" s="1"/>
+      <c r="H251" s="1"/>
+      <c r="I251" s="1"/>
+      <c r="J251" s="1"/>
+      <c r="K251" s="1"/>
+      <c r="L251" s="1"/>
+      <c r="M251" s="1"/>
+      <c r="N251" s="1"/>
+      <c r="O251" s="1"/>
+      <c r="P251" s="1"/>
+      <c r="Q251" s="1"/>
+      <c r="R251" s="1"/>
+      <c r="S251" s="1"/>
+      <c r="T251" s="1"/>
+      <c r="U251" s="1"/>
+      <c r="V251" s="1"/>
+      <c r="W251" s="1"/>
+      <c r="X251" s="1"/>
+      <c r="Y251" s="1"/>
+      <c r="Z251" s="1"/>
+      <c r="AA251" s="1"/>
+      <c r="AB251" s="1"/>
+    </row>
+    <row r="252" spans="1:28">
+      <c r="A252" s="3">
+        <v>249</v>
+      </c>
+      <c r="B252" s="28"/>
+      <c r="C252" s="1"/>
+      <c r="D252" s="1"/>
+      <c r="E252" s="1"/>
+      <c r="F252" s="1"/>
+      <c r="G252" s="1"/>
+      <c r="H252" s="1"/>
+      <c r="I252" s="1"/>
+      <c r="J252" s="1"/>
+      <c r="K252" s="1"/>
+      <c r="L252" s="1"/>
+      <c r="M252" s="1"/>
+      <c r="N252" s="1"/>
+      <c r="O252" s="1"/>
+      <c r="P252" s="1"/>
+      <c r="Q252" s="1"/>
+      <c r="R252" s="1"/>
+      <c r="S252" s="1"/>
+      <c r="T252" s="1"/>
+      <c r="U252" s="1"/>
+      <c r="V252" s="1"/>
+      <c r="W252" s="1"/>
+      <c r="X252" s="1"/>
+      <c r="Y252" s="1"/>
+      <c r="Z252" s="1"/>
+      <c r="AA252" s="1"/>
+      <c r="AB252" s="1"/>
+    </row>
+    <row r="253" spans="1:28">
+      <c r="A253" s="3">
+        <v>250</v>
+      </c>
+      <c r="B253" s="28"/>
+      <c r="C253" s="1"/>
+      <c r="D253" s="1"/>
+      <c r="E253" s="1"/>
+      <c r="F253" s="1"/>
+      <c r="G253" s="1"/>
+      <c r="H253" s="1"/>
+      <c r="I253" s="1"/>
+      <c r="J253" s="1"/>
+      <c r="K253" s="1"/>
+      <c r="L253" s="1"/>
+      <c r="M253" s="1"/>
+      <c r="N253" s="1"/>
+      <c r="O253" s="1"/>
+      <c r="P253" s="1"/>
+      <c r="Q253" s="1"/>
+      <c r="R253" s="1"/>
+      <c r="S253" s="1"/>
+      <c r="T253" s="1"/>
+      <c r="U253" s="1"/>
+      <c r="V253" s="1"/>
+      <c r="W253" s="1"/>
+      <c r="X253" s="1"/>
+      <c r="Y253" s="1"/>
+      <c r="Z253" s="1"/>
+      <c r="AA253" s="1"/>
+      <c r="AB253" s="1"/>
+    </row>
+    <row r="254" spans="1:28">
+      <c r="A254" s="3">
+        <v>251</v>
+      </c>
+      <c r="B254" s="28"/>
+      <c r="C254" s="1"/>
+      <c r="D254" s="1"/>
+      <c r="E254" s="1"/>
+      <c r="F254" s="1"/>
+      <c r="G254" s="1"/>
+      <c r="H254" s="1"/>
+      <c r="I254" s="1"/>
+      <c r="J254" s="1"/>
+      <c r="K254" s="1"/>
+      <c r="L254" s="1"/>
+      <c r="M254" s="1"/>
+      <c r="N254" s="1"/>
+      <c r="O254" s="1"/>
+      <c r="P254" s="1"/>
+      <c r="Q254" s="1"/>
+      <c r="R254" s="1"/>
+      <c r="S254" s="1"/>
+      <c r="T254" s="1"/>
+      <c r="U254" s="1"/>
+      <c r="V254" s="1"/>
+      <c r="W254" s="1"/>
+      <c r="X254" s="1"/>
+      <c r="Y254" s="1"/>
+      <c r="Z254" s="1"/>
+      <c r="AA254" s="1"/>
+      <c r="AB254" s="1"/>
+    </row>
+    <row r="255" spans="1:28">
+      <c r="A255" s="3">
+        <v>252</v>
+      </c>
+      <c r="B255" s="28"/>
+      <c r="C255" s="1"/>
+      <c r="D255" s="1"/>
+      <c r="E255" s="1"/>
+      <c r="F255" s="1"/>
+      <c r="G255" s="1"/>
+      <c r="H255" s="1"/>
+      <c r="I255" s="1"/>
+      <c r="J255" s="1"/>
+      <c r="K255" s="1"/>
+      <c r="L255" s="1"/>
+      <c r="M255" s="1"/>
+      <c r="N255" s="1"/>
+      <c r="O255" s="1"/>
+      <c r="P255" s="1"/>
+      <c r="Q255" s="1"/>
+      <c r="R255" s="1"/>
+      <c r="S255" s="1"/>
+      <c r="T255" s="1"/>
+      <c r="U255" s="1"/>
+      <c r="V255" s="1"/>
+      <c r="W255" s="1"/>
+      <c r="X255" s="1"/>
+      <c r="Y255" s="1"/>
+      <c r="Z255" s="1"/>
+      <c r="AA255" s="1"/>
+      <c r="AB255" s="1"/>
+    </row>
+    <row r="256" spans="1:28">
+      <c r="A256" s="3">
+        <v>253</v>
+      </c>
+      <c r="B256" s="28"/>
+      <c r="C256" s="1"/>
+      <c r="D256" s="1"/>
+      <c r="E256" s="1"/>
+      <c r="F256" s="1"/>
+      <c r="G256" s="1"/>
+      <c r="H256" s="1"/>
+      <c r="I256" s="1"/>
+      <c r="J256" s="1"/>
+      <c r="K256" s="1"/>
+      <c r="L256" s="1"/>
+      <c r="M256" s="1"/>
+      <c r="N256" s="1"/>
+      <c r="O256" s="1"/>
+      <c r="P256" s="1"/>
+      <c r="Q256" s="1"/>
+      <c r="R256" s="1"/>
+      <c r="S256" s="1"/>
+      <c r="T256" s="1"/>
+      <c r="U256" s="1"/>
+      <c r="V256" s="1"/>
+      <c r="W256" s="1"/>
+      <c r="X256" s="1"/>
+      <c r="Y256" s="1"/>
+      <c r="Z256" s="1"/>
+      <c r="AA256" s="1"/>
+      <c r="AB256" s="1"/>
+    </row>
+    <row r="257" spans="1:28">
+      <c r="A257" s="3">
+        <v>254</v>
+      </c>
+      <c r="B257" s="28"/>
+      <c r="C257" s="1"/>
+      <c r="D257" s="1"/>
+      <c r="E257" s="1"/>
+      <c r="F257" s="1"/>
+      <c r="G257" s="1"/>
+      <c r="H257" s="1"/>
+      <c r="I257" s="1"/>
+      <c r="J257" s="1"/>
+      <c r="K257" s="1"/>
+      <c r="L257" s="1"/>
+      <c r="M257" s="1"/>
+      <c r="N257" s="1"/>
+      <c r="O257" s="1"/>
+      <c r="P257" s="1"/>
+      <c r="Q257" s="1"/>
+      <c r="R257" s="1"/>
+      <c r="S257" s="1"/>
+      <c r="T257" s="1"/>
+      <c r="U257" s="1"/>
+      <c r="V257" s="1"/>
+      <c r="W257" s="1"/>
+      <c r="X257" s="1"/>
+      <c r="Y257" s="1"/>
+      <c r="Z257" s="1"/>
+      <c r="AA257" s="1"/>
+      <c r="AB257" s="1"/>
+    </row>
+    <row r="258" spans="1:28">
+      <c r="A258" s="3">
+        <v>255</v>
+      </c>
+      <c r="B258" s="28"/>
+      <c r="C258" s="1"/>
+      <c r="D258" s="1"/>
+      <c r="E258" s="1"/>
+      <c r="F258" s="1"/>
+      <c r="G258" s="1"/>
+      <c r="H258" s="1"/>
+      <c r="I258" s="1"/>
+      <c r="J258" s="1"/>
+      <c r="K258" s="1"/>
+      <c r="L258" s="1"/>
+      <c r="M258" s="1"/>
+      <c r="N258" s="1"/>
+      <c r="O258" s="1"/>
+      <c r="P258" s="1"/>
+      <c r="Q258" s="1"/>
+      <c r="R258" s="1"/>
+      <c r="S258" s="1"/>
+      <c r="T258" s="1"/>
+      <c r="U258" s="1"/>
+      <c r="V258" s="1"/>
+      <c r="W258" s="1"/>
+      <c r="X258" s="1"/>
+      <c r="Y258" s="1"/>
+      <c r="Z258" s="1"/>
+      <c r="AA258" s="1"/>
+      <c r="AB258" s="1"/>
+    </row>
+    <row r="259" spans="1:28">
+      <c r="A259" s="3">
+        <v>256</v>
+      </c>
+      <c r="B259" s="28"/>
+      <c r="C259" s="1"/>
+      <c r="D259" s="1"/>
+      <c r="E259" s="1"/>
+      <c r="F259" s="1"/>
+      <c r="G259" s="1"/>
+      <c r="H259" s="1"/>
+      <c r="I259" s="1"/>
+      <c r="J259" s="1"/>
+      <c r="K259" s="1"/>
+      <c r="L259" s="1"/>
+      <c r="M259" s="1"/>
+      <c r="N259" s="1"/>
+      <c r="O259" s="1"/>
+      <c r="P259" s="1"/>
+      <c r="Q259" s="1"/>
+      <c r="R259" s="1"/>
+      <c r="S259" s="1"/>
+      <c r="T259" s="1"/>
+      <c r="U259" s="1"/>
+      <c r="V259" s="1"/>
+      <c r="W259" s="1"/>
+      <c r="X259" s="1"/>
+      <c r="Y259" s="1"/>
+      <c r="Z259" s="1"/>
+      <c r="AA259" s="1"/>
+      <c r="AB259" s="1"/>
+    </row>
+    <row r="260" spans="1:28">
+      <c r="A260" s="3">
+        <v>257</v>
+      </c>
+      <c r="B260" s="28"/>
+      <c r="C260" s="1"/>
+      <c r="D260" s="1"/>
+      <c r="E260" s="1"/>
+      <c r="F260" s="1"/>
+      <c r="G260" s="1"/>
+      <c r="H260" s="1"/>
+      <c r="I260" s="1"/>
+      <c r="J260" s="1"/>
+      <c r="K260" s="1"/>
+      <c r="L260" s="1"/>
+      <c r="M260" s="1"/>
+      <c r="N260" s="1"/>
+      <c r="O260" s="1"/>
+      <c r="P260" s="1"/>
+      <c r="Q260" s="1"/>
+      <c r="R260" s="1"/>
+      <c r="S260" s="1"/>
+      <c r="T260" s="1"/>
+      <c r="U260" s="1"/>
+      <c r="V260" s="1"/>
+      <c r="W260" s="1"/>
+      <c r="X260" s="1"/>
+      <c r="Y260" s="1"/>
+      <c r="Z260" s="1"/>
+      <c r="AA260" s="1"/>
+      <c r="AB260" s="1"/>
+    </row>
+    <row r="261" spans="1:28">
+      <c r="A261" s="3">
+        <v>258</v>
+      </c>
+      <c r="B261" s="28"/>
+      <c r="C261" s="1"/>
+      <c r="D261" s="1"/>
+      <c r="E261" s="1"/>
+      <c r="F261" s="1"/>
+      <c r="G261" s="1"/>
+      <c r="H261" s="1"/>
+      <c r="I261" s="1"/>
+      <c r="J261" s="1"/>
+      <c r="K261" s="1"/>
+      <c r="L261" s="1"/>
+      <c r="M261" s="1"/>
+      <c r="N261" s="1"/>
+      <c r="O261" s="1"/>
+      <c r="P261" s="1"/>
+      <c r="Q261" s="1"/>
+      <c r="R261" s="1"/>
+      <c r="S261" s="1"/>
+      <c r="T261" s="1"/>
+      <c r="U261" s="1"/>
+      <c r="V261" s="1"/>
+      <c r="W261" s="1"/>
+      <c r="X261" s="1"/>
+      <c r="Y261" s="1"/>
+      <c r="Z261" s="1"/>
+      <c r="AA261" s="1"/>
+      <c r="AB261" s="1"/>
+    </row>
+    <row r="262" spans="1:28">
+      <c r="A262" s="3">
+        <v>259</v>
+      </c>
+      <c r="B262" s="28"/>
+      <c r="C262" s="1"/>
+      <c r="D262" s="1"/>
+      <c r="E262" s="1"/>
+      <c r="F262" s="1"/>
+      <c r="G262" s="1"/>
+      <c r="H262" s="1"/>
+      <c r="I262" s="1"/>
+      <c r="J262" s="1"/>
+      <c r="K262" s="1"/>
+      <c r="L262" s="1"/>
+      <c r="M262" s="1"/>
+      <c r="N262" s="1"/>
+      <c r="O262" s="1"/>
+      <c r="P262" s="1"/>
+      <c r="Q262" s="1"/>
+      <c r="R262" s="1"/>
+      <c r="S262" s="1"/>
+      <c r="T262" s="1"/>
+      <c r="U262" s="1"/>
+      <c r="V262" s="1"/>
+      <c r="W262" s="1"/>
+      <c r="X262" s="1"/>
+      <c r="Y262" s="1"/>
+      <c r="Z262" s="1"/>
+      <c r="AA262" s="1"/>
+      <c r="AB262" s="1"/>
+    </row>
+    <row r="263" spans="1:28">
+      <c r="A263" s="3">
+        <v>260</v>
+      </c>
+      <c r="B263" s="28"/>
+      <c r="C263" s="1"/>
+      <c r="D263" s="1"/>
+      <c r="E263" s="1"/>
+      <c r="F263" s="1"/>
+      <c r="G263" s="1"/>
+      <c r="H263" s="1"/>
+      <c r="I263" s="1"/>
+      <c r="J263" s="1"/>
+      <c r="K263" s="1"/>
+      <c r="L263" s="1"/>
+      <c r="M263" s="1"/>
+      <c r="N263" s="1"/>
+      <c r="O263" s="1"/>
+      <c r="P263" s="1"/>
+      <c r="Q263" s="1"/>
+      <c r="R263" s="1"/>
+      <c r="S263" s="1"/>
+      <c r="T263" s="1"/>
+      <c r="U263" s="1"/>
+      <c r="V263" s="1"/>
+      <c r="W263" s="1"/>
+      <c r="X263" s="1"/>
+      <c r="Y263" s="1"/>
+      <c r="Z263" s="1"/>
+      <c r="AA263" s="1"/>
+      <c r="AB263" s="1"/>
+    </row>
+    <row r="264" spans="1:28">
+      <c r="A264" s="3">
+        <v>261</v>
+      </c>
+      <c r="B264" s="28"/>
+      <c r="C264" s="1"/>
+      <c r="D264" s="1"/>
+      <c r="E264" s="1"/>
+      <c r="F264" s="1"/>
+      <c r="G264" s="1"/>
+      <c r="H264" s="1"/>
+      <c r="I264" s="1"/>
+      <c r="J264" s="1"/>
+      <c r="K264" s="1"/>
+      <c r="L264" s="1"/>
+      <c r="M264" s="1"/>
+      <c r="N264" s="1"/>
+      <c r="O264" s="1"/>
+      <c r="P264" s="1"/>
+      <c r="Q264" s="1"/>
+      <c r="R264" s="1"/>
+      <c r="S264" s="1"/>
+      <c r="T264" s="1"/>
+      <c r="U264" s="1"/>
+      <c r="V264" s="1"/>
+      <c r="W264" s="1"/>
+      <c r="X264" s="1"/>
+      <c r="Y264" s="1"/>
+      <c r="Z264" s="1"/>
+      <c r="AA264" s="1"/>
+      <c r="AB264" s="1"/>
+    </row>
+    <row r="265" spans="1:28">
+      <c r="A265" s="3">
+        <v>262</v>
+      </c>
+      <c r="B265" s="28"/>
+      <c r="C265" s="1"/>
+      <c r="D265" s="1"/>
+      <c r="E265" s="1"/>
+      <c r="F265" s="1"/>
+      <c r="G265" s="1"/>
+      <c r="H265" s="1"/>
+      <c r="I265" s="1"/>
+      <c r="J265" s="1"/>
+      <c r="K265" s="1"/>
+      <c r="L265" s="1"/>
+      <c r="M265" s="1"/>
+      <c r="N265" s="1"/>
+      <c r="O265" s="1"/>
+      <c r="P265" s="1"/>
+      <c r="Q265" s="1"/>
+      <c r="R265" s="1"/>
+      <c r="S265" s="1"/>
+      <c r="T265" s="1"/>
+      <c r="U265" s="1"/>
+      <c r="V265" s="1"/>
+      <c r="W265" s="1"/>
+      <c r="X265" s="1"/>
+      <c r="Y265" s="1"/>
+      <c r="Z265" s="1"/>
+      <c r="AA265" s="1"/>
+      <c r="AB265" s="1"/>
+    </row>
+    <row r="266" spans="1:28">
+      <c r="A266" s="3">
+        <v>263</v>
+      </c>
+      <c r="B266" s="28"/>
+      <c r="C266" s="1"/>
+      <c r="D266" s="1"/>
+      <c r="E266" s="1"/>
+      <c r="F266" s="1"/>
+      <c r="G266" s="1"/>
+      <c r="H266" s="1"/>
+      <c r="I266" s="1"/>
+      <c r="J266" s="1"/>
+      <c r="K266" s="1"/>
+      <c r="L266" s="1"/>
+      <c r="M266" s="1"/>
+      <c r="N266" s="1"/>
+      <c r="O266" s="1"/>
+      <c r="P266" s="1"/>
+      <c r="Q266" s="1"/>
+      <c r="R266" s="1"/>
+      <c r="S266" s="1"/>
+      <c r="T266" s="1"/>
+      <c r="U266" s="1"/>
+      <c r="V266" s="1"/>
+      <c r="W266" s="1"/>
+      <c r="X266" s="1"/>
+      <c r="Y266" s="1"/>
+      <c r="Z266" s="1"/>
+      <c r="AA266" s="1"/>
+      <c r="AB266" s="1"/>
+    </row>
+    <row r="267" spans="1:28">
+      <c r="A267" s="3">
+        <v>264</v>
+      </c>
+      <c r="B267" s="28"/>
+      <c r="C267" s="1"/>
+      <c r="D267" s="1"/>
+      <c r="E267" s="1"/>
+      <c r="F267" s="1"/>
+      <c r="G267" s="1"/>
+      <c r="H267" s="1"/>
+      <c r="I267" s="1"/>
+      <c r="J267" s="1"/>
+      <c r="K267" s="1"/>
+      <c r="L267" s="1"/>
+      <c r="M267" s="1"/>
+      <c r="N267" s="1"/>
+      <c r="O267" s="1"/>
+      <c r="P267" s="1"/>
+      <c r="Q267" s="1"/>
+      <c r="R267" s="1"/>
+      <c r="S267" s="1"/>
+      <c r="T267" s="1"/>
+      <c r="U267" s="1"/>
+      <c r="V267" s="1"/>
+      <c r="W267" s="1"/>
+      <c r="X267" s="1"/>
+      <c r="Y267" s="1"/>
+      <c r="Z267" s="1"/>
+      <c r="AA267" s="1"/>
+      <c r="AB267" s="1"/>
+    </row>
+    <row r="268" spans="1:28">
+      <c r="A268" s="3">
+        <v>265</v>
+      </c>
+      <c r="B268" s="28"/>
+      <c r="C268" s="1"/>
+      <c r="D268" s="1"/>
+      <c r="E268" s="1"/>
+      <c r="F268" s="1"/>
+      <c r="G268" s="1"/>
+      <c r="H268" s="1"/>
+      <c r="I268" s="1"/>
+      <c r="J268" s="1"/>
+      <c r="K268" s="1"/>
+      <c r="L268" s="1"/>
+      <c r="M268" s="1"/>
+      <c r="N268" s="1"/>
+      <c r="O268" s="1"/>
+      <c r="P268" s="1"/>
+      <c r="Q268" s="1"/>
+      <c r="R268" s="1"/>
+      <c r="S268" s="1"/>
+      <c r="T268" s="1"/>
+      <c r="U268" s="1"/>
+      <c r="V268" s="1"/>
+      <c r="W268" s="1"/>
+      <c r="X268" s="1"/>
+      <c r="Y268" s="1"/>
+      <c r="Z268" s="1"/>
+      <c r="AA268" s="1"/>
+      <c r="AB268" s="1"/>
+    </row>
+    <row r="269" spans="1:28">
+      <c r="A269" s="3">
+        <v>266</v>
+      </c>
+      <c r="B269" s="28"/>
+      <c r="C269" s="1"/>
+      <c r="D269" s="1"/>
+      <c r="E269" s="1"/>
+      <c r="F269" s="1"/>
+      <c r="G269" s="1"/>
+      <c r="H269" s="1"/>
+      <c r="I269" s="1"/>
+      <c r="J269" s="1"/>
+      <c r="K269" s="1"/>
+      <c r="L269" s="1"/>
+      <c r="M269" s="1"/>
+      <c r="N269" s="1"/>
+      <c r="O269" s="1"/>
+      <c r="P269" s="1"/>
+      <c r="Q269" s="1"/>
+      <c r="R269" s="1"/>
+      <c r="S269" s="1"/>
+      <c r="T269" s="1"/>
+      <c r="U269" s="1"/>
+      <c r="V269" s="1"/>
+      <c r="W269" s="1"/>
+      <c r="X269" s="1"/>
+      <c r="Y269" s="1"/>
+      <c r="Z269" s="1"/>
+      <c r="AA269" s="1"/>
+      <c r="AB269" s="1"/>
+    </row>
+    <row r="270" spans="1:28">
+      <c r="A270" s="3">
+        <v>267</v>
+      </c>
+      <c r="B270" s="28"/>
+      <c r="C270" s="1"/>
+      <c r="D270" s="1"/>
+      <c r="E270" s="1"/>
+      <c r="F270" s="1"/>
+      <c r="G270" s="1"/>
+      <c r="H270" s="1"/>
+      <c r="I270" s="1"/>
+      <c r="J270" s="1"/>
+      <c r="K270" s="1"/>
+      <c r="L270" s="1"/>
+      <c r="M270" s="1"/>
+      <c r="N270" s="1"/>
+      <c r="O270" s="1"/>
+      <c r="P270" s="1"/>
+      <c r="Q270" s="1"/>
+      <c r="R270" s="1"/>
+      <c r="S270" s="1"/>
+      <c r="T270" s="1"/>
+      <c r="U270" s="1"/>
+      <c r="V270" s="1"/>
+      <c r="W270" s="1"/>
+      <c r="X270" s="1"/>
+      <c r="Y270" s="1"/>
+      <c r="Z270" s="1"/>
+      <c r="AA270" s="1"/>
+      <c r="AB270" s="1"/>
+    </row>
+    <row r="271" spans="1:28">
+      <c r="A271" s="3">
+        <v>268</v>
+      </c>
+      <c r="B271" s="28"/>
+      <c r="C271" s="1"/>
+      <c r="D271" s="1"/>
+      <c r="E271" s="1"/>
+      <c r="F271" s="1"/>
+      <c r="G271" s="1"/>
+      <c r="H271" s="1"/>
+      <c r="I271" s="1"/>
+      <c r="J271" s="1"/>
+      <c r="K271" s="1"/>
+      <c r="L271" s="1"/>
+      <c r="M271" s="1"/>
+      <c r="N271" s="1"/>
+      <c r="O271" s="1"/>
+      <c r="P271" s="1"/>
+      <c r="Q271" s="1"/>
+      <c r="R271" s="1"/>
+      <c r="S271" s="1"/>
+      <c r="T271" s="1"/>
+      <c r="U271" s="1"/>
+      <c r="V271" s="1"/>
+      <c r="W271" s="1"/>
+      <c r="X271" s="1"/>
+      <c r="Y271" s="1"/>
+      <c r="Z271" s="1"/>
+      <c r="AA271" s="1"/>
+      <c r="AB271" s="1"/>
+    </row>
+    <row r="272" spans="1:28">
+      <c r="A272" s="3">
+        <v>269</v>
+      </c>
+      <c r="B272" s="28"/>
+      <c r="C272" s="1"/>
+      <c r="D272" s="1"/>
+      <c r="E272" s="1"/>
+      <c r="F272" s="1"/>
+      <c r="G272" s="1"/>
+      <c r="H272" s="1"/>
+      <c r="I272" s="1"/>
+      <c r="J272" s="1"/>
+      <c r="K272" s="1"/>
+      <c r="L272" s="1"/>
+      <c r="M272" s="1"/>
+      <c r="N272" s="1"/>
+      <c r="O272" s="1"/>
+      <c r="P272" s="1"/>
+      <c r="Q272" s="1"/>
+      <c r="R272" s="1"/>
+      <c r="S272" s="1"/>
+      <c r="T272" s="1"/>
+      <c r="U272" s="1"/>
+      <c r="V272" s="1"/>
+      <c r="W272" s="1"/>
+      <c r="X272" s="1"/>
+      <c r="Y272" s="1"/>
+      <c r="Z272" s="1"/>
+      <c r="AA272" s="1"/>
+      <c r="AB272" s="1"/>
+    </row>
+    <row r="273" spans="1:28">
+      <c r="A273" s="3">
+        <v>270</v>
+      </c>
+      <c r="B273" s="28"/>
+      <c r="C273" s="1"/>
+      <c r="D273" s="1"/>
+      <c r="E273" s="1"/>
+      <c r="F273" s="1"/>
+      <c r="G273" s="1"/>
+      <c r="H273" s="1"/>
+      <c r="I273" s="1"/>
+      <c r="J273" s="1"/>
+      <c r="K273" s="1"/>
+      <c r="L273" s="1"/>
+      <c r="M273" s="1"/>
+      <c r="N273" s="1"/>
+      <c r="O273" s="1"/>
+      <c r="P273" s="1"/>
+      <c r="Q273" s="1"/>
+      <c r="R273" s="1"/>
+      <c r="S273" s="1"/>
+      <c r="T273" s="1"/>
+      <c r="U273" s="1"/>
+      <c r="V273" s="1"/>
+      <c r="W273" s="1"/>
+      <c r="X273" s="1"/>
+      <c r="Y273" s="1"/>
+      <c r="Z273" s="1"/>
+      <c r="AA273" s="1"/>
+      <c r="AB273" s="1"/>
+    </row>
+    <row r="274" spans="1:28">
+      <c r="A274" s="3">
+        <v>271</v>
+      </c>
+      <c r="B274" s="28"/>
+      <c r="C274" s="1"/>
+      <c r="D274" s="1"/>
+      <c r="E274" s="1"/>
+      <c r="F274" s="1"/>
+      <c r="G274" s="1"/>
+      <c r="H274" s="1"/>
+      <c r="I274" s="1"/>
+      <c r="J274" s="1"/>
+      <c r="K274" s="1"/>
+      <c r="L274" s="1"/>
+      <c r="M274" s="1"/>
+      <c r="N274" s="1"/>
+      <c r="O274" s="1"/>
+      <c r="P274" s="1"/>
+      <c r="Q274" s="1"/>
+      <c r="R274" s="1"/>
+      <c r="S274" s="1"/>
+      <c r="T274" s="1"/>
+      <c r="U274" s="1"/>
+      <c r="V274" s="1"/>
+      <c r="W274" s="1"/>
+      <c r="X274" s="1"/>
+      <c r="Y274" s="1"/>
+      <c r="Z274" s="1"/>
+      <c r="AA274" s="1"/>
+      <c r="AB274" s="1"/>
+    </row>
+    <row r="275" spans="1:28">
+      <c r="A275" s="3">
+        <v>272</v>
+      </c>
+      <c r="B275" s="28"/>
+      <c r="C275" s="1"/>
+      <c r="D275" s="1"/>
+      <c r="E275" s="1"/>
+      <c r="F275" s="1"/>
+      <c r="G275" s="1"/>
+      <c r="H275" s="1"/>
+      <c r="I275" s="1"/>
+      <c r="J275" s="1"/>
+      <c r="K275" s="1"/>
+      <c r="L275" s="1"/>
+      <c r="M275" s="1"/>
+      <c r="N275" s="1"/>
+      <c r="O275" s="1"/>
+      <c r="P275" s="1"/>
+      <c r="Q275" s="1"/>
+      <c r="R275" s="1"/>
+      <c r="S275" s="1"/>
+      <c r="T275" s="1"/>
+      <c r="U275" s="1"/>
+      <c r="V275" s="1"/>
+      <c r="W275" s="1"/>
+      <c r="X275" s="1"/>
+      <c r="Y275" s="1"/>
+      <c r="Z275" s="1"/>
+      <c r="AA275" s="1"/>
+      <c r="AB275" s="1"/>
+    </row>
+    <row r="276" spans="1:28">
+      <c r="A276" s="3">
+        <v>273</v>
+      </c>
+      <c r="B276" s="28"/>
+      <c r="C276" s="1"/>
+      <c r="D276" s="1"/>
+      <c r="E276" s="1"/>
+      <c r="F276" s="1"/>
+      <c r="G276" s="1"/>
+      <c r="H276" s="1"/>
+      <c r="I276" s="1"/>
+      <c r="J276" s="1"/>
+      <c r="K276" s="1"/>
+      <c r="L276" s="1"/>
+      <c r="M276" s="1"/>
+      <c r="N276" s="1"/>
+      <c r="O276" s="1"/>
+      <c r="P276" s="1"/>
+      <c r="Q276" s="1"/>
+      <c r="R276" s="1"/>
+      <c r="S276" s="1"/>
+      <c r="T276" s="1"/>
+      <c r="U276" s="1"/>
+      <c r="V276" s="1"/>
+      <c r="W276" s="1"/>
+      <c r="X276" s="1"/>
+      <c r="Y276" s="1"/>
+      <c r="Z276" s="1"/>
+      <c r="AA276" s="1"/>
+      <c r="AB276" s="1"/>
+    </row>
+    <row r="277" spans="1:28">
+      <c r="A277" s="3">
+        <v>274</v>
+      </c>
+      <c r="B277" s="28"/>
+      <c r="C277" s="1"/>
+      <c r="D277" s="1"/>
+      <c r="E277" s="1"/>
+      <c r="F277" s="1"/>
+      <c r="G277" s="1"/>
+      <c r="H277" s="1"/>
+      <c r="I277" s="1"/>
+      <c r="J277" s="1"/>
+      <c r="K277" s="1"/>
+      <c r="L277" s="1"/>
+      <c r="M277" s="1"/>
+      <c r="N277" s="1"/>
+      <c r="O277" s="1"/>
+      <c r="P277" s="1"/>
+      <c r="Q277" s="1"/>
+      <c r="R277" s="1"/>
+      <c r="S277" s="1"/>
+      <c r="T277" s="1"/>
+      <c r="U277" s="1"/>
+      <c r="V277" s="1"/>
+      <c r="W277" s="1"/>
+      <c r="X277" s="1"/>
+      <c r="Y277" s="1"/>
+      <c r="Z277" s="1"/>
+      <c r="AA277" s="1"/>
+      <c r="AB277" s="1"/>
+    </row>
+    <row r="278" spans="1:28">
+      <c r="A278" s="3">
+        <v>275</v>
+      </c>
+      <c r="B278" s="28"/>
+      <c r="C278" s="1"/>
+      <c r="D278" s="1"/>
+      <c r="E278" s="1"/>
+      <c r="F278" s="1"/>
+      <c r="G278" s="1"/>
+      <c r="H278" s="1"/>
+      <c r="I278" s="1"/>
+      <c r="J278" s="1"/>
+      <c r="K278" s="1"/>
+      <c r="L278" s="1"/>
+      <c r="M278" s="1"/>
+      <c r="N278" s="1"/>
+      <c r="O278" s="1"/>
+      <c r="P278" s="1"/>
+      <c r="Q278" s="1"/>
+      <c r="R278" s="1"/>
+      <c r="S278" s="1"/>
+      <c r="T278" s="1"/>
+      <c r="U278" s="1"/>
+      <c r="V278" s="1"/>
+      <c r="W278" s="1"/>
+      <c r="X278" s="1"/>
+      <c r="Y278" s="1"/>
+      <c r="Z278" s="1"/>
+      <c r="AA278" s="1"/>
+      <c r="AB278" s="1"/>
+    </row>
+    <row r="279" spans="1:28">
+      <c r="A279" s="3">
+        <v>276</v>
+      </c>
+      <c r="B279" s="28"/>
+      <c r="C279" s="1"/>
+      <c r="D279" s="1"/>
+      <c r="E279" s="1"/>
+      <c r="F279" s="1"/>
+      <c r="G279" s="1"/>
+      <c r="H279" s="1"/>
+      <c r="I279" s="1"/>
+      <c r="J279" s="1"/>
+      <c r="K279" s="1"/>
+      <c r="L279" s="1"/>
+      <c r="M279" s="1"/>
+      <c r="N279" s="1"/>
+      <c r="O279" s="1"/>
+      <c r="P279" s="1"/>
+      <c r="Q279" s="1"/>
+      <c r="R279" s="1"/>
+      <c r="S279" s="1"/>
+      <c r="T279" s="1"/>
+      <c r="U279" s="1"/>
+      <c r="V279" s="1"/>
+      <c r="W279" s="1"/>
+      <c r="X279" s="1"/>
+      <c r="Y279" s="1"/>
+      <c r="Z279" s="1"/>
+      <c r="AA279" s="1"/>
+      <c r="AB279" s="1"/>
+    </row>
+    <row r="280" spans="1:28">
+      <c r="A280" s="3">
+        <v>277</v>
+      </c>
+      <c r="B280" s="28"/>
+      <c r="C280" s="1"/>
+      <c r="D280" s="1"/>
+      <c r="E280" s="1"/>
+      <c r="F280" s="1"/>
+      <c r="G280" s="1"/>
+      <c r="H280" s="1"/>
+      <c r="I280" s="1"/>
+      <c r="J280" s="1"/>
+      <c r="K280" s="1"/>
+      <c r="L280" s="1"/>
+      <c r="M280" s="1"/>
+      <c r="N280" s="1"/>
+      <c r="O280" s="1"/>
+      <c r="P280" s="1"/>
+      <c r="Q280" s="1"/>
+      <c r="R280" s="1"/>
+      <c r="S280" s="1"/>
+      <c r="T280" s="1"/>
+      <c r="U280" s="1"/>
+      <c r="V280" s="1"/>
+      <c r="W280" s="1"/>
+      <c r="X280" s="1"/>
+      <c r="Y280" s="1"/>
+      <c r="Z280" s="1"/>
+      <c r="AA280" s="1"/>
+      <c r="AB280" s="1"/>
+    </row>
   </sheetData>
   <autoFilter ref="A3:AA230" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="3">
@@ -10003,7 +11817,7 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C230 D4:D163 D181:D230 E4:AB230" xr:uid="{C452CDD0-B3A9-419A-AD4E-0E5CE327C346}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D181:D280 D4:D163 E4:AB280 C4:C280" xr:uid="{C452CDD0-B3A9-419A-AD4E-0E5CE327C346}">
       <formula1>"〇,×,△"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D164:D180" xr:uid="{E47C5A29-770A-4FF4-AE4B-E53AB5761727}">
@@ -10017,14 +11831,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8513D353-BD33-4F18-8682-09CF4EA59EE5}">
   <dimension ref="A2:H170"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="10.1875" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="16" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.8125" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.0625" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.9375" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="6.5625" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.08203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.9140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="6.58203125" style="16" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="16"/>
   </cols>
   <sheetData>
@@ -10355,7 +12169,9 @@
       <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="19"/>
+      <c r="A24" s="19" t="s">
+        <v>269</v>
+      </c>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
@@ -10365,7 +12181,9 @@
       <c r="H24" s="18"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="19"/>
+      <c r="A25" s="19" t="s">
+        <v>270</v>
+      </c>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\副業\LINE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CFD4556-EE53-435C-8FD5-6B20099E8699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E19D36D-FBC9-48FC-AACD-9636BA1F6C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="リスト" sheetId="1" r:id="rId1"/>
     <sheet name="進捗表" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">リスト!$A$3:$AA$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">リスト!$A$3:$AB$280</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="279">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -456,9 +456,6 @@
   </si>
   <si>
     <t>なんでこうなるの？</t>
-  </si>
-  <si>
-    <t>敬失礼しました</t>
   </si>
   <si>
     <t>おぬしー</t>
@@ -1354,6 +1351,63 @@
     <rPh sb="0" eb="2">
       <t>ヨウセイ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>馬1</t>
+    <rPh sb="0" eb="1">
+      <t>ウマ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>鯛1</t>
+    <rPh sb="0" eb="1">
+      <t>タイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>馬2</t>
+    <rPh sb="0" eb="1">
+      <t>ウマ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>推し1</t>
+    <rPh sb="0" eb="1">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>基本</t>
+    <rPh sb="0" eb="2">
+      <t>キホン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>失礼しました</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>時間だよ</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>急げ</t>
+    <rPh sb="0" eb="1">
+      <t>イソ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>旅したい</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1483,7 +1537,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1547,6 +1601,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1554,7 +1632,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1616,6 +1694,8 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1637,8 +1717,21 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2013,53 +2106,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB280"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:AC280"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
-    <col min="1" max="1" width="3.4140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="3.58203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.58203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="28" width="3.58203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.4375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.4375" style="34" customWidth="1"/>
+    <col min="3" max="3" width="33.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="3.5625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2.5625" bestFit="1" customWidth="1"/>
+    <col min="11" max="29" width="3.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="22.5">
-      <c r="A1" s="24"/>
-      <c r="B1" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="C1" s="27" t="s">
+    <row r="1" spans="1:29" ht="22.9">
+      <c r="A1" s="26"/>
+      <c r="B1" s="30" t="s">
+        <v>274</v>
+      </c>
+      <c r="C1" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-    </row>
-    <row r="2" spans="1:28" ht="22.5">
-      <c r="A2" s="25"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="e" vm="1">
+      <c r="D1" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+    </row>
+    <row r="2" spans="1:29" ht="22.9">
+      <c r="A2" s="27"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -2069,18 +2167,18 @@
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
-      <c r="O2" s="5" t="e" vm="2">
+      <c r="O2" s="5"/>
+      <c r="P2" s="5" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
-      <c r="R2" s="5" t="e" vm="3">
+      <c r="R2" s="5"/>
+      <c r="S2" s="5" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="S2" s="5" t="e" vm="4">
+      <c r="T2" s="5" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="T2" s="5"/>
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
@@ -2089,113 +2187,119 @@
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5"/>
-    </row>
-    <row r="3" spans="1:28" s="13" customFormat="1" ht="92.5" thickBot="1">
-      <c r="A3" s="26"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="11" t="s">
-        <v>124</v>
-      </c>
+      <c r="AC2" s="5"/>
+    </row>
+    <row r="3" spans="1:29" s="13" customFormat="1" ht="90.4" thickBot="1">
+      <c r="A3" s="28"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="25"/>
       <c r="D3" s="11" t="s">
         <v>123</v>
       </c>
       <c r="E3" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="J3" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="K3" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="L3" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="M3" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="N3" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="O3" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="P3" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="Q3" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="R3" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="S3" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="R3" s="11" t="s">
+      <c r="T3" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="S3" s="11" t="s">
+      <c r="U3" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="V3" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="T3" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="U3" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>232</v>
-      </c>
       <c r="W3" s="11" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="X3" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="Z3" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="Y3" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="Z3" s="11"/>
       <c r="AA3" s="11"/>
       <c r="AB3" s="11"/>
-    </row>
-    <row r="4" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1" thickTop="1">
+      <c r="AC3" s="11"/>
+    </row>
+    <row r="4" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E4" s="1"/>
+      <c r="B4" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="P4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
+      <c r="S4" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -2205,39 +2309,44 @@
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
-    </row>
-    <row r="5" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC4" s="1"/>
+    </row>
+    <row r="5" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E5" s="1"/>
+      <c r="B5" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="O5" s="1"/>
       <c r="P5" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q5" s="1"/>
+        <v>158</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
+      <c r="S5" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -2247,22 +2356,23 @@
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
-    </row>
-    <row r="6" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC5" s="1"/>
+    </row>
+    <row r="6" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="3">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="C6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="4" t="s">
+        <v>229</v>
+      </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -2283,15 +2393,16 @@
       <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
-    </row>
-    <row r="7" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC6" s="1"/>
+    </row>
+    <row r="7" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="1"/>
+      <c r="C7" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -2317,15 +2428,16 @@
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
-    </row>
-    <row r="8" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC7" s="1"/>
+    </row>
+    <row r="8" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="3">
         <v>5</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="1"/>
+      <c r="C8" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -2351,15 +2463,16 @@
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
-    </row>
-    <row r="9" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC8" s="1"/>
+    </row>
+    <row r="9" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="3">
         <v>6</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -2385,15 +2498,16 @@
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
-    </row>
-    <row r="10" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC9" s="1"/>
+    </row>
+    <row r="10" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="3">
         <v>7</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="1"/>
+      <c r="C10" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -2419,22 +2533,23 @@
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
-    </row>
-    <row r="11" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC10" s="1"/>
+    </row>
+    <row r="11" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="3">
         <v>8</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="C11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="4" t="s">
+        <v>230</v>
+      </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -2455,15 +2570,16 @@
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
-    </row>
-    <row r="12" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC11" s="1"/>
+    </row>
+    <row r="12" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="1"/>
+      <c r="C12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -2489,15 +2605,16 @@
       <c r="Z12" s="1"/>
       <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
-    </row>
-    <row r="13" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC12" s="1"/>
+    </row>
+    <row r="13" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="3">
         <v>10</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="1"/>
+      <c r="C13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -2523,15 +2640,16 @@
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
-    </row>
-    <row r="14" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC13" s="1"/>
+    </row>
+    <row r="14" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="3">
         <v>11</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="1"/>
+      <c r="C14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -2557,15 +2675,16 @@
       <c r="Z14" s="1"/>
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
-    </row>
-    <row r="15" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC14" s="1"/>
+    </row>
+    <row r="15" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="3">
         <v>12</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="1"/>
+      <c r="C15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -2591,15 +2710,16 @@
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
-    </row>
-    <row r="16" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC15" s="1"/>
+    </row>
+    <row r="16" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="3">
         <v>13</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="1"/>
+      <c r="C16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -2625,15 +2745,16 @@
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
-    </row>
-    <row r="17" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC16" s="1"/>
+    </row>
+    <row r="17" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="3">
         <v>14</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="1"/>
+      <c r="C17" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -2659,15 +2780,16 @@
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
-    </row>
-    <row r="18" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC17" s="1"/>
+    </row>
+    <row r="18" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="3">
         <v>15</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="1"/>
+      <c r="C18" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -2693,15 +2815,16 @@
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
-    </row>
-    <row r="19" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC18" s="1"/>
+    </row>
+    <row r="19" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="3">
         <v>16</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="1"/>
+      <c r="C19" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -2727,15 +2850,16 @@
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
-    </row>
-    <row r="20" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC19" s="1"/>
+    </row>
+    <row r="20" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="3">
         <v>17</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="1"/>
+      <c r="C20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -2761,15 +2885,16 @@
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
-    </row>
-    <row r="21" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC20" s="1"/>
+    </row>
+    <row r="21" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="3">
         <v>18</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="1"/>
+      <c r="C21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -2795,22 +2920,23 @@
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
-    </row>
-    <row r="22" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC21" s="1"/>
+    </row>
+    <row r="22" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="3">
         <v>19</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="1"/>
+      <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
-      <c r="G22" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -2831,15 +2957,16 @@
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
-    </row>
-    <row r="23" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC22" s="1"/>
+    </row>
+    <row r="23" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="3">
         <v>20</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="1"/>
+      <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -2865,15 +2992,16 @@
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
-    </row>
-    <row r="24" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC23" s="1"/>
+    </row>
+    <row r="24" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="3">
         <v>21</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="1"/>
+      <c r="C24" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -2899,15 +3027,16 @@
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
-    </row>
-    <row r="25" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC24" s="1"/>
+    </row>
+    <row r="25" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="3">
         <v>22</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="1"/>
+      <c r="C25" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -2933,15 +3062,16 @@
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
-    </row>
-    <row r="26" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC25" s="1"/>
+    </row>
+    <row r="26" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="3">
         <v>23</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="1"/>
+      <c r="C26" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -2967,15 +3097,16 @@
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
-    </row>
-    <row r="27" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC26" s="1"/>
+    </row>
+    <row r="27" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="3">
         <v>24</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="4" t="s">
+        <v>217</v>
+      </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -2988,10 +3119,10 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
-      <c r="P27" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
@@ -3003,15 +3134,16 @@
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
-    </row>
-    <row r="28" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC27" s="1"/>
+    </row>
+    <row r="28" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="3">
         <v>25</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="1"/>
+      <c r="C28" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
@@ -3037,15 +3169,16 @@
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
-    </row>
-    <row r="29" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC28" s="1"/>
+    </row>
+    <row r="29" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="3">
         <v>26</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="1"/>
+      <c r="C29" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
@@ -3071,15 +3204,16 @@
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
-    </row>
-    <row r="30" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC29" s="1"/>
+    </row>
+    <row r="30" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="3">
         <v>27</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="1"/>
+      <c r="C30" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -3105,24 +3239,25 @@
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
-    </row>
-    <row r="31" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC30" s="1"/>
+    </row>
+    <row r="31" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="3">
         <v>28</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="4" t="s">
+        <v>218</v>
+      </c>
       <c r="D31" s="1"/>
-      <c r="E31" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -3130,10 +3265,10 @@
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
-      <c r="P31" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
@@ -3145,20 +3280,21 @@
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
-    </row>
-    <row r="32" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC31" s="1"/>
+    </row>
+    <row r="32" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="3">
         <v>29</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="1"/>
+      <c r="C32" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -3181,15 +3317,16 @@
       <c r="Z32" s="1"/>
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
-    </row>
-    <row r="33" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC32" s="1"/>
+    </row>
+    <row r="33" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="3">
         <v>30</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="1"/>
+      <c r="C33" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -3215,15 +3352,16 @@
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
-    </row>
-    <row r="34" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC33" s="1"/>
+    </row>
+    <row r="34" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A34" s="3">
         <v>31</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="1"/>
+      <c r="C34" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
@@ -3249,15 +3387,16 @@
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
-    </row>
-    <row r="35" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC34" s="1"/>
+    </row>
+    <row r="35" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A35" s="3">
         <v>32</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="1"/>
+      <c r="C35" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
@@ -3283,15 +3422,16 @@
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
-    </row>
-    <row r="36" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC35" s="1"/>
+    </row>
+    <row r="36" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A36" s="3">
         <v>33</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="1"/>
+      <c r="C36" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
@@ -3317,15 +3457,16 @@
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
-    </row>
-    <row r="37" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC36" s="1"/>
+    </row>
+    <row r="37" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A37" s="3">
         <v>34</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="1"/>
+      <c r="C37" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -3351,15 +3492,16 @@
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
-    </row>
-    <row r="38" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC37" s="1"/>
+    </row>
+    <row r="38" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A38" s="3">
         <v>35</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="1"/>
+      <c r="C38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -3385,15 +3527,16 @@
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
-    </row>
-    <row r="39" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC38" s="1"/>
+    </row>
+    <row r="39" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A39" s="3">
         <v>36</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="1"/>
+      <c r="C39" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -3419,15 +3562,16 @@
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
-    </row>
-    <row r="40" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC39" s="1"/>
+    </row>
+    <row r="40" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A40" s="3">
         <v>37</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="1"/>
+      <c r="C40" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
@@ -3453,15 +3597,16 @@
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
-    </row>
-    <row r="41" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC40" s="1"/>
+    </row>
+    <row r="41" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A41" s="3">
         <v>38</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="1"/>
+      <c r="C41" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
@@ -3487,15 +3632,16 @@
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
-    </row>
-    <row r="42" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC41" s="1"/>
+    </row>
+    <row r="42" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A42" s="3">
         <v>39</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="1"/>
+      <c r="C42" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
@@ -3521,15 +3667,16 @@
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
-    </row>
-    <row r="43" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC42" s="1"/>
+    </row>
+    <row r="43" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A43" s="3">
         <v>40</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="1"/>
+      <c r="C43" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -3555,15 +3702,16 @@
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
-    </row>
-    <row r="44" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC43" s="1"/>
+    </row>
+    <row r="44" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A44" s="3">
         <v>41</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="1"/>
+      <c r="C44" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -3589,15 +3737,16 @@
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
-    </row>
-    <row r="45" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC44" s="1"/>
+    </row>
+    <row r="45" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A45" s="3">
         <v>42</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="1"/>
+      <c r="C45" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -3623,15 +3772,16 @@
       <c r="Z45" s="1"/>
       <c r="AA45" s="1"/>
       <c r="AB45" s="1"/>
-    </row>
-    <row r="46" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC45" s="1"/>
+    </row>
+    <row r="46" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A46" s="3">
         <v>43</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="1"/>
+      <c r="C46" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -3657,15 +3807,16 @@
       <c r="Z46" s="1"/>
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
-    </row>
-    <row r="47" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC46" s="1"/>
+    </row>
+    <row r="47" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A47" s="3">
         <v>44</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="1"/>
+      <c r="C47" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -3691,15 +3842,16 @@
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
-    </row>
-    <row r="48" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC47" s="1"/>
+    </row>
+    <row r="48" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A48" s="3">
         <v>45</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="1"/>
+      <c r="C48" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -3725,15 +3877,16 @@
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
-    </row>
-    <row r="49" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC48" s="1"/>
+    </row>
+    <row r="49" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A49" s="3">
         <v>46</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="1"/>
+      <c r="C49" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -3759,15 +3912,16 @@
       <c r="Z49" s="1"/>
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
-    </row>
-    <row r="50" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC49" s="1"/>
+    </row>
+    <row r="50" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A50" s="3">
         <v>47</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="1"/>
+      <c r="C50" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -3793,15 +3947,16 @@
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
-    </row>
-    <row r="51" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC50" s="1"/>
+    </row>
+    <row r="51" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A51" s="3">
         <v>48</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="1"/>
+      <c r="C51" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -3827,15 +3982,16 @@
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
-    </row>
-    <row r="52" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC51" s="1"/>
+    </row>
+    <row r="52" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A52" s="3">
         <v>49</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="1"/>
+      <c r="C52" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -3861,15 +4017,16 @@
       <c r="Z52" s="1"/>
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
-    </row>
-    <row r="53" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC52" s="1"/>
+    </row>
+    <row r="53" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A53" s="3">
         <v>50</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="1"/>
+      <c r="C53" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -3895,15 +4052,16 @@
       <c r="Z53" s="1"/>
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
-    </row>
-    <row r="54" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC53" s="1"/>
+    </row>
+    <row r="54" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A54" s="3">
         <v>51</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="1"/>
+      <c r="C54" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
@@ -3929,15 +4087,16 @@
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
-    </row>
-    <row r="55" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC54" s="1"/>
+    </row>
+    <row r="55" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A55" s="3">
         <v>52</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="1"/>
+      <c r="C55" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
@@ -3963,15 +4122,16 @@
       <c r="Z55" s="1"/>
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
-    </row>
-    <row r="56" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC55" s="1"/>
+    </row>
+    <row r="56" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A56" s="3">
         <v>53</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="1"/>
+      <c r="C56" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
@@ -3997,15 +4157,16 @@
       <c r="Z56" s="1"/>
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
-    </row>
-    <row r="57" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC56" s="1"/>
+    </row>
+    <row r="57" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A57" s="3">
         <v>54</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="1"/>
+      <c r="C57" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
@@ -4031,15 +4192,16 @@
       <c r="Z57" s="1"/>
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
-    </row>
-    <row r="58" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC57" s="1"/>
+    </row>
+    <row r="58" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A58" s="3">
         <v>55</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="1"/>
+      <c r="C58" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
@@ -4065,15 +4227,16 @@
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
-    </row>
-    <row r="59" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC58" s="1"/>
+    </row>
+    <row r="59" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A59" s="3">
         <v>56</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="1"/>
+      <c r="C59" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
@@ -4099,15 +4262,16 @@
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
-    </row>
-    <row r="60" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC59" s="1"/>
+    </row>
+    <row r="60" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A60" s="3">
         <v>57</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="1"/>
+      <c r="C60" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
@@ -4133,15 +4297,16 @@
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
-    </row>
-    <row r="61" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC60" s="1"/>
+    </row>
+    <row r="61" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A61" s="3">
         <v>58</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="1"/>
+      <c r="C61" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
@@ -4167,15 +4332,16 @@
       <c r="Z61" s="1"/>
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
-    </row>
-    <row r="62" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC61" s="1"/>
+    </row>
+    <row r="62" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A62" s="3">
         <v>59</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="1"/>
+      <c r="C62" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
@@ -4201,20 +4367,21 @@
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
-    </row>
-    <row r="63" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC62" s="1"/>
+    </row>
+    <row r="63" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A63" s="3">
         <v>60</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="1"/>
+      <c r="C63" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C63" s="1"/>
       <c r="D63" s="1"/>
-      <c r="E63" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -4237,15 +4404,16 @@
       <c r="Z63" s="1"/>
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
-    </row>
-    <row r="64" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC63" s="1"/>
+    </row>
+    <row r="64" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A64" s="3">
         <v>61</v>
       </c>
-      <c r="B64" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="4" t="s">
+        <v>219</v>
+      </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
@@ -4258,10 +4426,10 @@
       <c r="M64" s="1"/>
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
-      <c r="P64" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q64" s="1"/>
+      <c r="P64" s="1"/>
+      <c r="Q64" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
       <c r="T64" s="1"/>
@@ -4273,15 +4441,16 @@
       <c r="Z64" s="1"/>
       <c r="AA64" s="1"/>
       <c r="AB64" s="1"/>
-    </row>
-    <row r="65" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC64" s="1"/>
+    </row>
+    <row r="65" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A65" s="3">
         <v>62</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="1"/>
+      <c r="C65" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
@@ -4307,15 +4476,16 @@
       <c r="Z65" s="1"/>
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
-    </row>
-    <row r="66" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC65" s="1"/>
+    </row>
+    <row r="66" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A66" s="3">
         <v>63</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="1"/>
+      <c r="C66" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
@@ -4341,20 +4511,21 @@
       <c r="Z66" s="1"/>
       <c r="AA66" s="1"/>
       <c r="AB66" s="1"/>
-    </row>
-    <row r="67" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC66" s="1"/>
+    </row>
+    <row r="67" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A67" s="3">
         <v>64</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="1"/>
+      <c r="C67" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C67" s="1"/>
       <c r="D67" s="1"/>
-      <c r="E67" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -4377,20 +4548,21 @@
       <c r="Z67" s="1"/>
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
-    </row>
-    <row r="68" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC67" s="1"/>
+    </row>
+    <row r="68" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A68" s="3">
         <v>65</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="1"/>
+      <c r="C68" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C68" s="1"/>
       <c r="D68" s="1"/>
-      <c r="E68" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -4413,15 +4585,16 @@
       <c r="Z68" s="1"/>
       <c r="AA68" s="1"/>
       <c r="AB68" s="1"/>
-    </row>
-    <row r="69" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC68" s="1"/>
+    </row>
+    <row r="69" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A69" s="3">
         <v>66</v>
       </c>
-      <c r="B69" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="C69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="4" t="s">
+        <v>220</v>
+      </c>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
@@ -4434,10 +4607,10 @@
       <c r="M69" s="1"/>
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
-      <c r="P69" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q69" s="1"/>
+      <c r="P69" s="1"/>
+      <c r="Q69" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
       <c r="T69" s="1"/>
@@ -4449,20 +4622,21 @@
       <c r="Z69" s="1"/>
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
-    </row>
-    <row r="70" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC69" s="1"/>
+    </row>
+    <row r="70" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A70" s="3">
         <v>67</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="1"/>
+      <c r="C70" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C70" s="1"/>
       <c r="D70" s="1"/>
-      <c r="E70" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -4485,20 +4659,21 @@
       <c r="Z70" s="1"/>
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
-    </row>
-    <row r="71" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC70" s="1"/>
+    </row>
+    <row r="71" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A71" s="3">
         <v>68</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="1"/>
+      <c r="C71" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C71" s="1"/>
       <c r="D71" s="1"/>
-      <c r="E71" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -4521,15 +4696,16 @@
       <c r="Z71" s="1"/>
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
-    </row>
-    <row r="72" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC71" s="1"/>
+    </row>
+    <row r="72" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A72" s="3">
         <v>69</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="1"/>
+      <c r="C72" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
@@ -4555,15 +4731,16 @@
       <c r="Z72" s="1"/>
       <c r="AA72" s="1"/>
       <c r="AB72" s="1"/>
-    </row>
-    <row r="73" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC72" s="1"/>
+    </row>
+    <row r="73" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A73" s="3">
         <v>70</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="1"/>
+      <c r="C73" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -4589,15 +4766,16 @@
       <c r="Z73" s="1"/>
       <c r="AA73" s="1"/>
       <c r="AB73" s="1"/>
-    </row>
-    <row r="74" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC73" s="1"/>
+    </row>
+    <row r="74" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A74" s="3">
         <v>71</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="1"/>
+      <c r="C74" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
@@ -4623,15 +4801,16 @@
       <c r="Z74" s="1"/>
       <c r="AA74" s="1"/>
       <c r="AB74" s="1"/>
-    </row>
-    <row r="75" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC74" s="1"/>
+    </row>
+    <row r="75" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A75" s="3">
         <v>72</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="1"/>
+      <c r="C75" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
@@ -4657,20 +4836,21 @@
       <c r="Z75" s="1"/>
       <c r="AA75" s="1"/>
       <c r="AB75" s="1"/>
-    </row>
-    <row r="76" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC75" s="1"/>
+    </row>
+    <row r="76" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A76" s="3">
         <v>73</v>
       </c>
-      <c r="B76" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="D76" s="1"/>
-      <c r="E76" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -4682,10 +4862,10 @@
       <c r="O76" s="1"/>
       <c r="P76" s="1"/>
       <c r="Q76" s="1"/>
-      <c r="R76" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="S76" s="1"/>
+      <c r="R76" s="1"/>
+      <c r="S76" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
       <c r="V76" s="1"/>
@@ -4695,15 +4875,16 @@
       <c r="Z76" s="1"/>
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
-    </row>
-    <row r="77" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC76" s="1"/>
+    </row>
+    <row r="77" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A77" s="3">
         <v>74</v>
       </c>
-      <c r="B77" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="4" t="s">
+        <v>141</v>
+      </c>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -4718,10 +4899,10 @@
       <c r="O77" s="1"/>
       <c r="P77" s="1"/>
       <c r="Q77" s="1"/>
-      <c r="R77" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="S77" s="1"/>
+      <c r="R77" s="1"/>
+      <c r="S77" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T77" s="1"/>
       <c r="U77" s="1"/>
       <c r="V77" s="1"/>
@@ -4731,15 +4912,16 @@
       <c r="Z77" s="1"/>
       <c r="AA77" s="1"/>
       <c r="AB77" s="1"/>
-    </row>
-    <row r="78" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC77" s="1"/>
+    </row>
+    <row r="78" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A78" s="3">
         <v>75</v>
       </c>
-      <c r="B78" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="4" t="s">
+        <v>142</v>
+      </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
@@ -4754,10 +4936,10 @@
       <c r="O78" s="1"/>
       <c r="P78" s="1"/>
       <c r="Q78" s="1"/>
-      <c r="R78" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="S78" s="1"/>
+      <c r="R78" s="1"/>
+      <c r="S78" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
       <c r="V78" s="1"/>
@@ -4767,15 +4949,16 @@
       <c r="Z78" s="1"/>
       <c r="AA78" s="1"/>
       <c r="AB78" s="1"/>
-    </row>
-    <row r="79" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC78" s="1"/>
+    </row>
+    <row r="79" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A79" s="3">
         <v>76</v>
       </c>
-      <c r="B79" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
@@ -4790,10 +4973,10 @@
       <c r="O79" s="1"/>
       <c r="P79" s="1"/>
       <c r="Q79" s="1"/>
-      <c r="R79" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="S79" s="1"/>
+      <c r="R79" s="1"/>
+      <c r="S79" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T79" s="1"/>
       <c r="U79" s="1"/>
       <c r="V79" s="1"/>
@@ -4803,15 +4986,16 @@
       <c r="Z79" s="1"/>
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
-    </row>
-    <row r="80" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC79" s="1"/>
+    </row>
+    <row r="80" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A80" s="3">
         <v>77</v>
       </c>
-      <c r="B80" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
@@ -4826,10 +5010,10 @@
       <c r="O80" s="1"/>
       <c r="P80" s="1"/>
       <c r="Q80" s="1"/>
-      <c r="R80" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="S80" s="1"/>
+      <c r="R80" s="1"/>
+      <c r="S80" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T80" s="1"/>
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
@@ -4839,20 +5023,21 @@
       <c r="Z80" s="1"/>
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
-    </row>
-    <row r="81" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC80" s="1"/>
+    </row>
+    <row r="81" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A81" s="3">
         <v>78</v>
       </c>
-      <c r="B81" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="4" t="s">
+        <v>145</v>
+      </c>
       <c r="D81" s="1"/>
-      <c r="E81" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
@@ -4864,10 +5049,10 @@
       <c r="O81" s="1"/>
       <c r="P81" s="1"/>
       <c r="Q81" s="1"/>
-      <c r="R81" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="S81" s="1"/>
+      <c r="R81" s="1"/>
+      <c r="S81" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T81" s="1"/>
       <c r="U81" s="1"/>
       <c r="V81" s="1"/>
@@ -4877,15 +5062,16 @@
       <c r="Z81" s="1"/>
       <c r="AA81" s="1"/>
       <c r="AB81" s="1"/>
-    </row>
-    <row r="82" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC81" s="1"/>
+    </row>
+    <row r="82" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A82" s="3">
         <v>79</v>
       </c>
-      <c r="B82" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
@@ -4898,14 +5084,14 @@
       <c r="M82" s="1"/>
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
-      <c r="P82" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q82" s="1"/>
-      <c r="R82" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="S82" s="1"/>
+      <c r="P82" s="1"/>
+      <c r="Q82" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="R82" s="1"/>
+      <c r="S82" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T82" s="1"/>
       <c r="U82" s="1"/>
       <c r="V82" s="1"/>
@@ -4915,15 +5101,16 @@
       <c r="Z82" s="1"/>
       <c r="AA82" s="1"/>
       <c r="AB82" s="1"/>
-    </row>
-    <row r="83" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC82" s="1"/>
+    </row>
+    <row r="83" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A83" s="3">
         <v>80</v>
       </c>
-      <c r="B83" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
@@ -4938,13 +5125,13 @@
       <c r="O83" s="1"/>
       <c r="P83" s="1"/>
       <c r="Q83" s="1"/>
-      <c r="R83" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="R83" s="1"/>
       <c r="S83" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T83" s="1"/>
+        <v>158</v>
+      </c>
+      <c r="T83" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
       <c r="W83" s="1"/>
@@ -4953,15 +5140,16 @@
       <c r="Z83" s="1"/>
       <c r="AA83" s="1"/>
       <c r="AB83" s="1"/>
-    </row>
-    <row r="84" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC83" s="1"/>
+    </row>
+    <row r="84" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A84" s="3">
         <v>81</v>
       </c>
-      <c r="B84" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="4" t="s">
+        <v>148</v>
+      </c>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
@@ -4976,10 +5164,10 @@
       <c r="O84" s="1"/>
       <c r="P84" s="1"/>
       <c r="Q84" s="1"/>
-      <c r="R84" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="S84" s="1"/>
+      <c r="R84" s="1"/>
+      <c r="S84" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T84" s="1"/>
       <c r="U84" s="1"/>
       <c r="V84" s="1"/>
@@ -4989,15 +5177,16 @@
       <c r="Z84" s="1"/>
       <c r="AA84" s="1"/>
       <c r="AB84" s="1"/>
-    </row>
-    <row r="85" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC84" s="1"/>
+    </row>
+    <row r="85" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A85" s="3">
         <v>82</v>
       </c>
-      <c r="B85" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="4" t="s">
+        <v>149</v>
+      </c>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
@@ -5023,15 +5212,16 @@
       <c r="Z85" s="1"/>
       <c r="AA85" s="1"/>
       <c r="AB85" s="1"/>
-    </row>
-    <row r="86" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC85" s="1"/>
+    </row>
+    <row r="86" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A86" s="3">
         <v>83</v>
       </c>
-      <c r="B86" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="4" t="s">
+        <v>150</v>
+      </c>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
@@ -5057,15 +5247,16 @@
       <c r="Z86" s="1"/>
       <c r="AA86" s="1"/>
       <c r="AB86" s="1"/>
-    </row>
-    <row r="87" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC86" s="1"/>
+    </row>
+    <row r="87" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A87" s="3">
         <v>84</v>
       </c>
-      <c r="B87" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="4" t="s">
+        <v>151</v>
+      </c>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
@@ -5091,15 +5282,16 @@
       <c r="Z87" s="1"/>
       <c r="AA87" s="1"/>
       <c r="AB87" s="1"/>
-    </row>
-    <row r="88" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC87" s="1"/>
+    </row>
+    <row r="88" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A88" s="3">
         <v>85</v>
       </c>
-      <c r="B88" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="4" t="s">
+        <v>152</v>
+      </c>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -5112,10 +5304,10 @@
       <c r="M88" s="1"/>
       <c r="N88" s="1"/>
       <c r="O88" s="1"/>
-      <c r="P88" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q88" s="1"/>
+      <c r="P88" s="1"/>
+      <c r="Q88" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
       <c r="T88" s="1"/>
@@ -5127,15 +5319,16 @@
       <c r="Z88" s="1"/>
       <c r="AA88" s="1"/>
       <c r="AB88" s="1"/>
-    </row>
-    <row r="89" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC88" s="1"/>
+    </row>
+    <row r="89" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A89" s="3">
         <v>86</v>
       </c>
-      <c r="B89" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
@@ -5161,15 +5354,16 @@
       <c r="Z89" s="1"/>
       <c r="AA89" s="1"/>
       <c r="AB89" s="1"/>
-    </row>
-    <row r="90" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC89" s="1"/>
+    </row>
+    <row r="90" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A90" s="3">
         <v>87</v>
       </c>
-      <c r="B90" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C90" s="1"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="4" t="s">
+        <v>154</v>
+      </c>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
@@ -5195,15 +5389,16 @@
       <c r="Z90" s="1"/>
       <c r="AA90" s="1"/>
       <c r="AB90" s="1"/>
-    </row>
-    <row r="91" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC90" s="1"/>
+    </row>
+    <row r="91" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A91" s="3">
         <v>88</v>
       </c>
-      <c r="B91" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C91" s="1"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="4" t="s">
+        <v>155</v>
+      </c>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
@@ -5216,10 +5411,10 @@
       <c r="M91" s="1"/>
       <c r="N91" s="1"/>
       <c r="O91" s="1"/>
-      <c r="P91" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q91" s="1"/>
+      <c r="P91" s="1"/>
+      <c r="Q91" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
       <c r="T91" s="1"/>
@@ -5231,20 +5426,21 @@
       <c r="Z91" s="1"/>
       <c r="AA91" s="1"/>
       <c r="AB91" s="1"/>
-    </row>
-    <row r="92" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC91" s="1"/>
+    </row>
+    <row r="92" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A92" s="3">
         <v>89</v>
       </c>
-      <c r="B92" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="4" t="s">
+        <v>156</v>
+      </c>
       <c r="D92" s="1"/>
-      <c r="E92" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -5267,15 +5463,16 @@
       <c r="Z92" s="1"/>
       <c r="AA92" s="1"/>
       <c r="AB92" s="1"/>
-    </row>
-    <row r="93" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC92" s="1"/>
+    </row>
+    <row r="93" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A93" s="3">
         <v>90</v>
       </c>
-      <c r="B93" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C93" s="1"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="4" t="s">
+        <v>157</v>
+      </c>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
@@ -5301,15 +5498,16 @@
       <c r="Z93" s="1"/>
       <c r="AA93" s="1"/>
       <c r="AB93" s="1"/>
-    </row>
-    <row r="94" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC93" s="1"/>
+    </row>
+    <row r="94" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A94" s="3">
         <v>91</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="1"/>
+      <c r="C94" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
@@ -5335,15 +5533,16 @@
       <c r="Z94" s="1"/>
       <c r="AA94" s="1"/>
       <c r="AB94" s="1"/>
-    </row>
-    <row r="95" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC94" s="1"/>
+    </row>
+    <row r="95" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A95" s="3">
         <v>92</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="1"/>
+      <c r="C95" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
@@ -5369,15 +5568,16 @@
       <c r="Z95" s="1"/>
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
-    </row>
-    <row r="96" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC95" s="1"/>
+    </row>
+    <row r="96" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A96" s="3">
         <v>93</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="1"/>
+      <c r="C96" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
@@ -5403,15 +5603,16 @@
       <c r="Z96" s="1"/>
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
-    </row>
-    <row r="97" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC96" s="1"/>
+    </row>
+    <row r="97" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A97" s="3">
         <v>94</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="1"/>
+      <c r="C97" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
@@ -5437,22 +5638,23 @@
       <c r="Z97" s="1"/>
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
-    </row>
-    <row r="98" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC97" s="1"/>
+    </row>
+    <row r="98" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A98" s="3">
         <v>95</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="1"/>
+      <c r="C98" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
-      <c r="G98" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
@@ -5473,15 +5675,16 @@
       <c r="Z98" s="1"/>
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
-    </row>
-    <row r="99" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC98" s="1"/>
+    </row>
+    <row r="99" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A99" s="3">
         <v>96</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="1"/>
+      <c r="C99" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
@@ -5507,15 +5710,16 @@
       <c r="Z99" s="1"/>
       <c r="AA99" s="1"/>
       <c r="AB99" s="1"/>
-    </row>
-    <row r="100" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC99" s="1"/>
+    </row>
+    <row r="100" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A100" s="3">
         <v>97</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="1"/>
+      <c r="C100" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
@@ -5541,15 +5745,16 @@
       <c r="Z100" s="1"/>
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
-    </row>
-    <row r="101" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC100" s="1"/>
+    </row>
+    <row r="101" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A101" s="3">
         <v>98</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="1"/>
+      <c r="C101" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
@@ -5575,15 +5780,16 @@
       <c r="Z101" s="1"/>
       <c r="AA101" s="1"/>
       <c r="AB101" s="1"/>
-    </row>
-    <row r="102" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC101" s="1"/>
+    </row>
+    <row r="102" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A102" s="3">
         <v>99</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="1"/>
+      <c r="C102" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
@@ -5609,15 +5815,16 @@
       <c r="Z102" s="1"/>
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
-    </row>
-    <row r="103" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC102" s="1"/>
+    </row>
+    <row r="103" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A103" s="3">
         <v>100</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="1"/>
+      <c r="C103" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
@@ -5643,15 +5850,16 @@
       <c r="Z103" s="1"/>
       <c r="AA103" s="1"/>
       <c r="AB103" s="1"/>
-    </row>
-    <row r="104" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC103" s="1"/>
+    </row>
+    <row r="104" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A104" s="3">
         <v>101</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B104" s="1"/>
+      <c r="C104" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
@@ -5677,15 +5885,16 @@
       <c r="Z104" s="1"/>
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
-    </row>
-    <row r="105" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC104" s="1"/>
+    </row>
+    <row r="105" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A105" s="3">
         <v>102</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="1"/>
+      <c r="C105" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C105" s="1"/>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
@@ -5711,15 +5920,16 @@
       <c r="Z105" s="1"/>
       <c r="AA105" s="1"/>
       <c r="AB105" s="1"/>
-    </row>
-    <row r="106" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC105" s="1"/>
+    </row>
+    <row r="106" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A106" s="3">
         <v>103</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="1"/>
+      <c r="C106" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
@@ -5745,15 +5955,16 @@
       <c r="Z106" s="1"/>
       <c r="AA106" s="1"/>
       <c r="AB106" s="1"/>
-    </row>
-    <row r="107" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC106" s="1"/>
+    </row>
+    <row r="107" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A107" s="3">
         <v>104</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="1"/>
+      <c r="C107" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C107" s="1"/>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
@@ -5779,15 +5990,16 @@
       <c r="Z107" s="1"/>
       <c r="AA107" s="1"/>
       <c r="AB107" s="1"/>
-    </row>
-    <row r="108" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC107" s="1"/>
+    </row>
+    <row r="108" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A108" s="3">
         <v>105</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="1"/>
+      <c r="C108" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C108" s="1"/>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
@@ -5813,15 +6025,16 @@
       <c r="Z108" s="1"/>
       <c r="AA108" s="1"/>
       <c r="AB108" s="1"/>
-    </row>
-    <row r="109" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC108" s="1"/>
+    </row>
+    <row r="109" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A109" s="3">
         <v>106</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B109" s="1"/>
+      <c r="C109" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C109" s="1"/>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
@@ -5847,15 +6060,16 @@
       <c r="Z109" s="1"/>
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
-    </row>
-    <row r="110" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC109" s="1"/>
+    </row>
+    <row r="110" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A110" s="3">
         <v>107</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" s="1"/>
+      <c r="C110" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C110" s="1"/>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
@@ -5881,15 +6095,16 @@
       <c r="Z110" s="1"/>
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
-    </row>
-    <row r="111" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC110" s="1"/>
+    </row>
+    <row r="111" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A111" s="3">
         <v>108</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B111" s="1"/>
+      <c r="C111" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C111" s="1"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
@@ -5915,20 +6130,21 @@
       <c r="Z111" s="1"/>
       <c r="AA111" s="1"/>
       <c r="AB111" s="1"/>
-    </row>
-    <row r="112" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC111" s="1"/>
+    </row>
+    <row r="112" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A112" s="3">
         <v>109</v>
       </c>
-      <c r="B112" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="C112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="4" t="s">
+        <v>221</v>
+      </c>
       <c r="D112" s="1"/>
-      <c r="E112" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F112" s="1"/>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="G112" s="1"/>
       <c r="H112" s="1"/>
       <c r="I112" s="1"/>
@@ -5938,10 +6154,10 @@
       <c r="M112" s="1"/>
       <c r="N112" s="1"/>
       <c r="O112" s="1"/>
-      <c r="P112" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q112" s="1"/>
+      <c r="P112" s="1"/>
+      <c r="Q112" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="R112" s="1"/>
       <c r="S112" s="1"/>
       <c r="T112" s="1"/>
@@ -5953,15 +6169,16 @@
       <c r="Z112" s="1"/>
       <c r="AA112" s="1"/>
       <c r="AB112" s="1"/>
-    </row>
-    <row r="113" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC112" s="1"/>
+    </row>
+    <row r="113" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A113" s="3">
         <v>110</v>
       </c>
-      <c r="B113" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="C113" s="1"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="4" t="s">
+        <v>222</v>
+      </c>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
@@ -5974,10 +6191,10 @@
       <c r="M113" s="1"/>
       <c r="N113" s="1"/>
       <c r="O113" s="1"/>
-      <c r="P113" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q113" s="1"/>
+      <c r="P113" s="1"/>
+      <c r="Q113" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="R113" s="1"/>
       <c r="S113" s="1"/>
       <c r="T113" s="1"/>
@@ -5989,15 +6206,16 @@
       <c r="Z113" s="1"/>
       <c r="AA113" s="1"/>
       <c r="AB113" s="1"/>
-    </row>
-    <row r="114" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC113" s="1"/>
+    </row>
+    <row r="114" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A114" s="3">
         <v>111</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B114" s="1"/>
+      <c r="C114" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C114" s="1"/>
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
@@ -6023,20 +6241,21 @@
       <c r="Z114" s="1"/>
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
-    </row>
-    <row r="115" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC114" s="1"/>
+    </row>
+    <row r="115" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A115" s="3">
         <v>112</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B115" s="1"/>
+      <c r="C115" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C115" s="1"/>
       <c r="D115" s="1"/>
-      <c r="E115" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F115" s="1"/>
+      <c r="E115" s="1"/>
+      <c r="F115" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="G115" s="1"/>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
@@ -6059,15 +6278,16 @@
       <c r="Z115" s="1"/>
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
-    </row>
-    <row r="116" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC115" s="1"/>
+    </row>
+    <row r="116" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A116" s="3">
         <v>113</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="1"/>
+      <c r="C116" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C116" s="1"/>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
@@ -6093,15 +6313,16 @@
       <c r="Z116" s="1"/>
       <c r="AA116" s="1"/>
       <c r="AB116" s="1"/>
-    </row>
-    <row r="117" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC116" s="1"/>
+    </row>
+    <row r="117" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A117" s="3">
         <v>114</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B117" s="1"/>
+      <c r="C117" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C117" s="1"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
@@ -6127,15 +6348,16 @@
       <c r="Z117" s="1"/>
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
-    </row>
-    <row r="118" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC117" s="1"/>
+    </row>
+    <row r="118" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A118" s="3">
         <v>115</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B118" s="1"/>
+      <c r="C118" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C118" s="1"/>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
@@ -6161,15 +6383,16 @@
       <c r="Z118" s="1"/>
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
-    </row>
-    <row r="119" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC118" s="1"/>
+    </row>
+    <row r="119" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A119" s="3">
         <v>116</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="B119" s="1"/>
+      <c r="C119" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C119" s="1"/>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
@@ -6195,15 +6418,16 @@
       <c r="Z119" s="1"/>
       <c r="AA119" s="1"/>
       <c r="AB119" s="1"/>
-    </row>
-    <row r="120" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC119" s="1"/>
+    </row>
+    <row r="120" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A120" s="3">
         <v>117</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="B120" s="1"/>
+      <c r="C120" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C120" s="1"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
@@ -6229,15 +6453,16 @@
       <c r="Z120" s="1"/>
       <c r="AA120" s="1"/>
       <c r="AB120" s="1"/>
-    </row>
-    <row r="121" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC120" s="1"/>
+    </row>
+    <row r="121" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A121" s="3">
         <v>118</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B121" s="1"/>
+      <c r="C121" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C121" s="1"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
@@ -6263,15 +6488,16 @@
       <c r="Z121" s="1"/>
       <c r="AA121" s="1"/>
       <c r="AB121" s="1"/>
-    </row>
-    <row r="122" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC121" s="1"/>
+    </row>
+    <row r="122" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A122" s="3">
         <v>119</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" s="1"/>
+      <c r="C122" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C122" s="1"/>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
@@ -6297,15 +6523,16 @@
       <c r="Z122" s="1"/>
       <c r="AA122" s="1"/>
       <c r="AB122" s="1"/>
-    </row>
-    <row r="123" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC122" s="1"/>
+    </row>
+    <row r="123" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A123" s="3">
         <v>120</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="B123" s="1"/>
+      <c r="C123" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C123" s="1"/>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
@@ -6331,15 +6558,16 @@
       <c r="Z123" s="1"/>
       <c r="AA123" s="1"/>
       <c r="AB123" s="1"/>
-    </row>
-    <row r="124" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC123" s="1"/>
+    </row>
+    <row r="124" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A124" s="3">
         <v>121</v>
       </c>
-      <c r="B124" s="4" t="s">
+      <c r="B124" s="1"/>
+      <c r="C124" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C124" s="1"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
@@ -6365,15 +6593,16 @@
       <c r="Z124" s="1"/>
       <c r="AA124" s="1"/>
       <c r="AB124" s="1"/>
-    </row>
-    <row r="125" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC124" s="1"/>
+    </row>
+    <row r="125" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A125" s="3">
         <v>122</v>
       </c>
-      <c r="B125" s="4" t="s">
+      <c r="B125" s="1"/>
+      <c r="C125" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C125" s="1"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
@@ -6399,15 +6628,16 @@
       <c r="Z125" s="1"/>
       <c r="AA125" s="1"/>
       <c r="AB125" s="1"/>
-    </row>
-    <row r="126" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC125" s="1"/>
+    </row>
+    <row r="126" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A126" s="3">
         <v>123</v>
       </c>
-      <c r="B126" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C126" s="1"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="4" t="s">
+        <v>223</v>
+      </c>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
@@ -6420,10 +6650,10 @@
       <c r="M126" s="1"/>
       <c r="N126" s="1"/>
       <c r="O126" s="1"/>
-      <c r="P126" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q126" s="1"/>
+      <c r="P126" s="1"/>
+      <c r="Q126" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="R126" s="1"/>
       <c r="S126" s="1"/>
       <c r="T126" s="1"/>
@@ -6435,15 +6665,16 @@
       <c r="Z126" s="1"/>
       <c r="AA126" s="1"/>
       <c r="AB126" s="1"/>
-    </row>
-    <row r="127" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC126" s="1"/>
+    </row>
+    <row r="127" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A127" s="3">
         <v>124</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="B127" s="1"/>
+      <c r="C127" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
@@ -6469,15 +6700,16 @@
       <c r="Z127" s="1"/>
       <c r="AA127" s="1"/>
       <c r="AB127" s="1"/>
-    </row>
-    <row r="128" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC127" s="1"/>
+    </row>
+    <row r="128" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A128" s="3">
         <v>125</v>
       </c>
-      <c r="B128" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C128" s="1"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="4" t="s">
+        <v>224</v>
+      </c>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
@@ -6490,10 +6722,10 @@
       <c r="M128" s="1"/>
       <c r="N128" s="1"/>
       <c r="O128" s="1"/>
-      <c r="P128" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q128" s="1"/>
+      <c r="P128" s="1"/>
+      <c r="Q128" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="R128" s="1"/>
       <c r="S128" s="1"/>
       <c r="T128" s="1"/>
@@ -6505,15 +6737,16 @@
       <c r="Z128" s="1"/>
       <c r="AA128" s="1"/>
       <c r="AB128" s="1"/>
-    </row>
-    <row r="129" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC128" s="1"/>
+    </row>
+    <row r="129" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A129" s="3">
         <v>126</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="B129" s="1"/>
+      <c r="C129" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C129" s="1"/>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -6529,7 +6762,9 @@
       <c r="P129" s="1"/>
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
-      <c r="S129" s="1"/>
+      <c r="S129" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T129" s="1"/>
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
@@ -6539,15 +6774,16 @@
       <c r="Z129" s="1"/>
       <c r="AA129" s="1"/>
       <c r="AB129" s="1"/>
-    </row>
-    <row r="130" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC129" s="1"/>
+    </row>
+    <row r="130" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A130" s="3">
         <v>127</v>
       </c>
-      <c r="B130" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="C130" s="1"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="4" t="s">
+        <v>225</v>
+      </c>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
@@ -6560,10 +6796,10 @@
       <c r="M130" s="1"/>
       <c r="N130" s="1"/>
       <c r="O130" s="1"/>
-      <c r="P130" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q130" s="1"/>
+      <c r="P130" s="1"/>
+      <c r="Q130" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
       <c r="T130" s="1"/>
@@ -6575,15 +6811,16 @@
       <c r="Z130" s="1"/>
       <c r="AA130" s="1"/>
       <c r="AB130" s="1"/>
-    </row>
-    <row r="131" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC130" s="1"/>
+    </row>
+    <row r="131" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A131" s="3">
         <v>128</v>
       </c>
-      <c r="B131" s="4" t="s">
+      <c r="B131" s="1"/>
+      <c r="C131" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C131" s="1"/>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
@@ -6609,15 +6846,16 @@
       <c r="Z131" s="1"/>
       <c r="AA131" s="1"/>
       <c r="AB131" s="1"/>
-    </row>
-    <row r="132" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC131" s="1"/>
+    </row>
+    <row r="132" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A132" s="3">
         <v>129</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="B132" s="1"/>
+      <c r="C132" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C132" s="1"/>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
@@ -6643,15 +6881,16 @@
       <c r="Z132" s="1"/>
       <c r="AA132" s="1"/>
       <c r="AB132" s="1"/>
-    </row>
-    <row r="133" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC132" s="1"/>
+    </row>
+    <row r="133" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A133" s="3">
         <v>130</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="B133" s="1"/>
+      <c r="C133" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C133" s="1"/>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
@@ -6677,15 +6916,16 @@
       <c r="Z133" s="1"/>
       <c r="AA133" s="1"/>
       <c r="AB133" s="1"/>
-    </row>
-    <row r="134" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC133" s="1"/>
+    </row>
+    <row r="134" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A134" s="3">
         <v>131</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B134" s="1"/>
+      <c r="C134" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C134" s="1"/>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
@@ -6711,15 +6951,16 @@
       <c r="Z134" s="1"/>
       <c r="AA134" s="1"/>
       <c r="AB134" s="1"/>
-    </row>
-    <row r="135" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC134" s="1"/>
+    </row>
+    <row r="135" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A135" s="3">
         <v>132</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="B135" s="1"/>
+      <c r="C135" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C135" s="1"/>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
@@ -6745,15 +6986,16 @@
       <c r="Z135" s="1"/>
       <c r="AA135" s="1"/>
       <c r="AB135" s="1"/>
-    </row>
-    <row r="136" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC135" s="1"/>
+    </row>
+    <row r="136" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A136" s="3">
         <v>133</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="B136" s="1"/>
+      <c r="C136" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
@@ -6779,15 +7021,16 @@
       <c r="Z136" s="1"/>
       <c r="AA136" s="1"/>
       <c r="AB136" s="1"/>
-    </row>
-    <row r="137" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC136" s="1"/>
+    </row>
+    <row r="137" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A137" s="3">
         <v>134</v>
       </c>
-      <c r="B137" s="4" t="s">
+      <c r="B137" s="1"/>
+      <c r="C137" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C137" s="1"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
@@ -6813,15 +7056,16 @@
       <c r="Z137" s="1"/>
       <c r="AA137" s="1"/>
       <c r="AB137" s="1"/>
-    </row>
-    <row r="138" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC137" s="1"/>
+    </row>
+    <row r="138" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A138" s="3">
         <v>135</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="B138" s="1"/>
+      <c r="C138" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C138" s="1"/>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
@@ -6847,15 +7091,16 @@
       <c r="Z138" s="1"/>
       <c r="AA138" s="1"/>
       <c r="AB138" s="1"/>
-    </row>
-    <row r="139" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC138" s="1"/>
+    </row>
+    <row r="139" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A139" s="3">
         <v>136</v>
       </c>
-      <c r="B139" s="4" t="s">
+      <c r="B139" s="1"/>
+      <c r="C139" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
@@ -6881,15 +7126,16 @@
       <c r="Z139" s="1"/>
       <c r="AA139" s="1"/>
       <c r="AB139" s="1"/>
-    </row>
-    <row r="140" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC139" s="1"/>
+    </row>
+    <row r="140" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A140" s="3">
         <v>137</v>
       </c>
-      <c r="B140" s="4" t="s">
+      <c r="B140" s="1"/>
+      <c r="C140" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C140" s="1"/>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
@@ -6915,15 +7161,16 @@
       <c r="Z140" s="1"/>
       <c r="AA140" s="1"/>
       <c r="AB140" s="1"/>
-    </row>
-    <row r="141" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC140" s="1"/>
+    </row>
+    <row r="141" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A141" s="3">
         <v>138</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="B141" s="1"/>
+      <c r="C141" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C141" s="1"/>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
@@ -6949,15 +7196,16 @@
       <c r="Z141" s="1"/>
       <c r="AA141" s="1"/>
       <c r="AB141" s="1"/>
-    </row>
-    <row r="142" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC141" s="1"/>
+    </row>
+    <row r="142" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A142" s="3">
         <v>139</v>
       </c>
-      <c r="B142" s="4" t="s">
+      <c r="B142" s="1"/>
+      <c r="C142" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C142" s="1"/>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
@@ -6983,15 +7231,16 @@
       <c r="Z142" s="1"/>
       <c r="AA142" s="1"/>
       <c r="AB142" s="1"/>
-    </row>
-    <row r="143" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC142" s="1"/>
+    </row>
+    <row r="143" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A143" s="3">
         <v>140</v>
       </c>
-      <c r="B143" s="4" t="s">
+      <c r="B143" s="1"/>
+      <c r="C143" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C143" s="1"/>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
@@ -7017,15 +7266,16 @@
       <c r="Z143" s="1"/>
       <c r="AA143" s="1"/>
       <c r="AB143" s="1"/>
-    </row>
-    <row r="144" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC143" s="1"/>
+    </row>
+    <row r="144" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A144" s="3">
         <v>141</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="B144" s="1"/>
+      <c r="C144" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
@@ -7051,15 +7301,16 @@
       <c r="Z144" s="1"/>
       <c r="AA144" s="1"/>
       <c r="AB144" s="1"/>
-    </row>
-    <row r="145" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC144" s="1"/>
+    </row>
+    <row r="145" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A145" s="3">
         <v>142</v>
       </c>
-      <c r="B145" s="4" t="s">
+      <c r="B145" s="1"/>
+      <c r="C145" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C145" s="1"/>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
@@ -7085,15 +7336,16 @@
       <c r="Z145" s="1"/>
       <c r="AA145" s="1"/>
       <c r="AB145" s="1"/>
-    </row>
-    <row r="146" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC145" s="1"/>
+    </row>
+    <row r="146" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A146" s="3">
         <v>143</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="B146" s="1"/>
+      <c r="C146" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C146" s="1"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
@@ -7119,15 +7371,16 @@
       <c r="Z146" s="1"/>
       <c r="AA146" s="1"/>
       <c r="AB146" s="1"/>
-    </row>
-    <row r="147" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC146" s="1"/>
+    </row>
+    <row r="147" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A147" s="3">
         <v>144</v>
       </c>
-      <c r="B147" s="4" t="s">
+      <c r="B147" s="1"/>
+      <c r="C147" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C147" s="1"/>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
@@ -7153,15 +7406,16 @@
       <c r="Z147" s="1"/>
       <c r="AA147" s="1"/>
       <c r="AB147" s="1"/>
-    </row>
-    <row r="148" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC147" s="1"/>
+    </row>
+    <row r="148" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A148" s="3">
         <v>145</v>
       </c>
-      <c r="B148" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="C148" s="1"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="4" t="s">
+        <v>226</v>
+      </c>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
@@ -7174,10 +7428,10 @@
       <c r="M148" s="1"/>
       <c r="N148" s="1"/>
       <c r="O148" s="1"/>
-      <c r="P148" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q148" s="1"/>
+      <c r="P148" s="1"/>
+      <c r="Q148" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
       <c r="T148" s="1"/>
@@ -7189,15 +7443,16 @@
       <c r="Z148" s="1"/>
       <c r="AA148" s="1"/>
       <c r="AB148" s="1"/>
-    </row>
-    <row r="149" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC148" s="1"/>
+    </row>
+    <row r="149" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A149" s="3">
         <v>146</v>
       </c>
-      <c r="B149" s="4" t="s">
+      <c r="B149" s="1"/>
+      <c r="C149" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C149" s="1"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
@@ -7223,15 +7478,16 @@
       <c r="Z149" s="1"/>
       <c r="AA149" s="1"/>
       <c r="AB149" s="1"/>
-    </row>
-    <row r="150" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC149" s="1"/>
+    </row>
+    <row r="150" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A150" s="3">
         <v>147</v>
       </c>
-      <c r="B150" s="4" t="s">
+      <c r="B150" s="1"/>
+      <c r="C150" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C150" s="1"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
@@ -7257,15 +7513,16 @@
       <c r="Z150" s="1"/>
       <c r="AA150" s="1"/>
       <c r="AB150" s="1"/>
-    </row>
-    <row r="151" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC150" s="1"/>
+    </row>
+    <row r="151" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A151" s="3">
         <v>148</v>
       </c>
-      <c r="B151" s="4" t="s">
+      <c r="B151" s="1"/>
+      <c r="C151" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C151" s="1"/>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
@@ -7291,15 +7548,16 @@
       <c r="Z151" s="1"/>
       <c r="AA151" s="1"/>
       <c r="AB151" s="1"/>
-    </row>
-    <row r="152" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC151" s="1"/>
+    </row>
+    <row r="152" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A152" s="3">
         <v>149</v>
       </c>
-      <c r="B152" s="4" t="s">
+      <c r="B152" s="1"/>
+      <c r="C152" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C152" s="1"/>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
@@ -7325,19 +7583,20 @@
       <c r="Z152" s="1"/>
       <c r="AA152" s="1"/>
       <c r="AB152" s="1"/>
-    </row>
-    <row r="153" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC152" s="1"/>
+    </row>
+    <row r="153" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A153" s="3">
         <v>150</v>
       </c>
-      <c r="B153" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C153" s="1"/>
-      <c r="D153" s="1" t="s">
+      <c r="B153" s="1"/>
+      <c r="C153" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E153" s="1"/>
+      <c r="D153" s="1"/>
+      <c r="E153" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="F153" s="1"/>
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
@@ -7361,19 +7620,20 @@
       <c r="Z153" s="1"/>
       <c r="AA153" s="1"/>
       <c r="AB153" s="1"/>
-    </row>
-    <row r="154" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC153" s="1"/>
+    </row>
+    <row r="154" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A154" s="3">
         <v>151</v>
       </c>
-      <c r="B154" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C154" s="1"/>
-      <c r="D154" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E154" s="1"/>
+      <c r="B154" s="1"/>
+      <c r="C154" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D154" s="1"/>
+      <c r="E154" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="F154" s="1"/>
       <c r="G154" s="1"/>
       <c r="H154" s="1"/>
@@ -7397,19 +7657,20 @@
       <c r="Z154" s="1"/>
       <c r="AA154" s="1"/>
       <c r="AB154" s="1"/>
-    </row>
-    <row r="155" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC154" s="1"/>
+    </row>
+    <row r="155" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A155" s="3">
         <v>152</v>
       </c>
-      <c r="B155" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C155" s="1"/>
-      <c r="D155" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E155" s="1"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D155" s="1"/>
+      <c r="E155" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
       <c r="H155" s="1"/>
@@ -7420,10 +7681,10 @@
       <c r="M155" s="1"/>
       <c r="N155" s="1"/>
       <c r="O155" s="1"/>
-      <c r="P155" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q155" s="1"/>
+      <c r="P155" s="1"/>
+      <c r="Q155" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="R155" s="1"/>
       <c r="S155" s="1"/>
       <c r="T155" s="1"/>
@@ -7435,19 +7696,20 @@
       <c r="Z155" s="1"/>
       <c r="AA155" s="1"/>
       <c r="AB155" s="1"/>
-    </row>
-    <row r="156" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC155" s="1"/>
+    </row>
+    <row r="156" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A156" s="3">
         <v>153</v>
       </c>
-      <c r="B156" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C156" s="1"/>
-      <c r="D156" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E156" s="1"/>
+      <c r="B156" s="1"/>
+      <c r="C156" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D156" s="1"/>
+      <c r="E156" s="9" t="s">
+        <v>158</v>
+      </c>
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
       <c r="H156" s="1"/>
@@ -7471,19 +7733,20 @@
       <c r="Z156" s="1"/>
       <c r="AA156" s="1"/>
       <c r="AB156" s="1"/>
-    </row>
-    <row r="157" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC156" s="1"/>
+    </row>
+    <row r="157" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A157" s="3">
         <v>154</v>
       </c>
-      <c r="B157" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C157" s="1"/>
-      <c r="D157" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E157" s="1"/>
+      <c r="B157" s="1"/>
+      <c r="C157" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D157" s="1"/>
+      <c r="E157" s="9" t="s">
+        <v>158</v>
+      </c>
       <c r="F157" s="1"/>
       <c r="G157" s="1"/>
       <c r="H157" s="1"/>
@@ -7507,22 +7770,23 @@
       <c r="Z157" s="1"/>
       <c r="AA157" s="1"/>
       <c r="AB157" s="1"/>
-    </row>
-    <row r="158" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC157" s="1"/>
+    </row>
+    <row r="158" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A158" s="3">
         <v>155</v>
       </c>
-      <c r="B158" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C158" s="1"/>
-      <c r="D158" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="B158" s="1"/>
+      <c r="C158" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D158" s="1"/>
       <c r="E158" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F158" s="1"/>
+        <v>158</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
       <c r="I158" s="1"/>
@@ -7545,19 +7809,20 @@
       <c r="Z158" s="1"/>
       <c r="AA158" s="1"/>
       <c r="AB158" s="1"/>
-    </row>
-    <row r="159" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC158" s="1"/>
+    </row>
+    <row r="159" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A159" s="3">
         <v>156</v>
       </c>
-      <c r="B159" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C159" s="1"/>
-      <c r="D159" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="E159" s="1"/>
+      <c r="B159" s="1"/>
+      <c r="C159" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D159" s="1"/>
+      <c r="E159" s="10" t="s">
+        <v>158</v>
+      </c>
       <c r="F159" s="1"/>
       <c r="G159" s="1"/>
       <c r="H159" s="1"/>
@@ -7581,19 +7846,20 @@
       <c r="Z159" s="1"/>
       <c r="AA159" s="1"/>
       <c r="AB159" s="1"/>
-    </row>
-    <row r="160" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC159" s="1"/>
+    </row>
+    <row r="160" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A160" s="3">
         <v>157</v>
       </c>
-      <c r="B160" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="C160" s="1"/>
-      <c r="D160" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E160" s="1"/>
+      <c r="B160" s="1"/>
+      <c r="C160" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D160" s="1"/>
+      <c r="E160" s="9" t="s">
+        <v>158</v>
+      </c>
       <c r="F160" s="1"/>
       <c r="G160" s="1"/>
       <c r="H160" s="1"/>
@@ -7607,7 +7873,9 @@
       <c r="P160" s="1"/>
       <c r="Q160" s="1"/>
       <c r="R160" s="1"/>
-      <c r="S160" s="1"/>
+      <c r="S160" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T160" s="1"/>
       <c r="U160" s="1"/>
       <c r="V160" s="1"/>
@@ -7617,19 +7885,20 @@
       <c r="Z160" s="1"/>
       <c r="AA160" s="1"/>
       <c r="AB160" s="1"/>
-    </row>
-    <row r="161" spans="1:28" ht="15" customHeight="1">
+      <c r="AC160" s="1"/>
+    </row>
+    <row r="161" spans="1:29" ht="15" customHeight="1">
       <c r="A161" s="3">
         <v>158</v>
       </c>
-      <c r="B161" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C161" s="1"/>
-      <c r="D161" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E161" s="1"/>
+      <c r="B161" s="1"/>
+      <c r="C161" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D161" s="1"/>
+      <c r="E161" s="9" t="s">
+        <v>158</v>
+      </c>
       <c r="F161" s="1"/>
       <c r="G161" s="1"/>
       <c r="H161" s="1"/>
@@ -7653,19 +7922,20 @@
       <c r="Z161" s="1"/>
       <c r="AA161" s="1"/>
       <c r="AB161" s="1"/>
-    </row>
-    <row r="162" spans="1:28" ht="15" customHeight="1">
+      <c r="AC161" s="1"/>
+    </row>
+    <row r="162" spans="1:29" ht="15" customHeight="1">
       <c r="A162" s="3">
         <v>159</v>
       </c>
-      <c r="B162" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C162" s="1"/>
-      <c r="D162" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="E162" s="1"/>
+      <c r="B162" s="1"/>
+      <c r="C162" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D162" s="1"/>
+      <c r="E162" s="10" t="s">
+        <v>158</v>
+      </c>
       <c r="F162" s="1"/>
       <c r="G162" s="1"/>
       <c r="H162" s="1"/>
@@ -7689,19 +7959,20 @@
       <c r="Z162" s="1"/>
       <c r="AA162" s="1"/>
       <c r="AB162" s="1"/>
-    </row>
-    <row r="163" spans="1:28" ht="15" customHeight="1">
+      <c r="AC162" s="1"/>
+    </row>
+    <row r="163" spans="1:29" ht="15" customHeight="1">
       <c r="A163" s="3">
         <v>160</v>
       </c>
-      <c r="B163" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C163" s="1"/>
-      <c r="D163" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E163" s="1"/>
+      <c r="B163" s="1"/>
+      <c r="C163" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D163" s="1"/>
+      <c r="E163" s="9" t="s">
+        <v>158</v>
+      </c>
       <c r="F163" s="1"/>
       <c r="G163" s="1"/>
       <c r="H163" s="1"/>
@@ -7711,10 +7982,10 @@
       <c r="L163" s="1"/>
       <c r="M163" s="1"/>
       <c r="N163" s="1"/>
-      <c r="O163" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="P163" s="1"/>
+      <c r="O163" s="1"/>
+      <c r="P163" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
       <c r="S163" s="1"/>
@@ -7727,17 +7998,18 @@
       <c r="Z163" s="1"/>
       <c r="AA163" s="1"/>
       <c r="AB163" s="1"/>
-    </row>
-    <row r="164" spans="1:28" ht="15" customHeight="1">
+      <c r="AC163" s="1"/>
+    </row>
+    <row r="164" spans="1:29" ht="15" customHeight="1">
       <c r="A164" s="3">
         <v>161</v>
       </c>
-      <c r="B164" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C164" s="3"/>
-      <c r="D164" s="8"/>
-      <c r="E164" s="3"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D164" s="3"/>
+      <c r="E164" s="8"/>
       <c r="F164" s="3"/>
       <c r="G164" s="3"/>
       <c r="H164" s="3"/>
@@ -7747,15 +8019,15 @@
       <c r="L164" s="3"/>
       <c r="M164" s="3"/>
       <c r="N164" s="3"/>
-      <c r="O164" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="P164" s="3"/>
+      <c r="O164" s="3"/>
+      <c r="P164" s="3" t="s">
+        <v>158</v>
+      </c>
       <c r="Q164" s="3"/>
-      <c r="R164" s="1"/>
+      <c r="R164" s="3"/>
       <c r="S164" s="1"/>
       <c r="T164" s="1"/>
-      <c r="U164" s="3"/>
+      <c r="U164" s="1"/>
       <c r="V164" s="3"/>
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
@@ -7763,17 +8035,18 @@
       <c r="Z164" s="3"/>
       <c r="AA164" s="3"/>
       <c r="AB164" s="3"/>
-    </row>
-    <row r="165" spans="1:28" ht="15" customHeight="1">
+      <c r="AC164" s="3"/>
+    </row>
+    <row r="165" spans="1:29" ht="15" customHeight="1">
       <c r="A165" s="3">
         <v>162</v>
       </c>
-      <c r="B165" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C165" s="3"/>
-      <c r="D165" s="8"/>
-      <c r="E165" s="3"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D165" s="3"/>
+      <c r="E165" s="8"/>
       <c r="F165" s="3"/>
       <c r="G165" s="3"/>
       <c r="H165" s="3"/>
@@ -7786,10 +8059,12 @@
       <c r="O165" s="3"/>
       <c r="P165" s="3"/>
       <c r="Q165" s="3"/>
-      <c r="R165" s="1"/>
-      <c r="S165" s="1"/>
+      <c r="R165" s="3"/>
+      <c r="S165" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T165" s="1"/>
-      <c r="U165" s="3"/>
+      <c r="U165" s="1"/>
       <c r="V165" s="3"/>
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
@@ -7797,17 +8072,18 @@
       <c r="Z165" s="3"/>
       <c r="AA165" s="3"/>
       <c r="AB165" s="3"/>
-    </row>
-    <row r="166" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC165" s="3"/>
+    </row>
+    <row r="166" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A166" s="3">
         <v>163</v>
       </c>
-      <c r="B166" s="4" t="s">
+      <c r="B166" s="1"/>
+      <c r="C166" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C166" s="1"/>
-      <c r="D166" s="8"/>
-      <c r="E166" s="1"/>
+      <c r="D166" s="1"/>
+      <c r="E166" s="8"/>
       <c r="F166" s="1"/>
       <c r="G166" s="1"/>
       <c r="H166" s="1"/>
@@ -7831,17 +8107,18 @@
       <c r="Z166" s="1"/>
       <c r="AA166" s="1"/>
       <c r="AB166" s="1"/>
-    </row>
-    <row r="167" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC166" s="1"/>
+    </row>
+    <row r="167" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A167" s="3">
         <v>164</v>
       </c>
-      <c r="B167" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C167" s="1"/>
-      <c r="D167" s="8"/>
-      <c r="E167" s="1"/>
+      <c r="B167" s="1"/>
+      <c r="C167" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D167" s="1"/>
+      <c r="E167" s="8"/>
       <c r="F167" s="1"/>
       <c r="G167" s="1"/>
       <c r="H167" s="1"/>
@@ -7865,17 +8142,18 @@
       <c r="Z167" s="1"/>
       <c r="AA167" s="1"/>
       <c r="AB167" s="1"/>
-    </row>
-    <row r="168" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC167" s="1"/>
+    </row>
+    <row r="168" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A168" s="3">
         <v>165</v>
       </c>
-      <c r="B168" s="4" t="s">
+      <c r="B168" s="1"/>
+      <c r="C168" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C168" s="1"/>
-      <c r="D168" s="8"/>
-      <c r="E168" s="1"/>
+      <c r="D168" s="1"/>
+      <c r="E168" s="8"/>
       <c r="F168" s="1"/>
       <c r="G168" s="1"/>
       <c r="H168" s="1"/>
@@ -7899,17 +8177,18 @@
       <c r="Z168" s="1"/>
       <c r="AA168" s="1"/>
       <c r="AB168" s="1"/>
-    </row>
-    <row r="169" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC168" s="1"/>
+    </row>
+    <row r="169" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A169" s="3">
         <v>166</v>
       </c>
-      <c r="B169" s="4" t="s">
+      <c r="B169" s="1"/>
+      <c r="C169" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C169" s="1"/>
-      <c r="D169" s="8"/>
-      <c r="E169" s="1"/>
+      <c r="D169" s="1"/>
+      <c r="E169" s="8"/>
       <c r="F169" s="1"/>
       <c r="G169" s="1"/>
       <c r="H169" s="1"/>
@@ -7933,17 +8212,18 @@
       <c r="Z169" s="1"/>
       <c r="AA169" s="1"/>
       <c r="AB169" s="1"/>
-    </row>
-    <row r="170" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC169" s="1"/>
+    </row>
+    <row r="170" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A170" s="3">
         <v>167</v>
       </c>
-      <c r="B170" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C170" s="1"/>
-      <c r="D170" s="8"/>
-      <c r="E170" s="1"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D170" s="1"/>
+      <c r="E170" s="8"/>
       <c r="F170" s="1"/>
       <c r="G170" s="1"/>
       <c r="H170" s="1"/>
@@ -7967,17 +8247,18 @@
       <c r="Z170" s="1"/>
       <c r="AA170" s="1"/>
       <c r="AB170" s="1"/>
-    </row>
-    <row r="171" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC170" s="1"/>
+    </row>
+    <row r="171" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A171" s="3">
         <v>168</v>
       </c>
-      <c r="B171" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C171" s="1"/>
-      <c r="D171" s="8"/>
-      <c r="E171" s="1"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D171" s="1"/>
+      <c r="E171" s="8"/>
       <c r="F171" s="1"/>
       <c r="G171" s="1"/>
       <c r="H171" s="1"/>
@@ -8001,17 +8282,18 @@
       <c r="Z171" s="1"/>
       <c r="AA171" s="1"/>
       <c r="AB171" s="1"/>
-    </row>
-    <row r="172" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC171" s="1"/>
+    </row>
+    <row r="172" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A172" s="3">
         <v>169</v>
       </c>
-      <c r="B172" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C172" s="1"/>
-      <c r="D172" s="8"/>
-      <c r="E172" s="1"/>
+      <c r="B172" s="1"/>
+      <c r="C172" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D172" s="1"/>
+      <c r="E172" s="8"/>
       <c r="F172" s="1"/>
       <c r="G172" s="1"/>
       <c r="H172" s="1"/>
@@ -8021,10 +8303,10 @@
       <c r="L172" s="1"/>
       <c r="M172" s="1"/>
       <c r="N172" s="1"/>
-      <c r="O172" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="P172" s="1"/>
+      <c r="O172" s="1"/>
+      <c r="P172" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
       <c r="S172" s="1"/>
@@ -8037,17 +8319,18 @@
       <c r="Z172" s="1"/>
       <c r="AA172" s="1"/>
       <c r="AB172" s="1"/>
-    </row>
-    <row r="173" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC172" s="1"/>
+    </row>
+    <row r="173" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A173" s="3">
         <v>170</v>
       </c>
-      <c r="B173" s="4" t="s">
+      <c r="B173" s="1"/>
+      <c r="C173" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C173" s="1"/>
-      <c r="D173" s="8"/>
-      <c r="E173" s="1"/>
+      <c r="D173" s="1"/>
+      <c r="E173" s="8"/>
       <c r="F173" s="1"/>
       <c r="G173" s="1"/>
       <c r="H173" s="1"/>
@@ -8071,20 +8354,23 @@
       <c r="Z173" s="1"/>
       <c r="AA173" s="1"/>
       <c r="AB173" s="1"/>
-    </row>
-    <row r="174" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC173" s="1"/>
+    </row>
+    <row r="174" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A174" s="3">
         <v>171</v>
       </c>
-      <c r="B174" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C174" s="1"/>
-      <c r="D174" s="8"/>
-      <c r="E174" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F174" s="1"/>
+      <c r="B174" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D174" s="1"/>
+      <c r="E174" s="8"/>
+      <c r="F174" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="G174" s="1"/>
       <c r="H174" s="1"/>
       <c r="I174" s="1"/>
@@ -8093,15 +8379,17 @@
       <c r="L174" s="1"/>
       <c r="M174" s="1"/>
       <c r="N174" s="1"/>
-      <c r="O174" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="O174" s="1"/>
       <c r="P174" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q174" s="1"/>
+        <v>158</v>
+      </c>
+      <c r="Q174" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="R174" s="1"/>
-      <c r="S174" s="1"/>
+      <c r="S174" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T174" s="1"/>
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
@@ -8111,20 +8399,23 @@
       <c r="Z174" s="1"/>
       <c r="AA174" s="1"/>
       <c r="AB174" s="1"/>
-    </row>
-    <row r="175" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC174" s="1"/>
+    </row>
+    <row r="175" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A175" s="3">
         <v>172</v>
       </c>
-      <c r="B175" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C175" s="1"/>
-      <c r="D175" s="8"/>
-      <c r="E175" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F175" s="1"/>
+      <c r="B175" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D175" s="1"/>
+      <c r="E175" s="8"/>
+      <c r="F175" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="G175" s="1"/>
       <c r="H175" s="1"/>
       <c r="I175" s="1"/>
@@ -8137,7 +8428,9 @@
       <c r="P175" s="1"/>
       <c r="Q175" s="1"/>
       <c r="R175" s="1"/>
-      <c r="S175" s="1"/>
+      <c r="S175" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T175" s="1"/>
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
@@ -8147,20 +8440,23 @@
       <c r="Z175" s="1"/>
       <c r="AA175" s="1"/>
       <c r="AB175" s="1"/>
-    </row>
-    <row r="176" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC175" s="1"/>
+    </row>
+    <row r="176" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A176" s="3">
         <v>173</v>
       </c>
-      <c r="B176" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="C176" s="1"/>
-      <c r="D176" s="8"/>
-      <c r="E176" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F176" s="1"/>
+      <c r="B176" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D176" s="1"/>
+      <c r="E176" s="8"/>
+      <c r="F176" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
@@ -8169,15 +8465,17 @@
       <c r="L176" s="1"/>
       <c r="M176" s="1"/>
       <c r="N176" s="1"/>
-      <c r="O176" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="O176" s="1"/>
       <c r="P176" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q176" s="1"/>
+        <v>158</v>
+      </c>
+      <c r="Q176" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="R176" s="1"/>
-      <c r="S176" s="1"/>
+      <c r="S176" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T176" s="1"/>
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
@@ -8187,17 +8485,20 @@
       <c r="Z176" s="1"/>
       <c r="AA176" s="1"/>
       <c r="AB176" s="1"/>
-    </row>
-    <row r="177" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC176" s="1"/>
+    </row>
+    <row r="177" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A177" s="3">
         <v>174</v>
       </c>
-      <c r="B177" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="C177" s="1"/>
-      <c r="D177" s="8"/>
-      <c r="E177" s="1"/>
+      <c r="B177" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D177" s="1"/>
+      <c r="E177" s="8"/>
       <c r="F177" s="1"/>
       <c r="G177" s="1"/>
       <c r="H177" s="1"/>
@@ -8211,7 +8512,9 @@
       <c r="P177" s="1"/>
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
-      <c r="S177" s="1"/>
+      <c r="S177" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T177" s="1"/>
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
@@ -8221,17 +8524,20 @@
       <c r="Z177" s="1"/>
       <c r="AA177" s="1"/>
       <c r="AB177" s="1"/>
-    </row>
-    <row r="178" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC177" s="1"/>
+    </row>
+    <row r="178" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A178" s="3">
         <v>175</v>
       </c>
-      <c r="B178" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C178" s="1"/>
-      <c r="D178" s="8"/>
-      <c r="E178" s="1"/>
+      <c r="B178" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D178" s="1"/>
+      <c r="E178" s="8"/>
       <c r="F178" s="1"/>
       <c r="G178" s="1"/>
       <c r="H178" s="1"/>
@@ -8245,7 +8551,9 @@
       <c r="P178" s="1"/>
       <c r="Q178" s="1"/>
       <c r="R178" s="1"/>
-      <c r="S178" s="1"/>
+      <c r="S178" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T178" s="1"/>
       <c r="U178" s="1"/>
       <c r="V178" s="1"/>
@@ -8255,17 +8563,20 @@
       <c r="Z178" s="1"/>
       <c r="AA178" s="1"/>
       <c r="AB178" s="1"/>
-    </row>
-    <row r="179" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC178" s="1"/>
+    </row>
+    <row r="179" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A179" s="3">
         <v>176</v>
       </c>
-      <c r="B179" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="C179" s="1"/>
-      <c r="D179" s="8"/>
-      <c r="E179" s="1"/>
+      <c r="B179" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D179" s="1"/>
+      <c r="E179" s="8"/>
       <c r="F179" s="1"/>
       <c r="G179" s="1"/>
       <c r="H179" s="1"/>
@@ -8279,7 +8590,9 @@
       <c r="P179" s="1"/>
       <c r="Q179" s="1"/>
       <c r="R179" s="1"/>
-      <c r="S179" s="1"/>
+      <c r="S179" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T179" s="1"/>
       <c r="U179" s="1"/>
       <c r="V179" s="1"/>
@@ -8289,17 +8602,20 @@
       <c r="Z179" s="1"/>
       <c r="AA179" s="1"/>
       <c r="AB179" s="1"/>
-    </row>
-    <row r="180" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC179" s="1"/>
+    </row>
+    <row r="180" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A180" s="3">
         <v>177</v>
       </c>
-      <c r="B180" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C180" s="1"/>
-      <c r="D180" s="8"/>
-      <c r="E180" s="1"/>
+      <c r="B180" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D180" s="1"/>
+      <c r="E180" s="8"/>
       <c r="F180" s="1"/>
       <c r="G180" s="1"/>
       <c r="H180" s="1"/>
@@ -8309,13 +8625,15 @@
       <c r="L180" s="1"/>
       <c r="M180" s="1"/>
       <c r="N180" s="1"/>
-      <c r="O180" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="P180" s="1"/>
+      <c r="O180" s="1"/>
+      <c r="P180" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="Q180" s="1"/>
       <c r="R180" s="1"/>
-      <c r="S180" s="1"/>
+      <c r="S180" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T180" s="1"/>
       <c r="U180" s="1"/>
       <c r="V180" s="1"/>
@@ -8325,15 +8643,18 @@
       <c r="Z180" s="1"/>
       <c r="AA180" s="1"/>
       <c r="AB180" s="1"/>
-    </row>
-    <row r="181" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC180" s="1"/>
+    </row>
+    <row r="181" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A181" s="3">
         <v>178</v>
       </c>
-      <c r="B181" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C181" s="1"/>
+      <c r="B181" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>180</v>
+      </c>
       <c r="D181" s="1"/>
       <c r="E181" s="1"/>
       <c r="F181" s="1"/>
@@ -8349,7 +8670,9 @@
       <c r="P181" s="1"/>
       <c r="Q181" s="1"/>
       <c r="R181" s="1"/>
-      <c r="S181" s="1"/>
+      <c r="S181" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T181" s="1"/>
       <c r="U181" s="1"/>
       <c r="V181" s="1"/>
@@ -8359,15 +8682,18 @@
       <c r="Z181" s="1"/>
       <c r="AA181" s="1"/>
       <c r="AB181" s="1"/>
-    </row>
-    <row r="182" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC181" s="1"/>
+    </row>
+    <row r="182" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A182" s="3">
         <v>179</v>
       </c>
-      <c r="B182" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="C182" s="1"/>
+      <c r="B182" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>181</v>
+      </c>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
@@ -8383,7 +8709,9 @@
       <c r="P182" s="1"/>
       <c r="Q182" s="1"/>
       <c r="R182" s="1"/>
-      <c r="S182" s="1"/>
+      <c r="S182" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T182" s="1"/>
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
@@ -8393,15 +8721,18 @@
       <c r="Z182" s="1"/>
       <c r="AA182" s="1"/>
       <c r="AB182" s="1"/>
-    </row>
-    <row r="183" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC182" s="1"/>
+    </row>
+    <row r="183" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A183" s="3">
         <v>180</v>
       </c>
-      <c r="B183" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C183" s="1"/>
+      <c r="B183" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>182</v>
+      </c>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
@@ -8413,13 +8744,15 @@
       <c r="L183" s="1"/>
       <c r="M183" s="1"/>
       <c r="N183" s="1"/>
-      <c r="O183" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="P183" s="1"/>
+      <c r="O183" s="1"/>
+      <c r="P183" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="Q183" s="1"/>
       <c r="R183" s="1"/>
-      <c r="S183" s="1"/>
+      <c r="S183" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T183" s="1"/>
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
@@ -8429,15 +8762,18 @@
       <c r="Z183" s="1"/>
       <c r="AA183" s="1"/>
       <c r="AB183" s="1"/>
-    </row>
-    <row r="184" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC183" s="1"/>
+    </row>
+    <row r="184" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A184" s="3">
         <v>181</v>
       </c>
-      <c r="B184" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C184" s="1"/>
+      <c r="B184" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>183</v>
+      </c>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
       <c r="F184" s="1"/>
@@ -8449,13 +8785,15 @@
       <c r="L184" s="1"/>
       <c r="M184" s="1"/>
       <c r="N184" s="1"/>
-      <c r="O184" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="P184" s="1"/>
+      <c r="O184" s="1"/>
+      <c r="P184" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="Q184" s="1"/>
       <c r="R184" s="1"/>
-      <c r="S184" s="1"/>
+      <c r="S184" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T184" s="1"/>
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
@@ -8465,15 +8803,18 @@
       <c r="Z184" s="1"/>
       <c r="AA184" s="1"/>
       <c r="AB184" s="1"/>
-    </row>
-    <row r="185" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC184" s="1"/>
+    </row>
+    <row r="185" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A185" s="3">
         <v>182</v>
       </c>
-      <c r="B185" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C185" s="1"/>
+      <c r="B185" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>184</v>
+      </c>
       <c r="D185" s="1"/>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
@@ -8485,13 +8826,15 @@
       <c r="L185" s="1"/>
       <c r="M185" s="1"/>
       <c r="N185" s="1"/>
-      <c r="O185" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="P185" s="1"/>
+      <c r="O185" s="1"/>
+      <c r="P185" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="Q185" s="1"/>
       <c r="R185" s="1"/>
-      <c r="S185" s="1"/>
+      <c r="S185" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T185" s="1"/>
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
@@ -8501,15 +8844,16 @@
       <c r="Z185" s="1"/>
       <c r="AA185" s="1"/>
       <c r="AB185" s="1"/>
-    </row>
-    <row r="186" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC185" s="1"/>
+    </row>
+    <row r="186" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A186" s="3">
         <v>183</v>
       </c>
-      <c r="B186" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="C186" s="1"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="4" t="s">
+        <v>186</v>
+      </c>
       <c r="D186" s="1"/>
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
@@ -8527,39 +8871,40 @@
       <c r="R186" s="1"/>
       <c r="S186" s="1"/>
       <c r="T186" s="1"/>
-      <c r="U186" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="U186" s="1"/>
       <c r="V186" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="W186" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="X186" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Y186" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Z186" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA186" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AB186" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="187" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+        <v>158</v>
+      </c>
+      <c r="AC186" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="187" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A187" s="3">
         <v>184</v>
       </c>
-      <c r="B187" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C187" s="1"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="4" t="s">
+        <v>187</v>
+      </c>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
       <c r="F187" s="1"/>
@@ -8577,39 +8922,40 @@
       <c r="R187" s="1"/>
       <c r="S187" s="1"/>
       <c r="T187" s="1"/>
-      <c r="U187" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="U187" s="1"/>
       <c r="V187" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="W187" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="X187" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Y187" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Z187" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA187" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AB187" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="188" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+        <v>158</v>
+      </c>
+      <c r="AC187" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="188" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A188" s="3">
         <v>185</v>
       </c>
-      <c r="B188" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C188" s="1"/>
+      <c r="B188" s="1"/>
+      <c r="C188" s="4" t="s">
+        <v>188</v>
+      </c>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
       <c r="F188" s="1"/>
@@ -8621,47 +8967,48 @@
       <c r="L188" s="1"/>
       <c r="M188" s="1"/>
       <c r="N188" s="1"/>
-      <c r="O188" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="P188" s="1"/>
+      <c r="O188" s="1"/>
+      <c r="P188" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
       <c r="S188" s="1"/>
       <c r="T188" s="1"/>
-      <c r="U188" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="U188" s="1"/>
       <c r="V188" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="W188" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="X188" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Y188" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Z188" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA188" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AB188" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="189" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+        <v>158</v>
+      </c>
+      <c r="AC188" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="189" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A189" s="3">
         <v>186</v>
       </c>
-      <c r="B189" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="C189" s="1"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="4" t="s">
+        <v>189</v>
+      </c>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
       <c r="F189" s="1"/>
@@ -8679,39 +9026,40 @@
       <c r="R189" s="1"/>
       <c r="S189" s="1"/>
       <c r="T189" s="1"/>
-      <c r="U189" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="U189" s="1"/>
       <c r="V189" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="W189" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="X189" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Y189" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Z189" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA189" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AB189" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="190" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+        <v>158</v>
+      </c>
+      <c r="AC189" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="190" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A190" s="3">
         <v>187</v>
       </c>
-      <c r="B190" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="C190" s="1"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="4" t="s">
+        <v>190</v>
+      </c>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
@@ -8729,39 +9077,40 @@
       <c r="R190" s="1"/>
       <c r="S190" s="1"/>
       <c r="T190" s="1"/>
-      <c r="U190" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="U190" s="1"/>
       <c r="V190" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="W190" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="X190" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Y190" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Z190" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA190" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AB190" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="191" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+        <v>158</v>
+      </c>
+      <c r="AC190" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="191" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A191" s="3">
         <v>188</v>
       </c>
-      <c r="B191" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C191" s="1"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="4" t="s">
+        <v>191</v>
+      </c>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
       <c r="F191" s="1"/>
@@ -8779,39 +9128,40 @@
       <c r="R191" s="1"/>
       <c r="S191" s="1"/>
       <c r="T191" s="1"/>
-      <c r="U191" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="U191" s="1"/>
       <c r="V191" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="W191" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="X191" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Y191" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Z191" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA191" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AB191" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="192" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+        <v>158</v>
+      </c>
+      <c r="AC191" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="192" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A192" s="3">
         <v>189</v>
       </c>
-      <c r="B192" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="C192" s="1"/>
+      <c r="B192" s="1"/>
+      <c r="C192" s="4" t="s">
+        <v>192</v>
+      </c>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
       <c r="F192" s="1"/>
@@ -8828,9 +9178,11 @@
       <c r="Q192" s="1"/>
       <c r="R192" s="1"/>
       <c r="S192" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T192" s="1"/>
+        <v>158</v>
+      </c>
+      <c r="T192" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
       <c r="W192" s="1"/>
@@ -8839,15 +9191,16 @@
       <c r="Z192" s="1"/>
       <c r="AA192" s="1"/>
       <c r="AB192" s="1"/>
-    </row>
-    <row r="193" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC192" s="1"/>
+    </row>
+    <row r="193" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A193" s="3">
         <v>190</v>
       </c>
-      <c r="B193" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C193" s="1"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="4" t="s">
+        <v>193</v>
+      </c>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
@@ -8859,16 +9212,16 @@
       <c r="L193" s="1"/>
       <c r="M193" s="1"/>
       <c r="N193" s="1"/>
-      <c r="O193" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="P193" s="1"/>
+      <c r="O193" s="1"/>
+      <c r="P193" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
-      <c r="S193" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T193" s="1"/>
+      <c r="S193" s="1"/>
+      <c r="T193" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
       <c r="W193" s="1"/>
@@ -8877,15 +9230,16 @@
       <c r="Z193" s="1"/>
       <c r="AA193" s="1"/>
       <c r="AB193" s="1"/>
-    </row>
-    <row r="194" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC193" s="1"/>
+    </row>
+    <row r="194" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A194" s="3">
         <v>191</v>
       </c>
-      <c r="B194" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="C194" s="1"/>
+      <c r="B194" s="1"/>
+      <c r="C194" s="4" t="s">
+        <v>194</v>
+      </c>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
@@ -8901,10 +9255,10 @@
       <c r="P194" s="1"/>
       <c r="Q194" s="1"/>
       <c r="R194" s="1"/>
-      <c r="S194" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T194" s="1"/>
+      <c r="S194" s="1"/>
+      <c r="T194" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
       <c r="W194" s="1"/>
@@ -8913,15 +9267,16 @@
       <c r="Z194" s="1"/>
       <c r="AA194" s="1"/>
       <c r="AB194" s="1"/>
-    </row>
-    <row r="195" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC194" s="1"/>
+    </row>
+    <row r="195" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A195" s="3">
         <v>192</v>
       </c>
-      <c r="B195" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="C195" s="1"/>
+      <c r="B195" s="1"/>
+      <c r="C195" s="4" t="s">
+        <v>195</v>
+      </c>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
@@ -8937,10 +9292,10 @@
       <c r="P195" s="1"/>
       <c r="Q195" s="1"/>
       <c r="R195" s="1"/>
-      <c r="S195" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T195" s="1"/>
+      <c r="S195" s="1"/>
+      <c r="T195" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
       <c r="W195" s="1"/>
@@ -8949,15 +9304,16 @@
       <c r="Z195" s="1"/>
       <c r="AA195" s="1"/>
       <c r="AB195" s="1"/>
-    </row>
-    <row r="196" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC195" s="1"/>
+    </row>
+    <row r="196" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A196" s="3">
         <v>193</v>
       </c>
-      <c r="B196" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C196" s="1"/>
+      <c r="B196" s="1"/>
+      <c r="C196" s="4" t="s">
+        <v>196</v>
+      </c>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
       <c r="F196" s="1"/>
@@ -8973,10 +9329,10 @@
       <c r="P196" s="1"/>
       <c r="Q196" s="1"/>
       <c r="R196" s="1"/>
-      <c r="S196" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T196" s="1"/>
+      <c r="S196" s="1"/>
+      <c r="T196" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
       <c r="W196" s="1"/>
@@ -8985,15 +9341,16 @@
       <c r="Z196" s="1"/>
       <c r="AA196" s="1"/>
       <c r="AB196" s="1"/>
-    </row>
-    <row r="197" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC196" s="1"/>
+    </row>
+    <row r="197" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A197" s="3">
         <v>194</v>
       </c>
-      <c r="B197" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C197" s="1"/>
+      <c r="B197" s="1"/>
+      <c r="C197" s="4" t="s">
+        <v>197</v>
+      </c>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
@@ -9009,10 +9366,10 @@
       <c r="P197" s="1"/>
       <c r="Q197" s="1"/>
       <c r="R197" s="1"/>
-      <c r="S197" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T197" s="1"/>
+      <c r="S197" s="1"/>
+      <c r="T197" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
       <c r="W197" s="1"/>
@@ -9021,15 +9378,16 @@
       <c r="Z197" s="1"/>
       <c r="AA197" s="1"/>
       <c r="AB197" s="1"/>
-    </row>
-    <row r="198" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC197" s="1"/>
+    </row>
+    <row r="198" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A198" s="3">
         <v>195</v>
       </c>
-      <c r="B198" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C198" s="1"/>
+      <c r="B198" s="1"/>
+      <c r="C198" s="4" t="s">
+        <v>198</v>
+      </c>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
@@ -9045,10 +9403,10 @@
       <c r="P198" s="1"/>
       <c r="Q198" s="1"/>
       <c r="R198" s="1"/>
-      <c r="S198" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T198" s="1"/>
+      <c r="S198" s="1"/>
+      <c r="T198" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
       <c r="W198" s="1"/>
@@ -9057,15 +9415,16 @@
       <c r="Z198" s="1"/>
       <c r="AA198" s="1"/>
       <c r="AB198" s="1"/>
-    </row>
-    <row r="199" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC198" s="1"/>
+    </row>
+    <row r="199" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A199" s="3">
         <v>196</v>
       </c>
-      <c r="B199" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="C199" s="1"/>
+      <c r="B199" s="1"/>
+      <c r="C199" s="4" t="s">
+        <v>199</v>
+      </c>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
@@ -9081,10 +9440,10 @@
       <c r="P199" s="1"/>
       <c r="Q199" s="1"/>
       <c r="R199" s="1"/>
-      <c r="S199" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T199" s="1"/>
+      <c r="S199" s="1"/>
+      <c r="T199" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
       <c r="W199" s="1"/>
@@ -9093,15 +9452,16 @@
       <c r="Z199" s="1"/>
       <c r="AA199" s="1"/>
       <c r="AB199" s="1"/>
-    </row>
-    <row r="200" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC199" s="1"/>
+    </row>
+    <row r="200" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A200" s="3">
         <v>197</v>
       </c>
-      <c r="B200" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C200" s="1"/>
+      <c r="B200" s="1"/>
+      <c r="C200" s="4" t="s">
+        <v>200</v>
+      </c>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
       <c r="F200" s="1"/>
@@ -9117,10 +9477,10 @@
       <c r="P200" s="1"/>
       <c r="Q200" s="1"/>
       <c r="R200" s="1"/>
-      <c r="S200" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T200" s="1"/>
+      <c r="S200" s="1"/>
+      <c r="T200" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
       <c r="W200" s="1"/>
@@ -9129,15 +9489,16 @@
       <c r="Z200" s="1"/>
       <c r="AA200" s="1"/>
       <c r="AB200" s="1"/>
-    </row>
-    <row r="201" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC200" s="1"/>
+    </row>
+    <row r="201" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A201" s="3">
         <v>198</v>
       </c>
-      <c r="B201" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="C201" s="1"/>
+      <c r="B201" s="1"/>
+      <c r="C201" s="4" t="s">
+        <v>201</v>
+      </c>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
@@ -9153,10 +9514,10 @@
       <c r="P201" s="1"/>
       <c r="Q201" s="1"/>
       <c r="R201" s="1"/>
-      <c r="S201" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T201" s="1"/>
+      <c r="S201" s="1"/>
+      <c r="T201" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U201" s="1"/>
       <c r="V201" s="1"/>
       <c r="W201" s="1"/>
@@ -9165,15 +9526,16 @@
       <c r="Z201" s="1"/>
       <c r="AA201" s="1"/>
       <c r="AB201" s="1"/>
-    </row>
-    <row r="202" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC201" s="1"/>
+    </row>
+    <row r="202" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A202" s="3">
         <v>199</v>
       </c>
-      <c r="B202" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="C202" s="1"/>
+      <c r="B202" s="1"/>
+      <c r="C202" s="4" t="s">
+        <v>202</v>
+      </c>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
       <c r="F202" s="1"/>
@@ -9189,10 +9551,10 @@
       <c r="P202" s="1"/>
       <c r="Q202" s="1"/>
       <c r="R202" s="1"/>
-      <c r="S202" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T202" s="1"/>
+      <c r="S202" s="1"/>
+      <c r="T202" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U202" s="1"/>
       <c r="V202" s="1"/>
       <c r="W202" s="1"/>
@@ -9201,15 +9563,16 @@
       <c r="Z202" s="1"/>
       <c r="AA202" s="1"/>
       <c r="AB202" s="1"/>
-    </row>
-    <row r="203" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC202" s="1"/>
+    </row>
+    <row r="203" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A203" s="3">
         <v>200</v>
       </c>
-      <c r="B203" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="C203" s="1"/>
+      <c r="B203" s="1"/>
+      <c r="C203" s="4" t="s">
+        <v>203</v>
+      </c>
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
@@ -9221,16 +9584,16 @@
       <c r="L203" s="1"/>
       <c r="M203" s="1"/>
       <c r="N203" s="1"/>
-      <c r="O203" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="P203" s="1"/>
+      <c r="O203" s="1"/>
+      <c r="P203" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="Q203" s="1"/>
       <c r="R203" s="1"/>
-      <c r="S203" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T203" s="1"/>
+      <c r="S203" s="1"/>
+      <c r="T203" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U203" s="1"/>
       <c r="V203" s="1"/>
       <c r="W203" s="1"/>
@@ -9239,15 +9602,16 @@
       <c r="Z203" s="1"/>
       <c r="AA203" s="1"/>
       <c r="AB203" s="1"/>
-    </row>
-    <row r="204" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC203" s="1"/>
+    </row>
+    <row r="204" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A204" s="3">
         <v>201</v>
       </c>
-      <c r="B204" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="C204" s="1"/>
+      <c r="B204" s="1"/>
+      <c r="C204" s="4" t="s">
+        <v>204</v>
+      </c>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
@@ -9263,10 +9627,10 @@
       <c r="P204" s="1"/>
       <c r="Q204" s="1"/>
       <c r="R204" s="1"/>
-      <c r="S204" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T204" s="1"/>
+      <c r="S204" s="1"/>
+      <c r="T204" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U204" s="1"/>
       <c r="V204" s="1"/>
       <c r="W204" s="1"/>
@@ -9275,15 +9639,16 @@
       <c r="Z204" s="1"/>
       <c r="AA204" s="1"/>
       <c r="AB204" s="1"/>
-    </row>
-    <row r="205" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC204" s="1"/>
+    </row>
+    <row r="205" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A205" s="3">
         <v>202</v>
       </c>
-      <c r="B205" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="C205" s="1"/>
+      <c r="B205" s="1"/>
+      <c r="C205" s="4" t="s">
+        <v>205</v>
+      </c>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
       <c r="F205" s="1"/>
@@ -9299,10 +9664,10 @@
       <c r="P205" s="1"/>
       <c r="Q205" s="1"/>
       <c r="R205" s="1"/>
-      <c r="S205" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T205" s="1"/>
+      <c r="S205" s="1"/>
+      <c r="T205" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U205" s="1"/>
       <c r="V205" s="1"/>
       <c r="W205" s="1"/>
@@ -9311,15 +9676,16 @@
       <c r="Z205" s="1"/>
       <c r="AA205" s="1"/>
       <c r="AB205" s="1"/>
-    </row>
-    <row r="206" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC205" s="1"/>
+    </row>
+    <row r="206" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A206" s="3">
         <v>203</v>
       </c>
-      <c r="B206" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C206" s="1"/>
+      <c r="B206" s="1"/>
+      <c r="C206" s="4" t="s">
+        <v>206</v>
+      </c>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
       <c r="F206" s="1"/>
@@ -9335,10 +9701,10 @@
       <c r="P206" s="1"/>
       <c r="Q206" s="1"/>
       <c r="R206" s="1"/>
-      <c r="S206" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T206" s="1"/>
+      <c r="S206" s="1"/>
+      <c r="T206" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U206" s="1"/>
       <c r="V206" s="1"/>
       <c r="W206" s="1"/>
@@ -9347,15 +9713,16 @@
       <c r="Z206" s="1"/>
       <c r="AA206" s="1"/>
       <c r="AB206" s="1"/>
-    </row>
-    <row r="207" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC206" s="1"/>
+    </row>
+    <row r="207" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A207" s="3">
         <v>204</v>
       </c>
-      <c r="B207" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C207" s="1"/>
+      <c r="B207" s="1"/>
+      <c r="C207" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
       <c r="F207" s="1"/>
@@ -9367,16 +9734,16 @@
       <c r="L207" s="1"/>
       <c r="M207" s="1"/>
       <c r="N207" s="1"/>
-      <c r="O207" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="P207" s="1"/>
+      <c r="O207" s="1"/>
+      <c r="P207" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="Q207" s="1"/>
       <c r="R207" s="1"/>
-      <c r="S207" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T207" s="1"/>
+      <c r="S207" s="1"/>
+      <c r="T207" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U207" s="1"/>
       <c r="V207" s="1"/>
       <c r="W207" s="1"/>
@@ -9385,15 +9752,16 @@
       <c r="Z207" s="1"/>
       <c r="AA207" s="1"/>
       <c r="AB207" s="1"/>
-    </row>
-    <row r="208" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC207" s="1"/>
+    </row>
+    <row r="208" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A208" s="3">
         <v>205</v>
       </c>
-      <c r="B208" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C208" s="1"/>
+      <c r="B208" s="1"/>
+      <c r="C208" s="4" t="s">
+        <v>208</v>
+      </c>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
       <c r="F208" s="1"/>
@@ -9409,10 +9777,10 @@
       <c r="P208" s="1"/>
       <c r="Q208" s="1"/>
       <c r="R208" s="1"/>
-      <c r="S208" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T208" s="1"/>
+      <c r="S208" s="1"/>
+      <c r="T208" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U208" s="1"/>
       <c r="V208" s="1"/>
       <c r="W208" s="1"/>
@@ -9421,15 +9789,16 @@
       <c r="Z208" s="1"/>
       <c r="AA208" s="1"/>
       <c r="AB208" s="1"/>
-    </row>
-    <row r="209" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC208" s="1"/>
+    </row>
+    <row r="209" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A209" s="3">
         <v>206</v>
       </c>
-      <c r="B209" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="C209" s="1"/>
+      <c r="B209" s="1"/>
+      <c r="C209" s="4" t="s">
+        <v>209</v>
+      </c>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
       <c r="F209" s="1"/>
@@ -9445,10 +9814,10 @@
       <c r="P209" s="1"/>
       <c r="Q209" s="1"/>
       <c r="R209" s="1"/>
-      <c r="S209" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T209" s="1"/>
+      <c r="S209" s="1"/>
+      <c r="T209" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U209" s="1"/>
       <c r="V209" s="1"/>
       <c r="W209" s="1"/>
@@ -9457,15 +9826,16 @@
       <c r="Z209" s="1"/>
       <c r="AA209" s="1"/>
       <c r="AB209" s="1"/>
-    </row>
-    <row r="210" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC209" s="1"/>
+    </row>
+    <row r="210" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A210" s="3">
         <v>207</v>
       </c>
-      <c r="B210" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C210" s="1"/>
+      <c r="B210" s="1"/>
+      <c r="C210" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
       <c r="F210" s="1"/>
@@ -9481,10 +9851,10 @@
       <c r="P210" s="1"/>
       <c r="Q210" s="1"/>
       <c r="R210" s="1"/>
-      <c r="S210" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T210" s="1"/>
+      <c r="S210" s="1"/>
+      <c r="T210" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U210" s="1"/>
       <c r="V210" s="1"/>
       <c r="W210" s="1"/>
@@ -9493,15 +9863,16 @@
       <c r="Z210" s="1"/>
       <c r="AA210" s="1"/>
       <c r="AB210" s="1"/>
-    </row>
-    <row r="211" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC210" s="1"/>
+    </row>
+    <row r="211" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A211" s="3">
         <v>208</v>
       </c>
-      <c r="B211" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="C211" s="1"/>
+      <c r="B211" s="1"/>
+      <c r="C211" s="4" t="s">
+        <v>211</v>
+      </c>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
@@ -9517,10 +9888,10 @@
       <c r="P211" s="1"/>
       <c r="Q211" s="1"/>
       <c r="R211" s="1"/>
-      <c r="S211" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T211" s="1"/>
+      <c r="S211" s="1"/>
+      <c r="T211" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
       <c r="W211" s="1"/>
@@ -9529,15 +9900,16 @@
       <c r="Z211" s="1"/>
       <c r="AA211" s="1"/>
       <c r="AB211" s="1"/>
-    </row>
-    <row r="212" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC211" s="1"/>
+    </row>
+    <row r="212" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A212" s="3">
         <v>209</v>
       </c>
-      <c r="B212" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C212" s="1"/>
+      <c r="B212" s="1"/>
+      <c r="C212" s="4" t="s">
+        <v>212</v>
+      </c>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
       <c r="F212" s="1"/>
@@ -9553,10 +9925,10 @@
       <c r="P212" s="1"/>
       <c r="Q212" s="1"/>
       <c r="R212" s="1"/>
-      <c r="S212" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T212" s="1"/>
+      <c r="S212" s="1"/>
+      <c r="T212" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
       <c r="W212" s="1"/>
@@ -9565,15 +9937,16 @@
       <c r="Z212" s="1"/>
       <c r="AA212" s="1"/>
       <c r="AB212" s="1"/>
-    </row>
-    <row r="213" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC212" s="1"/>
+    </row>
+    <row r="213" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A213" s="3">
         <v>210</v>
       </c>
-      <c r="B213" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C213" s="1"/>
+      <c r="B213" s="1"/>
+      <c r="C213" s="4" t="s">
+        <v>213</v>
+      </c>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
       <c r="F213" s="1"/>
@@ -9589,10 +9962,10 @@
       <c r="P213" s="1"/>
       <c r="Q213" s="1"/>
       <c r="R213" s="1"/>
-      <c r="S213" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T213" s="1"/>
+      <c r="S213" s="1"/>
+      <c r="T213" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
       <c r="W213" s="1"/>
@@ -9601,15 +9974,16 @@
       <c r="Z213" s="1"/>
       <c r="AA213" s="1"/>
       <c r="AB213" s="1"/>
-    </row>
-    <row r="214" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC213" s="1"/>
+    </row>
+    <row r="214" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A214" s="3">
         <v>211</v>
       </c>
-      <c r="B214" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="C214" s="1"/>
+      <c r="B214" s="1"/>
+      <c r="C214" s="4" t="s">
+        <v>214</v>
+      </c>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
       <c r="F214" s="1"/>
@@ -9625,10 +9999,10 @@
       <c r="P214" s="1"/>
       <c r="Q214" s="1"/>
       <c r="R214" s="1"/>
-      <c r="S214" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T214" s="1"/>
+      <c r="S214" s="1"/>
+      <c r="T214" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U214" s="1"/>
       <c r="V214" s="1"/>
       <c r="W214" s="1"/>
@@ -9637,15 +10011,16 @@
       <c r="Z214" s="1"/>
       <c r="AA214" s="1"/>
       <c r="AB214" s="1"/>
-    </row>
-    <row r="215" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC214" s="1"/>
+    </row>
+    <row r="215" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A215" s="3">
         <v>212</v>
       </c>
-      <c r="B215" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="C215" s="1"/>
+      <c r="B215" s="1"/>
+      <c r="C215" s="4" t="s">
+        <v>215</v>
+      </c>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
       <c r="F215" s="1"/>
@@ -9657,10 +10032,10 @@
       <c r="L215" s="1"/>
       <c r="M215" s="1"/>
       <c r="N215" s="1"/>
-      <c r="O215" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="P215" s="1"/>
+      <c r="O215" s="1"/>
+      <c r="P215" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="Q215" s="1"/>
       <c r="R215" s="1"/>
       <c r="S215" s="1"/>
@@ -9673,15 +10048,18 @@
       <c r="Z215" s="1"/>
       <c r="AA215" s="1"/>
       <c r="AB215" s="1"/>
-    </row>
-    <row r="216" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC215" s="1"/>
+    </row>
+    <row r="216" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A216" s="3">
         <v>213</v>
       </c>
-      <c r="B216" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="C216" s="1"/>
+      <c r="B216" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>242</v>
+      </c>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
       <c r="F216" s="1"/>
@@ -9698,7 +10076,9 @@
       <c r="Q216" s="1"/>
       <c r="R216" s="1"/>
       <c r="S216" s="1"/>
-      <c r="T216" s="1"/>
+      <c r="T216" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U216" s="1"/>
       <c r="V216" s="1"/>
       <c r="W216" s="1"/>
@@ -9707,15 +10087,18 @@
       <c r="Z216" s="1"/>
       <c r="AA216" s="1"/>
       <c r="AB216" s="1"/>
-    </row>
-    <row r="217" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC216" s="1"/>
+    </row>
+    <row r="217" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A217" s="3">
         <v>214</v>
       </c>
-      <c r="B217" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="C217" s="1"/>
+      <c r="B217" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>243</v>
+      </c>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
       <c r="F217" s="1"/>
@@ -9732,7 +10115,9 @@
       <c r="Q217" s="1"/>
       <c r="R217" s="1"/>
       <c r="S217" s="1"/>
-      <c r="T217" s="1"/>
+      <c r="T217" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U217" s="1"/>
       <c r="V217" s="1"/>
       <c r="W217" s="1"/>
@@ -9741,15 +10126,18 @@
       <c r="Z217" s="1"/>
       <c r="AA217" s="1"/>
       <c r="AB217" s="1"/>
-    </row>
-    <row r="218" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC217" s="1"/>
+    </row>
+    <row r="218" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A218" s="3">
         <v>215</v>
       </c>
-      <c r="B218" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="C218" s="1"/>
+      <c r="B218" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>244</v>
+      </c>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
       <c r="F218" s="1"/>
@@ -9766,7 +10154,9 @@
       <c r="Q218" s="1"/>
       <c r="R218" s="1"/>
       <c r="S218" s="1"/>
-      <c r="T218" s="1"/>
+      <c r="T218" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="U218" s="1"/>
       <c r="V218" s="1"/>
       <c r="W218" s="1"/>
@@ -9775,15 +10165,16 @@
       <c r="Z218" s="1"/>
       <c r="AA218" s="1"/>
       <c r="AB218" s="1"/>
-    </row>
-    <row r="219" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC218" s="1"/>
+    </row>
+    <row r="219" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A219" s="3">
         <v>216</v>
       </c>
-      <c r="B219" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="C219" s="1"/>
+      <c r="B219" s="1"/>
+      <c r="C219" s="4" t="s">
+        <v>245</v>
+      </c>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
       <c r="F219" s="1"/>
@@ -9809,15 +10200,16 @@
       <c r="Z219" s="1"/>
       <c r="AA219" s="1"/>
       <c r="AB219" s="1"/>
-    </row>
-    <row r="220" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC219" s="1"/>
+    </row>
+    <row r="220" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A220" s="3">
         <v>217</v>
       </c>
-      <c r="B220" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="C220" s="1"/>
+      <c r="B220" s="1"/>
+      <c r="C220" s="4" t="s">
+        <v>246</v>
+      </c>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
       <c r="F220" s="1"/>
@@ -9843,15 +10235,16 @@
       <c r="Z220" s="1"/>
       <c r="AA220" s="1"/>
       <c r="AB220" s="1"/>
-    </row>
-    <row r="221" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC220" s="1"/>
+    </row>
+    <row r="221" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A221" s="3">
         <v>218</v>
       </c>
-      <c r="B221" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="C221" s="1"/>
+      <c r="B221" s="1"/>
+      <c r="C221" s="4" t="s">
+        <v>247</v>
+      </c>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
       <c r="F221" s="1"/>
@@ -9877,15 +10270,18 @@
       <c r="Z221" s="1"/>
       <c r="AA221" s="1"/>
       <c r="AB221" s="1"/>
-    </row>
-    <row r="222" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC221" s="1"/>
+    </row>
+    <row r="222" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A222" s="3">
         <v>219</v>
       </c>
-      <c r="B222" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C222" s="1"/>
+      <c r="B222" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>248</v>
+      </c>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
@@ -9911,15 +10307,16 @@
       <c r="Z222" s="1"/>
       <c r="AA222" s="1"/>
       <c r="AB222" s="1"/>
-    </row>
-    <row r="223" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC222" s="1"/>
+    </row>
+    <row r="223" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A223" s="3">
         <v>220</v>
       </c>
-      <c r="B223" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C223" s="1"/>
+      <c r="B223" s="1"/>
+      <c r="C223" s="4" t="s">
+        <v>249</v>
+      </c>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
@@ -9945,15 +10342,16 @@
       <c r="Z223" s="1"/>
       <c r="AA223" s="1"/>
       <c r="AB223" s="1"/>
-    </row>
-    <row r="224" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC223" s="1"/>
+    </row>
+    <row r="224" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A224" s="3">
         <v>221</v>
       </c>
-      <c r="B224" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="C224" s="1"/>
+      <c r="B224" s="1"/>
+      <c r="C224" s="4" t="s">
+        <v>250</v>
+      </c>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
       <c r="F224" s="1"/>
@@ -9979,15 +10377,16 @@
       <c r="Z224" s="1"/>
       <c r="AA224" s="1"/>
       <c r="AB224" s="1"/>
-    </row>
-    <row r="225" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC224" s="1"/>
+    </row>
+    <row r="225" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A225" s="3">
         <v>222</v>
       </c>
-      <c r="B225" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="C225" s="1"/>
+      <c r="B225" s="1"/>
+      <c r="C225" s="4" t="s">
+        <v>251</v>
+      </c>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
       <c r="F225" s="1"/>
@@ -10013,15 +10412,16 @@
       <c r="Z225" s="1"/>
       <c r="AA225" s="1"/>
       <c r="AB225" s="1"/>
-    </row>
-    <row r="226" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC225" s="1"/>
+    </row>
+    <row r="226" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A226" s="3">
         <v>223</v>
       </c>
-      <c r="B226" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C226" s="1"/>
+      <c r="B226" s="1"/>
+      <c r="C226" s="4" t="s">
+        <v>252</v>
+      </c>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
       <c r="F226" s="1"/>
@@ -10047,15 +10447,16 @@
       <c r="Z226" s="1"/>
       <c r="AA226" s="1"/>
       <c r="AB226" s="1"/>
-    </row>
-    <row r="227" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC226" s="1"/>
+    </row>
+    <row r="227" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A227" s="3">
         <v>224</v>
       </c>
-      <c r="B227" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="C227" s="1"/>
+      <c r="B227" s="1"/>
+      <c r="C227" s="4" t="s">
+        <v>253</v>
+      </c>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
@@ -10081,15 +10482,16 @@
       <c r="Z227" s="1"/>
       <c r="AA227" s="1"/>
       <c r="AB227" s="1"/>
-    </row>
-    <row r="228" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC227" s="1"/>
+    </row>
+    <row r="228" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A228" s="3">
         <v>225</v>
       </c>
-      <c r="B228" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="C228" s="1"/>
+      <c r="B228" s="1"/>
+      <c r="C228" s="4" t="s">
+        <v>254</v>
+      </c>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
@@ -10115,15 +10517,16 @@
       <c r="Z228" s="1"/>
       <c r="AA228" s="1"/>
       <c r="AB228" s="1"/>
-    </row>
-    <row r="229" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC228" s="1"/>
+    </row>
+    <row r="229" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A229" s="3">
         <v>226</v>
       </c>
-      <c r="B229" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="C229" s="1"/>
+      <c r="B229" s="1"/>
+      <c r="C229" s="4" t="s">
+        <v>255</v>
+      </c>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
       <c r="F229" s="1"/>
@@ -10149,15 +10552,16 @@
       <c r="Z229" s="1"/>
       <c r="AA229" s="1"/>
       <c r="AB229" s="1"/>
-    </row>
-    <row r="230" spans="1:28" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AC229" s="1"/>
+    </row>
+    <row r="230" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A230" s="3">
         <v>227</v>
       </c>
-      <c r="B230" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C230" s="1"/>
+      <c r="B230" s="1"/>
+      <c r="C230" s="4" t="s">
+        <v>256</v>
+      </c>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
       <c r="F230" s="1"/>
@@ -10183,15 +10587,16 @@
       <c r="Z230" s="1"/>
       <c r="AA230" s="1"/>
       <c r="AB230" s="1"/>
-    </row>
-    <row r="231" spans="1:28">
+      <c r="AC230" s="1"/>
+    </row>
+    <row r="231" spans="1:29">
       <c r="A231" s="3">
         <v>228</v>
       </c>
-      <c r="B231" s="28" t="s">
-        <v>258</v>
-      </c>
-      <c r="C231" s="1"/>
+      <c r="B231" s="1"/>
+      <c r="C231" s="21" t="s">
+        <v>257</v>
+      </c>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
       <c r="F231" s="1"/>
@@ -10217,15 +10622,16 @@
       <c r="Z231" s="1"/>
       <c r="AA231" s="1"/>
       <c r="AB231" s="1"/>
-    </row>
-    <row r="232" spans="1:28">
+      <c r="AC231" s="1"/>
+    </row>
+    <row r="232" spans="1:29">
       <c r="A232" s="3">
         <v>229</v>
       </c>
-      <c r="B232" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="C232" s="1"/>
+      <c r="B232" s="1"/>
+      <c r="C232" s="21" t="s">
+        <v>174</v>
+      </c>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
@@ -10251,15 +10657,18 @@
       <c r="Z232" s="1"/>
       <c r="AA232" s="1"/>
       <c r="AB232" s="1"/>
-    </row>
-    <row r="233" spans="1:28">
+      <c r="AC232" s="1"/>
+    </row>
+    <row r="233" spans="1:29">
       <c r="A233" s="3">
         <v>230</v>
       </c>
-      <c r="B233" s="29" t="s">
-        <v>259</v>
-      </c>
-      <c r="C233" s="1"/>
+      <c r="B233" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C233" s="22" t="s">
+        <v>258</v>
+      </c>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
       <c r="F233" s="1"/>
@@ -10285,15 +10694,16 @@
       <c r="Z233" s="1"/>
       <c r="AA233" s="1"/>
       <c r="AB233" s="1"/>
-    </row>
-    <row r="234" spans="1:28">
+      <c r="AC233" s="1"/>
+    </row>
+    <row r="234" spans="1:29">
       <c r="A234" s="3">
         <v>231</v>
       </c>
-      <c r="B234" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="C234" s="1"/>
+      <c r="B234" s="1"/>
+      <c r="C234" s="21" t="s">
+        <v>259</v>
+      </c>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
       <c r="F234" s="1"/>
@@ -10319,15 +10729,16 @@
       <c r="Z234" s="1"/>
       <c r="AA234" s="1"/>
       <c r="AB234" s="1"/>
-    </row>
-    <row r="235" spans="1:28">
+      <c r="AC234" s="1"/>
+    </row>
+    <row r="235" spans="1:29">
       <c r="A235" s="3">
         <v>232</v>
       </c>
-      <c r="B235" s="28" t="s">
-        <v>261</v>
-      </c>
-      <c r="C235" s="1"/>
+      <c r="B235" s="1"/>
+      <c r="C235" s="21" t="s">
+        <v>260</v>
+      </c>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
       <c r="F235" s="1"/>
@@ -10343,7 +10754,9 @@
       <c r="P235" s="1"/>
       <c r="Q235" s="1"/>
       <c r="R235" s="1"/>
-      <c r="S235" s="1"/>
+      <c r="S235" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T235" s="1"/>
       <c r="U235" s="1"/>
       <c r="V235" s="1"/>
@@ -10353,15 +10766,16 @@
       <c r="Z235" s="1"/>
       <c r="AA235" s="1"/>
       <c r="AB235" s="1"/>
-    </row>
-    <row r="236" spans="1:28">
+      <c r="AC235" s="1"/>
+    </row>
+    <row r="236" spans="1:29">
       <c r="A236" s="3">
         <v>233</v>
       </c>
-      <c r="B236" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="C236" s="1"/>
+      <c r="B236" s="1"/>
+      <c r="C236" s="21" t="s">
+        <v>261</v>
+      </c>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
       <c r="F236" s="1"/>
@@ -10387,15 +10801,16 @@
       <c r="Z236" s="1"/>
       <c r="AA236" s="1"/>
       <c r="AB236" s="1"/>
-    </row>
-    <row r="237" spans="1:28">
+      <c r="AC236" s="1"/>
+    </row>
+    <row r="237" spans="1:29">
       <c r="A237" s="3">
         <v>234</v>
       </c>
-      <c r="B237" s="28" t="s">
-        <v>263</v>
-      </c>
-      <c r="C237" s="1"/>
+      <c r="B237" s="1"/>
+      <c r="C237" s="21" t="s">
+        <v>262</v>
+      </c>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
       <c r="F237" s="1"/>
@@ -10421,15 +10836,16 @@
       <c r="Z237" s="1"/>
       <c r="AA237" s="1"/>
       <c r="AB237" s="1"/>
-    </row>
-    <row r="238" spans="1:28">
+      <c r="AC237" s="1"/>
+    </row>
+    <row r="238" spans="1:29">
       <c r="A238" s="3">
         <v>235</v>
       </c>
-      <c r="B238" s="28" t="s">
-        <v>264</v>
-      </c>
-      <c r="C238" s="1"/>
+      <c r="B238" s="1"/>
+      <c r="C238" s="21" t="s">
+        <v>263</v>
+      </c>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
       <c r="F238" s="1"/>
@@ -10455,15 +10871,16 @@
       <c r="Z238" s="1"/>
       <c r="AA238" s="1"/>
       <c r="AB238" s="1"/>
-    </row>
-    <row r="239" spans="1:28">
+      <c r="AC238" s="1"/>
+    </row>
+    <row r="239" spans="1:29">
       <c r="A239" s="3">
         <v>236</v>
       </c>
-      <c r="B239" s="28" t="s">
-        <v>265</v>
-      </c>
-      <c r="C239" s="1"/>
+      <c r="B239" s="1"/>
+      <c r="C239" s="21" t="s">
+        <v>264</v>
+      </c>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
       <c r="F239" s="1"/>
@@ -10489,15 +10906,16 @@
       <c r="Z239" s="1"/>
       <c r="AA239" s="1"/>
       <c r="AB239" s="1"/>
-    </row>
-    <row r="240" spans="1:28">
+      <c r="AC239" s="1"/>
+    </row>
+    <row r="240" spans="1:29">
       <c r="A240" s="3">
         <v>237</v>
       </c>
-      <c r="B240" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="C240" s="1"/>
+      <c r="B240" s="1"/>
+      <c r="C240" s="21" t="s">
+        <v>265</v>
+      </c>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
       <c r="F240" s="1"/>
@@ -10523,15 +10941,16 @@
       <c r="Z240" s="1"/>
       <c r="AA240" s="1"/>
       <c r="AB240" s="1"/>
-    </row>
-    <row r="241" spans="1:28">
+      <c r="AC240" s="1"/>
+    </row>
+    <row r="241" spans="1:29">
       <c r="A241" s="3">
         <v>238</v>
       </c>
-      <c r="B241" s="28" t="s">
-        <v>267</v>
-      </c>
-      <c r="C241" s="1"/>
+      <c r="B241" s="1"/>
+      <c r="C241" s="21" t="s">
+        <v>266</v>
+      </c>
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
       <c r="F241" s="1"/>
@@ -10557,15 +10976,16 @@
       <c r="Z241" s="1"/>
       <c r="AA241" s="1"/>
       <c r="AB241" s="1"/>
-    </row>
-    <row r="242" spans="1:28">
+      <c r="AC241" s="1"/>
+    </row>
+    <row r="242" spans="1:29">
       <c r="A242" s="3">
         <v>239</v>
       </c>
-      <c r="B242" s="28" t="s">
-        <v>268</v>
-      </c>
-      <c r="C242" s="1"/>
+      <c r="B242" s="1"/>
+      <c r="C242" s="21" t="s">
+        <v>267</v>
+      </c>
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
       <c r="F242" s="1"/>
@@ -10591,13 +11011,16 @@
       <c r="Z242" s="1"/>
       <c r="AA242" s="1"/>
       <c r="AB242" s="1"/>
-    </row>
-    <row r="243" spans="1:28">
+      <c r="AC242" s="1"/>
+    </row>
+    <row r="243" spans="1:29">
       <c r="A243" s="3">
         <v>240</v>
       </c>
-      <c r="B243" s="28"/>
-      <c r="C243" s="1"/>
+      <c r="B243" s="3"/>
+      <c r="C243" s="21" t="s">
+        <v>276</v>
+      </c>
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
       <c r="F243" s="1"/>
@@ -10613,7 +11036,9 @@
       <c r="P243" s="1"/>
       <c r="Q243" s="1"/>
       <c r="R243" s="1"/>
-      <c r="S243" s="1"/>
+      <c r="S243" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T243" s="1"/>
       <c r="U243" s="1"/>
       <c r="V243" s="1"/>
@@ -10623,13 +11048,16 @@
       <c r="Z243" s="1"/>
       <c r="AA243" s="1"/>
       <c r="AB243" s="1"/>
-    </row>
-    <row r="244" spans="1:28">
+      <c r="AC243" s="1"/>
+    </row>
+    <row r="244" spans="1:29">
       <c r="A244" s="3">
         <v>241</v>
       </c>
-      <c r="B244" s="28"/>
-      <c r="C244" s="1"/>
+      <c r="B244" s="3"/>
+      <c r="C244" s="21" t="s">
+        <v>277</v>
+      </c>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
       <c r="F244" s="1"/>
@@ -10645,7 +11073,9 @@
       <c r="P244" s="1"/>
       <c r="Q244" s="1"/>
       <c r="R244" s="1"/>
-      <c r="S244" s="1"/>
+      <c r="S244" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T244" s="1"/>
       <c r="U244" s="1"/>
       <c r="V244" s="1"/>
@@ -10655,13 +11085,16 @@
       <c r="Z244" s="1"/>
       <c r="AA244" s="1"/>
       <c r="AB244" s="1"/>
-    </row>
-    <row r="245" spans="1:28">
+      <c r="AC244" s="1"/>
+    </row>
+    <row r="245" spans="1:29">
       <c r="A245" s="3">
         <v>242</v>
       </c>
-      <c r="B245" s="28"/>
-      <c r="C245" s="1"/>
+      <c r="B245" s="3"/>
+      <c r="C245" s="21" t="s">
+        <v>278</v>
+      </c>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
       <c r="F245" s="1"/>
@@ -10677,7 +11110,9 @@
       <c r="P245" s="1"/>
       <c r="Q245" s="1"/>
       <c r="R245" s="1"/>
-      <c r="S245" s="1"/>
+      <c r="S245" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="T245" s="1"/>
       <c r="U245" s="1"/>
       <c r="V245" s="1"/>
@@ -10687,13 +11122,14 @@
       <c r="Z245" s="1"/>
       <c r="AA245" s="1"/>
       <c r="AB245" s="1"/>
-    </row>
-    <row r="246" spans="1:28">
+      <c r="AC245" s="1"/>
+    </row>
+    <row r="246" spans="1:29">
       <c r="A246" s="3">
         <v>243</v>
       </c>
-      <c r="B246" s="28"/>
-      <c r="C246" s="1"/>
+      <c r="B246" s="3"/>
+      <c r="C246" s="21"/>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
@@ -10719,13 +11155,14 @@
       <c r="Z246" s="1"/>
       <c r="AA246" s="1"/>
       <c r="AB246" s="1"/>
-    </row>
-    <row r="247" spans="1:28">
+      <c r="AC246" s="1"/>
+    </row>
+    <row r="247" spans="1:29">
       <c r="A247" s="3">
         <v>244</v>
       </c>
-      <c r="B247" s="28"/>
-      <c r="C247" s="1"/>
+      <c r="B247" s="3"/>
+      <c r="C247" s="21"/>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
       <c r="F247" s="1"/>
@@ -10751,13 +11188,14 @@
       <c r="Z247" s="1"/>
       <c r="AA247" s="1"/>
       <c r="AB247" s="1"/>
-    </row>
-    <row r="248" spans="1:28">
+      <c r="AC247" s="1"/>
+    </row>
+    <row r="248" spans="1:29">
       <c r="A248" s="3">
         <v>245</v>
       </c>
-      <c r="B248" s="28"/>
-      <c r="C248" s="1"/>
+      <c r="B248" s="3"/>
+      <c r="C248" s="21"/>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
       <c r="F248" s="1"/>
@@ -10783,13 +11221,14 @@
       <c r="Z248" s="1"/>
       <c r="AA248" s="1"/>
       <c r="AB248" s="1"/>
-    </row>
-    <row r="249" spans="1:28">
+      <c r="AC248" s="1"/>
+    </row>
+    <row r="249" spans="1:29">
       <c r="A249" s="3">
         <v>246</v>
       </c>
-      <c r="B249" s="28"/>
-      <c r="C249" s="1"/>
+      <c r="B249" s="3"/>
+      <c r="C249" s="21"/>
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
@@ -10815,13 +11254,14 @@
       <c r="Z249" s="1"/>
       <c r="AA249" s="1"/>
       <c r="AB249" s="1"/>
-    </row>
-    <row r="250" spans="1:28">
+      <c r="AC249" s="1"/>
+    </row>
+    <row r="250" spans="1:29">
       <c r="A250" s="3">
         <v>247</v>
       </c>
-      <c r="B250" s="28"/>
-      <c r="C250" s="1"/>
+      <c r="B250" s="3"/>
+      <c r="C250" s="21"/>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
@@ -10847,13 +11287,14 @@
       <c r="Z250" s="1"/>
       <c r="AA250" s="1"/>
       <c r="AB250" s="1"/>
-    </row>
-    <row r="251" spans="1:28">
+      <c r="AC250" s="1"/>
+    </row>
+    <row r="251" spans="1:29">
       <c r="A251" s="3">
         <v>248</v>
       </c>
-      <c r="B251" s="28"/>
-      <c r="C251" s="1"/>
+      <c r="B251" s="3"/>
+      <c r="C251" s="21"/>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
@@ -10879,13 +11320,14 @@
       <c r="Z251" s="1"/>
       <c r="AA251" s="1"/>
       <c r="AB251" s="1"/>
-    </row>
-    <row r="252" spans="1:28">
+      <c r="AC251" s="1"/>
+    </row>
+    <row r="252" spans="1:29">
       <c r="A252" s="3">
         <v>249</v>
       </c>
-      <c r="B252" s="28"/>
-      <c r="C252" s="1"/>
+      <c r="B252" s="3"/>
+      <c r="C252" s="21"/>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
@@ -10911,13 +11353,14 @@
       <c r="Z252" s="1"/>
       <c r="AA252" s="1"/>
       <c r="AB252" s="1"/>
-    </row>
-    <row r="253" spans="1:28">
+      <c r="AC252" s="1"/>
+    </row>
+    <row r="253" spans="1:29">
       <c r="A253" s="3">
         <v>250</v>
       </c>
-      <c r="B253" s="28"/>
-      <c r="C253" s="1"/>
+      <c r="B253" s="3"/>
+      <c r="C253" s="21"/>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
       <c r="F253" s="1"/>
@@ -10943,13 +11386,14 @@
       <c r="Z253" s="1"/>
       <c r="AA253" s="1"/>
       <c r="AB253" s="1"/>
-    </row>
-    <row r="254" spans="1:28">
+      <c r="AC253" s="1"/>
+    </row>
+    <row r="254" spans="1:29">
       <c r="A254" s="3">
         <v>251</v>
       </c>
-      <c r="B254" s="28"/>
-      <c r="C254" s="1"/>
+      <c r="B254" s="3"/>
+      <c r="C254" s="21"/>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
       <c r="F254" s="1"/>
@@ -10975,13 +11419,14 @@
       <c r="Z254" s="1"/>
       <c r="AA254" s="1"/>
       <c r="AB254" s="1"/>
-    </row>
-    <row r="255" spans="1:28">
+      <c r="AC254" s="1"/>
+    </row>
+    <row r="255" spans="1:29">
       <c r="A255" s="3">
         <v>252</v>
       </c>
-      <c r="B255" s="28"/>
-      <c r="C255" s="1"/>
+      <c r="B255" s="3"/>
+      <c r="C255" s="21"/>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
       <c r="F255" s="1"/>
@@ -11007,13 +11452,14 @@
       <c r="Z255" s="1"/>
       <c r="AA255" s="1"/>
       <c r="AB255" s="1"/>
-    </row>
-    <row r="256" spans="1:28">
+      <c r="AC255" s="1"/>
+    </row>
+    <row r="256" spans="1:29">
       <c r="A256" s="3">
         <v>253</v>
       </c>
-      <c r="B256" s="28"/>
-      <c r="C256" s="1"/>
+      <c r="B256" s="3"/>
+      <c r="C256" s="21"/>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>
@@ -11039,13 +11485,14 @@
       <c r="Z256" s="1"/>
       <c r="AA256" s="1"/>
       <c r="AB256" s="1"/>
-    </row>
-    <row r="257" spans="1:28">
+      <c r="AC256" s="1"/>
+    </row>
+    <row r="257" spans="1:29">
       <c r="A257" s="3">
         <v>254</v>
       </c>
-      <c r="B257" s="28"/>
-      <c r="C257" s="1"/>
+      <c r="B257" s="3"/>
+      <c r="C257" s="21"/>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
@@ -11071,13 +11518,14 @@
       <c r="Z257" s="1"/>
       <c r="AA257" s="1"/>
       <c r="AB257" s="1"/>
-    </row>
-    <row r="258" spans="1:28">
+      <c r="AC257" s="1"/>
+    </row>
+    <row r="258" spans="1:29">
       <c r="A258" s="3">
         <v>255</v>
       </c>
-      <c r="B258" s="28"/>
-      <c r="C258" s="1"/>
+      <c r="B258" s="3"/>
+      <c r="C258" s="21"/>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
       <c r="F258" s="1"/>
@@ -11103,13 +11551,14 @@
       <c r="Z258" s="1"/>
       <c r="AA258" s="1"/>
       <c r="AB258" s="1"/>
-    </row>
-    <row r="259" spans="1:28">
+      <c r="AC258" s="1"/>
+    </row>
+    <row r="259" spans="1:29">
       <c r="A259" s="3">
         <v>256</v>
       </c>
-      <c r="B259" s="28"/>
-      <c r="C259" s="1"/>
+      <c r="B259" s="3"/>
+      <c r="C259" s="21"/>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
       <c r="F259" s="1"/>
@@ -11135,13 +11584,14 @@
       <c r="Z259" s="1"/>
       <c r="AA259" s="1"/>
       <c r="AB259" s="1"/>
-    </row>
-    <row r="260" spans="1:28">
+      <c r="AC259" s="1"/>
+    </row>
+    <row r="260" spans="1:29">
       <c r="A260" s="3">
         <v>257</v>
       </c>
-      <c r="B260" s="28"/>
-      <c r="C260" s="1"/>
+      <c r="B260" s="3"/>
+      <c r="C260" s="21"/>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
       <c r="F260" s="1"/>
@@ -11167,13 +11617,14 @@
       <c r="Z260" s="1"/>
       <c r="AA260" s="1"/>
       <c r="AB260" s="1"/>
-    </row>
-    <row r="261" spans="1:28">
+      <c r="AC260" s="1"/>
+    </row>
+    <row r="261" spans="1:29">
       <c r="A261" s="3">
         <v>258</v>
       </c>
-      <c r="B261" s="28"/>
-      <c r="C261" s="1"/>
+      <c r="B261" s="3"/>
+      <c r="C261" s="21"/>
       <c r="D261" s="1"/>
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
@@ -11199,13 +11650,14 @@
       <c r="Z261" s="1"/>
       <c r="AA261" s="1"/>
       <c r="AB261" s="1"/>
-    </row>
-    <row r="262" spans="1:28">
+      <c r="AC261" s="1"/>
+    </row>
+    <row r="262" spans="1:29">
       <c r="A262" s="3">
         <v>259</v>
       </c>
-      <c r="B262" s="28"/>
-      <c r="C262" s="1"/>
+      <c r="B262" s="3"/>
+      <c r="C262" s="21"/>
       <c r="D262" s="1"/>
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
@@ -11231,13 +11683,14 @@
       <c r="Z262" s="1"/>
       <c r="AA262" s="1"/>
       <c r="AB262" s="1"/>
-    </row>
-    <row r="263" spans="1:28">
+      <c r="AC262" s="1"/>
+    </row>
+    <row r="263" spans="1:29">
       <c r="A263" s="3">
         <v>260</v>
       </c>
-      <c r="B263" s="28"/>
-      <c r="C263" s="1"/>
+      <c r="B263" s="3"/>
+      <c r="C263" s="21"/>
       <c r="D263" s="1"/>
       <c r="E263" s="1"/>
       <c r="F263" s="1"/>
@@ -11263,13 +11716,14 @@
       <c r="Z263" s="1"/>
       <c r="AA263" s="1"/>
       <c r="AB263" s="1"/>
-    </row>
-    <row r="264" spans="1:28">
+      <c r="AC263" s="1"/>
+    </row>
+    <row r="264" spans="1:29">
       <c r="A264" s="3">
         <v>261</v>
       </c>
-      <c r="B264" s="28"/>
-      <c r="C264" s="1"/>
+      <c r="B264" s="3"/>
+      <c r="C264" s="21"/>
       <c r="D264" s="1"/>
       <c r="E264" s="1"/>
       <c r="F264" s="1"/>
@@ -11295,13 +11749,14 @@
       <c r="Z264" s="1"/>
       <c r="AA264" s="1"/>
       <c r="AB264" s="1"/>
-    </row>
-    <row r="265" spans="1:28">
+      <c r="AC264" s="1"/>
+    </row>
+    <row r="265" spans="1:29">
       <c r="A265" s="3">
         <v>262</v>
       </c>
-      <c r="B265" s="28"/>
-      <c r="C265" s="1"/>
+      <c r="B265" s="3"/>
+      <c r="C265" s="21"/>
       <c r="D265" s="1"/>
       <c r="E265" s="1"/>
       <c r="F265" s="1"/>
@@ -11327,13 +11782,14 @@
       <c r="Z265" s="1"/>
       <c r="AA265" s="1"/>
       <c r="AB265" s="1"/>
-    </row>
-    <row r="266" spans="1:28">
+      <c r="AC265" s="1"/>
+    </row>
+    <row r="266" spans="1:29">
       <c r="A266" s="3">
         <v>263</v>
       </c>
-      <c r="B266" s="28"/>
-      <c r="C266" s="1"/>
+      <c r="B266" s="3"/>
+      <c r="C266" s="21"/>
       <c r="D266" s="1"/>
       <c r="E266" s="1"/>
       <c r="F266" s="1"/>
@@ -11359,13 +11815,14 @@
       <c r="Z266" s="1"/>
       <c r="AA266" s="1"/>
       <c r="AB266" s="1"/>
-    </row>
-    <row r="267" spans="1:28">
+      <c r="AC266" s="1"/>
+    </row>
+    <row r="267" spans="1:29">
       <c r="A267" s="3">
         <v>264</v>
       </c>
-      <c r="B267" s="28"/>
-      <c r="C267" s="1"/>
+      <c r="B267" s="3"/>
+      <c r="C267" s="21"/>
       <c r="D267" s="1"/>
       <c r="E267" s="1"/>
       <c r="F267" s="1"/>
@@ -11391,13 +11848,14 @@
       <c r="Z267" s="1"/>
       <c r="AA267" s="1"/>
       <c r="AB267" s="1"/>
-    </row>
-    <row r="268" spans="1:28">
+      <c r="AC267" s="1"/>
+    </row>
+    <row r="268" spans="1:29">
       <c r="A268" s="3">
         <v>265</v>
       </c>
-      <c r="B268" s="28"/>
-      <c r="C268" s="1"/>
+      <c r="B268" s="3"/>
+      <c r="C268" s="21"/>
       <c r="D268" s="1"/>
       <c r="E268" s="1"/>
       <c r="F268" s="1"/>
@@ -11423,13 +11881,14 @@
       <c r="Z268" s="1"/>
       <c r="AA268" s="1"/>
       <c r="AB268" s="1"/>
-    </row>
-    <row r="269" spans="1:28">
+      <c r="AC268" s="1"/>
+    </row>
+    <row r="269" spans="1:29">
       <c r="A269" s="3">
         <v>266</v>
       </c>
-      <c r="B269" s="28"/>
-      <c r="C269" s="1"/>
+      <c r="B269" s="3"/>
+      <c r="C269" s="21"/>
       <c r="D269" s="1"/>
       <c r="E269" s="1"/>
       <c r="F269" s="1"/>
@@ -11455,13 +11914,14 @@
       <c r="Z269" s="1"/>
       <c r="AA269" s="1"/>
       <c r="AB269" s="1"/>
-    </row>
-    <row r="270" spans="1:28">
+      <c r="AC269" s="1"/>
+    </row>
+    <row r="270" spans="1:29">
       <c r="A270" s="3">
         <v>267</v>
       </c>
-      <c r="B270" s="28"/>
-      <c r="C270" s="1"/>
+      <c r="B270" s="3"/>
+      <c r="C270" s="21"/>
       <c r="D270" s="1"/>
       <c r="E270" s="1"/>
       <c r="F270" s="1"/>
@@ -11487,13 +11947,14 @@
       <c r="Z270" s="1"/>
       <c r="AA270" s="1"/>
       <c r="AB270" s="1"/>
-    </row>
-    <row r="271" spans="1:28">
+      <c r="AC270" s="1"/>
+    </row>
+    <row r="271" spans="1:29">
       <c r="A271" s="3">
         <v>268</v>
       </c>
-      <c r="B271" s="28"/>
-      <c r="C271" s="1"/>
+      <c r="B271" s="3"/>
+      <c r="C271" s="21"/>
       <c r="D271" s="1"/>
       <c r="E271" s="1"/>
       <c r="F271" s="1"/>
@@ -11519,13 +11980,14 @@
       <c r="Z271" s="1"/>
       <c r="AA271" s="1"/>
       <c r="AB271" s="1"/>
-    </row>
-    <row r="272" spans="1:28">
+      <c r="AC271" s="1"/>
+    </row>
+    <row r="272" spans="1:29">
       <c r="A272" s="3">
         <v>269</v>
       </c>
-      <c r="B272" s="28"/>
-      <c r="C272" s="1"/>
+      <c r="B272" s="3"/>
+      <c r="C272" s="21"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
@@ -11551,13 +12013,14 @@
       <c r="Z272" s="1"/>
       <c r="AA272" s="1"/>
       <c r="AB272" s="1"/>
-    </row>
-    <row r="273" spans="1:28">
+      <c r="AC272" s="1"/>
+    </row>
+    <row r="273" spans="1:29">
       <c r="A273" s="3">
         <v>270</v>
       </c>
-      <c r="B273" s="28"/>
-      <c r="C273" s="1"/>
+      <c r="B273" s="3"/>
+      <c r="C273" s="21"/>
       <c r="D273" s="1"/>
       <c r="E273" s="1"/>
       <c r="F273" s="1"/>
@@ -11583,13 +12046,14 @@
       <c r="Z273" s="1"/>
       <c r="AA273" s="1"/>
       <c r="AB273" s="1"/>
-    </row>
-    <row r="274" spans="1:28">
+      <c r="AC273" s="1"/>
+    </row>
+    <row r="274" spans="1:29">
       <c r="A274" s="3">
         <v>271</v>
       </c>
-      <c r="B274" s="28"/>
-      <c r="C274" s="1"/>
+      <c r="B274" s="3"/>
+      <c r="C274" s="21"/>
       <c r="D274" s="1"/>
       <c r="E274" s="1"/>
       <c r="F274" s="1"/>
@@ -11615,13 +12079,14 @@
       <c r="Z274" s="1"/>
       <c r="AA274" s="1"/>
       <c r="AB274" s="1"/>
-    </row>
-    <row r="275" spans="1:28">
+      <c r="AC274" s="1"/>
+    </row>
+    <row r="275" spans="1:29">
       <c r="A275" s="3">
         <v>272</v>
       </c>
-      <c r="B275" s="28"/>
-      <c r="C275" s="1"/>
+      <c r="B275" s="3"/>
+      <c r="C275" s="21"/>
       <c r="D275" s="1"/>
       <c r="E275" s="1"/>
       <c r="F275" s="1"/>
@@ -11647,13 +12112,14 @@
       <c r="Z275" s="1"/>
       <c r="AA275" s="1"/>
       <c r="AB275" s="1"/>
-    </row>
-    <row r="276" spans="1:28">
+      <c r="AC275" s="1"/>
+    </row>
+    <row r="276" spans="1:29">
       <c r="A276" s="3">
         <v>273</v>
       </c>
-      <c r="B276" s="28"/>
-      <c r="C276" s="1"/>
+      <c r="B276" s="3"/>
+      <c r="C276" s="21"/>
       <c r="D276" s="1"/>
       <c r="E276" s="1"/>
       <c r="F276" s="1"/>
@@ -11679,13 +12145,14 @@
       <c r="Z276" s="1"/>
       <c r="AA276" s="1"/>
       <c r="AB276" s="1"/>
-    </row>
-    <row r="277" spans="1:28">
+      <c r="AC276" s="1"/>
+    </row>
+    <row r="277" spans="1:29">
       <c r="A277" s="3">
         <v>274</v>
       </c>
-      <c r="B277" s="28"/>
-      <c r="C277" s="1"/>
+      <c r="B277" s="3"/>
+      <c r="C277" s="21"/>
       <c r="D277" s="1"/>
       <c r="E277" s="1"/>
       <c r="F277" s="1"/>
@@ -11711,13 +12178,14 @@
       <c r="Z277" s="1"/>
       <c r="AA277" s="1"/>
       <c r="AB277" s="1"/>
-    </row>
-    <row r="278" spans="1:28">
+      <c r="AC277" s="1"/>
+    </row>
+    <row r="278" spans="1:29">
       <c r="A278" s="3">
         <v>275</v>
       </c>
-      <c r="B278" s="28"/>
-      <c r="C278" s="1"/>
+      <c r="B278" s="3"/>
+      <c r="C278" s="21"/>
       <c r="D278" s="1"/>
       <c r="E278" s="1"/>
       <c r="F278" s="1"/>
@@ -11743,13 +12211,14 @@
       <c r="Z278" s="1"/>
       <c r="AA278" s="1"/>
       <c r="AB278" s="1"/>
-    </row>
-    <row r="279" spans="1:28">
+      <c r="AC278" s="1"/>
+    </row>
+    <row r="279" spans="1:29">
       <c r="A279" s="3">
         <v>276</v>
       </c>
-      <c r="B279" s="28"/>
-      <c r="C279" s="1"/>
+      <c r="B279" s="3"/>
+      <c r="C279" s="21"/>
       <c r="D279" s="1"/>
       <c r="E279" s="1"/>
       <c r="F279" s="1"/>
@@ -11775,13 +12244,14 @@
       <c r="Z279" s="1"/>
       <c r="AA279" s="1"/>
       <c r="AB279" s="1"/>
-    </row>
-    <row r="280" spans="1:28">
+      <c r="AC279" s="1"/>
+    </row>
+    <row r="280" spans="1:29">
       <c r="A280" s="3">
         <v>277</v>
       </c>
-      <c r="B280" s="28"/>
-      <c r="C280" s="1"/>
+      <c r="B280" s="3"/>
+      <c r="C280" s="21"/>
       <c r="D280" s="1"/>
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
@@ -11807,20 +12277,26 @@
       <c r="Z280" s="1"/>
       <c r="AA280" s="1"/>
       <c r="AB280" s="1"/>
+      <c r="AC280" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AA230" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="3">
+  <autoFilter ref="A3:AB280" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="18">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
+  <mergeCells count="4">
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="D1:X1"/>
     <mergeCell ref="B1:B3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="C1:W1"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D181:D280 D4:D163 E4:AB280 C4:C280" xr:uid="{C452CDD0-B3A9-419A-AD4E-0E5CE327C346}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E181:E280 E4:E163 F4:AC280 D4:D280 B4:B242" xr:uid="{C452CDD0-B3A9-419A-AD4E-0E5CE327C346}">
       <formula1>"〇,×,△"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D164:D180" xr:uid="{E47C5A29-770A-4FF4-AE4B-E53AB5761727}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E164:E180" xr:uid="{E47C5A29-770A-4FF4-AE4B-E53AB5761727}">
       <formula1>",1,2,3,4,5,6,7,8,9,10,△,×"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11830,45 +12306,45 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8513D353-BD33-4F18-8682-09CF4EA59EE5}">
-  <dimension ref="A2:H170"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <dimension ref="A2:H171"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.649999999999999"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1875" style="16" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.08203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.9140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="6.58203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.8125" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.0625" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.9375" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="6.5625" style="16" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="16"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8">
       <c r="A2" s="14"/>
       <c r="B2" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="D2" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="E2" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="F2" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="H2" s="15" t="s">
         <v>238</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -11880,31 +12356,31 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="19" t="s">
-        <v>123</v>
+        <v>273</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H4" s="18"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -11916,10 +12392,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -11930,10 +12406,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -11944,7 +12420,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
@@ -11956,7 +12432,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
@@ -11968,7 +12444,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -11980,10 +12456,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
@@ -11994,7 +12470,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -12006,7 +12482,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -12018,7 +12494,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -12030,13 +12506,13 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
@@ -12046,13 +12522,13 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D16" s="18"/>
       <c r="E16" s="18"/>
@@ -12062,7 +12538,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
@@ -12074,67 +12550,69 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="19" t="s">
-        <v>138</v>
+        <v>270</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="19" t="s">
-        <v>139</v>
+        <v>272</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>159</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
       <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
+        <v>271</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>158</v>
+      </c>
       <c r="H20" s="18"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="19" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -12146,7 +12624,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="19" t="s">
-        <v>240</v>
+        <v>139</v>
       </c>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -12158,7 +12636,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="19" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -12170,7 +12648,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="19" t="s">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -12182,7 +12660,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="19" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -12193,7 +12671,9 @@
       <c r="H25" s="18"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="19"/>
+      <c r="A26" s="19" t="s">
+        <v>269</v>
+      </c>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
@@ -13642,10 +14122,20 @@
       <c r="G170" s="18"/>
       <c r="H170" s="18"/>
     </row>
+    <row r="171" spans="1:8">
+      <c r="A171" s="19"/>
+      <c r="B171" s="18"/>
+      <c r="C171" s="18"/>
+      <c r="D171" s="18"/>
+      <c r="E171" s="18"/>
+      <c r="F171" s="18"/>
+      <c r="G171" s="18"/>
+      <c r="H171" s="18"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:H170" xr:uid="{4997AC82-12EC-4AE6-8FAD-17E499A10CEB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:H171" xr:uid="{4997AC82-12EC-4AE6-8FAD-17E499A10CEB}">
       <formula1>"〇,×,△"</formula1>
     </dataValidation>
   </dataValidations>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E19D36D-FBC9-48FC-AACD-9636BA1F6C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F7EBA6F-093B-4271-8FBD-E5322D2FFF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="リスト" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="279">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -1499,7 +1499,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1533,6 +1533,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1632,7 +1638,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1696,6 +1702,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1726,11 +1738,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2111,7 +2120,7 @@
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="1" width="3.4375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.4375" style="34" customWidth="1"/>
+    <col min="2" max="2" width="3.4375" style="24" customWidth="1"/>
     <col min="3" max="3" width="33.75" bestFit="1" customWidth="1"/>
     <col min="4" max="9" width="3.5625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="2.5625" bestFit="1" customWidth="1"/>
@@ -2119,41 +2128,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="22.9">
-      <c r="A1" s="26"/>
-      <c r="B1" s="30" t="s">
+      <c r="A1" s="28"/>
+      <c r="B1" s="32" t="s">
         <v>274</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="29"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
     </row>
     <row r="2" spans="1:29" ht="22.9">
-      <c r="A2" s="27"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="24"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="e" vm="1">
         <v>#VALUE!</v>
@@ -2190,9 +2199,9 @@
       <c r="AC2" s="5"/>
     </row>
     <row r="3" spans="1:29" s="13" customFormat="1" ht="90.4" thickBot="1">
-      <c r="A3" s="28"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="25"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="27"/>
       <c r="D3" s="11" t="s">
         <v>123</v>
       </c>
@@ -2270,7 +2279,7 @@
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -2315,7 +2324,7 @@
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -8360,7 +8369,7 @@
       <c r="A174" s="3">
         <v>171</v>
       </c>
-      <c r="B174" s="33" t="s">
+      <c r="B174" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C174" s="6" t="s">
@@ -8405,7 +8414,7 @@
       <c r="A175" s="3">
         <v>172</v>
       </c>
-      <c r="B175" s="33" t="s">
+      <c r="B175" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C175" s="6" t="s">
@@ -8446,7 +8455,7 @@
       <c r="A176" s="3">
         <v>173</v>
       </c>
-      <c r="B176" s="33" t="s">
+      <c r="B176" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C176" s="6" t="s">
@@ -8491,7 +8500,7 @@
       <c r="A177" s="3">
         <v>174</v>
       </c>
-      <c r="B177" s="33" t="s">
+      <c r="B177" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C177" s="6" t="s">
@@ -8530,7 +8539,7 @@
       <c r="A178" s="3">
         <v>175</v>
       </c>
-      <c r="B178" s="33" t="s">
+      <c r="B178" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C178" s="6" t="s">
@@ -8569,7 +8578,7 @@
       <c r="A179" s="3">
         <v>176</v>
       </c>
-      <c r="B179" s="33" t="s">
+      <c r="B179" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C179" s="6" t="s">
@@ -8608,7 +8617,7 @@
       <c r="A180" s="3">
         <v>177</v>
       </c>
-      <c r="B180" s="33" t="s">
+      <c r="B180" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C180" s="6" t="s">
@@ -8649,7 +8658,7 @@
       <c r="A181" s="3">
         <v>178</v>
       </c>
-      <c r="B181" s="33" t="s">
+      <c r="B181" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C181" s="6" t="s">
@@ -8688,7 +8697,7 @@
       <c r="A182" s="3">
         <v>179</v>
       </c>
-      <c r="B182" s="33" t="s">
+      <c r="B182" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C182" s="6" t="s">
@@ -8727,7 +8736,7 @@
       <c r="A183" s="3">
         <v>180</v>
       </c>
-      <c r="B183" s="33" t="s">
+      <c r="B183" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C183" s="6" t="s">
@@ -8768,7 +8777,7 @@
       <c r="A184" s="3">
         <v>181</v>
       </c>
-      <c r="B184" s="33" t="s">
+      <c r="B184" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C184" s="6" t="s">
@@ -8809,7 +8818,7 @@
       <c r="A185" s="3">
         <v>182</v>
       </c>
-      <c r="B185" s="33" t="s">
+      <c r="B185" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C185" s="6" t="s">
@@ -10054,7 +10063,7 @@
       <c r="A216" s="3">
         <v>213</v>
       </c>
-      <c r="B216" s="33" t="s">
+      <c r="B216" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C216" s="6" t="s">
@@ -10093,7 +10102,7 @@
       <c r="A217" s="3">
         <v>214</v>
       </c>
-      <c r="B217" s="33" t="s">
+      <c r="B217" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C217" s="6" t="s">
@@ -10132,7 +10141,7 @@
       <c r="A218" s="3">
         <v>215</v>
       </c>
-      <c r="B218" s="33" t="s">
+      <c r="B218" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C218" s="6" t="s">
@@ -10276,7 +10285,7 @@
       <c r="A222" s="3">
         <v>219</v>
       </c>
-      <c r="B222" s="33" t="s">
+      <c r="B222" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C222" s="6" t="s">
@@ -10663,7 +10672,7 @@
       <c r="A233" s="3">
         <v>230</v>
       </c>
-      <c r="B233" s="33" t="s">
+      <c r="B233" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C233" s="22" t="s">
@@ -12579,9 +12588,13 @@
       <c r="B19" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
+      <c r="C19" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="D19" s="35"/>
+      <c r="E19" s="18" t="s">
+        <v>158</v>
+      </c>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
       <c r="H19" s="18"/>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F7EBA6F-093B-4271-8FBD-E5322D2FFF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122F8A0A-63D3-4F1B-BAA3-E67B953031C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="リスト" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="282">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -201,9 +201,6 @@
   </si>
   <si>
     <t>はっはっは～</t>
-  </si>
-  <si>
-    <t>笑わせるな</t>
   </si>
   <si>
     <t>やるじゃん</t>
@@ -1408,6 +1405,22 @@
   </si>
   <si>
     <t>旅したい</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>失礼する</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>いえ～い</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プレゼント</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>笑わせるな</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2130,13 +2143,13 @@
     <row r="1" spans="1:29" ht="22.9">
       <c r="A1" s="28"/>
       <c r="B1" s="32" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D1" s="31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E1" s="31"/>
       <c r="F1" s="31"/>
@@ -2203,73 +2216,73 @@
       <c r="B3" s="34"/>
       <c r="C3" s="27"/>
       <c r="D3" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="F3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="J3" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="K3" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="L3" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="M3" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="N3" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="O3" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="P3" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="Q3" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="R3" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="R3" s="11" t="s">
+      <c r="S3" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="S3" s="11" t="s">
+      <c r="T3" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="T3" s="11" t="s">
+      <c r="U3" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="V3" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="U3" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>139</v>
-      </c>
       <c r="W3" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="X3" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Y3" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="Z3" s="11" t="s">
         <v>268</v>
-      </c>
-      <c r="Z3" s="11" t="s">
-        <v>269</v>
       </c>
       <c r="AA3" s="11"/>
       <c r="AB3" s="11"/>
@@ -2280,19 +2293,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2302,18 +2315,20 @@
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
+      <c r="X4" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
@@ -2325,19 +2340,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -2347,20 +2362,22 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
+      <c r="X5" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
@@ -2373,14 +2390,14 @@
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -2397,7 +2414,9 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
+      <c r="X6" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
@@ -2467,7 +2486,9 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
+      <c r="X8" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
@@ -2550,14 +2571,14 @@
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -2574,7 +2595,9 @@
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
+      <c r="X11" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
@@ -2819,7 +2842,9 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
-      <c r="X18" s="1"/>
+      <c r="X18" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
@@ -2944,7 +2969,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -3031,7 +3056,9 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
-      <c r="X24" s="1"/>
+      <c r="X24" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
@@ -3066,7 +3093,9 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
+      <c r="X25" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
@@ -3114,7 +3143,7 @@
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -3130,7 +3159,7 @@
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
@@ -3243,7 +3272,9 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
+      <c r="X30" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
@@ -3256,16 +3287,16 @@
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -3276,7 +3307,7 @@
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
@@ -3302,7 +3333,7 @@
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -3566,7 +3597,9 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
-      <c r="X39" s="1"/>
+      <c r="X39" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
@@ -3601,7 +3634,9 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
-      <c r="X40" s="1"/>
+      <c r="X40" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
@@ -3636,7 +3671,9 @@
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
-      <c r="X41" s="1"/>
+      <c r="X41" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
@@ -3706,7 +3743,9 @@
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
-      <c r="X43" s="1"/>
+      <c r="X43" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
@@ -3719,7 +3758,7 @@
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="4" t="s">
-        <v>34</v>
+        <v>281</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -3754,7 +3793,7 @@
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -3789,7 +3828,7 @@
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -3824,7 +3863,7 @@
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -3859,7 +3898,7 @@
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -3881,7 +3920,9 @@
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
-      <c r="X48" s="1"/>
+      <c r="X48" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
@@ -3894,7 +3935,7 @@
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -3929,7 +3970,7 @@
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -3951,7 +3992,9 @@
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
-      <c r="X50" s="1"/>
+      <c r="X50" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
@@ -3964,7 +4007,7 @@
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -3999,7 +4042,7 @@
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -4034,7 +4077,7 @@
       </c>
       <c r="B53" s="1"/>
       <c r="C53" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -4069,7 +4112,7 @@
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -4091,7 +4134,9 @@
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
-      <c r="X54" s="1"/>
+      <c r="X54" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
@@ -4104,7 +4149,7 @@
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -4126,7 +4171,9 @@
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
       <c r="W55" s="1"/>
-      <c r="X55" s="1"/>
+      <c r="X55" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
       <c r="AA55" s="1"/>
@@ -4139,7 +4186,7 @@
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -4174,7 +4221,7 @@
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -4209,7 +4256,7 @@
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -4244,7 +4291,7 @@
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -4279,7 +4326,7 @@
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -4314,7 +4361,7 @@
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -4349,7 +4396,7 @@
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -4384,12 +4431,12 @@
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -4421,7 +4468,7 @@
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -4437,7 +4484,7 @@
       <c r="O64" s="1"/>
       <c r="P64" s="1"/>
       <c r="Q64" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
@@ -4445,7 +4492,9 @@
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
       <c r="W64" s="1"/>
-      <c r="X64" s="1"/>
+      <c r="X64" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
       <c r="AA64" s="1"/>
@@ -4458,7 +4507,7 @@
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -4480,7 +4529,9 @@
       <c r="U65" s="1"/>
       <c r="V65" s="1"/>
       <c r="W65" s="1"/>
-      <c r="X65" s="1"/>
+      <c r="X65" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
       <c r="AA65" s="1"/>
@@ -4493,7 +4544,7 @@
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -4528,12 +4579,12 @@
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -4552,7 +4603,9 @@
       <c r="U67" s="1"/>
       <c r="V67" s="1"/>
       <c r="W67" s="1"/>
-      <c r="X67" s="1"/>
+      <c r="X67" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
       <c r="AA67" s="1"/>
@@ -4565,12 +4618,12 @@
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -4602,7 +4655,7 @@
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -4618,7 +4671,7 @@
       <c r="O69" s="1"/>
       <c r="P69" s="1"/>
       <c r="Q69" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
@@ -4626,7 +4679,9 @@
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
       <c r="W69" s="1"/>
-      <c r="X69" s="1"/>
+      <c r="X69" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
       <c r="AA69" s="1"/>
@@ -4639,12 +4694,12 @@
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -4676,12 +4731,12 @@
       </c>
       <c r="B71" s="1"/>
       <c r="C71" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
@@ -4713,7 +4768,7 @@
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -4748,7 +4803,7 @@
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -4783,7 +4838,7 @@
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -4818,7 +4873,7 @@
       </c>
       <c r="B75" s="1"/>
       <c r="C75" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -4853,12 +4908,12 @@
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
@@ -4873,7 +4928,7 @@
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
       <c r="S76" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
@@ -4892,7 +4947,7 @@
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -4910,7 +4965,7 @@
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
       <c r="S77" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T77" s="1"/>
       <c r="U77" s="1"/>
@@ -4929,7 +4984,7 @@
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -4947,7 +5002,7 @@
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
       <c r="S78" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
@@ -4966,7 +5021,7 @@
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
@@ -4984,7 +5039,7 @@
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
       <c r="S79" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T79" s="1"/>
       <c r="U79" s="1"/>
@@ -5003,7 +5058,7 @@
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -5021,7 +5076,7 @@
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
       <c r="S80" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T80" s="1"/>
       <c r="U80" s="1"/>
@@ -5040,12 +5095,12 @@
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
@@ -5060,7 +5115,7 @@
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
       <c r="S81" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T81" s="1"/>
       <c r="U81" s="1"/>
@@ -5079,7 +5134,7 @@
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -5095,11 +5150,11 @@
       <c r="O82" s="1"/>
       <c r="P82" s="1"/>
       <c r="Q82" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R82" s="1"/>
       <c r="S82" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T82" s="1"/>
       <c r="U82" s="1"/>
@@ -5118,7 +5173,7 @@
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -5136,10 +5191,10 @@
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
       <c r="S83" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
@@ -5157,7 +5212,7 @@
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -5175,7 +5230,7 @@
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
       <c r="S84" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T84" s="1"/>
       <c r="U84" s="1"/>
@@ -5194,7 +5249,7 @@
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -5229,7 +5284,7 @@
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
@@ -5264,7 +5319,7 @@
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
@@ -5299,7 +5354,7 @@
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
@@ -5315,7 +5370,7 @@
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
@@ -5336,7 +5391,7 @@
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
@@ -5371,7 +5426,7 @@
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
@@ -5406,7 +5461,7 @@
       </c>
       <c r="B91" s="1"/>
       <c r="C91" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
@@ -5422,7 +5477,7 @@
       <c r="O91" s="1"/>
       <c r="P91" s="1"/>
       <c r="Q91" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
@@ -5443,12 +5498,12 @@
       </c>
       <c r="B92" s="1"/>
       <c r="C92" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
@@ -5480,7 +5535,7 @@
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
@@ -5515,7 +5570,7 @@
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
@@ -5550,7 +5605,7 @@
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
@@ -5585,7 +5640,7 @@
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
@@ -5620,7 +5675,7 @@
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
@@ -5655,14 +5710,14 @@
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
@@ -5727,7 +5782,7 @@
       </c>
       <c r="B100" s="1"/>
       <c r="C100" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
@@ -5762,7 +5817,7 @@
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
@@ -5797,7 +5852,7 @@
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
@@ -5832,7 +5887,7 @@
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
@@ -5867,7 +5922,7 @@
       </c>
       <c r="B104" s="1"/>
       <c r="C104" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
@@ -5902,7 +5957,7 @@
       </c>
       <c r="B105" s="1"/>
       <c r="C105" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
@@ -5924,7 +5979,9 @@
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
       <c r="W105" s="1"/>
-      <c r="X105" s="1"/>
+      <c r="X105" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
       <c r="AA105" s="1"/>
@@ -5937,7 +5994,7 @@
       </c>
       <c r="B106" s="1"/>
       <c r="C106" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
@@ -5972,7 +6029,7 @@
       </c>
       <c r="B107" s="1"/>
       <c r="C107" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
@@ -5994,7 +6051,9 @@
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
       <c r="W107" s="1"/>
-      <c r="X107" s="1"/>
+      <c r="X107" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
       <c r="AA107" s="1"/>
@@ -6007,7 +6066,7 @@
       </c>
       <c r="B108" s="1"/>
       <c r="C108" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
@@ -6042,7 +6101,7 @@
       </c>
       <c r="B109" s="1"/>
       <c r="C109" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
@@ -6064,7 +6123,9 @@
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
       <c r="W109" s="1"/>
-      <c r="X109" s="1"/>
+      <c r="X109" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
       <c r="AA109" s="1"/>
@@ -6077,7 +6138,7 @@
       </c>
       <c r="B110" s="1"/>
       <c r="C110" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
@@ -6112,7 +6173,7 @@
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
@@ -6147,12 +6208,12 @@
       </c>
       <c r="B112" s="1"/>
       <c r="C112" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
       <c r="F112" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G112" s="1"/>
       <c r="H112" s="1"/>
@@ -6165,7 +6226,7 @@
       <c r="O112" s="1"/>
       <c r="P112" s="1"/>
       <c r="Q112" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R112" s="1"/>
       <c r="S112" s="1"/>
@@ -6173,7 +6234,9 @@
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
       <c r="W112" s="1"/>
-      <c r="X112" s="1"/>
+      <c r="X112" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
       <c r="AA112" s="1"/>
@@ -6186,7 +6249,7 @@
       </c>
       <c r="B113" s="1"/>
       <c r="C113" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
@@ -6202,7 +6265,7 @@
       <c r="O113" s="1"/>
       <c r="P113" s="1"/>
       <c r="Q113" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R113" s="1"/>
       <c r="S113" s="1"/>
@@ -6258,12 +6321,12 @@
       </c>
       <c r="B115" s="1"/>
       <c r="C115" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="1"/>
@@ -6295,7 +6358,7 @@
       </c>
       <c r="B116" s="1"/>
       <c r="C116" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
@@ -6330,7 +6393,7 @@
       </c>
       <c r="B117" s="1"/>
       <c r="C117" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
@@ -6365,7 +6428,7 @@
       </c>
       <c r="B118" s="1"/>
       <c r="C118" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
@@ -6400,7 +6463,7 @@
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
@@ -6435,7 +6498,7 @@
       </c>
       <c r="B120" s="1"/>
       <c r="C120" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
@@ -6470,7 +6533,7 @@
       </c>
       <c r="B121" s="1"/>
       <c r="C121" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
@@ -6505,7 +6568,7 @@
       </c>
       <c r="B122" s="1"/>
       <c r="C122" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
@@ -6540,7 +6603,7 @@
       </c>
       <c r="B123" s="1"/>
       <c r="C123" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
@@ -6575,7 +6638,7 @@
       </c>
       <c r="B124" s="1"/>
       <c r="C124" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
@@ -6610,7 +6673,7 @@
       </c>
       <c r="B125" s="1"/>
       <c r="C125" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
@@ -6645,7 +6708,7 @@
       </c>
       <c r="B126" s="1"/>
       <c r="C126" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
@@ -6661,7 +6724,7 @@
       <c r="O126" s="1"/>
       <c r="P126" s="1"/>
       <c r="Q126" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R126" s="1"/>
       <c r="S126" s="1"/>
@@ -6682,7 +6745,7 @@
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
@@ -6717,7 +6780,7 @@
       </c>
       <c r="B128" s="1"/>
       <c r="C128" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
@@ -6733,7 +6796,7 @@
       <c r="O128" s="1"/>
       <c r="P128" s="1"/>
       <c r="Q128" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R128" s="1"/>
       <c r="S128" s="1"/>
@@ -6741,7 +6804,9 @@
       <c r="U128" s="1"/>
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
-      <c r="X128" s="1"/>
+      <c r="X128" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
       <c r="AA128" s="1"/>
@@ -6754,7 +6819,7 @@
       </c>
       <c r="B129" s="1"/>
       <c r="C129" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
@@ -6772,7 +6837,7 @@
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
       <c r="S129" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T129" s="1"/>
       <c r="U129" s="1"/>
@@ -6791,7 +6856,7 @@
       </c>
       <c r="B130" s="1"/>
       <c r="C130" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
@@ -6807,7 +6872,7 @@
       <c r="O130" s="1"/>
       <c r="P130" s="1"/>
       <c r="Q130" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
@@ -6815,7 +6880,9 @@
       <c r="U130" s="1"/>
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
-      <c r="X130" s="1"/>
+      <c r="X130" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
       <c r="AA130" s="1"/>
@@ -6828,7 +6895,7 @@
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
@@ -6850,7 +6917,9 @@
       <c r="U131" s="1"/>
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
-      <c r="X131" s="1"/>
+      <c r="X131" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
       <c r="AA131" s="1"/>
@@ -6863,7 +6932,7 @@
       </c>
       <c r="B132" s="1"/>
       <c r="C132" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
@@ -6898,7 +6967,7 @@
       </c>
       <c r="B133" s="1"/>
       <c r="C133" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
@@ -6933,7 +7002,7 @@
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
@@ -6968,7 +7037,7 @@
       </c>
       <c r="B135" s="1"/>
       <c r="C135" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
@@ -7003,7 +7072,7 @@
       </c>
       <c r="B136" s="1"/>
       <c r="C136" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
@@ -7038,7 +7107,7 @@
       </c>
       <c r="B137" s="1"/>
       <c r="C137" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
@@ -7073,7 +7142,7 @@
       </c>
       <c r="B138" s="1"/>
       <c r="C138" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -7108,7 +7177,7 @@
       </c>
       <c r="B139" s="1"/>
       <c r="C139" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
@@ -7143,7 +7212,7 @@
       </c>
       <c r="B140" s="1"/>
       <c r="C140" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
@@ -7178,7 +7247,7 @@
       </c>
       <c r="B141" s="1"/>
       <c r="C141" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
@@ -7213,7 +7282,7 @@
       </c>
       <c r="B142" s="1"/>
       <c r="C142" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
@@ -7248,7 +7317,7 @@
       </c>
       <c r="B143" s="1"/>
       <c r="C143" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
@@ -7283,7 +7352,7 @@
       </c>
       <c r="B144" s="1"/>
       <c r="C144" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
@@ -7318,7 +7387,7 @@
       </c>
       <c r="B145" s="1"/>
       <c r="C145" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
@@ -7353,7 +7422,7 @@
       </c>
       <c r="B146" s="1"/>
       <c r="C146" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
@@ -7388,7 +7457,7 @@
       </c>
       <c r="B147" s="1"/>
       <c r="C147" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
@@ -7423,7 +7492,7 @@
       </c>
       <c r="B148" s="1"/>
       <c r="C148" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
@@ -7439,7 +7508,7 @@
       <c r="O148" s="1"/>
       <c r="P148" s="1"/>
       <c r="Q148" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
@@ -7460,7 +7529,7 @@
       </c>
       <c r="B149" s="1"/>
       <c r="C149" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
@@ -7495,7 +7564,7 @@
       </c>
       <c r="B150" s="1"/>
       <c r="C150" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
@@ -7530,7 +7599,7 @@
       </c>
       <c r="B151" s="1"/>
       <c r="C151" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
@@ -7565,7 +7634,7 @@
       </c>
       <c r="B152" s="1"/>
       <c r="C152" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
@@ -7600,11 +7669,11 @@
       </c>
       <c r="B153" s="1"/>
       <c r="C153" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D153" s="1"/>
       <c r="E153" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F153" s="1"/>
       <c r="G153" s="1"/>
@@ -7637,11 +7706,11 @@
       </c>
       <c r="B154" s="1"/>
       <c r="C154" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D154" s="1"/>
       <c r="E154" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F154" s="1"/>
       <c r="G154" s="1"/>
@@ -7674,11 +7743,11 @@
       </c>
       <c r="B155" s="1"/>
       <c r="C155" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D155" s="1"/>
       <c r="E155" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
@@ -7692,7 +7761,7 @@
       <c r="O155" s="1"/>
       <c r="P155" s="1"/>
       <c r="Q155" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R155" s="1"/>
       <c r="S155" s="1"/>
@@ -7713,11 +7782,11 @@
       </c>
       <c r="B156" s="1"/>
       <c r="C156" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D156" s="1"/>
       <c r="E156" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
@@ -7750,11 +7819,11 @@
       </c>
       <c r="B157" s="1"/>
       <c r="C157" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D157" s="1"/>
       <c r="E157" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F157" s="1"/>
       <c r="G157" s="1"/>
@@ -7787,14 +7856,14 @@
       </c>
       <c r="B158" s="1"/>
       <c r="C158" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D158" s="1"/>
       <c r="E158" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
@@ -7826,11 +7895,11 @@
       </c>
       <c r="B159" s="1"/>
       <c r="C159" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D159" s="1"/>
       <c r="E159" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="1"/>
@@ -7863,11 +7932,11 @@
       </c>
       <c r="B160" s="1"/>
       <c r="C160" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D160" s="1"/>
       <c r="E160" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F160" s="1"/>
       <c r="G160" s="1"/>
@@ -7883,7 +7952,7 @@
       <c r="Q160" s="1"/>
       <c r="R160" s="1"/>
       <c r="S160" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T160" s="1"/>
       <c r="U160" s="1"/>
@@ -7902,11 +7971,11 @@
       </c>
       <c r="B161" s="1"/>
       <c r="C161" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D161" s="1"/>
       <c r="E161" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F161" s="1"/>
       <c r="G161" s="1"/>
@@ -7939,11 +8008,11 @@
       </c>
       <c r="B162" s="1"/>
       <c r="C162" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D162" s="1"/>
       <c r="E162" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F162" s="1"/>
       <c r="G162" s="1"/>
@@ -7976,11 +8045,11 @@
       </c>
       <c r="B163" s="1"/>
       <c r="C163" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D163" s="1"/>
       <c r="E163" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F163" s="1"/>
       <c r="G163" s="1"/>
@@ -7993,7 +8062,7 @@
       <c r="N163" s="1"/>
       <c r="O163" s="1"/>
       <c r="P163" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
@@ -8015,7 +8084,7 @@
       </c>
       <c r="B164" s="1"/>
       <c r="C164" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D164" s="3"/>
       <c r="E164" s="8"/>
@@ -8030,7 +8099,7 @@
       <c r="N164" s="3"/>
       <c r="O164" s="3"/>
       <c r="P164" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q164" s="3"/>
       <c r="R164" s="3"/>
@@ -8052,7 +8121,7 @@
       </c>
       <c r="B165" s="1"/>
       <c r="C165" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D165" s="3"/>
       <c r="E165" s="8"/>
@@ -8070,7 +8139,7 @@
       <c r="Q165" s="3"/>
       <c r="R165" s="3"/>
       <c r="S165" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T165" s="1"/>
       <c r="U165" s="1"/>
@@ -8089,7 +8158,7 @@
       </c>
       <c r="B166" s="1"/>
       <c r="C166" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D166" s="1"/>
       <c r="E166" s="8"/>
@@ -8124,7 +8193,7 @@
       </c>
       <c r="B167" s="1"/>
       <c r="C167" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D167" s="1"/>
       <c r="E167" s="8"/>
@@ -8159,7 +8228,7 @@
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D168" s="1"/>
       <c r="E168" s="8"/>
@@ -8194,7 +8263,7 @@
       </c>
       <c r="B169" s="1"/>
       <c r="C169" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D169" s="1"/>
       <c r="E169" s="8"/>
@@ -8229,7 +8298,7 @@
       </c>
       <c r="B170" s="1"/>
       <c r="C170" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D170" s="1"/>
       <c r="E170" s="8"/>
@@ -8264,7 +8333,7 @@
       </c>
       <c r="B171" s="1"/>
       <c r="C171" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D171" s="1"/>
       <c r="E171" s="8"/>
@@ -8299,7 +8368,7 @@
       </c>
       <c r="B172" s="1"/>
       <c r="C172" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D172" s="1"/>
       <c r="E172" s="8"/>
@@ -8314,7 +8383,7 @@
       <c r="N172" s="1"/>
       <c r="O172" s="1"/>
       <c r="P172" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
@@ -8336,7 +8405,7 @@
       </c>
       <c r="B173" s="1"/>
       <c r="C173" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D173" s="1"/>
       <c r="E173" s="8"/>
@@ -8370,15 +8439,15 @@
         <v>171</v>
       </c>
       <c r="B174" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D174" s="1"/>
       <c r="E174" s="8"/>
       <c r="F174" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G174" s="1"/>
       <c r="H174" s="1"/>
@@ -8390,14 +8459,14 @@
       <c r="N174" s="1"/>
       <c r="O174" s="1"/>
       <c r="P174" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q174" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R174" s="1"/>
       <c r="S174" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T174" s="1"/>
       <c r="U174" s="1"/>
@@ -8415,15 +8484,15 @@
         <v>172</v>
       </c>
       <c r="B175" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D175" s="1"/>
       <c r="E175" s="8"/>
       <c r="F175" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G175" s="1"/>
       <c r="H175" s="1"/>
@@ -8438,7 +8507,7 @@
       <c r="Q175" s="1"/>
       <c r="R175" s="1"/>
       <c r="S175" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T175" s="1"/>
       <c r="U175" s="1"/>
@@ -8456,15 +8525,15 @@
         <v>173</v>
       </c>
       <c r="B176" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D176" s="1"/>
       <c r="E176" s="8"/>
       <c r="F176" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
@@ -8476,14 +8545,14 @@
       <c r="N176" s="1"/>
       <c r="O176" s="1"/>
       <c r="P176" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q176" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R176" s="1"/>
       <c r="S176" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T176" s="1"/>
       <c r="U176" s="1"/>
@@ -8501,10 +8570,10 @@
         <v>174</v>
       </c>
       <c r="B177" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D177" s="1"/>
       <c r="E177" s="8"/>
@@ -8522,7 +8591,7 @@
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
       <c r="S177" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T177" s="1"/>
       <c r="U177" s="1"/>
@@ -8540,10 +8609,10 @@
         <v>175</v>
       </c>
       <c r="B178" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D178" s="1"/>
       <c r="E178" s="8"/>
@@ -8561,7 +8630,7 @@
       <c r="Q178" s="1"/>
       <c r="R178" s="1"/>
       <c r="S178" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T178" s="1"/>
       <c r="U178" s="1"/>
@@ -8579,10 +8648,10 @@
         <v>176</v>
       </c>
       <c r="B179" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D179" s="1"/>
       <c r="E179" s="8"/>
@@ -8600,7 +8669,7 @@
       <c r="Q179" s="1"/>
       <c r="R179" s="1"/>
       <c r="S179" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T179" s="1"/>
       <c r="U179" s="1"/>
@@ -8618,10 +8687,10 @@
         <v>177</v>
       </c>
       <c r="B180" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D180" s="1"/>
       <c r="E180" s="8"/>
@@ -8636,12 +8705,12 @@
       <c r="N180" s="1"/>
       <c r="O180" s="1"/>
       <c r="P180" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q180" s="1"/>
       <c r="R180" s="1"/>
       <c r="S180" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T180" s="1"/>
       <c r="U180" s="1"/>
@@ -8659,10 +8728,10 @@
         <v>178</v>
       </c>
       <c r="B181" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D181" s="1"/>
       <c r="E181" s="1"/>
@@ -8680,7 +8749,7 @@
       <c r="Q181" s="1"/>
       <c r="R181" s="1"/>
       <c r="S181" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T181" s="1"/>
       <c r="U181" s="1"/>
@@ -8698,10 +8767,10 @@
         <v>179</v>
       </c>
       <c r="B182" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
@@ -8719,13 +8788,15 @@
       <c r="Q182" s="1"/>
       <c r="R182" s="1"/>
       <c r="S182" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T182" s="1"/>
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
       <c r="W182" s="1"/>
-      <c r="X182" s="1"/>
+      <c r="X182" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
       <c r="AA182" s="1"/>
@@ -8737,10 +8808,10 @@
         <v>180</v>
       </c>
       <c r="B183" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
@@ -8755,18 +8826,20 @@
       <c r="N183" s="1"/>
       <c r="O183" s="1"/>
       <c r="P183" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q183" s="1"/>
       <c r="R183" s="1"/>
       <c r="S183" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T183" s="1"/>
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
       <c r="W183" s="1"/>
-      <c r="X183" s="1"/>
+      <c r="X183" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y183" s="1"/>
       <c r="Z183" s="1"/>
       <c r="AA183" s="1"/>
@@ -8778,10 +8851,10 @@
         <v>181</v>
       </c>
       <c r="B184" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
@@ -8796,18 +8869,20 @@
       <c r="N184" s="1"/>
       <c r="O184" s="1"/>
       <c r="P184" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q184" s="1"/>
       <c r="R184" s="1"/>
       <c r="S184" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T184" s="1"/>
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
       <c r="W184" s="1"/>
-      <c r="X184" s="1"/>
+      <c r="X184" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
       <c r="AA184" s="1"/>
@@ -8819,10 +8894,10 @@
         <v>182</v>
       </c>
       <c r="B185" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D185" s="1"/>
       <c r="E185" s="1"/>
@@ -8837,12 +8912,12 @@
       <c r="N185" s="1"/>
       <c r="O185" s="1"/>
       <c r="P185" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q185" s="1"/>
       <c r="R185" s="1"/>
       <c r="S185" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T185" s="1"/>
       <c r="U185" s="1"/>
@@ -8861,7 +8936,7 @@
       </c>
       <c r="B186" s="1"/>
       <c r="C186" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D186" s="1"/>
       <c r="E186" s="1"/>
@@ -8882,28 +8957,28 @@
       <c r="T186" s="1"/>
       <c r="U186" s="1"/>
       <c r="V186" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="W186" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="X186" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Y186" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Z186" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AA186" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AB186" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AC186" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="187" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
@@ -8912,7 +8987,7 @@
       </c>
       <c r="B187" s="1"/>
       <c r="C187" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
@@ -8933,28 +9008,28 @@
       <c r="T187" s="1"/>
       <c r="U187" s="1"/>
       <c r="V187" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="W187" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="X187" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Y187" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Z187" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AA187" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AB187" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AC187" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="188" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
@@ -8963,7 +9038,7 @@
       </c>
       <c r="B188" s="1"/>
       <c r="C188" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
@@ -8978,7 +9053,7 @@
       <c r="N188" s="1"/>
       <c r="O188" s="1"/>
       <c r="P188" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
@@ -8986,28 +9061,28 @@
       <c r="T188" s="1"/>
       <c r="U188" s="1"/>
       <c r="V188" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="W188" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="X188" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Y188" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Z188" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AA188" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AB188" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AC188" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="189" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
@@ -9016,7 +9091,7 @@
       </c>
       <c r="B189" s="1"/>
       <c r="C189" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
@@ -9037,28 +9112,28 @@
       <c r="T189" s="1"/>
       <c r="U189" s="1"/>
       <c r="V189" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="W189" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="X189" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Y189" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Z189" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AA189" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AB189" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AC189" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="190" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
@@ -9067,7 +9142,7 @@
       </c>
       <c r="B190" s="1"/>
       <c r="C190" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
@@ -9088,28 +9163,28 @@
       <c r="T190" s="1"/>
       <c r="U190" s="1"/>
       <c r="V190" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="W190" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="X190" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Y190" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Z190" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AA190" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AB190" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AC190" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="191" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
@@ -9118,7 +9193,7 @@
       </c>
       <c r="B191" s="1"/>
       <c r="C191" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
@@ -9139,28 +9214,28 @@
       <c r="T191" s="1"/>
       <c r="U191" s="1"/>
       <c r="V191" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="W191" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="X191" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Y191" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Z191" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AA191" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AB191" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AC191" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="192" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
@@ -9169,7 +9244,7 @@
       </c>
       <c r="B192" s="1"/>
       <c r="C192" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
@@ -9187,10 +9262,10 @@
       <c r="Q192" s="1"/>
       <c r="R192" s="1"/>
       <c r="S192" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T192" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
@@ -9208,7 +9283,7 @@
       </c>
       <c r="B193" s="1"/>
       <c r="C193" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
@@ -9223,13 +9298,13 @@
       <c r="N193" s="1"/>
       <c r="O193" s="1"/>
       <c r="P193" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
       <c r="S193" s="1"/>
       <c r="T193" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
@@ -9247,7 +9322,7 @@
       </c>
       <c r="B194" s="1"/>
       <c r="C194" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
@@ -9266,7 +9341,7 @@
       <c r="R194" s="1"/>
       <c r="S194" s="1"/>
       <c r="T194" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
@@ -9284,7 +9359,7 @@
       </c>
       <c r="B195" s="1"/>
       <c r="C195" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
@@ -9303,7 +9378,7 @@
       <c r="R195" s="1"/>
       <c r="S195" s="1"/>
       <c r="T195" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
@@ -9321,7 +9396,7 @@
       </c>
       <c r="B196" s="1"/>
       <c r="C196" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
@@ -9340,7 +9415,7 @@
       <c r="R196" s="1"/>
       <c r="S196" s="1"/>
       <c r="T196" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
@@ -9358,7 +9433,7 @@
       </c>
       <c r="B197" s="1"/>
       <c r="C197" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
@@ -9377,7 +9452,7 @@
       <c r="R197" s="1"/>
       <c r="S197" s="1"/>
       <c r="T197" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
@@ -9395,7 +9470,7 @@
       </c>
       <c r="B198" s="1"/>
       <c r="C198" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
@@ -9414,12 +9489,14 @@
       <c r="R198" s="1"/>
       <c r="S198" s="1"/>
       <c r="T198" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
       <c r="W198" s="1"/>
-      <c r="X198" s="1"/>
+      <c r="X198" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
       <c r="AA198" s="1"/>
@@ -9432,7 +9509,7 @@
       </c>
       <c r="B199" s="1"/>
       <c r="C199" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
@@ -9451,12 +9528,14 @@
       <c r="R199" s="1"/>
       <c r="S199" s="1"/>
       <c r="T199" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
       <c r="W199" s="1"/>
-      <c r="X199" s="1"/>
+      <c r="X199" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y199" s="1"/>
       <c r="Z199" s="1"/>
       <c r="AA199" s="1"/>
@@ -9469,7 +9548,7 @@
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
@@ -9488,7 +9567,7 @@
       <c r="R200" s="1"/>
       <c r="S200" s="1"/>
       <c r="T200" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
@@ -9506,7 +9585,7 @@
       </c>
       <c r="B201" s="1"/>
       <c r="C201" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
@@ -9525,12 +9604,14 @@
       <c r="R201" s="1"/>
       <c r="S201" s="1"/>
       <c r="T201" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U201" s="1"/>
       <c r="V201" s="1"/>
       <c r="W201" s="1"/>
-      <c r="X201" s="1"/>
+      <c r="X201" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
       <c r="AA201" s="1"/>
@@ -9543,7 +9624,7 @@
       </c>
       <c r="B202" s="1"/>
       <c r="C202" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
@@ -9562,7 +9643,7 @@
       <c r="R202" s="1"/>
       <c r="S202" s="1"/>
       <c r="T202" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U202" s="1"/>
       <c r="V202" s="1"/>
@@ -9580,7 +9661,7 @@
       </c>
       <c r="B203" s="1"/>
       <c r="C203" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
@@ -9595,13 +9676,13 @@
       <c r="N203" s="1"/>
       <c r="O203" s="1"/>
       <c r="P203" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q203" s="1"/>
       <c r="R203" s="1"/>
       <c r="S203" s="1"/>
       <c r="T203" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U203" s="1"/>
       <c r="V203" s="1"/>
@@ -9619,7 +9700,7 @@
       </c>
       <c r="B204" s="1"/>
       <c r="C204" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
@@ -9638,7 +9719,7 @@
       <c r="R204" s="1"/>
       <c r="S204" s="1"/>
       <c r="T204" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U204" s="1"/>
       <c r="V204" s="1"/>
@@ -9656,7 +9737,7 @@
       </c>
       <c r="B205" s="1"/>
       <c r="C205" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
@@ -9675,7 +9756,7 @@
       <c r="R205" s="1"/>
       <c r="S205" s="1"/>
       <c r="T205" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U205" s="1"/>
       <c r="V205" s="1"/>
@@ -9693,7 +9774,7 @@
       </c>
       <c r="B206" s="1"/>
       <c r="C206" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
@@ -9712,7 +9793,7 @@
       <c r="R206" s="1"/>
       <c r="S206" s="1"/>
       <c r="T206" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U206" s="1"/>
       <c r="V206" s="1"/>
@@ -9730,7 +9811,7 @@
       </c>
       <c r="B207" s="1"/>
       <c r="C207" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
@@ -9745,13 +9826,13 @@
       <c r="N207" s="1"/>
       <c r="O207" s="1"/>
       <c r="P207" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q207" s="1"/>
       <c r="R207" s="1"/>
       <c r="S207" s="1"/>
       <c r="T207" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U207" s="1"/>
       <c r="V207" s="1"/>
@@ -9769,7 +9850,7 @@
       </c>
       <c r="B208" s="1"/>
       <c r="C208" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
@@ -9788,7 +9869,7 @@
       <c r="R208" s="1"/>
       <c r="S208" s="1"/>
       <c r="T208" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U208" s="1"/>
       <c r="V208" s="1"/>
@@ -9806,7 +9887,7 @@
       </c>
       <c r="B209" s="1"/>
       <c r="C209" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
@@ -9825,7 +9906,7 @@
       <c r="R209" s="1"/>
       <c r="S209" s="1"/>
       <c r="T209" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U209" s="1"/>
       <c r="V209" s="1"/>
@@ -9843,7 +9924,7 @@
       </c>
       <c r="B210" s="1"/>
       <c r="C210" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
@@ -9862,7 +9943,7 @@
       <c r="R210" s="1"/>
       <c r="S210" s="1"/>
       <c r="T210" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U210" s="1"/>
       <c r="V210" s="1"/>
@@ -9880,7 +9961,7 @@
       </c>
       <c r="B211" s="1"/>
       <c r="C211" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
@@ -9899,7 +9980,7 @@
       <c r="R211" s="1"/>
       <c r="S211" s="1"/>
       <c r="T211" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
@@ -9917,7 +9998,7 @@
       </c>
       <c r="B212" s="1"/>
       <c r="C212" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
@@ -9936,7 +10017,7 @@
       <c r="R212" s="1"/>
       <c r="S212" s="1"/>
       <c r="T212" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
@@ -9954,7 +10035,7 @@
       </c>
       <c r="B213" s="1"/>
       <c r="C213" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
@@ -9973,7 +10054,7 @@
       <c r="R213" s="1"/>
       <c r="S213" s="1"/>
       <c r="T213" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
@@ -9991,7 +10072,7 @@
       </c>
       <c r="B214" s="1"/>
       <c r="C214" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
@@ -10010,7 +10091,7 @@
       <c r="R214" s="1"/>
       <c r="S214" s="1"/>
       <c r="T214" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U214" s="1"/>
       <c r="V214" s="1"/>
@@ -10028,7 +10109,7 @@
       </c>
       <c r="B215" s="1"/>
       <c r="C215" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
@@ -10043,7 +10124,7 @@
       <c r="N215" s="1"/>
       <c r="O215" s="1"/>
       <c r="P215" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q215" s="1"/>
       <c r="R215" s="1"/>
@@ -10064,10 +10145,10 @@
         <v>213</v>
       </c>
       <c r="B216" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
@@ -10086,12 +10167,14 @@
       <c r="R216" s="1"/>
       <c r="S216" s="1"/>
       <c r="T216" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U216" s="1"/>
       <c r="V216" s="1"/>
       <c r="W216" s="1"/>
-      <c r="X216" s="1"/>
+      <c r="X216" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y216" s="1"/>
       <c r="Z216" s="1"/>
       <c r="AA216" s="1"/>
@@ -10103,10 +10186,10 @@
         <v>214</v>
       </c>
       <c r="B217" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
@@ -10125,12 +10208,14 @@
       <c r="R217" s="1"/>
       <c r="S217" s="1"/>
       <c r="T217" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U217" s="1"/>
       <c r="V217" s="1"/>
       <c r="W217" s="1"/>
-      <c r="X217" s="1"/>
+      <c r="X217" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y217" s="1"/>
       <c r="Z217" s="1"/>
       <c r="AA217" s="1"/>
@@ -10142,10 +10227,10 @@
         <v>215</v>
       </c>
       <c r="B218" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
@@ -10164,12 +10249,14 @@
       <c r="R218" s="1"/>
       <c r="S218" s="1"/>
       <c r="T218" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U218" s="1"/>
       <c r="V218" s="1"/>
       <c r="W218" s="1"/>
-      <c r="X218" s="1"/>
+      <c r="X218" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y218" s="1"/>
       <c r="Z218" s="1"/>
       <c r="AA218" s="1"/>
@@ -10182,7 +10269,7 @@
       </c>
       <c r="B219" s="1"/>
       <c r="C219" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
@@ -10217,7 +10304,7 @@
       </c>
       <c r="B220" s="1"/>
       <c r="C220" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
@@ -10252,7 +10339,7 @@
       </c>
       <c r="B221" s="1"/>
       <c r="C221" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
@@ -10286,10 +10373,10 @@
         <v>219</v>
       </c>
       <c r="B222" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
@@ -10324,7 +10411,7 @@
       </c>
       <c r="B223" s="1"/>
       <c r="C223" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
@@ -10359,7 +10446,7 @@
       </c>
       <c r="B224" s="1"/>
       <c r="C224" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
@@ -10394,7 +10481,7 @@
       </c>
       <c r="B225" s="1"/>
       <c r="C225" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
@@ -10429,7 +10516,7 @@
       </c>
       <c r="B226" s="1"/>
       <c r="C226" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
@@ -10464,7 +10551,7 @@
       </c>
       <c r="B227" s="1"/>
       <c r="C227" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
@@ -10499,7 +10586,7 @@
       </c>
       <c r="B228" s="1"/>
       <c r="C228" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
@@ -10534,7 +10621,7 @@
       </c>
       <c r="B229" s="1"/>
       <c r="C229" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
@@ -10569,7 +10656,7 @@
       </c>
       <c r="B230" s="1"/>
       <c r="C230" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
@@ -10604,7 +10691,7 @@
       </c>
       <c r="B231" s="1"/>
       <c r="C231" s="21" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
@@ -10639,7 +10726,7 @@
       </c>
       <c r="B232" s="1"/>
       <c r="C232" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
@@ -10673,10 +10760,10 @@
         <v>230</v>
       </c>
       <c r="B233" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C233" s="22" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
@@ -10711,7 +10798,7 @@
       </c>
       <c r="B234" s="1"/>
       <c r="C234" s="21" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
@@ -10746,7 +10833,7 @@
       </c>
       <c r="B235" s="1"/>
       <c r="C235" s="21" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
@@ -10764,7 +10851,7 @@
       <c r="Q235" s="1"/>
       <c r="R235" s="1"/>
       <c r="S235" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T235" s="1"/>
       <c r="U235" s="1"/>
@@ -10783,7 +10870,7 @@
       </c>
       <c r="B236" s="1"/>
       <c r="C236" s="21" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
@@ -10818,7 +10905,7 @@
       </c>
       <c r="B237" s="1"/>
       <c r="C237" s="21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
@@ -10853,7 +10940,7 @@
       </c>
       <c r="B238" s="1"/>
       <c r="C238" s="21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
@@ -10888,7 +10975,7 @@
       </c>
       <c r="B239" s="1"/>
       <c r="C239" s="21" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
@@ -10923,7 +11010,7 @@
       </c>
       <c r="B240" s="1"/>
       <c r="C240" s="21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
@@ -10958,7 +11045,7 @@
       </c>
       <c r="B241" s="1"/>
       <c r="C241" s="21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
@@ -10993,7 +11080,7 @@
       </c>
       <c r="B242" s="1"/>
       <c r="C242" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
@@ -11028,7 +11115,7 @@
       </c>
       <c r="B243" s="3"/>
       <c r="C243" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
@@ -11046,7 +11133,7 @@
       <c r="Q243" s="1"/>
       <c r="R243" s="1"/>
       <c r="S243" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T243" s="1"/>
       <c r="U243" s="1"/>
@@ -11065,7 +11152,7 @@
       </c>
       <c r="B244" s="3"/>
       <c r="C244" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
@@ -11083,7 +11170,7 @@
       <c r="Q244" s="1"/>
       <c r="R244" s="1"/>
       <c r="S244" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T244" s="1"/>
       <c r="U244" s="1"/>
@@ -11102,7 +11189,7 @@
       </c>
       <c r="B245" s="3"/>
       <c r="C245" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
@@ -11120,7 +11207,7 @@
       <c r="Q245" s="1"/>
       <c r="R245" s="1"/>
       <c r="S245" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T245" s="1"/>
       <c r="U245" s="1"/>
@@ -11138,7 +11225,9 @@
         <v>243</v>
       </c>
       <c r="B246" s="3"/>
-      <c r="C246" s="21"/>
+      <c r="C246" s="21" t="s">
+        <v>278</v>
+      </c>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
@@ -11159,7 +11248,9 @@
       <c r="U246" s="1"/>
       <c r="V246" s="1"/>
       <c r="W246" s="1"/>
-      <c r="X246" s="1"/>
+      <c r="X246" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y246" s="1"/>
       <c r="Z246" s="1"/>
       <c r="AA246" s="1"/>
@@ -11171,7 +11262,9 @@
         <v>244</v>
       </c>
       <c r="B247" s="3"/>
-      <c r="C247" s="21"/>
+      <c r="C247" s="21" t="s">
+        <v>279</v>
+      </c>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
       <c r="F247" s="1"/>
@@ -11192,7 +11285,9 @@
       <c r="U247" s="1"/>
       <c r="V247" s="1"/>
       <c r="W247" s="1"/>
-      <c r="X247" s="1"/>
+      <c r="X247" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y247" s="1"/>
       <c r="Z247" s="1"/>
       <c r="AA247" s="1"/>
@@ -11204,7 +11299,9 @@
         <v>245</v>
       </c>
       <c r="B248" s="3"/>
-      <c r="C248" s="21"/>
+      <c r="C248" s="21" t="s">
+        <v>280</v>
+      </c>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
       <c r="F248" s="1"/>
@@ -11225,7 +11322,9 @@
       <c r="U248" s="1"/>
       <c r="V248" s="1"/>
       <c r="W248" s="1"/>
-      <c r="X248" s="1"/>
+      <c r="X248" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="Y248" s="1"/>
       <c r="Z248" s="1"/>
       <c r="AA248" s="1"/>
@@ -12330,30 +12429,30 @@
     <row r="2" spans="1:8">
       <c r="A2" s="14"/>
       <c r="B2" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="D2" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="E2" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="F2" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="H2" s="15" t="s">
         <v>237</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -12365,31 +12464,31 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="19" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H4" s="18"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -12401,10 +12500,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -12415,10 +12514,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -12429,7 +12528,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
@@ -12441,7 +12540,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
@@ -12453,7 +12552,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -12465,10 +12564,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
@@ -12479,7 +12578,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -12491,7 +12590,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -12503,7 +12602,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -12515,13 +12614,13 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
@@ -12531,13 +12630,13 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D16" s="18"/>
       <c r="E16" s="18"/>
@@ -12547,7 +12646,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
@@ -12559,41 +12658,41 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D19" s="35"/>
       <c r="E19" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
@@ -12601,31 +12700,31 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H20" s="18"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -12637,7 +12736,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -12649,7 +12748,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -12661,7 +12760,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="19" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -12673,7 +12772,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="19" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -12685,7 +12784,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="19" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122F8A0A-63D3-4F1B-BAA3-E67B953031C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45315113-31CF-485F-845D-D8E346C1CAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="4">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -80,8 +80,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="4">
+  <valueMetadata count="5">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -93,6 +100,9 @@
     </bk>
     <bk>
       <rc t="1" v="3"/>
+    </bk>
+    <bk>
+      <rc t="1" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -1819,7 +1829,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -1834,6 +1844,10 @@
   </rv>
   <rv s="0">
     <v>3</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>4</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -1854,6 +1868,7 @@
   <rel r:id="rId2"/>
   <rel r:id="rId3"/>
   <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
 </richValueRels>
 </file>
 
@@ -2204,7 +2219,9 @@
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
+      <c r="X2" s="5" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45315113-31CF-485F-845D-D8E346C1CAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4F049C-AB47-4D0E-B4B9-3DEBFF99AE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="リスト" sheetId="1" r:id="rId1"/>
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="296">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -1431,6 +1431,95 @@
   </si>
   <si>
     <t>笑わせるな</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>猫のさくら</t>
+    <rPh sb="0" eb="1">
+      <t>ネコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>リンゴ顔</t>
+    <rPh sb="3" eb="4">
+      <t>カオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>猫にリボン</t>
+    <rPh sb="0" eb="1">
+      <t>ネコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>猫のさくら</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>リンゴ顔</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>猫にリボン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>増えた</t>
+    <rPh sb="0" eb="1">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>減った</t>
+    <rPh sb="0" eb="1">
+      <t>ヘ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>まだまだ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ひらがな文字</t>
+    <rPh sb="4" eb="6">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ひらがな文字</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>今日会社</t>
+    <rPh sb="0" eb="2">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>昭和の言葉</t>
+    <rPh sb="0" eb="2">
+      <t>ショウワ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コトバ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>昭和のことば</t>
+    <rPh sb="0" eb="2">
+      <t>ショウワ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1731,6 +1820,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1760,9 +1852,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2143,8 +2232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:AC280"/>
+  <dimension ref="A1:AI280"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="1" width="3.4375" bestFit="1" customWidth="1"/>
@@ -2152,45 +2240,45 @@
     <col min="3" max="3" width="33.75" bestFit="1" customWidth="1"/>
     <col min="4" max="9" width="3.5625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="2.5625" bestFit="1" customWidth="1"/>
-    <col min="11" max="29" width="3.5625" bestFit="1" customWidth="1"/>
+    <col min="11" max="35" width="3.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="22.9">
-      <c r="A1" s="28"/>
-      <c r="B1" s="32" t="s">
+    <row r="1" spans="1:35" ht="22.9">
+      <c r="A1" s="29"/>
+      <c r="B1" s="33" t="s">
         <v>273</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
-      <c r="W1" s="31"/>
-      <c r="X1" s="31"/>
-    </row>
-    <row r="2" spans="1:29" ht="22.9">
-      <c r="A2" s="29"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="26"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="32"/>
+    </row>
+    <row r="2" spans="1:35" ht="22.9">
+      <c r="A2" s="30"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="27"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="e" vm="1">
         <v>#VALUE!</v>
@@ -2227,11 +2315,17 @@
       <c r="AA2" s="5"/>
       <c r="AB2" s="5"/>
       <c r="AC2" s="5"/>
-    </row>
-    <row r="3" spans="1:29" s="13" customFormat="1" ht="90.4" thickBot="1">
-      <c r="A3" s="30"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="27"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+    </row>
+    <row r="3" spans="1:35" s="13" customFormat="1" ht="106.9" thickBot="1">
+      <c r="A3" s="31"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="28"/>
       <c r="D3" s="11" t="s">
         <v>122</v>
       </c>
@@ -2301,11 +2395,27 @@
       <c r="Z3" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="AA3" s="11"/>
-      <c r="AB3" s="11"/>
-      <c r="AC3" s="11"/>
-    </row>
-    <row r="4" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1" thickTop="1">
+      <c r="AA3" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB3" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="AC3" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="AD3" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="AE3" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="AF3" s="11"/>
+      <c r="AG3" s="11"/>
+      <c r="AH3" s="11"/>
+      <c r="AI3" s="11"/>
+    </row>
+    <row r="4" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -2351,8 +2461,14 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
-    </row>
-    <row r="5" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="1"/>
+      <c r="AI4" s="1"/>
+    </row>
+    <row r="5" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -2400,8 +2516,14 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
-    </row>
-    <row r="6" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="1"/>
+      <c r="AH5" s="1"/>
+      <c r="AI5" s="1"/>
+    </row>
+    <row r="6" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -2439,8 +2561,14 @@
       <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
-    </row>
-    <row r="7" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="1"/>
+      <c r="AI6" s="1"/>
+    </row>
+    <row r="7" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -2474,8 +2602,14 @@
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
-    </row>
-    <row r="8" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="1"/>
+      <c r="AI7" s="1"/>
+    </row>
+    <row r="8" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -2511,8 +2645,14 @@
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
-    </row>
-    <row r="9" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD8" s="1"/>
+      <c r="AE8" s="1"/>
+      <c r="AF8" s="1"/>
+      <c r="AG8" s="1"/>
+      <c r="AH8" s="1"/>
+      <c r="AI8" s="1"/>
+    </row>
+    <row r="9" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -2546,8 +2686,14 @@
       <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
-    </row>
-    <row r="10" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+      <c r="AI9" s="1"/>
+    </row>
+    <row r="10" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -2581,8 +2727,14 @@
       <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
-    </row>
-    <row r="11" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1"/>
+      <c r="AF10" s="1"/>
+      <c r="AG10" s="1"/>
+      <c r="AH10" s="1"/>
+      <c r="AI10" s="1"/>
+    </row>
+    <row r="11" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -2620,8 +2772,14 @@
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
-    </row>
-    <row r="12" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="1"/>
+      <c r="AI11" s="1"/>
+    </row>
+    <row r="12" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -2655,8 +2813,14 @@
       <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
-    </row>
-    <row r="13" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD12" s="1"/>
+      <c r="AE12" s="1"/>
+      <c r="AF12" s="1"/>
+      <c r="AG12" s="1"/>
+      <c r="AH12" s="1"/>
+      <c r="AI12" s="1"/>
+    </row>
+    <row r="13" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -2690,8 +2854,14 @@
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
-    </row>
-    <row r="14" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD13" s="1"/>
+      <c r="AE13" s="1"/>
+      <c r="AF13" s="1"/>
+      <c r="AG13" s="1"/>
+      <c r="AH13" s="1"/>
+      <c r="AI13" s="1"/>
+    </row>
+    <row r="14" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -2725,8 +2895,14 @@
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
-    </row>
-    <row r="15" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD14" s="1"/>
+      <c r="AE14" s="1"/>
+      <c r="AF14" s="1"/>
+      <c r="AG14" s="1"/>
+      <c r="AH14" s="1"/>
+      <c r="AI14" s="1"/>
+    </row>
+    <row r="15" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -2760,8 +2936,14 @@
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
-    </row>
-    <row r="16" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD15" s="1"/>
+      <c r="AE15" s="1"/>
+      <c r="AF15" s="1"/>
+      <c r="AG15" s="1"/>
+      <c r="AH15" s="1"/>
+      <c r="AI15" s="1"/>
+    </row>
+    <row r="16" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -2795,8 +2977,14 @@
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
-    </row>
-    <row r="17" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD16" s="1"/>
+      <c r="AE16" s="1"/>
+      <c r="AF16" s="1"/>
+      <c r="AG16" s="1"/>
+      <c r="AH16" s="1"/>
+      <c r="AI16" s="1"/>
+    </row>
+    <row r="17" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -2830,8 +3018,14 @@
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
-    </row>
-    <row r="18" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD17" s="1"/>
+      <c r="AE17" s="1"/>
+      <c r="AF17" s="1"/>
+      <c r="AG17" s="1"/>
+      <c r="AH17" s="1"/>
+      <c r="AI17" s="1"/>
+    </row>
+    <row r="18" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -2867,8 +3061,14 @@
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
-    </row>
-    <row r="19" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD18" s="1"/>
+      <c r="AE18" s="1"/>
+      <c r="AF18" s="1"/>
+      <c r="AG18" s="1"/>
+      <c r="AH18" s="1"/>
+      <c r="AI18" s="1"/>
+    </row>
+    <row r="19" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -2902,8 +3102,14 @@
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
-    </row>
-    <row r="20" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD19" s="1"/>
+      <c r="AE19" s="1"/>
+      <c r="AF19" s="1"/>
+      <c r="AG19" s="1"/>
+      <c r="AH19" s="1"/>
+      <c r="AI19" s="1"/>
+    </row>
+    <row r="20" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -2937,8 +3143,14 @@
       <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
-    </row>
-    <row r="21" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD20" s="1"/>
+      <c r="AE20" s="1"/>
+      <c r="AF20" s="1"/>
+      <c r="AG20" s="1"/>
+      <c r="AH20" s="1"/>
+      <c r="AI20" s="1"/>
+    </row>
+    <row r="21" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -2972,8 +3184,14 @@
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
-    </row>
-    <row r="22" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD21" s="1"/>
+      <c r="AE21" s="1"/>
+      <c r="AF21" s="1"/>
+      <c r="AG21" s="1"/>
+      <c r="AH21" s="1"/>
+      <c r="AI21" s="1"/>
+    </row>
+    <row r="22" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -3009,8 +3227,14 @@
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
-    </row>
-    <row r="23" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD22" s="1"/>
+      <c r="AE22" s="1"/>
+      <c r="AF22" s="1"/>
+      <c r="AG22" s="1"/>
+      <c r="AH22" s="1"/>
+      <c r="AI22" s="1"/>
+    </row>
+    <row r="23" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -3044,8 +3268,14 @@
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
-    </row>
-    <row r="24" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD23" s="1"/>
+      <c r="AE23" s="1"/>
+      <c r="AF23" s="1"/>
+      <c r="AG23" s="1"/>
+      <c r="AH23" s="1"/>
+      <c r="AI23" s="1"/>
+    </row>
+    <row r="24" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -3081,8 +3311,14 @@
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
-    </row>
-    <row r="25" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD24" s="1"/>
+      <c r="AE24" s="1"/>
+      <c r="AF24" s="1"/>
+      <c r="AG24" s="1"/>
+      <c r="AH24" s="1"/>
+      <c r="AI24" s="1"/>
+    </row>
+    <row r="25" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -3118,8 +3354,14 @@
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
-    </row>
-    <row r="26" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD25" s="1"/>
+      <c r="AE25" s="1"/>
+      <c r="AF25" s="1"/>
+      <c r="AG25" s="1"/>
+      <c r="AH25" s="1"/>
+      <c r="AI25" s="1"/>
+    </row>
+    <row r="26" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -3153,8 +3395,14 @@
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
-    </row>
-    <row r="27" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD26" s="1"/>
+      <c r="AE26" s="1"/>
+      <c r="AF26" s="1"/>
+      <c r="AG26" s="1"/>
+      <c r="AH26" s="1"/>
+      <c r="AI26" s="1"/>
+    </row>
+    <row r="27" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -3190,8 +3438,14 @@
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
-    </row>
-    <row r="28" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD27" s="1"/>
+      <c r="AE27" s="1"/>
+      <c r="AF27" s="1"/>
+      <c r="AG27" s="1"/>
+      <c r="AH27" s="1"/>
+      <c r="AI27" s="1"/>
+    </row>
+    <row r="28" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -3225,8 +3479,14 @@
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
-    </row>
-    <row r="29" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD28" s="1"/>
+      <c r="AE28" s="1"/>
+      <c r="AF28" s="1"/>
+      <c r="AG28" s="1"/>
+      <c r="AH28" s="1"/>
+      <c r="AI28" s="1"/>
+    </row>
+    <row r="29" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -3260,8 +3520,14 @@
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
-    </row>
-    <row r="30" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD29" s="1"/>
+      <c r="AE29" s="1"/>
+      <c r="AF29" s="1"/>
+      <c r="AG29" s="1"/>
+      <c r="AH29" s="1"/>
+      <c r="AI29" s="1"/>
+    </row>
+    <row r="30" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -3297,8 +3563,14 @@
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
-    </row>
-    <row r="31" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD30" s="1"/>
+      <c r="AE30" s="1"/>
+      <c r="AF30" s="1"/>
+      <c r="AG30" s="1"/>
+      <c r="AH30" s="1"/>
+      <c r="AI30" s="1"/>
+    </row>
+    <row r="31" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -3338,8 +3610,14 @@
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
-    </row>
-    <row r="32" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD31" s="1"/>
+      <c r="AE31" s="1"/>
+      <c r="AF31" s="1"/>
+      <c r="AG31" s="1"/>
+      <c r="AH31" s="1"/>
+      <c r="AI31" s="1"/>
+    </row>
+    <row r="32" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -3375,8 +3653,14 @@
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
-    </row>
-    <row r="33" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD32" s="1"/>
+      <c r="AE32" s="1"/>
+      <c r="AF32" s="1"/>
+      <c r="AG32" s="1"/>
+      <c r="AH32" s="1"/>
+      <c r="AI32" s="1"/>
+    </row>
+    <row r="33" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -3410,8 +3694,14 @@
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
-    </row>
-    <row r="34" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD33" s="1"/>
+      <c r="AE33" s="1"/>
+      <c r="AF33" s="1"/>
+      <c r="AG33" s="1"/>
+      <c r="AH33" s="1"/>
+      <c r="AI33" s="1"/>
+    </row>
+    <row r="34" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -3445,8 +3735,14 @@
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
-    </row>
-    <row r="35" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD34" s="1"/>
+      <c r="AE34" s="1"/>
+      <c r="AF34" s="1"/>
+      <c r="AG34" s="1"/>
+      <c r="AH34" s="1"/>
+      <c r="AI34" s="1"/>
+    </row>
+    <row r="35" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -3480,8 +3776,14 @@
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
-    </row>
-    <row r="36" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD35" s="1"/>
+      <c r="AE35" s="1"/>
+      <c r="AF35" s="1"/>
+      <c r="AG35" s="1"/>
+      <c r="AH35" s="1"/>
+      <c r="AI35" s="1"/>
+    </row>
+    <row r="36" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -3515,8 +3817,14 @@
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
-    </row>
-    <row r="37" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD36" s="1"/>
+      <c r="AE36" s="1"/>
+      <c r="AF36" s="1"/>
+      <c r="AG36" s="1"/>
+      <c r="AH36" s="1"/>
+      <c r="AI36" s="1"/>
+    </row>
+    <row r="37" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -3550,8 +3858,14 @@
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
-    </row>
-    <row r="38" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD37" s="1"/>
+      <c r="AE37" s="1"/>
+      <c r="AF37" s="1"/>
+      <c r="AG37" s="1"/>
+      <c r="AH37" s="1"/>
+      <c r="AI37" s="1"/>
+    </row>
+    <row r="38" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -3585,8 +3899,14 @@
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
-    </row>
-    <row r="39" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD38" s="1"/>
+      <c r="AE38" s="1"/>
+      <c r="AF38" s="1"/>
+      <c r="AG38" s="1"/>
+      <c r="AH38" s="1"/>
+      <c r="AI38" s="1"/>
+    </row>
+    <row r="39" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -3622,8 +3942,14 @@
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
-    </row>
-    <row r="40" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD39" s="1"/>
+      <c r="AE39" s="1"/>
+      <c r="AF39" s="1"/>
+      <c r="AG39" s="1"/>
+      <c r="AH39" s="1"/>
+      <c r="AI39" s="1"/>
+    </row>
+    <row r="40" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -3659,8 +3985,14 @@
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
-    </row>
-    <row r="41" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD40" s="1"/>
+      <c r="AE40" s="1"/>
+      <c r="AF40" s="1"/>
+      <c r="AG40" s="1"/>
+      <c r="AH40" s="1"/>
+      <c r="AI40" s="1"/>
+    </row>
+    <row r="41" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -3696,8 +4028,14 @@
       <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
-    </row>
-    <row r="42" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD41" s="1"/>
+      <c r="AE41" s="1"/>
+      <c r="AF41" s="1"/>
+      <c r="AG41" s="1"/>
+      <c r="AH41" s="1"/>
+      <c r="AI41" s="1"/>
+    </row>
+    <row r="42" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -3731,8 +4069,14 @@
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
-    </row>
-    <row r="43" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD42" s="1"/>
+      <c r="AE42" s="1"/>
+      <c r="AF42" s="1"/>
+      <c r="AG42" s="1"/>
+      <c r="AH42" s="1"/>
+      <c r="AI42" s="1"/>
+    </row>
+    <row r="43" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -3768,8 +4112,14 @@
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
-    </row>
-    <row r="44" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD43" s="1"/>
+      <c r="AE43" s="1"/>
+      <c r="AF43" s="1"/>
+      <c r="AG43" s="1"/>
+      <c r="AH43" s="1"/>
+      <c r="AI43" s="1"/>
+    </row>
+    <row r="44" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -3803,8 +4153,14 @@
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
-    </row>
-    <row r="45" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD44" s="1"/>
+      <c r="AE44" s="1"/>
+      <c r="AF44" s="1"/>
+      <c r="AG44" s="1"/>
+      <c r="AH44" s="1"/>
+      <c r="AI44" s="1"/>
+    </row>
+    <row r="45" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -3838,8 +4194,14 @@
       <c r="AA45" s="1"/>
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
-    </row>
-    <row r="46" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD45" s="1"/>
+      <c r="AE45" s="1"/>
+      <c r="AF45" s="1"/>
+      <c r="AG45" s="1"/>
+      <c r="AH45" s="1"/>
+      <c r="AI45" s="1"/>
+    </row>
+    <row r="46" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -3873,8 +4235,14 @@
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
-    </row>
-    <row r="47" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD46" s="1"/>
+      <c r="AE46" s="1"/>
+      <c r="AF46" s="1"/>
+      <c r="AG46" s="1"/>
+      <c r="AH46" s="1"/>
+      <c r="AI46" s="1"/>
+    </row>
+    <row r="47" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -3908,8 +4276,14 @@
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
-    </row>
-    <row r="48" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD47" s="1"/>
+      <c r="AE47" s="1"/>
+      <c r="AF47" s="1"/>
+      <c r="AG47" s="1"/>
+      <c r="AH47" s="1"/>
+      <c r="AI47" s="1"/>
+    </row>
+    <row r="48" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -3945,8 +4319,14 @@
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
-    </row>
-    <row r="49" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD48" s="1"/>
+      <c r="AE48" s="1"/>
+      <c r="AF48" s="1"/>
+      <c r="AG48" s="1"/>
+      <c r="AH48" s="1"/>
+      <c r="AI48" s="1"/>
+    </row>
+    <row r="49" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -3980,8 +4360,14 @@
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
-    </row>
-    <row r="50" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD49" s="1"/>
+      <c r="AE49" s="1"/>
+      <c r="AF49" s="1"/>
+      <c r="AG49" s="1"/>
+      <c r="AH49" s="1"/>
+      <c r="AI49" s="1"/>
+    </row>
+    <row r="50" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -4017,8 +4403,14 @@
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
-    </row>
-    <row r="51" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD50" s="1"/>
+      <c r="AE50" s="1"/>
+      <c r="AF50" s="1"/>
+      <c r="AG50" s="1"/>
+      <c r="AH50" s="1"/>
+      <c r="AI50" s="1"/>
+    </row>
+    <row r="51" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -4052,8 +4444,14 @@
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
-    </row>
-    <row r="52" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD51" s="1"/>
+      <c r="AE51" s="1"/>
+      <c r="AF51" s="1"/>
+      <c r="AG51" s="1"/>
+      <c r="AH51" s="1"/>
+      <c r="AI51" s="1"/>
+    </row>
+    <row r="52" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -4087,8 +4485,14 @@
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
-    </row>
-    <row r="53" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD52" s="1"/>
+      <c r="AE52" s="1"/>
+      <c r="AF52" s="1"/>
+      <c r="AG52" s="1"/>
+      <c r="AH52" s="1"/>
+      <c r="AI52" s="1"/>
+    </row>
+    <row r="53" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -4122,8 +4526,14 @@
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
-    </row>
-    <row r="54" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD53" s="1"/>
+      <c r="AE53" s="1"/>
+      <c r="AF53" s="1"/>
+      <c r="AG53" s="1"/>
+      <c r="AH53" s="1"/>
+      <c r="AI53" s="1"/>
+    </row>
+    <row r="54" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A54" s="3">
         <v>51</v>
       </c>
@@ -4159,8 +4569,14 @@
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
-    </row>
-    <row r="55" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD54" s="1"/>
+      <c r="AE54" s="1"/>
+      <c r="AF54" s="1"/>
+      <c r="AG54" s="1"/>
+      <c r="AH54" s="1"/>
+      <c r="AI54" s="1"/>
+    </row>
+    <row r="55" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -4196,8 +4612,14 @@
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
-    </row>
-    <row r="56" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD55" s="1"/>
+      <c r="AE55" s="1"/>
+      <c r="AF55" s="1"/>
+      <c r="AG55" s="1"/>
+      <c r="AH55" s="1"/>
+      <c r="AI55" s="1"/>
+    </row>
+    <row r="56" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -4231,8 +4653,14 @@
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
-    </row>
-    <row r="57" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD56" s="1"/>
+      <c r="AE56" s="1"/>
+      <c r="AF56" s="1"/>
+      <c r="AG56" s="1"/>
+      <c r="AH56" s="1"/>
+      <c r="AI56" s="1"/>
+    </row>
+    <row r="57" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -4266,8 +4694,14 @@
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
-    </row>
-    <row r="58" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD57" s="1"/>
+      <c r="AE57" s="1"/>
+      <c r="AF57" s="1"/>
+      <c r="AG57" s="1"/>
+      <c r="AH57" s="1"/>
+      <c r="AI57" s="1"/>
+    </row>
+    <row r="58" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -4301,8 +4735,14 @@
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
-    </row>
-    <row r="59" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD58" s="1"/>
+      <c r="AE58" s="1"/>
+      <c r="AF58" s="1"/>
+      <c r="AG58" s="1"/>
+      <c r="AH58" s="1"/>
+      <c r="AI58" s="1"/>
+    </row>
+    <row r="59" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -4336,8 +4776,14 @@
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
-    </row>
-    <row r="60" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD59" s="1"/>
+      <c r="AE59" s="1"/>
+      <c r="AF59" s="1"/>
+      <c r="AG59" s="1"/>
+      <c r="AH59" s="1"/>
+      <c r="AI59" s="1"/>
+    </row>
+    <row r="60" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -4371,8 +4817,14 @@
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
-    </row>
-    <row r="61" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD60" s="1"/>
+      <c r="AE60" s="1"/>
+      <c r="AF60" s="1"/>
+      <c r="AG60" s="1"/>
+      <c r="AH60" s="1"/>
+      <c r="AI60" s="1"/>
+    </row>
+    <row r="61" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -4406,8 +4858,14 @@
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
-    </row>
-    <row r="62" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD61" s="1"/>
+      <c r="AE61" s="1"/>
+      <c r="AF61" s="1"/>
+      <c r="AG61" s="1"/>
+      <c r="AH61" s="1"/>
+      <c r="AI61" s="1"/>
+    </row>
+    <row r="62" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -4441,8 +4899,14 @@
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
-    </row>
-    <row r="63" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD62" s="1"/>
+      <c r="AE62" s="1"/>
+      <c r="AF62" s="1"/>
+      <c r="AG62" s="1"/>
+      <c r="AH62" s="1"/>
+      <c r="AI62" s="1"/>
+    </row>
+    <row r="63" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A63" s="3">
         <v>60</v>
       </c>
@@ -4478,8 +4942,14 @@
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
-    </row>
-    <row r="64" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD63" s="1"/>
+      <c r="AE63" s="1"/>
+      <c r="AF63" s="1"/>
+      <c r="AG63" s="1"/>
+      <c r="AH63" s="1"/>
+      <c r="AI63" s="1"/>
+    </row>
+    <row r="64" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A64" s="3">
         <v>61</v>
       </c>
@@ -4517,8 +4987,14 @@
       <c r="AA64" s="1"/>
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
-    </row>
-    <row r="65" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD64" s="1"/>
+      <c r="AE64" s="1"/>
+      <c r="AF64" s="1"/>
+      <c r="AG64" s="1"/>
+      <c r="AH64" s="1"/>
+      <c r="AI64" s="1"/>
+    </row>
+    <row r="65" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A65" s="3">
         <v>62</v>
       </c>
@@ -4554,8 +5030,14 @@
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
-    </row>
-    <row r="66" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD65" s="1"/>
+      <c r="AE65" s="1"/>
+      <c r="AF65" s="1"/>
+      <c r="AG65" s="1"/>
+      <c r="AH65" s="1"/>
+      <c r="AI65" s="1"/>
+    </row>
+    <row r="66" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A66" s="3">
         <v>63</v>
       </c>
@@ -4589,8 +5071,14 @@
       <c r="AA66" s="1"/>
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
-    </row>
-    <row r="67" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD66" s="1"/>
+      <c r="AE66" s="1"/>
+      <c r="AF66" s="1"/>
+      <c r="AG66" s="1"/>
+      <c r="AH66" s="1"/>
+      <c r="AI66" s="1"/>
+    </row>
+    <row r="67" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A67" s="3">
         <v>64</v>
       </c>
@@ -4628,8 +5116,14 @@
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
-    </row>
-    <row r="68" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD67" s="1"/>
+      <c r="AE67" s="1"/>
+      <c r="AF67" s="1"/>
+      <c r="AG67" s="1"/>
+      <c r="AH67" s="1"/>
+      <c r="AI67" s="1"/>
+    </row>
+    <row r="68" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A68" s="3">
         <v>65</v>
       </c>
@@ -4665,8 +5159,14 @@
       <c r="AA68" s="1"/>
       <c r="AB68" s="1"/>
       <c r="AC68" s="1"/>
-    </row>
-    <row r="69" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD68" s="1"/>
+      <c r="AE68" s="1"/>
+      <c r="AF68" s="1"/>
+      <c r="AG68" s="1"/>
+      <c r="AH68" s="1"/>
+      <c r="AI68" s="1"/>
+    </row>
+    <row r="69" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A69" s="3">
         <v>66</v>
       </c>
@@ -4704,8 +5204,14 @@
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
-    </row>
-    <row r="70" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD69" s="1"/>
+      <c r="AE69" s="1"/>
+      <c r="AF69" s="1"/>
+      <c r="AG69" s="1"/>
+      <c r="AH69" s="1"/>
+      <c r="AI69" s="1"/>
+    </row>
+    <row r="70" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A70" s="3">
         <v>67</v>
       </c>
@@ -4741,8 +5247,14 @@
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
-    </row>
-    <row r="71" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD70" s="1"/>
+      <c r="AE70" s="1"/>
+      <c r="AF70" s="1"/>
+      <c r="AG70" s="1"/>
+      <c r="AH70" s="1"/>
+      <c r="AI70" s="1"/>
+    </row>
+    <row r="71" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A71" s="3">
         <v>68</v>
       </c>
@@ -4778,8 +5290,14 @@
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
-    </row>
-    <row r="72" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD71" s="1"/>
+      <c r="AE71" s="1"/>
+      <c r="AF71" s="1"/>
+      <c r="AG71" s="1"/>
+      <c r="AH71" s="1"/>
+      <c r="AI71" s="1"/>
+    </row>
+    <row r="72" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A72" s="3">
         <v>69</v>
       </c>
@@ -4813,8 +5331,14 @@
       <c r="AA72" s="1"/>
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
-    </row>
-    <row r="73" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD72" s="1"/>
+      <c r="AE72" s="1"/>
+      <c r="AF72" s="1"/>
+      <c r="AG72" s="1"/>
+      <c r="AH72" s="1"/>
+      <c r="AI72" s="1"/>
+    </row>
+    <row r="73" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A73" s="3">
         <v>70</v>
       </c>
@@ -4848,8 +5372,14 @@
       <c r="AA73" s="1"/>
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
-    </row>
-    <row r="74" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD73" s="1"/>
+      <c r="AE73" s="1"/>
+      <c r="AF73" s="1"/>
+      <c r="AG73" s="1"/>
+      <c r="AH73" s="1"/>
+      <c r="AI73" s="1"/>
+    </row>
+    <row r="74" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A74" s="3">
         <v>71</v>
       </c>
@@ -4883,8 +5413,14 @@
       <c r="AA74" s="1"/>
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
-    </row>
-    <row r="75" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD74" s="1"/>
+      <c r="AE74" s="1"/>
+      <c r="AF74" s="1"/>
+      <c r="AG74" s="1"/>
+      <c r="AH74" s="1"/>
+      <c r="AI74" s="1"/>
+    </row>
+    <row r="75" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A75" s="3">
         <v>72</v>
       </c>
@@ -4918,8 +5454,14 @@
       <c r="AA75" s="1"/>
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
-    </row>
-    <row r="76" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+      <c r="AD75" s="1"/>
+      <c r="AE75" s="1"/>
+      <c r="AF75" s="1"/>
+      <c r="AG75" s="1"/>
+      <c r="AH75" s="1"/>
+      <c r="AI75" s="1"/>
+    </row>
+    <row r="76" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A76" s="3">
         <v>73</v>
       </c>
@@ -4957,8 +5499,14 @@
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
-    </row>
-    <row r="77" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+      <c r="AD76" s="1"/>
+      <c r="AE76" s="1"/>
+      <c r="AF76" s="1"/>
+      <c r="AG76" s="1"/>
+      <c r="AH76" s="1"/>
+      <c r="AI76" s="1"/>
+    </row>
+    <row r="77" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A77" s="3">
         <v>74</v>
       </c>
@@ -4994,8 +5542,14 @@
       <c r="AA77" s="1"/>
       <c r="AB77" s="1"/>
       <c r="AC77" s="1"/>
-    </row>
-    <row r="78" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+      <c r="AD77" s="1"/>
+      <c r="AE77" s="1"/>
+      <c r="AF77" s="1"/>
+      <c r="AG77" s="1"/>
+      <c r="AH77" s="1"/>
+      <c r="AI77" s="1"/>
+    </row>
+    <row r="78" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A78" s="3">
         <v>75</v>
       </c>
@@ -5031,8 +5585,14 @@
       <c r="AA78" s="1"/>
       <c r="AB78" s="1"/>
       <c r="AC78" s="1"/>
-    </row>
-    <row r="79" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+      <c r="AD78" s="1"/>
+      <c r="AE78" s="1"/>
+      <c r="AF78" s="1"/>
+      <c r="AG78" s="1"/>
+      <c r="AH78" s="1"/>
+      <c r="AI78" s="1"/>
+    </row>
+    <row r="79" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A79" s="3">
         <v>76</v>
       </c>
@@ -5068,8 +5628,14 @@
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
       <c r="AC79" s="1"/>
-    </row>
-    <row r="80" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+      <c r="AD79" s="1"/>
+      <c r="AE79" s="1"/>
+      <c r="AF79" s="1"/>
+      <c r="AG79" s="1"/>
+      <c r="AH79" s="1"/>
+      <c r="AI79" s="1"/>
+    </row>
+    <row r="80" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A80" s="3">
         <v>77</v>
       </c>
@@ -5105,8 +5671,14 @@
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
       <c r="AC80" s="1"/>
-    </row>
-    <row r="81" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+      <c r="AD80" s="1"/>
+      <c r="AE80" s="1"/>
+      <c r="AF80" s="1"/>
+      <c r="AG80" s="1"/>
+      <c r="AH80" s="1"/>
+      <c r="AI80" s="1"/>
+    </row>
+    <row r="81" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A81" s="3">
         <v>78</v>
       </c>
@@ -5144,8 +5716,14 @@
       <c r="AA81" s="1"/>
       <c r="AB81" s="1"/>
       <c r="AC81" s="1"/>
-    </row>
-    <row r="82" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+      <c r="AD81" s="1"/>
+      <c r="AE81" s="1"/>
+      <c r="AF81" s="1"/>
+      <c r="AG81" s="1"/>
+      <c r="AH81" s="1"/>
+      <c r="AI81" s="1"/>
+    </row>
+    <row r="82" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A82" s="3">
         <v>79</v>
       </c>
@@ -5183,8 +5761,14 @@
       <c r="AA82" s="1"/>
       <c r="AB82" s="1"/>
       <c r="AC82" s="1"/>
-    </row>
-    <row r="83" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+      <c r="AD82" s="1"/>
+      <c r="AE82" s="1"/>
+      <c r="AF82" s="1"/>
+      <c r="AG82" s="1"/>
+      <c r="AH82" s="1"/>
+      <c r="AI82" s="1"/>
+    </row>
+    <row r="83" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A83" s="3">
         <v>80</v>
       </c>
@@ -5222,8 +5806,14 @@
       <c r="AA83" s="1"/>
       <c r="AB83" s="1"/>
       <c r="AC83" s="1"/>
-    </row>
-    <row r="84" spans="1:29" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+      <c r="AD83" s="1"/>
+      <c r="AE83" s="1"/>
+      <c r="AF83" s="1"/>
+      <c r="AG83" s="1"/>
+      <c r="AH83" s="1"/>
+      <c r="AI83" s="1"/>
+    </row>
+    <row r="84" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A84" s="3">
         <v>81</v>
       </c>
@@ -5259,8 +5849,14 @@
       <c r="AA84" s="1"/>
       <c r="AB84" s="1"/>
       <c r="AC84" s="1"/>
-    </row>
-    <row r="85" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD84" s="1"/>
+      <c r="AE84" s="1"/>
+      <c r="AF84" s="1"/>
+      <c r="AG84" s="1"/>
+      <c r="AH84" s="1"/>
+      <c r="AI84" s="1"/>
+    </row>
+    <row r="85" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A85" s="3">
         <v>82</v>
       </c>
@@ -5294,8 +5890,14 @@
       <c r="AA85" s="1"/>
       <c r="AB85" s="1"/>
       <c r="AC85" s="1"/>
-    </row>
-    <row r="86" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD85" s="1"/>
+      <c r="AE85" s="1"/>
+      <c r="AF85" s="1"/>
+      <c r="AG85" s="1"/>
+      <c r="AH85" s="1"/>
+      <c r="AI85" s="1"/>
+    </row>
+    <row r="86" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A86" s="3">
         <v>83</v>
       </c>
@@ -5329,8 +5931,14 @@
       <c r="AA86" s="1"/>
       <c r="AB86" s="1"/>
       <c r="AC86" s="1"/>
-    </row>
-    <row r="87" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD86" s="1"/>
+      <c r="AE86" s="1"/>
+      <c r="AF86" s="1"/>
+      <c r="AG86" s="1"/>
+      <c r="AH86" s="1"/>
+      <c r="AI86" s="1"/>
+    </row>
+    <row r="87" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A87" s="3">
         <v>84</v>
       </c>
@@ -5364,8 +5972,14 @@
       <c r="AA87" s="1"/>
       <c r="AB87" s="1"/>
       <c r="AC87" s="1"/>
-    </row>
-    <row r="88" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD87" s="1"/>
+      <c r="AE87" s="1"/>
+      <c r="AF87" s="1"/>
+      <c r="AG87" s="1"/>
+      <c r="AH87" s="1"/>
+      <c r="AI87" s="1"/>
+    </row>
+    <row r="88" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A88" s="3">
         <v>85</v>
       </c>
@@ -5401,8 +6015,14 @@
       <c r="AA88" s="1"/>
       <c r="AB88" s="1"/>
       <c r="AC88" s="1"/>
-    </row>
-    <row r="89" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD88" s="1"/>
+      <c r="AE88" s="1"/>
+      <c r="AF88" s="1"/>
+      <c r="AG88" s="1"/>
+      <c r="AH88" s="1"/>
+      <c r="AI88" s="1"/>
+    </row>
+    <row r="89" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A89" s="3">
         <v>86</v>
       </c>
@@ -5436,8 +6056,14 @@
       <c r="AA89" s="1"/>
       <c r="AB89" s="1"/>
       <c r="AC89" s="1"/>
-    </row>
-    <row r="90" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD89" s="1"/>
+      <c r="AE89" s="1"/>
+      <c r="AF89" s="1"/>
+      <c r="AG89" s="1"/>
+      <c r="AH89" s="1"/>
+      <c r="AI89" s="1"/>
+    </row>
+    <row r="90" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A90" s="3">
         <v>87</v>
       </c>
@@ -5471,8 +6097,14 @@
       <c r="AA90" s="1"/>
       <c r="AB90" s="1"/>
       <c r="AC90" s="1"/>
-    </row>
-    <row r="91" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD90" s="1"/>
+      <c r="AE90" s="1"/>
+      <c r="AF90" s="1"/>
+      <c r="AG90" s="1"/>
+      <c r="AH90" s="1"/>
+      <c r="AI90" s="1"/>
+    </row>
+    <row r="91" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A91" s="3">
         <v>88</v>
       </c>
@@ -5508,8 +6140,14 @@
       <c r="AA91" s="1"/>
       <c r="AB91" s="1"/>
       <c r="AC91" s="1"/>
-    </row>
-    <row r="92" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD91" s="1"/>
+      <c r="AE91" s="1"/>
+      <c r="AF91" s="1"/>
+      <c r="AG91" s="1"/>
+      <c r="AH91" s="1"/>
+      <c r="AI91" s="1"/>
+    </row>
+    <row r="92" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A92" s="3">
         <v>89</v>
       </c>
@@ -5545,8 +6183,14 @@
       <c r="AA92" s="1"/>
       <c r="AB92" s="1"/>
       <c r="AC92" s="1"/>
-    </row>
-    <row r="93" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD92" s="1"/>
+      <c r="AE92" s="1"/>
+      <c r="AF92" s="1"/>
+      <c r="AG92" s="1"/>
+      <c r="AH92" s="1"/>
+      <c r="AI92" s="1"/>
+    </row>
+    <row r="93" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A93" s="3">
         <v>90</v>
       </c>
@@ -5580,8 +6224,14 @@
       <c r="AA93" s="1"/>
       <c r="AB93" s="1"/>
       <c r="AC93" s="1"/>
-    </row>
-    <row r="94" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD93" s="1"/>
+      <c r="AE93" s="1"/>
+      <c r="AF93" s="1"/>
+      <c r="AG93" s="1"/>
+      <c r="AH93" s="1"/>
+      <c r="AI93" s="1"/>
+    </row>
+    <row r="94" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A94" s="3">
         <v>91</v>
       </c>
@@ -5615,8 +6265,14 @@
       <c r="AA94" s="1"/>
       <c r="AB94" s="1"/>
       <c r="AC94" s="1"/>
-    </row>
-    <row r="95" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD94" s="1"/>
+      <c r="AE94" s="1"/>
+      <c r="AF94" s="1"/>
+      <c r="AG94" s="1"/>
+      <c r="AH94" s="1"/>
+      <c r="AI94" s="1"/>
+    </row>
+    <row r="95" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A95" s="3">
         <v>92</v>
       </c>
@@ -5650,8 +6306,14 @@
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
       <c r="AC95" s="1"/>
-    </row>
-    <row r="96" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD95" s="1"/>
+      <c r="AE95" s="1"/>
+      <c r="AF95" s="1"/>
+      <c r="AG95" s="1"/>
+      <c r="AH95" s="1"/>
+      <c r="AI95" s="1"/>
+    </row>
+    <row r="96" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A96" s="3">
         <v>93</v>
       </c>
@@ -5685,8 +6347,14 @@
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
       <c r="AC96" s="1"/>
-    </row>
-    <row r="97" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD96" s="1"/>
+      <c r="AE96" s="1"/>
+      <c r="AF96" s="1"/>
+      <c r="AG96" s="1"/>
+      <c r="AH96" s="1"/>
+      <c r="AI96" s="1"/>
+    </row>
+    <row r="97" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A97" s="3">
         <v>94</v>
       </c>
@@ -5720,8 +6388,14 @@
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
       <c r="AC97" s="1"/>
-    </row>
-    <row r="98" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD97" s="1"/>
+      <c r="AE97" s="1"/>
+      <c r="AF97" s="1"/>
+      <c r="AG97" s="1"/>
+      <c r="AH97" s="1"/>
+      <c r="AI97" s="1"/>
+    </row>
+    <row r="98" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A98" s="3">
         <v>95</v>
       </c>
@@ -5757,8 +6431,14 @@
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
       <c r="AC98" s="1"/>
-    </row>
-    <row r="99" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD98" s="1"/>
+      <c r="AE98" s="1"/>
+      <c r="AF98" s="1"/>
+      <c r="AG98" s="1"/>
+      <c r="AH98" s="1"/>
+      <c r="AI98" s="1"/>
+    </row>
+    <row r="99" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A99" s="3">
         <v>96</v>
       </c>
@@ -5792,8 +6472,14 @@
       <c r="AA99" s="1"/>
       <c r="AB99" s="1"/>
       <c r="AC99" s="1"/>
-    </row>
-    <row r="100" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD99" s="1"/>
+      <c r="AE99" s="1"/>
+      <c r="AF99" s="1"/>
+      <c r="AG99" s="1"/>
+      <c r="AH99" s="1"/>
+      <c r="AI99" s="1"/>
+    </row>
+    <row r="100" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A100" s="3">
         <v>97</v>
       </c>
@@ -5827,8 +6513,14 @@
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
       <c r="AC100" s="1"/>
-    </row>
-    <row r="101" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD100" s="1"/>
+      <c r="AE100" s="1"/>
+      <c r="AF100" s="1"/>
+      <c r="AG100" s="1"/>
+      <c r="AH100" s="1"/>
+      <c r="AI100" s="1"/>
+    </row>
+    <row r="101" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A101" s="3">
         <v>98</v>
       </c>
@@ -5862,8 +6554,14 @@
       <c r="AA101" s="1"/>
       <c r="AB101" s="1"/>
       <c r="AC101" s="1"/>
-    </row>
-    <row r="102" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD101" s="1"/>
+      <c r="AE101" s="1"/>
+      <c r="AF101" s="1"/>
+      <c r="AG101" s="1"/>
+      <c r="AH101" s="1"/>
+      <c r="AI101" s="1"/>
+    </row>
+    <row r="102" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A102" s="3">
         <v>99</v>
       </c>
@@ -5897,8 +6595,14 @@
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
       <c r="AC102" s="1"/>
-    </row>
-    <row r="103" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD102" s="1"/>
+      <c r="AE102" s="1"/>
+      <c r="AF102" s="1"/>
+      <c r="AG102" s="1"/>
+      <c r="AH102" s="1"/>
+      <c r="AI102" s="1"/>
+    </row>
+    <row r="103" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A103" s="3">
         <v>100</v>
       </c>
@@ -5932,8 +6636,14 @@
       <c r="AA103" s="1"/>
       <c r="AB103" s="1"/>
       <c r="AC103" s="1"/>
-    </row>
-    <row r="104" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD103" s="1"/>
+      <c r="AE103" s="1"/>
+      <c r="AF103" s="1"/>
+      <c r="AG103" s="1"/>
+      <c r="AH103" s="1"/>
+      <c r="AI103" s="1"/>
+    </row>
+    <row r="104" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A104" s="3">
         <v>101</v>
       </c>
@@ -5967,8 +6677,14 @@
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
       <c r="AC104" s="1"/>
-    </row>
-    <row r="105" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD104" s="1"/>
+      <c r="AE104" s="1"/>
+      <c r="AF104" s="1"/>
+      <c r="AG104" s="1"/>
+      <c r="AH104" s="1"/>
+      <c r="AI104" s="1"/>
+    </row>
+    <row r="105" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A105" s="3">
         <v>102</v>
       </c>
@@ -6004,8 +6720,14 @@
       <c r="AA105" s="1"/>
       <c r="AB105" s="1"/>
       <c r="AC105" s="1"/>
-    </row>
-    <row r="106" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD105" s="1"/>
+      <c r="AE105" s="1"/>
+      <c r="AF105" s="1"/>
+      <c r="AG105" s="1"/>
+      <c r="AH105" s="1"/>
+      <c r="AI105" s="1"/>
+    </row>
+    <row r="106" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A106" s="3">
         <v>103</v>
       </c>
@@ -6039,8 +6761,14 @@
       <c r="AA106" s="1"/>
       <c r="AB106" s="1"/>
       <c r="AC106" s="1"/>
-    </row>
-    <row r="107" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD106" s="1"/>
+      <c r="AE106" s="1"/>
+      <c r="AF106" s="1"/>
+      <c r="AG106" s="1"/>
+      <c r="AH106" s="1"/>
+      <c r="AI106" s="1"/>
+    </row>
+    <row r="107" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A107" s="3">
         <v>104</v>
       </c>
@@ -6076,8 +6804,14 @@
       <c r="AA107" s="1"/>
       <c r="AB107" s="1"/>
       <c r="AC107" s="1"/>
-    </row>
-    <row r="108" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD107" s="1"/>
+      <c r="AE107" s="1"/>
+      <c r="AF107" s="1"/>
+      <c r="AG107" s="1"/>
+      <c r="AH107" s="1"/>
+      <c r="AI107" s="1"/>
+    </row>
+    <row r="108" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A108" s="3">
         <v>105</v>
       </c>
@@ -6111,8 +6845,14 @@
       <c r="AA108" s="1"/>
       <c r="AB108" s="1"/>
       <c r="AC108" s="1"/>
-    </row>
-    <row r="109" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD108" s="1"/>
+      <c r="AE108" s="1"/>
+      <c r="AF108" s="1"/>
+      <c r="AG108" s="1"/>
+      <c r="AH108" s="1"/>
+      <c r="AI108" s="1"/>
+    </row>
+    <row r="109" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A109" s="3">
         <v>106</v>
       </c>
@@ -6148,8 +6888,14 @@
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
       <c r="AC109" s="1"/>
-    </row>
-    <row r="110" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD109" s="1"/>
+      <c r="AE109" s="1"/>
+      <c r="AF109" s="1"/>
+      <c r="AG109" s="1"/>
+      <c r="AH109" s="1"/>
+      <c r="AI109" s="1"/>
+    </row>
+    <row r="110" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A110" s="3">
         <v>107</v>
       </c>
@@ -6183,8 +6929,14 @@
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
       <c r="AC110" s="1"/>
-    </row>
-    <row r="111" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD110" s="1"/>
+      <c r="AE110" s="1"/>
+      <c r="AF110" s="1"/>
+      <c r="AG110" s="1"/>
+      <c r="AH110" s="1"/>
+      <c r="AI110" s="1"/>
+    </row>
+    <row r="111" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A111" s="3">
         <v>108</v>
       </c>
@@ -6218,8 +6970,14 @@
       <c r="AA111" s="1"/>
       <c r="AB111" s="1"/>
       <c r="AC111" s="1"/>
-    </row>
-    <row r="112" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD111" s="1"/>
+      <c r="AE111" s="1"/>
+      <c r="AF111" s="1"/>
+      <c r="AG111" s="1"/>
+      <c r="AH111" s="1"/>
+      <c r="AI111" s="1"/>
+    </row>
+    <row r="112" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A112" s="3">
         <v>109</v>
       </c>
@@ -6259,8 +7017,14 @@
       <c r="AA112" s="1"/>
       <c r="AB112" s="1"/>
       <c r="AC112" s="1"/>
-    </row>
-    <row r="113" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD112" s="1"/>
+      <c r="AE112" s="1"/>
+      <c r="AF112" s="1"/>
+      <c r="AG112" s="1"/>
+      <c r="AH112" s="1"/>
+      <c r="AI112" s="1"/>
+    </row>
+    <row r="113" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A113" s="3">
         <v>110</v>
       </c>
@@ -6296,8 +7060,14 @@
       <c r="AA113" s="1"/>
       <c r="AB113" s="1"/>
       <c r="AC113" s="1"/>
-    </row>
-    <row r="114" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD113" s="1"/>
+      <c r="AE113" s="1"/>
+      <c r="AF113" s="1"/>
+      <c r="AG113" s="1"/>
+      <c r="AH113" s="1"/>
+      <c r="AI113" s="1"/>
+    </row>
+    <row r="114" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A114" s="3">
         <v>111</v>
       </c>
@@ -6331,8 +7101,14 @@
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
       <c r="AC114" s="1"/>
-    </row>
-    <row r="115" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD114" s="1"/>
+      <c r="AE114" s="1"/>
+      <c r="AF114" s="1"/>
+      <c r="AG114" s="1"/>
+      <c r="AH114" s="1"/>
+      <c r="AI114" s="1"/>
+    </row>
+    <row r="115" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A115" s="3">
         <v>112</v>
       </c>
@@ -6368,8 +7144,14 @@
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
       <c r="AC115" s="1"/>
-    </row>
-    <row r="116" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD115" s="1"/>
+      <c r="AE115" s="1"/>
+      <c r="AF115" s="1"/>
+      <c r="AG115" s="1"/>
+      <c r="AH115" s="1"/>
+      <c r="AI115" s="1"/>
+    </row>
+    <row r="116" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A116" s="3">
         <v>113</v>
       </c>
@@ -6403,8 +7185,14 @@
       <c r="AA116" s="1"/>
       <c r="AB116" s="1"/>
       <c r="AC116" s="1"/>
-    </row>
-    <row r="117" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD116" s="1"/>
+      <c r="AE116" s="1"/>
+      <c r="AF116" s="1"/>
+      <c r="AG116" s="1"/>
+      <c r="AH116" s="1"/>
+      <c r="AI116" s="1"/>
+    </row>
+    <row r="117" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A117" s="3">
         <v>114</v>
       </c>
@@ -6438,8 +7226,14 @@
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
       <c r="AC117" s="1"/>
-    </row>
-    <row r="118" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD117" s="1"/>
+      <c r="AE117" s="1"/>
+      <c r="AF117" s="1"/>
+      <c r="AG117" s="1"/>
+      <c r="AH117" s="1"/>
+      <c r="AI117" s="1"/>
+    </row>
+    <row r="118" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A118" s="3">
         <v>115</v>
       </c>
@@ -6473,8 +7267,14 @@
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
       <c r="AC118" s="1"/>
-    </row>
-    <row r="119" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD118" s="1"/>
+      <c r="AE118" s="1"/>
+      <c r="AF118" s="1"/>
+      <c r="AG118" s="1"/>
+      <c r="AH118" s="1"/>
+      <c r="AI118" s="1"/>
+    </row>
+    <row r="119" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A119" s="3">
         <v>116</v>
       </c>
@@ -6508,8 +7308,14 @@
       <c r="AA119" s="1"/>
       <c r="AB119" s="1"/>
       <c r="AC119" s="1"/>
-    </row>
-    <row r="120" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD119" s="1"/>
+      <c r="AE119" s="1"/>
+      <c r="AF119" s="1"/>
+      <c r="AG119" s="1"/>
+      <c r="AH119" s="1"/>
+      <c r="AI119" s="1"/>
+    </row>
+    <row r="120" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A120" s="3">
         <v>117</v>
       </c>
@@ -6543,8 +7349,14 @@
       <c r="AA120" s="1"/>
       <c r="AB120" s="1"/>
       <c r="AC120" s="1"/>
-    </row>
-    <row r="121" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD120" s="1"/>
+      <c r="AE120" s="1"/>
+      <c r="AF120" s="1"/>
+      <c r="AG120" s="1"/>
+      <c r="AH120" s="1"/>
+      <c r="AI120" s="1"/>
+    </row>
+    <row r="121" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A121" s="3">
         <v>118</v>
       </c>
@@ -6578,8 +7390,14 @@
       <c r="AA121" s="1"/>
       <c r="AB121" s="1"/>
       <c r="AC121" s="1"/>
-    </row>
-    <row r="122" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD121" s="1"/>
+      <c r="AE121" s="1"/>
+      <c r="AF121" s="1"/>
+      <c r="AG121" s="1"/>
+      <c r="AH121" s="1"/>
+      <c r="AI121" s="1"/>
+    </row>
+    <row r="122" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A122" s="3">
         <v>119</v>
       </c>
@@ -6613,8 +7431,14 @@
       <c r="AA122" s="1"/>
       <c r="AB122" s="1"/>
       <c r="AC122" s="1"/>
-    </row>
-    <row r="123" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD122" s="1"/>
+      <c r="AE122" s="1"/>
+      <c r="AF122" s="1"/>
+      <c r="AG122" s="1"/>
+      <c r="AH122" s="1"/>
+      <c r="AI122" s="1"/>
+    </row>
+    <row r="123" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A123" s="3">
         <v>120</v>
       </c>
@@ -6648,8 +7472,14 @@
       <c r="AA123" s="1"/>
       <c r="AB123" s="1"/>
       <c r="AC123" s="1"/>
-    </row>
-    <row r="124" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD123" s="1"/>
+      <c r="AE123" s="1"/>
+      <c r="AF123" s="1"/>
+      <c r="AG123" s="1"/>
+      <c r="AH123" s="1"/>
+      <c r="AI123" s="1"/>
+    </row>
+    <row r="124" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A124" s="3">
         <v>121</v>
       </c>
@@ -6683,8 +7513,14 @@
       <c r="AA124" s="1"/>
       <c r="AB124" s="1"/>
       <c r="AC124" s="1"/>
-    </row>
-    <row r="125" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD124" s="1"/>
+      <c r="AE124" s="1"/>
+      <c r="AF124" s="1"/>
+      <c r="AG124" s="1"/>
+      <c r="AH124" s="1"/>
+      <c r="AI124" s="1"/>
+    </row>
+    <row r="125" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A125" s="3">
         <v>122</v>
       </c>
@@ -6718,8 +7554,14 @@
       <c r="AA125" s="1"/>
       <c r="AB125" s="1"/>
       <c r="AC125" s="1"/>
-    </row>
-    <row r="126" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD125" s="1"/>
+      <c r="AE125" s="1"/>
+      <c r="AF125" s="1"/>
+      <c r="AG125" s="1"/>
+      <c r="AH125" s="1"/>
+      <c r="AI125" s="1"/>
+    </row>
+    <row r="126" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A126" s="3">
         <v>123</v>
       </c>
@@ -6755,8 +7597,14 @@
       <c r="AA126" s="1"/>
       <c r="AB126" s="1"/>
       <c r="AC126" s="1"/>
-    </row>
-    <row r="127" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD126" s="1"/>
+      <c r="AE126" s="1"/>
+      <c r="AF126" s="1"/>
+      <c r="AG126" s="1"/>
+      <c r="AH126" s="1"/>
+      <c r="AI126" s="1"/>
+    </row>
+    <row r="127" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A127" s="3">
         <v>124</v>
       </c>
@@ -6790,8 +7638,14 @@
       <c r="AA127" s="1"/>
       <c r="AB127" s="1"/>
       <c r="AC127" s="1"/>
-    </row>
-    <row r="128" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD127" s="1"/>
+      <c r="AE127" s="1"/>
+      <c r="AF127" s="1"/>
+      <c r="AG127" s="1"/>
+      <c r="AH127" s="1"/>
+      <c r="AI127" s="1"/>
+    </row>
+    <row r="128" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A128" s="3">
         <v>125</v>
       </c>
@@ -6829,8 +7683,14 @@
       <c r="AA128" s="1"/>
       <c r="AB128" s="1"/>
       <c r="AC128" s="1"/>
-    </row>
-    <row r="129" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD128" s="1"/>
+      <c r="AE128" s="1"/>
+      <c r="AF128" s="1"/>
+      <c r="AG128" s="1"/>
+      <c r="AH128" s="1"/>
+      <c r="AI128" s="1"/>
+    </row>
+    <row r="129" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A129" s="3">
         <v>126</v>
       </c>
@@ -6866,8 +7726,14 @@
       <c r="AA129" s="1"/>
       <c r="AB129" s="1"/>
       <c r="AC129" s="1"/>
-    </row>
-    <row r="130" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD129" s="1"/>
+      <c r="AE129" s="1"/>
+      <c r="AF129" s="1"/>
+      <c r="AG129" s="1"/>
+      <c r="AH129" s="1"/>
+      <c r="AI129" s="1"/>
+    </row>
+    <row r="130" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A130" s="3">
         <v>127</v>
       </c>
@@ -6905,8 +7771,14 @@
       <c r="AA130" s="1"/>
       <c r="AB130" s="1"/>
       <c r="AC130" s="1"/>
-    </row>
-    <row r="131" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD130" s="1"/>
+      <c r="AE130" s="1"/>
+      <c r="AF130" s="1"/>
+      <c r="AG130" s="1"/>
+      <c r="AH130" s="1"/>
+      <c r="AI130" s="1"/>
+    </row>
+    <row r="131" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A131" s="3">
         <v>128</v>
       </c>
@@ -6942,8 +7814,14 @@
       <c r="AA131" s="1"/>
       <c r="AB131" s="1"/>
       <c r="AC131" s="1"/>
-    </row>
-    <row r="132" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD131" s="1"/>
+      <c r="AE131" s="1"/>
+      <c r="AF131" s="1"/>
+      <c r="AG131" s="1"/>
+      <c r="AH131" s="1"/>
+      <c r="AI131" s="1"/>
+    </row>
+    <row r="132" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A132" s="3">
         <v>129</v>
       </c>
@@ -6977,8 +7855,14 @@
       <c r="AA132" s="1"/>
       <c r="AB132" s="1"/>
       <c r="AC132" s="1"/>
-    </row>
-    <row r="133" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD132" s="1"/>
+      <c r="AE132" s="1"/>
+      <c r="AF132" s="1"/>
+      <c r="AG132" s="1"/>
+      <c r="AH132" s="1"/>
+      <c r="AI132" s="1"/>
+    </row>
+    <row r="133" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A133" s="3">
         <v>130</v>
       </c>
@@ -7012,8 +7896,14 @@
       <c r="AA133" s="1"/>
       <c r="AB133" s="1"/>
       <c r="AC133" s="1"/>
-    </row>
-    <row r="134" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD133" s="1"/>
+      <c r="AE133" s="1"/>
+      <c r="AF133" s="1"/>
+      <c r="AG133" s="1"/>
+      <c r="AH133" s="1"/>
+      <c r="AI133" s="1"/>
+    </row>
+    <row r="134" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A134" s="3">
         <v>131</v>
       </c>
@@ -7047,8 +7937,14 @@
       <c r="AA134" s="1"/>
       <c r="AB134" s="1"/>
       <c r="AC134" s="1"/>
-    </row>
-    <row r="135" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD134" s="1"/>
+      <c r="AE134" s="1"/>
+      <c r="AF134" s="1"/>
+      <c r="AG134" s="1"/>
+      <c r="AH134" s="1"/>
+      <c r="AI134" s="1"/>
+    </row>
+    <row r="135" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A135" s="3">
         <v>132</v>
       </c>
@@ -7082,8 +7978,14 @@
       <c r="AA135" s="1"/>
       <c r="AB135" s="1"/>
       <c r="AC135" s="1"/>
-    </row>
-    <row r="136" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD135" s="1"/>
+      <c r="AE135" s="1"/>
+      <c r="AF135" s="1"/>
+      <c r="AG135" s="1"/>
+      <c r="AH135" s="1"/>
+      <c r="AI135" s="1"/>
+    </row>
+    <row r="136" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A136" s="3">
         <v>133</v>
       </c>
@@ -7117,8 +8019,14 @@
       <c r="AA136" s="1"/>
       <c r="AB136" s="1"/>
       <c r="AC136" s="1"/>
-    </row>
-    <row r="137" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD136" s="1"/>
+      <c r="AE136" s="1"/>
+      <c r="AF136" s="1"/>
+      <c r="AG136" s="1"/>
+      <c r="AH136" s="1"/>
+      <c r="AI136" s="1"/>
+    </row>
+    <row r="137" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A137" s="3">
         <v>134</v>
       </c>
@@ -7152,8 +8060,14 @@
       <c r="AA137" s="1"/>
       <c r="AB137" s="1"/>
       <c r="AC137" s="1"/>
-    </row>
-    <row r="138" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD137" s="1"/>
+      <c r="AE137" s="1"/>
+      <c r="AF137" s="1"/>
+      <c r="AG137" s="1"/>
+      <c r="AH137" s="1"/>
+      <c r="AI137" s="1"/>
+    </row>
+    <row r="138" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A138" s="3">
         <v>135</v>
       </c>
@@ -7187,8 +8101,14 @@
       <c r="AA138" s="1"/>
       <c r="AB138" s="1"/>
       <c r="AC138" s="1"/>
-    </row>
-    <row r="139" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD138" s="1"/>
+      <c r="AE138" s="1"/>
+      <c r="AF138" s="1"/>
+      <c r="AG138" s="1"/>
+      <c r="AH138" s="1"/>
+      <c r="AI138" s="1"/>
+    </row>
+    <row r="139" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A139" s="3">
         <v>136</v>
       </c>
@@ -7222,8 +8142,14 @@
       <c r="AA139" s="1"/>
       <c r="AB139" s="1"/>
       <c r="AC139" s="1"/>
-    </row>
-    <row r="140" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD139" s="1"/>
+      <c r="AE139" s="1"/>
+      <c r="AF139" s="1"/>
+      <c r="AG139" s="1"/>
+      <c r="AH139" s="1"/>
+      <c r="AI139" s="1"/>
+    </row>
+    <row r="140" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A140" s="3">
         <v>137</v>
       </c>
@@ -7257,8 +8183,14 @@
       <c r="AA140" s="1"/>
       <c r="AB140" s="1"/>
       <c r="AC140" s="1"/>
-    </row>
-    <row r="141" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD140" s="1"/>
+      <c r="AE140" s="1"/>
+      <c r="AF140" s="1"/>
+      <c r="AG140" s="1"/>
+      <c r="AH140" s="1"/>
+      <c r="AI140" s="1"/>
+    </row>
+    <row r="141" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A141" s="3">
         <v>138</v>
       </c>
@@ -7292,8 +8224,14 @@
       <c r="AA141" s="1"/>
       <c r="AB141" s="1"/>
       <c r="AC141" s="1"/>
-    </row>
-    <row r="142" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD141" s="1"/>
+      <c r="AE141" s="1"/>
+      <c r="AF141" s="1"/>
+      <c r="AG141" s="1"/>
+      <c r="AH141" s="1"/>
+      <c r="AI141" s="1"/>
+    </row>
+    <row r="142" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A142" s="3">
         <v>139</v>
       </c>
@@ -7327,8 +8265,14 @@
       <c r="AA142" s="1"/>
       <c r="AB142" s="1"/>
       <c r="AC142" s="1"/>
-    </row>
-    <row r="143" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD142" s="1"/>
+      <c r="AE142" s="1"/>
+      <c r="AF142" s="1"/>
+      <c r="AG142" s="1"/>
+      <c r="AH142" s="1"/>
+      <c r="AI142" s="1"/>
+    </row>
+    <row r="143" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A143" s="3">
         <v>140</v>
       </c>
@@ -7362,8 +8306,14 @@
       <c r="AA143" s="1"/>
       <c r="AB143" s="1"/>
       <c r="AC143" s="1"/>
-    </row>
-    <row r="144" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD143" s="1"/>
+      <c r="AE143" s="1"/>
+      <c r="AF143" s="1"/>
+      <c r="AG143" s="1"/>
+      <c r="AH143" s="1"/>
+      <c r="AI143" s="1"/>
+    </row>
+    <row r="144" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A144" s="3">
         <v>141</v>
       </c>
@@ -7397,8 +8347,14 @@
       <c r="AA144" s="1"/>
       <c r="AB144" s="1"/>
       <c r="AC144" s="1"/>
-    </row>
-    <row r="145" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD144" s="1"/>
+      <c r="AE144" s="1"/>
+      <c r="AF144" s="1"/>
+      <c r="AG144" s="1"/>
+      <c r="AH144" s="1"/>
+      <c r="AI144" s="1"/>
+    </row>
+    <row r="145" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A145" s="3">
         <v>142</v>
       </c>
@@ -7432,8 +8388,14 @@
       <c r="AA145" s="1"/>
       <c r="AB145" s="1"/>
       <c r="AC145" s="1"/>
-    </row>
-    <row r="146" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD145" s="1"/>
+      <c r="AE145" s="1"/>
+      <c r="AF145" s="1"/>
+      <c r="AG145" s="1"/>
+      <c r="AH145" s="1"/>
+      <c r="AI145" s="1"/>
+    </row>
+    <row r="146" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A146" s="3">
         <v>143</v>
       </c>
@@ -7467,8 +8429,14 @@
       <c r="AA146" s="1"/>
       <c r="AB146" s="1"/>
       <c r="AC146" s="1"/>
-    </row>
-    <row r="147" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD146" s="1"/>
+      <c r="AE146" s="1"/>
+      <c r="AF146" s="1"/>
+      <c r="AG146" s="1"/>
+      <c r="AH146" s="1"/>
+      <c r="AI146" s="1"/>
+    </row>
+    <row r="147" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A147" s="3">
         <v>144</v>
       </c>
@@ -7502,8 +8470,14 @@
       <c r="AA147" s="1"/>
       <c r="AB147" s="1"/>
       <c r="AC147" s="1"/>
-    </row>
-    <row r="148" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD147" s="1"/>
+      <c r="AE147" s="1"/>
+      <c r="AF147" s="1"/>
+      <c r="AG147" s="1"/>
+      <c r="AH147" s="1"/>
+      <c r="AI147" s="1"/>
+    </row>
+    <row r="148" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A148" s="3">
         <v>145</v>
       </c>
@@ -7539,8 +8513,14 @@
       <c r="AA148" s="1"/>
       <c r="AB148" s="1"/>
       <c r="AC148" s="1"/>
-    </row>
-    <row r="149" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD148" s="1"/>
+      <c r="AE148" s="1"/>
+      <c r="AF148" s="1"/>
+      <c r="AG148" s="1"/>
+      <c r="AH148" s="1"/>
+      <c r="AI148" s="1"/>
+    </row>
+    <row r="149" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A149" s="3">
         <v>146</v>
       </c>
@@ -7574,8 +8554,14 @@
       <c r="AA149" s="1"/>
       <c r="AB149" s="1"/>
       <c r="AC149" s="1"/>
-    </row>
-    <row r="150" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD149" s="1"/>
+      <c r="AE149" s="1"/>
+      <c r="AF149" s="1"/>
+      <c r="AG149" s="1"/>
+      <c r="AH149" s="1"/>
+      <c r="AI149" s="1"/>
+    </row>
+    <row r="150" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A150" s="3">
         <v>147</v>
       </c>
@@ -7609,8 +8595,14 @@
       <c r="AA150" s="1"/>
       <c r="AB150" s="1"/>
       <c r="AC150" s="1"/>
-    </row>
-    <row r="151" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD150" s="1"/>
+      <c r="AE150" s="1"/>
+      <c r="AF150" s="1"/>
+      <c r="AG150" s="1"/>
+      <c r="AH150" s="1"/>
+      <c r="AI150" s="1"/>
+    </row>
+    <row r="151" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A151" s="3">
         <v>148</v>
       </c>
@@ -7644,8 +8636,14 @@
       <c r="AA151" s="1"/>
       <c r="AB151" s="1"/>
       <c r="AC151" s="1"/>
-    </row>
-    <row r="152" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD151" s="1"/>
+      <c r="AE151" s="1"/>
+      <c r="AF151" s="1"/>
+      <c r="AG151" s="1"/>
+      <c r="AH151" s="1"/>
+      <c r="AI151" s="1"/>
+    </row>
+    <row r="152" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A152" s="3">
         <v>149</v>
       </c>
@@ -7679,8 +8677,14 @@
       <c r="AA152" s="1"/>
       <c r="AB152" s="1"/>
       <c r="AC152" s="1"/>
-    </row>
-    <row r="153" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD152" s="1"/>
+      <c r="AE152" s="1"/>
+      <c r="AF152" s="1"/>
+      <c r="AG152" s="1"/>
+      <c r="AH152" s="1"/>
+      <c r="AI152" s="1"/>
+    </row>
+    <row r="153" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A153" s="3">
         <v>150</v>
       </c>
@@ -7716,8 +8720,14 @@
       <c r="AA153" s="1"/>
       <c r="AB153" s="1"/>
       <c r="AC153" s="1"/>
-    </row>
-    <row r="154" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD153" s="1"/>
+      <c r="AE153" s="1"/>
+      <c r="AF153" s="1"/>
+      <c r="AG153" s="1"/>
+      <c r="AH153" s="1"/>
+      <c r="AI153" s="1"/>
+    </row>
+    <row r="154" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A154" s="3">
         <v>151</v>
       </c>
@@ -7753,8 +8763,14 @@
       <c r="AA154" s="1"/>
       <c r="AB154" s="1"/>
       <c r="AC154" s="1"/>
-    </row>
-    <row r="155" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD154" s="1"/>
+      <c r="AE154" s="1"/>
+      <c r="AF154" s="1"/>
+      <c r="AG154" s="1"/>
+      <c r="AH154" s="1"/>
+      <c r="AI154" s="1"/>
+    </row>
+    <row r="155" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A155" s="3">
         <v>152</v>
       </c>
@@ -7792,8 +8808,14 @@
       <c r="AA155" s="1"/>
       <c r="AB155" s="1"/>
       <c r="AC155" s="1"/>
-    </row>
-    <row r="156" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD155" s="1"/>
+      <c r="AE155" s="1"/>
+      <c r="AF155" s="1"/>
+      <c r="AG155" s="1"/>
+      <c r="AH155" s="1"/>
+      <c r="AI155" s="1"/>
+    </row>
+    <row r="156" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A156" s="3">
         <v>153</v>
       </c>
@@ -7829,8 +8851,14 @@
       <c r="AA156" s="1"/>
       <c r="AB156" s="1"/>
       <c r="AC156" s="1"/>
-    </row>
-    <row r="157" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD156" s="1"/>
+      <c r="AE156" s="1"/>
+      <c r="AF156" s="1"/>
+      <c r="AG156" s="1"/>
+      <c r="AH156" s="1"/>
+      <c r="AI156" s="1"/>
+    </row>
+    <row r="157" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A157" s="3">
         <v>154</v>
       </c>
@@ -7866,8 +8894,14 @@
       <c r="AA157" s="1"/>
       <c r="AB157" s="1"/>
       <c r="AC157" s="1"/>
-    </row>
-    <row r="158" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD157" s="1"/>
+      <c r="AE157" s="1"/>
+      <c r="AF157" s="1"/>
+      <c r="AG157" s="1"/>
+      <c r="AH157" s="1"/>
+      <c r="AI157" s="1"/>
+    </row>
+    <row r="158" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A158" s="3">
         <v>155</v>
       </c>
@@ -7905,8 +8939,14 @@
       <c r="AA158" s="1"/>
       <c r="AB158" s="1"/>
       <c r="AC158" s="1"/>
-    </row>
-    <row r="159" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD158" s="1"/>
+      <c r="AE158" s="1"/>
+      <c r="AF158" s="1"/>
+      <c r="AG158" s="1"/>
+      <c r="AH158" s="1"/>
+      <c r="AI158" s="1"/>
+    </row>
+    <row r="159" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A159" s="3">
         <v>156</v>
       </c>
@@ -7942,8 +8982,14 @@
       <c r="AA159" s="1"/>
       <c r="AB159" s="1"/>
       <c r="AC159" s="1"/>
-    </row>
-    <row r="160" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD159" s="1"/>
+      <c r="AE159" s="1"/>
+      <c r="AF159" s="1"/>
+      <c r="AG159" s="1"/>
+      <c r="AH159" s="1"/>
+      <c r="AI159" s="1"/>
+    </row>
+    <row r="160" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A160" s="3">
         <v>157</v>
       </c>
@@ -7981,8 +9027,14 @@
       <c r="AA160" s="1"/>
       <c r="AB160" s="1"/>
       <c r="AC160" s="1"/>
-    </row>
-    <row r="161" spans="1:29" ht="15" customHeight="1">
+      <c r="AD160" s="1"/>
+      <c r="AE160" s="1"/>
+      <c r="AF160" s="1"/>
+      <c r="AG160" s="1"/>
+      <c r="AH160" s="1"/>
+      <c r="AI160" s="1"/>
+    </row>
+    <row r="161" spans="1:35" ht="15" customHeight="1">
       <c r="A161" s="3">
         <v>158</v>
       </c>
@@ -8018,8 +9070,14 @@
       <c r="AA161" s="1"/>
       <c r="AB161" s="1"/>
       <c r="AC161" s="1"/>
-    </row>
-    <row r="162" spans="1:29" ht="15" customHeight="1">
+      <c r="AD161" s="1"/>
+      <c r="AE161" s="1"/>
+      <c r="AF161" s="1"/>
+      <c r="AG161" s="1"/>
+      <c r="AH161" s="1"/>
+      <c r="AI161" s="1"/>
+    </row>
+    <row r="162" spans="1:35" ht="15" customHeight="1">
       <c r="A162" s="3">
         <v>159</v>
       </c>
@@ -8055,8 +9113,14 @@
       <c r="AA162" s="1"/>
       <c r="AB162" s="1"/>
       <c r="AC162" s="1"/>
-    </row>
-    <row r="163" spans="1:29" ht="15" customHeight="1">
+      <c r="AD162" s="1"/>
+      <c r="AE162" s="1"/>
+      <c r="AF162" s="1"/>
+      <c r="AG162" s="1"/>
+      <c r="AH162" s="1"/>
+      <c r="AI162" s="1"/>
+    </row>
+    <row r="163" spans="1:35" ht="15" customHeight="1">
       <c r="A163" s="3">
         <v>160</v>
       </c>
@@ -8094,8 +9158,14 @@
       <c r="AA163" s="1"/>
       <c r="AB163" s="1"/>
       <c r="AC163" s="1"/>
-    </row>
-    <row r="164" spans="1:29" ht="15" customHeight="1">
+      <c r="AD163" s="1"/>
+      <c r="AE163" s="1"/>
+      <c r="AF163" s="1"/>
+      <c r="AG163" s="1"/>
+      <c r="AH163" s="1"/>
+      <c r="AI163" s="1"/>
+    </row>
+    <row r="164" spans="1:35" ht="15" customHeight="1">
       <c r="A164" s="3">
         <v>161</v>
       </c>
@@ -8131,8 +9201,14 @@
       <c r="AA164" s="3"/>
       <c r="AB164" s="3"/>
       <c r="AC164" s="3"/>
-    </row>
-    <row r="165" spans="1:29" ht="15" customHeight="1">
+      <c r="AD164" s="3"/>
+      <c r="AE164" s="3"/>
+      <c r="AF164" s="3"/>
+      <c r="AG164" s="3"/>
+      <c r="AH164" s="3"/>
+      <c r="AI164" s="3"/>
+    </row>
+    <row r="165" spans="1:35" ht="15" customHeight="1">
       <c r="A165" s="3">
         <v>162</v>
       </c>
@@ -8168,8 +9244,14 @@
       <c r="AA165" s="3"/>
       <c r="AB165" s="3"/>
       <c r="AC165" s="3"/>
-    </row>
-    <row r="166" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD165" s="3"/>
+      <c r="AE165" s="3"/>
+      <c r="AF165" s="3"/>
+      <c r="AG165" s="3"/>
+      <c r="AH165" s="3"/>
+      <c r="AI165" s="3"/>
+    </row>
+    <row r="166" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A166" s="3">
         <v>163</v>
       </c>
@@ -8203,8 +9285,14 @@
       <c r="AA166" s="1"/>
       <c r="AB166" s="1"/>
       <c r="AC166" s="1"/>
-    </row>
-    <row r="167" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD166" s="1"/>
+      <c r="AE166" s="1"/>
+      <c r="AF166" s="1"/>
+      <c r="AG166" s="1"/>
+      <c r="AH166" s="1"/>
+      <c r="AI166" s="1"/>
+    </row>
+    <row r="167" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A167" s="3">
         <v>164</v>
       </c>
@@ -8238,8 +9326,14 @@
       <c r="AA167" s="1"/>
       <c r="AB167" s="1"/>
       <c r="AC167" s="1"/>
-    </row>
-    <row r="168" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD167" s="1"/>
+      <c r="AE167" s="1"/>
+      <c r="AF167" s="1"/>
+      <c r="AG167" s="1"/>
+      <c r="AH167" s="1"/>
+      <c r="AI167" s="1"/>
+    </row>
+    <row r="168" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A168" s="3">
         <v>165</v>
       </c>
@@ -8273,8 +9367,14 @@
       <c r="AA168" s="1"/>
       <c r="AB168" s="1"/>
       <c r="AC168" s="1"/>
-    </row>
-    <row r="169" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD168" s="1"/>
+      <c r="AE168" s="1"/>
+      <c r="AF168" s="1"/>
+      <c r="AG168" s="1"/>
+      <c r="AH168" s="1"/>
+      <c r="AI168" s="1"/>
+    </row>
+    <row r="169" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A169" s="3">
         <v>166</v>
       </c>
@@ -8308,8 +9408,14 @@
       <c r="AA169" s="1"/>
       <c r="AB169" s="1"/>
       <c r="AC169" s="1"/>
-    </row>
-    <row r="170" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD169" s="1"/>
+      <c r="AE169" s="1"/>
+      <c r="AF169" s="1"/>
+      <c r="AG169" s="1"/>
+      <c r="AH169" s="1"/>
+      <c r="AI169" s="1"/>
+    </row>
+    <row r="170" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A170" s="3">
         <v>167</v>
       </c>
@@ -8343,8 +9449,14 @@
       <c r="AA170" s="1"/>
       <c r="AB170" s="1"/>
       <c r="AC170" s="1"/>
-    </row>
-    <row r="171" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD170" s="1"/>
+      <c r="AE170" s="1"/>
+      <c r="AF170" s="1"/>
+      <c r="AG170" s="1"/>
+      <c r="AH170" s="1"/>
+      <c r="AI170" s="1"/>
+    </row>
+    <row r="171" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A171" s="3">
         <v>168</v>
       </c>
@@ -8378,8 +9490,14 @@
       <c r="AA171" s="1"/>
       <c r="AB171" s="1"/>
       <c r="AC171" s="1"/>
-    </row>
-    <row r="172" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD171" s="1"/>
+      <c r="AE171" s="1"/>
+      <c r="AF171" s="1"/>
+      <c r="AG171" s="1"/>
+      <c r="AH171" s="1"/>
+      <c r="AI171" s="1"/>
+    </row>
+    <row r="172" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A172" s="3">
         <v>169</v>
       </c>
@@ -8415,8 +9533,14 @@
       <c r="AA172" s="1"/>
       <c r="AB172" s="1"/>
       <c r="AC172" s="1"/>
-    </row>
-    <row r="173" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD172" s="1"/>
+      <c r="AE172" s="1"/>
+      <c r="AF172" s="1"/>
+      <c r="AG172" s="1"/>
+      <c r="AH172" s="1"/>
+      <c r="AI172" s="1"/>
+    </row>
+    <row r="173" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A173" s="3">
         <v>170</v>
       </c>
@@ -8450,8 +9574,14 @@
       <c r="AA173" s="1"/>
       <c r="AB173" s="1"/>
       <c r="AC173" s="1"/>
-    </row>
-    <row r="174" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD173" s="1"/>
+      <c r="AE173" s="1"/>
+      <c r="AF173" s="1"/>
+      <c r="AG173" s="1"/>
+      <c r="AH173" s="1"/>
+      <c r="AI173" s="1"/>
+    </row>
+    <row r="174" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A174" s="3">
         <v>171</v>
       </c>
@@ -8495,8 +9625,14 @@
       <c r="AA174" s="1"/>
       <c r="AB174" s="1"/>
       <c r="AC174" s="1"/>
-    </row>
-    <row r="175" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD174" s="1"/>
+      <c r="AE174" s="1"/>
+      <c r="AF174" s="1"/>
+      <c r="AG174" s="1"/>
+      <c r="AH174" s="1"/>
+      <c r="AI174" s="1"/>
+    </row>
+    <row r="175" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A175" s="3">
         <v>172</v>
       </c>
@@ -8536,8 +9672,14 @@
       <c r="AA175" s="1"/>
       <c r="AB175" s="1"/>
       <c r="AC175" s="1"/>
-    </row>
-    <row r="176" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD175" s="1"/>
+      <c r="AE175" s="1"/>
+      <c r="AF175" s="1"/>
+      <c r="AG175" s="1"/>
+      <c r="AH175" s="1"/>
+      <c r="AI175" s="1"/>
+    </row>
+    <row r="176" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A176" s="3">
         <v>173</v>
       </c>
@@ -8581,8 +9723,14 @@
       <c r="AA176" s="1"/>
       <c r="AB176" s="1"/>
       <c r="AC176" s="1"/>
-    </row>
-    <row r="177" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD176" s="1"/>
+      <c r="AE176" s="1"/>
+      <c r="AF176" s="1"/>
+      <c r="AG176" s="1"/>
+      <c r="AH176" s="1"/>
+      <c r="AI176" s="1"/>
+    </row>
+    <row r="177" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A177" s="3">
         <v>174</v>
       </c>
@@ -8620,8 +9768,14 @@
       <c r="AA177" s="1"/>
       <c r="AB177" s="1"/>
       <c r="AC177" s="1"/>
-    </row>
-    <row r="178" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD177" s="1"/>
+      <c r="AE177" s="1"/>
+      <c r="AF177" s="1"/>
+      <c r="AG177" s="1"/>
+      <c r="AH177" s="1"/>
+      <c r="AI177" s="1"/>
+    </row>
+    <row r="178" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A178" s="3">
         <v>175</v>
       </c>
@@ -8659,8 +9813,14 @@
       <c r="AA178" s="1"/>
       <c r="AB178" s="1"/>
       <c r="AC178" s="1"/>
-    </row>
-    <row r="179" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD178" s="1"/>
+      <c r="AE178" s="1"/>
+      <c r="AF178" s="1"/>
+      <c r="AG178" s="1"/>
+      <c r="AH178" s="1"/>
+      <c r="AI178" s="1"/>
+    </row>
+    <row r="179" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A179" s="3">
         <v>176</v>
       </c>
@@ -8698,8 +9858,14 @@
       <c r="AA179" s="1"/>
       <c r="AB179" s="1"/>
       <c r="AC179" s="1"/>
-    </row>
-    <row r="180" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD179" s="1"/>
+      <c r="AE179" s="1"/>
+      <c r="AF179" s="1"/>
+      <c r="AG179" s="1"/>
+      <c r="AH179" s="1"/>
+      <c r="AI179" s="1"/>
+    </row>
+    <row r="180" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A180" s="3">
         <v>177</v>
       </c>
@@ -8739,8 +9905,14 @@
       <c r="AA180" s="1"/>
       <c r="AB180" s="1"/>
       <c r="AC180" s="1"/>
-    </row>
-    <row r="181" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD180" s="1"/>
+      <c r="AE180" s="1"/>
+      <c r="AF180" s="1"/>
+      <c r="AG180" s="1"/>
+      <c r="AH180" s="1"/>
+      <c r="AI180" s="1"/>
+    </row>
+    <row r="181" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A181" s="3">
         <v>178</v>
       </c>
@@ -8778,8 +9950,14 @@
       <c r="AA181" s="1"/>
       <c r="AB181" s="1"/>
       <c r="AC181" s="1"/>
-    </row>
-    <row r="182" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD181" s="1"/>
+      <c r="AE181" s="1"/>
+      <c r="AF181" s="1"/>
+      <c r="AG181" s="1"/>
+      <c r="AH181" s="1"/>
+      <c r="AI181" s="1"/>
+    </row>
+    <row r="182" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A182" s="3">
         <v>179</v>
       </c>
@@ -8819,8 +9997,14 @@
       <c r="AA182" s="1"/>
       <c r="AB182" s="1"/>
       <c r="AC182" s="1"/>
-    </row>
-    <row r="183" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD182" s="1"/>
+      <c r="AE182" s="1"/>
+      <c r="AF182" s="1"/>
+      <c r="AG182" s="1"/>
+      <c r="AH182" s="1"/>
+      <c r="AI182" s="1"/>
+    </row>
+    <row r="183" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A183" s="3">
         <v>180</v>
       </c>
@@ -8862,8 +10046,14 @@
       <c r="AA183" s="1"/>
       <c r="AB183" s="1"/>
       <c r="AC183" s="1"/>
-    </row>
-    <row r="184" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD183" s="1"/>
+      <c r="AE183" s="1"/>
+      <c r="AF183" s="1"/>
+      <c r="AG183" s="1"/>
+      <c r="AH183" s="1"/>
+      <c r="AI183" s="1"/>
+    </row>
+    <row r="184" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A184" s="3">
         <v>181</v>
       </c>
@@ -8905,8 +10095,14 @@
       <c r="AA184" s="1"/>
       <c r="AB184" s="1"/>
       <c r="AC184" s="1"/>
-    </row>
-    <row r="185" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD184" s="1"/>
+      <c r="AE184" s="1"/>
+      <c r="AF184" s="1"/>
+      <c r="AG184" s="1"/>
+      <c r="AH184" s="1"/>
+      <c r="AI184" s="1"/>
+    </row>
+    <row r="185" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A185" s="3">
         <v>182</v>
       </c>
@@ -8946,8 +10142,14 @@
       <c r="AA185" s="1"/>
       <c r="AB185" s="1"/>
       <c r="AC185" s="1"/>
-    </row>
-    <row r="186" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD185" s="1"/>
+      <c r="AE185" s="1"/>
+      <c r="AF185" s="1"/>
+      <c r="AG185" s="1"/>
+      <c r="AH185" s="1"/>
+      <c r="AI185" s="1"/>
+    </row>
+    <row r="186" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A186" s="3">
         <v>183</v>
       </c>
@@ -8988,17 +10190,17 @@
       <c r="Z186" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="AA186" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AB186" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC186" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="187" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AA186" s="1"/>
+      <c r="AB186" s="1"/>
+      <c r="AC186" s="1"/>
+      <c r="AD186" s="1"/>
+      <c r="AE186" s="1"/>
+      <c r="AF186" s="1"/>
+      <c r="AG186" s="1"/>
+      <c r="AH186" s="1"/>
+      <c r="AI186" s="1"/>
+    </row>
+    <row r="187" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A187" s="3">
         <v>184</v>
       </c>
@@ -9039,17 +10241,17 @@
       <c r="Z187" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="AA187" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AB187" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC187" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="188" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AA187" s="1"/>
+      <c r="AB187" s="1"/>
+      <c r="AC187" s="1"/>
+      <c r="AD187" s="1"/>
+      <c r="AE187" s="1"/>
+      <c r="AF187" s="1"/>
+      <c r="AG187" s="1"/>
+      <c r="AH187" s="1"/>
+      <c r="AI187" s="1"/>
+    </row>
+    <row r="188" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A188" s="3">
         <v>185</v>
       </c>
@@ -9092,17 +10294,17 @@
       <c r="Z188" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="AA188" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AB188" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC188" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="189" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AA188" s="1"/>
+      <c r="AB188" s="1"/>
+      <c r="AC188" s="1"/>
+      <c r="AD188" s="1"/>
+      <c r="AE188" s="1"/>
+      <c r="AF188" s="1"/>
+      <c r="AG188" s="1"/>
+      <c r="AH188" s="1"/>
+      <c r="AI188" s="1"/>
+    </row>
+    <row r="189" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A189" s="3">
         <v>186</v>
       </c>
@@ -9143,17 +10345,17 @@
       <c r="Z189" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="AA189" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AB189" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC189" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="190" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AA189" s="1"/>
+      <c r="AB189" s="1"/>
+      <c r="AC189" s="1"/>
+      <c r="AD189" s="1"/>
+      <c r="AE189" s="1"/>
+      <c r="AF189" s="1"/>
+      <c r="AG189" s="1"/>
+      <c r="AH189" s="1"/>
+      <c r="AI189" s="1"/>
+    </row>
+    <row r="190" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A190" s="3">
         <v>187</v>
       </c>
@@ -9194,17 +10396,17 @@
       <c r="Z190" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="AA190" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AB190" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC190" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="191" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AA190" s="1"/>
+      <c r="AB190" s="1"/>
+      <c r="AC190" s="1"/>
+      <c r="AD190" s="1"/>
+      <c r="AE190" s="1"/>
+      <c r="AF190" s="1"/>
+      <c r="AG190" s="1"/>
+      <c r="AH190" s="1"/>
+      <c r="AI190" s="1"/>
+    </row>
+    <row r="191" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A191" s="3">
         <v>188</v>
       </c>
@@ -9245,17 +10447,17 @@
       <c r="Z191" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="AA191" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AB191" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC191" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="192" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AA191" s="1"/>
+      <c r="AB191" s="1"/>
+      <c r="AC191" s="1"/>
+      <c r="AD191" s="1"/>
+      <c r="AE191" s="1"/>
+      <c r="AF191" s="1"/>
+      <c r="AG191" s="1"/>
+      <c r="AH191" s="1"/>
+      <c r="AI191" s="1"/>
+    </row>
+    <row r="192" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A192" s="3">
         <v>189</v>
       </c>
@@ -9293,8 +10495,14 @@
       <c r="AA192" s="1"/>
       <c r="AB192" s="1"/>
       <c r="AC192" s="1"/>
-    </row>
-    <row r="193" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD192" s="1"/>
+      <c r="AE192" s="1"/>
+      <c r="AF192" s="1"/>
+      <c r="AG192" s="1"/>
+      <c r="AH192" s="1"/>
+      <c r="AI192" s="1"/>
+    </row>
+    <row r="193" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A193" s="3">
         <v>190</v>
       </c>
@@ -9332,8 +10540,14 @@
       <c r="AA193" s="1"/>
       <c r="AB193" s="1"/>
       <c r="AC193" s="1"/>
-    </row>
-    <row r="194" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD193" s="1"/>
+      <c r="AE193" s="1"/>
+      <c r="AF193" s="1"/>
+      <c r="AG193" s="1"/>
+      <c r="AH193" s="1"/>
+      <c r="AI193" s="1"/>
+    </row>
+    <row r="194" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A194" s="3">
         <v>191</v>
       </c>
@@ -9369,8 +10583,14 @@
       <c r="AA194" s="1"/>
       <c r="AB194" s="1"/>
       <c r="AC194" s="1"/>
-    </row>
-    <row r="195" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD194" s="1"/>
+      <c r="AE194" s="1"/>
+      <c r="AF194" s="1"/>
+      <c r="AG194" s="1"/>
+      <c r="AH194" s="1"/>
+      <c r="AI194" s="1"/>
+    </row>
+    <row r="195" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A195" s="3">
         <v>192</v>
       </c>
@@ -9406,8 +10626,14 @@
       <c r="AA195" s="1"/>
       <c r="AB195" s="1"/>
       <c r="AC195" s="1"/>
-    </row>
-    <row r="196" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD195" s="1"/>
+      <c r="AE195" s="1"/>
+      <c r="AF195" s="1"/>
+      <c r="AG195" s="1"/>
+      <c r="AH195" s="1"/>
+      <c r="AI195" s="1"/>
+    </row>
+    <row r="196" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A196" s="3">
         <v>193</v>
       </c>
@@ -9443,8 +10669,14 @@
       <c r="AA196" s="1"/>
       <c r="AB196" s="1"/>
       <c r="AC196" s="1"/>
-    </row>
-    <row r="197" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD196" s="1"/>
+      <c r="AE196" s="1"/>
+      <c r="AF196" s="1"/>
+      <c r="AG196" s="1"/>
+      <c r="AH196" s="1"/>
+      <c r="AI196" s="1"/>
+    </row>
+    <row r="197" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A197" s="3">
         <v>194</v>
       </c>
@@ -9480,8 +10712,14 @@
       <c r="AA197" s="1"/>
       <c r="AB197" s="1"/>
       <c r="AC197" s="1"/>
-    </row>
-    <row r="198" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD197" s="1"/>
+      <c r="AE197" s="1"/>
+      <c r="AF197" s="1"/>
+      <c r="AG197" s="1"/>
+      <c r="AH197" s="1"/>
+      <c r="AI197" s="1"/>
+    </row>
+    <row r="198" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A198" s="3">
         <v>195</v>
       </c>
@@ -9519,8 +10757,14 @@
       <c r="AA198" s="1"/>
       <c r="AB198" s="1"/>
       <c r="AC198" s="1"/>
-    </row>
-    <row r="199" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD198" s="1"/>
+      <c r="AE198" s="1"/>
+      <c r="AF198" s="1"/>
+      <c r="AG198" s="1"/>
+      <c r="AH198" s="1"/>
+      <c r="AI198" s="1"/>
+    </row>
+    <row r="199" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A199" s="3">
         <v>196</v>
       </c>
@@ -9558,8 +10802,14 @@
       <c r="AA199" s="1"/>
       <c r="AB199" s="1"/>
       <c r="AC199" s="1"/>
-    </row>
-    <row r="200" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD199" s="1"/>
+      <c r="AE199" s="1"/>
+      <c r="AF199" s="1"/>
+      <c r="AG199" s="1"/>
+      <c r="AH199" s="1"/>
+      <c r="AI199" s="1"/>
+    </row>
+    <row r="200" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A200" s="3">
         <v>197</v>
       </c>
@@ -9595,8 +10845,14 @@
       <c r="AA200" s="1"/>
       <c r="AB200" s="1"/>
       <c r="AC200" s="1"/>
-    </row>
-    <row r="201" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD200" s="1"/>
+      <c r="AE200" s="1"/>
+      <c r="AF200" s="1"/>
+      <c r="AG200" s="1"/>
+      <c r="AH200" s="1"/>
+      <c r="AI200" s="1"/>
+    </row>
+    <row r="201" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A201" s="3">
         <v>198</v>
       </c>
@@ -9634,8 +10890,14 @@
       <c r="AA201" s="1"/>
       <c r="AB201" s="1"/>
       <c r="AC201" s="1"/>
-    </row>
-    <row r="202" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD201" s="1"/>
+      <c r="AE201" s="1"/>
+      <c r="AF201" s="1"/>
+      <c r="AG201" s="1"/>
+      <c r="AH201" s="1"/>
+      <c r="AI201" s="1"/>
+    </row>
+    <row r="202" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A202" s="3">
         <v>199</v>
       </c>
@@ -9671,8 +10933,14 @@
       <c r="AA202" s="1"/>
       <c r="AB202" s="1"/>
       <c r="AC202" s="1"/>
-    </row>
-    <row r="203" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD202" s="1"/>
+      <c r="AE202" s="1"/>
+      <c r="AF202" s="1"/>
+      <c r="AG202" s="1"/>
+      <c r="AH202" s="1"/>
+      <c r="AI202" s="1"/>
+    </row>
+    <row r="203" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A203" s="3">
         <v>200</v>
       </c>
@@ -9710,8 +10978,14 @@
       <c r="AA203" s="1"/>
       <c r="AB203" s="1"/>
       <c r="AC203" s="1"/>
-    </row>
-    <row r="204" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD203" s="1"/>
+      <c r="AE203" s="1"/>
+      <c r="AF203" s="1"/>
+      <c r="AG203" s="1"/>
+      <c r="AH203" s="1"/>
+      <c r="AI203" s="1"/>
+    </row>
+    <row r="204" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A204" s="3">
         <v>201</v>
       </c>
@@ -9747,8 +11021,14 @@
       <c r="AA204" s="1"/>
       <c r="AB204" s="1"/>
       <c r="AC204" s="1"/>
-    </row>
-    <row r="205" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD204" s="1"/>
+      <c r="AE204" s="1"/>
+      <c r="AF204" s="1"/>
+      <c r="AG204" s="1"/>
+      <c r="AH204" s="1"/>
+      <c r="AI204" s="1"/>
+    </row>
+    <row r="205" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A205" s="3">
         <v>202</v>
       </c>
@@ -9784,8 +11064,14 @@
       <c r="AA205" s="1"/>
       <c r="AB205" s="1"/>
       <c r="AC205" s="1"/>
-    </row>
-    <row r="206" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD205" s="1"/>
+      <c r="AE205" s="1"/>
+      <c r="AF205" s="1"/>
+      <c r="AG205" s="1"/>
+      <c r="AH205" s="1"/>
+      <c r="AI205" s="1"/>
+    </row>
+    <row r="206" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A206" s="3">
         <v>203</v>
       </c>
@@ -9821,8 +11107,14 @@
       <c r="AA206" s="1"/>
       <c r="AB206" s="1"/>
       <c r="AC206" s="1"/>
-    </row>
-    <row r="207" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD206" s="1"/>
+      <c r="AE206" s="1"/>
+      <c r="AF206" s="1"/>
+      <c r="AG206" s="1"/>
+      <c r="AH206" s="1"/>
+      <c r="AI206" s="1"/>
+    </row>
+    <row r="207" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A207" s="3">
         <v>204</v>
       </c>
@@ -9860,8 +11152,14 @@
       <c r="AA207" s="1"/>
       <c r="AB207" s="1"/>
       <c r="AC207" s="1"/>
-    </row>
-    <row r="208" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD207" s="1"/>
+      <c r="AE207" s="1"/>
+      <c r="AF207" s="1"/>
+      <c r="AG207" s="1"/>
+      <c r="AH207" s="1"/>
+      <c r="AI207" s="1"/>
+    </row>
+    <row r="208" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A208" s="3">
         <v>205</v>
       </c>
@@ -9897,8 +11195,14 @@
       <c r="AA208" s="1"/>
       <c r="AB208" s="1"/>
       <c r="AC208" s="1"/>
-    </row>
-    <row r="209" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD208" s="1"/>
+      <c r="AE208" s="1"/>
+      <c r="AF208" s="1"/>
+      <c r="AG208" s="1"/>
+      <c r="AH208" s="1"/>
+      <c r="AI208" s="1"/>
+    </row>
+    <row r="209" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A209" s="3">
         <v>206</v>
       </c>
@@ -9934,8 +11238,14 @@
       <c r="AA209" s="1"/>
       <c r="AB209" s="1"/>
       <c r="AC209" s="1"/>
-    </row>
-    <row r="210" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD209" s="1"/>
+      <c r="AE209" s="1"/>
+      <c r="AF209" s="1"/>
+      <c r="AG209" s="1"/>
+      <c r="AH209" s="1"/>
+      <c r="AI209" s="1"/>
+    </row>
+    <row r="210" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A210" s="3">
         <v>207</v>
       </c>
@@ -9971,8 +11281,14 @@
       <c r="AA210" s="1"/>
       <c r="AB210" s="1"/>
       <c r="AC210" s="1"/>
-    </row>
-    <row r="211" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD210" s="1"/>
+      <c r="AE210" s="1"/>
+      <c r="AF210" s="1"/>
+      <c r="AG210" s="1"/>
+      <c r="AH210" s="1"/>
+      <c r="AI210" s="1"/>
+    </row>
+    <row r="211" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A211" s="3">
         <v>208</v>
       </c>
@@ -10008,8 +11324,14 @@
       <c r="AA211" s="1"/>
       <c r="AB211" s="1"/>
       <c r="AC211" s="1"/>
-    </row>
-    <row r="212" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD211" s="1"/>
+      <c r="AE211" s="1"/>
+      <c r="AF211" s="1"/>
+      <c r="AG211" s="1"/>
+      <c r="AH211" s="1"/>
+      <c r="AI211" s="1"/>
+    </row>
+    <row r="212" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A212" s="3">
         <v>209</v>
       </c>
@@ -10045,8 +11367,14 @@
       <c r="AA212" s="1"/>
       <c r="AB212" s="1"/>
       <c r="AC212" s="1"/>
-    </row>
-    <row r="213" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD212" s="1"/>
+      <c r="AE212" s="1"/>
+      <c r="AF212" s="1"/>
+      <c r="AG212" s="1"/>
+      <c r="AH212" s="1"/>
+      <c r="AI212" s="1"/>
+    </row>
+    <row r="213" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A213" s="3">
         <v>210</v>
       </c>
@@ -10082,8 +11410,14 @@
       <c r="AA213" s="1"/>
       <c r="AB213" s="1"/>
       <c r="AC213" s="1"/>
-    </row>
-    <row r="214" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD213" s="1"/>
+      <c r="AE213" s="1"/>
+      <c r="AF213" s="1"/>
+      <c r="AG213" s="1"/>
+      <c r="AH213" s="1"/>
+      <c r="AI213" s="1"/>
+    </row>
+    <row r="214" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A214" s="3">
         <v>211</v>
       </c>
@@ -10119,8 +11453,14 @@
       <c r="AA214" s="1"/>
       <c r="AB214" s="1"/>
       <c r="AC214" s="1"/>
-    </row>
-    <row r="215" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD214" s="1"/>
+      <c r="AE214" s="1"/>
+      <c r="AF214" s="1"/>
+      <c r="AG214" s="1"/>
+      <c r="AH214" s="1"/>
+      <c r="AI214" s="1"/>
+    </row>
+    <row r="215" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A215" s="3">
         <v>212</v>
       </c>
@@ -10156,8 +11496,14 @@
       <c r="AA215" s="1"/>
       <c r="AB215" s="1"/>
       <c r="AC215" s="1"/>
-    </row>
-    <row r="216" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD215" s="1"/>
+      <c r="AE215" s="1"/>
+      <c r="AF215" s="1"/>
+      <c r="AG215" s="1"/>
+      <c r="AH215" s="1"/>
+      <c r="AI215" s="1"/>
+    </row>
+    <row r="216" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A216" s="3">
         <v>213</v>
       </c>
@@ -10197,8 +11543,14 @@
       <c r="AA216" s="1"/>
       <c r="AB216" s="1"/>
       <c r="AC216" s="1"/>
-    </row>
-    <row r="217" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD216" s="1"/>
+      <c r="AE216" s="1"/>
+      <c r="AF216" s="1"/>
+      <c r="AG216" s="1"/>
+      <c r="AH216" s="1"/>
+      <c r="AI216" s="1"/>
+    </row>
+    <row r="217" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A217" s="3">
         <v>214</v>
       </c>
@@ -10238,8 +11590,14 @@
       <c r="AA217" s="1"/>
       <c r="AB217" s="1"/>
       <c r="AC217" s="1"/>
-    </row>
-    <row r="218" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD217" s="1"/>
+      <c r="AE217" s="1"/>
+      <c r="AF217" s="1"/>
+      <c r="AG217" s="1"/>
+      <c r="AH217" s="1"/>
+      <c r="AI217" s="1"/>
+    </row>
+    <row r="218" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A218" s="3">
         <v>215</v>
       </c>
@@ -10279,8 +11637,14 @@
       <c r="AA218" s="1"/>
       <c r="AB218" s="1"/>
       <c r="AC218" s="1"/>
-    </row>
-    <row r="219" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD218" s="1"/>
+      <c r="AE218" s="1"/>
+      <c r="AF218" s="1"/>
+      <c r="AG218" s="1"/>
+      <c r="AH218" s="1"/>
+      <c r="AI218" s="1"/>
+    </row>
+    <row r="219" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A219" s="3">
         <v>216</v>
       </c>
@@ -10314,8 +11678,14 @@
       <c r="AA219" s="1"/>
       <c r="AB219" s="1"/>
       <c r="AC219" s="1"/>
-    </row>
-    <row r="220" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD219" s="1"/>
+      <c r="AE219" s="1"/>
+      <c r="AF219" s="1"/>
+      <c r="AG219" s="1"/>
+      <c r="AH219" s="1"/>
+      <c r="AI219" s="1"/>
+    </row>
+    <row r="220" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A220" s="3">
         <v>217</v>
       </c>
@@ -10349,8 +11719,14 @@
       <c r="AA220" s="1"/>
       <c r="AB220" s="1"/>
       <c r="AC220" s="1"/>
-    </row>
-    <row r="221" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD220" s="1"/>
+      <c r="AE220" s="1"/>
+      <c r="AF220" s="1"/>
+      <c r="AG220" s="1"/>
+      <c r="AH220" s="1"/>
+      <c r="AI220" s="1"/>
+    </row>
+    <row r="221" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A221" s="3">
         <v>218</v>
       </c>
@@ -10384,8 +11760,14 @@
       <c r="AA221" s="1"/>
       <c r="AB221" s="1"/>
       <c r="AC221" s="1"/>
-    </row>
-    <row r="222" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD221" s="1"/>
+      <c r="AE221" s="1"/>
+      <c r="AF221" s="1"/>
+      <c r="AG221" s="1"/>
+      <c r="AH221" s="1"/>
+      <c r="AI221" s="1"/>
+    </row>
+    <row r="222" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A222" s="3">
         <v>219</v>
       </c>
@@ -10421,8 +11803,14 @@
       <c r="AA222" s="1"/>
       <c r="AB222" s="1"/>
       <c r="AC222" s="1"/>
-    </row>
-    <row r="223" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD222" s="1"/>
+      <c r="AE222" s="1"/>
+      <c r="AF222" s="1"/>
+      <c r="AG222" s="1"/>
+      <c r="AH222" s="1"/>
+      <c r="AI222" s="1"/>
+    </row>
+    <row r="223" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A223" s="3">
         <v>220</v>
       </c>
@@ -10456,8 +11844,14 @@
       <c r="AA223" s="1"/>
       <c r="AB223" s="1"/>
       <c r="AC223" s="1"/>
-    </row>
-    <row r="224" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD223" s="1"/>
+      <c r="AE223" s="1"/>
+      <c r="AF223" s="1"/>
+      <c r="AG223" s="1"/>
+      <c r="AH223" s="1"/>
+      <c r="AI223" s="1"/>
+    </row>
+    <row r="224" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A224" s="3">
         <v>221</v>
       </c>
@@ -10491,8 +11885,14 @@
       <c r="AA224" s="1"/>
       <c r="AB224" s="1"/>
       <c r="AC224" s="1"/>
-    </row>
-    <row r="225" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD224" s="1"/>
+      <c r="AE224" s="1"/>
+      <c r="AF224" s="1"/>
+      <c r="AG224" s="1"/>
+      <c r="AH224" s="1"/>
+      <c r="AI224" s="1"/>
+    </row>
+    <row r="225" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A225" s="3">
         <v>222</v>
       </c>
@@ -10526,8 +11926,14 @@
       <c r="AA225" s="1"/>
       <c r="AB225" s="1"/>
       <c r="AC225" s="1"/>
-    </row>
-    <row r="226" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD225" s="1"/>
+      <c r="AE225" s="1"/>
+      <c r="AF225" s="1"/>
+      <c r="AG225" s="1"/>
+      <c r="AH225" s="1"/>
+      <c r="AI225" s="1"/>
+    </row>
+    <row r="226" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A226" s="3">
         <v>223</v>
       </c>
@@ -10561,8 +11967,14 @@
       <c r="AA226" s="1"/>
       <c r="AB226" s="1"/>
       <c r="AC226" s="1"/>
-    </row>
-    <row r="227" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD226" s="1"/>
+      <c r="AE226" s="1"/>
+      <c r="AF226" s="1"/>
+      <c r="AG226" s="1"/>
+      <c r="AH226" s="1"/>
+      <c r="AI226" s="1"/>
+    </row>
+    <row r="227" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A227" s="3">
         <v>224</v>
       </c>
@@ -10596,8 +12008,14 @@
       <c r="AA227" s="1"/>
       <c r="AB227" s="1"/>
       <c r="AC227" s="1"/>
-    </row>
-    <row r="228" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD227" s="1"/>
+      <c r="AE227" s="1"/>
+      <c r="AF227" s="1"/>
+      <c r="AG227" s="1"/>
+      <c r="AH227" s="1"/>
+      <c r="AI227" s="1"/>
+    </row>
+    <row r="228" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A228" s="3">
         <v>225</v>
       </c>
@@ -10631,8 +12049,14 @@
       <c r="AA228" s="1"/>
       <c r="AB228" s="1"/>
       <c r="AC228" s="1"/>
-    </row>
-    <row r="229" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD228" s="1"/>
+      <c r="AE228" s="1"/>
+      <c r="AF228" s="1"/>
+      <c r="AG228" s="1"/>
+      <c r="AH228" s="1"/>
+      <c r="AI228" s="1"/>
+    </row>
+    <row r="229" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A229" s="3">
         <v>226</v>
       </c>
@@ -10666,8 +12090,14 @@
       <c r="AA229" s="1"/>
       <c r="AB229" s="1"/>
       <c r="AC229" s="1"/>
-    </row>
-    <row r="230" spans="1:29" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AD229" s="1"/>
+      <c r="AE229" s="1"/>
+      <c r="AF229" s="1"/>
+      <c r="AG229" s="1"/>
+      <c r="AH229" s="1"/>
+      <c r="AI229" s="1"/>
+    </row>
+    <row r="230" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A230" s="3">
         <v>227</v>
       </c>
@@ -10701,8 +12131,14 @@
       <c r="AA230" s="1"/>
       <c r="AB230" s="1"/>
       <c r="AC230" s="1"/>
-    </row>
-    <row r="231" spans="1:29">
+      <c r="AD230" s="1"/>
+      <c r="AE230" s="1"/>
+      <c r="AF230" s="1"/>
+      <c r="AG230" s="1"/>
+      <c r="AH230" s="1"/>
+      <c r="AI230" s="1"/>
+    </row>
+    <row r="231" spans="1:35">
       <c r="A231" s="3">
         <v>228</v>
       </c>
@@ -10736,8 +12172,14 @@
       <c r="AA231" s="1"/>
       <c r="AB231" s="1"/>
       <c r="AC231" s="1"/>
-    </row>
-    <row r="232" spans="1:29">
+      <c r="AD231" s="1"/>
+      <c r="AE231" s="1"/>
+      <c r="AF231" s="1"/>
+      <c r="AG231" s="1"/>
+      <c r="AH231" s="1"/>
+      <c r="AI231" s="1"/>
+    </row>
+    <row r="232" spans="1:35">
       <c r="A232" s="3">
         <v>229</v>
       </c>
@@ -10771,8 +12213,14 @@
       <c r="AA232" s="1"/>
       <c r="AB232" s="1"/>
       <c r="AC232" s="1"/>
-    </row>
-    <row r="233" spans="1:29">
+      <c r="AD232" s="1"/>
+      <c r="AE232" s="1"/>
+      <c r="AF232" s="1"/>
+      <c r="AG232" s="1"/>
+      <c r="AH232" s="1"/>
+      <c r="AI232" s="1"/>
+    </row>
+    <row r="233" spans="1:35">
       <c r="A233" s="3">
         <v>230</v>
       </c>
@@ -10808,8 +12256,14 @@
       <c r="AA233" s="1"/>
       <c r="AB233" s="1"/>
       <c r="AC233" s="1"/>
-    </row>
-    <row r="234" spans="1:29">
+      <c r="AD233" s="1"/>
+      <c r="AE233" s="1"/>
+      <c r="AF233" s="1"/>
+      <c r="AG233" s="1"/>
+      <c r="AH233" s="1"/>
+      <c r="AI233" s="1"/>
+    </row>
+    <row r="234" spans="1:35">
       <c r="A234" s="3">
         <v>231</v>
       </c>
@@ -10843,8 +12297,14 @@
       <c r="AA234" s="1"/>
       <c r="AB234" s="1"/>
       <c r="AC234" s="1"/>
-    </row>
-    <row r="235" spans="1:29">
+      <c r="AD234" s="1"/>
+      <c r="AE234" s="1"/>
+      <c r="AF234" s="1"/>
+      <c r="AG234" s="1"/>
+      <c r="AH234" s="1"/>
+      <c r="AI234" s="1"/>
+    </row>
+    <row r="235" spans="1:35">
       <c r="A235" s="3">
         <v>232</v>
       </c>
@@ -10880,8 +12340,14 @@
       <c r="AA235" s="1"/>
       <c r="AB235" s="1"/>
       <c r="AC235" s="1"/>
-    </row>
-    <row r="236" spans="1:29">
+      <c r="AD235" s="1"/>
+      <c r="AE235" s="1"/>
+      <c r="AF235" s="1"/>
+      <c r="AG235" s="1"/>
+      <c r="AH235" s="1"/>
+      <c r="AI235" s="1"/>
+    </row>
+    <row r="236" spans="1:35">
       <c r="A236" s="3">
         <v>233</v>
       </c>
@@ -10915,8 +12381,14 @@
       <c r="AA236" s="1"/>
       <c r="AB236" s="1"/>
       <c r="AC236" s="1"/>
-    </row>
-    <row r="237" spans="1:29">
+      <c r="AD236" s="1"/>
+      <c r="AE236" s="1"/>
+      <c r="AF236" s="1"/>
+      <c r="AG236" s="1"/>
+      <c r="AH236" s="1"/>
+      <c r="AI236" s="1"/>
+    </row>
+    <row r="237" spans="1:35">
       <c r="A237" s="3">
         <v>234</v>
       </c>
@@ -10950,8 +12422,14 @@
       <c r="AA237" s="1"/>
       <c r="AB237" s="1"/>
       <c r="AC237" s="1"/>
-    </row>
-    <row r="238" spans="1:29">
+      <c r="AD237" s="1"/>
+      <c r="AE237" s="1"/>
+      <c r="AF237" s="1"/>
+      <c r="AG237" s="1"/>
+      <c r="AH237" s="1"/>
+      <c r="AI237" s="1"/>
+    </row>
+    <row r="238" spans="1:35">
       <c r="A238" s="3">
         <v>235</v>
       </c>
@@ -10985,8 +12463,14 @@
       <c r="AA238" s="1"/>
       <c r="AB238" s="1"/>
       <c r="AC238" s="1"/>
-    </row>
-    <row r="239" spans="1:29">
+      <c r="AD238" s="1"/>
+      <c r="AE238" s="1"/>
+      <c r="AF238" s="1"/>
+      <c r="AG238" s="1"/>
+      <c r="AH238" s="1"/>
+      <c r="AI238" s="1"/>
+    </row>
+    <row r="239" spans="1:35">
       <c r="A239" s="3">
         <v>236</v>
       </c>
@@ -11020,8 +12504,14 @@
       <c r="AA239" s="1"/>
       <c r="AB239" s="1"/>
       <c r="AC239" s="1"/>
-    </row>
-    <row r="240" spans="1:29">
+      <c r="AD239" s="1"/>
+      <c r="AE239" s="1"/>
+      <c r="AF239" s="1"/>
+      <c r="AG239" s="1"/>
+      <c r="AH239" s="1"/>
+      <c r="AI239" s="1"/>
+    </row>
+    <row r="240" spans="1:35">
       <c r="A240" s="3">
         <v>237</v>
       </c>
@@ -11055,8 +12545,14 @@
       <c r="AA240" s="1"/>
       <c r="AB240" s="1"/>
       <c r="AC240" s="1"/>
-    </row>
-    <row r="241" spans="1:29">
+      <c r="AD240" s="1"/>
+      <c r="AE240" s="1"/>
+      <c r="AF240" s="1"/>
+      <c r="AG240" s="1"/>
+      <c r="AH240" s="1"/>
+      <c r="AI240" s="1"/>
+    </row>
+    <row r="241" spans="1:35">
       <c r="A241" s="3">
         <v>238</v>
       </c>
@@ -11090,8 +12586,14 @@
       <c r="AA241" s="1"/>
       <c r="AB241" s="1"/>
       <c r="AC241" s="1"/>
-    </row>
-    <row r="242" spans="1:29">
+      <c r="AD241" s="1"/>
+      <c r="AE241" s="1"/>
+      <c r="AF241" s="1"/>
+      <c r="AG241" s="1"/>
+      <c r="AH241" s="1"/>
+      <c r="AI241" s="1"/>
+    </row>
+    <row r="242" spans="1:35">
       <c r="A242" s="3">
         <v>239</v>
       </c>
@@ -11125,8 +12627,14 @@
       <c r="AA242" s="1"/>
       <c r="AB242" s="1"/>
       <c r="AC242" s="1"/>
-    </row>
-    <row r="243" spans="1:29">
+      <c r="AD242" s="1"/>
+      <c r="AE242" s="1"/>
+      <c r="AF242" s="1"/>
+      <c r="AG242" s="1"/>
+      <c r="AH242" s="1"/>
+      <c r="AI242" s="1"/>
+    </row>
+    <row r="243" spans="1:35">
       <c r="A243" s="3">
         <v>240</v>
       </c>
@@ -11162,8 +12670,14 @@
       <c r="AA243" s="1"/>
       <c r="AB243" s="1"/>
       <c r="AC243" s="1"/>
-    </row>
-    <row r="244" spans="1:29">
+      <c r="AD243" s="1"/>
+      <c r="AE243" s="1"/>
+      <c r="AF243" s="1"/>
+      <c r="AG243" s="1"/>
+      <c r="AH243" s="1"/>
+      <c r="AI243" s="1"/>
+    </row>
+    <row r="244" spans="1:35">
       <c r="A244" s="3">
         <v>241</v>
       </c>
@@ -11199,8 +12713,14 @@
       <c r="AA244" s="1"/>
       <c r="AB244" s="1"/>
       <c r="AC244" s="1"/>
-    </row>
-    <row r="245" spans="1:29">
+      <c r="AD244" s="1"/>
+      <c r="AE244" s="1"/>
+      <c r="AF244" s="1"/>
+      <c r="AG244" s="1"/>
+      <c r="AH244" s="1"/>
+      <c r="AI244" s="1"/>
+    </row>
+    <row r="245" spans="1:35">
       <c r="A245" s="3">
         <v>242</v>
       </c>
@@ -11236,8 +12756,14 @@
       <c r="AA245" s="1"/>
       <c r="AB245" s="1"/>
       <c r="AC245" s="1"/>
-    </row>
-    <row r="246" spans="1:29">
+      <c r="AD245" s="1"/>
+      <c r="AE245" s="1"/>
+      <c r="AF245" s="1"/>
+      <c r="AG245" s="1"/>
+      <c r="AH245" s="1"/>
+      <c r="AI245" s="1"/>
+    </row>
+    <row r="246" spans="1:35">
       <c r="A246" s="3">
         <v>243</v>
       </c>
@@ -11273,8 +12799,14 @@
       <c r="AA246" s="1"/>
       <c r="AB246" s="1"/>
       <c r="AC246" s="1"/>
-    </row>
-    <row r="247" spans="1:29">
+      <c r="AD246" s="1"/>
+      <c r="AE246" s="1"/>
+      <c r="AF246" s="1"/>
+      <c r="AG246" s="1"/>
+      <c r="AH246" s="1"/>
+      <c r="AI246" s="1"/>
+    </row>
+    <row r="247" spans="1:35">
       <c r="A247" s="3">
         <v>244</v>
       </c>
@@ -11310,8 +12842,14 @@
       <c r="AA247" s="1"/>
       <c r="AB247" s="1"/>
       <c r="AC247" s="1"/>
-    </row>
-    <row r="248" spans="1:29">
+      <c r="AD247" s="1"/>
+      <c r="AE247" s="1"/>
+      <c r="AF247" s="1"/>
+      <c r="AG247" s="1"/>
+      <c r="AH247" s="1"/>
+      <c r="AI247" s="1"/>
+    </row>
+    <row r="248" spans="1:35">
       <c r="A248" s="3">
         <v>245</v>
       </c>
@@ -11347,13 +12885,21 @@
       <c r="AA248" s="1"/>
       <c r="AB248" s="1"/>
       <c r="AC248" s="1"/>
-    </row>
-    <row r="249" spans="1:29">
+      <c r="AD248" s="1"/>
+      <c r="AE248" s="1"/>
+      <c r="AF248" s="1"/>
+      <c r="AG248" s="1"/>
+      <c r="AH248" s="1"/>
+      <c r="AI248" s="1"/>
+    </row>
+    <row r="249" spans="1:35">
       <c r="A249" s="3">
         <v>246</v>
       </c>
       <c r="B249" s="3"/>
-      <c r="C249" s="21"/>
+      <c r="C249" s="21" t="s">
+        <v>288</v>
+      </c>
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
@@ -11380,13 +12926,21 @@
       <c r="AA249" s="1"/>
       <c r="AB249" s="1"/>
       <c r="AC249" s="1"/>
-    </row>
-    <row r="250" spans="1:29">
+      <c r="AD249" s="1"/>
+      <c r="AE249" s="1"/>
+      <c r="AF249" s="1"/>
+      <c r="AG249" s="1"/>
+      <c r="AH249" s="1"/>
+      <c r="AI249" s="1"/>
+    </row>
+    <row r="250" spans="1:35">
       <c r="A250" s="3">
         <v>247</v>
       </c>
       <c r="B250" s="3"/>
-      <c r="C250" s="21"/>
+      <c r="C250" s="21" t="s">
+        <v>289</v>
+      </c>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
@@ -11413,13 +12967,21 @@
       <c r="AA250" s="1"/>
       <c r="AB250" s="1"/>
       <c r="AC250" s="1"/>
-    </row>
-    <row r="251" spans="1:29">
+      <c r="AD250" s="1"/>
+      <c r="AE250" s="1"/>
+      <c r="AF250" s="1"/>
+      <c r="AG250" s="1"/>
+      <c r="AH250" s="1"/>
+      <c r="AI250" s="1"/>
+    </row>
+    <row r="251" spans="1:35">
       <c r="A251" s="3">
         <v>248</v>
       </c>
       <c r="B251" s="3"/>
-      <c r="C251" s="21"/>
+      <c r="C251" s="21" t="s">
+        <v>290</v>
+      </c>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
@@ -11446,13 +13008,21 @@
       <c r="AA251" s="1"/>
       <c r="AB251" s="1"/>
       <c r="AC251" s="1"/>
-    </row>
-    <row r="252" spans="1:29">
+      <c r="AD251" s="1"/>
+      <c r="AE251" s="1"/>
+      <c r="AF251" s="1"/>
+      <c r="AG251" s="1"/>
+      <c r="AH251" s="1"/>
+      <c r="AI251" s="1"/>
+    </row>
+    <row r="252" spans="1:35">
       <c r="A252" s="3">
         <v>249</v>
       </c>
       <c r="B252" s="3"/>
-      <c r="C252" s="21"/>
+      <c r="C252" s="21" t="s">
+        <v>293</v>
+      </c>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
@@ -11479,8 +13049,14 @@
       <c r="AA252" s="1"/>
       <c r="AB252" s="1"/>
       <c r="AC252" s="1"/>
-    </row>
-    <row r="253" spans="1:29">
+      <c r="AD252" s="1"/>
+      <c r="AE252" s="1"/>
+      <c r="AF252" s="1"/>
+      <c r="AG252" s="1"/>
+      <c r="AH252" s="1"/>
+      <c r="AI252" s="1"/>
+    </row>
+    <row r="253" spans="1:35">
       <c r="A253" s="3">
         <v>250</v>
       </c>
@@ -11512,8 +13088,14 @@
       <c r="AA253" s="1"/>
       <c r="AB253" s="1"/>
       <c r="AC253" s="1"/>
-    </row>
-    <row r="254" spans="1:29">
+      <c r="AD253" s="1"/>
+      <c r="AE253" s="1"/>
+      <c r="AF253" s="1"/>
+      <c r="AG253" s="1"/>
+      <c r="AH253" s="1"/>
+      <c r="AI253" s="1"/>
+    </row>
+    <row r="254" spans="1:35">
       <c r="A254" s="3">
         <v>251</v>
       </c>
@@ -11545,8 +13127,14 @@
       <c r="AA254" s="1"/>
       <c r="AB254" s="1"/>
       <c r="AC254" s="1"/>
-    </row>
-    <row r="255" spans="1:29">
+      <c r="AD254" s="1"/>
+      <c r="AE254" s="1"/>
+      <c r="AF254" s="1"/>
+      <c r="AG254" s="1"/>
+      <c r="AH254" s="1"/>
+      <c r="AI254" s="1"/>
+    </row>
+    <row r="255" spans="1:35">
       <c r="A255" s="3">
         <v>252</v>
       </c>
@@ -11578,8 +13166,14 @@
       <c r="AA255" s="1"/>
       <c r="AB255" s="1"/>
       <c r="AC255" s="1"/>
-    </row>
-    <row r="256" spans="1:29">
+      <c r="AD255" s="1"/>
+      <c r="AE255" s="1"/>
+      <c r="AF255" s="1"/>
+      <c r="AG255" s="1"/>
+      <c r="AH255" s="1"/>
+      <c r="AI255" s="1"/>
+    </row>
+    <row r="256" spans="1:35">
       <c r="A256" s="3">
         <v>253</v>
       </c>
@@ -11611,8 +13205,14 @@
       <c r="AA256" s="1"/>
       <c r="AB256" s="1"/>
       <c r="AC256" s="1"/>
-    </row>
-    <row r="257" spans="1:29">
+      <c r="AD256" s="1"/>
+      <c r="AE256" s="1"/>
+      <c r="AF256" s="1"/>
+      <c r="AG256" s="1"/>
+      <c r="AH256" s="1"/>
+      <c r="AI256" s="1"/>
+    </row>
+    <row r="257" spans="1:35">
       <c r="A257" s="3">
         <v>254</v>
       </c>
@@ -11644,8 +13244,14 @@
       <c r="AA257" s="1"/>
       <c r="AB257" s="1"/>
       <c r="AC257" s="1"/>
-    </row>
-    <row r="258" spans="1:29">
+      <c r="AD257" s="1"/>
+      <c r="AE257" s="1"/>
+      <c r="AF257" s="1"/>
+      <c r="AG257" s="1"/>
+      <c r="AH257" s="1"/>
+      <c r="AI257" s="1"/>
+    </row>
+    <row r="258" spans="1:35">
       <c r="A258" s="3">
         <v>255</v>
       </c>
@@ -11677,8 +13283,14 @@
       <c r="AA258" s="1"/>
       <c r="AB258" s="1"/>
       <c r="AC258" s="1"/>
-    </row>
-    <row r="259" spans="1:29">
+      <c r="AD258" s="1"/>
+      <c r="AE258" s="1"/>
+      <c r="AF258" s="1"/>
+      <c r="AG258" s="1"/>
+      <c r="AH258" s="1"/>
+      <c r="AI258" s="1"/>
+    </row>
+    <row r="259" spans="1:35">
       <c r="A259" s="3">
         <v>256</v>
       </c>
@@ -11710,8 +13322,14 @@
       <c r="AA259" s="1"/>
       <c r="AB259" s="1"/>
       <c r="AC259" s="1"/>
-    </row>
-    <row r="260" spans="1:29">
+      <c r="AD259" s="1"/>
+      <c r="AE259" s="1"/>
+      <c r="AF259" s="1"/>
+      <c r="AG259" s="1"/>
+      <c r="AH259" s="1"/>
+      <c r="AI259" s="1"/>
+    </row>
+    <row r="260" spans="1:35">
       <c r="A260" s="3">
         <v>257</v>
       </c>
@@ -11743,8 +13361,14 @@
       <c r="AA260" s="1"/>
       <c r="AB260" s="1"/>
       <c r="AC260" s="1"/>
-    </row>
-    <row r="261" spans="1:29">
+      <c r="AD260" s="1"/>
+      <c r="AE260" s="1"/>
+      <c r="AF260" s="1"/>
+      <c r="AG260" s="1"/>
+      <c r="AH260" s="1"/>
+      <c r="AI260" s="1"/>
+    </row>
+    <row r="261" spans="1:35">
       <c r="A261" s="3">
         <v>258</v>
       </c>
@@ -11776,8 +13400,14 @@
       <c r="AA261" s="1"/>
       <c r="AB261" s="1"/>
       <c r="AC261" s="1"/>
-    </row>
-    <row r="262" spans="1:29">
+      <c r="AD261" s="1"/>
+      <c r="AE261" s="1"/>
+      <c r="AF261" s="1"/>
+      <c r="AG261" s="1"/>
+      <c r="AH261" s="1"/>
+      <c r="AI261" s="1"/>
+    </row>
+    <row r="262" spans="1:35">
       <c r="A262" s="3">
         <v>259</v>
       </c>
@@ -11809,8 +13439,14 @@
       <c r="AA262" s="1"/>
       <c r="AB262" s="1"/>
       <c r="AC262" s="1"/>
-    </row>
-    <row r="263" spans="1:29">
+      <c r="AD262" s="1"/>
+      <c r="AE262" s="1"/>
+      <c r="AF262" s="1"/>
+      <c r="AG262" s="1"/>
+      <c r="AH262" s="1"/>
+      <c r="AI262" s="1"/>
+    </row>
+    <row r="263" spans="1:35">
       <c r="A263" s="3">
         <v>260</v>
       </c>
@@ -11842,8 +13478,14 @@
       <c r="AA263" s="1"/>
       <c r="AB263" s="1"/>
       <c r="AC263" s="1"/>
-    </row>
-    <row r="264" spans="1:29">
+      <c r="AD263" s="1"/>
+      <c r="AE263" s="1"/>
+      <c r="AF263" s="1"/>
+      <c r="AG263" s="1"/>
+      <c r="AH263" s="1"/>
+      <c r="AI263" s="1"/>
+    </row>
+    <row r="264" spans="1:35">
       <c r="A264" s="3">
         <v>261</v>
       </c>
@@ -11875,8 +13517,14 @@
       <c r="AA264" s="1"/>
       <c r="AB264" s="1"/>
       <c r="AC264" s="1"/>
-    </row>
-    <row r="265" spans="1:29">
+      <c r="AD264" s="1"/>
+      <c r="AE264" s="1"/>
+      <c r="AF264" s="1"/>
+      <c r="AG264" s="1"/>
+      <c r="AH264" s="1"/>
+      <c r="AI264" s="1"/>
+    </row>
+    <row r="265" spans="1:35">
       <c r="A265" s="3">
         <v>262</v>
       </c>
@@ -11908,8 +13556,14 @@
       <c r="AA265" s="1"/>
       <c r="AB265" s="1"/>
       <c r="AC265" s="1"/>
-    </row>
-    <row r="266" spans="1:29">
+      <c r="AD265" s="1"/>
+      <c r="AE265" s="1"/>
+      <c r="AF265" s="1"/>
+      <c r="AG265" s="1"/>
+      <c r="AH265" s="1"/>
+      <c r="AI265" s="1"/>
+    </row>
+    <row r="266" spans="1:35">
       <c r="A266" s="3">
         <v>263</v>
       </c>
@@ -11941,8 +13595,14 @@
       <c r="AA266" s="1"/>
       <c r="AB266" s="1"/>
       <c r="AC266" s="1"/>
-    </row>
-    <row r="267" spans="1:29">
+      <c r="AD266" s="1"/>
+      <c r="AE266" s="1"/>
+      <c r="AF266" s="1"/>
+      <c r="AG266" s="1"/>
+      <c r="AH266" s="1"/>
+      <c r="AI266" s="1"/>
+    </row>
+    <row r="267" spans="1:35">
       <c r="A267" s="3">
         <v>264</v>
       </c>
@@ -11974,8 +13634,14 @@
       <c r="AA267" s="1"/>
       <c r="AB267" s="1"/>
       <c r="AC267" s="1"/>
-    </row>
-    <row r="268" spans="1:29">
+      <c r="AD267" s="1"/>
+      <c r="AE267" s="1"/>
+      <c r="AF267" s="1"/>
+      <c r="AG267" s="1"/>
+      <c r="AH267" s="1"/>
+      <c r="AI267" s="1"/>
+    </row>
+    <row r="268" spans="1:35">
       <c r="A268" s="3">
         <v>265</v>
       </c>
@@ -12007,8 +13673,14 @@
       <c r="AA268" s="1"/>
       <c r="AB268" s="1"/>
       <c r="AC268" s="1"/>
-    </row>
-    <row r="269" spans="1:29">
+      <c r="AD268" s="1"/>
+      <c r="AE268" s="1"/>
+      <c r="AF268" s="1"/>
+      <c r="AG268" s="1"/>
+      <c r="AH268" s="1"/>
+      <c r="AI268" s="1"/>
+    </row>
+    <row r="269" spans="1:35">
       <c r="A269" s="3">
         <v>266</v>
       </c>
@@ -12040,8 +13712,14 @@
       <c r="AA269" s="1"/>
       <c r="AB269" s="1"/>
       <c r="AC269" s="1"/>
-    </row>
-    <row r="270" spans="1:29">
+      <c r="AD269" s="1"/>
+      <c r="AE269" s="1"/>
+      <c r="AF269" s="1"/>
+      <c r="AG269" s="1"/>
+      <c r="AH269" s="1"/>
+      <c r="AI269" s="1"/>
+    </row>
+    <row r="270" spans="1:35">
       <c r="A270" s="3">
         <v>267</v>
       </c>
@@ -12073,8 +13751,14 @@
       <c r="AA270" s="1"/>
       <c r="AB270" s="1"/>
       <c r="AC270" s="1"/>
-    </row>
-    <row r="271" spans="1:29">
+      <c r="AD270" s="1"/>
+      <c r="AE270" s="1"/>
+      <c r="AF270" s="1"/>
+      <c r="AG270" s="1"/>
+      <c r="AH270" s="1"/>
+      <c r="AI270" s="1"/>
+    </row>
+    <row r="271" spans="1:35">
       <c r="A271" s="3">
         <v>268</v>
       </c>
@@ -12106,8 +13790,14 @@
       <c r="AA271" s="1"/>
       <c r="AB271" s="1"/>
       <c r="AC271" s="1"/>
-    </row>
-    <row r="272" spans="1:29">
+      <c r="AD271" s="1"/>
+      <c r="AE271" s="1"/>
+      <c r="AF271" s="1"/>
+      <c r="AG271" s="1"/>
+      <c r="AH271" s="1"/>
+      <c r="AI271" s="1"/>
+    </row>
+    <row r="272" spans="1:35">
       <c r="A272" s="3">
         <v>269</v>
       </c>
@@ -12139,8 +13829,14 @@
       <c r="AA272" s="1"/>
       <c r="AB272" s="1"/>
       <c r="AC272" s="1"/>
-    </row>
-    <row r="273" spans="1:29">
+      <c r="AD272" s="1"/>
+      <c r="AE272" s="1"/>
+      <c r="AF272" s="1"/>
+      <c r="AG272" s="1"/>
+      <c r="AH272" s="1"/>
+      <c r="AI272" s="1"/>
+    </row>
+    <row r="273" spans="1:35">
       <c r="A273" s="3">
         <v>270</v>
       </c>
@@ -12172,8 +13868,14 @@
       <c r="AA273" s="1"/>
       <c r="AB273" s="1"/>
       <c r="AC273" s="1"/>
-    </row>
-    <row r="274" spans="1:29">
+      <c r="AD273" s="1"/>
+      <c r="AE273" s="1"/>
+      <c r="AF273" s="1"/>
+      <c r="AG273" s="1"/>
+      <c r="AH273" s="1"/>
+      <c r="AI273" s="1"/>
+    </row>
+    <row r="274" spans="1:35">
       <c r="A274" s="3">
         <v>271</v>
       </c>
@@ -12205,8 +13907,14 @@
       <c r="AA274" s="1"/>
       <c r="AB274" s="1"/>
       <c r="AC274" s="1"/>
-    </row>
-    <row r="275" spans="1:29">
+      <c r="AD274" s="1"/>
+      <c r="AE274" s="1"/>
+      <c r="AF274" s="1"/>
+      <c r="AG274" s="1"/>
+      <c r="AH274" s="1"/>
+      <c r="AI274" s="1"/>
+    </row>
+    <row r="275" spans="1:35">
       <c r="A275" s="3">
         <v>272</v>
       </c>
@@ -12238,8 +13946,14 @@
       <c r="AA275" s="1"/>
       <c r="AB275" s="1"/>
       <c r="AC275" s="1"/>
-    </row>
-    <row r="276" spans="1:29">
+      <c r="AD275" s="1"/>
+      <c r="AE275" s="1"/>
+      <c r="AF275" s="1"/>
+      <c r="AG275" s="1"/>
+      <c r="AH275" s="1"/>
+      <c r="AI275" s="1"/>
+    </row>
+    <row r="276" spans="1:35">
       <c r="A276" s="3">
         <v>273</v>
       </c>
@@ -12271,8 +13985,14 @@
       <c r="AA276" s="1"/>
       <c r="AB276" s="1"/>
       <c r="AC276" s="1"/>
-    </row>
-    <row r="277" spans="1:29">
+      <c r="AD276" s="1"/>
+      <c r="AE276" s="1"/>
+      <c r="AF276" s="1"/>
+      <c r="AG276" s="1"/>
+      <c r="AH276" s="1"/>
+      <c r="AI276" s="1"/>
+    </row>
+    <row r="277" spans="1:35">
       <c r="A277" s="3">
         <v>274</v>
       </c>
@@ -12304,8 +14024,14 @@
       <c r="AA277" s="1"/>
       <c r="AB277" s="1"/>
       <c r="AC277" s="1"/>
-    </row>
-    <row r="278" spans="1:29">
+      <c r="AD277" s="1"/>
+      <c r="AE277" s="1"/>
+      <c r="AF277" s="1"/>
+      <c r="AG277" s="1"/>
+      <c r="AH277" s="1"/>
+      <c r="AI277" s="1"/>
+    </row>
+    <row r="278" spans="1:35">
       <c r="A278" s="3">
         <v>275</v>
       </c>
@@ -12337,8 +14063,14 @@
       <c r="AA278" s="1"/>
       <c r="AB278" s="1"/>
       <c r="AC278" s="1"/>
-    </row>
-    <row r="279" spans="1:29">
+      <c r="AD278" s="1"/>
+      <c r="AE278" s="1"/>
+      <c r="AF278" s="1"/>
+      <c r="AG278" s="1"/>
+      <c r="AH278" s="1"/>
+      <c r="AI278" s="1"/>
+    </row>
+    <row r="279" spans="1:35">
       <c r="A279" s="3">
         <v>276</v>
       </c>
@@ -12370,8 +14102,14 @@
       <c r="AA279" s="1"/>
       <c r="AB279" s="1"/>
       <c r="AC279" s="1"/>
-    </row>
-    <row r="280" spans="1:29">
+      <c r="AD279" s="1"/>
+      <c r="AE279" s="1"/>
+      <c r="AF279" s="1"/>
+      <c r="AG279" s="1"/>
+      <c r="AH279" s="1"/>
+      <c r="AI279" s="1"/>
+    </row>
+    <row r="280" spans="1:35">
       <c r="A280" s="3">
         <v>277</v>
       </c>
@@ -12403,13 +14141,15 @@
       <c r="AA280" s="1"/>
       <c r="AB280" s="1"/>
       <c r="AC280" s="1"/>
+      <c r="AD280" s="1"/>
+      <c r="AE280" s="1"/>
+      <c r="AF280" s="1"/>
+      <c r="AG280" s="1"/>
+      <c r="AH280" s="1"/>
+      <c r="AI280" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AB280" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="18">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A3:AB280" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="4">
     <mergeCell ref="C1:C3"/>
     <mergeCell ref="A1:A3"/>
@@ -12418,7 +14158,7 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E181:E280 E4:E163 F4:AC280 D4:D280 B4:B242" xr:uid="{C452CDD0-B3A9-419A-AD4E-0E5CE327C346}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E181:E280 E4:E163 F4:AI280 D4:D280 B4:B242" xr:uid="{C452CDD0-B3A9-419A-AD4E-0E5CE327C346}">
       <formula1>"〇,×,△"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E164:E180" xr:uid="{E47C5A29-770A-4FF4-AE4B-E53AB5761727}">
@@ -12434,7 +14174,7 @@
   <dimension ref="A2:H171"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.649999999999999"/>
   <cols>
-    <col min="1" max="1" width="10.1875" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="16" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.8125" style="16" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="14.0625" style="16" bestFit="1" customWidth="1"/>
@@ -12707,13 +14447,19 @@
       <c r="C19" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="D19" s="35"/>
+      <c r="D19" s="25"/>
       <c r="E19" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
+      <c r="F19" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="19" t="s">
@@ -12779,13 +14525,25 @@
       <c r="A24" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
+      <c r="B24" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="D24" s="25"/>
+      <c r="E24" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="H24" s="18" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="19" t="s">
@@ -12812,7 +14570,9 @@
       <c r="H26" s="18"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="19"/>
+      <c r="A27" s="19" t="s">
+        <v>282</v>
+      </c>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
@@ -12822,7 +14582,9 @@
       <c r="H27" s="18"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="19"/>
+      <c r="A28" s="19" t="s">
+        <v>283</v>
+      </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
@@ -12832,7 +14594,9 @@
       <c r="H28" s="18"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="19"/>
+      <c r="A29" s="19" t="s">
+        <v>284</v>
+      </c>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
@@ -12842,7 +14606,9 @@
       <c r="H29" s="18"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="19"/>
+      <c r="A30" s="19" t="s">
+        <v>292</v>
+      </c>
       <c r="B30" s="18"/>
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
@@ -12852,7 +14618,9 @@
       <c r="H30" s="18"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="19"/>
+      <c r="A31" s="19" t="s">
+        <v>295</v>
+      </c>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
       <c r="D31" s="18"/>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4F049C-AB47-4D0E-B4B9-3DEBFF99AE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7604DCAB-4506-44F8-93CB-3CEFA91029B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="リスト" sheetId="1" r:id="rId1"/>
     <sheet name="進捗表" sheetId="2" r:id="rId2"/>
+    <sheet name="昭和のことば" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">リスト!$A$3:$AB$280</definedName>
@@ -109,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="379">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -1520,6 +1521,288 @@
     <rPh sb="0" eb="2">
       <t>ショウワ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>受験</t>
+    <rPh sb="0" eb="2">
+      <t>ジュケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>受験</t>
+    <rPh sb="0" eb="2">
+      <t>ジュケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>勝つ</t>
+    <rPh sb="0" eb="1">
+      <t>カツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>受かる</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>負けるな</t>
+    <rPh sb="0" eb="1">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ナウい</t>
+  </si>
+  <si>
+    <t>アベック</t>
+  </si>
+  <si>
+    <t>マブダチ</t>
+  </si>
+  <si>
+    <t>余裕のよっちゃん</t>
+  </si>
+  <si>
+    <t>ぶりっこ</t>
+  </si>
+  <si>
+    <t>バイなら</t>
+  </si>
+  <si>
+    <t>モーレツ社員</t>
+  </si>
+  <si>
+    <t>窓際族</t>
+  </si>
+  <si>
+    <t>花金（はなきん）</t>
+  </si>
+  <si>
+    <t>ドロンする</t>
+  </si>
+  <si>
+    <t>盤石（ばんじゃく）</t>
+  </si>
+  <si>
+    <t>チャンネルを回す</t>
+  </si>
+  <si>
+    <t>半ドン</t>
+  </si>
+  <si>
+    <t>おニュー</t>
+  </si>
+  <si>
+    <t>ズック</t>
+  </si>
+  <si>
+    <t>合点承知（がってんしょうち）</t>
+  </si>
+  <si>
+    <t>よっこいしょういち</t>
+  </si>
+  <si>
+    <t>めんごめんご</t>
+  </si>
+  <si>
+    <t>冗談はよしこさん</t>
+  </si>
+  <si>
+    <t>ガビーン</t>
+  </si>
+  <si>
+    <t>団地族（だんちぞく）</t>
+  </si>
+  <si>
+    <t>カミナリ族</t>
+  </si>
+  <si>
+    <t>三種の神器（さんしゅのじんぎ）</t>
+  </si>
+  <si>
+    <t>竹の子族</t>
+  </si>
+  <si>
+    <t>ランデブー</t>
+  </si>
+  <si>
+    <t>イカす</t>
+  </si>
+  <si>
+    <t>とっくり</t>
+  </si>
+  <si>
+    <t>ギロッポン</t>
+  </si>
+  <si>
+    <t>シースー</t>
+  </si>
+  <si>
+    <t>シーメー</t>
+  </si>
+  <si>
+    <t>ザギン</t>
+  </si>
+  <si>
+    <t>バリ</t>
+  </si>
+  <si>
+    <t>儲かりまっか？</t>
+  </si>
+  <si>
+    <t>ええかっこしい</t>
+  </si>
+  <si>
+    <t>いちびり</t>
+  </si>
+  <si>
+    <t>ケチくさい</t>
+  </si>
+  <si>
+    <t>おべっか</t>
+  </si>
+  <si>
+    <t>自分（じぶん）</t>
+  </si>
+  <si>
+    <t>ええしの子</t>
+  </si>
+  <si>
+    <t>パチもん</t>
+  </si>
+  <si>
+    <t>べっちょない</t>
+  </si>
+  <si>
+    <t>さら</t>
+  </si>
+  <si>
+    <t>おばん</t>
+  </si>
+  <si>
+    <t>おっさん</t>
+  </si>
+  <si>
+    <t>ほかす</t>
+  </si>
+  <si>
+    <t>シュッとしてる</t>
+  </si>
+  <si>
+    <t>カチカチ山</t>
+  </si>
+  <si>
+    <t>おちょくる</t>
+  </si>
+  <si>
+    <t>けったいな</t>
+  </si>
+  <si>
+    <t>おっちん</t>
+  </si>
+  <si>
+    <t>べべた</t>
+  </si>
+  <si>
+    <t>めめ（おめめ）</t>
+  </si>
+  <si>
+    <t>飴ちゃん</t>
+  </si>
+  <si>
+    <t>関西</t>
+    <rPh sb="0" eb="2">
+      <t>カンサイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>№</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>なんぼのもんじゃい！</t>
+  </si>
+  <si>
+    <t>ワレ</t>
+  </si>
+  <si>
+    <t>ええ加減にさらせ</t>
+  </si>
+  <si>
+    <t>ぐぜる</t>
+  </si>
+  <si>
+    <t>いらち</t>
+  </si>
+  <si>
+    <t>おまはん</t>
+  </si>
+  <si>
+    <t>どんつき</t>
+  </si>
+  <si>
+    <t>レイコー</t>
+  </si>
+  <si>
+    <t>パーマあてる</t>
+  </si>
+  <si>
+    <t>ごんた</t>
+  </si>
+  <si>
+    <t>あかんたれ</t>
+  </si>
+  <si>
+    <t>スカタン</t>
+  </si>
+  <si>
+    <t>ケツ割る</t>
+  </si>
+  <si>
+    <t>ええ塩梅（あんばい）</t>
+  </si>
+  <si>
+    <t>けったいくそ悪い</t>
+  </si>
+  <si>
+    <t>おもろない</t>
+  </si>
+  <si>
+    <t>おおきに</t>
+  </si>
+  <si>
+    <t>すまん</t>
+  </si>
+  <si>
+    <t>しらんけど</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ギャル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>必須</t>
+    <rPh sb="0" eb="2">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ハイカラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>しゃ～ない</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1611,7 +1894,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1651,6 +1934,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1750,7 +2039,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1853,6 +2142,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2410,7 +2702,9 @@
       <c r="AE3" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="AF3" s="11"/>
+      <c r="AF3" s="11" t="s">
+        <v>296</v>
+      </c>
       <c r="AG3" s="11"/>
       <c r="AH3" s="11"/>
       <c r="AI3" s="11"/>
@@ -13061,7 +13355,9 @@
         <v>250</v>
       </c>
       <c r="B253" s="3"/>
-      <c r="C253" s="21"/>
+      <c r="C253" s="21" t="s">
+        <v>298</v>
+      </c>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
       <c r="F253" s="1"/>
@@ -13100,7 +13396,9 @@
         <v>251</v>
       </c>
       <c r="B254" s="3"/>
-      <c r="C254" s="21"/>
+      <c r="C254" s="21" t="s">
+        <v>299</v>
+      </c>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
       <c r="F254" s="1"/>
@@ -13139,7 +13437,9 @@
         <v>252</v>
       </c>
       <c r="B255" s="3"/>
-      <c r="C255" s="21"/>
+      <c r="C255" s="21" t="s">
+        <v>300</v>
+      </c>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
       <c r="F255" s="1"/>
@@ -14630,7 +14930,9 @@
       <c r="H31" s="18"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="19"/>
+      <c r="A32" s="19" t="s">
+        <v>297</v>
+      </c>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
       <c r="D32" s="18"/>
@@ -16040,4 +16342,2259 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B979FDD-83A3-41C6-8CB0-C39167BCC619}">
+  <dimension ref="A1:E221"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <cols>
+    <col min="1" max="1" width="3.8125" customWidth="1"/>
+    <col min="2" max="2" width="4.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.625" customWidth="1"/>
+    <col min="4" max="4" width="29.1875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="38" t="s">
+        <v>355</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>354</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>376</v>
+      </c>
+      <c r="D1" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="38"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="36">
+        <v>1</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="36" t="s">
+        <v>301</v>
+      </c>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="36">
+        <v>2</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="36">
+        <v>3</v>
+      </c>
+      <c r="B4" s="36"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="36">
+        <v>4</v>
+      </c>
+      <c r="B5" s="36"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="36" t="s">
+        <v>304</v>
+      </c>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="36">
+        <v>5</v>
+      </c>
+      <c r="B6" s="36"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="36">
+        <v>6</v>
+      </c>
+      <c r="B7" s="36"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="36" t="s">
+        <v>306</v>
+      </c>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="36">
+        <v>7</v>
+      </c>
+      <c r="B8" s="36"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="36" t="s">
+        <v>307</v>
+      </c>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="36">
+        <v>8</v>
+      </c>
+      <c r="B9" s="36"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="36">
+        <v>9</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="36" t="s">
+        <v>309</v>
+      </c>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="36">
+        <v>10</v>
+      </c>
+      <c r="B11" s="36"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="36" t="s">
+        <v>310</v>
+      </c>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="36">
+        <v>11</v>
+      </c>
+      <c r="B12" s="36"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="36" t="s">
+        <v>311</v>
+      </c>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="36">
+        <v>12</v>
+      </c>
+      <c r="B13" s="36"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="36" t="s">
+        <v>312</v>
+      </c>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="36">
+        <v>13</v>
+      </c>
+      <c r="B14" s="36"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="36" t="s">
+        <v>313</v>
+      </c>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="36">
+        <v>14</v>
+      </c>
+      <c r="B15" s="36"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="36" t="s">
+        <v>314</v>
+      </c>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="36">
+        <v>15</v>
+      </c>
+      <c r="B16" s="36"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="36" t="s">
+        <v>315</v>
+      </c>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="36">
+        <v>16</v>
+      </c>
+      <c r="B17" s="36"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="36" t="s">
+        <v>316</v>
+      </c>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="36">
+        <v>17</v>
+      </c>
+      <c r="B18" s="36"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="36" t="s">
+        <v>317</v>
+      </c>
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="36">
+        <v>18</v>
+      </c>
+      <c r="B19" s="36"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="36" t="s">
+        <v>318</v>
+      </c>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="36">
+        <v>19</v>
+      </c>
+      <c r="B20" s="36"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="36" t="s">
+        <v>319</v>
+      </c>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="36">
+        <v>20</v>
+      </c>
+      <c r="B21" s="36"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="36" t="s">
+        <v>320</v>
+      </c>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="36">
+        <v>21</v>
+      </c>
+      <c r="B22" s="36"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="36" t="s">
+        <v>321</v>
+      </c>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="36">
+        <v>22</v>
+      </c>
+      <c r="B23" s="36"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="36" t="s">
+        <v>322</v>
+      </c>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="36">
+        <v>23</v>
+      </c>
+      <c r="B24" s="36"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="36" t="s">
+        <v>323</v>
+      </c>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="36">
+        <v>24</v>
+      </c>
+      <c r="B25" s="36"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="36">
+        <v>25</v>
+      </c>
+      <c r="B26" s="36"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="36" t="s">
+        <v>325</v>
+      </c>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="36">
+        <v>26</v>
+      </c>
+      <c r="B27" s="36"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="36" t="s">
+        <v>326</v>
+      </c>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="36">
+        <v>27</v>
+      </c>
+      <c r="B28" s="36"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="36" t="s">
+        <v>327</v>
+      </c>
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="36">
+        <v>28</v>
+      </c>
+      <c r="B29" s="36"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="36" t="s">
+        <v>328</v>
+      </c>
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="36">
+        <v>29</v>
+      </c>
+      <c r="B30" s="36"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="E30" s="3"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="36">
+        <v>30</v>
+      </c>
+      <c r="B31" s="36"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="36" t="s">
+        <v>330</v>
+      </c>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="36">
+        <v>31</v>
+      </c>
+      <c r="B32" s="36"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="36" t="s">
+        <v>331</v>
+      </c>
+      <c r="E32" s="3"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="36">
+        <v>32</v>
+      </c>
+      <c r="B33" s="36"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="36">
+        <v>33</v>
+      </c>
+      <c r="B34" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="36" t="s">
+        <v>333</v>
+      </c>
+      <c r="E34" s="3"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="36">
+        <v>34</v>
+      </c>
+      <c r="B35" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="36" t="s">
+        <v>334</v>
+      </c>
+      <c r="E35" s="3"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="36" t="s">
+        <v>335</v>
+      </c>
+      <c r="E36" s="3"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="36">
+        <v>36</v>
+      </c>
+      <c r="B37" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="E37" s="3"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="36">
+        <v>37</v>
+      </c>
+      <c r="B38" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="36" t="s">
+        <v>337</v>
+      </c>
+      <c r="E38" s="3"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="36">
+        <v>38</v>
+      </c>
+      <c r="B39" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="36" t="s">
+        <v>338</v>
+      </c>
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="36">
+        <v>39</v>
+      </c>
+      <c r="B40" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="36" t="s">
+        <v>339</v>
+      </c>
+      <c r="E40" s="3"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="36">
+        <v>40</v>
+      </c>
+      <c r="B41" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="36" t="s">
+        <v>340</v>
+      </c>
+      <c r="E41" s="3"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="36">
+        <v>41</v>
+      </c>
+      <c r="B42" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="36" t="s">
+        <v>341</v>
+      </c>
+      <c r="E42" s="3"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="36">
+        <v>42</v>
+      </c>
+      <c r="B43" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="36" t="s">
+        <v>342</v>
+      </c>
+      <c r="E43" s="3"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="36">
+        <v>43</v>
+      </c>
+      <c r="B44" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="36" t="s">
+        <v>343</v>
+      </c>
+      <c r="E44" s="3"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="36">
+        <v>44</v>
+      </c>
+      <c r="B45" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="36" t="s">
+        <v>344</v>
+      </c>
+      <c r="E45" s="3"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="36">
+        <v>45</v>
+      </c>
+      <c r="B46" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="36" t="s">
+        <v>345</v>
+      </c>
+      <c r="E46" s="3"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="36">
+        <v>46</v>
+      </c>
+      <c r="B47" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="36" t="s">
+        <v>346</v>
+      </c>
+      <c r="E47" s="3"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="36">
+        <v>47</v>
+      </c>
+      <c r="B48" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="36" t="s">
+        <v>347</v>
+      </c>
+      <c r="E48" s="3"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="36">
+        <v>48</v>
+      </c>
+      <c r="B49" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C49" s="3"/>
+      <c r="D49" s="36" t="s">
+        <v>348</v>
+      </c>
+      <c r="E49" s="3"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="36">
+        <v>49</v>
+      </c>
+      <c r="B50" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="36" t="s">
+        <v>349</v>
+      </c>
+      <c r="E50" s="3"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="36">
+        <v>50</v>
+      </c>
+      <c r="B51" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="36" t="s">
+        <v>350</v>
+      </c>
+      <c r="E51" s="3"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="36">
+        <v>51</v>
+      </c>
+      <c r="B52" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="36" t="s">
+        <v>351</v>
+      </c>
+      <c r="E52" s="3"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="36">
+        <v>52</v>
+      </c>
+      <c r="B53" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C53" s="3"/>
+      <c r="D53" s="36" t="s">
+        <v>352</v>
+      </c>
+      <c r="E53" s="3"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="36">
+        <v>53</v>
+      </c>
+      <c r="B54" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C54" s="3"/>
+      <c r="D54" s="36" t="s">
+        <v>353</v>
+      </c>
+      <c r="E54" s="3"/>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="36">
+        <v>54</v>
+      </c>
+      <c r="B55" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C55" s="3"/>
+      <c r="D55" s="36" t="s">
+        <v>356</v>
+      </c>
+      <c r="E55" s="3"/>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="36">
+        <v>55</v>
+      </c>
+      <c r="B56" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="36" t="s">
+        <v>357</v>
+      </c>
+      <c r="E56" s="3"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="36">
+        <v>56</v>
+      </c>
+      <c r="B57" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="36" t="s">
+        <v>358</v>
+      </c>
+      <c r="E57" s="3"/>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="36">
+        <v>57</v>
+      </c>
+      <c r="B58" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="36" t="s">
+        <v>359</v>
+      </c>
+      <c r="E58" s="3"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="36">
+        <v>58</v>
+      </c>
+      <c r="B59" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="36" t="s">
+        <v>360</v>
+      </c>
+      <c r="E59" s="3"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="36">
+        <v>59</v>
+      </c>
+      <c r="B60" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="36" t="s">
+        <v>361</v>
+      </c>
+      <c r="E60" s="3"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="36">
+        <v>60</v>
+      </c>
+      <c r="B61" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="36" t="s">
+        <v>362</v>
+      </c>
+      <c r="E61" s="3"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="36">
+        <v>61</v>
+      </c>
+      <c r="B62" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="36" t="s">
+        <v>363</v>
+      </c>
+      <c r="E62" s="3"/>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="36">
+        <v>62</v>
+      </c>
+      <c r="B63" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C63" s="3"/>
+      <c r="D63" s="36" t="s">
+        <v>364</v>
+      </c>
+      <c r="E63" s="3"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="36">
+        <v>63</v>
+      </c>
+      <c r="B64" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="36" t="s">
+        <v>365</v>
+      </c>
+      <c r="E64" s="3"/>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="36">
+        <v>64</v>
+      </c>
+      <c r="B65" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C65" s="3"/>
+      <c r="D65" s="36" t="s">
+        <v>366</v>
+      </c>
+      <c r="E65" s="3"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="36">
+        <v>65</v>
+      </c>
+      <c r="B66" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C66" s="3"/>
+      <c r="D66" s="36" t="s">
+        <v>367</v>
+      </c>
+      <c r="E66" s="3"/>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="36">
+        <v>66</v>
+      </c>
+      <c r="B67" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="D67" s="36" t="s">
+        <v>368</v>
+      </c>
+      <c r="E67" s="3"/>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="36">
+        <v>67</v>
+      </c>
+      <c r="B68" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C68" s="3"/>
+      <c r="D68" s="36" t="s">
+        <v>369</v>
+      </c>
+      <c r="E68" s="3"/>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="36">
+        <v>68</v>
+      </c>
+      <c r="B69" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C69" s="3"/>
+      <c r="D69" s="36" t="s">
+        <v>370</v>
+      </c>
+      <c r="E69" s="3"/>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="36">
+        <v>69</v>
+      </c>
+      <c r="B70" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C70" s="3"/>
+      <c r="D70" s="36" t="s">
+        <v>371</v>
+      </c>
+      <c r="E70" s="3"/>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="36">
+        <v>70</v>
+      </c>
+      <c r="B71" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D71" s="37" t="s">
+        <v>372</v>
+      </c>
+      <c r="E71" s="3"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="36">
+        <v>71</v>
+      </c>
+      <c r="B72" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D72" s="37" t="s">
+        <v>373</v>
+      </c>
+      <c r="E72" s="3"/>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="36">
+        <v>72</v>
+      </c>
+      <c r="B73" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D73" s="37" t="s">
+        <v>374</v>
+      </c>
+      <c r="E73" s="3"/>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="36">
+        <v>73</v>
+      </c>
+      <c r="B74" s="36"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="36" t="s">
+        <v>375</v>
+      </c>
+      <c r="E74" s="3"/>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="36">
+        <v>74</v>
+      </c>
+      <c r="B75" s="36"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="36" t="s">
+        <v>377</v>
+      </c>
+      <c r="E75" s="3"/>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="36">
+        <v>75</v>
+      </c>
+      <c r="B76" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="36" t="s">
+        <v>378</v>
+      </c>
+      <c r="E76" s="3"/>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="36">
+        <v>76</v>
+      </c>
+      <c r="B77" s="36"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="36"/>
+      <c r="E77" s="3"/>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="36">
+        <v>77</v>
+      </c>
+      <c r="B78" s="36"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="3"/>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="36">
+        <v>78</v>
+      </c>
+      <c r="B79" s="36"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="36"/>
+      <c r="E79" s="3"/>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="36">
+        <v>79</v>
+      </c>
+      <c r="B80" s="36"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="36"/>
+      <c r="E80" s="3"/>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="36">
+        <v>80</v>
+      </c>
+      <c r="B81" s="36"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="36"/>
+      <c r="E81" s="3"/>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="36">
+        <v>81</v>
+      </c>
+      <c r="B82" s="36"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="36"/>
+      <c r="E82" s="3"/>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="36">
+        <v>82</v>
+      </c>
+      <c r="B83" s="36"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="36"/>
+      <c r="E83" s="3"/>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="36">
+        <v>83</v>
+      </c>
+      <c r="B84" s="36"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="3"/>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="36">
+        <v>84</v>
+      </c>
+      <c r="B85" s="36"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="36"/>
+      <c r="E85" s="3"/>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="36">
+        <v>85</v>
+      </c>
+      <c r="B86" s="36"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="36"/>
+      <c r="E86" s="3"/>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="36">
+        <v>86</v>
+      </c>
+      <c r="B87" s="36"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="36"/>
+      <c r="E87" s="3"/>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="36">
+        <v>87</v>
+      </c>
+      <c r="B88" s="36"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="36"/>
+      <c r="E88" s="3"/>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="36">
+        <v>88</v>
+      </c>
+      <c r="B89" s="36"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="3"/>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="36">
+        <v>89</v>
+      </c>
+      <c r="B90" s="36"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="36"/>
+      <c r="E90" s="3"/>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="36">
+        <v>90</v>
+      </c>
+      <c r="B91" s="36"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="36"/>
+      <c r="E91" s="3"/>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="36">
+        <v>91</v>
+      </c>
+      <c r="B92" s="36"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="36"/>
+      <c r="E92" s="3"/>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="36">
+        <v>92</v>
+      </c>
+      <c r="B93" s="36"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="36"/>
+      <c r="E93" s="3"/>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="36">
+        <v>93</v>
+      </c>
+      <c r="B94" s="36"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="36"/>
+      <c r="E94" s="3"/>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="36">
+        <v>94</v>
+      </c>
+      <c r="B95" s="36"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="3"/>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="36">
+        <v>95</v>
+      </c>
+      <c r="B96" s="36"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="36"/>
+      <c r="E96" s="3"/>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="36">
+        <v>96</v>
+      </c>
+      <c r="B97" s="36"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="36"/>
+      <c r="E97" s="3"/>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="36">
+        <v>97</v>
+      </c>
+      <c r="B98" s="36"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="36"/>
+      <c r="E98" s="3"/>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="36">
+        <v>98</v>
+      </c>
+      <c r="B99" s="36"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="36"/>
+      <c r="E99" s="3"/>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="36">
+        <v>99</v>
+      </c>
+      <c r="B100" s="36"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="36"/>
+      <c r="E100" s="3"/>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="36">
+        <v>100</v>
+      </c>
+      <c r="B101" s="36"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="36"/>
+      <c r="E101" s="3"/>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="36">
+        <v>101</v>
+      </c>
+      <c r="B102" s="36"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="36"/>
+      <c r="E102" s="3"/>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="36">
+        <v>102</v>
+      </c>
+      <c r="B103" s="36"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="36"/>
+      <c r="E103" s="3"/>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="36">
+        <v>103</v>
+      </c>
+      <c r="B104" s="36"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="36"/>
+      <c r="E104" s="3"/>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="36">
+        <v>104</v>
+      </c>
+      <c r="B105" s="36"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="36"/>
+      <c r="E105" s="3"/>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="36">
+        <v>105</v>
+      </c>
+      <c r="B106" s="36"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="36"/>
+      <c r="E106" s="3"/>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="36">
+        <v>106</v>
+      </c>
+      <c r="B107" s="36"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="36"/>
+      <c r="E107" s="3"/>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="36">
+        <v>107</v>
+      </c>
+      <c r="B108" s="36"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="36"/>
+      <c r="E108" s="3"/>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="36">
+        <v>108</v>
+      </c>
+      <c r="B109" s="36"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="36"/>
+      <c r="E109" s="3"/>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="36">
+        <v>109</v>
+      </c>
+      <c r="B110" s="36"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="36"/>
+      <c r="E110" s="3"/>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="36">
+        <v>110</v>
+      </c>
+      <c r="B111" s="36"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="36"/>
+      <c r="E111" s="3"/>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="36">
+        <v>111</v>
+      </c>
+      <c r="B112" s="36"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="36"/>
+      <c r="E112" s="3"/>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="36">
+        <v>112</v>
+      </c>
+      <c r="B113" s="36"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="36"/>
+      <c r="E113" s="3"/>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="36">
+        <v>113</v>
+      </c>
+      <c r="B114" s="36"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="36"/>
+      <c r="E114" s="3"/>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="36">
+        <v>114</v>
+      </c>
+      <c r="B115" s="36"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="36"/>
+      <c r="E115" s="3"/>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="36">
+        <v>115</v>
+      </c>
+      <c r="B116" s="36"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="36"/>
+      <c r="E116" s="3"/>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="36">
+        <v>116</v>
+      </c>
+      <c r="B117" s="36"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="36"/>
+      <c r="E117" s="3"/>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="36">
+        <v>117</v>
+      </c>
+      <c r="B118" s="36"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="36"/>
+      <c r="E118" s="3"/>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="36">
+        <v>118</v>
+      </c>
+      <c r="B119" s="36"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="36"/>
+      <c r="E119" s="3"/>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="36">
+        <v>119</v>
+      </c>
+      <c r="B120" s="36"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="36"/>
+      <c r="E120" s="3"/>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="36">
+        <v>120</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="3"/>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="36">
+        <v>121</v>
+      </c>
+      <c r="B122" s="36"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="36"/>
+      <c r="E122" s="3"/>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="36">
+        <v>122</v>
+      </c>
+      <c r="B123" s="36"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="36"/>
+      <c r="E123" s="3"/>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="36">
+        <v>123</v>
+      </c>
+      <c r="B124" s="36"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="36"/>
+      <c r="E124" s="3"/>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="36">
+        <v>124</v>
+      </c>
+      <c r="B125" s="36"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="36"/>
+      <c r="E125" s="3"/>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="36">
+        <v>125</v>
+      </c>
+      <c r="B126" s="36"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="36"/>
+      <c r="E126" s="3"/>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="36">
+        <v>126</v>
+      </c>
+      <c r="B127" s="36"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="36"/>
+      <c r="E127" s="3"/>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="36">
+        <v>127</v>
+      </c>
+      <c r="B128" s="36"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="36"/>
+      <c r="E128" s="3"/>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="36">
+        <v>128</v>
+      </c>
+      <c r="B129" s="36"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="36"/>
+      <c r="E129" s="3"/>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="36">
+        <v>129</v>
+      </c>
+      <c r="B130" s="36"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="36"/>
+      <c r="E130" s="3"/>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="36">
+        <v>130</v>
+      </c>
+      <c r="B131" s="36"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="36"/>
+      <c r="E131" s="3"/>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" s="36">
+        <v>131</v>
+      </c>
+      <c r="B132" s="36"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="36"/>
+      <c r="E132" s="3"/>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="36">
+        <v>132</v>
+      </c>
+      <c r="B133" s="36"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="36"/>
+      <c r="E133" s="3"/>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="36">
+        <v>133</v>
+      </c>
+      <c r="B134" s="36"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="36"/>
+      <c r="E134" s="3"/>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="36">
+        <v>134</v>
+      </c>
+      <c r="B135" s="36"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="36"/>
+      <c r="E135" s="3"/>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="36">
+        <v>135</v>
+      </c>
+      <c r="B136" s="36"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="36"/>
+      <c r="E136" s="3"/>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="36">
+        <v>136</v>
+      </c>
+      <c r="B137" s="36"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="36"/>
+      <c r="E137" s="3"/>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="36">
+        <v>137</v>
+      </c>
+      <c r="B138" s="36"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="36"/>
+      <c r="E138" s="3"/>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="36">
+        <v>138</v>
+      </c>
+      <c r="B139" s="36"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="36"/>
+      <c r="E139" s="3"/>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="36">
+        <v>139</v>
+      </c>
+      <c r="B140" s="36"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="36"/>
+      <c r="E140" s="3"/>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="36">
+        <v>140</v>
+      </c>
+      <c r="B141" s="36"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="36"/>
+      <c r="E141" s="3"/>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="36">
+        <v>141</v>
+      </c>
+      <c r="B142" s="36"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="36"/>
+      <c r="E142" s="3"/>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="36">
+        <v>142</v>
+      </c>
+      <c r="B143" s="36"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="36"/>
+      <c r="E143" s="3"/>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="36">
+        <v>143</v>
+      </c>
+      <c r="B144" s="36"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="36"/>
+      <c r="E144" s="3"/>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="36">
+        <v>144</v>
+      </c>
+      <c r="B145" s="36"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="36"/>
+      <c r="E145" s="3"/>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="36">
+        <v>145</v>
+      </c>
+      <c r="B146" s="36"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="36"/>
+      <c r="E146" s="3"/>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="36">
+        <v>146</v>
+      </c>
+      <c r="B147" s="36"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="36"/>
+      <c r="E147" s="3"/>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="36">
+        <v>147</v>
+      </c>
+      <c r="B148" s="36"/>
+      <c r="C148" s="3"/>
+      <c r="D148" s="36"/>
+      <c r="E148" s="3"/>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="36">
+        <v>148</v>
+      </c>
+      <c r="B149" s="36"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="36"/>
+      <c r="E149" s="3"/>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="36">
+        <v>149</v>
+      </c>
+      <c r="B150" s="36"/>
+      <c r="C150" s="3"/>
+      <c r="D150" s="36"/>
+      <c r="E150" s="3"/>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="36">
+        <v>150</v>
+      </c>
+      <c r="B151" s="36"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="36"/>
+      <c r="E151" s="3"/>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="36">
+        <v>151</v>
+      </c>
+      <c r="B152" s="36"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="36"/>
+      <c r="E152" s="3"/>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="36">
+        <v>152</v>
+      </c>
+      <c r="B153" s="36"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="36"/>
+      <c r="E153" s="3"/>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="36">
+        <v>153</v>
+      </c>
+      <c r="B154" s="36"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="36"/>
+      <c r="E154" s="3"/>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="36">
+        <v>154</v>
+      </c>
+      <c r="B155" s="36"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="36"/>
+      <c r="E155" s="3"/>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="36">
+        <v>155</v>
+      </c>
+      <c r="B156" s="36"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="36"/>
+      <c r="E156" s="3"/>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="36">
+        <v>156</v>
+      </c>
+      <c r="B157" s="36"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="36"/>
+      <c r="E157" s="3"/>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="36">
+        <v>157</v>
+      </c>
+      <c r="B158" s="36"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="36"/>
+      <c r="E158" s="3"/>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="36">
+        <v>158</v>
+      </c>
+      <c r="B159" s="36"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="36"/>
+      <c r="E159" s="3"/>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" s="36">
+        <v>159</v>
+      </c>
+      <c r="B160" s="36"/>
+      <c r="C160" s="3"/>
+      <c r="D160" s="36"/>
+      <c r="E160" s="3"/>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="36">
+        <v>160</v>
+      </c>
+      <c r="B161" s="36"/>
+      <c r="C161" s="3"/>
+      <c r="D161" s="36"/>
+      <c r="E161" s="3"/>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="36">
+        <v>161</v>
+      </c>
+      <c r="B162" s="36"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="36"/>
+      <c r="E162" s="3"/>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="36">
+        <v>162</v>
+      </c>
+      <c r="B163" s="36"/>
+      <c r="C163" s="3"/>
+      <c r="D163" s="36"/>
+      <c r="E163" s="3"/>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="36">
+        <v>163</v>
+      </c>
+      <c r="B164" s="36"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="36"/>
+      <c r="E164" s="3"/>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="36">
+        <v>164</v>
+      </c>
+      <c r="B165" s="36"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="36"/>
+      <c r="E165" s="3"/>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="36">
+        <v>165</v>
+      </c>
+      <c r="B166" s="36"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="36"/>
+      <c r="E166" s="3"/>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="36">
+        <v>166</v>
+      </c>
+      <c r="B167" s="36"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="36"/>
+      <c r="E167" s="3"/>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="36">
+        <v>167</v>
+      </c>
+      <c r="B168" s="36"/>
+      <c r="C168" s="3"/>
+      <c r="D168" s="36"/>
+      <c r="E168" s="3"/>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="36">
+        <v>168</v>
+      </c>
+      <c r="B169" s="36"/>
+      <c r="C169" s="3"/>
+      <c r="D169" s="36"/>
+      <c r="E169" s="3"/>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="36">
+        <v>169</v>
+      </c>
+      <c r="B170" s="36"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="36"/>
+      <c r="E170" s="3"/>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="36">
+        <v>170</v>
+      </c>
+      <c r="B171" s="36"/>
+      <c r="C171" s="3"/>
+      <c r="D171" s="36"/>
+      <c r="E171" s="3"/>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="36">
+        <v>171</v>
+      </c>
+      <c r="B172" s="36"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="36"/>
+      <c r="E172" s="3"/>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="36">
+        <v>172</v>
+      </c>
+      <c r="B173" s="36"/>
+      <c r="C173" s="3"/>
+      <c r="D173" s="36"/>
+      <c r="E173" s="3"/>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="36">
+        <v>173</v>
+      </c>
+      <c r="B174" s="36"/>
+      <c r="C174" s="3"/>
+      <c r="D174" s="36"/>
+      <c r="E174" s="3"/>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="36">
+        <v>174</v>
+      </c>
+      <c r="B175" s="36"/>
+      <c r="C175" s="3"/>
+      <c r="D175" s="36"/>
+      <c r="E175" s="3"/>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="36">
+        <v>175</v>
+      </c>
+      <c r="B176" s="36"/>
+      <c r="C176" s="3"/>
+      <c r="D176" s="36"/>
+      <c r="E176" s="3"/>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="36">
+        <v>176</v>
+      </c>
+      <c r="B177" s="36"/>
+      <c r="C177" s="3"/>
+      <c r="D177" s="36"/>
+      <c r="E177" s="3"/>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="36">
+        <v>177</v>
+      </c>
+      <c r="B178" s="36"/>
+      <c r="C178" s="3"/>
+      <c r="D178" s="36"/>
+      <c r="E178" s="3"/>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="36">
+        <v>178</v>
+      </c>
+      <c r="B179" s="36"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="36"/>
+      <c r="E179" s="3"/>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="36">
+        <v>179</v>
+      </c>
+      <c r="B180" s="36"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="36"/>
+      <c r="E180" s="3"/>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="36">
+        <v>180</v>
+      </c>
+      <c r="B181" s="36"/>
+      <c r="C181" s="3"/>
+      <c r="D181" s="36"/>
+      <c r="E181" s="3"/>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="36">
+        <v>181</v>
+      </c>
+      <c r="B182" s="36"/>
+      <c r="C182" s="3"/>
+      <c r="D182" s="36"/>
+      <c r="E182" s="3"/>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="36">
+        <v>182</v>
+      </c>
+      <c r="B183" s="36"/>
+      <c r="C183" s="3"/>
+      <c r="D183" s="36"/>
+      <c r="E183" s="3"/>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="36">
+        <v>183</v>
+      </c>
+      <c r="B184" s="36"/>
+      <c r="C184" s="3"/>
+      <c r="D184" s="36"/>
+      <c r="E184" s="3"/>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="36">
+        <v>184</v>
+      </c>
+      <c r="B185" s="36"/>
+      <c r="C185" s="3"/>
+      <c r="D185" s="36"/>
+      <c r="E185" s="3"/>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" s="36">
+        <v>185</v>
+      </c>
+      <c r="B186" s="36"/>
+      <c r="C186" s="3"/>
+      <c r="D186" s="36"/>
+      <c r="E186" s="3"/>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" s="36">
+        <v>186</v>
+      </c>
+      <c r="B187" s="36"/>
+      <c r="C187" s="3"/>
+      <c r="D187" s="36"/>
+      <c r="E187" s="3"/>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="36">
+        <v>187</v>
+      </c>
+      <c r="B188" s="36"/>
+      <c r="C188" s="3"/>
+      <c r="D188" s="36"/>
+      <c r="E188" s="3"/>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="36">
+        <v>188</v>
+      </c>
+      <c r="B189" s="36"/>
+      <c r="C189" s="3"/>
+      <c r="D189" s="36"/>
+      <c r="E189" s="3"/>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="36">
+        <v>189</v>
+      </c>
+      <c r="B190" s="36"/>
+      <c r="C190" s="3"/>
+      <c r="D190" s="36"/>
+      <c r="E190" s="3"/>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="36">
+        <v>190</v>
+      </c>
+      <c r="B191" s="36"/>
+      <c r="C191" s="3"/>
+      <c r="D191" s="36"/>
+      <c r="E191" s="3"/>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="36">
+        <v>191</v>
+      </c>
+      <c r="B192" s="36"/>
+      <c r="C192" s="3"/>
+      <c r="D192" s="36"/>
+      <c r="E192" s="3"/>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="36">
+        <v>192</v>
+      </c>
+      <c r="B193" s="36"/>
+      <c r="C193" s="3"/>
+      <c r="D193" s="36"/>
+      <c r="E193" s="3"/>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="36">
+        <v>193</v>
+      </c>
+      <c r="B194" s="36"/>
+      <c r="C194" s="3"/>
+      <c r="D194" s="36"/>
+      <c r="E194" s="3"/>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="36">
+        <v>194</v>
+      </c>
+      <c r="B195" s="36"/>
+      <c r="C195" s="3"/>
+      <c r="D195" s="36"/>
+      <c r="E195" s="3"/>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="36">
+        <v>195</v>
+      </c>
+      <c r="B196" s="36"/>
+      <c r="C196" s="3"/>
+      <c r="D196" s="36"/>
+      <c r="E196" s="3"/>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="36">
+        <v>196</v>
+      </c>
+      <c r="B197" s="36"/>
+      <c r="C197" s="3"/>
+      <c r="D197" s="36"/>
+      <c r="E197" s="3"/>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="36">
+        <v>197</v>
+      </c>
+      <c r="B198" s="36"/>
+      <c r="C198" s="3"/>
+      <c r="D198" s="36"/>
+      <c r="E198" s="3"/>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="36">
+        <v>198</v>
+      </c>
+      <c r="B199" s="36"/>
+      <c r="C199" s="3"/>
+      <c r="D199" s="36"/>
+      <c r="E199" s="3"/>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="36">
+        <v>199</v>
+      </c>
+      <c r="B200" s="36"/>
+      <c r="C200" s="3"/>
+      <c r="D200" s="36"/>
+      <c r="E200" s="3"/>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="36">
+        <v>200</v>
+      </c>
+      <c r="B201" s="36"/>
+      <c r="C201" s="3"/>
+      <c r="D201" s="36"/>
+      <c r="E201" s="3"/>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="36">
+        <v>201</v>
+      </c>
+      <c r="B202" s="36"/>
+      <c r="C202" s="3"/>
+      <c r="D202" s="36"/>
+      <c r="E202" s="3"/>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="36">
+        <v>202</v>
+      </c>
+      <c r="B203" s="36"/>
+      <c r="C203" s="3"/>
+      <c r="D203" s="36"/>
+      <c r="E203" s="3"/>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="36">
+        <v>203</v>
+      </c>
+      <c r="B204" s="36"/>
+      <c r="C204" s="3"/>
+      <c r="D204" s="36"/>
+      <c r="E204" s="3"/>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="36">
+        <v>204</v>
+      </c>
+      <c r="B205" s="36"/>
+      <c r="C205" s="3"/>
+      <c r="D205" s="36"/>
+      <c r="E205" s="3"/>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="36">
+        <v>205</v>
+      </c>
+      <c r="B206" s="36"/>
+      <c r="C206" s="3"/>
+      <c r="D206" s="36"/>
+      <c r="E206" s="3"/>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="36">
+        <v>206</v>
+      </c>
+      <c r="B207" s="36"/>
+      <c r="C207" s="3"/>
+      <c r="D207" s="36"/>
+      <c r="E207" s="3"/>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="36">
+        <v>207</v>
+      </c>
+      <c r="B208" s="36"/>
+      <c r="C208" s="3"/>
+      <c r="D208" s="36"/>
+      <c r="E208" s="3"/>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="36">
+        <v>208</v>
+      </c>
+      <c r="B209" s="36"/>
+      <c r="C209" s="3"/>
+      <c r="D209" s="36"/>
+      <c r="E209" s="3"/>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="36">
+        <v>209</v>
+      </c>
+      <c r="B210" s="36"/>
+      <c r="C210" s="3"/>
+      <c r="D210" s="36"/>
+      <c r="E210" s="3"/>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="36">
+        <v>210</v>
+      </c>
+      <c r="B211" s="36"/>
+      <c r="C211" s="3"/>
+      <c r="D211" s="36"/>
+      <c r="E211" s="3"/>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="36">
+        <v>211</v>
+      </c>
+      <c r="B212" s="36"/>
+      <c r="C212" s="3"/>
+      <c r="D212" s="36"/>
+      <c r="E212" s="3"/>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="36">
+        <v>212</v>
+      </c>
+      <c r="B213" s="36"/>
+      <c r="C213" s="3"/>
+      <c r="D213" s="36"/>
+      <c r="E213" s="3"/>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="36">
+        <v>213</v>
+      </c>
+      <c r="B214" s="36"/>
+      <c r="C214" s="3"/>
+      <c r="D214" s="36"/>
+      <c r="E214" s="3"/>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="36">
+        <v>214</v>
+      </c>
+      <c r="B215" s="36"/>
+      <c r="C215" s="3"/>
+      <c r="D215" s="36"/>
+      <c r="E215" s="3"/>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="36">
+        <v>215</v>
+      </c>
+      <c r="B216" s="36"/>
+      <c r="C216" s="3"/>
+      <c r="D216" s="36"/>
+      <c r="E216" s="3"/>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="36">
+        <v>216</v>
+      </c>
+      <c r="B217" s="36"/>
+      <c r="C217" s="3"/>
+      <c r="D217" s="36"/>
+      <c r="E217" s="3"/>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="36">
+        <v>217</v>
+      </c>
+      <c r="B218" s="36"/>
+      <c r="C218" s="3"/>
+      <c r="D218" s="36"/>
+      <c r="E218" s="3"/>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="36">
+        <v>218</v>
+      </c>
+      <c r="B219" s="36"/>
+      <c r="C219" s="3"/>
+      <c r="D219" s="36"/>
+      <c r="E219" s="3"/>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="36">
+        <v>219</v>
+      </c>
+      <c r="B220" s="36"/>
+      <c r="C220" s="3"/>
+      <c r="D220" s="36"/>
+      <c r="E220" s="3"/>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="36">
+        <v>220</v>
+      </c>
+      <c r="B221" s="36"/>
+      <c r="C221" s="3"/>
+      <c r="D221" s="36"/>
+      <c r="E221" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E221 C2:C221" xr:uid="{BB1BFAF5-92CA-4009-8ED1-905216C51CB6}">
+      <formula1>"〇,×,△"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7604DCAB-4506-44F8-93CB-3CEFA91029B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4069C655-AAF4-483F-9E07-507671A7DE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="リスト" sheetId="1" r:id="rId1"/>
@@ -2039,7 +2039,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2112,6 +2112,9 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2142,9 +2145,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2525,52 +2531,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI280"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="3.4375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.4375" style="24" customWidth="1"/>
+    <col min="1" max="1" width="3.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.4140625" style="24" customWidth="1"/>
     <col min="3" max="3" width="33.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="3.5625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="2.5625" bestFit="1" customWidth="1"/>
-    <col min="11" max="35" width="3.5625" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="3.58203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2.58203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="35" width="3.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="22.9">
-      <c r="A1" s="29"/>
-      <c r="B1" s="33" t="s">
+    <row r="1" spans="1:35" ht="22.5">
+      <c r="A1" s="32"/>
+      <c r="B1" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-    </row>
-    <row r="2" spans="1:35" ht="22.9">
-      <c r="A2" s="30"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="27"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+    </row>
+    <row r="2" spans="1:35" ht="22.5">
+      <c r="A2" s="33"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="30"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="e" vm="1">
         <v>#VALUE!</v>
@@ -2614,10 +2620,10 @@
       <c r="AH2" s="5"/>
       <c r="AI2" s="5"/>
     </row>
-    <row r="3" spans="1:35" s="13" customFormat="1" ht="106.9" thickBot="1">
-      <c r="A3" s="31"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="28"/>
+    <row r="3" spans="1:35" s="13" customFormat="1" ht="109.5" thickBot="1">
+      <c r="A3" s="34"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="11" t="s">
         <v>122</v>
       </c>
@@ -2756,7 +2762,7 @@
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
+      <c r="AE4" s="39"/>
       <c r="AF4" s="1"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="1"/>
@@ -2811,7 +2817,7 @@
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
-      <c r="AE5" s="1"/>
+      <c r="AE5" s="39"/>
       <c r="AF5" s="1"/>
       <c r="AG5" s="1"/>
       <c r="AH5" s="1"/>
@@ -2856,7 +2862,7 @@
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
+      <c r="AE6" s="39"/>
       <c r="AF6" s="1"/>
       <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
@@ -2897,7 +2903,7 @@
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
-      <c r="AE7" s="1"/>
+      <c r="AE7" s="39"/>
       <c r="AF7" s="1"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
@@ -2940,7 +2946,7 @@
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
+      <c r="AE8" s="39"/>
       <c r="AF8" s="1"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="1"/>
@@ -2981,7 +2987,7 @@
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
+      <c r="AE9" s="39"/>
       <c r="AF9" s="1"/>
       <c r="AG9" s="1"/>
       <c r="AH9" s="1"/>
@@ -3022,7 +3028,7 @@
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
-      <c r="AE10" s="1"/>
+      <c r="AE10" s="39"/>
       <c r="AF10" s="1"/>
       <c r="AG10" s="1"/>
       <c r="AH10" s="1"/>
@@ -3067,7 +3073,7 @@
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
-      <c r="AE11" s="1"/>
+      <c r="AE11" s="39"/>
       <c r="AF11" s="1"/>
       <c r="AG11" s="1"/>
       <c r="AH11" s="1"/>
@@ -3108,7 +3114,7 @@
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
+      <c r="AE12" s="39"/>
       <c r="AF12" s="1"/>
       <c r="AG12" s="1"/>
       <c r="AH12" s="1"/>
@@ -3149,7 +3155,7 @@
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
       <c r="AD13" s="1"/>
-      <c r="AE13" s="1"/>
+      <c r="AE13" s="39"/>
       <c r="AF13" s="1"/>
       <c r="AG13" s="1"/>
       <c r="AH13" s="1"/>
@@ -3190,7 +3196,7 @@
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
+      <c r="AE14" s="39"/>
       <c r="AF14" s="1"/>
       <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>
@@ -3231,7 +3237,7 @@
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
       <c r="AD15" s="1"/>
-      <c r="AE15" s="1"/>
+      <c r="AE15" s="39"/>
       <c r="AF15" s="1"/>
       <c r="AG15" s="1"/>
       <c r="AH15" s="1"/>
@@ -3272,7 +3278,7 @@
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
-      <c r="AE16" s="1"/>
+      <c r="AE16" s="39"/>
       <c r="AF16" s="1"/>
       <c r="AG16" s="1"/>
       <c r="AH16" s="1"/>
@@ -3313,7 +3319,7 @@
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
       <c r="AD17" s="1"/>
-      <c r="AE17" s="1"/>
+      <c r="AE17" s="39"/>
       <c r="AF17" s="1"/>
       <c r="AG17" s="1"/>
       <c r="AH17" s="1"/>
@@ -3356,7 +3362,7 @@
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
-      <c r="AE18" s="1"/>
+      <c r="AE18" s="39"/>
       <c r="AF18" s="1"/>
       <c r="AG18" s="1"/>
       <c r="AH18" s="1"/>
@@ -3397,7 +3403,7 @@
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
-      <c r="AE19" s="1"/>
+      <c r="AE19" s="39"/>
       <c r="AF19" s="1"/>
       <c r="AG19" s="1"/>
       <c r="AH19" s="1"/>
@@ -3438,7 +3444,7 @@
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
-      <c r="AE20" s="1"/>
+      <c r="AE20" s="39"/>
       <c r="AF20" s="1"/>
       <c r="AG20" s="1"/>
       <c r="AH20" s="1"/>
@@ -3479,7 +3485,7 @@
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
-      <c r="AE21" s="1"/>
+      <c r="AE21" s="39"/>
       <c r="AF21" s="1"/>
       <c r="AG21" s="1"/>
       <c r="AH21" s="1"/>
@@ -3522,7 +3528,7 @@
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
       <c r="AD22" s="1"/>
-      <c r="AE22" s="1"/>
+      <c r="AE22" s="39"/>
       <c r="AF22" s="1"/>
       <c r="AG22" s="1"/>
       <c r="AH22" s="1"/>
@@ -3563,7 +3569,7 @@
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
       <c r="AD23" s="1"/>
-      <c r="AE23" s="1"/>
+      <c r="AE23" s="39"/>
       <c r="AF23" s="1"/>
       <c r="AG23" s="1"/>
       <c r="AH23" s="1"/>
@@ -3606,7 +3612,7 @@
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
-      <c r="AE24" s="1"/>
+      <c r="AE24" s="39"/>
       <c r="AF24" s="1"/>
       <c r="AG24" s="1"/>
       <c r="AH24" s="1"/>
@@ -3649,7 +3655,7 @@
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
-      <c r="AE25" s="1"/>
+      <c r="AE25" s="39"/>
       <c r="AF25" s="1"/>
       <c r="AG25" s="1"/>
       <c r="AH25" s="1"/>
@@ -3690,7 +3696,7 @@
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
       <c r="AD26" s="1"/>
-      <c r="AE26" s="1"/>
+      <c r="AE26" s="39"/>
       <c r="AF26" s="1"/>
       <c r="AG26" s="1"/>
       <c r="AH26" s="1"/>
@@ -3733,7 +3739,7 @@
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
       <c r="AD27" s="1"/>
-      <c r="AE27" s="1"/>
+      <c r="AE27" s="39"/>
       <c r="AF27" s="1"/>
       <c r="AG27" s="1"/>
       <c r="AH27" s="1"/>
@@ -3774,7 +3780,7 @@
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
       <c r="AD28" s="1"/>
-      <c r="AE28" s="1"/>
+      <c r="AE28" s="39"/>
       <c r="AF28" s="1"/>
       <c r="AG28" s="1"/>
       <c r="AH28" s="1"/>
@@ -3815,7 +3821,7 @@
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
-      <c r="AE29" s="1"/>
+      <c r="AE29" s="39"/>
       <c r="AF29" s="1"/>
       <c r="AG29" s="1"/>
       <c r="AH29" s="1"/>
@@ -3858,7 +3864,7 @@
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
-      <c r="AE30" s="1"/>
+      <c r="AE30" s="39"/>
       <c r="AF30" s="1"/>
       <c r="AG30" s="1"/>
       <c r="AH30" s="1"/>
@@ -3905,7 +3911,7 @@
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
       <c r="AD31" s="1"/>
-      <c r="AE31" s="1"/>
+      <c r="AE31" s="39"/>
       <c r="AF31" s="1"/>
       <c r="AG31" s="1"/>
       <c r="AH31" s="1"/>
@@ -3948,7 +3954,7 @@
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
       <c r="AD32" s="1"/>
-      <c r="AE32" s="1"/>
+      <c r="AE32" s="39"/>
       <c r="AF32" s="1"/>
       <c r="AG32" s="1"/>
       <c r="AH32" s="1"/>
@@ -3989,7 +3995,7 @@
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
       <c r="AD33" s="1"/>
-      <c r="AE33" s="1"/>
+      <c r="AE33" s="39"/>
       <c r="AF33" s="1"/>
       <c r="AG33" s="1"/>
       <c r="AH33" s="1"/>
@@ -4030,7 +4036,7 @@
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
-      <c r="AE34" s="1"/>
+      <c r="AE34" s="39"/>
       <c r="AF34" s="1"/>
       <c r="AG34" s="1"/>
       <c r="AH34" s="1"/>
@@ -4071,7 +4077,7 @@
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
       <c r="AD35" s="1"/>
-      <c r="AE35" s="1"/>
+      <c r="AE35" s="39"/>
       <c r="AF35" s="1"/>
       <c r="AG35" s="1"/>
       <c r="AH35" s="1"/>
@@ -4112,7 +4118,7 @@
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
       <c r="AD36" s="1"/>
-      <c r="AE36" s="1"/>
+      <c r="AE36" s="39"/>
       <c r="AF36" s="1"/>
       <c r="AG36" s="1"/>
       <c r="AH36" s="1"/>
@@ -4153,7 +4159,7 @@
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
-      <c r="AE37" s="1"/>
+      <c r="AE37" s="39"/>
       <c r="AF37" s="1"/>
       <c r="AG37" s="1"/>
       <c r="AH37" s="1"/>
@@ -4194,7 +4200,7 @@
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
-      <c r="AE38" s="1"/>
+      <c r="AE38" s="39"/>
       <c r="AF38" s="1"/>
       <c r="AG38" s="1"/>
       <c r="AH38" s="1"/>
@@ -4237,7 +4243,7 @@
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
       <c r="AD39" s="1"/>
-      <c r="AE39" s="1"/>
+      <c r="AE39" s="39"/>
       <c r="AF39" s="1"/>
       <c r="AG39" s="1"/>
       <c r="AH39" s="1"/>
@@ -4280,7 +4286,7 @@
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
-      <c r="AE40" s="1"/>
+      <c r="AE40" s="39"/>
       <c r="AF40" s="1"/>
       <c r="AG40" s="1"/>
       <c r="AH40" s="1"/>
@@ -4323,7 +4329,7 @@
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
       <c r="AD41" s="1"/>
-      <c r="AE41" s="1"/>
+      <c r="AE41" s="39"/>
       <c r="AF41" s="1"/>
       <c r="AG41" s="1"/>
       <c r="AH41" s="1"/>
@@ -4364,7 +4370,7 @@
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
       <c r="AD42" s="1"/>
-      <c r="AE42" s="1"/>
+      <c r="AE42" s="39"/>
       <c r="AF42" s="1"/>
       <c r="AG42" s="1"/>
       <c r="AH42" s="1"/>
@@ -4407,7 +4413,7 @@
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
       <c r="AD43" s="1"/>
-      <c r="AE43" s="1"/>
+      <c r="AE43" s="39"/>
       <c r="AF43" s="1"/>
       <c r="AG43" s="1"/>
       <c r="AH43" s="1"/>
@@ -4448,7 +4454,7 @@
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
-      <c r="AE44" s="1"/>
+      <c r="AE44" s="39"/>
       <c r="AF44" s="1"/>
       <c r="AG44" s="1"/>
       <c r="AH44" s="1"/>
@@ -4489,7 +4495,7 @@
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
       <c r="AD45" s="1"/>
-      <c r="AE45" s="1"/>
+      <c r="AE45" s="39"/>
       <c r="AF45" s="1"/>
       <c r="AG45" s="1"/>
       <c r="AH45" s="1"/>
@@ -4530,7 +4536,7 @@
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
-      <c r="AE46" s="1"/>
+      <c r="AE46" s="39"/>
       <c r="AF46" s="1"/>
       <c r="AG46" s="1"/>
       <c r="AH46" s="1"/>
@@ -4571,7 +4577,7 @@
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
       <c r="AD47" s="1"/>
-      <c r="AE47" s="1"/>
+      <c r="AE47" s="39"/>
       <c r="AF47" s="1"/>
       <c r="AG47" s="1"/>
       <c r="AH47" s="1"/>
@@ -4614,7 +4620,7 @@
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
       <c r="AD48" s="1"/>
-      <c r="AE48" s="1"/>
+      <c r="AE48" s="39"/>
       <c r="AF48" s="1"/>
       <c r="AG48" s="1"/>
       <c r="AH48" s="1"/>
@@ -4655,7 +4661,7 @@
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
       <c r="AD49" s="1"/>
-      <c r="AE49" s="1"/>
+      <c r="AE49" s="39"/>
       <c r="AF49" s="1"/>
       <c r="AG49" s="1"/>
       <c r="AH49" s="1"/>
@@ -4698,7 +4704,7 @@
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
-      <c r="AE50" s="1"/>
+      <c r="AE50" s="39"/>
       <c r="AF50" s="1"/>
       <c r="AG50" s="1"/>
       <c r="AH50" s="1"/>
@@ -4739,7 +4745,7 @@
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
-      <c r="AE51" s="1"/>
+      <c r="AE51" s="39"/>
       <c r="AF51" s="1"/>
       <c r="AG51" s="1"/>
       <c r="AH51" s="1"/>
@@ -4780,7 +4786,7 @@
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
-      <c r="AE52" s="1"/>
+      <c r="AE52" s="39"/>
       <c r="AF52" s="1"/>
       <c r="AG52" s="1"/>
       <c r="AH52" s="1"/>
@@ -4821,7 +4827,7 @@
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
       <c r="AD53" s="1"/>
-      <c r="AE53" s="1"/>
+      <c r="AE53" s="39"/>
       <c r="AF53" s="1"/>
       <c r="AG53" s="1"/>
       <c r="AH53" s="1"/>
@@ -4864,7 +4870,7 @@
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
-      <c r="AE54" s="1"/>
+      <c r="AE54" s="39"/>
       <c r="AF54" s="1"/>
       <c r="AG54" s="1"/>
       <c r="AH54" s="1"/>
@@ -4907,7 +4913,7 @@
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
       <c r="AD55" s="1"/>
-      <c r="AE55" s="1"/>
+      <c r="AE55" s="39"/>
       <c r="AF55" s="1"/>
       <c r="AG55" s="1"/>
       <c r="AH55" s="1"/>
@@ -4948,7 +4954,7 @@
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
-      <c r="AE56" s="1"/>
+      <c r="AE56" s="39"/>
       <c r="AF56" s="1"/>
       <c r="AG56" s="1"/>
       <c r="AH56" s="1"/>
@@ -4989,7 +4995,7 @@
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
       <c r="AD57" s="1"/>
-      <c r="AE57" s="1"/>
+      <c r="AE57" s="39"/>
       <c r="AF57" s="1"/>
       <c r="AG57" s="1"/>
       <c r="AH57" s="1"/>
@@ -5030,7 +5036,7 @@
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
       <c r="AD58" s="1"/>
-      <c r="AE58" s="1"/>
+      <c r="AE58" s="39"/>
       <c r="AF58" s="1"/>
       <c r="AG58" s="1"/>
       <c r="AH58" s="1"/>
@@ -5071,7 +5077,7 @@
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
       <c r="AD59" s="1"/>
-      <c r="AE59" s="1"/>
+      <c r="AE59" s="39"/>
       <c r="AF59" s="1"/>
       <c r="AG59" s="1"/>
       <c r="AH59" s="1"/>
@@ -5112,7 +5118,7 @@
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
       <c r="AD60" s="1"/>
-      <c r="AE60" s="1"/>
+      <c r="AE60" s="39"/>
       <c r="AF60" s="1"/>
       <c r="AG60" s="1"/>
       <c r="AH60" s="1"/>
@@ -5153,7 +5159,7 @@
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
       <c r="AD61" s="1"/>
-      <c r="AE61" s="1"/>
+      <c r="AE61" s="39"/>
       <c r="AF61" s="1"/>
       <c r="AG61" s="1"/>
       <c r="AH61" s="1"/>
@@ -5194,7 +5200,7 @@
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
       <c r="AD62" s="1"/>
-      <c r="AE62" s="1"/>
+      <c r="AE62" s="39"/>
       <c r="AF62" s="1"/>
       <c r="AG62" s="1"/>
       <c r="AH62" s="1"/>
@@ -5237,7 +5243,7 @@
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
       <c r="AD63" s="1"/>
-      <c r="AE63" s="1"/>
+      <c r="AE63" s="39"/>
       <c r="AF63" s="1"/>
       <c r="AG63" s="1"/>
       <c r="AH63" s="1"/>
@@ -5282,7 +5288,7 @@
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
       <c r="AD64" s="1"/>
-      <c r="AE64" s="1"/>
+      <c r="AE64" s="39"/>
       <c r="AF64" s="1"/>
       <c r="AG64" s="1"/>
       <c r="AH64" s="1"/>
@@ -5325,7 +5331,7 @@
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
       <c r="AD65" s="1"/>
-      <c r="AE65" s="1"/>
+      <c r="AE65" s="39"/>
       <c r="AF65" s="1"/>
       <c r="AG65" s="1"/>
       <c r="AH65" s="1"/>
@@ -5366,7 +5372,7 @@
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
       <c r="AD66" s="1"/>
-      <c r="AE66" s="1"/>
+      <c r="AE66" s="39"/>
       <c r="AF66" s="1"/>
       <c r="AG66" s="1"/>
       <c r="AH66" s="1"/>
@@ -5411,7 +5417,7 @@
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
       <c r="AD67" s="1"/>
-      <c r="AE67" s="1"/>
+      <c r="AE67" s="39"/>
       <c r="AF67" s="1"/>
       <c r="AG67" s="1"/>
       <c r="AH67" s="1"/>
@@ -5454,7 +5460,7 @@
       <c r="AB68" s="1"/>
       <c r="AC68" s="1"/>
       <c r="AD68" s="1"/>
-      <c r="AE68" s="1"/>
+      <c r="AE68" s="39"/>
       <c r="AF68" s="1"/>
       <c r="AG68" s="1"/>
       <c r="AH68" s="1"/>
@@ -5499,7 +5505,7 @@
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
       <c r="AD69" s="1"/>
-      <c r="AE69" s="1"/>
+      <c r="AE69" s="39"/>
       <c r="AF69" s="1"/>
       <c r="AG69" s="1"/>
       <c r="AH69" s="1"/>
@@ -5542,7 +5548,7 @@
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
       <c r="AD70" s="1"/>
-      <c r="AE70" s="1"/>
+      <c r="AE70" s="39"/>
       <c r="AF70" s="1"/>
       <c r="AG70" s="1"/>
       <c r="AH70" s="1"/>
@@ -5585,7 +5591,7 @@
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
       <c r="AD71" s="1"/>
-      <c r="AE71" s="1"/>
+      <c r="AE71" s="39"/>
       <c r="AF71" s="1"/>
       <c r="AG71" s="1"/>
       <c r="AH71" s="1"/>
@@ -5626,7 +5632,7 @@
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
       <c r="AD72" s="1"/>
-      <c r="AE72" s="1"/>
+      <c r="AE72" s="39"/>
       <c r="AF72" s="1"/>
       <c r="AG72" s="1"/>
       <c r="AH72" s="1"/>
@@ -5667,7 +5673,7 @@
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
       <c r="AD73" s="1"/>
-      <c r="AE73" s="1"/>
+      <c r="AE73" s="39"/>
       <c r="AF73" s="1"/>
       <c r="AG73" s="1"/>
       <c r="AH73" s="1"/>
@@ -5708,7 +5714,7 @@
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
       <c r="AD74" s="1"/>
-      <c r="AE74" s="1"/>
+      <c r="AE74" s="39"/>
       <c r="AF74" s="1"/>
       <c r="AG74" s="1"/>
       <c r="AH74" s="1"/>
@@ -5749,7 +5755,7 @@
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
       <c r="AD75" s="1"/>
-      <c r="AE75" s="1"/>
+      <c r="AE75" s="39"/>
       <c r="AF75" s="1"/>
       <c r="AG75" s="1"/>
       <c r="AH75" s="1"/>
@@ -5794,7 +5800,7 @@
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
       <c r="AD76" s="1"/>
-      <c r="AE76" s="1"/>
+      <c r="AE76" s="39"/>
       <c r="AF76" s="1"/>
       <c r="AG76" s="1"/>
       <c r="AH76" s="1"/>
@@ -5837,7 +5843,7 @@
       <c r="AB77" s="1"/>
       <c r="AC77" s="1"/>
       <c r="AD77" s="1"/>
-      <c r="AE77" s="1"/>
+      <c r="AE77" s="39"/>
       <c r="AF77" s="1"/>
       <c r="AG77" s="1"/>
       <c r="AH77" s="1"/>
@@ -5880,7 +5886,7 @@
       <c r="AB78" s="1"/>
       <c r="AC78" s="1"/>
       <c r="AD78" s="1"/>
-      <c r="AE78" s="1"/>
+      <c r="AE78" s="39"/>
       <c r="AF78" s="1"/>
       <c r="AG78" s="1"/>
       <c r="AH78" s="1"/>
@@ -5923,7 +5929,7 @@
       <c r="AB79" s="1"/>
       <c r="AC79" s="1"/>
       <c r="AD79" s="1"/>
-      <c r="AE79" s="1"/>
+      <c r="AE79" s="39"/>
       <c r="AF79" s="1"/>
       <c r="AG79" s="1"/>
       <c r="AH79" s="1"/>
@@ -5966,7 +5972,7 @@
       <c r="AB80" s="1"/>
       <c r="AC80" s="1"/>
       <c r="AD80" s="1"/>
-      <c r="AE80" s="1"/>
+      <c r="AE80" s="39"/>
       <c r="AF80" s="1"/>
       <c r="AG80" s="1"/>
       <c r="AH80" s="1"/>
@@ -6011,7 +6017,7 @@
       <c r="AB81" s="1"/>
       <c r="AC81" s="1"/>
       <c r="AD81" s="1"/>
-      <c r="AE81" s="1"/>
+      <c r="AE81" s="39"/>
       <c r="AF81" s="1"/>
       <c r="AG81" s="1"/>
       <c r="AH81" s="1"/>
@@ -6056,7 +6062,7 @@
       <c r="AB82" s="1"/>
       <c r="AC82" s="1"/>
       <c r="AD82" s="1"/>
-      <c r="AE82" s="1"/>
+      <c r="AE82" s="39"/>
       <c r="AF82" s="1"/>
       <c r="AG82" s="1"/>
       <c r="AH82" s="1"/>
@@ -6101,7 +6107,7 @@
       <c r="AB83" s="1"/>
       <c r="AC83" s="1"/>
       <c r="AD83" s="1"/>
-      <c r="AE83" s="1"/>
+      <c r="AE83" s="39"/>
       <c r="AF83" s="1"/>
       <c r="AG83" s="1"/>
       <c r="AH83" s="1"/>
@@ -6144,7 +6150,7 @@
       <c r="AB84" s="1"/>
       <c r="AC84" s="1"/>
       <c r="AD84" s="1"/>
-      <c r="AE84" s="1"/>
+      <c r="AE84" s="39"/>
       <c r="AF84" s="1"/>
       <c r="AG84" s="1"/>
       <c r="AH84" s="1"/>
@@ -6185,7 +6191,7 @@
       <c r="AB85" s="1"/>
       <c r="AC85" s="1"/>
       <c r="AD85" s="1"/>
-      <c r="AE85" s="1"/>
+      <c r="AE85" s="39"/>
       <c r="AF85" s="1"/>
       <c r="AG85" s="1"/>
       <c r="AH85" s="1"/>
@@ -6226,7 +6232,7 @@
       <c r="AB86" s="1"/>
       <c r="AC86" s="1"/>
       <c r="AD86" s="1"/>
-      <c r="AE86" s="1"/>
+      <c r="AE86" s="39"/>
       <c r="AF86" s="1"/>
       <c r="AG86" s="1"/>
       <c r="AH86" s="1"/>
@@ -6267,7 +6273,7 @@
       <c r="AB87" s="1"/>
       <c r="AC87" s="1"/>
       <c r="AD87" s="1"/>
-      <c r="AE87" s="1"/>
+      <c r="AE87" s="39"/>
       <c r="AF87" s="1"/>
       <c r="AG87" s="1"/>
       <c r="AH87" s="1"/>
@@ -6310,7 +6316,7 @@
       <c r="AB88" s="1"/>
       <c r="AC88" s="1"/>
       <c r="AD88" s="1"/>
-      <c r="AE88" s="1"/>
+      <c r="AE88" s="39"/>
       <c r="AF88" s="1"/>
       <c r="AG88" s="1"/>
       <c r="AH88" s="1"/>
@@ -6351,7 +6357,7 @@
       <c r="AB89" s="1"/>
       <c r="AC89" s="1"/>
       <c r="AD89" s="1"/>
-      <c r="AE89" s="1"/>
+      <c r="AE89" s="39"/>
       <c r="AF89" s="1"/>
       <c r="AG89" s="1"/>
       <c r="AH89" s="1"/>
@@ -6392,7 +6398,7 @@
       <c r="AB90" s="1"/>
       <c r="AC90" s="1"/>
       <c r="AD90" s="1"/>
-      <c r="AE90" s="1"/>
+      <c r="AE90" s="39"/>
       <c r="AF90" s="1"/>
       <c r="AG90" s="1"/>
       <c r="AH90" s="1"/>
@@ -6435,7 +6441,7 @@
       <c r="AB91" s="1"/>
       <c r="AC91" s="1"/>
       <c r="AD91" s="1"/>
-      <c r="AE91" s="1"/>
+      <c r="AE91" s="39"/>
       <c r="AF91" s="1"/>
       <c r="AG91" s="1"/>
       <c r="AH91" s="1"/>
@@ -6478,7 +6484,7 @@
       <c r="AB92" s="1"/>
       <c r="AC92" s="1"/>
       <c r="AD92" s="1"/>
-      <c r="AE92" s="1"/>
+      <c r="AE92" s="39"/>
       <c r="AF92" s="1"/>
       <c r="AG92" s="1"/>
       <c r="AH92" s="1"/>
@@ -6519,7 +6525,7 @@
       <c r="AB93" s="1"/>
       <c r="AC93" s="1"/>
       <c r="AD93" s="1"/>
-      <c r="AE93" s="1"/>
+      <c r="AE93" s="39"/>
       <c r="AF93" s="1"/>
       <c r="AG93" s="1"/>
       <c r="AH93" s="1"/>
@@ -6560,7 +6566,7 @@
       <c r="AB94" s="1"/>
       <c r="AC94" s="1"/>
       <c r="AD94" s="1"/>
-      <c r="AE94" s="1"/>
+      <c r="AE94" s="39"/>
       <c r="AF94" s="1"/>
       <c r="AG94" s="1"/>
       <c r="AH94" s="1"/>
@@ -6601,7 +6607,7 @@
       <c r="AB95" s="1"/>
       <c r="AC95" s="1"/>
       <c r="AD95" s="1"/>
-      <c r="AE95" s="1"/>
+      <c r="AE95" s="39"/>
       <c r="AF95" s="1"/>
       <c r="AG95" s="1"/>
       <c r="AH95" s="1"/>
@@ -6642,7 +6648,7 @@
       <c r="AB96" s="1"/>
       <c r="AC96" s="1"/>
       <c r="AD96" s="1"/>
-      <c r="AE96" s="1"/>
+      <c r="AE96" s="39"/>
       <c r="AF96" s="1"/>
       <c r="AG96" s="1"/>
       <c r="AH96" s="1"/>
@@ -6683,7 +6689,7 @@
       <c r="AB97" s="1"/>
       <c r="AC97" s="1"/>
       <c r="AD97" s="1"/>
-      <c r="AE97" s="1"/>
+      <c r="AE97" s="39"/>
       <c r="AF97" s="1"/>
       <c r="AG97" s="1"/>
       <c r="AH97" s="1"/>
@@ -6726,7 +6732,7 @@
       <c r="AB98" s="1"/>
       <c r="AC98" s="1"/>
       <c r="AD98" s="1"/>
-      <c r="AE98" s="1"/>
+      <c r="AE98" s="39"/>
       <c r="AF98" s="1"/>
       <c r="AG98" s="1"/>
       <c r="AH98" s="1"/>
@@ -6767,7 +6773,7 @@
       <c r="AB99" s="1"/>
       <c r="AC99" s="1"/>
       <c r="AD99" s="1"/>
-      <c r="AE99" s="1"/>
+      <c r="AE99" s="39"/>
       <c r="AF99" s="1"/>
       <c r="AG99" s="1"/>
       <c r="AH99" s="1"/>
@@ -6808,7 +6814,7 @@
       <c r="AB100" s="1"/>
       <c r="AC100" s="1"/>
       <c r="AD100" s="1"/>
-      <c r="AE100" s="1"/>
+      <c r="AE100" s="39"/>
       <c r="AF100" s="1"/>
       <c r="AG100" s="1"/>
       <c r="AH100" s="1"/>
@@ -6849,7 +6855,7 @@
       <c r="AB101" s="1"/>
       <c r="AC101" s="1"/>
       <c r="AD101" s="1"/>
-      <c r="AE101" s="1"/>
+      <c r="AE101" s="39"/>
       <c r="AF101" s="1"/>
       <c r="AG101" s="1"/>
       <c r="AH101" s="1"/>
@@ -6890,7 +6896,7 @@
       <c r="AB102" s="1"/>
       <c r="AC102" s="1"/>
       <c r="AD102" s="1"/>
-      <c r="AE102" s="1"/>
+      <c r="AE102" s="39"/>
       <c r="AF102" s="1"/>
       <c r="AG102" s="1"/>
       <c r="AH102" s="1"/>
@@ -6931,7 +6937,7 @@
       <c r="AB103" s="1"/>
       <c r="AC103" s="1"/>
       <c r="AD103" s="1"/>
-      <c r="AE103" s="1"/>
+      <c r="AE103" s="39"/>
       <c r="AF103" s="1"/>
       <c r="AG103" s="1"/>
       <c r="AH103" s="1"/>
@@ -6972,7 +6978,7 @@
       <c r="AB104" s="1"/>
       <c r="AC104" s="1"/>
       <c r="AD104" s="1"/>
-      <c r="AE104" s="1"/>
+      <c r="AE104" s="39"/>
       <c r="AF104" s="1"/>
       <c r="AG104" s="1"/>
       <c r="AH104" s="1"/>
@@ -7015,7 +7021,7 @@
       <c r="AB105" s="1"/>
       <c r="AC105" s="1"/>
       <c r="AD105" s="1"/>
-      <c r="AE105" s="1"/>
+      <c r="AE105" s="39"/>
       <c r="AF105" s="1"/>
       <c r="AG105" s="1"/>
       <c r="AH105" s="1"/>
@@ -7056,7 +7062,7 @@
       <c r="AB106" s="1"/>
       <c r="AC106" s="1"/>
       <c r="AD106" s="1"/>
-      <c r="AE106" s="1"/>
+      <c r="AE106" s="39"/>
       <c r="AF106" s="1"/>
       <c r="AG106" s="1"/>
       <c r="AH106" s="1"/>
@@ -7099,7 +7105,7 @@
       <c r="AB107" s="1"/>
       <c r="AC107" s="1"/>
       <c r="AD107" s="1"/>
-      <c r="AE107" s="1"/>
+      <c r="AE107" s="39"/>
       <c r="AF107" s="1"/>
       <c r="AG107" s="1"/>
       <c r="AH107" s="1"/>
@@ -7140,7 +7146,7 @@
       <c r="AB108" s="1"/>
       <c r="AC108" s="1"/>
       <c r="AD108" s="1"/>
-      <c r="AE108" s="1"/>
+      <c r="AE108" s="39"/>
       <c r="AF108" s="1"/>
       <c r="AG108" s="1"/>
       <c r="AH108" s="1"/>
@@ -7183,7 +7189,7 @@
       <c r="AB109" s="1"/>
       <c r="AC109" s="1"/>
       <c r="AD109" s="1"/>
-      <c r="AE109" s="1"/>
+      <c r="AE109" s="39"/>
       <c r="AF109" s="1"/>
       <c r="AG109" s="1"/>
       <c r="AH109" s="1"/>
@@ -7224,7 +7230,7 @@
       <c r="AB110" s="1"/>
       <c r="AC110" s="1"/>
       <c r="AD110" s="1"/>
-      <c r="AE110" s="1"/>
+      <c r="AE110" s="39"/>
       <c r="AF110" s="1"/>
       <c r="AG110" s="1"/>
       <c r="AH110" s="1"/>
@@ -7265,7 +7271,7 @@
       <c r="AB111" s="1"/>
       <c r="AC111" s="1"/>
       <c r="AD111" s="1"/>
-      <c r="AE111" s="1"/>
+      <c r="AE111" s="39"/>
       <c r="AF111" s="1"/>
       <c r="AG111" s="1"/>
       <c r="AH111" s="1"/>
@@ -7312,7 +7318,7 @@
       <c r="AB112" s="1"/>
       <c r="AC112" s="1"/>
       <c r="AD112" s="1"/>
-      <c r="AE112" s="1"/>
+      <c r="AE112" s="39"/>
       <c r="AF112" s="1"/>
       <c r="AG112" s="1"/>
       <c r="AH112" s="1"/>
@@ -7355,7 +7361,7 @@
       <c r="AB113" s="1"/>
       <c r="AC113" s="1"/>
       <c r="AD113" s="1"/>
-      <c r="AE113" s="1"/>
+      <c r="AE113" s="39"/>
       <c r="AF113" s="1"/>
       <c r="AG113" s="1"/>
       <c r="AH113" s="1"/>
@@ -7396,7 +7402,7 @@
       <c r="AB114" s="1"/>
       <c r="AC114" s="1"/>
       <c r="AD114" s="1"/>
-      <c r="AE114" s="1"/>
+      <c r="AE114" s="39"/>
       <c r="AF114" s="1"/>
       <c r="AG114" s="1"/>
       <c r="AH114" s="1"/>
@@ -7439,7 +7445,7 @@
       <c r="AB115" s="1"/>
       <c r="AC115" s="1"/>
       <c r="AD115" s="1"/>
-      <c r="AE115" s="1"/>
+      <c r="AE115" s="39"/>
       <c r="AF115" s="1"/>
       <c r="AG115" s="1"/>
       <c r="AH115" s="1"/>
@@ -7480,7 +7486,7 @@
       <c r="AB116" s="1"/>
       <c r="AC116" s="1"/>
       <c r="AD116" s="1"/>
-      <c r="AE116" s="1"/>
+      <c r="AE116" s="39"/>
       <c r="AF116" s="1"/>
       <c r="AG116" s="1"/>
       <c r="AH116" s="1"/>
@@ -7521,7 +7527,7 @@
       <c r="AB117" s="1"/>
       <c r="AC117" s="1"/>
       <c r="AD117" s="1"/>
-      <c r="AE117" s="1"/>
+      <c r="AE117" s="39"/>
       <c r="AF117" s="1"/>
       <c r="AG117" s="1"/>
       <c r="AH117" s="1"/>
@@ -7562,7 +7568,7 @@
       <c r="AB118" s="1"/>
       <c r="AC118" s="1"/>
       <c r="AD118" s="1"/>
-      <c r="AE118" s="1"/>
+      <c r="AE118" s="39"/>
       <c r="AF118" s="1"/>
       <c r="AG118" s="1"/>
       <c r="AH118" s="1"/>
@@ -7603,7 +7609,7 @@
       <c r="AB119" s="1"/>
       <c r="AC119" s="1"/>
       <c r="AD119" s="1"/>
-      <c r="AE119" s="1"/>
+      <c r="AE119" s="39"/>
       <c r="AF119" s="1"/>
       <c r="AG119" s="1"/>
       <c r="AH119" s="1"/>
@@ -7644,7 +7650,7 @@
       <c r="AB120" s="1"/>
       <c r="AC120" s="1"/>
       <c r="AD120" s="1"/>
-      <c r="AE120" s="1"/>
+      <c r="AE120" s="39"/>
       <c r="AF120" s="1"/>
       <c r="AG120" s="1"/>
       <c r="AH120" s="1"/>
@@ -7685,7 +7691,7 @@
       <c r="AB121" s="1"/>
       <c r="AC121" s="1"/>
       <c r="AD121" s="1"/>
-      <c r="AE121" s="1"/>
+      <c r="AE121" s="39"/>
       <c r="AF121" s="1"/>
       <c r="AG121" s="1"/>
       <c r="AH121" s="1"/>
@@ -7726,7 +7732,7 @@
       <c r="AB122" s="1"/>
       <c r="AC122" s="1"/>
       <c r="AD122" s="1"/>
-      <c r="AE122" s="1"/>
+      <c r="AE122" s="39"/>
       <c r="AF122" s="1"/>
       <c r="AG122" s="1"/>
       <c r="AH122" s="1"/>
@@ -7767,7 +7773,7 @@
       <c r="AB123" s="1"/>
       <c r="AC123" s="1"/>
       <c r="AD123" s="1"/>
-      <c r="AE123" s="1"/>
+      <c r="AE123" s="39"/>
       <c r="AF123" s="1"/>
       <c r="AG123" s="1"/>
       <c r="AH123" s="1"/>
@@ -7808,7 +7814,7 @@
       <c r="AB124" s="1"/>
       <c r="AC124" s="1"/>
       <c r="AD124" s="1"/>
-      <c r="AE124" s="1"/>
+      <c r="AE124" s="39"/>
       <c r="AF124" s="1"/>
       <c r="AG124" s="1"/>
       <c r="AH124" s="1"/>
@@ -7849,7 +7855,7 @@
       <c r="AB125" s="1"/>
       <c r="AC125" s="1"/>
       <c r="AD125" s="1"/>
-      <c r="AE125" s="1"/>
+      <c r="AE125" s="39"/>
       <c r="AF125" s="1"/>
       <c r="AG125" s="1"/>
       <c r="AH125" s="1"/>
@@ -7892,7 +7898,7 @@
       <c r="AB126" s="1"/>
       <c r="AC126" s="1"/>
       <c r="AD126" s="1"/>
-      <c r="AE126" s="1"/>
+      <c r="AE126" s="39"/>
       <c r="AF126" s="1"/>
       <c r="AG126" s="1"/>
       <c r="AH126" s="1"/>
@@ -7933,7 +7939,7 @@
       <c r="AB127" s="1"/>
       <c r="AC127" s="1"/>
       <c r="AD127" s="1"/>
-      <c r="AE127" s="1"/>
+      <c r="AE127" s="39"/>
       <c r="AF127" s="1"/>
       <c r="AG127" s="1"/>
       <c r="AH127" s="1"/>
@@ -7978,7 +7984,7 @@
       <c r="AB128" s="1"/>
       <c r="AC128" s="1"/>
       <c r="AD128" s="1"/>
-      <c r="AE128" s="1"/>
+      <c r="AE128" s="39"/>
       <c r="AF128" s="1"/>
       <c r="AG128" s="1"/>
       <c r="AH128" s="1"/>
@@ -8021,7 +8027,7 @@
       <c r="AB129" s="1"/>
       <c r="AC129" s="1"/>
       <c r="AD129" s="1"/>
-      <c r="AE129" s="1"/>
+      <c r="AE129" s="39"/>
       <c r="AF129" s="1"/>
       <c r="AG129" s="1"/>
       <c r="AH129" s="1"/>
@@ -8066,7 +8072,7 @@
       <c r="AB130" s="1"/>
       <c r="AC130" s="1"/>
       <c r="AD130" s="1"/>
-      <c r="AE130" s="1"/>
+      <c r="AE130" s="39"/>
       <c r="AF130" s="1"/>
       <c r="AG130" s="1"/>
       <c r="AH130" s="1"/>
@@ -8109,7 +8115,7 @@
       <c r="AB131" s="1"/>
       <c r="AC131" s="1"/>
       <c r="AD131" s="1"/>
-      <c r="AE131" s="1"/>
+      <c r="AE131" s="39"/>
       <c r="AF131" s="1"/>
       <c r="AG131" s="1"/>
       <c r="AH131" s="1"/>
@@ -8150,7 +8156,7 @@
       <c r="AB132" s="1"/>
       <c r="AC132" s="1"/>
       <c r="AD132" s="1"/>
-      <c r="AE132" s="1"/>
+      <c r="AE132" s="39"/>
       <c r="AF132" s="1"/>
       <c r="AG132" s="1"/>
       <c r="AH132" s="1"/>
@@ -8191,7 +8197,7 @@
       <c r="AB133" s="1"/>
       <c r="AC133" s="1"/>
       <c r="AD133" s="1"/>
-      <c r="AE133" s="1"/>
+      <c r="AE133" s="39"/>
       <c r="AF133" s="1"/>
       <c r="AG133" s="1"/>
       <c r="AH133" s="1"/>
@@ -8232,7 +8238,7 @@
       <c r="AB134" s="1"/>
       <c r="AC134" s="1"/>
       <c r="AD134" s="1"/>
-      <c r="AE134" s="1"/>
+      <c r="AE134" s="39"/>
       <c r="AF134" s="1"/>
       <c r="AG134" s="1"/>
       <c r="AH134" s="1"/>
@@ -8273,7 +8279,7 @@
       <c r="AB135" s="1"/>
       <c r="AC135" s="1"/>
       <c r="AD135" s="1"/>
-      <c r="AE135" s="1"/>
+      <c r="AE135" s="39"/>
       <c r="AF135" s="1"/>
       <c r="AG135" s="1"/>
       <c r="AH135" s="1"/>
@@ -8314,7 +8320,7 @@
       <c r="AB136" s="1"/>
       <c r="AC136" s="1"/>
       <c r="AD136" s="1"/>
-      <c r="AE136" s="1"/>
+      <c r="AE136" s="39"/>
       <c r="AF136" s="1"/>
       <c r="AG136" s="1"/>
       <c r="AH136" s="1"/>
@@ -8355,7 +8361,7 @@
       <c r="AB137" s="1"/>
       <c r="AC137" s="1"/>
       <c r="AD137" s="1"/>
-      <c r="AE137" s="1"/>
+      <c r="AE137" s="39"/>
       <c r="AF137" s="1"/>
       <c r="AG137" s="1"/>
       <c r="AH137" s="1"/>
@@ -8396,7 +8402,7 @@
       <c r="AB138" s="1"/>
       <c r="AC138" s="1"/>
       <c r="AD138" s="1"/>
-      <c r="AE138" s="1"/>
+      <c r="AE138" s="39"/>
       <c r="AF138" s="1"/>
       <c r="AG138" s="1"/>
       <c r="AH138" s="1"/>
@@ -8437,7 +8443,7 @@
       <c r="AB139" s="1"/>
       <c r="AC139" s="1"/>
       <c r="AD139" s="1"/>
-      <c r="AE139" s="1"/>
+      <c r="AE139" s="39"/>
       <c r="AF139" s="1"/>
       <c r="AG139" s="1"/>
       <c r="AH139" s="1"/>
@@ -8478,7 +8484,7 @@
       <c r="AB140" s="1"/>
       <c r="AC140" s="1"/>
       <c r="AD140" s="1"/>
-      <c r="AE140" s="1"/>
+      <c r="AE140" s="39"/>
       <c r="AF140" s="1"/>
       <c r="AG140" s="1"/>
       <c r="AH140" s="1"/>
@@ -8519,7 +8525,7 @@
       <c r="AB141" s="1"/>
       <c r="AC141" s="1"/>
       <c r="AD141" s="1"/>
-      <c r="AE141" s="1"/>
+      <c r="AE141" s="39"/>
       <c r="AF141" s="1"/>
       <c r="AG141" s="1"/>
       <c r="AH141" s="1"/>
@@ -8560,7 +8566,7 @@
       <c r="AB142" s="1"/>
       <c r="AC142" s="1"/>
       <c r="AD142" s="1"/>
-      <c r="AE142" s="1"/>
+      <c r="AE142" s="39"/>
       <c r="AF142" s="1"/>
       <c r="AG142" s="1"/>
       <c r="AH142" s="1"/>
@@ -8601,7 +8607,7 @@
       <c r="AB143" s="1"/>
       <c r="AC143" s="1"/>
       <c r="AD143" s="1"/>
-      <c r="AE143" s="1"/>
+      <c r="AE143" s="39"/>
       <c r="AF143" s="1"/>
       <c r="AG143" s="1"/>
       <c r="AH143" s="1"/>
@@ -8642,7 +8648,7 @@
       <c r="AB144" s="1"/>
       <c r="AC144" s="1"/>
       <c r="AD144" s="1"/>
-      <c r="AE144" s="1"/>
+      <c r="AE144" s="39"/>
       <c r="AF144" s="1"/>
       <c r="AG144" s="1"/>
       <c r="AH144" s="1"/>
@@ -8683,7 +8689,7 @@
       <c r="AB145" s="1"/>
       <c r="AC145" s="1"/>
       <c r="AD145" s="1"/>
-      <c r="AE145" s="1"/>
+      <c r="AE145" s="39"/>
       <c r="AF145" s="1"/>
       <c r="AG145" s="1"/>
       <c r="AH145" s="1"/>
@@ -8724,7 +8730,7 @@
       <c r="AB146" s="1"/>
       <c r="AC146" s="1"/>
       <c r="AD146" s="1"/>
-      <c r="AE146" s="1"/>
+      <c r="AE146" s="39"/>
       <c r="AF146" s="1"/>
       <c r="AG146" s="1"/>
       <c r="AH146" s="1"/>
@@ -8765,7 +8771,7 @@
       <c r="AB147" s="1"/>
       <c r="AC147" s="1"/>
       <c r="AD147" s="1"/>
-      <c r="AE147" s="1"/>
+      <c r="AE147" s="39"/>
       <c r="AF147" s="1"/>
       <c r="AG147" s="1"/>
       <c r="AH147" s="1"/>
@@ -8808,7 +8814,7 @@
       <c r="AB148" s="1"/>
       <c r="AC148" s="1"/>
       <c r="AD148" s="1"/>
-      <c r="AE148" s="1"/>
+      <c r="AE148" s="39"/>
       <c r="AF148" s="1"/>
       <c r="AG148" s="1"/>
       <c r="AH148" s="1"/>
@@ -8849,7 +8855,7 @@
       <c r="AB149" s="1"/>
       <c r="AC149" s="1"/>
       <c r="AD149" s="1"/>
-      <c r="AE149" s="1"/>
+      <c r="AE149" s="39"/>
       <c r="AF149" s="1"/>
       <c r="AG149" s="1"/>
       <c r="AH149" s="1"/>
@@ -8890,7 +8896,7 @@
       <c r="AB150" s="1"/>
       <c r="AC150" s="1"/>
       <c r="AD150" s="1"/>
-      <c r="AE150" s="1"/>
+      <c r="AE150" s="39"/>
       <c r="AF150" s="1"/>
       <c r="AG150" s="1"/>
       <c r="AH150" s="1"/>
@@ -8931,7 +8937,7 @@
       <c r="AB151" s="1"/>
       <c r="AC151" s="1"/>
       <c r="AD151" s="1"/>
-      <c r="AE151" s="1"/>
+      <c r="AE151" s="39"/>
       <c r="AF151" s="1"/>
       <c r="AG151" s="1"/>
       <c r="AH151" s="1"/>
@@ -8972,7 +8978,7 @@
       <c r="AB152" s="1"/>
       <c r="AC152" s="1"/>
       <c r="AD152" s="1"/>
-      <c r="AE152" s="1"/>
+      <c r="AE152" s="39"/>
       <c r="AF152" s="1"/>
       <c r="AG152" s="1"/>
       <c r="AH152" s="1"/>
@@ -9015,7 +9021,7 @@
       <c r="AB153" s="1"/>
       <c r="AC153" s="1"/>
       <c r="AD153" s="1"/>
-      <c r="AE153" s="1"/>
+      <c r="AE153" s="39"/>
       <c r="AF153" s="1"/>
       <c r="AG153" s="1"/>
       <c r="AH153" s="1"/>
@@ -9058,7 +9064,7 @@
       <c r="AB154" s="1"/>
       <c r="AC154" s="1"/>
       <c r="AD154" s="1"/>
-      <c r="AE154" s="1"/>
+      <c r="AE154" s="39"/>
       <c r="AF154" s="1"/>
       <c r="AG154" s="1"/>
       <c r="AH154" s="1"/>
@@ -9103,7 +9109,7 @@
       <c r="AB155" s="1"/>
       <c r="AC155" s="1"/>
       <c r="AD155" s="1"/>
-      <c r="AE155" s="1"/>
+      <c r="AE155" s="39"/>
       <c r="AF155" s="1"/>
       <c r="AG155" s="1"/>
       <c r="AH155" s="1"/>
@@ -9146,7 +9152,7 @@
       <c r="AB156" s="1"/>
       <c r="AC156" s="1"/>
       <c r="AD156" s="1"/>
-      <c r="AE156" s="1"/>
+      <c r="AE156" s="39"/>
       <c r="AF156" s="1"/>
       <c r="AG156" s="1"/>
       <c r="AH156" s="1"/>
@@ -9189,7 +9195,7 @@
       <c r="AB157" s="1"/>
       <c r="AC157" s="1"/>
       <c r="AD157" s="1"/>
-      <c r="AE157" s="1"/>
+      <c r="AE157" s="39"/>
       <c r="AF157" s="1"/>
       <c r="AG157" s="1"/>
       <c r="AH157" s="1"/>
@@ -9234,7 +9240,7 @@
       <c r="AB158" s="1"/>
       <c r="AC158" s="1"/>
       <c r="AD158" s="1"/>
-      <c r="AE158" s="1"/>
+      <c r="AE158" s="39"/>
       <c r="AF158" s="1"/>
       <c r="AG158" s="1"/>
       <c r="AH158" s="1"/>
@@ -9277,7 +9283,7 @@
       <c r="AB159" s="1"/>
       <c r="AC159" s="1"/>
       <c r="AD159" s="1"/>
-      <c r="AE159" s="1"/>
+      <c r="AE159" s="39"/>
       <c r="AF159" s="1"/>
       <c r="AG159" s="1"/>
       <c r="AH159" s="1"/>
@@ -9322,7 +9328,7 @@
       <c r="AB160" s="1"/>
       <c r="AC160" s="1"/>
       <c r="AD160" s="1"/>
-      <c r="AE160" s="1"/>
+      <c r="AE160" s="39"/>
       <c r="AF160" s="1"/>
       <c r="AG160" s="1"/>
       <c r="AH160" s="1"/>
@@ -9365,7 +9371,7 @@
       <c r="AB161" s="1"/>
       <c r="AC161" s="1"/>
       <c r="AD161" s="1"/>
-      <c r="AE161" s="1"/>
+      <c r="AE161" s="39"/>
       <c r="AF161" s="1"/>
       <c r="AG161" s="1"/>
       <c r="AH161" s="1"/>
@@ -9408,7 +9414,7 @@
       <c r="AB162" s="1"/>
       <c r="AC162" s="1"/>
       <c r="AD162" s="1"/>
-      <c r="AE162" s="1"/>
+      <c r="AE162" s="39"/>
       <c r="AF162" s="1"/>
       <c r="AG162" s="1"/>
       <c r="AH162" s="1"/>
@@ -9453,7 +9459,7 @@
       <c r="AB163" s="1"/>
       <c r="AC163" s="1"/>
       <c r="AD163" s="1"/>
-      <c r="AE163" s="1"/>
+      <c r="AE163" s="39"/>
       <c r="AF163" s="1"/>
       <c r="AG163" s="1"/>
       <c r="AH163" s="1"/>
@@ -9496,7 +9502,7 @@
       <c r="AB164" s="3"/>
       <c r="AC164" s="3"/>
       <c r="AD164" s="3"/>
-      <c r="AE164" s="3"/>
+      <c r="AE164" s="40"/>
       <c r="AF164" s="3"/>
       <c r="AG164" s="3"/>
       <c r="AH164" s="3"/>
@@ -9539,7 +9545,7 @@
       <c r="AB165" s="3"/>
       <c r="AC165" s="3"/>
       <c r="AD165" s="3"/>
-      <c r="AE165" s="3"/>
+      <c r="AE165" s="40"/>
       <c r="AF165" s="3"/>
       <c r="AG165" s="3"/>
       <c r="AH165" s="3"/>
@@ -9580,7 +9586,7 @@
       <c r="AB166" s="1"/>
       <c r="AC166" s="1"/>
       <c r="AD166" s="1"/>
-      <c r="AE166" s="1"/>
+      <c r="AE166" s="39"/>
       <c r="AF166" s="1"/>
       <c r="AG166" s="1"/>
       <c r="AH166" s="1"/>
@@ -9621,7 +9627,7 @@
       <c r="AB167" s="1"/>
       <c r="AC167" s="1"/>
       <c r="AD167" s="1"/>
-      <c r="AE167" s="1"/>
+      <c r="AE167" s="39"/>
       <c r="AF167" s="1"/>
       <c r="AG167" s="1"/>
       <c r="AH167" s="1"/>
@@ -9662,7 +9668,7 @@
       <c r="AB168" s="1"/>
       <c r="AC168" s="1"/>
       <c r="AD168" s="1"/>
-      <c r="AE168" s="1"/>
+      <c r="AE168" s="39"/>
       <c r="AF168" s="1"/>
       <c r="AG168" s="1"/>
       <c r="AH168" s="1"/>
@@ -9703,7 +9709,7 @@
       <c r="AB169" s="1"/>
       <c r="AC169" s="1"/>
       <c r="AD169" s="1"/>
-      <c r="AE169" s="1"/>
+      <c r="AE169" s="39"/>
       <c r="AF169" s="1"/>
       <c r="AG169" s="1"/>
       <c r="AH169" s="1"/>
@@ -9744,7 +9750,7 @@
       <c r="AB170" s="1"/>
       <c r="AC170" s="1"/>
       <c r="AD170" s="1"/>
-      <c r="AE170" s="1"/>
+      <c r="AE170" s="39"/>
       <c r="AF170" s="1"/>
       <c r="AG170" s="1"/>
       <c r="AH170" s="1"/>
@@ -9785,7 +9791,7 @@
       <c r="AB171" s="1"/>
       <c r="AC171" s="1"/>
       <c r="AD171" s="1"/>
-      <c r="AE171" s="1"/>
+      <c r="AE171" s="39"/>
       <c r="AF171" s="1"/>
       <c r="AG171" s="1"/>
       <c r="AH171" s="1"/>
@@ -9828,7 +9834,7 @@
       <c r="AB172" s="1"/>
       <c r="AC172" s="1"/>
       <c r="AD172" s="1"/>
-      <c r="AE172" s="1"/>
+      <c r="AE172" s="39"/>
       <c r="AF172" s="1"/>
       <c r="AG172" s="1"/>
       <c r="AH172" s="1"/>
@@ -9869,7 +9875,7 @@
       <c r="AB173" s="1"/>
       <c r="AC173" s="1"/>
       <c r="AD173" s="1"/>
-      <c r="AE173" s="1"/>
+      <c r="AE173" s="39"/>
       <c r="AF173" s="1"/>
       <c r="AG173" s="1"/>
       <c r="AH173" s="1"/>
@@ -9920,7 +9926,7 @@
       <c r="AB174" s="1"/>
       <c r="AC174" s="1"/>
       <c r="AD174" s="1"/>
-      <c r="AE174" s="1"/>
+      <c r="AE174" s="39"/>
       <c r="AF174" s="1"/>
       <c r="AG174" s="1"/>
       <c r="AH174" s="1"/>
@@ -9967,7 +9973,7 @@
       <c r="AB175" s="1"/>
       <c r="AC175" s="1"/>
       <c r="AD175" s="1"/>
-      <c r="AE175" s="1"/>
+      <c r="AE175" s="39"/>
       <c r="AF175" s="1"/>
       <c r="AG175" s="1"/>
       <c r="AH175" s="1"/>
@@ -10018,7 +10024,7 @@
       <c r="AB176" s="1"/>
       <c r="AC176" s="1"/>
       <c r="AD176" s="1"/>
-      <c r="AE176" s="1"/>
+      <c r="AE176" s="39"/>
       <c r="AF176" s="1"/>
       <c r="AG176" s="1"/>
       <c r="AH176" s="1"/>
@@ -10063,7 +10069,7 @@
       <c r="AB177" s="1"/>
       <c r="AC177" s="1"/>
       <c r="AD177" s="1"/>
-      <c r="AE177" s="1"/>
+      <c r="AE177" s="39"/>
       <c r="AF177" s="1"/>
       <c r="AG177" s="1"/>
       <c r="AH177" s="1"/>
@@ -10108,7 +10114,7 @@
       <c r="AB178" s="1"/>
       <c r="AC178" s="1"/>
       <c r="AD178" s="1"/>
-      <c r="AE178" s="1"/>
+      <c r="AE178" s="39"/>
       <c r="AF178" s="1"/>
       <c r="AG178" s="1"/>
       <c r="AH178" s="1"/>
@@ -10153,7 +10159,7 @@
       <c r="AB179" s="1"/>
       <c r="AC179" s="1"/>
       <c r="AD179" s="1"/>
-      <c r="AE179" s="1"/>
+      <c r="AE179" s="39"/>
       <c r="AF179" s="1"/>
       <c r="AG179" s="1"/>
       <c r="AH179" s="1"/>
@@ -10200,7 +10206,7 @@
       <c r="AB180" s="1"/>
       <c r="AC180" s="1"/>
       <c r="AD180" s="1"/>
-      <c r="AE180" s="1"/>
+      <c r="AE180" s="39"/>
       <c r="AF180" s="1"/>
       <c r="AG180" s="1"/>
       <c r="AH180" s="1"/>
@@ -10245,7 +10251,7 @@
       <c r="AB181" s="1"/>
       <c r="AC181" s="1"/>
       <c r="AD181" s="1"/>
-      <c r="AE181" s="1"/>
+      <c r="AE181" s="39"/>
       <c r="AF181" s="1"/>
       <c r="AG181" s="1"/>
       <c r="AH181" s="1"/>
@@ -10292,7 +10298,7 @@
       <c r="AB182" s="1"/>
       <c r="AC182" s="1"/>
       <c r="AD182" s="1"/>
-      <c r="AE182" s="1"/>
+      <c r="AE182" s="39"/>
       <c r="AF182" s="1"/>
       <c r="AG182" s="1"/>
       <c r="AH182" s="1"/>
@@ -10341,7 +10347,7 @@
       <c r="AB183" s="1"/>
       <c r="AC183" s="1"/>
       <c r="AD183" s="1"/>
-      <c r="AE183" s="1"/>
+      <c r="AE183" s="39"/>
       <c r="AF183" s="1"/>
       <c r="AG183" s="1"/>
       <c r="AH183" s="1"/>
@@ -10390,7 +10396,7 @@
       <c r="AB184" s="1"/>
       <c r="AC184" s="1"/>
       <c r="AD184" s="1"/>
-      <c r="AE184" s="1"/>
+      <c r="AE184" s="39"/>
       <c r="AF184" s="1"/>
       <c r="AG184" s="1"/>
       <c r="AH184" s="1"/>
@@ -10437,7 +10443,7 @@
       <c r="AB185" s="1"/>
       <c r="AC185" s="1"/>
       <c r="AD185" s="1"/>
-      <c r="AE185" s="1"/>
+      <c r="AE185" s="39"/>
       <c r="AF185" s="1"/>
       <c r="AG185" s="1"/>
       <c r="AH185" s="1"/>
@@ -10488,7 +10494,7 @@
       <c r="AB186" s="1"/>
       <c r="AC186" s="1"/>
       <c r="AD186" s="1"/>
-      <c r="AE186" s="1"/>
+      <c r="AE186" s="39"/>
       <c r="AF186" s="1"/>
       <c r="AG186" s="1"/>
       <c r="AH186" s="1"/>
@@ -10539,7 +10545,7 @@
       <c r="AB187" s="1"/>
       <c r="AC187" s="1"/>
       <c r="AD187" s="1"/>
-      <c r="AE187" s="1"/>
+      <c r="AE187" s="39"/>
       <c r="AF187" s="1"/>
       <c r="AG187" s="1"/>
       <c r="AH187" s="1"/>
@@ -10592,7 +10598,7 @@
       <c r="AB188" s="1"/>
       <c r="AC188" s="1"/>
       <c r="AD188" s="1"/>
-      <c r="AE188" s="1"/>
+      <c r="AE188" s="39"/>
       <c r="AF188" s="1"/>
       <c r="AG188" s="1"/>
       <c r="AH188" s="1"/>
@@ -10643,7 +10649,7 @@
       <c r="AB189" s="1"/>
       <c r="AC189" s="1"/>
       <c r="AD189" s="1"/>
-      <c r="AE189" s="1"/>
+      <c r="AE189" s="39"/>
       <c r="AF189" s="1"/>
       <c r="AG189" s="1"/>
       <c r="AH189" s="1"/>
@@ -10694,7 +10700,7 @@
       <c r="AB190" s="1"/>
       <c r="AC190" s="1"/>
       <c r="AD190" s="1"/>
-      <c r="AE190" s="1"/>
+      <c r="AE190" s="39"/>
       <c r="AF190" s="1"/>
       <c r="AG190" s="1"/>
       <c r="AH190" s="1"/>
@@ -10745,7 +10751,7 @@
       <c r="AB191" s="1"/>
       <c r="AC191" s="1"/>
       <c r="AD191" s="1"/>
-      <c r="AE191" s="1"/>
+      <c r="AE191" s="39"/>
       <c r="AF191" s="1"/>
       <c r="AG191" s="1"/>
       <c r="AH191" s="1"/>
@@ -10790,7 +10796,7 @@
       <c r="AB192" s="1"/>
       <c r="AC192" s="1"/>
       <c r="AD192" s="1"/>
-      <c r="AE192" s="1"/>
+      <c r="AE192" s="39"/>
       <c r="AF192" s="1"/>
       <c r="AG192" s="1"/>
       <c r="AH192" s="1"/>
@@ -10835,7 +10841,7 @@
       <c r="AB193" s="1"/>
       <c r="AC193" s="1"/>
       <c r="AD193" s="1"/>
-      <c r="AE193" s="1"/>
+      <c r="AE193" s="39"/>
       <c r="AF193" s="1"/>
       <c r="AG193" s="1"/>
       <c r="AH193" s="1"/>
@@ -10878,7 +10884,7 @@
       <c r="AB194" s="1"/>
       <c r="AC194" s="1"/>
       <c r="AD194" s="1"/>
-      <c r="AE194" s="1"/>
+      <c r="AE194" s="39"/>
       <c r="AF194" s="1"/>
       <c r="AG194" s="1"/>
       <c r="AH194" s="1"/>
@@ -10921,7 +10927,7 @@
       <c r="AB195" s="1"/>
       <c r="AC195" s="1"/>
       <c r="AD195" s="1"/>
-      <c r="AE195" s="1"/>
+      <c r="AE195" s="39"/>
       <c r="AF195" s="1"/>
       <c r="AG195" s="1"/>
       <c r="AH195" s="1"/>
@@ -10964,7 +10970,7 @@
       <c r="AB196" s="1"/>
       <c r="AC196" s="1"/>
       <c r="AD196" s="1"/>
-      <c r="AE196" s="1"/>
+      <c r="AE196" s="39"/>
       <c r="AF196" s="1"/>
       <c r="AG196" s="1"/>
       <c r="AH196" s="1"/>
@@ -11007,7 +11013,7 @@
       <c r="AB197" s="1"/>
       <c r="AC197" s="1"/>
       <c r="AD197" s="1"/>
-      <c r="AE197" s="1"/>
+      <c r="AE197" s="39"/>
       <c r="AF197" s="1"/>
       <c r="AG197" s="1"/>
       <c r="AH197" s="1"/>
@@ -11052,7 +11058,7 @@
       <c r="AB198" s="1"/>
       <c r="AC198" s="1"/>
       <c r="AD198" s="1"/>
-      <c r="AE198" s="1"/>
+      <c r="AE198" s="39"/>
       <c r="AF198" s="1"/>
       <c r="AG198" s="1"/>
       <c r="AH198" s="1"/>
@@ -11097,7 +11103,7 @@
       <c r="AB199" s="1"/>
       <c r="AC199" s="1"/>
       <c r="AD199" s="1"/>
-      <c r="AE199" s="1"/>
+      <c r="AE199" s="39"/>
       <c r="AF199" s="1"/>
       <c r="AG199" s="1"/>
       <c r="AH199" s="1"/>
@@ -11140,7 +11146,7 @@
       <c r="AB200" s="1"/>
       <c r="AC200" s="1"/>
       <c r="AD200" s="1"/>
-      <c r="AE200" s="1"/>
+      <c r="AE200" s="39"/>
       <c r="AF200" s="1"/>
       <c r="AG200" s="1"/>
       <c r="AH200" s="1"/>
@@ -11185,7 +11191,7 @@
       <c r="AB201" s="1"/>
       <c r="AC201" s="1"/>
       <c r="AD201" s="1"/>
-      <c r="AE201" s="1"/>
+      <c r="AE201" s="39"/>
       <c r="AF201" s="1"/>
       <c r="AG201" s="1"/>
       <c r="AH201" s="1"/>
@@ -11228,7 +11234,7 @@
       <c r="AB202" s="1"/>
       <c r="AC202" s="1"/>
       <c r="AD202" s="1"/>
-      <c r="AE202" s="1"/>
+      <c r="AE202" s="39"/>
       <c r="AF202" s="1"/>
       <c r="AG202" s="1"/>
       <c r="AH202" s="1"/>
@@ -11273,7 +11279,7 @@
       <c r="AB203" s="1"/>
       <c r="AC203" s="1"/>
       <c r="AD203" s="1"/>
-      <c r="AE203" s="1"/>
+      <c r="AE203" s="39"/>
       <c r="AF203" s="1"/>
       <c r="AG203" s="1"/>
       <c r="AH203" s="1"/>
@@ -11316,7 +11322,7 @@
       <c r="AB204" s="1"/>
       <c r="AC204" s="1"/>
       <c r="AD204" s="1"/>
-      <c r="AE204" s="1"/>
+      <c r="AE204" s="39"/>
       <c r="AF204" s="1"/>
       <c r="AG204" s="1"/>
       <c r="AH204" s="1"/>
@@ -11359,7 +11365,7 @@
       <c r="AB205" s="1"/>
       <c r="AC205" s="1"/>
       <c r="AD205" s="1"/>
-      <c r="AE205" s="1"/>
+      <c r="AE205" s="39"/>
       <c r="AF205" s="1"/>
       <c r="AG205" s="1"/>
       <c r="AH205" s="1"/>
@@ -11402,7 +11408,7 @@
       <c r="AB206" s="1"/>
       <c r="AC206" s="1"/>
       <c r="AD206" s="1"/>
-      <c r="AE206" s="1"/>
+      <c r="AE206" s="39"/>
       <c r="AF206" s="1"/>
       <c r="AG206" s="1"/>
       <c r="AH206" s="1"/>
@@ -11447,7 +11453,7 @@
       <c r="AB207" s="1"/>
       <c r="AC207" s="1"/>
       <c r="AD207" s="1"/>
-      <c r="AE207" s="1"/>
+      <c r="AE207" s="39"/>
       <c r="AF207" s="1"/>
       <c r="AG207" s="1"/>
       <c r="AH207" s="1"/>
@@ -11490,7 +11496,7 @@
       <c r="AB208" s="1"/>
       <c r="AC208" s="1"/>
       <c r="AD208" s="1"/>
-      <c r="AE208" s="1"/>
+      <c r="AE208" s="39"/>
       <c r="AF208" s="1"/>
       <c r="AG208" s="1"/>
       <c r="AH208" s="1"/>
@@ -11533,7 +11539,7 @@
       <c r="AB209" s="1"/>
       <c r="AC209" s="1"/>
       <c r="AD209" s="1"/>
-      <c r="AE209" s="1"/>
+      <c r="AE209" s="39"/>
       <c r="AF209" s="1"/>
       <c r="AG209" s="1"/>
       <c r="AH209" s="1"/>
@@ -11576,7 +11582,7 @@
       <c r="AB210" s="1"/>
       <c r="AC210" s="1"/>
       <c r="AD210" s="1"/>
-      <c r="AE210" s="1"/>
+      <c r="AE210" s="39"/>
       <c r="AF210" s="1"/>
       <c r="AG210" s="1"/>
       <c r="AH210" s="1"/>
@@ -11619,7 +11625,7 @@
       <c r="AB211" s="1"/>
       <c r="AC211" s="1"/>
       <c r="AD211" s="1"/>
-      <c r="AE211" s="1"/>
+      <c r="AE211" s="39"/>
       <c r="AF211" s="1"/>
       <c r="AG211" s="1"/>
       <c r="AH211" s="1"/>
@@ -11662,7 +11668,7 @@
       <c r="AB212" s="1"/>
       <c r="AC212" s="1"/>
       <c r="AD212" s="1"/>
-      <c r="AE212" s="1"/>
+      <c r="AE212" s="39"/>
       <c r="AF212" s="1"/>
       <c r="AG212" s="1"/>
       <c r="AH212" s="1"/>
@@ -11705,7 +11711,7 @@
       <c r="AB213" s="1"/>
       <c r="AC213" s="1"/>
       <c r="AD213" s="1"/>
-      <c r="AE213" s="1"/>
+      <c r="AE213" s="39"/>
       <c r="AF213" s="1"/>
       <c r="AG213" s="1"/>
       <c r="AH213" s="1"/>
@@ -11748,7 +11754,7 @@
       <c r="AB214" s="1"/>
       <c r="AC214" s="1"/>
       <c r="AD214" s="1"/>
-      <c r="AE214" s="1"/>
+      <c r="AE214" s="39"/>
       <c r="AF214" s="1"/>
       <c r="AG214" s="1"/>
       <c r="AH214" s="1"/>
@@ -11791,7 +11797,7 @@
       <c r="AB215" s="1"/>
       <c r="AC215" s="1"/>
       <c r="AD215" s="1"/>
-      <c r="AE215" s="1"/>
+      <c r="AE215" s="39"/>
       <c r="AF215" s="1"/>
       <c r="AG215" s="1"/>
       <c r="AH215" s="1"/>
@@ -11838,7 +11844,7 @@
       <c r="AB216" s="1"/>
       <c r="AC216" s="1"/>
       <c r="AD216" s="1"/>
-      <c r="AE216" s="1"/>
+      <c r="AE216" s="39"/>
       <c r="AF216" s="1"/>
       <c r="AG216" s="1"/>
       <c r="AH216" s="1"/>
@@ -11885,7 +11891,7 @@
       <c r="AB217" s="1"/>
       <c r="AC217" s="1"/>
       <c r="AD217" s="1"/>
-      <c r="AE217" s="1"/>
+      <c r="AE217" s="39"/>
       <c r="AF217" s="1"/>
       <c r="AG217" s="1"/>
       <c r="AH217" s="1"/>
@@ -11932,7 +11938,7 @@
       <c r="AB218" s="1"/>
       <c r="AC218" s="1"/>
       <c r="AD218" s="1"/>
-      <c r="AE218" s="1"/>
+      <c r="AE218" s="39"/>
       <c r="AF218" s="1"/>
       <c r="AG218" s="1"/>
       <c r="AH218" s="1"/>
@@ -11973,7 +11979,7 @@
       <c r="AB219" s="1"/>
       <c r="AC219" s="1"/>
       <c r="AD219" s="1"/>
-      <c r="AE219" s="1"/>
+      <c r="AE219" s="39"/>
       <c r="AF219" s="1"/>
       <c r="AG219" s="1"/>
       <c r="AH219" s="1"/>
@@ -12014,7 +12020,7 @@
       <c r="AB220" s="1"/>
       <c r="AC220" s="1"/>
       <c r="AD220" s="1"/>
-      <c r="AE220" s="1"/>
+      <c r="AE220" s="39"/>
       <c r="AF220" s="1"/>
       <c r="AG220" s="1"/>
       <c r="AH220" s="1"/>
@@ -12055,7 +12061,7 @@
       <c r="AB221" s="1"/>
       <c r="AC221" s="1"/>
       <c r="AD221" s="1"/>
-      <c r="AE221" s="1"/>
+      <c r="AE221" s="39"/>
       <c r="AF221" s="1"/>
       <c r="AG221" s="1"/>
       <c r="AH221" s="1"/>
@@ -12098,7 +12104,7 @@
       <c r="AB222" s="1"/>
       <c r="AC222" s="1"/>
       <c r="AD222" s="1"/>
-      <c r="AE222" s="1"/>
+      <c r="AE222" s="39"/>
       <c r="AF222" s="1"/>
       <c r="AG222" s="1"/>
       <c r="AH222" s="1"/>
@@ -12139,7 +12145,7 @@
       <c r="AB223" s="1"/>
       <c r="AC223" s="1"/>
       <c r="AD223" s="1"/>
-      <c r="AE223" s="1"/>
+      <c r="AE223" s="39"/>
       <c r="AF223" s="1"/>
       <c r="AG223" s="1"/>
       <c r="AH223" s="1"/>
@@ -12180,7 +12186,7 @@
       <c r="AB224" s="1"/>
       <c r="AC224" s="1"/>
       <c r="AD224" s="1"/>
-      <c r="AE224" s="1"/>
+      <c r="AE224" s="39"/>
       <c r="AF224" s="1"/>
       <c r="AG224" s="1"/>
       <c r="AH224" s="1"/>
@@ -12221,7 +12227,7 @@
       <c r="AB225" s="1"/>
       <c r="AC225" s="1"/>
       <c r="AD225" s="1"/>
-      <c r="AE225" s="1"/>
+      <c r="AE225" s="39"/>
       <c r="AF225" s="1"/>
       <c r="AG225" s="1"/>
       <c r="AH225" s="1"/>
@@ -12262,7 +12268,7 @@
       <c r="AB226" s="1"/>
       <c r="AC226" s="1"/>
       <c r="AD226" s="1"/>
-      <c r="AE226" s="1"/>
+      <c r="AE226" s="39"/>
       <c r="AF226" s="1"/>
       <c r="AG226" s="1"/>
       <c r="AH226" s="1"/>
@@ -12303,7 +12309,7 @@
       <c r="AB227" s="1"/>
       <c r="AC227" s="1"/>
       <c r="AD227" s="1"/>
-      <c r="AE227" s="1"/>
+      <c r="AE227" s="39"/>
       <c r="AF227" s="1"/>
       <c r="AG227" s="1"/>
       <c r="AH227" s="1"/>
@@ -12344,7 +12350,7 @@
       <c r="AB228" s="1"/>
       <c r="AC228" s="1"/>
       <c r="AD228" s="1"/>
-      <c r="AE228" s="1"/>
+      <c r="AE228" s="39"/>
       <c r="AF228" s="1"/>
       <c r="AG228" s="1"/>
       <c r="AH228" s="1"/>
@@ -12385,7 +12391,7 @@
       <c r="AB229" s="1"/>
       <c r="AC229" s="1"/>
       <c r="AD229" s="1"/>
-      <c r="AE229" s="1"/>
+      <c r="AE229" s="39"/>
       <c r="AF229" s="1"/>
       <c r="AG229" s="1"/>
       <c r="AH229" s="1"/>
@@ -12426,7 +12432,7 @@
       <c r="AB230" s="1"/>
       <c r="AC230" s="1"/>
       <c r="AD230" s="1"/>
-      <c r="AE230" s="1"/>
+      <c r="AE230" s="39"/>
       <c r="AF230" s="1"/>
       <c r="AG230" s="1"/>
       <c r="AH230" s="1"/>
@@ -12467,7 +12473,7 @@
       <c r="AB231" s="1"/>
       <c r="AC231" s="1"/>
       <c r="AD231" s="1"/>
-      <c r="AE231" s="1"/>
+      <c r="AE231" s="39"/>
       <c r="AF231" s="1"/>
       <c r="AG231" s="1"/>
       <c r="AH231" s="1"/>
@@ -12508,7 +12514,7 @@
       <c r="AB232" s="1"/>
       <c r="AC232" s="1"/>
       <c r="AD232" s="1"/>
-      <c r="AE232" s="1"/>
+      <c r="AE232" s="39"/>
       <c r="AF232" s="1"/>
       <c r="AG232" s="1"/>
       <c r="AH232" s="1"/>
@@ -12551,7 +12557,7 @@
       <c r="AB233" s="1"/>
       <c r="AC233" s="1"/>
       <c r="AD233" s="1"/>
-      <c r="AE233" s="1"/>
+      <c r="AE233" s="39"/>
       <c r="AF233" s="1"/>
       <c r="AG233" s="1"/>
       <c r="AH233" s="1"/>
@@ -12592,7 +12598,7 @@
       <c r="AB234" s="1"/>
       <c r="AC234" s="1"/>
       <c r="AD234" s="1"/>
-      <c r="AE234" s="1"/>
+      <c r="AE234" s="39"/>
       <c r="AF234" s="1"/>
       <c r="AG234" s="1"/>
       <c r="AH234" s="1"/>
@@ -12635,7 +12641,7 @@
       <c r="AB235" s="1"/>
       <c r="AC235" s="1"/>
       <c r="AD235" s="1"/>
-      <c r="AE235" s="1"/>
+      <c r="AE235" s="39"/>
       <c r="AF235" s="1"/>
       <c r="AG235" s="1"/>
       <c r="AH235" s="1"/>
@@ -12676,7 +12682,7 @@
       <c r="AB236" s="1"/>
       <c r="AC236" s="1"/>
       <c r="AD236" s="1"/>
-      <c r="AE236" s="1"/>
+      <c r="AE236" s="39"/>
       <c r="AF236" s="1"/>
       <c r="AG236" s="1"/>
       <c r="AH236" s="1"/>
@@ -12717,7 +12723,7 @@
       <c r="AB237" s="1"/>
       <c r="AC237" s="1"/>
       <c r="AD237" s="1"/>
-      <c r="AE237" s="1"/>
+      <c r="AE237" s="39"/>
       <c r="AF237" s="1"/>
       <c r="AG237" s="1"/>
       <c r="AH237" s="1"/>
@@ -12758,7 +12764,7 @@
       <c r="AB238" s="1"/>
       <c r="AC238" s="1"/>
       <c r="AD238" s="1"/>
-      <c r="AE238" s="1"/>
+      <c r="AE238" s="39"/>
       <c r="AF238" s="1"/>
       <c r="AG238" s="1"/>
       <c r="AH238" s="1"/>
@@ -12799,7 +12805,7 @@
       <c r="AB239" s="1"/>
       <c r="AC239" s="1"/>
       <c r="AD239" s="1"/>
-      <c r="AE239" s="1"/>
+      <c r="AE239" s="39"/>
       <c r="AF239" s="1"/>
       <c r="AG239" s="1"/>
       <c r="AH239" s="1"/>
@@ -12840,7 +12846,7 @@
       <c r="AB240" s="1"/>
       <c r="AC240" s="1"/>
       <c r="AD240" s="1"/>
-      <c r="AE240" s="1"/>
+      <c r="AE240" s="39"/>
       <c r="AF240" s="1"/>
       <c r="AG240" s="1"/>
       <c r="AH240" s="1"/>
@@ -12881,7 +12887,7 @@
       <c r="AB241" s="1"/>
       <c r="AC241" s="1"/>
       <c r="AD241" s="1"/>
-      <c r="AE241" s="1"/>
+      <c r="AE241" s="39"/>
       <c r="AF241" s="1"/>
       <c r="AG241" s="1"/>
       <c r="AH241" s="1"/>
@@ -12922,7 +12928,7 @@
       <c r="AB242" s="1"/>
       <c r="AC242" s="1"/>
       <c r="AD242" s="1"/>
-      <c r="AE242" s="1"/>
+      <c r="AE242" s="39"/>
       <c r="AF242" s="1"/>
       <c r="AG242" s="1"/>
       <c r="AH242" s="1"/>
@@ -12965,7 +12971,7 @@
       <c r="AB243" s="1"/>
       <c r="AC243" s="1"/>
       <c r="AD243" s="1"/>
-      <c r="AE243" s="1"/>
+      <c r="AE243" s="39"/>
       <c r="AF243" s="1"/>
       <c r="AG243" s="1"/>
       <c r="AH243" s="1"/>
@@ -13008,7 +13014,7 @@
       <c r="AB244" s="1"/>
       <c r="AC244" s="1"/>
       <c r="AD244" s="1"/>
-      <c r="AE244" s="1"/>
+      <c r="AE244" s="39"/>
       <c r="AF244" s="1"/>
       <c r="AG244" s="1"/>
       <c r="AH244" s="1"/>
@@ -13051,7 +13057,7 @@
       <c r="AB245" s="1"/>
       <c r="AC245" s="1"/>
       <c r="AD245" s="1"/>
-      <c r="AE245" s="1"/>
+      <c r="AE245" s="39"/>
       <c r="AF245" s="1"/>
       <c r="AG245" s="1"/>
       <c r="AH245" s="1"/>
@@ -13094,7 +13100,7 @@
       <c r="AB246" s="1"/>
       <c r="AC246" s="1"/>
       <c r="AD246" s="1"/>
-      <c r="AE246" s="1"/>
+      <c r="AE246" s="39"/>
       <c r="AF246" s="1"/>
       <c r="AG246" s="1"/>
       <c r="AH246" s="1"/>
@@ -13137,7 +13143,7 @@
       <c r="AB247" s="1"/>
       <c r="AC247" s="1"/>
       <c r="AD247" s="1"/>
-      <c r="AE247" s="1"/>
+      <c r="AE247" s="39"/>
       <c r="AF247" s="1"/>
       <c r="AG247" s="1"/>
       <c r="AH247" s="1"/>
@@ -13180,7 +13186,7 @@
       <c r="AB248" s="1"/>
       <c r="AC248" s="1"/>
       <c r="AD248" s="1"/>
-      <c r="AE248" s="1"/>
+      <c r="AE248" s="39"/>
       <c r="AF248" s="1"/>
       <c r="AG248" s="1"/>
       <c r="AH248" s="1"/>
@@ -13221,7 +13227,7 @@
       <c r="AB249" s="1"/>
       <c r="AC249" s="1"/>
       <c r="AD249" s="1"/>
-      <c r="AE249" s="1"/>
+      <c r="AE249" s="39"/>
       <c r="AF249" s="1"/>
       <c r="AG249" s="1"/>
       <c r="AH249" s="1"/>
@@ -13262,7 +13268,7 @@
       <c r="AB250" s="1"/>
       <c r="AC250" s="1"/>
       <c r="AD250" s="1"/>
-      <c r="AE250" s="1"/>
+      <c r="AE250" s="39"/>
       <c r="AF250" s="1"/>
       <c r="AG250" s="1"/>
       <c r="AH250" s="1"/>
@@ -13303,7 +13309,7 @@
       <c r="AB251" s="1"/>
       <c r="AC251" s="1"/>
       <c r="AD251" s="1"/>
-      <c r="AE251" s="1"/>
+      <c r="AE251" s="39"/>
       <c r="AF251" s="1"/>
       <c r="AG251" s="1"/>
       <c r="AH251" s="1"/>
@@ -13344,7 +13350,7 @@
       <c r="AB252" s="1"/>
       <c r="AC252" s="1"/>
       <c r="AD252" s="1"/>
-      <c r="AE252" s="1"/>
+      <c r="AE252" s="39"/>
       <c r="AF252" s="1"/>
       <c r="AG252" s="1"/>
       <c r="AH252" s="1"/>
@@ -13385,7 +13391,7 @@
       <c r="AB253" s="1"/>
       <c r="AC253" s="1"/>
       <c r="AD253" s="1"/>
-      <c r="AE253" s="1"/>
+      <c r="AE253" s="39"/>
       <c r="AF253" s="1"/>
       <c r="AG253" s="1"/>
       <c r="AH253" s="1"/>
@@ -13426,7 +13432,7 @@
       <c r="AB254" s="1"/>
       <c r="AC254" s="1"/>
       <c r="AD254" s="1"/>
-      <c r="AE254" s="1"/>
+      <c r="AE254" s="39"/>
       <c r="AF254" s="1"/>
       <c r="AG254" s="1"/>
       <c r="AH254" s="1"/>
@@ -13467,7 +13473,7 @@
       <c r="AB255" s="1"/>
       <c r="AC255" s="1"/>
       <c r="AD255" s="1"/>
-      <c r="AE255" s="1"/>
+      <c r="AE255" s="39"/>
       <c r="AF255" s="1"/>
       <c r="AG255" s="1"/>
       <c r="AH255" s="1"/>
@@ -13506,7 +13512,7 @@
       <c r="AB256" s="1"/>
       <c r="AC256" s="1"/>
       <c r="AD256" s="1"/>
-      <c r="AE256" s="1"/>
+      <c r="AE256" s="39"/>
       <c r="AF256" s="1"/>
       <c r="AG256" s="1"/>
       <c r="AH256" s="1"/>
@@ -13545,7 +13551,7 @@
       <c r="AB257" s="1"/>
       <c r="AC257" s="1"/>
       <c r="AD257" s="1"/>
-      <c r="AE257" s="1"/>
+      <c r="AE257" s="39"/>
       <c r="AF257" s="1"/>
       <c r="AG257" s="1"/>
       <c r="AH257" s="1"/>
@@ -13584,7 +13590,7 @@
       <c r="AB258" s="1"/>
       <c r="AC258" s="1"/>
       <c r="AD258" s="1"/>
-      <c r="AE258" s="1"/>
+      <c r="AE258" s="39"/>
       <c r="AF258" s="1"/>
       <c r="AG258" s="1"/>
       <c r="AH258" s="1"/>
@@ -13623,7 +13629,7 @@
       <c r="AB259" s="1"/>
       <c r="AC259" s="1"/>
       <c r="AD259" s="1"/>
-      <c r="AE259" s="1"/>
+      <c r="AE259" s="39"/>
       <c r="AF259" s="1"/>
       <c r="AG259" s="1"/>
       <c r="AH259" s="1"/>
@@ -13662,7 +13668,7 @@
       <c r="AB260" s="1"/>
       <c r="AC260" s="1"/>
       <c r="AD260" s="1"/>
-      <c r="AE260" s="1"/>
+      <c r="AE260" s="39"/>
       <c r="AF260" s="1"/>
       <c r="AG260" s="1"/>
       <c r="AH260" s="1"/>
@@ -13701,7 +13707,7 @@
       <c r="AB261" s="1"/>
       <c r="AC261" s="1"/>
       <c r="AD261" s="1"/>
-      <c r="AE261" s="1"/>
+      <c r="AE261" s="39"/>
       <c r="AF261" s="1"/>
       <c r="AG261" s="1"/>
       <c r="AH261" s="1"/>
@@ -13740,7 +13746,7 @@
       <c r="AB262" s="1"/>
       <c r="AC262" s="1"/>
       <c r="AD262" s="1"/>
-      <c r="AE262" s="1"/>
+      <c r="AE262" s="39"/>
       <c r="AF262" s="1"/>
       <c r="AG262" s="1"/>
       <c r="AH262" s="1"/>
@@ -13779,7 +13785,7 @@
       <c r="AB263" s="1"/>
       <c r="AC263" s="1"/>
       <c r="AD263" s="1"/>
-      <c r="AE263" s="1"/>
+      <c r="AE263" s="39"/>
       <c r="AF263" s="1"/>
       <c r="AG263" s="1"/>
       <c r="AH263" s="1"/>
@@ -13818,7 +13824,7 @@
       <c r="AB264" s="1"/>
       <c r="AC264" s="1"/>
       <c r="AD264" s="1"/>
-      <c r="AE264" s="1"/>
+      <c r="AE264" s="39"/>
       <c r="AF264" s="1"/>
       <c r="AG264" s="1"/>
       <c r="AH264" s="1"/>
@@ -13857,7 +13863,7 @@
       <c r="AB265" s="1"/>
       <c r="AC265" s="1"/>
       <c r="AD265" s="1"/>
-      <c r="AE265" s="1"/>
+      <c r="AE265" s="39"/>
       <c r="AF265" s="1"/>
       <c r="AG265" s="1"/>
       <c r="AH265" s="1"/>
@@ -13896,7 +13902,7 @@
       <c r="AB266" s="1"/>
       <c r="AC266" s="1"/>
       <c r="AD266" s="1"/>
-      <c r="AE266" s="1"/>
+      <c r="AE266" s="39"/>
       <c r="AF266" s="1"/>
       <c r="AG266" s="1"/>
       <c r="AH266" s="1"/>
@@ -13935,7 +13941,7 @@
       <c r="AB267" s="1"/>
       <c r="AC267" s="1"/>
       <c r="AD267" s="1"/>
-      <c r="AE267" s="1"/>
+      <c r="AE267" s="39"/>
       <c r="AF267" s="1"/>
       <c r="AG267" s="1"/>
       <c r="AH267" s="1"/>
@@ -13974,7 +13980,7 @@
       <c r="AB268" s="1"/>
       <c r="AC268" s="1"/>
       <c r="AD268" s="1"/>
-      <c r="AE268" s="1"/>
+      <c r="AE268" s="39"/>
       <c r="AF268" s="1"/>
       <c r="AG268" s="1"/>
       <c r="AH268" s="1"/>
@@ -14013,7 +14019,7 @@
       <c r="AB269" s="1"/>
       <c r="AC269" s="1"/>
       <c r="AD269" s="1"/>
-      <c r="AE269" s="1"/>
+      <c r="AE269" s="39"/>
       <c r="AF269" s="1"/>
       <c r="AG269" s="1"/>
       <c r="AH269" s="1"/>
@@ -14052,7 +14058,7 @@
       <c r="AB270" s="1"/>
       <c r="AC270" s="1"/>
       <c r="AD270" s="1"/>
-      <c r="AE270" s="1"/>
+      <c r="AE270" s="39"/>
       <c r="AF270" s="1"/>
       <c r="AG270" s="1"/>
       <c r="AH270" s="1"/>
@@ -14091,7 +14097,7 @@
       <c r="AB271" s="1"/>
       <c r="AC271" s="1"/>
       <c r="AD271" s="1"/>
-      <c r="AE271" s="1"/>
+      <c r="AE271" s="39"/>
       <c r="AF271" s="1"/>
       <c r="AG271" s="1"/>
       <c r="AH271" s="1"/>
@@ -14130,7 +14136,7 @@
       <c r="AB272" s="1"/>
       <c r="AC272" s="1"/>
       <c r="AD272" s="1"/>
-      <c r="AE272" s="1"/>
+      <c r="AE272" s="39"/>
       <c r="AF272" s="1"/>
       <c r="AG272" s="1"/>
       <c r="AH272" s="1"/>
@@ -14169,7 +14175,7 @@
       <c r="AB273" s="1"/>
       <c r="AC273" s="1"/>
       <c r="AD273" s="1"/>
-      <c r="AE273" s="1"/>
+      <c r="AE273" s="39"/>
       <c r="AF273" s="1"/>
       <c r="AG273" s="1"/>
       <c r="AH273" s="1"/>
@@ -14208,7 +14214,7 @@
       <c r="AB274" s="1"/>
       <c r="AC274" s="1"/>
       <c r="AD274" s="1"/>
-      <c r="AE274" s="1"/>
+      <c r="AE274" s="39"/>
       <c r="AF274" s="1"/>
       <c r="AG274" s="1"/>
       <c r="AH274" s="1"/>
@@ -14247,7 +14253,7 @@
       <c r="AB275" s="1"/>
       <c r="AC275" s="1"/>
       <c r="AD275" s="1"/>
-      <c r="AE275" s="1"/>
+      <c r="AE275" s="39"/>
       <c r="AF275" s="1"/>
       <c r="AG275" s="1"/>
       <c r="AH275" s="1"/>
@@ -14286,7 +14292,7 @@
       <c r="AB276" s="1"/>
       <c r="AC276" s="1"/>
       <c r="AD276" s="1"/>
-      <c r="AE276" s="1"/>
+      <c r="AE276" s="39"/>
       <c r="AF276" s="1"/>
       <c r="AG276" s="1"/>
       <c r="AH276" s="1"/>
@@ -14325,7 +14331,7 @@
       <c r="AB277" s="1"/>
       <c r="AC277" s="1"/>
       <c r="AD277" s="1"/>
-      <c r="AE277" s="1"/>
+      <c r="AE277" s="39"/>
       <c r="AF277" s="1"/>
       <c r="AG277" s="1"/>
       <c r="AH277" s="1"/>
@@ -14364,7 +14370,7 @@
       <c r="AB278" s="1"/>
       <c r="AC278" s="1"/>
       <c r="AD278" s="1"/>
-      <c r="AE278" s="1"/>
+      <c r="AE278" s="39"/>
       <c r="AF278" s="1"/>
       <c r="AG278" s="1"/>
       <c r="AH278" s="1"/>
@@ -14403,7 +14409,7 @@
       <c r="AB279" s="1"/>
       <c r="AC279" s="1"/>
       <c r="AD279" s="1"/>
-      <c r="AE279" s="1"/>
+      <c r="AE279" s="39"/>
       <c r="AF279" s="1"/>
       <c r="AG279" s="1"/>
       <c r="AH279" s="1"/>
@@ -14442,7 +14448,7 @@
       <c r="AB280" s="1"/>
       <c r="AC280" s="1"/>
       <c r="AD280" s="1"/>
-      <c r="AE280" s="1"/>
+      <c r="AE280" s="39"/>
       <c r="AF280" s="1"/>
       <c r="AG280" s="1"/>
       <c r="AH280" s="1"/>
@@ -14472,14 +14478,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8513D353-BD33-4F18-8682-09CF4EA59EE5}">
   <dimension ref="A2:H171"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08203125" style="16" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.8125" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.0625" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.9375" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="6.5625" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.08203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.9140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="6.58203125" style="16" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="16"/>
   </cols>
   <sheetData>
@@ -16347,2245 +16353,2245 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B979FDD-83A3-41C6-8CB0-C39167BCC619}">
   <dimension ref="A1:E221"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="3.8125" customWidth="1"/>
-    <col min="2" max="2" width="4.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.625" customWidth="1"/>
-    <col min="4" max="4" width="29.1875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.83203125" customWidth="1"/>
+    <col min="2" max="2" width="4.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.58203125" customWidth="1"/>
+    <col min="4" max="4" width="29.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="28" t="s">
         <v>355</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="28" t="s">
         <v>354</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="28" t="s">
         <v>376</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="E1" s="38"/>
+      <c r="E1" s="28"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="36">
+      <c r="A2" s="26">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
+      <c r="B2" s="26"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="26" t="s">
         <v>301</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="36">
+      <c r="A3" s="26">
         <v>2</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="26"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="26" t="s">
         <v>302</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="36">
+      <c r="A4" s="26">
         <v>3</v>
       </c>
-      <c r="B4" s="36"/>
+      <c r="B4" s="26"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="26" t="s">
         <v>303</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="36">
+      <c r="A5" s="26">
         <v>4</v>
       </c>
-      <c r="B5" s="36"/>
+      <c r="B5" s="26"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="26" t="s">
         <v>304</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="36">
+      <c r="A6" s="26">
         <v>5</v>
       </c>
-      <c r="B6" s="36"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="26" t="s">
         <v>305</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="36">
+      <c r="A7" s="26">
         <v>6</v>
       </c>
-      <c r="B7" s="36"/>
+      <c r="B7" s="26"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="26" t="s">
         <v>306</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="36">
+      <c r="A8" s="26">
         <v>7</v>
       </c>
-      <c r="B8" s="36"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="26" t="s">
         <v>307</v>
       </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="36">
+      <c r="A9" s="26">
         <v>8</v>
       </c>
-      <c r="B9" s="36"/>
+      <c r="B9" s="26"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="26" t="s">
         <v>308</v>
       </c>
       <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="36">
+      <c r="A10" s="26">
         <v>9</v>
       </c>
-      <c r="B10" s="36"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="26" t="s">
         <v>309</v>
       </c>
       <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="36">
+      <c r="A11" s="26">
         <v>10</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="26" t="s">
         <v>310</v>
       </c>
       <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="36">
+      <c r="A12" s="26">
         <v>11</v>
       </c>
-      <c r="B12" s="36"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="26" t="s">
         <v>311</v>
       </c>
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="36">
+      <c r="A13" s="26">
         <v>12</v>
       </c>
-      <c r="B13" s="36"/>
+      <c r="B13" s="26"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="26" t="s">
         <v>312</v>
       </c>
       <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="36">
+      <c r="A14" s="26">
         <v>13</v>
       </c>
-      <c r="B14" s="36"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="26" t="s">
         <v>313</v>
       </c>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="36">
+      <c r="A15" s="26">
         <v>14</v>
       </c>
-      <c r="B15" s="36"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="36" t="s">
+      <c r="D15" s="26" t="s">
         <v>314</v>
       </c>
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="36">
+      <c r="A16" s="26">
         <v>15</v>
       </c>
-      <c r="B16" s="36"/>
+      <c r="B16" s="26"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="26" t="s">
         <v>315</v>
       </c>
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="36">
+      <c r="A17" s="26">
         <v>16</v>
       </c>
-      <c r="B17" s="36"/>
+      <c r="B17" s="26"/>
       <c r="C17" s="3"/>
-      <c r="D17" s="36" t="s">
+      <c r="D17" s="26" t="s">
         <v>316</v>
       </c>
       <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="36">
+      <c r="A18" s="26">
         <v>17</v>
       </c>
-      <c r="B18" s="36"/>
+      <c r="B18" s="26"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="36" t="s">
+      <c r="D18" s="26" t="s">
         <v>317</v>
       </c>
       <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="36">
+      <c r="A19" s="26">
         <v>18</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="26"/>
       <c r="C19" s="3"/>
-      <c r="D19" s="36" t="s">
+      <c r="D19" s="26" t="s">
         <v>318</v>
       </c>
       <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="36">
+      <c r="A20" s="26">
         <v>19</v>
       </c>
-      <c r="B20" s="36"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="3"/>
-      <c r="D20" s="36" t="s">
+      <c r="D20" s="26" t="s">
         <v>319</v>
       </c>
       <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="36">
+      <c r="A21" s="26">
         <v>20</v>
       </c>
-      <c r="B21" s="36"/>
+      <c r="B21" s="26"/>
       <c r="C21" s="3"/>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="26" t="s">
         <v>320</v>
       </c>
       <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="36">
+      <c r="A22" s="26">
         <v>21</v>
       </c>
-      <c r="B22" s="36"/>
+      <c r="B22" s="26"/>
       <c r="C22" s="3"/>
-      <c r="D22" s="36" t="s">
+      <c r="D22" s="26" t="s">
         <v>321</v>
       </c>
       <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="36">
+      <c r="A23" s="26">
         <v>22</v>
       </c>
-      <c r="B23" s="36"/>
+      <c r="B23" s="26"/>
       <c r="C23" s="3"/>
-      <c r="D23" s="36" t="s">
+      <c r="D23" s="26" t="s">
         <v>322</v>
       </c>
       <c r="E23" s="3"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="36">
+      <c r="A24" s="26">
         <v>23</v>
       </c>
-      <c r="B24" s="36"/>
+      <c r="B24" s="26"/>
       <c r="C24" s="3"/>
-      <c r="D24" s="36" t="s">
+      <c r="D24" s="26" t="s">
         <v>323</v>
       </c>
       <c r="E24" s="3"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="36">
+      <c r="A25" s="26">
         <v>24</v>
       </c>
-      <c r="B25" s="36"/>
+      <c r="B25" s="26"/>
       <c r="C25" s="3"/>
-      <c r="D25" s="36" t="s">
+      <c r="D25" s="26" t="s">
         <v>324</v>
       </c>
       <c r="E25" s="3"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="36">
+      <c r="A26" s="26">
         <v>25</v>
       </c>
-      <c r="B26" s="36"/>
+      <c r="B26" s="26"/>
       <c r="C26" s="3"/>
-      <c r="D26" s="36" t="s">
+      <c r="D26" s="26" t="s">
         <v>325</v>
       </c>
       <c r="E26" s="3"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="36">
+      <c r="A27" s="26">
         <v>26</v>
       </c>
-      <c r="B27" s="36"/>
+      <c r="B27" s="26"/>
       <c r="C27" s="3"/>
-      <c r="D27" s="36" t="s">
+      <c r="D27" s="26" t="s">
         <v>326</v>
       </c>
       <c r="E27" s="3"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="36">
+      <c r="A28" s="26">
         <v>27</v>
       </c>
-      <c r="B28" s="36"/>
+      <c r="B28" s="26"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="36" t="s">
+      <c r="D28" s="26" t="s">
         <v>327</v>
       </c>
       <c r="E28" s="3"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="36">
+      <c r="A29" s="26">
         <v>28</v>
       </c>
-      <c r="B29" s="36"/>
+      <c r="B29" s="26"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="36" t="s">
+      <c r="D29" s="26" t="s">
         <v>328</v>
       </c>
       <c r="E29" s="3"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="36">
+      <c r="A30" s="26">
         <v>29</v>
       </c>
-      <c r="B30" s="36"/>
+      <c r="B30" s="26"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="36" t="s">
+      <c r="D30" s="26" t="s">
         <v>329</v>
       </c>
       <c r="E30" s="3"/>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="36">
+      <c r="A31" s="26">
         <v>30</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="26"/>
       <c r="C31" s="3"/>
-      <c r="D31" s="36" t="s">
+      <c r="D31" s="26" t="s">
         <v>330</v>
       </c>
       <c r="E31" s="3"/>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="36">
+      <c r="A32" s="26">
         <v>31</v>
       </c>
-      <c r="B32" s="36"/>
+      <c r="B32" s="26"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="36" t="s">
+      <c r="D32" s="26" t="s">
         <v>331</v>
       </c>
       <c r="E32" s="3"/>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="36">
+      <c r="A33" s="26">
         <v>32</v>
       </c>
-      <c r="B33" s="36"/>
+      <c r="B33" s="26"/>
       <c r="C33" s="3"/>
-      <c r="D33" s="36" t="s">
+      <c r="D33" s="26" t="s">
         <v>332</v>
       </c>
       <c r="E33" s="3"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="36">
+      <c r="A34" s="26">
         <v>33</v>
       </c>
-      <c r="B34" s="36" t="s">
+      <c r="B34" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C34" s="3"/>
-      <c r="D34" s="36" t="s">
+      <c r="D34" s="26" t="s">
         <v>333</v>
       </c>
       <c r="E34" s="3"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="36">
+      <c r="A35" s="26">
         <v>34</v>
       </c>
-      <c r="B35" s="36" t="s">
+      <c r="B35" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C35" s="3"/>
-      <c r="D35" s="36" t="s">
+      <c r="D35" s="26" t="s">
         <v>334</v>
       </c>
       <c r="E35" s="3"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="36">
+      <c r="A36" s="26">
         <v>35</v>
       </c>
-      <c r="B36" s="36" t="s">
+      <c r="B36" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C36" s="3"/>
-      <c r="D36" s="36" t="s">
+      <c r="D36" s="26" t="s">
         <v>335</v>
       </c>
       <c r="E36" s="3"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="36">
+      <c r="A37" s="26">
         <v>36</v>
       </c>
-      <c r="B37" s="36" t="s">
+      <c r="B37" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C37" s="3"/>
-      <c r="D37" s="36" t="s">
+      <c r="D37" s="26" t="s">
         <v>336</v>
       </c>
       <c r="E37" s="3"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="36">
+      <c r="A38" s="26">
         <v>37</v>
       </c>
-      <c r="B38" s="36" t="s">
+      <c r="B38" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C38" s="3"/>
-      <c r="D38" s="36" t="s">
+      <c r="D38" s="26" t="s">
         <v>337</v>
       </c>
       <c r="E38" s="3"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="36">
+      <c r="A39" s="26">
         <v>38</v>
       </c>
-      <c r="B39" s="36" t="s">
+      <c r="B39" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C39" s="3"/>
-      <c r="D39" s="36" t="s">
+      <c r="D39" s="26" t="s">
         <v>338</v>
       </c>
       <c r="E39" s="3"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="36">
+      <c r="A40" s="26">
         <v>39</v>
       </c>
-      <c r="B40" s="36" t="s">
+      <c r="B40" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C40" s="3"/>
-      <c r="D40" s="36" t="s">
+      <c r="D40" s="26" t="s">
         <v>339</v>
       </c>
       <c r="E40" s="3"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="36">
+      <c r="A41" s="26">
         <v>40</v>
       </c>
-      <c r="B41" s="36" t="s">
+      <c r="B41" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C41" s="3"/>
-      <c r="D41" s="36" t="s">
+      <c r="D41" s="26" t="s">
         <v>340</v>
       </c>
       <c r="E41" s="3"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="36">
+      <c r="A42" s="26">
         <v>41</v>
       </c>
-      <c r="B42" s="36" t="s">
+      <c r="B42" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="36" t="s">
+      <c r="D42" s="26" t="s">
         <v>341</v>
       </c>
       <c r="E42" s="3"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="36">
+      <c r="A43" s="26">
         <v>42</v>
       </c>
-      <c r="B43" s="36" t="s">
+      <c r="B43" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C43" s="3"/>
-      <c r="D43" s="36" t="s">
+      <c r="D43" s="26" t="s">
         <v>342</v>
       </c>
       <c r="E43" s="3"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="36">
+      <c r="A44" s="26">
         <v>43</v>
       </c>
-      <c r="B44" s="36" t="s">
+      <c r="B44" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C44" s="3"/>
-      <c r="D44" s="36" t="s">
+      <c r="D44" s="26" t="s">
         <v>343</v>
       </c>
       <c r="E44" s="3"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="36">
+      <c r="A45" s="26">
         <v>44</v>
       </c>
-      <c r="B45" s="36" t="s">
+      <c r="B45" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C45" s="3"/>
-      <c r="D45" s="36" t="s">
+      <c r="D45" s="26" t="s">
         <v>344</v>
       </c>
       <c r="E45" s="3"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="36">
+      <c r="A46" s="26">
         <v>45</v>
       </c>
-      <c r="B46" s="36" t="s">
+      <c r="B46" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C46" s="3"/>
-      <c r="D46" s="36" t="s">
+      <c r="D46" s="26" t="s">
         <v>345</v>
       </c>
       <c r="E46" s="3"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="36">
+      <c r="A47" s="26">
         <v>46</v>
       </c>
-      <c r="B47" s="36" t="s">
+      <c r="B47" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C47" s="3"/>
-      <c r="D47" s="36" t="s">
+      <c r="D47" s="26" t="s">
         <v>346</v>
       </c>
       <c r="E47" s="3"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="36">
+      <c r="A48" s="26">
         <v>47</v>
       </c>
-      <c r="B48" s="36" t="s">
+      <c r="B48" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C48" s="3"/>
-      <c r="D48" s="36" t="s">
+      <c r="D48" s="26" t="s">
         <v>347</v>
       </c>
       <c r="E48" s="3"/>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="36">
+      <c r="A49" s="26">
         <v>48</v>
       </c>
-      <c r="B49" s="36" t="s">
+      <c r="B49" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C49" s="3"/>
-      <c r="D49" s="36" t="s">
+      <c r="D49" s="26" t="s">
         <v>348</v>
       </c>
       <c r="E49" s="3"/>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="36">
+      <c r="A50" s="26">
         <v>49</v>
       </c>
-      <c r="B50" s="36" t="s">
+      <c r="B50" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C50" s="3"/>
-      <c r="D50" s="36" t="s">
+      <c r="D50" s="26" t="s">
         <v>349</v>
       </c>
       <c r="E50" s="3"/>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="36">
+      <c r="A51" s="26">
         <v>50</v>
       </c>
-      <c r="B51" s="36" t="s">
+      <c r="B51" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C51" s="3"/>
-      <c r="D51" s="36" t="s">
+      <c r="D51" s="26" t="s">
         <v>350</v>
       </c>
       <c r="E51" s="3"/>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="36">
+      <c r="A52" s="26">
         <v>51</v>
       </c>
-      <c r="B52" s="36" t="s">
+      <c r="B52" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C52" s="3"/>
-      <c r="D52" s="36" t="s">
+      <c r="D52" s="26" t="s">
         <v>351</v>
       </c>
       <c r="E52" s="3"/>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="36">
+      <c r="A53" s="26">
         <v>52</v>
       </c>
-      <c r="B53" s="36" t="s">
+      <c r="B53" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C53" s="3"/>
-      <c r="D53" s="36" t="s">
+      <c r="D53" s="26" t="s">
         <v>352</v>
       </c>
       <c r="E53" s="3"/>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="36">
+      <c r="A54" s="26">
         <v>53</v>
       </c>
-      <c r="B54" s="36" t="s">
+      <c r="B54" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C54" s="3"/>
-      <c r="D54" s="36" t="s">
+      <c r="D54" s="26" t="s">
         <v>353</v>
       </c>
       <c r="E54" s="3"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="36">
+      <c r="A55" s="26">
         <v>54</v>
       </c>
-      <c r="B55" s="36" t="s">
+      <c r="B55" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C55" s="3"/>
-      <c r="D55" s="36" t="s">
+      <c r="D55" s="26" t="s">
         <v>356</v>
       </c>
       <c r="E55" s="3"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="36">
+      <c r="A56" s="26">
         <v>55</v>
       </c>
-      <c r="B56" s="36" t="s">
+      <c r="B56" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C56" s="3"/>
-      <c r="D56" s="36" t="s">
+      <c r="D56" s="26" t="s">
         <v>357</v>
       </c>
       <c r="E56" s="3"/>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="36">
+      <c r="A57" s="26">
         <v>56</v>
       </c>
-      <c r="B57" s="36" t="s">
+      <c r="B57" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C57" s="3"/>
-      <c r="D57" s="36" t="s">
+      <c r="D57" s="26" t="s">
         <v>358</v>
       </c>
       <c r="E57" s="3"/>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="36">
+      <c r="A58" s="26">
         <v>57</v>
       </c>
-      <c r="B58" s="36" t="s">
+      <c r="B58" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C58" s="3"/>
-      <c r="D58" s="36" t="s">
+      <c r="D58" s="26" t="s">
         <v>359</v>
       </c>
       <c r="E58" s="3"/>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="36">
+      <c r="A59" s="26">
         <v>58</v>
       </c>
-      <c r="B59" s="36" t="s">
+      <c r="B59" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C59" s="3"/>
-      <c r="D59" s="36" t="s">
+      <c r="D59" s="26" t="s">
         <v>360</v>
       </c>
       <c r="E59" s="3"/>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="36">
+      <c r="A60" s="26">
         <v>59</v>
       </c>
-      <c r="B60" s="36" t="s">
+      <c r="B60" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C60" s="3"/>
-      <c r="D60" s="36" t="s">
+      <c r="D60" s="26" t="s">
         <v>361</v>
       </c>
       <c r="E60" s="3"/>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="36">
+      <c r="A61" s="26">
         <v>60</v>
       </c>
-      <c r="B61" s="36" t="s">
+      <c r="B61" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C61" s="3"/>
-      <c r="D61" s="36" t="s">
+      <c r="D61" s="26" t="s">
         <v>362</v>
       </c>
       <c r="E61" s="3"/>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="36">
+      <c r="A62" s="26">
         <v>61</v>
       </c>
-      <c r="B62" s="36" t="s">
+      <c r="B62" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C62" s="3"/>
-      <c r="D62" s="36" t="s">
+      <c r="D62" s="26" t="s">
         <v>363</v>
       </c>
       <c r="E62" s="3"/>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="36">
+      <c r="A63" s="26">
         <v>62</v>
       </c>
-      <c r="B63" s="36" t="s">
+      <c r="B63" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C63" s="3"/>
-      <c r="D63" s="36" t="s">
+      <c r="D63" s="26" t="s">
         <v>364</v>
       </c>
       <c r="E63" s="3"/>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="36">
+      <c r="A64" s="26">
         <v>63</v>
       </c>
-      <c r="B64" s="36" t="s">
+      <c r="B64" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C64" s="3"/>
-      <c r="D64" s="36" t="s">
+      <c r="D64" s="26" t="s">
         <v>365</v>
       </c>
       <c r="E64" s="3"/>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="36">
+      <c r="A65" s="26">
         <v>64</v>
       </c>
-      <c r="B65" s="36" t="s">
+      <c r="B65" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C65" s="3"/>
-      <c r="D65" s="36" t="s">
+      <c r="D65" s="26" t="s">
         <v>366</v>
       </c>
       <c r="E65" s="3"/>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="36">
+      <c r="A66" s="26">
         <v>65</v>
       </c>
-      <c r="B66" s="36" t="s">
+      <c r="B66" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C66" s="3"/>
-      <c r="D66" s="36" t="s">
+      <c r="D66" s="26" t="s">
         <v>367</v>
       </c>
       <c r="E66" s="3"/>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="36">
+      <c r="A67" s="26">
         <v>66</v>
       </c>
-      <c r="B67" s="36" t="s">
+      <c r="B67" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C67" s="3"/>
-      <c r="D67" s="36" t="s">
+      <c r="D67" s="26" t="s">
         <v>368</v>
       </c>
       <c r="E67" s="3"/>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="36">
+      <c r="A68" s="26">
         <v>67</v>
       </c>
-      <c r="B68" s="36" t="s">
+      <c r="B68" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C68" s="3"/>
-      <c r="D68" s="36" t="s">
+      <c r="D68" s="26" t="s">
         <v>369</v>
       </c>
       <c r="E68" s="3"/>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="36">
+      <c r="A69" s="26">
         <v>68</v>
       </c>
-      <c r="B69" s="36" t="s">
+      <c r="B69" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C69" s="3"/>
-      <c r="D69" s="36" t="s">
+      <c r="D69" s="26" t="s">
         <v>370</v>
       </c>
       <c r="E69" s="3"/>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="36">
+      <c r="A70" s="26">
         <v>69</v>
       </c>
-      <c r="B70" s="36" t="s">
+      <c r="B70" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C70" s="3"/>
-      <c r="D70" s="36" t="s">
+      <c r="D70" s="26" t="s">
         <v>371</v>
       </c>
       <c r="E70" s="3"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="36">
+      <c r="A71" s="26">
         <v>70</v>
       </c>
-      <c r="B71" s="36" t="s">
+      <c r="B71" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D71" s="37" t="s">
+      <c r="D71" s="27" t="s">
         <v>372</v>
       </c>
       <c r="E71" s="3"/>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="36">
+      <c r="A72" s="26">
         <v>71</v>
       </c>
-      <c r="B72" s="36" t="s">
+      <c r="B72" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D72" s="37" t="s">
+      <c r="D72" s="27" t="s">
         <v>373</v>
       </c>
       <c r="E72" s="3"/>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="36">
+      <c r="A73" s="26">
         <v>72</v>
       </c>
-      <c r="B73" s="36" t="s">
+      <c r="B73" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D73" s="37" t="s">
+      <c r="D73" s="27" t="s">
         <v>374</v>
       </c>
       <c r="E73" s="3"/>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="36">
+      <c r="A74" s="26">
         <v>73</v>
       </c>
-      <c r="B74" s="36"/>
+      <c r="B74" s="26"/>
       <c r="C74" s="3"/>
-      <c r="D74" s="36" t="s">
+      <c r="D74" s="26" t="s">
         <v>375</v>
       </c>
       <c r="E74" s="3"/>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="36">
+      <c r="A75" s="26">
         <v>74</v>
       </c>
-      <c r="B75" s="36"/>
+      <c r="B75" s="26"/>
       <c r="C75" s="3"/>
-      <c r="D75" s="36" t="s">
+      <c r="D75" s="26" t="s">
         <v>377</v>
       </c>
       <c r="E75" s="3"/>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="36">
+      <c r="A76" s="26">
         <v>75</v>
       </c>
-      <c r="B76" s="36" t="s">
+      <c r="B76" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C76" s="3"/>
-      <c r="D76" s="36" t="s">
+      <c r="D76" s="26" t="s">
         <v>378</v>
       </c>
       <c r="E76" s="3"/>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="36">
+      <c r="A77" s="26">
         <v>76</v>
       </c>
-      <c r="B77" s="36"/>
+      <c r="B77" s="26"/>
       <c r="C77" s="3"/>
-      <c r="D77" s="36"/>
+      <c r="D77" s="26"/>
       <c r="E77" s="3"/>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="36">
+      <c r="A78" s="26">
         <v>77</v>
       </c>
-      <c r="B78" s="36"/>
+      <c r="B78" s="26"/>
       <c r="C78" s="3"/>
-      <c r="D78" s="36"/>
+      <c r="D78" s="26"/>
       <c r="E78" s="3"/>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="36">
+      <c r="A79" s="26">
         <v>78</v>
       </c>
-      <c r="B79" s="36"/>
+      <c r="B79" s="26"/>
       <c r="C79" s="3"/>
-      <c r="D79" s="36"/>
+      <c r="D79" s="26"/>
       <c r="E79" s="3"/>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="36">
+      <c r="A80" s="26">
         <v>79</v>
       </c>
-      <c r="B80" s="36"/>
+      <c r="B80" s="26"/>
       <c r="C80" s="3"/>
-      <c r="D80" s="36"/>
+      <c r="D80" s="26"/>
       <c r="E80" s="3"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="36">
+      <c r="A81" s="26">
         <v>80</v>
       </c>
-      <c r="B81" s="36"/>
+      <c r="B81" s="26"/>
       <c r="C81" s="3"/>
-      <c r="D81" s="36"/>
+      <c r="D81" s="26"/>
       <c r="E81" s="3"/>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="36">
+      <c r="A82" s="26">
         <v>81</v>
       </c>
-      <c r="B82" s="36"/>
+      <c r="B82" s="26"/>
       <c r="C82" s="3"/>
-      <c r="D82" s="36"/>
+      <c r="D82" s="26"/>
       <c r="E82" s="3"/>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="36">
+      <c r="A83" s="26">
         <v>82</v>
       </c>
-      <c r="B83" s="36"/>
+      <c r="B83" s="26"/>
       <c r="C83" s="3"/>
-      <c r="D83" s="36"/>
+      <c r="D83" s="26"/>
       <c r="E83" s="3"/>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="36">
+      <c r="A84" s="26">
         <v>83</v>
       </c>
-      <c r="B84" s="36"/>
+      <c r="B84" s="26"/>
       <c r="C84" s="3"/>
-      <c r="D84" s="36"/>
+      <c r="D84" s="26"/>
       <c r="E84" s="3"/>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="36">
+      <c r="A85" s="26">
         <v>84</v>
       </c>
-      <c r="B85" s="36"/>
+      <c r="B85" s="26"/>
       <c r="C85" s="3"/>
-      <c r="D85" s="36"/>
+      <c r="D85" s="26"/>
       <c r="E85" s="3"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="36">
+      <c r="A86" s="26">
         <v>85</v>
       </c>
-      <c r="B86" s="36"/>
+      <c r="B86" s="26"/>
       <c r="C86" s="3"/>
-      <c r="D86" s="36"/>
+      <c r="D86" s="26"/>
       <c r="E86" s="3"/>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="36">
+      <c r="A87" s="26">
         <v>86</v>
       </c>
-      <c r="B87" s="36"/>
+      <c r="B87" s="26"/>
       <c r="C87" s="3"/>
-      <c r="D87" s="36"/>
+      <c r="D87" s="26"/>
       <c r="E87" s="3"/>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="36">
+      <c r="A88" s="26">
         <v>87</v>
       </c>
-      <c r="B88" s="36"/>
+      <c r="B88" s="26"/>
       <c r="C88" s="3"/>
-      <c r="D88" s="36"/>
+      <c r="D88" s="26"/>
       <c r="E88" s="3"/>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="36">
+      <c r="A89" s="26">
         <v>88</v>
       </c>
-      <c r="B89" s="36"/>
+      <c r="B89" s="26"/>
       <c r="C89" s="3"/>
-      <c r="D89" s="36"/>
+      <c r="D89" s="26"/>
       <c r="E89" s="3"/>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="36">
+      <c r="A90" s="26">
         <v>89</v>
       </c>
-      <c r="B90" s="36"/>
+      <c r="B90" s="26"/>
       <c r="C90" s="3"/>
-      <c r="D90" s="36"/>
+      <c r="D90" s="26"/>
       <c r="E90" s="3"/>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="36">
+      <c r="A91" s="26">
         <v>90</v>
       </c>
-      <c r="B91" s="36"/>
+      <c r="B91" s="26"/>
       <c r="C91" s="3"/>
-      <c r="D91" s="36"/>
+      <c r="D91" s="26"/>
       <c r="E91" s="3"/>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="36">
+      <c r="A92" s="26">
         <v>91</v>
       </c>
-      <c r="B92" s="36"/>
+      <c r="B92" s="26"/>
       <c r="C92" s="3"/>
-      <c r="D92" s="36"/>
+      <c r="D92" s="26"/>
       <c r="E92" s="3"/>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="36">
+      <c r="A93" s="26">
         <v>92</v>
       </c>
-      <c r="B93" s="36"/>
+      <c r="B93" s="26"/>
       <c r="C93" s="3"/>
-      <c r="D93" s="36"/>
+      <c r="D93" s="26"/>
       <c r="E93" s="3"/>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="36">
+      <c r="A94" s="26">
         <v>93</v>
       </c>
-      <c r="B94" s="36"/>
+      <c r="B94" s="26"/>
       <c r="C94" s="3"/>
-      <c r="D94" s="36"/>
+      <c r="D94" s="26"/>
       <c r="E94" s="3"/>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="36">
+      <c r="A95" s="26">
         <v>94</v>
       </c>
-      <c r="B95" s="36"/>
+      <c r="B95" s="26"/>
       <c r="C95" s="3"/>
-      <c r="D95" s="36"/>
+      <c r="D95" s="26"/>
       <c r="E95" s="3"/>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="36">
+      <c r="A96" s="26">
         <v>95</v>
       </c>
-      <c r="B96" s="36"/>
+      <c r="B96" s="26"/>
       <c r="C96" s="3"/>
-      <c r="D96" s="36"/>
+      <c r="D96" s="26"/>
       <c r="E96" s="3"/>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="36">
+      <c r="A97" s="26">
         <v>96</v>
       </c>
-      <c r="B97" s="36"/>
+      <c r="B97" s="26"/>
       <c r="C97" s="3"/>
-      <c r="D97" s="36"/>
+      <c r="D97" s="26"/>
       <c r="E97" s="3"/>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="36">
+      <c r="A98" s="26">
         <v>97</v>
       </c>
-      <c r="B98" s="36"/>
+      <c r="B98" s="26"/>
       <c r="C98" s="3"/>
-      <c r="D98" s="36"/>
+      <c r="D98" s="26"/>
       <c r="E98" s="3"/>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="36">
+      <c r="A99" s="26">
         <v>98</v>
       </c>
-      <c r="B99" s="36"/>
+      <c r="B99" s="26"/>
       <c r="C99" s="3"/>
-      <c r="D99" s="36"/>
+      <c r="D99" s="26"/>
       <c r="E99" s="3"/>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="36">
+      <c r="A100" s="26">
         <v>99</v>
       </c>
-      <c r="B100" s="36"/>
+      <c r="B100" s="26"/>
       <c r="C100" s="3"/>
-      <c r="D100" s="36"/>
+      <c r="D100" s="26"/>
       <c r="E100" s="3"/>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="36">
+      <c r="A101" s="26">
         <v>100</v>
       </c>
-      <c r="B101" s="36"/>
+      <c r="B101" s="26"/>
       <c r="C101" s="3"/>
-      <c r="D101" s="36"/>
+      <c r="D101" s="26"/>
       <c r="E101" s="3"/>
     </row>
     <row r="102" spans="1:5">
-      <c r="A102" s="36">
+      <c r="A102" s="26">
         <v>101</v>
       </c>
-      <c r="B102" s="36"/>
+      <c r="B102" s="26"/>
       <c r="C102" s="3"/>
-      <c r="D102" s="36"/>
+      <c r="D102" s="26"/>
       <c r="E102" s="3"/>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="36">
+      <c r="A103" s="26">
         <v>102</v>
       </c>
-      <c r="B103" s="36"/>
+      <c r="B103" s="26"/>
       <c r="C103" s="3"/>
-      <c r="D103" s="36"/>
+      <c r="D103" s="26"/>
       <c r="E103" s="3"/>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="36">
+      <c r="A104" s="26">
         <v>103</v>
       </c>
-      <c r="B104" s="36"/>
+      <c r="B104" s="26"/>
       <c r="C104" s="3"/>
-      <c r="D104" s="36"/>
+      <c r="D104" s="26"/>
       <c r="E104" s="3"/>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="36">
+      <c r="A105" s="26">
         <v>104</v>
       </c>
-      <c r="B105" s="36"/>
+      <c r="B105" s="26"/>
       <c r="C105" s="3"/>
-      <c r="D105" s="36"/>
+      <c r="D105" s="26"/>
       <c r="E105" s="3"/>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="36">
+      <c r="A106" s="26">
         <v>105</v>
       </c>
-      <c r="B106" s="36"/>
+      <c r="B106" s="26"/>
       <c r="C106" s="3"/>
-      <c r="D106" s="36"/>
+      <c r="D106" s="26"/>
       <c r="E106" s="3"/>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="36">
+      <c r="A107" s="26">
         <v>106</v>
       </c>
-      <c r="B107" s="36"/>
+      <c r="B107" s="26"/>
       <c r="C107" s="3"/>
-      <c r="D107" s="36"/>
+      <c r="D107" s="26"/>
       <c r="E107" s="3"/>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="36">
+      <c r="A108" s="26">
         <v>107</v>
       </c>
-      <c r="B108" s="36"/>
+      <c r="B108" s="26"/>
       <c r="C108" s="3"/>
-      <c r="D108" s="36"/>
+      <c r="D108" s="26"/>
       <c r="E108" s="3"/>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="36">
+      <c r="A109" s="26">
         <v>108</v>
       </c>
-      <c r="B109" s="36"/>
+      <c r="B109" s="26"/>
       <c r="C109" s="3"/>
-      <c r="D109" s="36"/>
+      <c r="D109" s="26"/>
       <c r="E109" s="3"/>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="36">
+      <c r="A110" s="26">
         <v>109</v>
       </c>
-      <c r="B110" s="36"/>
+      <c r="B110" s="26"/>
       <c r="C110" s="3"/>
-      <c r="D110" s="36"/>
+      <c r="D110" s="26"/>
       <c r="E110" s="3"/>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="36">
+      <c r="A111" s="26">
         <v>110</v>
       </c>
-      <c r="B111" s="36"/>
+      <c r="B111" s="26"/>
       <c r="C111" s="3"/>
-      <c r="D111" s="36"/>
+      <c r="D111" s="26"/>
       <c r="E111" s="3"/>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="36">
+      <c r="A112" s="26">
         <v>111</v>
       </c>
-      <c r="B112" s="36"/>
+      <c r="B112" s="26"/>
       <c r="C112" s="3"/>
-      <c r="D112" s="36"/>
+      <c r="D112" s="26"/>
       <c r="E112" s="3"/>
     </row>
     <row r="113" spans="1:5">
-      <c r="A113" s="36">
+      <c r="A113" s="26">
         <v>112</v>
       </c>
-      <c r="B113" s="36"/>
+      <c r="B113" s="26"/>
       <c r="C113" s="3"/>
-      <c r="D113" s="36"/>
+      <c r="D113" s="26"/>
       <c r="E113" s="3"/>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="36">
+      <c r="A114" s="26">
         <v>113</v>
       </c>
-      <c r="B114" s="36"/>
+      <c r="B114" s="26"/>
       <c r="C114" s="3"/>
-      <c r="D114" s="36"/>
+      <c r="D114" s="26"/>
       <c r="E114" s="3"/>
     </row>
     <row r="115" spans="1:5">
-      <c r="A115" s="36">
+      <c r="A115" s="26">
         <v>114</v>
       </c>
-      <c r="B115" s="36"/>
+      <c r="B115" s="26"/>
       <c r="C115" s="3"/>
-      <c r="D115" s="36"/>
+      <c r="D115" s="26"/>
       <c r="E115" s="3"/>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="36">
+      <c r="A116" s="26">
         <v>115</v>
       </c>
-      <c r="B116" s="36"/>
+      <c r="B116" s="26"/>
       <c r="C116" s="3"/>
-      <c r="D116" s="36"/>
+      <c r="D116" s="26"/>
       <c r="E116" s="3"/>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="36">
+      <c r="A117" s="26">
         <v>116</v>
       </c>
-      <c r="B117" s="36"/>
+      <c r="B117" s="26"/>
       <c r="C117" s="3"/>
-      <c r="D117" s="36"/>
+      <c r="D117" s="26"/>
       <c r="E117" s="3"/>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="36">
+      <c r="A118" s="26">
         <v>117</v>
       </c>
-      <c r="B118" s="36"/>
+      <c r="B118" s="26"/>
       <c r="C118" s="3"/>
-      <c r="D118" s="36"/>
+      <c r="D118" s="26"/>
       <c r="E118" s="3"/>
     </row>
     <row r="119" spans="1:5">
-      <c r="A119" s="36">
+      <c r="A119" s="26">
         <v>118</v>
       </c>
-      <c r="B119" s="36"/>
+      <c r="B119" s="26"/>
       <c r="C119" s="3"/>
-      <c r="D119" s="36"/>
+      <c r="D119" s="26"/>
       <c r="E119" s="3"/>
     </row>
     <row r="120" spans="1:5">
-      <c r="A120" s="36">
+      <c r="A120" s="26">
         <v>119</v>
       </c>
-      <c r="B120" s="36"/>
+      <c r="B120" s="26"/>
       <c r="C120" s="3"/>
-      <c r="D120" s="36"/>
+      <c r="D120" s="26"/>
       <c r="E120" s="3"/>
     </row>
     <row r="121" spans="1:5">
-      <c r="A121" s="36">
+      <c r="A121" s="26">
         <v>120</v>
       </c>
-      <c r="B121" s="36"/>
+      <c r="B121" s="26"/>
       <c r="C121" s="3"/>
-      <c r="D121" s="36"/>
+      <c r="D121" s="26"/>
       <c r="E121" s="3"/>
     </row>
     <row r="122" spans="1:5">
-      <c r="A122" s="36">
+      <c r="A122" s="26">
         <v>121</v>
       </c>
-      <c r="B122" s="36"/>
+      <c r="B122" s="26"/>
       <c r="C122" s="3"/>
-      <c r="D122" s="36"/>
+      <c r="D122" s="26"/>
       <c r="E122" s="3"/>
     </row>
     <row r="123" spans="1:5">
-      <c r="A123" s="36">
+      <c r="A123" s="26">
         <v>122</v>
       </c>
-      <c r="B123" s="36"/>
+      <c r="B123" s="26"/>
       <c r="C123" s="3"/>
-      <c r="D123" s="36"/>
+      <c r="D123" s="26"/>
       <c r="E123" s="3"/>
     </row>
     <row r="124" spans="1:5">
-      <c r="A124" s="36">
+      <c r="A124" s="26">
         <v>123</v>
       </c>
-      <c r="B124" s="36"/>
+      <c r="B124" s="26"/>
       <c r="C124" s="3"/>
-      <c r="D124" s="36"/>
+      <c r="D124" s="26"/>
       <c r="E124" s="3"/>
     </row>
     <row r="125" spans="1:5">
-      <c r="A125" s="36">
+      <c r="A125" s="26">
         <v>124</v>
       </c>
-      <c r="B125" s="36"/>
+      <c r="B125" s="26"/>
       <c r="C125" s="3"/>
-      <c r="D125" s="36"/>
+      <c r="D125" s="26"/>
       <c r="E125" s="3"/>
     </row>
     <row r="126" spans="1:5">
-      <c r="A126" s="36">
+      <c r="A126" s="26">
         <v>125</v>
       </c>
-      <c r="B126" s="36"/>
+      <c r="B126" s="26"/>
       <c r="C126" s="3"/>
-      <c r="D126" s="36"/>
+      <c r="D126" s="26"/>
       <c r="E126" s="3"/>
     </row>
     <row r="127" spans="1:5">
-      <c r="A127" s="36">
+      <c r="A127" s="26">
         <v>126</v>
       </c>
-      <c r="B127" s="36"/>
+      <c r="B127" s="26"/>
       <c r="C127" s="3"/>
-      <c r="D127" s="36"/>
+      <c r="D127" s="26"/>
       <c r="E127" s="3"/>
     </row>
     <row r="128" spans="1:5">
-      <c r="A128" s="36">
+      <c r="A128" s="26">
         <v>127</v>
       </c>
-      <c r="B128" s="36"/>
+      <c r="B128" s="26"/>
       <c r="C128" s="3"/>
-      <c r="D128" s="36"/>
+      <c r="D128" s="26"/>
       <c r="E128" s="3"/>
     </row>
     <row r="129" spans="1:5">
-      <c r="A129" s="36">
+      <c r="A129" s="26">
         <v>128</v>
       </c>
-      <c r="B129" s="36"/>
+      <c r="B129" s="26"/>
       <c r="C129" s="3"/>
-      <c r="D129" s="36"/>
+      <c r="D129" s="26"/>
       <c r="E129" s="3"/>
     </row>
     <row r="130" spans="1:5">
-      <c r="A130" s="36">
+      <c r="A130" s="26">
         <v>129</v>
       </c>
-      <c r="B130" s="36"/>
+      <c r="B130" s="26"/>
       <c r="C130" s="3"/>
-      <c r="D130" s="36"/>
+      <c r="D130" s="26"/>
       <c r="E130" s="3"/>
     </row>
     <row r="131" spans="1:5">
-      <c r="A131" s="36">
+      <c r="A131" s="26">
         <v>130</v>
       </c>
-      <c r="B131" s="36"/>
+      <c r="B131" s="26"/>
       <c r="C131" s="3"/>
-      <c r="D131" s="36"/>
+      <c r="D131" s="26"/>
       <c r="E131" s="3"/>
     </row>
     <row r="132" spans="1:5">
-      <c r="A132" s="36">
+      <c r="A132" s="26">
         <v>131</v>
       </c>
-      <c r="B132" s="36"/>
+      <c r="B132" s="26"/>
       <c r="C132" s="3"/>
-      <c r="D132" s="36"/>
+      <c r="D132" s="26"/>
       <c r="E132" s="3"/>
     </row>
     <row r="133" spans="1:5">
-      <c r="A133" s="36">
+      <c r="A133" s="26">
         <v>132</v>
       </c>
-      <c r="B133" s="36"/>
+      <c r="B133" s="26"/>
       <c r="C133" s="3"/>
-      <c r="D133" s="36"/>
+      <c r="D133" s="26"/>
       <c r="E133" s="3"/>
     </row>
     <row r="134" spans="1:5">
-      <c r="A134" s="36">
+      <c r="A134" s="26">
         <v>133</v>
       </c>
-      <c r="B134" s="36"/>
+      <c r="B134" s="26"/>
       <c r="C134" s="3"/>
-      <c r="D134" s="36"/>
+      <c r="D134" s="26"/>
       <c r="E134" s="3"/>
     </row>
     <row r="135" spans="1:5">
-      <c r="A135" s="36">
+      <c r="A135" s="26">
         <v>134</v>
       </c>
-      <c r="B135" s="36"/>
+      <c r="B135" s="26"/>
       <c r="C135" s="3"/>
-      <c r="D135" s="36"/>
+      <c r="D135" s="26"/>
       <c r="E135" s="3"/>
     </row>
     <row r="136" spans="1:5">
-      <c r="A136" s="36">
+      <c r="A136" s="26">
         <v>135</v>
       </c>
-      <c r="B136" s="36"/>
+      <c r="B136" s="26"/>
       <c r="C136" s="3"/>
-      <c r="D136" s="36"/>
+      <c r="D136" s="26"/>
       <c r="E136" s="3"/>
     </row>
     <row r="137" spans="1:5">
-      <c r="A137" s="36">
+      <c r="A137" s="26">
         <v>136</v>
       </c>
-      <c r="B137" s="36"/>
+      <c r="B137" s="26"/>
       <c r="C137" s="3"/>
-      <c r="D137" s="36"/>
+      <c r="D137" s="26"/>
       <c r="E137" s="3"/>
     </row>
     <row r="138" spans="1:5">
-      <c r="A138" s="36">
+      <c r="A138" s="26">
         <v>137</v>
       </c>
-      <c r="B138" s="36"/>
+      <c r="B138" s="26"/>
       <c r="C138" s="3"/>
-      <c r="D138" s="36"/>
+      <c r="D138" s="26"/>
       <c r="E138" s="3"/>
     </row>
     <row r="139" spans="1:5">
-      <c r="A139" s="36">
+      <c r="A139" s="26">
         <v>138</v>
       </c>
-      <c r="B139" s="36"/>
+      <c r="B139" s="26"/>
       <c r="C139" s="3"/>
-      <c r="D139" s="36"/>
+      <c r="D139" s="26"/>
       <c r="E139" s="3"/>
     </row>
     <row r="140" spans="1:5">
-      <c r="A140" s="36">
+      <c r="A140" s="26">
         <v>139</v>
       </c>
-      <c r="B140" s="36"/>
+      <c r="B140" s="26"/>
       <c r="C140" s="3"/>
-      <c r="D140" s="36"/>
+      <c r="D140" s="26"/>
       <c r="E140" s="3"/>
     </row>
     <row r="141" spans="1:5">
-      <c r="A141" s="36">
+      <c r="A141" s="26">
         <v>140</v>
       </c>
-      <c r="B141" s="36"/>
+      <c r="B141" s="26"/>
       <c r="C141" s="3"/>
-      <c r="D141" s="36"/>
+      <c r="D141" s="26"/>
       <c r="E141" s="3"/>
     </row>
     <row r="142" spans="1:5">
-      <c r="A142" s="36">
+      <c r="A142" s="26">
         <v>141</v>
       </c>
-      <c r="B142" s="36"/>
+      <c r="B142" s="26"/>
       <c r="C142" s="3"/>
-      <c r="D142" s="36"/>
+      <c r="D142" s="26"/>
       <c r="E142" s="3"/>
     </row>
     <row r="143" spans="1:5">
-      <c r="A143" s="36">
+      <c r="A143" s="26">
         <v>142</v>
       </c>
-      <c r="B143" s="36"/>
+      <c r="B143" s="26"/>
       <c r="C143" s="3"/>
-      <c r="D143" s="36"/>
+      <c r="D143" s="26"/>
       <c r="E143" s="3"/>
     </row>
     <row r="144" spans="1:5">
-      <c r="A144" s="36">
+      <c r="A144" s="26">
         <v>143</v>
       </c>
-      <c r="B144" s="36"/>
+      <c r="B144" s="26"/>
       <c r="C144" s="3"/>
-      <c r="D144" s="36"/>
+      <c r="D144" s="26"/>
       <c r="E144" s="3"/>
     </row>
     <row r="145" spans="1:5">
-      <c r="A145" s="36">
+      <c r="A145" s="26">
         <v>144</v>
       </c>
-      <c r="B145" s="36"/>
+      <c r="B145" s="26"/>
       <c r="C145" s="3"/>
-      <c r="D145" s="36"/>
+      <c r="D145" s="26"/>
       <c r="E145" s="3"/>
     </row>
     <row r="146" spans="1:5">
-      <c r="A146" s="36">
+      <c r="A146" s="26">
         <v>145</v>
       </c>
-      <c r="B146" s="36"/>
+      <c r="B146" s="26"/>
       <c r="C146" s="3"/>
-      <c r="D146" s="36"/>
+      <c r="D146" s="26"/>
       <c r="E146" s="3"/>
     </row>
     <row r="147" spans="1:5">
-      <c r="A147" s="36">
+      <c r="A147" s="26">
         <v>146</v>
       </c>
-      <c r="B147" s="36"/>
+      <c r="B147" s="26"/>
       <c r="C147" s="3"/>
-      <c r="D147" s="36"/>
+      <c r="D147" s="26"/>
       <c r="E147" s="3"/>
     </row>
     <row r="148" spans="1:5">
-      <c r="A148" s="36">
+      <c r="A148" s="26">
         <v>147</v>
       </c>
-      <c r="B148" s="36"/>
+      <c r="B148" s="26"/>
       <c r="C148" s="3"/>
-      <c r="D148" s="36"/>
+      <c r="D148" s="26"/>
       <c r="E148" s="3"/>
     </row>
     <row r="149" spans="1:5">
-      <c r="A149" s="36">
+      <c r="A149" s="26">
         <v>148</v>
       </c>
-      <c r="B149" s="36"/>
+      <c r="B149" s="26"/>
       <c r="C149" s="3"/>
-      <c r="D149" s="36"/>
+      <c r="D149" s="26"/>
       <c r="E149" s="3"/>
     </row>
     <row r="150" spans="1:5">
-      <c r="A150" s="36">
+      <c r="A150" s="26">
         <v>149</v>
       </c>
-      <c r="B150" s="36"/>
+      <c r="B150" s="26"/>
       <c r="C150" s="3"/>
-      <c r="D150" s="36"/>
+      <c r="D150" s="26"/>
       <c r="E150" s="3"/>
     </row>
     <row r="151" spans="1:5">
-      <c r="A151" s="36">
+      <c r="A151" s="26">
         <v>150</v>
       </c>
-      <c r="B151" s="36"/>
+      <c r="B151" s="26"/>
       <c r="C151" s="3"/>
-      <c r="D151" s="36"/>
+      <c r="D151" s="26"/>
       <c r="E151" s="3"/>
     </row>
     <row r="152" spans="1:5">
-      <c r="A152" s="36">
+      <c r="A152" s="26">
         <v>151</v>
       </c>
-      <c r="B152" s="36"/>
+      <c r="B152" s="26"/>
       <c r="C152" s="3"/>
-      <c r="D152" s="36"/>
+      <c r="D152" s="26"/>
       <c r="E152" s="3"/>
     </row>
     <row r="153" spans="1:5">
-      <c r="A153" s="36">
+      <c r="A153" s="26">
         <v>152</v>
       </c>
-      <c r="B153" s="36"/>
+      <c r="B153" s="26"/>
       <c r="C153" s="3"/>
-      <c r="D153" s="36"/>
+      <c r="D153" s="26"/>
       <c r="E153" s="3"/>
     </row>
     <row r="154" spans="1:5">
-      <c r="A154" s="36">
+      <c r="A154" s="26">
         <v>153</v>
       </c>
-      <c r="B154" s="36"/>
+      <c r="B154" s="26"/>
       <c r="C154" s="3"/>
-      <c r="D154" s="36"/>
+      <c r="D154" s="26"/>
       <c r="E154" s="3"/>
     </row>
     <row r="155" spans="1:5">
-      <c r="A155" s="36">
+      <c r="A155" s="26">
         <v>154</v>
       </c>
-      <c r="B155" s="36"/>
+      <c r="B155" s="26"/>
       <c r="C155" s="3"/>
-      <c r="D155" s="36"/>
+      <c r="D155" s="26"/>
       <c r="E155" s="3"/>
     </row>
     <row r="156" spans="1:5">
-      <c r="A156" s="36">
+      <c r="A156" s="26">
         <v>155</v>
       </c>
-      <c r="B156" s="36"/>
+      <c r="B156" s="26"/>
       <c r="C156" s="3"/>
-      <c r="D156" s="36"/>
+      <c r="D156" s="26"/>
       <c r="E156" s="3"/>
     </row>
     <row r="157" spans="1:5">
-      <c r="A157" s="36">
+      <c r="A157" s="26">
         <v>156</v>
       </c>
-      <c r="B157" s="36"/>
+      <c r="B157" s="26"/>
       <c r="C157" s="3"/>
-      <c r="D157" s="36"/>
+      <c r="D157" s="26"/>
       <c r="E157" s="3"/>
     </row>
     <row r="158" spans="1:5">
-      <c r="A158" s="36">
-        <v>157</v>
-      </c>
-      <c r="B158" s="36"/>
+      <c r="A158" s="26">
+        <v>157</v>
+      </c>
+      <c r="B158" s="26"/>
       <c r="C158" s="3"/>
-      <c r="D158" s="36"/>
+      <c r="D158" s="26"/>
       <c r="E158" s="3"/>
     </row>
     <row r="159" spans="1:5">
-      <c r="A159" s="36">
+      <c r="A159" s="26">
         <v>158</v>
       </c>
-      <c r="B159" s="36"/>
+      <c r="B159" s="26"/>
       <c r="C159" s="3"/>
-      <c r="D159" s="36"/>
+      <c r="D159" s="26"/>
       <c r="E159" s="3"/>
     </row>
     <row r="160" spans="1:5">
-      <c r="A160" s="36">
+      <c r="A160" s="26">
         <v>159</v>
       </c>
-      <c r="B160" s="36"/>
+      <c r="B160" s="26"/>
       <c r="C160" s="3"/>
-      <c r="D160" s="36"/>
+      <c r="D160" s="26"/>
       <c r="E160" s="3"/>
     </row>
     <row r="161" spans="1:5">
-      <c r="A161" s="36">
+      <c r="A161" s="26">
         <v>160</v>
       </c>
-      <c r="B161" s="36"/>
+      <c r="B161" s="26"/>
       <c r="C161" s="3"/>
-      <c r="D161" s="36"/>
+      <c r="D161" s="26"/>
       <c r="E161" s="3"/>
     </row>
     <row r="162" spans="1:5">
-      <c r="A162" s="36">
+      <c r="A162" s="26">
         <v>161</v>
       </c>
-      <c r="B162" s="36"/>
+      <c r="B162" s="26"/>
       <c r="C162" s="3"/>
-      <c r="D162" s="36"/>
+      <c r="D162" s="26"/>
       <c r="E162" s="3"/>
     </row>
     <row r="163" spans="1:5">
-      <c r="A163" s="36">
+      <c r="A163" s="26">
         <v>162</v>
       </c>
-      <c r="B163" s="36"/>
+      <c r="B163" s="26"/>
       <c r="C163" s="3"/>
-      <c r="D163" s="36"/>
+      <c r="D163" s="26"/>
       <c r="E163" s="3"/>
     </row>
     <row r="164" spans="1:5">
-      <c r="A164" s="36">
+      <c r="A164" s="26">
         <v>163</v>
       </c>
-      <c r="B164" s="36"/>
+      <c r="B164" s="26"/>
       <c r="C164" s="3"/>
-      <c r="D164" s="36"/>
+      <c r="D164" s="26"/>
       <c r="E164" s="3"/>
     </row>
     <row r="165" spans="1:5">
-      <c r="A165" s="36">
+      <c r="A165" s="26">
         <v>164</v>
       </c>
-      <c r="B165" s="36"/>
+      <c r="B165" s="26"/>
       <c r="C165" s="3"/>
-      <c r="D165" s="36"/>
+      <c r="D165" s="26"/>
       <c r="E165" s="3"/>
     </row>
     <row r="166" spans="1:5">
-      <c r="A166" s="36">
+      <c r="A166" s="26">
         <v>165</v>
       </c>
-      <c r="B166" s="36"/>
+      <c r="B166" s="26"/>
       <c r="C166" s="3"/>
-      <c r="D166" s="36"/>
+      <c r="D166" s="26"/>
       <c r="E166" s="3"/>
     </row>
     <row r="167" spans="1:5">
-      <c r="A167" s="36">
+      <c r="A167" s="26">
         <v>166</v>
       </c>
-      <c r="B167" s="36"/>
+      <c r="B167" s="26"/>
       <c r="C167" s="3"/>
-      <c r="D167" s="36"/>
+      <c r="D167" s="26"/>
       <c r="E167" s="3"/>
     </row>
     <row r="168" spans="1:5">
-      <c r="A168" s="36">
+      <c r="A168" s="26">
         <v>167</v>
       </c>
-      <c r="B168" s="36"/>
+      <c r="B168" s="26"/>
       <c r="C168" s="3"/>
-      <c r="D168" s="36"/>
+      <c r="D168" s="26"/>
       <c r="E168" s="3"/>
     </row>
     <row r="169" spans="1:5">
-      <c r="A169" s="36">
+      <c r="A169" s="26">
         <v>168</v>
       </c>
-      <c r="B169" s="36"/>
+      <c r="B169" s="26"/>
       <c r="C169" s="3"/>
-      <c r="D169" s="36"/>
+      <c r="D169" s="26"/>
       <c r="E169" s="3"/>
     </row>
     <row r="170" spans="1:5">
-      <c r="A170" s="36">
+      <c r="A170" s="26">
         <v>169</v>
       </c>
-      <c r="B170" s="36"/>
+      <c r="B170" s="26"/>
       <c r="C170" s="3"/>
-      <c r="D170" s="36"/>
+      <c r="D170" s="26"/>
       <c r="E170" s="3"/>
     </row>
     <row r="171" spans="1:5">
-      <c r="A171" s="36">
+      <c r="A171" s="26">
         <v>170</v>
       </c>
-      <c r="B171" s="36"/>
+      <c r="B171" s="26"/>
       <c r="C171" s="3"/>
-      <c r="D171" s="36"/>
+      <c r="D171" s="26"/>
       <c r="E171" s="3"/>
     </row>
     <row r="172" spans="1:5">
-      <c r="A172" s="36">
+      <c r="A172" s="26">
         <v>171</v>
       </c>
-      <c r="B172" s="36"/>
+      <c r="B172" s="26"/>
       <c r="C172" s="3"/>
-      <c r="D172" s="36"/>
+      <c r="D172" s="26"/>
       <c r="E172" s="3"/>
     </row>
     <row r="173" spans="1:5">
-      <c r="A173" s="36">
+      <c r="A173" s="26">
         <v>172</v>
       </c>
-      <c r="B173" s="36"/>
+      <c r="B173" s="26"/>
       <c r="C173" s="3"/>
-      <c r="D173" s="36"/>
+      <c r="D173" s="26"/>
       <c r="E173" s="3"/>
     </row>
     <row r="174" spans="1:5">
-      <c r="A174" s="36">
+      <c r="A174" s="26">
         <v>173</v>
       </c>
-      <c r="B174" s="36"/>
+      <c r="B174" s="26"/>
       <c r="C174" s="3"/>
-      <c r="D174" s="36"/>
+      <c r="D174" s="26"/>
       <c r="E174" s="3"/>
     </row>
     <row r="175" spans="1:5">
-      <c r="A175" s="36">
+      <c r="A175" s="26">
         <v>174</v>
       </c>
-      <c r="B175" s="36"/>
+      <c r="B175" s="26"/>
       <c r="C175" s="3"/>
-      <c r="D175" s="36"/>
+      <c r="D175" s="26"/>
       <c r="E175" s="3"/>
     </row>
     <row r="176" spans="1:5">
-      <c r="A176" s="36">
+      <c r="A176" s="26">
         <v>175</v>
       </c>
-      <c r="B176" s="36"/>
+      <c r="B176" s="26"/>
       <c r="C176" s="3"/>
-      <c r="D176" s="36"/>
+      <c r="D176" s="26"/>
       <c r="E176" s="3"/>
     </row>
     <row r="177" spans="1:5">
-      <c r="A177" s="36">
+      <c r="A177" s="26">
         <v>176</v>
       </c>
-      <c r="B177" s="36"/>
+      <c r="B177" s="26"/>
       <c r="C177" s="3"/>
-      <c r="D177" s="36"/>
+      <c r="D177" s="26"/>
       <c r="E177" s="3"/>
     </row>
     <row r="178" spans="1:5">
-      <c r="A178" s="36">
+      <c r="A178" s="26">
         <v>177</v>
       </c>
-      <c r="B178" s="36"/>
+      <c r="B178" s="26"/>
       <c r="C178" s="3"/>
-      <c r="D178" s="36"/>
+      <c r="D178" s="26"/>
       <c r="E178" s="3"/>
     </row>
     <row r="179" spans="1:5">
-      <c r="A179" s="36">
+      <c r="A179" s="26">
         <v>178</v>
       </c>
-      <c r="B179" s="36"/>
+      <c r="B179" s="26"/>
       <c r="C179" s="3"/>
-      <c r="D179" s="36"/>
+      <c r="D179" s="26"/>
       <c r="E179" s="3"/>
     </row>
     <row r="180" spans="1:5">
-      <c r="A180" s="36">
+      <c r="A180" s="26">
         <v>179</v>
       </c>
-      <c r="B180" s="36"/>
+      <c r="B180" s="26"/>
       <c r="C180" s="3"/>
-      <c r="D180" s="36"/>
+      <c r="D180" s="26"/>
       <c r="E180" s="3"/>
     </row>
     <row r="181" spans="1:5">
-      <c r="A181" s="36">
+      <c r="A181" s="26">
         <v>180</v>
       </c>
-      <c r="B181" s="36"/>
+      <c r="B181" s="26"/>
       <c r="C181" s="3"/>
-      <c r="D181" s="36"/>
+      <c r="D181" s="26"/>
       <c r="E181" s="3"/>
     </row>
     <row r="182" spans="1:5">
-      <c r="A182" s="36">
+      <c r="A182" s="26">
         <v>181</v>
       </c>
-      <c r="B182" s="36"/>
+      <c r="B182" s="26"/>
       <c r="C182" s="3"/>
-      <c r="D182" s="36"/>
+      <c r="D182" s="26"/>
       <c r="E182" s="3"/>
     </row>
     <row r="183" spans="1:5">
-      <c r="A183" s="36">
+      <c r="A183" s="26">
         <v>182</v>
       </c>
-      <c r="B183" s="36"/>
+      <c r="B183" s="26"/>
       <c r="C183" s="3"/>
-      <c r="D183" s="36"/>
+      <c r="D183" s="26"/>
       <c r="E183" s="3"/>
     </row>
     <row r="184" spans="1:5">
-      <c r="A184" s="36">
+      <c r="A184" s="26">
         <v>183</v>
       </c>
-      <c r="B184" s="36"/>
+      <c r="B184" s="26"/>
       <c r="C184" s="3"/>
-      <c r="D184" s="36"/>
+      <c r="D184" s="26"/>
       <c r="E184" s="3"/>
     </row>
     <row r="185" spans="1:5">
-      <c r="A185" s="36">
+      <c r="A185" s="26">
         <v>184</v>
       </c>
-      <c r="B185" s="36"/>
+      <c r="B185" s="26"/>
       <c r="C185" s="3"/>
-      <c r="D185" s="36"/>
+      <c r="D185" s="26"/>
       <c r="E185" s="3"/>
     </row>
     <row r="186" spans="1:5">
-      <c r="A186" s="36">
+      <c r="A186" s="26">
         <v>185</v>
       </c>
-      <c r="B186" s="36"/>
+      <c r="B186" s="26"/>
       <c r="C186" s="3"/>
-      <c r="D186" s="36"/>
+      <c r="D186" s="26"/>
       <c r="E186" s="3"/>
     </row>
     <row r="187" spans="1:5">
-      <c r="A187" s="36">
+      <c r="A187" s="26">
         <v>186</v>
       </c>
-      <c r="B187" s="36"/>
+      <c r="B187" s="26"/>
       <c r="C187" s="3"/>
-      <c r="D187" s="36"/>
+      <c r="D187" s="26"/>
       <c r="E187" s="3"/>
     </row>
     <row r="188" spans="1:5">
-      <c r="A188" s="36">
+      <c r="A188" s="26">
         <v>187</v>
       </c>
-      <c r="B188" s="36"/>
+      <c r="B188" s="26"/>
       <c r="C188" s="3"/>
-      <c r="D188" s="36"/>
+      <c r="D188" s="26"/>
       <c r="E188" s="3"/>
     </row>
     <row r="189" spans="1:5">
-      <c r="A189" s="36">
+      <c r="A189" s="26">
         <v>188</v>
       </c>
-      <c r="B189" s="36"/>
+      <c r="B189" s="26"/>
       <c r="C189" s="3"/>
-      <c r="D189" s="36"/>
+      <c r="D189" s="26"/>
       <c r="E189" s="3"/>
     </row>
     <row r="190" spans="1:5">
-      <c r="A190" s="36">
+      <c r="A190" s="26">
         <v>189</v>
       </c>
-      <c r="B190" s="36"/>
+      <c r="B190" s="26"/>
       <c r="C190" s="3"/>
-      <c r="D190" s="36"/>
+      <c r="D190" s="26"/>
       <c r="E190" s="3"/>
     </row>
     <row r="191" spans="1:5">
-      <c r="A191" s="36">
+      <c r="A191" s="26">
         <v>190</v>
       </c>
-      <c r="B191" s="36"/>
+      <c r="B191" s="26"/>
       <c r="C191" s="3"/>
-      <c r="D191" s="36"/>
+      <c r="D191" s="26"/>
       <c r="E191" s="3"/>
     </row>
     <row r="192" spans="1:5">
-      <c r="A192" s="36">
+      <c r="A192" s="26">
         <v>191</v>
       </c>
-      <c r="B192" s="36"/>
+      <c r="B192" s="26"/>
       <c r="C192" s="3"/>
-      <c r="D192" s="36"/>
+      <c r="D192" s="26"/>
       <c r="E192" s="3"/>
     </row>
     <row r="193" spans="1:5">
-      <c r="A193" s="36">
+      <c r="A193" s="26">
         <v>192</v>
       </c>
-      <c r="B193" s="36"/>
+      <c r="B193" s="26"/>
       <c r="C193" s="3"/>
-      <c r="D193" s="36"/>
+      <c r="D193" s="26"/>
       <c r="E193" s="3"/>
     </row>
     <row r="194" spans="1:5">
-      <c r="A194" s="36">
+      <c r="A194" s="26">
         <v>193</v>
       </c>
-      <c r="B194" s="36"/>
+      <c r="B194" s="26"/>
       <c r="C194" s="3"/>
-      <c r="D194" s="36"/>
+      <c r="D194" s="26"/>
       <c r="E194" s="3"/>
     </row>
     <row r="195" spans="1:5">
-      <c r="A195" s="36">
+      <c r="A195" s="26">
         <v>194</v>
       </c>
-      <c r="B195" s="36"/>
+      <c r="B195" s="26"/>
       <c r="C195" s="3"/>
-      <c r="D195" s="36"/>
+      <c r="D195" s="26"/>
       <c r="E195" s="3"/>
     </row>
     <row r="196" spans="1:5">
-      <c r="A196" s="36">
+      <c r="A196" s="26">
         <v>195</v>
       </c>
-      <c r="B196" s="36"/>
+      <c r="B196" s="26"/>
       <c r="C196" s="3"/>
-      <c r="D196" s="36"/>
+      <c r="D196" s="26"/>
       <c r="E196" s="3"/>
     </row>
     <row r="197" spans="1:5">
-      <c r="A197" s="36">
+      <c r="A197" s="26">
         <v>196</v>
       </c>
-      <c r="B197" s="36"/>
+      <c r="B197" s="26"/>
       <c r="C197" s="3"/>
-      <c r="D197" s="36"/>
+      <c r="D197" s="26"/>
       <c r="E197" s="3"/>
     </row>
     <row r="198" spans="1:5">
-      <c r="A198" s="36">
+      <c r="A198" s="26">
         <v>197</v>
       </c>
-      <c r="B198" s="36"/>
+      <c r="B198" s="26"/>
       <c r="C198" s="3"/>
-      <c r="D198" s="36"/>
+      <c r="D198" s="26"/>
       <c r="E198" s="3"/>
     </row>
     <row r="199" spans="1:5">
-      <c r="A199" s="36">
+      <c r="A199" s="26">
         <v>198</v>
       </c>
-      <c r="B199" s="36"/>
+      <c r="B199" s="26"/>
       <c r="C199" s="3"/>
-      <c r="D199" s="36"/>
+      <c r="D199" s="26"/>
       <c r="E199" s="3"/>
     </row>
     <row r="200" spans="1:5">
-      <c r="A200" s="36">
+      <c r="A200" s="26">
         <v>199</v>
       </c>
-      <c r="B200" s="36"/>
+      <c r="B200" s="26"/>
       <c r="C200" s="3"/>
-      <c r="D200" s="36"/>
+      <c r="D200" s="26"/>
       <c r="E200" s="3"/>
     </row>
     <row r="201" spans="1:5">
-      <c r="A201" s="36">
+      <c r="A201" s="26">
         <v>200</v>
       </c>
-      <c r="B201" s="36"/>
+      <c r="B201" s="26"/>
       <c r="C201" s="3"/>
-      <c r="D201" s="36"/>
+      <c r="D201" s="26"/>
       <c r="E201" s="3"/>
     </row>
     <row r="202" spans="1:5">
-      <c r="A202" s="36">
+      <c r="A202" s="26">
         <v>201</v>
       </c>
-      <c r="B202" s="36"/>
+      <c r="B202" s="26"/>
       <c r="C202" s="3"/>
-      <c r="D202" s="36"/>
+      <c r="D202" s="26"/>
       <c r="E202" s="3"/>
     </row>
     <row r="203" spans="1:5">
-      <c r="A203" s="36">
+      <c r="A203" s="26">
         <v>202</v>
       </c>
-      <c r="B203" s="36"/>
+      <c r="B203" s="26"/>
       <c r="C203" s="3"/>
-      <c r="D203" s="36"/>
+      <c r="D203" s="26"/>
       <c r="E203" s="3"/>
     </row>
     <row r="204" spans="1:5">
-      <c r="A204" s="36">
+      <c r="A204" s="26">
         <v>203</v>
       </c>
-      <c r="B204" s="36"/>
+      <c r="B204" s="26"/>
       <c r="C204" s="3"/>
-      <c r="D204" s="36"/>
+      <c r="D204" s="26"/>
       <c r="E204" s="3"/>
     </row>
     <row r="205" spans="1:5">
-      <c r="A205" s="36">
+      <c r="A205" s="26">
         <v>204</v>
       </c>
-      <c r="B205" s="36"/>
+      <c r="B205" s="26"/>
       <c r="C205" s="3"/>
-      <c r="D205" s="36"/>
+      <c r="D205" s="26"/>
       <c r="E205" s="3"/>
     </row>
     <row r="206" spans="1:5">
-      <c r="A206" s="36">
+      <c r="A206" s="26">
         <v>205</v>
       </c>
-      <c r="B206" s="36"/>
+      <c r="B206" s="26"/>
       <c r="C206" s="3"/>
-      <c r="D206" s="36"/>
+      <c r="D206" s="26"/>
       <c r="E206" s="3"/>
     </row>
     <row r="207" spans="1:5">
-      <c r="A207" s="36">
+      <c r="A207" s="26">
         <v>206</v>
       </c>
-      <c r="B207" s="36"/>
+      <c r="B207" s="26"/>
       <c r="C207" s="3"/>
-      <c r="D207" s="36"/>
+      <c r="D207" s="26"/>
       <c r="E207" s="3"/>
     </row>
     <row r="208" spans="1:5">
-      <c r="A208" s="36">
+      <c r="A208" s="26">
         <v>207</v>
       </c>
-      <c r="B208" s="36"/>
+      <c r="B208" s="26"/>
       <c r="C208" s="3"/>
-      <c r="D208" s="36"/>
+      <c r="D208" s="26"/>
       <c r="E208" s="3"/>
     </row>
     <row r="209" spans="1:5">
-      <c r="A209" s="36">
+      <c r="A209" s="26">
         <v>208</v>
       </c>
-      <c r="B209" s="36"/>
+      <c r="B209" s="26"/>
       <c r="C209" s="3"/>
-      <c r="D209" s="36"/>
+      <c r="D209" s="26"/>
       <c r="E209" s="3"/>
     </row>
     <row r="210" spans="1:5">
-      <c r="A210" s="36">
+      <c r="A210" s="26">
         <v>209</v>
       </c>
-      <c r="B210" s="36"/>
+      <c r="B210" s="26"/>
       <c r="C210" s="3"/>
-      <c r="D210" s="36"/>
+      <c r="D210" s="26"/>
       <c r="E210" s="3"/>
     </row>
     <row r="211" spans="1:5">
-      <c r="A211" s="36">
+      <c r="A211" s="26">
         <v>210</v>
       </c>
-      <c r="B211" s="36"/>
+      <c r="B211" s="26"/>
       <c r="C211" s="3"/>
-      <c r="D211" s="36"/>
+      <c r="D211" s="26"/>
       <c r="E211" s="3"/>
     </row>
     <row r="212" spans="1:5">
-      <c r="A212" s="36">
+      <c r="A212" s="26">
         <v>211</v>
       </c>
-      <c r="B212" s="36"/>
+      <c r="B212" s="26"/>
       <c r="C212" s="3"/>
-      <c r="D212" s="36"/>
+      <c r="D212" s="26"/>
       <c r="E212" s="3"/>
     </row>
     <row r="213" spans="1:5">
-      <c r="A213" s="36">
+      <c r="A213" s="26">
         <v>212</v>
       </c>
-      <c r="B213" s="36"/>
+      <c r="B213" s="26"/>
       <c r="C213" s="3"/>
-      <c r="D213" s="36"/>
+      <c r="D213" s="26"/>
       <c r="E213" s="3"/>
     </row>
     <row r="214" spans="1:5">
-      <c r="A214" s="36">
+      <c r="A214" s="26">
         <v>213</v>
       </c>
-      <c r="B214" s="36"/>
+      <c r="B214" s="26"/>
       <c r="C214" s="3"/>
-      <c r="D214" s="36"/>
+      <c r="D214" s="26"/>
       <c r="E214" s="3"/>
     </row>
     <row r="215" spans="1:5">
-      <c r="A215" s="36">
+      <c r="A215" s="26">
         <v>214</v>
       </c>
-      <c r="B215" s="36"/>
+      <c r="B215" s="26"/>
       <c r="C215" s="3"/>
-      <c r="D215" s="36"/>
+      <c r="D215" s="26"/>
       <c r="E215" s="3"/>
     </row>
     <row r="216" spans="1:5">
-      <c r="A216" s="36">
+      <c r="A216" s="26">
         <v>215</v>
       </c>
-      <c r="B216" s="36"/>
+      <c r="B216" s="26"/>
       <c r="C216" s="3"/>
-      <c r="D216" s="36"/>
+      <c r="D216" s="26"/>
       <c r="E216" s="3"/>
     </row>
     <row r="217" spans="1:5">
-      <c r="A217" s="36">
+      <c r="A217" s="26">
         <v>216</v>
       </c>
-      <c r="B217" s="36"/>
+      <c r="B217" s="26"/>
       <c r="C217" s="3"/>
-      <c r="D217" s="36"/>
+      <c r="D217" s="26"/>
       <c r="E217" s="3"/>
     </row>
     <row r="218" spans="1:5">
-      <c r="A218" s="36">
+      <c r="A218" s="26">
         <v>217</v>
       </c>
-      <c r="B218" s="36"/>
+      <c r="B218" s="26"/>
       <c r="C218" s="3"/>
-      <c r="D218" s="36"/>
+      <c r="D218" s="26"/>
       <c r="E218" s="3"/>
     </row>
     <row r="219" spans="1:5">
-      <c r="A219" s="36">
+      <c r="A219" s="26">
         <v>218</v>
       </c>
-      <c r="B219" s="36"/>
+      <c r="B219" s="26"/>
       <c r="C219" s="3"/>
-      <c r="D219" s="36"/>
+      <c r="D219" s="26"/>
       <c r="E219" s="3"/>
     </row>
     <row r="220" spans="1:5">
-      <c r="A220" s="36">
+      <c r="A220" s="26">
         <v>219</v>
       </c>
-      <c r="B220" s="36"/>
+      <c r="B220" s="26"/>
       <c r="C220" s="3"/>
-      <c r="D220" s="36"/>
+      <c r="D220" s="26"/>
       <c r="E220" s="3"/>
     </row>
     <row r="221" spans="1:5">
-      <c r="A221" s="36">
+      <c r="A221" s="26">
         <v>220</v>
       </c>
-      <c r="B221" s="36"/>
+      <c r="B221" s="26"/>
       <c r="C221" s="3"/>
-      <c r="D221" s="36"/>
+      <c r="D221" s="26"/>
       <c r="E221" s="3"/>
     </row>
   </sheetData>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4069C655-AAF4-483F-9E07-507671A7DE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDBF346-C711-40BA-AB8E-844B4D3AFF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="リスト" sheetId="1" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="396">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -1803,6 +1803,74 @@
   </si>
   <si>
     <t>しゃ～ない</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>なんでやねん</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>せやねん</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ほんまかいな</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ちゃうねん</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>めっちゃ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>めんどくさっ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ほかす</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>なおす</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>こすい</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>しんどい</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>いてまう</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ほな</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>あかん</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>えらい</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>どつくぞ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>しばくぞ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>よろしゅう</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2039,7 +2107,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2115,6 +2183,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2145,12 +2219,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2542,41 +2611,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="22.5">
-      <c r="A1" s="32"/>
-      <c r="B1" s="36" t="s">
+      <c r="A1" s="34"/>
+      <c r="B1" s="38" t="s">
         <v>273</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
     </row>
     <row r="2" spans="1:35" ht="22.5">
-      <c r="A2" s="33"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="30"/>
+      <c r="A2" s="35"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="32"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="e" vm="1">
         <v>#VALUE!</v>
@@ -2621,9 +2690,9 @@
       <c r="AI2" s="5"/>
     </row>
     <row r="3" spans="1:35" s="13" customFormat="1" ht="109.5" thickBot="1">
-      <c r="A3" s="34"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="31"/>
+      <c r="A3" s="36"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="33"/>
       <c r="D3" s="11" t="s">
         <v>122</v>
       </c>
@@ -2762,7 +2831,7 @@
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
-      <c r="AE4" s="39"/>
+      <c r="AE4" s="29"/>
       <c r="AF4" s="1"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="1"/>
@@ -2817,7 +2886,7 @@
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
-      <c r="AE5" s="39"/>
+      <c r="AE5" s="29"/>
       <c r="AF5" s="1"/>
       <c r="AG5" s="1"/>
       <c r="AH5" s="1"/>
@@ -2862,7 +2931,7 @@
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
-      <c r="AE6" s="39"/>
+      <c r="AE6" s="29"/>
       <c r="AF6" s="1"/>
       <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
@@ -2903,7 +2972,7 @@
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
-      <c r="AE7" s="39"/>
+      <c r="AE7" s="29"/>
       <c r="AF7" s="1"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
@@ -2946,7 +3015,7 @@
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
-      <c r="AE8" s="39"/>
+      <c r="AE8" s="29"/>
       <c r="AF8" s="1"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="1"/>
@@ -2987,7 +3056,7 @@
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
-      <c r="AE9" s="39"/>
+      <c r="AE9" s="29"/>
       <c r="AF9" s="1"/>
       <c r="AG9" s="1"/>
       <c r="AH9" s="1"/>
@@ -3028,7 +3097,7 @@
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
-      <c r="AE10" s="39"/>
+      <c r="AE10" s="29"/>
       <c r="AF10" s="1"/>
       <c r="AG10" s="1"/>
       <c r="AH10" s="1"/>
@@ -3073,7 +3142,7 @@
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
-      <c r="AE11" s="39"/>
+      <c r="AE11" s="29"/>
       <c r="AF11" s="1"/>
       <c r="AG11" s="1"/>
       <c r="AH11" s="1"/>
@@ -3114,7 +3183,7 @@
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
-      <c r="AE12" s="39"/>
+      <c r="AE12" s="29"/>
       <c r="AF12" s="1"/>
       <c r="AG12" s="1"/>
       <c r="AH12" s="1"/>
@@ -3155,7 +3224,7 @@
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
       <c r="AD13" s="1"/>
-      <c r="AE13" s="39"/>
+      <c r="AE13" s="29"/>
       <c r="AF13" s="1"/>
       <c r="AG13" s="1"/>
       <c r="AH13" s="1"/>
@@ -3196,7 +3265,7 @@
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
-      <c r="AE14" s="39"/>
+      <c r="AE14" s="29"/>
       <c r="AF14" s="1"/>
       <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>
@@ -3237,7 +3306,7 @@
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
       <c r="AD15" s="1"/>
-      <c r="AE15" s="39"/>
+      <c r="AE15" s="29"/>
       <c r="AF15" s="1"/>
       <c r="AG15" s="1"/>
       <c r="AH15" s="1"/>
@@ -3278,7 +3347,7 @@
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
-      <c r="AE16" s="39"/>
+      <c r="AE16" s="29"/>
       <c r="AF16" s="1"/>
       <c r="AG16" s="1"/>
       <c r="AH16" s="1"/>
@@ -3319,7 +3388,7 @@
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
       <c r="AD17" s="1"/>
-      <c r="AE17" s="39"/>
+      <c r="AE17" s="29"/>
       <c r="AF17" s="1"/>
       <c r="AG17" s="1"/>
       <c r="AH17" s="1"/>
@@ -3362,7 +3431,7 @@
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
-      <c r="AE18" s="39"/>
+      <c r="AE18" s="29"/>
       <c r="AF18" s="1"/>
       <c r="AG18" s="1"/>
       <c r="AH18" s="1"/>
@@ -3403,7 +3472,7 @@
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
-      <c r="AE19" s="39"/>
+      <c r="AE19" s="29"/>
       <c r="AF19" s="1"/>
       <c r="AG19" s="1"/>
       <c r="AH19" s="1"/>
@@ -3444,7 +3513,7 @@
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
-      <c r="AE20" s="39"/>
+      <c r="AE20" s="29"/>
       <c r="AF20" s="1"/>
       <c r="AG20" s="1"/>
       <c r="AH20" s="1"/>
@@ -3485,7 +3554,7 @@
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
-      <c r="AE21" s="39"/>
+      <c r="AE21" s="29"/>
       <c r="AF21" s="1"/>
       <c r="AG21" s="1"/>
       <c r="AH21" s="1"/>
@@ -3528,7 +3597,7 @@
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
       <c r="AD22" s="1"/>
-      <c r="AE22" s="39"/>
+      <c r="AE22" s="29"/>
       <c r="AF22" s="1"/>
       <c r="AG22" s="1"/>
       <c r="AH22" s="1"/>
@@ -3569,7 +3638,7 @@
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
       <c r="AD23" s="1"/>
-      <c r="AE23" s="39"/>
+      <c r="AE23" s="29"/>
       <c r="AF23" s="1"/>
       <c r="AG23" s="1"/>
       <c r="AH23" s="1"/>
@@ -3612,7 +3681,7 @@
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
-      <c r="AE24" s="39"/>
+      <c r="AE24" s="29"/>
       <c r="AF24" s="1"/>
       <c r="AG24" s="1"/>
       <c r="AH24" s="1"/>
@@ -3655,7 +3724,7 @@
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
-      <c r="AE25" s="39"/>
+      <c r="AE25" s="29"/>
       <c r="AF25" s="1"/>
       <c r="AG25" s="1"/>
       <c r="AH25" s="1"/>
@@ -3696,7 +3765,7 @@
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
       <c r="AD26" s="1"/>
-      <c r="AE26" s="39"/>
+      <c r="AE26" s="29"/>
       <c r="AF26" s="1"/>
       <c r="AG26" s="1"/>
       <c r="AH26" s="1"/>
@@ -3739,7 +3808,7 @@
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
       <c r="AD27" s="1"/>
-      <c r="AE27" s="39"/>
+      <c r="AE27" s="29"/>
       <c r="AF27" s="1"/>
       <c r="AG27" s="1"/>
       <c r="AH27" s="1"/>
@@ -3780,7 +3849,7 @@
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
       <c r="AD28" s="1"/>
-      <c r="AE28" s="39"/>
+      <c r="AE28" s="29"/>
       <c r="AF28" s="1"/>
       <c r="AG28" s="1"/>
       <c r="AH28" s="1"/>
@@ -3821,7 +3890,7 @@
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
-      <c r="AE29" s="39"/>
+      <c r="AE29" s="29"/>
       <c r="AF29" s="1"/>
       <c r="AG29" s="1"/>
       <c r="AH29" s="1"/>
@@ -3864,7 +3933,7 @@
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
-      <c r="AE30" s="39"/>
+      <c r="AE30" s="29"/>
       <c r="AF30" s="1"/>
       <c r="AG30" s="1"/>
       <c r="AH30" s="1"/>
@@ -3911,7 +3980,7 @@
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
       <c r="AD31" s="1"/>
-      <c r="AE31" s="39"/>
+      <c r="AE31" s="29"/>
       <c r="AF31" s="1"/>
       <c r="AG31" s="1"/>
       <c r="AH31" s="1"/>
@@ -3954,7 +4023,7 @@
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
       <c r="AD32" s="1"/>
-      <c r="AE32" s="39"/>
+      <c r="AE32" s="29"/>
       <c r="AF32" s="1"/>
       <c r="AG32" s="1"/>
       <c r="AH32" s="1"/>
@@ -3995,7 +4064,7 @@
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
       <c r="AD33" s="1"/>
-      <c r="AE33" s="39"/>
+      <c r="AE33" s="29"/>
       <c r="AF33" s="1"/>
       <c r="AG33" s="1"/>
       <c r="AH33" s="1"/>
@@ -4036,7 +4105,7 @@
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
-      <c r="AE34" s="39"/>
+      <c r="AE34" s="29"/>
       <c r="AF34" s="1"/>
       <c r="AG34" s="1"/>
       <c r="AH34" s="1"/>
@@ -4077,7 +4146,7 @@
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
       <c r="AD35" s="1"/>
-      <c r="AE35" s="39"/>
+      <c r="AE35" s="29"/>
       <c r="AF35" s="1"/>
       <c r="AG35" s="1"/>
       <c r="AH35" s="1"/>
@@ -4118,7 +4187,7 @@
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
       <c r="AD36" s="1"/>
-      <c r="AE36" s="39"/>
+      <c r="AE36" s="29"/>
       <c r="AF36" s="1"/>
       <c r="AG36" s="1"/>
       <c r="AH36" s="1"/>
@@ -4159,7 +4228,7 @@
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
-      <c r="AE37" s="39"/>
+      <c r="AE37" s="29"/>
       <c r="AF37" s="1"/>
       <c r="AG37" s="1"/>
       <c r="AH37" s="1"/>
@@ -4200,7 +4269,7 @@
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
-      <c r="AE38" s="39"/>
+      <c r="AE38" s="29"/>
       <c r="AF38" s="1"/>
       <c r="AG38" s="1"/>
       <c r="AH38" s="1"/>
@@ -4243,7 +4312,7 @@
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
       <c r="AD39" s="1"/>
-      <c r="AE39" s="39"/>
+      <c r="AE39" s="29"/>
       <c r="AF39" s="1"/>
       <c r="AG39" s="1"/>
       <c r="AH39" s="1"/>
@@ -4286,7 +4355,7 @@
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
-      <c r="AE40" s="39"/>
+      <c r="AE40" s="29"/>
       <c r="AF40" s="1"/>
       <c r="AG40" s="1"/>
       <c r="AH40" s="1"/>
@@ -4329,7 +4398,7 @@
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
       <c r="AD41" s="1"/>
-      <c r="AE41" s="39"/>
+      <c r="AE41" s="29"/>
       <c r="AF41" s="1"/>
       <c r="AG41" s="1"/>
       <c r="AH41" s="1"/>
@@ -4370,7 +4439,7 @@
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
       <c r="AD42" s="1"/>
-      <c r="AE42" s="39"/>
+      <c r="AE42" s="29"/>
       <c r="AF42" s="1"/>
       <c r="AG42" s="1"/>
       <c r="AH42" s="1"/>
@@ -4413,7 +4482,7 @@
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
       <c r="AD43" s="1"/>
-      <c r="AE43" s="39"/>
+      <c r="AE43" s="29"/>
       <c r="AF43" s="1"/>
       <c r="AG43" s="1"/>
       <c r="AH43" s="1"/>
@@ -4454,7 +4523,7 @@
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
-      <c r="AE44" s="39"/>
+      <c r="AE44" s="29"/>
       <c r="AF44" s="1"/>
       <c r="AG44" s="1"/>
       <c r="AH44" s="1"/>
@@ -4495,7 +4564,7 @@
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
       <c r="AD45" s="1"/>
-      <c r="AE45" s="39"/>
+      <c r="AE45" s="29"/>
       <c r="AF45" s="1"/>
       <c r="AG45" s="1"/>
       <c r="AH45" s="1"/>
@@ -4536,7 +4605,7 @@
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
-      <c r="AE46" s="39"/>
+      <c r="AE46" s="29"/>
       <c r="AF46" s="1"/>
       <c r="AG46" s="1"/>
       <c r="AH46" s="1"/>
@@ -4577,7 +4646,7 @@
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
       <c r="AD47" s="1"/>
-      <c r="AE47" s="39"/>
+      <c r="AE47" s="29"/>
       <c r="AF47" s="1"/>
       <c r="AG47" s="1"/>
       <c r="AH47" s="1"/>
@@ -4620,7 +4689,7 @@
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
       <c r="AD48" s="1"/>
-      <c r="AE48" s="39"/>
+      <c r="AE48" s="29"/>
       <c r="AF48" s="1"/>
       <c r="AG48" s="1"/>
       <c r="AH48" s="1"/>
@@ -4661,7 +4730,7 @@
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
       <c r="AD49" s="1"/>
-      <c r="AE49" s="39"/>
+      <c r="AE49" s="29"/>
       <c r="AF49" s="1"/>
       <c r="AG49" s="1"/>
       <c r="AH49" s="1"/>
@@ -4704,7 +4773,7 @@
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
-      <c r="AE50" s="39"/>
+      <c r="AE50" s="29"/>
       <c r="AF50" s="1"/>
       <c r="AG50" s="1"/>
       <c r="AH50" s="1"/>
@@ -4745,7 +4814,7 @@
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
-      <c r="AE51" s="39"/>
+      <c r="AE51" s="29"/>
       <c r="AF51" s="1"/>
       <c r="AG51" s="1"/>
       <c r="AH51" s="1"/>
@@ -4786,7 +4855,7 @@
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
-      <c r="AE52" s="39"/>
+      <c r="AE52" s="29"/>
       <c r="AF52" s="1"/>
       <c r="AG52" s="1"/>
       <c r="AH52" s="1"/>
@@ -4827,7 +4896,7 @@
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
       <c r="AD53" s="1"/>
-      <c r="AE53" s="39"/>
+      <c r="AE53" s="29"/>
       <c r="AF53" s="1"/>
       <c r="AG53" s="1"/>
       <c r="AH53" s="1"/>
@@ -4870,7 +4939,7 @@
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
-      <c r="AE54" s="39"/>
+      <c r="AE54" s="29"/>
       <c r="AF54" s="1"/>
       <c r="AG54" s="1"/>
       <c r="AH54" s="1"/>
@@ -4913,7 +4982,7 @@
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
       <c r="AD55" s="1"/>
-      <c r="AE55" s="39"/>
+      <c r="AE55" s="29"/>
       <c r="AF55" s="1"/>
       <c r="AG55" s="1"/>
       <c r="AH55" s="1"/>
@@ -4954,7 +5023,7 @@
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
-      <c r="AE56" s="39"/>
+      <c r="AE56" s="29"/>
       <c r="AF56" s="1"/>
       <c r="AG56" s="1"/>
       <c r="AH56" s="1"/>
@@ -4995,7 +5064,7 @@
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
       <c r="AD57" s="1"/>
-      <c r="AE57" s="39"/>
+      <c r="AE57" s="29"/>
       <c r="AF57" s="1"/>
       <c r="AG57" s="1"/>
       <c r="AH57" s="1"/>
@@ -5036,7 +5105,7 @@
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
       <c r="AD58" s="1"/>
-      <c r="AE58" s="39"/>
+      <c r="AE58" s="29"/>
       <c r="AF58" s="1"/>
       <c r="AG58" s="1"/>
       <c r="AH58" s="1"/>
@@ -5077,7 +5146,7 @@
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
       <c r="AD59" s="1"/>
-      <c r="AE59" s="39"/>
+      <c r="AE59" s="29"/>
       <c r="AF59" s="1"/>
       <c r="AG59" s="1"/>
       <c r="AH59" s="1"/>
@@ -5118,7 +5187,7 @@
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
       <c r="AD60" s="1"/>
-      <c r="AE60" s="39"/>
+      <c r="AE60" s="29"/>
       <c r="AF60" s="1"/>
       <c r="AG60" s="1"/>
       <c r="AH60" s="1"/>
@@ -5159,7 +5228,7 @@
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
       <c r="AD61" s="1"/>
-      <c r="AE61" s="39"/>
+      <c r="AE61" s="29"/>
       <c r="AF61" s="1"/>
       <c r="AG61" s="1"/>
       <c r="AH61" s="1"/>
@@ -5200,7 +5269,7 @@
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
       <c r="AD62" s="1"/>
-      <c r="AE62" s="39"/>
+      <c r="AE62" s="29"/>
       <c r="AF62" s="1"/>
       <c r="AG62" s="1"/>
       <c r="AH62" s="1"/>
@@ -5243,7 +5312,7 @@
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
       <c r="AD63" s="1"/>
-      <c r="AE63" s="39"/>
+      <c r="AE63" s="29"/>
       <c r="AF63" s="1"/>
       <c r="AG63" s="1"/>
       <c r="AH63" s="1"/>
@@ -5288,7 +5357,7 @@
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
       <c r="AD64" s="1"/>
-      <c r="AE64" s="39"/>
+      <c r="AE64" s="29"/>
       <c r="AF64" s="1"/>
       <c r="AG64" s="1"/>
       <c r="AH64" s="1"/>
@@ -5331,7 +5400,7 @@
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
       <c r="AD65" s="1"/>
-      <c r="AE65" s="39"/>
+      <c r="AE65" s="29"/>
       <c r="AF65" s="1"/>
       <c r="AG65" s="1"/>
       <c r="AH65" s="1"/>
@@ -5372,7 +5441,7 @@
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
       <c r="AD66" s="1"/>
-      <c r="AE66" s="39"/>
+      <c r="AE66" s="29"/>
       <c r="AF66" s="1"/>
       <c r="AG66" s="1"/>
       <c r="AH66" s="1"/>
@@ -5417,7 +5486,7 @@
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
       <c r="AD67" s="1"/>
-      <c r="AE67" s="39"/>
+      <c r="AE67" s="29"/>
       <c r="AF67" s="1"/>
       <c r="AG67" s="1"/>
       <c r="AH67" s="1"/>
@@ -5460,7 +5529,7 @@
       <c r="AB68" s="1"/>
       <c r="AC68" s="1"/>
       <c r="AD68" s="1"/>
-      <c r="AE68" s="39"/>
+      <c r="AE68" s="29"/>
       <c r="AF68" s="1"/>
       <c r="AG68" s="1"/>
       <c r="AH68" s="1"/>
@@ -5505,7 +5574,7 @@
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
       <c r="AD69" s="1"/>
-      <c r="AE69" s="39"/>
+      <c r="AE69" s="29"/>
       <c r="AF69" s="1"/>
       <c r="AG69" s="1"/>
       <c r="AH69" s="1"/>
@@ -5548,7 +5617,7 @@
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
       <c r="AD70" s="1"/>
-      <c r="AE70" s="39"/>
+      <c r="AE70" s="29"/>
       <c r="AF70" s="1"/>
       <c r="AG70" s="1"/>
       <c r="AH70" s="1"/>
@@ -5591,7 +5660,7 @@
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
       <c r="AD71" s="1"/>
-      <c r="AE71" s="39"/>
+      <c r="AE71" s="29"/>
       <c r="AF71" s="1"/>
       <c r="AG71" s="1"/>
       <c r="AH71" s="1"/>
@@ -5632,7 +5701,7 @@
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
       <c r="AD72" s="1"/>
-      <c r="AE72" s="39"/>
+      <c r="AE72" s="29"/>
       <c r="AF72" s="1"/>
       <c r="AG72" s="1"/>
       <c r="AH72" s="1"/>
@@ -5673,7 +5742,7 @@
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
       <c r="AD73" s="1"/>
-      <c r="AE73" s="39"/>
+      <c r="AE73" s="29"/>
       <c r="AF73" s="1"/>
       <c r="AG73" s="1"/>
       <c r="AH73" s="1"/>
@@ -5714,7 +5783,7 @@
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
       <c r="AD74" s="1"/>
-      <c r="AE74" s="39"/>
+      <c r="AE74" s="29"/>
       <c r="AF74" s="1"/>
       <c r="AG74" s="1"/>
       <c r="AH74" s="1"/>
@@ -5755,7 +5824,7 @@
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
       <c r="AD75" s="1"/>
-      <c r="AE75" s="39"/>
+      <c r="AE75" s="29"/>
       <c r="AF75" s="1"/>
       <c r="AG75" s="1"/>
       <c r="AH75" s="1"/>
@@ -5800,7 +5869,7 @@
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
       <c r="AD76" s="1"/>
-      <c r="AE76" s="39"/>
+      <c r="AE76" s="29"/>
       <c r="AF76" s="1"/>
       <c r="AG76" s="1"/>
       <c r="AH76" s="1"/>
@@ -5843,7 +5912,7 @@
       <c r="AB77" s="1"/>
       <c r="AC77" s="1"/>
       <c r="AD77" s="1"/>
-      <c r="AE77" s="39"/>
+      <c r="AE77" s="29"/>
       <c r="AF77" s="1"/>
       <c r="AG77" s="1"/>
       <c r="AH77" s="1"/>
@@ -5886,7 +5955,7 @@
       <c r="AB78" s="1"/>
       <c r="AC78" s="1"/>
       <c r="AD78" s="1"/>
-      <c r="AE78" s="39"/>
+      <c r="AE78" s="29"/>
       <c r="AF78" s="1"/>
       <c r="AG78" s="1"/>
       <c r="AH78" s="1"/>
@@ -5929,7 +5998,7 @@
       <c r="AB79" s="1"/>
       <c r="AC79" s="1"/>
       <c r="AD79" s="1"/>
-      <c r="AE79" s="39"/>
+      <c r="AE79" s="29"/>
       <c r="AF79" s="1"/>
       <c r="AG79" s="1"/>
       <c r="AH79" s="1"/>
@@ -5972,7 +6041,7 @@
       <c r="AB80" s="1"/>
       <c r="AC80" s="1"/>
       <c r="AD80" s="1"/>
-      <c r="AE80" s="39"/>
+      <c r="AE80" s="29"/>
       <c r="AF80" s="1"/>
       <c r="AG80" s="1"/>
       <c r="AH80" s="1"/>
@@ -6017,7 +6086,7 @@
       <c r="AB81" s="1"/>
       <c r="AC81" s="1"/>
       <c r="AD81" s="1"/>
-      <c r="AE81" s="39"/>
+      <c r="AE81" s="29"/>
       <c r="AF81" s="1"/>
       <c r="AG81" s="1"/>
       <c r="AH81" s="1"/>
@@ -6062,7 +6131,7 @@
       <c r="AB82" s="1"/>
       <c r="AC82" s="1"/>
       <c r="AD82" s="1"/>
-      <c r="AE82" s="39"/>
+      <c r="AE82" s="29"/>
       <c r="AF82" s="1"/>
       <c r="AG82" s="1"/>
       <c r="AH82" s="1"/>
@@ -6107,7 +6176,7 @@
       <c r="AB83" s="1"/>
       <c r="AC83" s="1"/>
       <c r="AD83" s="1"/>
-      <c r="AE83" s="39"/>
+      <c r="AE83" s="29"/>
       <c r="AF83" s="1"/>
       <c r="AG83" s="1"/>
       <c r="AH83" s="1"/>
@@ -6150,7 +6219,7 @@
       <c r="AB84" s="1"/>
       <c r="AC84" s="1"/>
       <c r="AD84" s="1"/>
-      <c r="AE84" s="39"/>
+      <c r="AE84" s="29"/>
       <c r="AF84" s="1"/>
       <c r="AG84" s="1"/>
       <c r="AH84" s="1"/>
@@ -6191,7 +6260,7 @@
       <c r="AB85" s="1"/>
       <c r="AC85" s="1"/>
       <c r="AD85" s="1"/>
-      <c r="AE85" s="39"/>
+      <c r="AE85" s="29"/>
       <c r="AF85" s="1"/>
       <c r="AG85" s="1"/>
       <c r="AH85" s="1"/>
@@ -6232,7 +6301,7 @@
       <c r="AB86" s="1"/>
       <c r="AC86" s="1"/>
       <c r="AD86" s="1"/>
-      <c r="AE86" s="39"/>
+      <c r="AE86" s="29"/>
       <c r="AF86" s="1"/>
       <c r="AG86" s="1"/>
       <c r="AH86" s="1"/>
@@ -6273,7 +6342,7 @@
       <c r="AB87" s="1"/>
       <c r="AC87" s="1"/>
       <c r="AD87" s="1"/>
-      <c r="AE87" s="39"/>
+      <c r="AE87" s="29"/>
       <c r="AF87" s="1"/>
       <c r="AG87" s="1"/>
       <c r="AH87" s="1"/>
@@ -6316,7 +6385,7 @@
       <c r="AB88" s="1"/>
       <c r="AC88" s="1"/>
       <c r="AD88" s="1"/>
-      <c r="AE88" s="39"/>
+      <c r="AE88" s="29"/>
       <c r="AF88" s="1"/>
       <c r="AG88" s="1"/>
       <c r="AH88" s="1"/>
@@ -6357,7 +6426,7 @@
       <c r="AB89" s="1"/>
       <c r="AC89" s="1"/>
       <c r="AD89" s="1"/>
-      <c r="AE89" s="39"/>
+      <c r="AE89" s="29"/>
       <c r="AF89" s="1"/>
       <c r="AG89" s="1"/>
       <c r="AH89" s="1"/>
@@ -6398,7 +6467,7 @@
       <c r="AB90" s="1"/>
       <c r="AC90" s="1"/>
       <c r="AD90" s="1"/>
-      <c r="AE90" s="39"/>
+      <c r="AE90" s="29"/>
       <c r="AF90" s="1"/>
       <c r="AG90" s="1"/>
       <c r="AH90" s="1"/>
@@ -6441,7 +6510,7 @@
       <c r="AB91" s="1"/>
       <c r="AC91" s="1"/>
       <c r="AD91" s="1"/>
-      <c r="AE91" s="39"/>
+      <c r="AE91" s="29"/>
       <c r="AF91" s="1"/>
       <c r="AG91" s="1"/>
       <c r="AH91" s="1"/>
@@ -6484,7 +6553,7 @@
       <c r="AB92" s="1"/>
       <c r="AC92" s="1"/>
       <c r="AD92" s="1"/>
-      <c r="AE92" s="39"/>
+      <c r="AE92" s="29"/>
       <c r="AF92" s="1"/>
       <c r="AG92" s="1"/>
       <c r="AH92" s="1"/>
@@ -6525,7 +6594,7 @@
       <c r="AB93" s="1"/>
       <c r="AC93" s="1"/>
       <c r="AD93" s="1"/>
-      <c r="AE93" s="39"/>
+      <c r="AE93" s="29"/>
       <c r="AF93" s="1"/>
       <c r="AG93" s="1"/>
       <c r="AH93" s="1"/>
@@ -6566,7 +6635,7 @@
       <c r="AB94" s="1"/>
       <c r="AC94" s="1"/>
       <c r="AD94" s="1"/>
-      <c r="AE94" s="39"/>
+      <c r="AE94" s="29"/>
       <c r="AF94" s="1"/>
       <c r="AG94" s="1"/>
       <c r="AH94" s="1"/>
@@ -6607,7 +6676,7 @@
       <c r="AB95" s="1"/>
       <c r="AC95" s="1"/>
       <c r="AD95" s="1"/>
-      <c r="AE95" s="39"/>
+      <c r="AE95" s="29"/>
       <c r="AF95" s="1"/>
       <c r="AG95" s="1"/>
       <c r="AH95" s="1"/>
@@ -6648,7 +6717,7 @@
       <c r="AB96" s="1"/>
       <c r="AC96" s="1"/>
       <c r="AD96" s="1"/>
-      <c r="AE96" s="39"/>
+      <c r="AE96" s="29"/>
       <c r="AF96" s="1"/>
       <c r="AG96" s="1"/>
       <c r="AH96" s="1"/>
@@ -6689,7 +6758,7 @@
       <c r="AB97" s="1"/>
       <c r="AC97" s="1"/>
       <c r="AD97" s="1"/>
-      <c r="AE97" s="39"/>
+      <c r="AE97" s="29"/>
       <c r="AF97" s="1"/>
       <c r="AG97" s="1"/>
       <c r="AH97" s="1"/>
@@ -6732,7 +6801,7 @@
       <c r="AB98" s="1"/>
       <c r="AC98" s="1"/>
       <c r="AD98" s="1"/>
-      <c r="AE98" s="39"/>
+      <c r="AE98" s="29"/>
       <c r="AF98" s="1"/>
       <c r="AG98" s="1"/>
       <c r="AH98" s="1"/>
@@ -6773,7 +6842,7 @@
       <c r="AB99" s="1"/>
       <c r="AC99" s="1"/>
       <c r="AD99" s="1"/>
-      <c r="AE99" s="39"/>
+      <c r="AE99" s="29"/>
       <c r="AF99" s="1"/>
       <c r="AG99" s="1"/>
       <c r="AH99" s="1"/>
@@ -6814,7 +6883,7 @@
       <c r="AB100" s="1"/>
       <c r="AC100" s="1"/>
       <c r="AD100" s="1"/>
-      <c r="AE100" s="39"/>
+      <c r="AE100" s="29"/>
       <c r="AF100" s="1"/>
       <c r="AG100" s="1"/>
       <c r="AH100" s="1"/>
@@ -6855,7 +6924,7 @@
       <c r="AB101" s="1"/>
       <c r="AC101" s="1"/>
       <c r="AD101" s="1"/>
-      <c r="AE101" s="39"/>
+      <c r="AE101" s="29"/>
       <c r="AF101" s="1"/>
       <c r="AG101" s="1"/>
       <c r="AH101" s="1"/>
@@ -6896,7 +6965,7 @@
       <c r="AB102" s="1"/>
       <c r="AC102" s="1"/>
       <c r="AD102" s="1"/>
-      <c r="AE102" s="39"/>
+      <c r="AE102" s="29"/>
       <c r="AF102" s="1"/>
       <c r="AG102" s="1"/>
       <c r="AH102" s="1"/>
@@ -6937,7 +7006,7 @@
       <c r="AB103" s="1"/>
       <c r="AC103" s="1"/>
       <c r="AD103" s="1"/>
-      <c r="AE103" s="39"/>
+      <c r="AE103" s="29"/>
       <c r="AF103" s="1"/>
       <c r="AG103" s="1"/>
       <c r="AH103" s="1"/>
@@ -6978,7 +7047,7 @@
       <c r="AB104" s="1"/>
       <c r="AC104" s="1"/>
       <c r="AD104" s="1"/>
-      <c r="AE104" s="39"/>
+      <c r="AE104" s="29"/>
       <c r="AF104" s="1"/>
       <c r="AG104" s="1"/>
       <c r="AH104" s="1"/>
@@ -7021,7 +7090,7 @@
       <c r="AB105" s="1"/>
       <c r="AC105" s="1"/>
       <c r="AD105" s="1"/>
-      <c r="AE105" s="39"/>
+      <c r="AE105" s="29"/>
       <c r="AF105" s="1"/>
       <c r="AG105" s="1"/>
       <c r="AH105" s="1"/>
@@ -7062,7 +7131,7 @@
       <c r="AB106" s="1"/>
       <c r="AC106" s="1"/>
       <c r="AD106" s="1"/>
-      <c r="AE106" s="39"/>
+      <c r="AE106" s="29"/>
       <c r="AF106" s="1"/>
       <c r="AG106" s="1"/>
       <c r="AH106" s="1"/>
@@ -7105,7 +7174,7 @@
       <c r="AB107" s="1"/>
       <c r="AC107" s="1"/>
       <c r="AD107" s="1"/>
-      <c r="AE107" s="39"/>
+      <c r="AE107" s="29"/>
       <c r="AF107" s="1"/>
       <c r="AG107" s="1"/>
       <c r="AH107" s="1"/>
@@ -7146,7 +7215,7 @@
       <c r="AB108" s="1"/>
       <c r="AC108" s="1"/>
       <c r="AD108" s="1"/>
-      <c r="AE108" s="39"/>
+      <c r="AE108" s="29"/>
       <c r="AF108" s="1"/>
       <c r="AG108" s="1"/>
       <c r="AH108" s="1"/>
@@ -7189,7 +7258,7 @@
       <c r="AB109" s="1"/>
       <c r="AC109" s="1"/>
       <c r="AD109" s="1"/>
-      <c r="AE109" s="39"/>
+      <c r="AE109" s="29"/>
       <c r="AF109" s="1"/>
       <c r="AG109" s="1"/>
       <c r="AH109" s="1"/>
@@ -7230,7 +7299,7 @@
       <c r="AB110" s="1"/>
       <c r="AC110" s="1"/>
       <c r="AD110" s="1"/>
-      <c r="AE110" s="39"/>
+      <c r="AE110" s="29"/>
       <c r="AF110" s="1"/>
       <c r="AG110" s="1"/>
       <c r="AH110" s="1"/>
@@ -7271,7 +7340,7 @@
       <c r="AB111" s="1"/>
       <c r="AC111" s="1"/>
       <c r="AD111" s="1"/>
-      <c r="AE111" s="39"/>
+      <c r="AE111" s="29"/>
       <c r="AF111" s="1"/>
       <c r="AG111" s="1"/>
       <c r="AH111" s="1"/>
@@ -7318,7 +7387,7 @@
       <c r="AB112" s="1"/>
       <c r="AC112" s="1"/>
       <c r="AD112" s="1"/>
-      <c r="AE112" s="39"/>
+      <c r="AE112" s="29"/>
       <c r="AF112" s="1"/>
       <c r="AG112" s="1"/>
       <c r="AH112" s="1"/>
@@ -7361,7 +7430,7 @@
       <c r="AB113" s="1"/>
       <c r="AC113" s="1"/>
       <c r="AD113" s="1"/>
-      <c r="AE113" s="39"/>
+      <c r="AE113" s="29"/>
       <c r="AF113" s="1"/>
       <c r="AG113" s="1"/>
       <c r="AH113" s="1"/>
@@ -7402,7 +7471,7 @@
       <c r="AB114" s="1"/>
       <c r="AC114" s="1"/>
       <c r="AD114" s="1"/>
-      <c r="AE114" s="39"/>
+      <c r="AE114" s="29"/>
       <c r="AF114" s="1"/>
       <c r="AG114" s="1"/>
       <c r="AH114" s="1"/>
@@ -7445,7 +7514,7 @@
       <c r="AB115" s="1"/>
       <c r="AC115" s="1"/>
       <c r="AD115" s="1"/>
-      <c r="AE115" s="39"/>
+      <c r="AE115" s="29"/>
       <c r="AF115" s="1"/>
       <c r="AG115" s="1"/>
       <c r="AH115" s="1"/>
@@ -7486,7 +7555,7 @@
       <c r="AB116" s="1"/>
       <c r="AC116" s="1"/>
       <c r="AD116" s="1"/>
-      <c r="AE116" s="39"/>
+      <c r="AE116" s="29"/>
       <c r="AF116" s="1"/>
       <c r="AG116" s="1"/>
       <c r="AH116" s="1"/>
@@ -7527,7 +7596,7 @@
       <c r="AB117" s="1"/>
       <c r="AC117" s="1"/>
       <c r="AD117" s="1"/>
-      <c r="AE117" s="39"/>
+      <c r="AE117" s="29"/>
       <c r="AF117" s="1"/>
       <c r="AG117" s="1"/>
       <c r="AH117" s="1"/>
@@ -7568,7 +7637,7 @@
       <c r="AB118" s="1"/>
       <c r="AC118" s="1"/>
       <c r="AD118" s="1"/>
-      <c r="AE118" s="39"/>
+      <c r="AE118" s="29"/>
       <c r="AF118" s="1"/>
       <c r="AG118" s="1"/>
       <c r="AH118" s="1"/>
@@ -7609,7 +7678,7 @@
       <c r="AB119" s="1"/>
       <c r="AC119" s="1"/>
       <c r="AD119" s="1"/>
-      <c r="AE119" s="39"/>
+      <c r="AE119" s="29"/>
       <c r="AF119" s="1"/>
       <c r="AG119" s="1"/>
       <c r="AH119" s="1"/>
@@ -7650,7 +7719,7 @@
       <c r="AB120" s="1"/>
       <c r="AC120" s="1"/>
       <c r="AD120" s="1"/>
-      <c r="AE120" s="39"/>
+      <c r="AE120" s="29"/>
       <c r="AF120" s="1"/>
       <c r="AG120" s="1"/>
       <c r="AH120" s="1"/>
@@ -7691,7 +7760,7 @@
       <c r="AB121" s="1"/>
       <c r="AC121" s="1"/>
       <c r="AD121" s="1"/>
-      <c r="AE121" s="39"/>
+      <c r="AE121" s="29"/>
       <c r="AF121" s="1"/>
       <c r="AG121" s="1"/>
       <c r="AH121" s="1"/>
@@ -7732,7 +7801,7 @@
       <c r="AB122" s="1"/>
       <c r="AC122" s="1"/>
       <c r="AD122" s="1"/>
-      <c r="AE122" s="39"/>
+      <c r="AE122" s="29"/>
       <c r="AF122" s="1"/>
       <c r="AG122" s="1"/>
       <c r="AH122" s="1"/>
@@ -7773,7 +7842,7 @@
       <c r="AB123" s="1"/>
       <c r="AC123" s="1"/>
       <c r="AD123" s="1"/>
-      <c r="AE123" s="39"/>
+      <c r="AE123" s="29"/>
       <c r="AF123" s="1"/>
       <c r="AG123" s="1"/>
       <c r="AH123" s="1"/>
@@ -7814,7 +7883,7 @@
       <c r="AB124" s="1"/>
       <c r="AC124" s="1"/>
       <c r="AD124" s="1"/>
-      <c r="AE124" s="39"/>
+      <c r="AE124" s="29"/>
       <c r="AF124" s="1"/>
       <c r="AG124" s="1"/>
       <c r="AH124" s="1"/>
@@ -7855,7 +7924,7 @@
       <c r="AB125" s="1"/>
       <c r="AC125" s="1"/>
       <c r="AD125" s="1"/>
-      <c r="AE125" s="39"/>
+      <c r="AE125" s="29"/>
       <c r="AF125" s="1"/>
       <c r="AG125" s="1"/>
       <c r="AH125" s="1"/>
@@ -7898,7 +7967,7 @@
       <c r="AB126" s="1"/>
       <c r="AC126" s="1"/>
       <c r="AD126" s="1"/>
-      <c r="AE126" s="39"/>
+      <c r="AE126" s="29"/>
       <c r="AF126" s="1"/>
       <c r="AG126" s="1"/>
       <c r="AH126" s="1"/>
@@ -7939,7 +8008,7 @@
       <c r="AB127" s="1"/>
       <c r="AC127" s="1"/>
       <c r="AD127" s="1"/>
-      <c r="AE127" s="39"/>
+      <c r="AE127" s="29"/>
       <c r="AF127" s="1"/>
       <c r="AG127" s="1"/>
       <c r="AH127" s="1"/>
@@ -7984,7 +8053,7 @@
       <c r="AB128" s="1"/>
       <c r="AC128" s="1"/>
       <c r="AD128" s="1"/>
-      <c r="AE128" s="39"/>
+      <c r="AE128" s="29"/>
       <c r="AF128" s="1"/>
       <c r="AG128" s="1"/>
       <c r="AH128" s="1"/>
@@ -8027,7 +8096,7 @@
       <c r="AB129" s="1"/>
       <c r="AC129" s="1"/>
       <c r="AD129" s="1"/>
-      <c r="AE129" s="39"/>
+      <c r="AE129" s="29"/>
       <c r="AF129" s="1"/>
       <c r="AG129" s="1"/>
       <c r="AH129" s="1"/>
@@ -8072,7 +8141,7 @@
       <c r="AB130" s="1"/>
       <c r="AC130" s="1"/>
       <c r="AD130" s="1"/>
-      <c r="AE130" s="39"/>
+      <c r="AE130" s="29"/>
       <c r="AF130" s="1"/>
       <c r="AG130" s="1"/>
       <c r="AH130" s="1"/>
@@ -8115,7 +8184,7 @@
       <c r="AB131" s="1"/>
       <c r="AC131" s="1"/>
       <c r="AD131" s="1"/>
-      <c r="AE131" s="39"/>
+      <c r="AE131" s="29"/>
       <c r="AF131" s="1"/>
       <c r="AG131" s="1"/>
       <c r="AH131" s="1"/>
@@ -8156,7 +8225,7 @@
       <c r="AB132" s="1"/>
       <c r="AC132" s="1"/>
       <c r="AD132" s="1"/>
-      <c r="AE132" s="39"/>
+      <c r="AE132" s="29"/>
       <c r="AF132" s="1"/>
       <c r="AG132" s="1"/>
       <c r="AH132" s="1"/>
@@ -8197,7 +8266,7 @@
       <c r="AB133" s="1"/>
       <c r="AC133" s="1"/>
       <c r="AD133" s="1"/>
-      <c r="AE133" s="39"/>
+      <c r="AE133" s="29"/>
       <c r="AF133" s="1"/>
       <c r="AG133" s="1"/>
       <c r="AH133" s="1"/>
@@ -8238,7 +8307,7 @@
       <c r="AB134" s="1"/>
       <c r="AC134" s="1"/>
       <c r="AD134" s="1"/>
-      <c r="AE134" s="39"/>
+      <c r="AE134" s="29"/>
       <c r="AF134" s="1"/>
       <c r="AG134" s="1"/>
       <c r="AH134" s="1"/>
@@ -8279,7 +8348,7 @@
       <c r="AB135" s="1"/>
       <c r="AC135" s="1"/>
       <c r="AD135" s="1"/>
-      <c r="AE135" s="39"/>
+      <c r="AE135" s="29"/>
       <c r="AF135" s="1"/>
       <c r="AG135" s="1"/>
       <c r="AH135" s="1"/>
@@ -8320,7 +8389,7 @@
       <c r="AB136" s="1"/>
       <c r="AC136" s="1"/>
       <c r="AD136" s="1"/>
-      <c r="AE136" s="39"/>
+      <c r="AE136" s="29"/>
       <c r="AF136" s="1"/>
       <c r="AG136" s="1"/>
       <c r="AH136" s="1"/>
@@ -8361,7 +8430,7 @@
       <c r="AB137" s="1"/>
       <c r="AC137" s="1"/>
       <c r="AD137" s="1"/>
-      <c r="AE137" s="39"/>
+      <c r="AE137" s="29"/>
       <c r="AF137" s="1"/>
       <c r="AG137" s="1"/>
       <c r="AH137" s="1"/>
@@ -8402,7 +8471,7 @@
       <c r="AB138" s="1"/>
       <c r="AC138" s="1"/>
       <c r="AD138" s="1"/>
-      <c r="AE138" s="39"/>
+      <c r="AE138" s="29"/>
       <c r="AF138" s="1"/>
       <c r="AG138" s="1"/>
       <c r="AH138" s="1"/>
@@ -8443,7 +8512,7 @@
       <c r="AB139" s="1"/>
       <c r="AC139" s="1"/>
       <c r="AD139" s="1"/>
-      <c r="AE139" s="39"/>
+      <c r="AE139" s="29"/>
       <c r="AF139" s="1"/>
       <c r="AG139" s="1"/>
       <c r="AH139" s="1"/>
@@ -8484,7 +8553,7 @@
       <c r="AB140" s="1"/>
       <c r="AC140" s="1"/>
       <c r="AD140" s="1"/>
-      <c r="AE140" s="39"/>
+      <c r="AE140" s="29"/>
       <c r="AF140" s="1"/>
       <c r="AG140" s="1"/>
       <c r="AH140" s="1"/>
@@ -8525,7 +8594,7 @@
       <c r="AB141" s="1"/>
       <c r="AC141" s="1"/>
       <c r="AD141" s="1"/>
-      <c r="AE141" s="39"/>
+      <c r="AE141" s="29"/>
       <c r="AF141" s="1"/>
       <c r="AG141" s="1"/>
       <c r="AH141" s="1"/>
@@ -8566,7 +8635,7 @@
       <c r="AB142" s="1"/>
       <c r="AC142" s="1"/>
       <c r="AD142" s="1"/>
-      <c r="AE142" s="39"/>
+      <c r="AE142" s="29"/>
       <c r="AF142" s="1"/>
       <c r="AG142" s="1"/>
       <c r="AH142" s="1"/>
@@ -8607,7 +8676,7 @@
       <c r="AB143" s="1"/>
       <c r="AC143" s="1"/>
       <c r="AD143" s="1"/>
-      <c r="AE143" s="39"/>
+      <c r="AE143" s="29"/>
       <c r="AF143" s="1"/>
       <c r="AG143" s="1"/>
       <c r="AH143" s="1"/>
@@ -8648,7 +8717,7 @@
       <c r="AB144" s="1"/>
       <c r="AC144" s="1"/>
       <c r="AD144" s="1"/>
-      <c r="AE144" s="39"/>
+      <c r="AE144" s="29"/>
       <c r="AF144" s="1"/>
       <c r="AG144" s="1"/>
       <c r="AH144" s="1"/>
@@ -8689,7 +8758,7 @@
       <c r="AB145" s="1"/>
       <c r="AC145" s="1"/>
       <c r="AD145" s="1"/>
-      <c r="AE145" s="39"/>
+      <c r="AE145" s="29"/>
       <c r="AF145" s="1"/>
       <c r="AG145" s="1"/>
       <c r="AH145" s="1"/>
@@ -8730,7 +8799,7 @@
       <c r="AB146" s="1"/>
       <c r="AC146" s="1"/>
       <c r="AD146" s="1"/>
-      <c r="AE146" s="39"/>
+      <c r="AE146" s="29"/>
       <c r="AF146" s="1"/>
       <c r="AG146" s="1"/>
       <c r="AH146" s="1"/>
@@ -8771,7 +8840,7 @@
       <c r="AB147" s="1"/>
       <c r="AC147" s="1"/>
       <c r="AD147" s="1"/>
-      <c r="AE147" s="39"/>
+      <c r="AE147" s="29"/>
       <c r="AF147" s="1"/>
       <c r="AG147" s="1"/>
       <c r="AH147" s="1"/>
@@ -8814,7 +8883,7 @@
       <c r="AB148" s="1"/>
       <c r="AC148" s="1"/>
       <c r="AD148" s="1"/>
-      <c r="AE148" s="39"/>
+      <c r="AE148" s="29"/>
       <c r="AF148" s="1"/>
       <c r="AG148" s="1"/>
       <c r="AH148" s="1"/>
@@ -8855,7 +8924,7 @@
       <c r="AB149" s="1"/>
       <c r="AC149" s="1"/>
       <c r="AD149" s="1"/>
-      <c r="AE149" s="39"/>
+      <c r="AE149" s="29"/>
       <c r="AF149" s="1"/>
       <c r="AG149" s="1"/>
       <c r="AH149" s="1"/>
@@ -8896,7 +8965,7 @@
       <c r="AB150" s="1"/>
       <c r="AC150" s="1"/>
       <c r="AD150" s="1"/>
-      <c r="AE150" s="39"/>
+      <c r="AE150" s="29"/>
       <c r="AF150" s="1"/>
       <c r="AG150" s="1"/>
       <c r="AH150" s="1"/>
@@ -8937,7 +9006,7 @@
       <c r="AB151" s="1"/>
       <c r="AC151" s="1"/>
       <c r="AD151" s="1"/>
-      <c r="AE151" s="39"/>
+      <c r="AE151" s="29"/>
       <c r="AF151" s="1"/>
       <c r="AG151" s="1"/>
       <c r="AH151" s="1"/>
@@ -8978,7 +9047,7 @@
       <c r="AB152" s="1"/>
       <c r="AC152" s="1"/>
       <c r="AD152" s="1"/>
-      <c r="AE152" s="39"/>
+      <c r="AE152" s="29"/>
       <c r="AF152" s="1"/>
       <c r="AG152" s="1"/>
       <c r="AH152" s="1"/>
@@ -9021,7 +9090,7 @@
       <c r="AB153" s="1"/>
       <c r="AC153" s="1"/>
       <c r="AD153" s="1"/>
-      <c r="AE153" s="39"/>
+      <c r="AE153" s="29"/>
       <c r="AF153" s="1"/>
       <c r="AG153" s="1"/>
       <c r="AH153" s="1"/>
@@ -9064,7 +9133,7 @@
       <c r="AB154" s="1"/>
       <c r="AC154" s="1"/>
       <c r="AD154" s="1"/>
-      <c r="AE154" s="39"/>
+      <c r="AE154" s="29"/>
       <c r="AF154" s="1"/>
       <c r="AG154" s="1"/>
       <c r="AH154" s="1"/>
@@ -9109,7 +9178,7 @@
       <c r="AB155" s="1"/>
       <c r="AC155" s="1"/>
       <c r="AD155" s="1"/>
-      <c r="AE155" s="39"/>
+      <c r="AE155" s="29"/>
       <c r="AF155" s="1"/>
       <c r="AG155" s="1"/>
       <c r="AH155" s="1"/>
@@ -9152,7 +9221,7 @@
       <c r="AB156" s="1"/>
       <c r="AC156" s="1"/>
       <c r="AD156" s="1"/>
-      <c r="AE156" s="39"/>
+      <c r="AE156" s="29"/>
       <c r="AF156" s="1"/>
       <c r="AG156" s="1"/>
       <c r="AH156" s="1"/>
@@ -9195,7 +9264,7 @@
       <c r="AB157" s="1"/>
       <c r="AC157" s="1"/>
       <c r="AD157" s="1"/>
-      <c r="AE157" s="39"/>
+      <c r="AE157" s="29"/>
       <c r="AF157" s="1"/>
       <c r="AG157" s="1"/>
       <c r="AH157" s="1"/>
@@ -9240,7 +9309,7 @@
       <c r="AB158" s="1"/>
       <c r="AC158" s="1"/>
       <c r="AD158" s="1"/>
-      <c r="AE158" s="39"/>
+      <c r="AE158" s="29"/>
       <c r="AF158" s="1"/>
       <c r="AG158" s="1"/>
       <c r="AH158" s="1"/>
@@ -9283,7 +9352,7 @@
       <c r="AB159" s="1"/>
       <c r="AC159" s="1"/>
       <c r="AD159" s="1"/>
-      <c r="AE159" s="39"/>
+      <c r="AE159" s="29"/>
       <c r="AF159" s="1"/>
       <c r="AG159" s="1"/>
       <c r="AH159" s="1"/>
@@ -9328,7 +9397,7 @@
       <c r="AB160" s="1"/>
       <c r="AC160" s="1"/>
       <c r="AD160" s="1"/>
-      <c r="AE160" s="39"/>
+      <c r="AE160" s="29"/>
       <c r="AF160" s="1"/>
       <c r="AG160" s="1"/>
       <c r="AH160" s="1"/>
@@ -9371,7 +9440,7 @@
       <c r="AB161" s="1"/>
       <c r="AC161" s="1"/>
       <c r="AD161" s="1"/>
-      <c r="AE161" s="39"/>
+      <c r="AE161" s="29"/>
       <c r="AF161" s="1"/>
       <c r="AG161" s="1"/>
       <c r="AH161" s="1"/>
@@ -9414,7 +9483,7 @@
       <c r="AB162" s="1"/>
       <c r="AC162" s="1"/>
       <c r="AD162" s="1"/>
-      <c r="AE162" s="39"/>
+      <c r="AE162" s="29"/>
       <c r="AF162" s="1"/>
       <c r="AG162" s="1"/>
       <c r="AH162" s="1"/>
@@ -9459,7 +9528,7 @@
       <c r="AB163" s="1"/>
       <c r="AC163" s="1"/>
       <c r="AD163" s="1"/>
-      <c r="AE163" s="39"/>
+      <c r="AE163" s="29"/>
       <c r="AF163" s="1"/>
       <c r="AG163" s="1"/>
       <c r="AH163" s="1"/>
@@ -9502,7 +9571,7 @@
       <c r="AB164" s="3"/>
       <c r="AC164" s="3"/>
       <c r="AD164" s="3"/>
-      <c r="AE164" s="40"/>
+      <c r="AE164" s="30"/>
       <c r="AF164" s="3"/>
       <c r="AG164" s="3"/>
       <c r="AH164" s="3"/>
@@ -9545,7 +9614,7 @@
       <c r="AB165" s="3"/>
       <c r="AC165" s="3"/>
       <c r="AD165" s="3"/>
-      <c r="AE165" s="40"/>
+      <c r="AE165" s="30"/>
       <c r="AF165" s="3"/>
       <c r="AG165" s="3"/>
       <c r="AH165" s="3"/>
@@ -9586,7 +9655,7 @@
       <c r="AB166" s="1"/>
       <c r="AC166" s="1"/>
       <c r="AD166" s="1"/>
-      <c r="AE166" s="39"/>
+      <c r="AE166" s="29"/>
       <c r="AF166" s="1"/>
       <c r="AG166" s="1"/>
       <c r="AH166" s="1"/>
@@ -9627,7 +9696,7 @@
       <c r="AB167" s="1"/>
       <c r="AC167" s="1"/>
       <c r="AD167" s="1"/>
-      <c r="AE167" s="39"/>
+      <c r="AE167" s="29"/>
       <c r="AF167" s="1"/>
       <c r="AG167" s="1"/>
       <c r="AH167" s="1"/>
@@ -9668,7 +9737,7 @@
       <c r="AB168" s="1"/>
       <c r="AC168" s="1"/>
       <c r="AD168" s="1"/>
-      <c r="AE168" s="39"/>
+      <c r="AE168" s="29"/>
       <c r="AF168" s="1"/>
       <c r="AG168" s="1"/>
       <c r="AH168" s="1"/>
@@ -9709,7 +9778,7 @@
       <c r="AB169" s="1"/>
       <c r="AC169" s="1"/>
       <c r="AD169" s="1"/>
-      <c r="AE169" s="39"/>
+      <c r="AE169" s="29"/>
       <c r="AF169" s="1"/>
       <c r="AG169" s="1"/>
       <c r="AH169" s="1"/>
@@ -9750,7 +9819,7 @@
       <c r="AB170" s="1"/>
       <c r="AC170" s="1"/>
       <c r="AD170" s="1"/>
-      <c r="AE170" s="39"/>
+      <c r="AE170" s="29"/>
       <c r="AF170" s="1"/>
       <c r="AG170" s="1"/>
       <c r="AH170" s="1"/>
@@ -9791,7 +9860,7 @@
       <c r="AB171" s="1"/>
       <c r="AC171" s="1"/>
       <c r="AD171" s="1"/>
-      <c r="AE171" s="39"/>
+      <c r="AE171" s="29"/>
       <c r="AF171" s="1"/>
       <c r="AG171" s="1"/>
       <c r="AH171" s="1"/>
@@ -9834,7 +9903,7 @@
       <c r="AB172" s="1"/>
       <c r="AC172" s="1"/>
       <c r="AD172" s="1"/>
-      <c r="AE172" s="39"/>
+      <c r="AE172" s="29"/>
       <c r="AF172" s="1"/>
       <c r="AG172" s="1"/>
       <c r="AH172" s="1"/>
@@ -9875,7 +9944,7 @@
       <c r="AB173" s="1"/>
       <c r="AC173" s="1"/>
       <c r="AD173" s="1"/>
-      <c r="AE173" s="39"/>
+      <c r="AE173" s="29"/>
       <c r="AF173" s="1"/>
       <c r="AG173" s="1"/>
       <c r="AH173" s="1"/>
@@ -9926,7 +9995,7 @@
       <c r="AB174" s="1"/>
       <c r="AC174" s="1"/>
       <c r="AD174" s="1"/>
-      <c r="AE174" s="39"/>
+      <c r="AE174" s="29"/>
       <c r="AF174" s="1"/>
       <c r="AG174" s="1"/>
       <c r="AH174" s="1"/>
@@ -9973,7 +10042,7 @@
       <c r="AB175" s="1"/>
       <c r="AC175" s="1"/>
       <c r="AD175" s="1"/>
-      <c r="AE175" s="39"/>
+      <c r="AE175" s="29"/>
       <c r="AF175" s="1"/>
       <c r="AG175" s="1"/>
       <c r="AH175" s="1"/>
@@ -10024,7 +10093,7 @@
       <c r="AB176" s="1"/>
       <c r="AC176" s="1"/>
       <c r="AD176" s="1"/>
-      <c r="AE176" s="39"/>
+      <c r="AE176" s="29"/>
       <c r="AF176" s="1"/>
       <c r="AG176" s="1"/>
       <c r="AH176" s="1"/>
@@ -10069,7 +10138,7 @@
       <c r="AB177" s="1"/>
       <c r="AC177" s="1"/>
       <c r="AD177" s="1"/>
-      <c r="AE177" s="39"/>
+      <c r="AE177" s="29"/>
       <c r="AF177" s="1"/>
       <c r="AG177" s="1"/>
       <c r="AH177" s="1"/>
@@ -10114,7 +10183,7 @@
       <c r="AB178" s="1"/>
       <c r="AC178" s="1"/>
       <c r="AD178" s="1"/>
-      <c r="AE178" s="39"/>
+      <c r="AE178" s="29"/>
       <c r="AF178" s="1"/>
       <c r="AG178" s="1"/>
       <c r="AH178" s="1"/>
@@ -10159,7 +10228,7 @@
       <c r="AB179" s="1"/>
       <c r="AC179" s="1"/>
       <c r="AD179" s="1"/>
-      <c r="AE179" s="39"/>
+      <c r="AE179" s="29"/>
       <c r="AF179" s="1"/>
       <c r="AG179" s="1"/>
       <c r="AH179" s="1"/>
@@ -10206,7 +10275,7 @@
       <c r="AB180" s="1"/>
       <c r="AC180" s="1"/>
       <c r="AD180" s="1"/>
-      <c r="AE180" s="39"/>
+      <c r="AE180" s="29"/>
       <c r="AF180" s="1"/>
       <c r="AG180" s="1"/>
       <c r="AH180" s="1"/>
@@ -10251,7 +10320,7 @@
       <c r="AB181" s="1"/>
       <c r="AC181" s="1"/>
       <c r="AD181" s="1"/>
-      <c r="AE181" s="39"/>
+      <c r="AE181" s="29"/>
       <c r="AF181" s="1"/>
       <c r="AG181" s="1"/>
       <c r="AH181" s="1"/>
@@ -10298,7 +10367,7 @@
       <c r="AB182" s="1"/>
       <c r="AC182" s="1"/>
       <c r="AD182" s="1"/>
-      <c r="AE182" s="39"/>
+      <c r="AE182" s="29"/>
       <c r="AF182" s="1"/>
       <c r="AG182" s="1"/>
       <c r="AH182" s="1"/>
@@ -10347,7 +10416,7 @@
       <c r="AB183" s="1"/>
       <c r="AC183" s="1"/>
       <c r="AD183" s="1"/>
-      <c r="AE183" s="39"/>
+      <c r="AE183" s="29"/>
       <c r="AF183" s="1"/>
       <c r="AG183" s="1"/>
       <c r="AH183" s="1"/>
@@ -10396,7 +10465,7 @@
       <c r="AB184" s="1"/>
       <c r="AC184" s="1"/>
       <c r="AD184" s="1"/>
-      <c r="AE184" s="39"/>
+      <c r="AE184" s="29"/>
       <c r="AF184" s="1"/>
       <c r="AG184" s="1"/>
       <c r="AH184" s="1"/>
@@ -10443,7 +10512,7 @@
       <c r="AB185" s="1"/>
       <c r="AC185" s="1"/>
       <c r="AD185" s="1"/>
-      <c r="AE185" s="39"/>
+      <c r="AE185" s="29"/>
       <c r="AF185" s="1"/>
       <c r="AG185" s="1"/>
       <c r="AH185" s="1"/>
@@ -10494,7 +10563,7 @@
       <c r="AB186" s="1"/>
       <c r="AC186" s="1"/>
       <c r="AD186" s="1"/>
-      <c r="AE186" s="39"/>
+      <c r="AE186" s="29"/>
       <c r="AF186" s="1"/>
       <c r="AG186" s="1"/>
       <c r="AH186" s="1"/>
@@ -10545,7 +10614,7 @@
       <c r="AB187" s="1"/>
       <c r="AC187" s="1"/>
       <c r="AD187" s="1"/>
-      <c r="AE187" s="39"/>
+      <c r="AE187" s="29"/>
       <c r="AF187" s="1"/>
       <c r="AG187" s="1"/>
       <c r="AH187" s="1"/>
@@ -10598,7 +10667,7 @@
       <c r="AB188" s="1"/>
       <c r="AC188" s="1"/>
       <c r="AD188" s="1"/>
-      <c r="AE188" s="39"/>
+      <c r="AE188" s="29"/>
       <c r="AF188" s="1"/>
       <c r="AG188" s="1"/>
       <c r="AH188" s="1"/>
@@ -10649,7 +10718,7 @@
       <c r="AB189" s="1"/>
       <c r="AC189" s="1"/>
       <c r="AD189" s="1"/>
-      <c r="AE189" s="39"/>
+      <c r="AE189" s="29"/>
       <c r="AF189" s="1"/>
       <c r="AG189" s="1"/>
       <c r="AH189" s="1"/>
@@ -10700,7 +10769,7 @@
       <c r="AB190" s="1"/>
       <c r="AC190" s="1"/>
       <c r="AD190" s="1"/>
-      <c r="AE190" s="39"/>
+      <c r="AE190" s="29"/>
       <c r="AF190" s="1"/>
       <c r="AG190" s="1"/>
       <c r="AH190" s="1"/>
@@ -10751,7 +10820,7 @@
       <c r="AB191" s="1"/>
       <c r="AC191" s="1"/>
       <c r="AD191" s="1"/>
-      <c r="AE191" s="39"/>
+      <c r="AE191" s="29"/>
       <c r="AF191" s="1"/>
       <c r="AG191" s="1"/>
       <c r="AH191" s="1"/>
@@ -10796,7 +10865,7 @@
       <c r="AB192" s="1"/>
       <c r="AC192" s="1"/>
       <c r="AD192" s="1"/>
-      <c r="AE192" s="39"/>
+      <c r="AE192" s="29"/>
       <c r="AF192" s="1"/>
       <c r="AG192" s="1"/>
       <c r="AH192" s="1"/>
@@ -10841,7 +10910,7 @@
       <c r="AB193" s="1"/>
       <c r="AC193" s="1"/>
       <c r="AD193" s="1"/>
-      <c r="AE193" s="39"/>
+      <c r="AE193" s="29"/>
       <c r="AF193" s="1"/>
       <c r="AG193" s="1"/>
       <c r="AH193" s="1"/>
@@ -10884,7 +10953,7 @@
       <c r="AB194" s="1"/>
       <c r="AC194" s="1"/>
       <c r="AD194" s="1"/>
-      <c r="AE194" s="39"/>
+      <c r="AE194" s="29"/>
       <c r="AF194" s="1"/>
       <c r="AG194" s="1"/>
       <c r="AH194" s="1"/>
@@ -10927,7 +10996,7 @@
       <c r="AB195" s="1"/>
       <c r="AC195" s="1"/>
       <c r="AD195" s="1"/>
-      <c r="AE195" s="39"/>
+      <c r="AE195" s="29"/>
       <c r="AF195" s="1"/>
       <c r="AG195" s="1"/>
       <c r="AH195" s="1"/>
@@ -10970,7 +11039,7 @@
       <c r="AB196" s="1"/>
       <c r="AC196" s="1"/>
       <c r="AD196" s="1"/>
-      <c r="AE196" s="39"/>
+      <c r="AE196" s="29"/>
       <c r="AF196" s="1"/>
       <c r="AG196" s="1"/>
       <c r="AH196" s="1"/>
@@ -11013,7 +11082,7 @@
       <c r="AB197" s="1"/>
       <c r="AC197" s="1"/>
       <c r="AD197" s="1"/>
-      <c r="AE197" s="39"/>
+      <c r="AE197" s="29"/>
       <c r="AF197" s="1"/>
       <c r="AG197" s="1"/>
       <c r="AH197" s="1"/>
@@ -11058,7 +11127,7 @@
       <c r="AB198" s="1"/>
       <c r="AC198" s="1"/>
       <c r="AD198" s="1"/>
-      <c r="AE198" s="39"/>
+      <c r="AE198" s="29"/>
       <c r="AF198" s="1"/>
       <c r="AG198" s="1"/>
       <c r="AH198" s="1"/>
@@ -11103,7 +11172,7 @@
       <c r="AB199" s="1"/>
       <c r="AC199" s="1"/>
       <c r="AD199" s="1"/>
-      <c r="AE199" s="39"/>
+      <c r="AE199" s="29"/>
       <c r="AF199" s="1"/>
       <c r="AG199" s="1"/>
       <c r="AH199" s="1"/>
@@ -11146,7 +11215,7 @@
       <c r="AB200" s="1"/>
       <c r="AC200" s="1"/>
       <c r="AD200" s="1"/>
-      <c r="AE200" s="39"/>
+      <c r="AE200" s="29"/>
       <c r="AF200" s="1"/>
       <c r="AG200" s="1"/>
       <c r="AH200" s="1"/>
@@ -11191,7 +11260,7 @@
       <c r="AB201" s="1"/>
       <c r="AC201" s="1"/>
       <c r="AD201" s="1"/>
-      <c r="AE201" s="39"/>
+      <c r="AE201" s="29"/>
       <c r="AF201" s="1"/>
       <c r="AG201" s="1"/>
       <c r="AH201" s="1"/>
@@ -11234,7 +11303,7 @@
       <c r="AB202" s="1"/>
       <c r="AC202" s="1"/>
       <c r="AD202" s="1"/>
-      <c r="AE202" s="39"/>
+      <c r="AE202" s="29"/>
       <c r="AF202" s="1"/>
       <c r="AG202" s="1"/>
       <c r="AH202" s="1"/>
@@ -11279,7 +11348,7 @@
       <c r="AB203" s="1"/>
       <c r="AC203" s="1"/>
       <c r="AD203" s="1"/>
-      <c r="AE203" s="39"/>
+      <c r="AE203" s="29"/>
       <c r="AF203" s="1"/>
       <c r="AG203" s="1"/>
       <c r="AH203" s="1"/>
@@ -11322,7 +11391,7 @@
       <c r="AB204" s="1"/>
       <c r="AC204" s="1"/>
       <c r="AD204" s="1"/>
-      <c r="AE204" s="39"/>
+      <c r="AE204" s="29"/>
       <c r="AF204" s="1"/>
       <c r="AG204" s="1"/>
       <c r="AH204" s="1"/>
@@ -11365,7 +11434,7 @@
       <c r="AB205" s="1"/>
       <c r="AC205" s="1"/>
       <c r="AD205" s="1"/>
-      <c r="AE205" s="39"/>
+      <c r="AE205" s="29"/>
       <c r="AF205" s="1"/>
       <c r="AG205" s="1"/>
       <c r="AH205" s="1"/>
@@ -11408,7 +11477,7 @@
       <c r="AB206" s="1"/>
       <c r="AC206" s="1"/>
       <c r="AD206" s="1"/>
-      <c r="AE206" s="39"/>
+      <c r="AE206" s="29"/>
       <c r="AF206" s="1"/>
       <c r="AG206" s="1"/>
       <c r="AH206" s="1"/>
@@ -11453,7 +11522,7 @@
       <c r="AB207" s="1"/>
       <c r="AC207" s="1"/>
       <c r="AD207" s="1"/>
-      <c r="AE207" s="39"/>
+      <c r="AE207" s="29"/>
       <c r="AF207" s="1"/>
       <c r="AG207" s="1"/>
       <c r="AH207" s="1"/>
@@ -11496,7 +11565,7 @@
       <c r="AB208" s="1"/>
       <c r="AC208" s="1"/>
       <c r="AD208" s="1"/>
-      <c r="AE208" s="39"/>
+      <c r="AE208" s="29"/>
       <c r="AF208" s="1"/>
       <c r="AG208" s="1"/>
       <c r="AH208" s="1"/>
@@ -11539,7 +11608,7 @@
       <c r="AB209" s="1"/>
       <c r="AC209" s="1"/>
       <c r="AD209" s="1"/>
-      <c r="AE209" s="39"/>
+      <c r="AE209" s="29"/>
       <c r="AF209" s="1"/>
       <c r="AG209" s="1"/>
       <c r="AH209" s="1"/>
@@ -11582,7 +11651,7 @@
       <c r="AB210" s="1"/>
       <c r="AC210" s="1"/>
       <c r="AD210" s="1"/>
-      <c r="AE210" s="39"/>
+      <c r="AE210" s="29"/>
       <c r="AF210" s="1"/>
       <c r="AG210" s="1"/>
       <c r="AH210" s="1"/>
@@ -11625,7 +11694,7 @@
       <c r="AB211" s="1"/>
       <c r="AC211" s="1"/>
       <c r="AD211" s="1"/>
-      <c r="AE211" s="39"/>
+      <c r="AE211" s="29"/>
       <c r="AF211" s="1"/>
       <c r="AG211" s="1"/>
       <c r="AH211" s="1"/>
@@ -11668,7 +11737,7 @@
       <c r="AB212" s="1"/>
       <c r="AC212" s="1"/>
       <c r="AD212" s="1"/>
-      <c r="AE212" s="39"/>
+      <c r="AE212" s="29"/>
       <c r="AF212" s="1"/>
       <c r="AG212" s="1"/>
       <c r="AH212" s="1"/>
@@ -11711,7 +11780,7 @@
       <c r="AB213" s="1"/>
       <c r="AC213" s="1"/>
       <c r="AD213" s="1"/>
-      <c r="AE213" s="39"/>
+      <c r="AE213" s="29"/>
       <c r="AF213" s="1"/>
       <c r="AG213" s="1"/>
       <c r="AH213" s="1"/>
@@ -11754,7 +11823,7 @@
       <c r="AB214" s="1"/>
       <c r="AC214" s="1"/>
       <c r="AD214" s="1"/>
-      <c r="AE214" s="39"/>
+      <c r="AE214" s="29"/>
       <c r="AF214" s="1"/>
       <c r="AG214" s="1"/>
       <c r="AH214" s="1"/>
@@ -11797,7 +11866,7 @@
       <c r="AB215" s="1"/>
       <c r="AC215" s="1"/>
       <c r="AD215" s="1"/>
-      <c r="AE215" s="39"/>
+      <c r="AE215" s="29"/>
       <c r="AF215" s="1"/>
       <c r="AG215" s="1"/>
       <c r="AH215" s="1"/>
@@ -11844,7 +11913,7 @@
       <c r="AB216" s="1"/>
       <c r="AC216" s="1"/>
       <c r="AD216" s="1"/>
-      <c r="AE216" s="39"/>
+      <c r="AE216" s="29"/>
       <c r="AF216" s="1"/>
       <c r="AG216" s="1"/>
       <c r="AH216" s="1"/>
@@ -11891,7 +11960,7 @@
       <c r="AB217" s="1"/>
       <c r="AC217" s="1"/>
       <c r="AD217" s="1"/>
-      <c r="AE217" s="39"/>
+      <c r="AE217" s="29"/>
       <c r="AF217" s="1"/>
       <c r="AG217" s="1"/>
       <c r="AH217" s="1"/>
@@ -11938,7 +12007,7 @@
       <c r="AB218" s="1"/>
       <c r="AC218" s="1"/>
       <c r="AD218" s="1"/>
-      <c r="AE218" s="39"/>
+      <c r="AE218" s="29"/>
       <c r="AF218" s="1"/>
       <c r="AG218" s="1"/>
       <c r="AH218" s="1"/>
@@ -11979,7 +12048,7 @@
       <c r="AB219" s="1"/>
       <c r="AC219" s="1"/>
       <c r="AD219" s="1"/>
-      <c r="AE219" s="39"/>
+      <c r="AE219" s="29"/>
       <c r="AF219" s="1"/>
       <c r="AG219" s="1"/>
       <c r="AH219" s="1"/>
@@ -12020,7 +12089,7 @@
       <c r="AB220" s="1"/>
       <c r="AC220" s="1"/>
       <c r="AD220" s="1"/>
-      <c r="AE220" s="39"/>
+      <c r="AE220" s="29"/>
       <c r="AF220" s="1"/>
       <c r="AG220" s="1"/>
       <c r="AH220" s="1"/>
@@ -12061,7 +12130,7 @@
       <c r="AB221" s="1"/>
       <c r="AC221" s="1"/>
       <c r="AD221" s="1"/>
-      <c r="AE221" s="39"/>
+      <c r="AE221" s="29"/>
       <c r="AF221" s="1"/>
       <c r="AG221" s="1"/>
       <c r="AH221" s="1"/>
@@ -12104,7 +12173,7 @@
       <c r="AB222" s="1"/>
       <c r="AC222" s="1"/>
       <c r="AD222" s="1"/>
-      <c r="AE222" s="39"/>
+      <c r="AE222" s="29"/>
       <c r="AF222" s="1"/>
       <c r="AG222" s="1"/>
       <c r="AH222" s="1"/>
@@ -12145,7 +12214,7 @@
       <c r="AB223" s="1"/>
       <c r="AC223" s="1"/>
       <c r="AD223" s="1"/>
-      <c r="AE223" s="39"/>
+      <c r="AE223" s="29"/>
       <c r="AF223" s="1"/>
       <c r="AG223" s="1"/>
       <c r="AH223" s="1"/>
@@ -12186,7 +12255,7 @@
       <c r="AB224" s="1"/>
       <c r="AC224" s="1"/>
       <c r="AD224" s="1"/>
-      <c r="AE224" s="39"/>
+      <c r="AE224" s="29"/>
       <c r="AF224" s="1"/>
       <c r="AG224" s="1"/>
       <c r="AH224" s="1"/>
@@ -12227,7 +12296,7 @@
       <c r="AB225" s="1"/>
       <c r="AC225" s="1"/>
       <c r="AD225" s="1"/>
-      <c r="AE225" s="39"/>
+      <c r="AE225" s="29"/>
       <c r="AF225" s="1"/>
       <c r="AG225" s="1"/>
       <c r="AH225" s="1"/>
@@ -12268,7 +12337,7 @@
       <c r="AB226" s="1"/>
       <c r="AC226" s="1"/>
       <c r="AD226" s="1"/>
-      <c r="AE226" s="39"/>
+      <c r="AE226" s="29"/>
       <c r="AF226" s="1"/>
       <c r="AG226" s="1"/>
       <c r="AH226" s="1"/>
@@ -12309,7 +12378,7 @@
       <c r="AB227" s="1"/>
       <c r="AC227" s="1"/>
       <c r="AD227" s="1"/>
-      <c r="AE227" s="39"/>
+      <c r="AE227" s="29"/>
       <c r="AF227" s="1"/>
       <c r="AG227" s="1"/>
       <c r="AH227" s="1"/>
@@ -12350,7 +12419,7 @@
       <c r="AB228" s="1"/>
       <c r="AC228" s="1"/>
       <c r="AD228" s="1"/>
-      <c r="AE228" s="39"/>
+      <c r="AE228" s="29"/>
       <c r="AF228" s="1"/>
       <c r="AG228" s="1"/>
       <c r="AH228" s="1"/>
@@ -12391,7 +12460,7 @@
       <c r="AB229" s="1"/>
       <c r="AC229" s="1"/>
       <c r="AD229" s="1"/>
-      <c r="AE229" s="39"/>
+      <c r="AE229" s="29"/>
       <c r="AF229" s="1"/>
       <c r="AG229" s="1"/>
       <c r="AH229" s="1"/>
@@ -12432,7 +12501,7 @@
       <c r="AB230" s="1"/>
       <c r="AC230" s="1"/>
       <c r="AD230" s="1"/>
-      <c r="AE230" s="39"/>
+      <c r="AE230" s="29"/>
       <c r="AF230" s="1"/>
       <c r="AG230" s="1"/>
       <c r="AH230" s="1"/>
@@ -12473,7 +12542,7 @@
       <c r="AB231" s="1"/>
       <c r="AC231" s="1"/>
       <c r="AD231" s="1"/>
-      <c r="AE231" s="39"/>
+      <c r="AE231" s="29"/>
       <c r="AF231" s="1"/>
       <c r="AG231" s="1"/>
       <c r="AH231" s="1"/>
@@ -12514,7 +12583,7 @@
       <c r="AB232" s="1"/>
       <c r="AC232" s="1"/>
       <c r="AD232" s="1"/>
-      <c r="AE232" s="39"/>
+      <c r="AE232" s="29"/>
       <c r="AF232" s="1"/>
       <c r="AG232" s="1"/>
       <c r="AH232" s="1"/>
@@ -12557,7 +12626,7 @@
       <c r="AB233" s="1"/>
       <c r="AC233" s="1"/>
       <c r="AD233" s="1"/>
-      <c r="AE233" s="39"/>
+      <c r="AE233" s="29"/>
       <c r="AF233" s="1"/>
       <c r="AG233" s="1"/>
       <c r="AH233" s="1"/>
@@ -12598,7 +12667,7 @@
       <c r="AB234" s="1"/>
       <c r="AC234" s="1"/>
       <c r="AD234" s="1"/>
-      <c r="AE234" s="39"/>
+      <c r="AE234" s="29"/>
       <c r="AF234" s="1"/>
       <c r="AG234" s="1"/>
       <c r="AH234" s="1"/>
@@ -12641,7 +12710,7 @@
       <c r="AB235" s="1"/>
       <c r="AC235" s="1"/>
       <c r="AD235" s="1"/>
-      <c r="AE235" s="39"/>
+      <c r="AE235" s="29"/>
       <c r="AF235" s="1"/>
       <c r="AG235" s="1"/>
       <c r="AH235" s="1"/>
@@ -12682,7 +12751,7 @@
       <c r="AB236" s="1"/>
       <c r="AC236" s="1"/>
       <c r="AD236" s="1"/>
-      <c r="AE236" s="39"/>
+      <c r="AE236" s="29"/>
       <c r="AF236" s="1"/>
       <c r="AG236" s="1"/>
       <c r="AH236" s="1"/>
@@ -12723,7 +12792,7 @@
       <c r="AB237" s="1"/>
       <c r="AC237" s="1"/>
       <c r="AD237" s="1"/>
-      <c r="AE237" s="39"/>
+      <c r="AE237" s="29"/>
       <c r="AF237" s="1"/>
       <c r="AG237" s="1"/>
       <c r="AH237" s="1"/>
@@ -12764,7 +12833,7 @@
       <c r="AB238" s="1"/>
       <c r="AC238" s="1"/>
       <c r="AD238" s="1"/>
-      <c r="AE238" s="39"/>
+      <c r="AE238" s="29"/>
       <c r="AF238" s="1"/>
       <c r="AG238" s="1"/>
       <c r="AH238" s="1"/>
@@ -12805,7 +12874,7 @@
       <c r="AB239" s="1"/>
       <c r="AC239" s="1"/>
       <c r="AD239" s="1"/>
-      <c r="AE239" s="39"/>
+      <c r="AE239" s="29"/>
       <c r="AF239" s="1"/>
       <c r="AG239" s="1"/>
       <c r="AH239" s="1"/>
@@ -12846,7 +12915,7 @@
       <c r="AB240" s="1"/>
       <c r="AC240" s="1"/>
       <c r="AD240" s="1"/>
-      <c r="AE240" s="39"/>
+      <c r="AE240" s="29"/>
       <c r="AF240" s="1"/>
       <c r="AG240" s="1"/>
       <c r="AH240" s="1"/>
@@ -12887,7 +12956,7 @@
       <c r="AB241" s="1"/>
       <c r="AC241" s="1"/>
       <c r="AD241" s="1"/>
-      <c r="AE241" s="39"/>
+      <c r="AE241" s="29"/>
       <c r="AF241" s="1"/>
       <c r="AG241" s="1"/>
       <c r="AH241" s="1"/>
@@ -12928,7 +12997,7 @@
       <c r="AB242" s="1"/>
       <c r="AC242" s="1"/>
       <c r="AD242" s="1"/>
-      <c r="AE242" s="39"/>
+      <c r="AE242" s="29"/>
       <c r="AF242" s="1"/>
       <c r="AG242" s="1"/>
       <c r="AH242" s="1"/>
@@ -12971,7 +13040,7 @@
       <c r="AB243" s="1"/>
       <c r="AC243" s="1"/>
       <c r="AD243" s="1"/>
-      <c r="AE243" s="39"/>
+      <c r="AE243" s="29"/>
       <c r="AF243" s="1"/>
       <c r="AG243" s="1"/>
       <c r="AH243" s="1"/>
@@ -13014,7 +13083,7 @@
       <c r="AB244" s="1"/>
       <c r="AC244" s="1"/>
       <c r="AD244" s="1"/>
-      <c r="AE244" s="39"/>
+      <c r="AE244" s="29"/>
       <c r="AF244" s="1"/>
       <c r="AG244" s="1"/>
       <c r="AH244" s="1"/>
@@ -13057,7 +13126,7 @@
       <c r="AB245" s="1"/>
       <c r="AC245" s="1"/>
       <c r="AD245" s="1"/>
-      <c r="AE245" s="39"/>
+      <c r="AE245" s="29"/>
       <c r="AF245" s="1"/>
       <c r="AG245" s="1"/>
       <c r="AH245" s="1"/>
@@ -13100,7 +13169,7 @@
       <c r="AB246" s="1"/>
       <c r="AC246" s="1"/>
       <c r="AD246" s="1"/>
-      <c r="AE246" s="39"/>
+      <c r="AE246" s="29"/>
       <c r="AF246" s="1"/>
       <c r="AG246" s="1"/>
       <c r="AH246" s="1"/>
@@ -13143,7 +13212,7 @@
       <c r="AB247" s="1"/>
       <c r="AC247" s="1"/>
       <c r="AD247" s="1"/>
-      <c r="AE247" s="39"/>
+      <c r="AE247" s="29"/>
       <c r="AF247" s="1"/>
       <c r="AG247" s="1"/>
       <c r="AH247" s="1"/>
@@ -13186,7 +13255,7 @@
       <c r="AB248" s="1"/>
       <c r="AC248" s="1"/>
       <c r="AD248" s="1"/>
-      <c r="AE248" s="39"/>
+      <c r="AE248" s="29"/>
       <c r="AF248" s="1"/>
       <c r="AG248" s="1"/>
       <c r="AH248" s="1"/>
@@ -13227,7 +13296,7 @@
       <c r="AB249" s="1"/>
       <c r="AC249" s="1"/>
       <c r="AD249" s="1"/>
-      <c r="AE249" s="39"/>
+      <c r="AE249" s="29"/>
       <c r="AF249" s="1"/>
       <c r="AG249" s="1"/>
       <c r="AH249" s="1"/>
@@ -13268,7 +13337,7 @@
       <c r="AB250" s="1"/>
       <c r="AC250" s="1"/>
       <c r="AD250" s="1"/>
-      <c r="AE250" s="39"/>
+      <c r="AE250" s="29"/>
       <c r="AF250" s="1"/>
       <c r="AG250" s="1"/>
       <c r="AH250" s="1"/>
@@ -13309,7 +13378,7 @@
       <c r="AB251" s="1"/>
       <c r="AC251" s="1"/>
       <c r="AD251" s="1"/>
-      <c r="AE251" s="39"/>
+      <c r="AE251" s="29"/>
       <c r="AF251" s="1"/>
       <c r="AG251" s="1"/>
       <c r="AH251" s="1"/>
@@ -13350,7 +13419,7 @@
       <c r="AB252" s="1"/>
       <c r="AC252" s="1"/>
       <c r="AD252" s="1"/>
-      <c r="AE252" s="39"/>
+      <c r="AE252" s="29"/>
       <c r="AF252" s="1"/>
       <c r="AG252" s="1"/>
       <c r="AH252" s="1"/>
@@ -13391,7 +13460,7 @@
       <c r="AB253" s="1"/>
       <c r="AC253" s="1"/>
       <c r="AD253" s="1"/>
-      <c r="AE253" s="39"/>
+      <c r="AE253" s="29"/>
       <c r="AF253" s="1"/>
       <c r="AG253" s="1"/>
       <c r="AH253" s="1"/>
@@ -13432,7 +13501,7 @@
       <c r="AB254" s="1"/>
       <c r="AC254" s="1"/>
       <c r="AD254" s="1"/>
-      <c r="AE254" s="39"/>
+      <c r="AE254" s="29"/>
       <c r="AF254" s="1"/>
       <c r="AG254" s="1"/>
       <c r="AH254" s="1"/>
@@ -13473,7 +13542,7 @@
       <c r="AB255" s="1"/>
       <c r="AC255" s="1"/>
       <c r="AD255" s="1"/>
-      <c r="AE255" s="39"/>
+      <c r="AE255" s="29"/>
       <c r="AF255" s="1"/>
       <c r="AG255" s="1"/>
       <c r="AH255" s="1"/>
@@ -13512,7 +13581,7 @@
       <c r="AB256" s="1"/>
       <c r="AC256" s="1"/>
       <c r="AD256" s="1"/>
-      <c r="AE256" s="39"/>
+      <c r="AE256" s="29"/>
       <c r="AF256" s="1"/>
       <c r="AG256" s="1"/>
       <c r="AH256" s="1"/>
@@ -13551,7 +13620,7 @@
       <c r="AB257" s="1"/>
       <c r="AC257" s="1"/>
       <c r="AD257" s="1"/>
-      <c r="AE257" s="39"/>
+      <c r="AE257" s="29"/>
       <c r="AF257" s="1"/>
       <c r="AG257" s="1"/>
       <c r="AH257" s="1"/>
@@ -13590,7 +13659,7 @@
       <c r="AB258" s="1"/>
       <c r="AC258" s="1"/>
       <c r="AD258" s="1"/>
-      <c r="AE258" s="39"/>
+      <c r="AE258" s="29"/>
       <c r="AF258" s="1"/>
       <c r="AG258" s="1"/>
       <c r="AH258" s="1"/>
@@ -13629,7 +13698,7 @@
       <c r="AB259" s="1"/>
       <c r="AC259" s="1"/>
       <c r="AD259" s="1"/>
-      <c r="AE259" s="39"/>
+      <c r="AE259" s="29"/>
       <c r="AF259" s="1"/>
       <c r="AG259" s="1"/>
       <c r="AH259" s="1"/>
@@ -13668,7 +13737,7 @@
       <c r="AB260" s="1"/>
       <c r="AC260" s="1"/>
       <c r="AD260" s="1"/>
-      <c r="AE260" s="39"/>
+      <c r="AE260" s="29"/>
       <c r="AF260" s="1"/>
       <c r="AG260" s="1"/>
       <c r="AH260" s="1"/>
@@ -13707,7 +13776,7 @@
       <c r="AB261" s="1"/>
       <c r="AC261" s="1"/>
       <c r="AD261" s="1"/>
-      <c r="AE261" s="39"/>
+      <c r="AE261" s="29"/>
       <c r="AF261" s="1"/>
       <c r="AG261" s="1"/>
       <c r="AH261" s="1"/>
@@ -13746,7 +13815,7 @@
       <c r="AB262" s="1"/>
       <c r="AC262" s="1"/>
       <c r="AD262" s="1"/>
-      <c r="AE262" s="39"/>
+      <c r="AE262" s="29"/>
       <c r="AF262" s="1"/>
       <c r="AG262" s="1"/>
       <c r="AH262" s="1"/>
@@ -13785,7 +13854,7 @@
       <c r="AB263" s="1"/>
       <c r="AC263" s="1"/>
       <c r="AD263" s="1"/>
-      <c r="AE263" s="39"/>
+      <c r="AE263" s="29"/>
       <c r="AF263" s="1"/>
       <c r="AG263" s="1"/>
       <c r="AH263" s="1"/>
@@ -13824,7 +13893,7 @@
       <c r="AB264" s="1"/>
       <c r="AC264" s="1"/>
       <c r="AD264" s="1"/>
-      <c r="AE264" s="39"/>
+      <c r="AE264" s="29"/>
       <c r="AF264" s="1"/>
       <c r="AG264" s="1"/>
       <c r="AH264" s="1"/>
@@ -13863,7 +13932,7 @@
       <c r="AB265" s="1"/>
       <c r="AC265" s="1"/>
       <c r="AD265" s="1"/>
-      <c r="AE265" s="39"/>
+      <c r="AE265" s="29"/>
       <c r="AF265" s="1"/>
       <c r="AG265" s="1"/>
       <c r="AH265" s="1"/>
@@ -13902,7 +13971,7 @@
       <c r="AB266" s="1"/>
       <c r="AC266" s="1"/>
       <c r="AD266" s="1"/>
-      <c r="AE266" s="39"/>
+      <c r="AE266" s="29"/>
       <c r="AF266" s="1"/>
       <c r="AG266" s="1"/>
       <c r="AH266" s="1"/>
@@ -13941,7 +14010,7 @@
       <c r="AB267" s="1"/>
       <c r="AC267" s="1"/>
       <c r="AD267" s="1"/>
-      <c r="AE267" s="39"/>
+      <c r="AE267" s="29"/>
       <c r="AF267" s="1"/>
       <c r="AG267" s="1"/>
       <c r="AH267" s="1"/>
@@ -13980,7 +14049,7 @@
       <c r="AB268" s="1"/>
       <c r="AC268" s="1"/>
       <c r="AD268" s="1"/>
-      <c r="AE268" s="39"/>
+      <c r="AE268" s="29"/>
       <c r="AF268" s="1"/>
       <c r="AG268" s="1"/>
       <c r="AH268" s="1"/>
@@ -14019,7 +14088,7 @@
       <c r="AB269" s="1"/>
       <c r="AC269" s="1"/>
       <c r="AD269" s="1"/>
-      <c r="AE269" s="39"/>
+      <c r="AE269" s="29"/>
       <c r="AF269" s="1"/>
       <c r="AG269" s="1"/>
       <c r="AH269" s="1"/>
@@ -14058,7 +14127,7 @@
       <c r="AB270" s="1"/>
       <c r="AC270" s="1"/>
       <c r="AD270" s="1"/>
-      <c r="AE270" s="39"/>
+      <c r="AE270" s="29"/>
       <c r="AF270" s="1"/>
       <c r="AG270" s="1"/>
       <c r="AH270" s="1"/>
@@ -14097,7 +14166,7 @@
       <c r="AB271" s="1"/>
       <c r="AC271" s="1"/>
       <c r="AD271" s="1"/>
-      <c r="AE271" s="39"/>
+      <c r="AE271" s="29"/>
       <c r="AF271" s="1"/>
       <c r="AG271" s="1"/>
       <c r="AH271" s="1"/>
@@ -14136,7 +14205,7 @@
       <c r="AB272" s="1"/>
       <c r="AC272" s="1"/>
       <c r="AD272" s="1"/>
-      <c r="AE272" s="39"/>
+      <c r="AE272" s="29"/>
       <c r="AF272" s="1"/>
       <c r="AG272" s="1"/>
       <c r="AH272" s="1"/>
@@ -14175,7 +14244,7 @@
       <c r="AB273" s="1"/>
       <c r="AC273" s="1"/>
       <c r="AD273" s="1"/>
-      <c r="AE273" s="39"/>
+      <c r="AE273" s="29"/>
       <c r="AF273" s="1"/>
       <c r="AG273" s="1"/>
       <c r="AH273" s="1"/>
@@ -14214,7 +14283,7 @@
       <c r="AB274" s="1"/>
       <c r="AC274" s="1"/>
       <c r="AD274" s="1"/>
-      <c r="AE274" s="39"/>
+      <c r="AE274" s="29"/>
       <c r="AF274" s="1"/>
       <c r="AG274" s="1"/>
       <c r="AH274" s="1"/>
@@ -14253,7 +14322,7 @@
       <c r="AB275" s="1"/>
       <c r="AC275" s="1"/>
       <c r="AD275" s="1"/>
-      <c r="AE275" s="39"/>
+      <c r="AE275" s="29"/>
       <c r="AF275" s="1"/>
       <c r="AG275" s="1"/>
       <c r="AH275" s="1"/>
@@ -14292,7 +14361,7 @@
       <c r="AB276" s="1"/>
       <c r="AC276" s="1"/>
       <c r="AD276" s="1"/>
-      <c r="AE276" s="39"/>
+      <c r="AE276" s="29"/>
       <c r="AF276" s="1"/>
       <c r="AG276" s="1"/>
       <c r="AH276" s="1"/>
@@ -14331,7 +14400,7 @@
       <c r="AB277" s="1"/>
       <c r="AC277" s="1"/>
       <c r="AD277" s="1"/>
-      <c r="AE277" s="39"/>
+      <c r="AE277" s="29"/>
       <c r="AF277" s="1"/>
       <c r="AG277" s="1"/>
       <c r="AH277" s="1"/>
@@ -14370,7 +14439,7 @@
       <c r="AB278" s="1"/>
       <c r="AC278" s="1"/>
       <c r="AD278" s="1"/>
-      <c r="AE278" s="39"/>
+      <c r="AE278" s="29"/>
       <c r="AF278" s="1"/>
       <c r="AG278" s="1"/>
       <c r="AH278" s="1"/>
@@ -14409,7 +14478,7 @@
       <c r="AB279" s="1"/>
       <c r="AC279" s="1"/>
       <c r="AD279" s="1"/>
-      <c r="AE279" s="39"/>
+      <c r="AE279" s="29"/>
       <c r="AF279" s="1"/>
       <c r="AG279" s="1"/>
       <c r="AH279" s="1"/>
@@ -14448,7 +14517,7 @@
       <c r="AB280" s="1"/>
       <c r="AC280" s="1"/>
       <c r="AD280" s="1"/>
-      <c r="AE280" s="39"/>
+      <c r="AE280" s="29"/>
       <c r="AF280" s="1"/>
       <c r="AG280" s="1"/>
       <c r="AH280" s="1"/>
@@ -17204,7 +17273,7 @@
         <v>354</v>
       </c>
       <c r="C70" s="3"/>
-      <c r="D70" s="26" t="s">
+      <c r="D70" s="27" t="s">
         <v>371</v>
       </c>
       <c r="E70" s="3"/>
@@ -17284,7 +17353,7 @@
         <v>354</v>
       </c>
       <c r="C76" s="3"/>
-      <c r="D76" s="26" t="s">
+      <c r="D76" s="27" t="s">
         <v>378</v>
       </c>
       <c r="E76" s="3"/>
@@ -17293,153 +17362,221 @@
       <c r="A77" s="26">
         <v>76</v>
       </c>
-      <c r="B77" s="26"/>
+      <c r="B77" s="26" t="s">
+        <v>354</v>
+      </c>
       <c r="C77" s="3"/>
-      <c r="D77" s="26"/>
+      <c r="D77" s="27" t="s">
+        <v>379</v>
+      </c>
       <c r="E77" s="3"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="26">
         <v>77</v>
       </c>
-      <c r="B78" s="26"/>
+      <c r="B78" s="26" t="s">
+        <v>354</v>
+      </c>
       <c r="C78" s="3"/>
-      <c r="D78" s="26"/>
+      <c r="D78" s="27" t="s">
+        <v>380</v>
+      </c>
       <c r="E78" s="3"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="26">
         <v>78</v>
       </c>
-      <c r="B79" s="26"/>
+      <c r="B79" s="26" t="s">
+        <v>354</v>
+      </c>
       <c r="C79" s="3"/>
-      <c r="D79" s="26"/>
+      <c r="D79" s="27" t="s">
+        <v>381</v>
+      </c>
       <c r="E79" s="3"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="26">
         <v>79</v>
       </c>
-      <c r="B80" s="26"/>
+      <c r="B80" s="26" t="s">
+        <v>354</v>
+      </c>
       <c r="C80" s="3"/>
-      <c r="D80" s="26"/>
+      <c r="D80" s="27" t="s">
+        <v>382</v>
+      </c>
       <c r="E80" s="3"/>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="26">
         <v>80</v>
       </c>
-      <c r="B81" s="26"/>
+      <c r="B81" s="26" t="s">
+        <v>354</v>
+      </c>
       <c r="C81" s="3"/>
-      <c r="D81" s="26"/>
+      <c r="D81" s="26" t="s">
+        <v>383</v>
+      </c>
       <c r="E81" s="3"/>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="26">
         <v>81</v>
       </c>
-      <c r="B82" s="26"/>
+      <c r="B82" s="26" t="s">
+        <v>354</v>
+      </c>
       <c r="C82" s="3"/>
-      <c r="D82" s="26"/>
+      <c r="D82" s="26" t="s">
+        <v>384</v>
+      </c>
       <c r="E82" s="3"/>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="26">
         <v>82</v>
       </c>
-      <c r="B83" s="26"/>
+      <c r="B83" s="26" t="s">
+        <v>354</v>
+      </c>
       <c r="C83" s="3"/>
-      <c r="D83" s="26"/>
+      <c r="D83" s="41" t="s">
+        <v>385</v>
+      </c>
       <c r="E83" s="3"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="26">
         <v>83</v>
       </c>
-      <c r="B84" s="26"/>
+      <c r="B84" s="26" t="s">
+        <v>354</v>
+      </c>
       <c r="C84" s="3"/>
-      <c r="D84" s="26"/>
+      <c r="D84" s="26" t="s">
+        <v>386</v>
+      </c>
       <c r="E84" s="3"/>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="26">
         <v>84</v>
       </c>
-      <c r="B85" s="26"/>
+      <c r="B85" s="26" t="s">
+        <v>354</v>
+      </c>
       <c r="C85" s="3"/>
-      <c r="D85" s="26"/>
+      <c r="D85" s="26" t="s">
+        <v>387</v>
+      </c>
       <c r="E85" s="3"/>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="26">
         <v>85</v>
       </c>
-      <c r="B86" s="26"/>
+      <c r="B86" s="26" t="s">
+        <v>354</v>
+      </c>
       <c r="C86" s="3"/>
-      <c r="D86" s="26"/>
+      <c r="D86" s="26" t="s">
+        <v>388</v>
+      </c>
       <c r="E86" s="3"/>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="26">
         <v>86</v>
       </c>
-      <c r="B87" s="26"/>
+      <c r="B87" s="26" t="s">
+        <v>354</v>
+      </c>
       <c r="C87" s="3"/>
-      <c r="D87" s="26"/>
+      <c r="D87" s="26" t="s">
+        <v>389</v>
+      </c>
       <c r="E87" s="3"/>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="26">
         <v>87</v>
       </c>
-      <c r="B88" s="26"/>
+      <c r="B88" s="26" t="s">
+        <v>354</v>
+      </c>
       <c r="C88" s="3"/>
-      <c r="D88" s="26"/>
+      <c r="D88" s="26" t="s">
+        <v>390</v>
+      </c>
       <c r="E88" s="3"/>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="26">
         <v>88</v>
       </c>
-      <c r="B89" s="26"/>
+      <c r="B89" s="26" t="s">
+        <v>354</v>
+      </c>
       <c r="C89" s="3"/>
-      <c r="D89" s="26"/>
+      <c r="D89" s="27" t="s">
+        <v>391</v>
+      </c>
       <c r="E89" s="3"/>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="26">
         <v>89</v>
       </c>
-      <c r="B90" s="26"/>
+      <c r="B90" s="26" t="s">
+        <v>354</v>
+      </c>
       <c r="C90" s="3"/>
-      <c r="D90" s="26"/>
+      <c r="D90" s="26" t="s">
+        <v>392</v>
+      </c>
       <c r="E90" s="3"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="26">
         <v>90</v>
       </c>
-      <c r="B91" s="26"/>
+      <c r="B91" s="26" t="s">
+        <v>354</v>
+      </c>
       <c r="C91" s="3"/>
-      <c r="D91" s="26"/>
+      <c r="D91" s="41" t="s">
+        <v>393</v>
+      </c>
       <c r="E91" s="3"/>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="26">
         <v>91</v>
       </c>
-      <c r="B92" s="26"/>
+      <c r="B92" s="26" t="s">
+        <v>354</v>
+      </c>
       <c r="C92" s="3"/>
-      <c r="D92" s="26"/>
+      <c r="D92" s="41" t="s">
+        <v>394</v>
+      </c>
       <c r="E92" s="3"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="26">
         <v>92</v>
       </c>
-      <c r="B93" s="26"/>
+      <c r="B93" s="26" t="s">
+        <v>354</v>
+      </c>
       <c r="C93" s="3"/>
-      <c r="D93" s="26"/>
+      <c r="D93" s="27" t="s">
+        <v>395</v>
+      </c>
       <c r="E93" s="3"/>
     </row>
     <row r="94" spans="1:5">

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\副業\LINE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDBF346-C711-40BA-AB8E-844B4D3AFF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678919BE-119C-47B5-9116-AB61A93A5AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="リスト" sheetId="1" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="397">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -1658,30 +1658,12 @@
     <t>儲かりまっか？</t>
   </si>
   <si>
-    <t>ええかっこしい</t>
-  </si>
-  <si>
-    <t>いちびり</t>
-  </si>
-  <si>
     <t>ケチくさい</t>
   </si>
   <si>
     <t>おべっか</t>
   </si>
   <si>
-    <t>自分（じぶん）</t>
-  </si>
-  <si>
-    <t>ええしの子</t>
-  </si>
-  <si>
-    <t>パチもん</t>
-  </si>
-  <si>
-    <t>べっちょない</t>
-  </si>
-  <si>
     <t>さら</t>
   </si>
   <si>
@@ -1689,18 +1671,6 @@
   </si>
   <si>
     <t>おっさん</t>
-  </si>
-  <si>
-    <t>ほかす</t>
-  </si>
-  <si>
-    <t>シュッとしてる</t>
-  </si>
-  <si>
-    <t>カチカチ山</t>
-  </si>
-  <si>
-    <t>おちょくる</t>
   </si>
   <si>
     <t>けったいな</t>
@@ -1846,10 +1816,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>いてまう</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ほな</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1871,6 +1837,60 @@
   </si>
   <si>
     <t>よろしゅう</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>いてまうで</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ええかっこしい～</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>いちびりぃ～</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自分（じぶん）や</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ええしの子</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>パチもん</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>べっちょない</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シュッとしてる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>カチカチ山</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おちょくるな</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>関西弁</t>
+    <rPh sb="0" eb="3">
+      <t>カンサイベン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>関西弁１</t>
+    <rPh sb="0" eb="3">
+      <t>カンサイベン</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2107,7 +2127,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2219,7 +2239,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2600,17 +2619,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI280"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
-    <col min="1" max="1" width="3.4140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.4140625" style="24" customWidth="1"/>
+    <col min="1" max="1" width="3.4375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.4375" style="24" customWidth="1"/>
     <col min="3" max="3" width="33.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="3.58203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="2.58203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="35" width="3.58203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="3.5625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2.5625" bestFit="1" customWidth="1"/>
+    <col min="11" max="35" width="3.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="22.5">
+    <row r="1" spans="1:35" ht="22.9">
       <c r="A1" s="34"/>
       <c r="B1" s="38" t="s">
         <v>273</v>
@@ -2642,7 +2661,7 @@
       <c r="W1" s="37"/>
       <c r="X1" s="37"/>
     </row>
-    <row r="2" spans="1:35" ht="22.5">
+    <row r="2" spans="1:35" ht="22.9">
       <c r="A2" s="35"/>
       <c r="B2" s="39"/>
       <c r="C2" s="32"/>
@@ -2689,7 +2708,7 @@
       <c r="AH2" s="5"/>
       <c r="AI2" s="5"/>
     </row>
-    <row r="3" spans="1:35" s="13" customFormat="1" ht="109.5" thickBot="1">
+    <row r="3" spans="1:35" s="13" customFormat="1" ht="106.9" thickBot="1">
       <c r="A3" s="36"/>
       <c r="B3" s="40"/>
       <c r="C3" s="33"/>
@@ -2780,7 +2799,9 @@
       <c r="AF3" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="AG3" s="11"/>
+      <c r="AG3" s="11" t="s">
+        <v>395</v>
+      </c>
       <c r="AH3" s="11"/>
       <c r="AI3" s="11"/>
     </row>
@@ -2833,7 +2854,7 @@
       <c r="AD4" s="1"/>
       <c r="AE4" s="29"/>
       <c r="AF4" s="1"/>
-      <c r="AG4" s="1"/>
+      <c r="AG4" s="29"/>
       <c r="AH4" s="1"/>
       <c r="AI4" s="1"/>
     </row>
@@ -2888,7 +2909,7 @@
       <c r="AD5" s="1"/>
       <c r="AE5" s="29"/>
       <c r="AF5" s="1"/>
-      <c r="AG5" s="1"/>
+      <c r="AG5" s="29"/>
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
     </row>
@@ -2933,7 +2954,7 @@
       <c r="AD6" s="1"/>
       <c r="AE6" s="29"/>
       <c r="AF6" s="1"/>
-      <c r="AG6" s="1"/>
+      <c r="AG6" s="29"/>
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
     </row>
@@ -2974,7 +2995,7 @@
       <c r="AD7" s="1"/>
       <c r="AE7" s="29"/>
       <c r="AF7" s="1"/>
-      <c r="AG7" s="1"/>
+      <c r="AG7" s="29"/>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
     </row>
@@ -3017,7 +3038,7 @@
       <c r="AD8" s="1"/>
       <c r="AE8" s="29"/>
       <c r="AF8" s="1"/>
-      <c r="AG8" s="1"/>
+      <c r="AG8" s="29"/>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
     </row>
@@ -3058,7 +3079,7 @@
       <c r="AD9" s="1"/>
       <c r="AE9" s="29"/>
       <c r="AF9" s="1"/>
-      <c r="AG9" s="1"/>
+      <c r="AG9" s="29"/>
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
     </row>
@@ -3099,7 +3120,7 @@
       <c r="AD10" s="1"/>
       <c r="AE10" s="29"/>
       <c r="AF10" s="1"/>
-      <c r="AG10" s="1"/>
+      <c r="AG10" s="29"/>
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
     </row>
@@ -3144,7 +3165,7 @@
       <c r="AD11" s="1"/>
       <c r="AE11" s="29"/>
       <c r="AF11" s="1"/>
-      <c r="AG11" s="1"/>
+      <c r="AG11" s="29"/>
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
     </row>
@@ -3185,7 +3206,7 @@
       <c r="AD12" s="1"/>
       <c r="AE12" s="29"/>
       <c r="AF12" s="1"/>
-      <c r="AG12" s="1"/>
+      <c r="AG12" s="29"/>
       <c r="AH12" s="1"/>
       <c r="AI12" s="1"/>
     </row>
@@ -3226,7 +3247,7 @@
       <c r="AD13" s="1"/>
       <c r="AE13" s="29"/>
       <c r="AF13" s="1"/>
-      <c r="AG13" s="1"/>
+      <c r="AG13" s="29"/>
       <c r="AH13" s="1"/>
       <c r="AI13" s="1"/>
     </row>
@@ -3267,7 +3288,7 @@
       <c r="AD14" s="1"/>
       <c r="AE14" s="29"/>
       <c r="AF14" s="1"/>
-      <c r="AG14" s="1"/>
+      <c r="AG14" s="29"/>
       <c r="AH14" s="1"/>
       <c r="AI14" s="1"/>
     </row>
@@ -3308,7 +3329,7 @@
       <c r="AD15" s="1"/>
       <c r="AE15" s="29"/>
       <c r="AF15" s="1"/>
-      <c r="AG15" s="1"/>
+      <c r="AG15" s="29"/>
       <c r="AH15" s="1"/>
       <c r="AI15" s="1"/>
     </row>
@@ -3349,7 +3370,7 @@
       <c r="AD16" s="1"/>
       <c r="AE16" s="29"/>
       <c r="AF16" s="1"/>
-      <c r="AG16" s="1"/>
+      <c r="AG16" s="29"/>
       <c r="AH16" s="1"/>
       <c r="AI16" s="1"/>
     </row>
@@ -3390,7 +3411,7 @@
       <c r="AD17" s="1"/>
       <c r="AE17" s="29"/>
       <c r="AF17" s="1"/>
-      <c r="AG17" s="1"/>
+      <c r="AG17" s="29"/>
       <c r="AH17" s="1"/>
       <c r="AI17" s="1"/>
     </row>
@@ -3433,7 +3454,7 @@
       <c r="AD18" s="1"/>
       <c r="AE18" s="29"/>
       <c r="AF18" s="1"/>
-      <c r="AG18" s="1"/>
+      <c r="AG18" s="29"/>
       <c r="AH18" s="1"/>
       <c r="AI18" s="1"/>
     </row>
@@ -3474,7 +3495,7 @@
       <c r="AD19" s="1"/>
       <c r="AE19" s="29"/>
       <c r="AF19" s="1"/>
-      <c r="AG19" s="1"/>
+      <c r="AG19" s="29"/>
       <c r="AH19" s="1"/>
       <c r="AI19" s="1"/>
     </row>
@@ -3515,7 +3536,7 @@
       <c r="AD20" s="1"/>
       <c r="AE20" s="29"/>
       <c r="AF20" s="1"/>
-      <c r="AG20" s="1"/>
+      <c r="AG20" s="29"/>
       <c r="AH20" s="1"/>
       <c r="AI20" s="1"/>
     </row>
@@ -3556,7 +3577,7 @@
       <c r="AD21" s="1"/>
       <c r="AE21" s="29"/>
       <c r="AF21" s="1"/>
-      <c r="AG21" s="1"/>
+      <c r="AG21" s="29"/>
       <c r="AH21" s="1"/>
       <c r="AI21" s="1"/>
     </row>
@@ -3599,7 +3620,7 @@
       <c r="AD22" s="1"/>
       <c r="AE22" s="29"/>
       <c r="AF22" s="1"/>
-      <c r="AG22" s="1"/>
+      <c r="AG22" s="29"/>
       <c r="AH22" s="1"/>
       <c r="AI22" s="1"/>
     </row>
@@ -3640,7 +3661,7 @@
       <c r="AD23" s="1"/>
       <c r="AE23" s="29"/>
       <c r="AF23" s="1"/>
-      <c r="AG23" s="1"/>
+      <c r="AG23" s="29"/>
       <c r="AH23" s="1"/>
       <c r="AI23" s="1"/>
     </row>
@@ -3683,7 +3704,7 @@
       <c r="AD24" s="1"/>
       <c r="AE24" s="29"/>
       <c r="AF24" s="1"/>
-      <c r="AG24" s="1"/>
+      <c r="AG24" s="29"/>
       <c r="AH24" s="1"/>
       <c r="AI24" s="1"/>
     </row>
@@ -3726,7 +3747,7 @@
       <c r="AD25" s="1"/>
       <c r="AE25" s="29"/>
       <c r="AF25" s="1"/>
-      <c r="AG25" s="1"/>
+      <c r="AG25" s="29"/>
       <c r="AH25" s="1"/>
       <c r="AI25" s="1"/>
     </row>
@@ -3767,7 +3788,7 @@
       <c r="AD26" s="1"/>
       <c r="AE26" s="29"/>
       <c r="AF26" s="1"/>
-      <c r="AG26" s="1"/>
+      <c r="AG26" s="29"/>
       <c r="AH26" s="1"/>
       <c r="AI26" s="1"/>
     </row>
@@ -3810,7 +3831,7 @@
       <c r="AD27" s="1"/>
       <c r="AE27" s="29"/>
       <c r="AF27" s="1"/>
-      <c r="AG27" s="1"/>
+      <c r="AG27" s="29"/>
       <c r="AH27" s="1"/>
       <c r="AI27" s="1"/>
     </row>
@@ -3851,7 +3872,7 @@
       <c r="AD28" s="1"/>
       <c r="AE28" s="29"/>
       <c r="AF28" s="1"/>
-      <c r="AG28" s="1"/>
+      <c r="AG28" s="29"/>
       <c r="AH28" s="1"/>
       <c r="AI28" s="1"/>
     </row>
@@ -3892,7 +3913,7 @@
       <c r="AD29" s="1"/>
       <c r="AE29" s="29"/>
       <c r="AF29" s="1"/>
-      <c r="AG29" s="1"/>
+      <c r="AG29" s="29"/>
       <c r="AH29" s="1"/>
       <c r="AI29" s="1"/>
     </row>
@@ -3935,7 +3956,7 @@
       <c r="AD30" s="1"/>
       <c r="AE30" s="29"/>
       <c r="AF30" s="1"/>
-      <c r="AG30" s="1"/>
+      <c r="AG30" s="29"/>
       <c r="AH30" s="1"/>
       <c r="AI30" s="1"/>
     </row>
@@ -3982,7 +4003,7 @@
       <c r="AD31" s="1"/>
       <c r="AE31" s="29"/>
       <c r="AF31" s="1"/>
-      <c r="AG31" s="1"/>
+      <c r="AG31" s="29"/>
       <c r="AH31" s="1"/>
       <c r="AI31" s="1"/>
     </row>
@@ -4025,7 +4046,7 @@
       <c r="AD32" s="1"/>
       <c r="AE32" s="29"/>
       <c r="AF32" s="1"/>
-      <c r="AG32" s="1"/>
+      <c r="AG32" s="29"/>
       <c r="AH32" s="1"/>
       <c r="AI32" s="1"/>
     </row>
@@ -4066,7 +4087,7 @@
       <c r="AD33" s="1"/>
       <c r="AE33" s="29"/>
       <c r="AF33" s="1"/>
-      <c r="AG33" s="1"/>
+      <c r="AG33" s="29"/>
       <c r="AH33" s="1"/>
       <c r="AI33" s="1"/>
     </row>
@@ -4107,7 +4128,7 @@
       <c r="AD34" s="1"/>
       <c r="AE34" s="29"/>
       <c r="AF34" s="1"/>
-      <c r="AG34" s="1"/>
+      <c r="AG34" s="29"/>
       <c r="AH34" s="1"/>
       <c r="AI34" s="1"/>
     </row>
@@ -4148,7 +4169,7 @@
       <c r="AD35" s="1"/>
       <c r="AE35" s="29"/>
       <c r="AF35" s="1"/>
-      <c r="AG35" s="1"/>
+      <c r="AG35" s="29"/>
       <c r="AH35" s="1"/>
       <c r="AI35" s="1"/>
     </row>
@@ -4189,7 +4210,7 @@
       <c r="AD36" s="1"/>
       <c r="AE36" s="29"/>
       <c r="AF36" s="1"/>
-      <c r="AG36" s="1"/>
+      <c r="AG36" s="29"/>
       <c r="AH36" s="1"/>
       <c r="AI36" s="1"/>
     </row>
@@ -4230,7 +4251,7 @@
       <c r="AD37" s="1"/>
       <c r="AE37" s="29"/>
       <c r="AF37" s="1"/>
-      <c r="AG37" s="1"/>
+      <c r="AG37" s="29"/>
       <c r="AH37" s="1"/>
       <c r="AI37" s="1"/>
     </row>
@@ -4271,7 +4292,7 @@
       <c r="AD38" s="1"/>
       <c r="AE38" s="29"/>
       <c r="AF38" s="1"/>
-      <c r="AG38" s="1"/>
+      <c r="AG38" s="29"/>
       <c r="AH38" s="1"/>
       <c r="AI38" s="1"/>
     </row>
@@ -4314,7 +4335,7 @@
       <c r="AD39" s="1"/>
       <c r="AE39" s="29"/>
       <c r="AF39" s="1"/>
-      <c r="AG39" s="1"/>
+      <c r="AG39" s="29"/>
       <c r="AH39" s="1"/>
       <c r="AI39" s="1"/>
     </row>
@@ -4357,7 +4378,7 @@
       <c r="AD40" s="1"/>
       <c r="AE40" s="29"/>
       <c r="AF40" s="1"/>
-      <c r="AG40" s="1"/>
+      <c r="AG40" s="29"/>
       <c r="AH40" s="1"/>
       <c r="AI40" s="1"/>
     </row>
@@ -4400,7 +4421,7 @@
       <c r="AD41" s="1"/>
       <c r="AE41" s="29"/>
       <c r="AF41" s="1"/>
-      <c r="AG41" s="1"/>
+      <c r="AG41" s="29"/>
       <c r="AH41" s="1"/>
       <c r="AI41" s="1"/>
     </row>
@@ -4441,7 +4462,7 @@
       <c r="AD42" s="1"/>
       <c r="AE42" s="29"/>
       <c r="AF42" s="1"/>
-      <c r="AG42" s="1"/>
+      <c r="AG42" s="29"/>
       <c r="AH42" s="1"/>
       <c r="AI42" s="1"/>
     </row>
@@ -4484,7 +4505,7 @@
       <c r="AD43" s="1"/>
       <c r="AE43" s="29"/>
       <c r="AF43" s="1"/>
-      <c r="AG43" s="1"/>
+      <c r="AG43" s="29"/>
       <c r="AH43" s="1"/>
       <c r="AI43" s="1"/>
     </row>
@@ -4525,7 +4546,7 @@
       <c r="AD44" s="1"/>
       <c r="AE44" s="29"/>
       <c r="AF44" s="1"/>
-      <c r="AG44" s="1"/>
+      <c r="AG44" s="29"/>
       <c r="AH44" s="1"/>
       <c r="AI44" s="1"/>
     </row>
@@ -4566,7 +4587,7 @@
       <c r="AD45" s="1"/>
       <c r="AE45" s="29"/>
       <c r="AF45" s="1"/>
-      <c r="AG45" s="1"/>
+      <c r="AG45" s="29"/>
       <c r="AH45" s="1"/>
       <c r="AI45" s="1"/>
     </row>
@@ -4607,7 +4628,7 @@
       <c r="AD46" s="1"/>
       <c r="AE46" s="29"/>
       <c r="AF46" s="1"/>
-      <c r="AG46" s="1"/>
+      <c r="AG46" s="29"/>
       <c r="AH46" s="1"/>
       <c r="AI46" s="1"/>
     </row>
@@ -4648,7 +4669,7 @@
       <c r="AD47" s="1"/>
       <c r="AE47" s="29"/>
       <c r="AF47" s="1"/>
-      <c r="AG47" s="1"/>
+      <c r="AG47" s="29"/>
       <c r="AH47" s="1"/>
       <c r="AI47" s="1"/>
     </row>
@@ -4691,7 +4712,7 @@
       <c r="AD48" s="1"/>
       <c r="AE48" s="29"/>
       <c r="AF48" s="1"/>
-      <c r="AG48" s="1"/>
+      <c r="AG48" s="29"/>
       <c r="AH48" s="1"/>
       <c r="AI48" s="1"/>
     </row>
@@ -4732,7 +4753,7 @@
       <c r="AD49" s="1"/>
       <c r="AE49" s="29"/>
       <c r="AF49" s="1"/>
-      <c r="AG49" s="1"/>
+      <c r="AG49" s="29"/>
       <c r="AH49" s="1"/>
       <c r="AI49" s="1"/>
     </row>
@@ -4775,7 +4796,7 @@
       <c r="AD50" s="1"/>
       <c r="AE50" s="29"/>
       <c r="AF50" s="1"/>
-      <c r="AG50" s="1"/>
+      <c r="AG50" s="29"/>
       <c r="AH50" s="1"/>
       <c r="AI50" s="1"/>
     </row>
@@ -4816,7 +4837,7 @@
       <c r="AD51" s="1"/>
       <c r="AE51" s="29"/>
       <c r="AF51" s="1"/>
-      <c r="AG51" s="1"/>
+      <c r="AG51" s="29"/>
       <c r="AH51" s="1"/>
       <c r="AI51" s="1"/>
     </row>
@@ -4857,7 +4878,7 @@
       <c r="AD52" s="1"/>
       <c r="AE52" s="29"/>
       <c r="AF52" s="1"/>
-      <c r="AG52" s="1"/>
+      <c r="AG52" s="29"/>
       <c r="AH52" s="1"/>
       <c r="AI52" s="1"/>
     </row>
@@ -4898,7 +4919,7 @@
       <c r="AD53" s="1"/>
       <c r="AE53" s="29"/>
       <c r="AF53" s="1"/>
-      <c r="AG53" s="1"/>
+      <c r="AG53" s="29"/>
       <c r="AH53" s="1"/>
       <c r="AI53" s="1"/>
     </row>
@@ -4941,7 +4962,7 @@
       <c r="AD54" s="1"/>
       <c r="AE54" s="29"/>
       <c r="AF54" s="1"/>
-      <c r="AG54" s="1"/>
+      <c r="AG54" s="29"/>
       <c r="AH54" s="1"/>
       <c r="AI54" s="1"/>
     </row>
@@ -4984,7 +5005,7 @@
       <c r="AD55" s="1"/>
       <c r="AE55" s="29"/>
       <c r="AF55" s="1"/>
-      <c r="AG55" s="1"/>
+      <c r="AG55" s="29"/>
       <c r="AH55" s="1"/>
       <c r="AI55" s="1"/>
     </row>
@@ -5025,7 +5046,7 @@
       <c r="AD56" s="1"/>
       <c r="AE56" s="29"/>
       <c r="AF56" s="1"/>
-      <c r="AG56" s="1"/>
+      <c r="AG56" s="29"/>
       <c r="AH56" s="1"/>
       <c r="AI56" s="1"/>
     </row>
@@ -5066,7 +5087,7 @@
       <c r="AD57" s="1"/>
       <c r="AE57" s="29"/>
       <c r="AF57" s="1"/>
-      <c r="AG57" s="1"/>
+      <c r="AG57" s="29"/>
       <c r="AH57" s="1"/>
       <c r="AI57" s="1"/>
     </row>
@@ -5107,7 +5128,7 @@
       <c r="AD58" s="1"/>
       <c r="AE58" s="29"/>
       <c r="AF58" s="1"/>
-      <c r="AG58" s="1"/>
+      <c r="AG58" s="29"/>
       <c r="AH58" s="1"/>
       <c r="AI58" s="1"/>
     </row>
@@ -5148,7 +5169,7 @@
       <c r="AD59" s="1"/>
       <c r="AE59" s="29"/>
       <c r="AF59" s="1"/>
-      <c r="AG59" s="1"/>
+      <c r="AG59" s="29"/>
       <c r="AH59" s="1"/>
       <c r="AI59" s="1"/>
     </row>
@@ -5189,7 +5210,7 @@
       <c r="AD60" s="1"/>
       <c r="AE60" s="29"/>
       <c r="AF60" s="1"/>
-      <c r="AG60" s="1"/>
+      <c r="AG60" s="29"/>
       <c r="AH60" s="1"/>
       <c r="AI60" s="1"/>
     </row>
@@ -5230,7 +5251,7 @@
       <c r="AD61" s="1"/>
       <c r="AE61" s="29"/>
       <c r="AF61" s="1"/>
-      <c r="AG61" s="1"/>
+      <c r="AG61" s="29"/>
       <c r="AH61" s="1"/>
       <c r="AI61" s="1"/>
     </row>
@@ -5271,7 +5292,7 @@
       <c r="AD62" s="1"/>
       <c r="AE62" s="29"/>
       <c r="AF62" s="1"/>
-      <c r="AG62" s="1"/>
+      <c r="AG62" s="29"/>
       <c r="AH62" s="1"/>
       <c r="AI62" s="1"/>
     </row>
@@ -5314,7 +5335,7 @@
       <c r="AD63" s="1"/>
       <c r="AE63" s="29"/>
       <c r="AF63" s="1"/>
-      <c r="AG63" s="1"/>
+      <c r="AG63" s="29"/>
       <c r="AH63" s="1"/>
       <c r="AI63" s="1"/>
     </row>
@@ -5359,7 +5380,7 @@
       <c r="AD64" s="1"/>
       <c r="AE64" s="29"/>
       <c r="AF64" s="1"/>
-      <c r="AG64" s="1"/>
+      <c r="AG64" s="29"/>
       <c r="AH64" s="1"/>
       <c r="AI64" s="1"/>
     </row>
@@ -5402,7 +5423,7 @@
       <c r="AD65" s="1"/>
       <c r="AE65" s="29"/>
       <c r="AF65" s="1"/>
-      <c r="AG65" s="1"/>
+      <c r="AG65" s="29"/>
       <c r="AH65" s="1"/>
       <c r="AI65" s="1"/>
     </row>
@@ -5443,7 +5464,7 @@
       <c r="AD66" s="1"/>
       <c r="AE66" s="29"/>
       <c r="AF66" s="1"/>
-      <c r="AG66" s="1"/>
+      <c r="AG66" s="29"/>
       <c r="AH66" s="1"/>
       <c r="AI66" s="1"/>
     </row>
@@ -5488,7 +5509,7 @@
       <c r="AD67" s="1"/>
       <c r="AE67" s="29"/>
       <c r="AF67" s="1"/>
-      <c r="AG67" s="1"/>
+      <c r="AG67" s="29"/>
       <c r="AH67" s="1"/>
       <c r="AI67" s="1"/>
     </row>
@@ -5531,7 +5552,7 @@
       <c r="AD68" s="1"/>
       <c r="AE68" s="29"/>
       <c r="AF68" s="1"/>
-      <c r="AG68" s="1"/>
+      <c r="AG68" s="29"/>
       <c r="AH68" s="1"/>
       <c r="AI68" s="1"/>
     </row>
@@ -5576,7 +5597,7 @@
       <c r="AD69" s="1"/>
       <c r="AE69" s="29"/>
       <c r="AF69" s="1"/>
-      <c r="AG69" s="1"/>
+      <c r="AG69" s="29"/>
       <c r="AH69" s="1"/>
       <c r="AI69" s="1"/>
     </row>
@@ -5619,7 +5640,7 @@
       <c r="AD70" s="1"/>
       <c r="AE70" s="29"/>
       <c r="AF70" s="1"/>
-      <c r="AG70" s="1"/>
+      <c r="AG70" s="29"/>
       <c r="AH70" s="1"/>
       <c r="AI70" s="1"/>
     </row>
@@ -5662,7 +5683,7 @@
       <c r="AD71" s="1"/>
       <c r="AE71" s="29"/>
       <c r="AF71" s="1"/>
-      <c r="AG71" s="1"/>
+      <c r="AG71" s="29"/>
       <c r="AH71" s="1"/>
       <c r="AI71" s="1"/>
     </row>
@@ -5703,7 +5724,7 @@
       <c r="AD72" s="1"/>
       <c r="AE72" s="29"/>
       <c r="AF72" s="1"/>
-      <c r="AG72" s="1"/>
+      <c r="AG72" s="29"/>
       <c r="AH72" s="1"/>
       <c r="AI72" s="1"/>
     </row>
@@ -5744,7 +5765,7 @@
       <c r="AD73" s="1"/>
       <c r="AE73" s="29"/>
       <c r="AF73" s="1"/>
-      <c r="AG73" s="1"/>
+      <c r="AG73" s="29"/>
       <c r="AH73" s="1"/>
       <c r="AI73" s="1"/>
     </row>
@@ -5785,7 +5806,7 @@
       <c r="AD74" s="1"/>
       <c r="AE74" s="29"/>
       <c r="AF74" s="1"/>
-      <c r="AG74" s="1"/>
+      <c r="AG74" s="29"/>
       <c r="AH74" s="1"/>
       <c r="AI74" s="1"/>
     </row>
@@ -5826,7 +5847,7 @@
       <c r="AD75" s="1"/>
       <c r="AE75" s="29"/>
       <c r="AF75" s="1"/>
-      <c r="AG75" s="1"/>
+      <c r="AG75" s="29"/>
       <c r="AH75" s="1"/>
       <c r="AI75" s="1"/>
     </row>
@@ -5871,7 +5892,7 @@
       <c r="AD76" s="1"/>
       <c r="AE76" s="29"/>
       <c r="AF76" s="1"/>
-      <c r="AG76" s="1"/>
+      <c r="AG76" s="29"/>
       <c r="AH76" s="1"/>
       <c r="AI76" s="1"/>
     </row>
@@ -5914,7 +5935,7 @@
       <c r="AD77" s="1"/>
       <c r="AE77" s="29"/>
       <c r="AF77" s="1"/>
-      <c r="AG77" s="1"/>
+      <c r="AG77" s="29"/>
       <c r="AH77" s="1"/>
       <c r="AI77" s="1"/>
     </row>
@@ -5957,7 +5978,7 @@
       <c r="AD78" s="1"/>
       <c r="AE78" s="29"/>
       <c r="AF78" s="1"/>
-      <c r="AG78" s="1"/>
+      <c r="AG78" s="29"/>
       <c r="AH78" s="1"/>
       <c r="AI78" s="1"/>
     </row>
@@ -6000,7 +6021,7 @@
       <c r="AD79" s="1"/>
       <c r="AE79" s="29"/>
       <c r="AF79" s="1"/>
-      <c r="AG79" s="1"/>
+      <c r="AG79" s="29"/>
       <c r="AH79" s="1"/>
       <c r="AI79" s="1"/>
     </row>
@@ -6043,7 +6064,7 @@
       <c r="AD80" s="1"/>
       <c r="AE80" s="29"/>
       <c r="AF80" s="1"/>
-      <c r="AG80" s="1"/>
+      <c r="AG80" s="29"/>
       <c r="AH80" s="1"/>
       <c r="AI80" s="1"/>
     </row>
@@ -6088,7 +6109,7 @@
       <c r="AD81" s="1"/>
       <c r="AE81" s="29"/>
       <c r="AF81" s="1"/>
-      <c r="AG81" s="1"/>
+      <c r="AG81" s="29"/>
       <c r="AH81" s="1"/>
       <c r="AI81" s="1"/>
     </row>
@@ -6133,7 +6154,7 @@
       <c r="AD82" s="1"/>
       <c r="AE82" s="29"/>
       <c r="AF82" s="1"/>
-      <c r="AG82" s="1"/>
+      <c r="AG82" s="29"/>
       <c r="AH82" s="1"/>
       <c r="AI82" s="1"/>
     </row>
@@ -6178,7 +6199,7 @@
       <c r="AD83" s="1"/>
       <c r="AE83" s="29"/>
       <c r="AF83" s="1"/>
-      <c r="AG83" s="1"/>
+      <c r="AG83" s="29"/>
       <c r="AH83" s="1"/>
       <c r="AI83" s="1"/>
     </row>
@@ -6221,7 +6242,7 @@
       <c r="AD84" s="1"/>
       <c r="AE84" s="29"/>
       <c r="AF84" s="1"/>
-      <c r="AG84" s="1"/>
+      <c r="AG84" s="29"/>
       <c r="AH84" s="1"/>
       <c r="AI84" s="1"/>
     </row>
@@ -6262,7 +6283,7 @@
       <c r="AD85" s="1"/>
       <c r="AE85" s="29"/>
       <c r="AF85" s="1"/>
-      <c r="AG85" s="1"/>
+      <c r="AG85" s="29"/>
       <c r="AH85" s="1"/>
       <c r="AI85" s="1"/>
     </row>
@@ -6303,7 +6324,7 @@
       <c r="AD86" s="1"/>
       <c r="AE86" s="29"/>
       <c r="AF86" s="1"/>
-      <c r="AG86" s="1"/>
+      <c r="AG86" s="29"/>
       <c r="AH86" s="1"/>
       <c r="AI86" s="1"/>
     </row>
@@ -6344,7 +6365,7 @@
       <c r="AD87" s="1"/>
       <c r="AE87" s="29"/>
       <c r="AF87" s="1"/>
-      <c r="AG87" s="1"/>
+      <c r="AG87" s="29"/>
       <c r="AH87" s="1"/>
       <c r="AI87" s="1"/>
     </row>
@@ -6387,7 +6408,7 @@
       <c r="AD88" s="1"/>
       <c r="AE88" s="29"/>
       <c r="AF88" s="1"/>
-      <c r="AG88" s="1"/>
+      <c r="AG88" s="29"/>
       <c r="AH88" s="1"/>
       <c r="AI88" s="1"/>
     </row>
@@ -6428,7 +6449,7 @@
       <c r="AD89" s="1"/>
       <c r="AE89" s="29"/>
       <c r="AF89" s="1"/>
-      <c r="AG89" s="1"/>
+      <c r="AG89" s="29"/>
       <c r="AH89" s="1"/>
       <c r="AI89" s="1"/>
     </row>
@@ -6469,7 +6490,7 @@
       <c r="AD90" s="1"/>
       <c r="AE90" s="29"/>
       <c r="AF90" s="1"/>
-      <c r="AG90" s="1"/>
+      <c r="AG90" s="29"/>
       <c r="AH90" s="1"/>
       <c r="AI90" s="1"/>
     </row>
@@ -6512,7 +6533,7 @@
       <c r="AD91" s="1"/>
       <c r="AE91" s="29"/>
       <c r="AF91" s="1"/>
-      <c r="AG91" s="1"/>
+      <c r="AG91" s="29"/>
       <c r="AH91" s="1"/>
       <c r="AI91" s="1"/>
     </row>
@@ -6555,7 +6576,7 @@
       <c r="AD92" s="1"/>
       <c r="AE92" s="29"/>
       <c r="AF92" s="1"/>
-      <c r="AG92" s="1"/>
+      <c r="AG92" s="29"/>
       <c r="AH92" s="1"/>
       <c r="AI92" s="1"/>
     </row>
@@ -6596,7 +6617,7 @@
       <c r="AD93" s="1"/>
       <c r="AE93" s="29"/>
       <c r="AF93" s="1"/>
-      <c r="AG93" s="1"/>
+      <c r="AG93" s="29"/>
       <c r="AH93" s="1"/>
       <c r="AI93" s="1"/>
     </row>
@@ -6637,7 +6658,7 @@
       <c r="AD94" s="1"/>
       <c r="AE94" s="29"/>
       <c r="AF94" s="1"/>
-      <c r="AG94" s="1"/>
+      <c r="AG94" s="29"/>
       <c r="AH94" s="1"/>
       <c r="AI94" s="1"/>
     </row>
@@ -6678,7 +6699,7 @@
       <c r="AD95" s="1"/>
       <c r="AE95" s="29"/>
       <c r="AF95" s="1"/>
-      <c r="AG95" s="1"/>
+      <c r="AG95" s="29"/>
       <c r="AH95" s="1"/>
       <c r="AI95" s="1"/>
     </row>
@@ -6719,7 +6740,7 @@
       <c r="AD96" s="1"/>
       <c r="AE96" s="29"/>
       <c r="AF96" s="1"/>
-      <c r="AG96" s="1"/>
+      <c r="AG96" s="29"/>
       <c r="AH96" s="1"/>
       <c r="AI96" s="1"/>
     </row>
@@ -6760,7 +6781,7 @@
       <c r="AD97" s="1"/>
       <c r="AE97" s="29"/>
       <c r="AF97" s="1"/>
-      <c r="AG97" s="1"/>
+      <c r="AG97" s="29"/>
       <c r="AH97" s="1"/>
       <c r="AI97" s="1"/>
     </row>
@@ -6803,7 +6824,7 @@
       <c r="AD98" s="1"/>
       <c r="AE98" s="29"/>
       <c r="AF98" s="1"/>
-      <c r="AG98" s="1"/>
+      <c r="AG98" s="29"/>
       <c r="AH98" s="1"/>
       <c r="AI98" s="1"/>
     </row>
@@ -6844,7 +6865,7 @@
       <c r="AD99" s="1"/>
       <c r="AE99" s="29"/>
       <c r="AF99" s="1"/>
-      <c r="AG99" s="1"/>
+      <c r="AG99" s="29"/>
       <c r="AH99" s="1"/>
       <c r="AI99" s="1"/>
     </row>
@@ -6885,7 +6906,7 @@
       <c r="AD100" s="1"/>
       <c r="AE100" s="29"/>
       <c r="AF100" s="1"/>
-      <c r="AG100" s="1"/>
+      <c r="AG100" s="29"/>
       <c r="AH100" s="1"/>
       <c r="AI100" s="1"/>
     </row>
@@ -6926,7 +6947,7 @@
       <c r="AD101" s="1"/>
       <c r="AE101" s="29"/>
       <c r="AF101" s="1"/>
-      <c r="AG101" s="1"/>
+      <c r="AG101" s="29"/>
       <c r="AH101" s="1"/>
       <c r="AI101" s="1"/>
     </row>
@@ -6967,7 +6988,7 @@
       <c r="AD102" s="1"/>
       <c r="AE102" s="29"/>
       <c r="AF102" s="1"/>
-      <c r="AG102" s="1"/>
+      <c r="AG102" s="29"/>
       <c r="AH102" s="1"/>
       <c r="AI102" s="1"/>
     </row>
@@ -7008,7 +7029,7 @@
       <c r="AD103" s="1"/>
       <c r="AE103" s="29"/>
       <c r="AF103" s="1"/>
-      <c r="AG103" s="1"/>
+      <c r="AG103" s="29"/>
       <c r="AH103" s="1"/>
       <c r="AI103" s="1"/>
     </row>
@@ -7049,7 +7070,7 @@
       <c r="AD104" s="1"/>
       <c r="AE104" s="29"/>
       <c r="AF104" s="1"/>
-      <c r="AG104" s="1"/>
+      <c r="AG104" s="29"/>
       <c r="AH104" s="1"/>
       <c r="AI104" s="1"/>
     </row>
@@ -7092,7 +7113,7 @@
       <c r="AD105" s="1"/>
       <c r="AE105" s="29"/>
       <c r="AF105" s="1"/>
-      <c r="AG105" s="1"/>
+      <c r="AG105" s="29"/>
       <c r="AH105" s="1"/>
       <c r="AI105" s="1"/>
     </row>
@@ -7133,7 +7154,7 @@
       <c r="AD106" s="1"/>
       <c r="AE106" s="29"/>
       <c r="AF106" s="1"/>
-      <c r="AG106" s="1"/>
+      <c r="AG106" s="29"/>
       <c r="AH106" s="1"/>
       <c r="AI106" s="1"/>
     </row>
@@ -7176,7 +7197,7 @@
       <c r="AD107" s="1"/>
       <c r="AE107" s="29"/>
       <c r="AF107" s="1"/>
-      <c r="AG107" s="1"/>
+      <c r="AG107" s="29"/>
       <c r="AH107" s="1"/>
       <c r="AI107" s="1"/>
     </row>
@@ -7217,7 +7238,7 @@
       <c r="AD108" s="1"/>
       <c r="AE108" s="29"/>
       <c r="AF108" s="1"/>
-      <c r="AG108" s="1"/>
+      <c r="AG108" s="29"/>
       <c r="AH108" s="1"/>
       <c r="AI108" s="1"/>
     </row>
@@ -7260,7 +7281,7 @@
       <c r="AD109" s="1"/>
       <c r="AE109" s="29"/>
       <c r="AF109" s="1"/>
-      <c r="AG109" s="1"/>
+      <c r="AG109" s="29"/>
       <c r="AH109" s="1"/>
       <c r="AI109" s="1"/>
     </row>
@@ -7301,7 +7322,7 @@
       <c r="AD110" s="1"/>
       <c r="AE110" s="29"/>
       <c r="AF110" s="1"/>
-      <c r="AG110" s="1"/>
+      <c r="AG110" s="29"/>
       <c r="AH110" s="1"/>
       <c r="AI110" s="1"/>
     </row>
@@ -7342,7 +7363,7 @@
       <c r="AD111" s="1"/>
       <c r="AE111" s="29"/>
       <c r="AF111" s="1"/>
-      <c r="AG111" s="1"/>
+      <c r="AG111" s="29"/>
       <c r="AH111" s="1"/>
       <c r="AI111" s="1"/>
     </row>
@@ -7389,7 +7410,7 @@
       <c r="AD112" s="1"/>
       <c r="AE112" s="29"/>
       <c r="AF112" s="1"/>
-      <c r="AG112" s="1"/>
+      <c r="AG112" s="29"/>
       <c r="AH112" s="1"/>
       <c r="AI112" s="1"/>
     </row>
@@ -7432,7 +7453,7 @@
       <c r="AD113" s="1"/>
       <c r="AE113" s="29"/>
       <c r="AF113" s="1"/>
-      <c r="AG113" s="1"/>
+      <c r="AG113" s="29"/>
       <c r="AH113" s="1"/>
       <c r="AI113" s="1"/>
     </row>
@@ -7473,7 +7494,7 @@
       <c r="AD114" s="1"/>
       <c r="AE114" s="29"/>
       <c r="AF114" s="1"/>
-      <c r="AG114" s="1"/>
+      <c r="AG114" s="29"/>
       <c r="AH114" s="1"/>
       <c r="AI114" s="1"/>
     </row>
@@ -7516,7 +7537,7 @@
       <c r="AD115" s="1"/>
       <c r="AE115" s="29"/>
       <c r="AF115" s="1"/>
-      <c r="AG115" s="1"/>
+      <c r="AG115" s="29"/>
       <c r="AH115" s="1"/>
       <c r="AI115" s="1"/>
     </row>
@@ -7557,7 +7578,7 @@
       <c r="AD116" s="1"/>
       <c r="AE116" s="29"/>
       <c r="AF116" s="1"/>
-      <c r="AG116" s="1"/>
+      <c r="AG116" s="29"/>
       <c r="AH116" s="1"/>
       <c r="AI116" s="1"/>
     </row>
@@ -7598,7 +7619,7 @@
       <c r="AD117" s="1"/>
       <c r="AE117" s="29"/>
       <c r="AF117" s="1"/>
-      <c r="AG117" s="1"/>
+      <c r="AG117" s="29"/>
       <c r="AH117" s="1"/>
       <c r="AI117" s="1"/>
     </row>
@@ -7639,7 +7660,7 @@
       <c r="AD118" s="1"/>
       <c r="AE118" s="29"/>
       <c r="AF118" s="1"/>
-      <c r="AG118" s="1"/>
+      <c r="AG118" s="29"/>
       <c r="AH118" s="1"/>
       <c r="AI118" s="1"/>
     </row>
@@ -7680,7 +7701,7 @@
       <c r="AD119" s="1"/>
       <c r="AE119" s="29"/>
       <c r="AF119" s="1"/>
-      <c r="AG119" s="1"/>
+      <c r="AG119" s="29"/>
       <c r="AH119" s="1"/>
       <c r="AI119" s="1"/>
     </row>
@@ -7721,7 +7742,7 @@
       <c r="AD120" s="1"/>
       <c r="AE120" s="29"/>
       <c r="AF120" s="1"/>
-      <c r="AG120" s="1"/>
+      <c r="AG120" s="29"/>
       <c r="AH120" s="1"/>
       <c r="AI120" s="1"/>
     </row>
@@ -7762,7 +7783,7 @@
       <c r="AD121" s="1"/>
       <c r="AE121" s="29"/>
       <c r="AF121" s="1"/>
-      <c r="AG121" s="1"/>
+      <c r="AG121" s="29"/>
       <c r="AH121" s="1"/>
       <c r="AI121" s="1"/>
     </row>
@@ -7803,7 +7824,7 @@
       <c r="AD122" s="1"/>
       <c r="AE122" s="29"/>
       <c r="AF122" s="1"/>
-      <c r="AG122" s="1"/>
+      <c r="AG122" s="29"/>
       <c r="AH122" s="1"/>
       <c r="AI122" s="1"/>
     </row>
@@ -7844,7 +7865,7 @@
       <c r="AD123" s="1"/>
       <c r="AE123" s="29"/>
       <c r="AF123" s="1"/>
-      <c r="AG123" s="1"/>
+      <c r="AG123" s="29"/>
       <c r="AH123" s="1"/>
       <c r="AI123" s="1"/>
     </row>
@@ -7885,7 +7906,7 @@
       <c r="AD124" s="1"/>
       <c r="AE124" s="29"/>
       <c r="AF124" s="1"/>
-      <c r="AG124" s="1"/>
+      <c r="AG124" s="29"/>
       <c r="AH124" s="1"/>
       <c r="AI124" s="1"/>
     </row>
@@ -7926,7 +7947,7 @@
       <c r="AD125" s="1"/>
       <c r="AE125" s="29"/>
       <c r="AF125" s="1"/>
-      <c r="AG125" s="1"/>
+      <c r="AG125" s="29"/>
       <c r="AH125" s="1"/>
       <c r="AI125" s="1"/>
     </row>
@@ -7969,7 +7990,7 @@
       <c r="AD126" s="1"/>
       <c r="AE126" s="29"/>
       <c r="AF126" s="1"/>
-      <c r="AG126" s="1"/>
+      <c r="AG126" s="29"/>
       <c r="AH126" s="1"/>
       <c r="AI126" s="1"/>
     </row>
@@ -8010,7 +8031,7 @@
       <c r="AD127" s="1"/>
       <c r="AE127" s="29"/>
       <c r="AF127" s="1"/>
-      <c r="AG127" s="1"/>
+      <c r="AG127" s="29"/>
       <c r="AH127" s="1"/>
       <c r="AI127" s="1"/>
     </row>
@@ -8055,7 +8076,7 @@
       <c r="AD128" s="1"/>
       <c r="AE128" s="29"/>
       <c r="AF128" s="1"/>
-      <c r="AG128" s="1"/>
+      <c r="AG128" s="29"/>
       <c r="AH128" s="1"/>
       <c r="AI128" s="1"/>
     </row>
@@ -8098,7 +8119,7 @@
       <c r="AD129" s="1"/>
       <c r="AE129" s="29"/>
       <c r="AF129" s="1"/>
-      <c r="AG129" s="1"/>
+      <c r="AG129" s="29"/>
       <c r="AH129" s="1"/>
       <c r="AI129" s="1"/>
     </row>
@@ -8143,7 +8164,7 @@
       <c r="AD130" s="1"/>
       <c r="AE130" s="29"/>
       <c r="AF130" s="1"/>
-      <c r="AG130" s="1"/>
+      <c r="AG130" s="29"/>
       <c r="AH130" s="1"/>
       <c r="AI130" s="1"/>
     </row>
@@ -8186,7 +8207,7 @@
       <c r="AD131" s="1"/>
       <c r="AE131" s="29"/>
       <c r="AF131" s="1"/>
-      <c r="AG131" s="1"/>
+      <c r="AG131" s="29"/>
       <c r="AH131" s="1"/>
       <c r="AI131" s="1"/>
     </row>
@@ -8227,7 +8248,7 @@
       <c r="AD132" s="1"/>
       <c r="AE132" s="29"/>
       <c r="AF132" s="1"/>
-      <c r="AG132" s="1"/>
+      <c r="AG132" s="29"/>
       <c r="AH132" s="1"/>
       <c r="AI132" s="1"/>
     </row>
@@ -8268,7 +8289,7 @@
       <c r="AD133" s="1"/>
       <c r="AE133" s="29"/>
       <c r="AF133" s="1"/>
-      <c r="AG133" s="1"/>
+      <c r="AG133" s="29"/>
       <c r="AH133" s="1"/>
       <c r="AI133" s="1"/>
     </row>
@@ -8309,7 +8330,7 @@
       <c r="AD134" s="1"/>
       <c r="AE134" s="29"/>
       <c r="AF134" s="1"/>
-      <c r="AG134" s="1"/>
+      <c r="AG134" s="29"/>
       <c r="AH134" s="1"/>
       <c r="AI134" s="1"/>
     </row>
@@ -8350,7 +8371,7 @@
       <c r="AD135" s="1"/>
       <c r="AE135" s="29"/>
       <c r="AF135" s="1"/>
-      <c r="AG135" s="1"/>
+      <c r="AG135" s="29"/>
       <c r="AH135" s="1"/>
       <c r="AI135" s="1"/>
     </row>
@@ -8391,7 +8412,7 @@
       <c r="AD136" s="1"/>
       <c r="AE136" s="29"/>
       <c r="AF136" s="1"/>
-      <c r="AG136" s="1"/>
+      <c r="AG136" s="29"/>
       <c r="AH136" s="1"/>
       <c r="AI136" s="1"/>
     </row>
@@ -8432,7 +8453,7 @@
       <c r="AD137" s="1"/>
       <c r="AE137" s="29"/>
       <c r="AF137" s="1"/>
-      <c r="AG137" s="1"/>
+      <c r="AG137" s="29"/>
       <c r="AH137" s="1"/>
       <c r="AI137" s="1"/>
     </row>
@@ -8473,7 +8494,7 @@
       <c r="AD138" s="1"/>
       <c r="AE138" s="29"/>
       <c r="AF138" s="1"/>
-      <c r="AG138" s="1"/>
+      <c r="AG138" s="29"/>
       <c r="AH138" s="1"/>
       <c r="AI138" s="1"/>
     </row>
@@ -8514,7 +8535,7 @@
       <c r="AD139" s="1"/>
       <c r="AE139" s="29"/>
       <c r="AF139" s="1"/>
-      <c r="AG139" s="1"/>
+      <c r="AG139" s="29"/>
       <c r="AH139" s="1"/>
       <c r="AI139" s="1"/>
     </row>
@@ -8555,7 +8576,7 @@
       <c r="AD140" s="1"/>
       <c r="AE140" s="29"/>
       <c r="AF140" s="1"/>
-      <c r="AG140" s="1"/>
+      <c r="AG140" s="29"/>
       <c r="AH140" s="1"/>
       <c r="AI140" s="1"/>
     </row>
@@ -8596,7 +8617,7 @@
       <c r="AD141" s="1"/>
       <c r="AE141" s="29"/>
       <c r="AF141" s="1"/>
-      <c r="AG141" s="1"/>
+      <c r="AG141" s="29"/>
       <c r="AH141" s="1"/>
       <c r="AI141" s="1"/>
     </row>
@@ -8637,7 +8658,7 @@
       <c r="AD142" s="1"/>
       <c r="AE142" s="29"/>
       <c r="AF142" s="1"/>
-      <c r="AG142" s="1"/>
+      <c r="AG142" s="29"/>
       <c r="AH142" s="1"/>
       <c r="AI142" s="1"/>
     </row>
@@ -8678,7 +8699,7 @@
       <c r="AD143" s="1"/>
       <c r="AE143" s="29"/>
       <c r="AF143" s="1"/>
-      <c r="AG143" s="1"/>
+      <c r="AG143" s="29"/>
       <c r="AH143" s="1"/>
       <c r="AI143" s="1"/>
     </row>
@@ -8719,7 +8740,7 @@
       <c r="AD144" s="1"/>
       <c r="AE144" s="29"/>
       <c r="AF144" s="1"/>
-      <c r="AG144" s="1"/>
+      <c r="AG144" s="29"/>
       <c r="AH144" s="1"/>
       <c r="AI144" s="1"/>
     </row>
@@ -8760,7 +8781,7 @@
       <c r="AD145" s="1"/>
       <c r="AE145" s="29"/>
       <c r="AF145" s="1"/>
-      <c r="AG145" s="1"/>
+      <c r="AG145" s="29"/>
       <c r="AH145" s="1"/>
       <c r="AI145" s="1"/>
     </row>
@@ -8801,7 +8822,7 @@
       <c r="AD146" s="1"/>
       <c r="AE146" s="29"/>
       <c r="AF146" s="1"/>
-      <c r="AG146" s="1"/>
+      <c r="AG146" s="29"/>
       <c r="AH146" s="1"/>
       <c r="AI146" s="1"/>
     </row>
@@ -8842,7 +8863,7 @@
       <c r="AD147" s="1"/>
       <c r="AE147" s="29"/>
       <c r="AF147" s="1"/>
-      <c r="AG147" s="1"/>
+      <c r="AG147" s="29"/>
       <c r="AH147" s="1"/>
       <c r="AI147" s="1"/>
     </row>
@@ -8885,7 +8906,7 @@
       <c r="AD148" s="1"/>
       <c r="AE148" s="29"/>
       <c r="AF148" s="1"/>
-      <c r="AG148" s="1"/>
+      <c r="AG148" s="29"/>
       <c r="AH148" s="1"/>
       <c r="AI148" s="1"/>
     </row>
@@ -8926,7 +8947,7 @@
       <c r="AD149" s="1"/>
       <c r="AE149" s="29"/>
       <c r="AF149" s="1"/>
-      <c r="AG149" s="1"/>
+      <c r="AG149" s="29"/>
       <c r="AH149" s="1"/>
       <c r="AI149" s="1"/>
     </row>
@@ -8967,7 +8988,7 @@
       <c r="AD150" s="1"/>
       <c r="AE150" s="29"/>
       <c r="AF150" s="1"/>
-      <c r="AG150" s="1"/>
+      <c r="AG150" s="29"/>
       <c r="AH150" s="1"/>
       <c r="AI150" s="1"/>
     </row>
@@ -9008,7 +9029,7 @@
       <c r="AD151" s="1"/>
       <c r="AE151" s="29"/>
       <c r="AF151" s="1"/>
-      <c r="AG151" s="1"/>
+      <c r="AG151" s="29"/>
       <c r="AH151" s="1"/>
       <c r="AI151" s="1"/>
     </row>
@@ -9049,7 +9070,7 @@
       <c r="AD152" s="1"/>
       <c r="AE152" s="29"/>
       <c r="AF152" s="1"/>
-      <c r="AG152" s="1"/>
+      <c r="AG152" s="29"/>
       <c r="AH152" s="1"/>
       <c r="AI152" s="1"/>
     </row>
@@ -9092,7 +9113,7 @@
       <c r="AD153" s="1"/>
       <c r="AE153" s="29"/>
       <c r="AF153" s="1"/>
-      <c r="AG153" s="1"/>
+      <c r="AG153" s="29"/>
       <c r="AH153" s="1"/>
       <c r="AI153" s="1"/>
     </row>
@@ -9135,7 +9156,7 @@
       <c r="AD154" s="1"/>
       <c r="AE154" s="29"/>
       <c r="AF154" s="1"/>
-      <c r="AG154" s="1"/>
+      <c r="AG154" s="29"/>
       <c r="AH154" s="1"/>
       <c r="AI154" s="1"/>
     </row>
@@ -9180,7 +9201,7 @@
       <c r="AD155" s="1"/>
       <c r="AE155" s="29"/>
       <c r="AF155" s="1"/>
-      <c r="AG155" s="1"/>
+      <c r="AG155" s="29"/>
       <c r="AH155" s="1"/>
       <c r="AI155" s="1"/>
     </row>
@@ -9223,7 +9244,7 @@
       <c r="AD156" s="1"/>
       <c r="AE156" s="29"/>
       <c r="AF156" s="1"/>
-      <c r="AG156" s="1"/>
+      <c r="AG156" s="29"/>
       <c r="AH156" s="1"/>
       <c r="AI156" s="1"/>
     </row>
@@ -9266,7 +9287,7 @@
       <c r="AD157" s="1"/>
       <c r="AE157" s="29"/>
       <c r="AF157" s="1"/>
-      <c r="AG157" s="1"/>
+      <c r="AG157" s="29"/>
       <c r="AH157" s="1"/>
       <c r="AI157" s="1"/>
     </row>
@@ -9311,7 +9332,7 @@
       <c r="AD158" s="1"/>
       <c r="AE158" s="29"/>
       <c r="AF158" s="1"/>
-      <c r="AG158" s="1"/>
+      <c r="AG158" s="29"/>
       <c r="AH158" s="1"/>
       <c r="AI158" s="1"/>
     </row>
@@ -9354,7 +9375,7 @@
       <c r="AD159" s="1"/>
       <c r="AE159" s="29"/>
       <c r="AF159" s="1"/>
-      <c r="AG159" s="1"/>
+      <c r="AG159" s="29"/>
       <c r="AH159" s="1"/>
       <c r="AI159" s="1"/>
     </row>
@@ -9399,7 +9420,7 @@
       <c r="AD160" s="1"/>
       <c r="AE160" s="29"/>
       <c r="AF160" s="1"/>
-      <c r="AG160" s="1"/>
+      <c r="AG160" s="29"/>
       <c r="AH160" s="1"/>
       <c r="AI160" s="1"/>
     </row>
@@ -9442,7 +9463,7 @@
       <c r="AD161" s="1"/>
       <c r="AE161" s="29"/>
       <c r="AF161" s="1"/>
-      <c r="AG161" s="1"/>
+      <c r="AG161" s="29"/>
       <c r="AH161" s="1"/>
       <c r="AI161" s="1"/>
     </row>
@@ -9485,7 +9506,7 @@
       <c r="AD162" s="1"/>
       <c r="AE162" s="29"/>
       <c r="AF162" s="1"/>
-      <c r="AG162" s="1"/>
+      <c r="AG162" s="29"/>
       <c r="AH162" s="1"/>
       <c r="AI162" s="1"/>
     </row>
@@ -9530,7 +9551,7 @@
       <c r="AD163" s="1"/>
       <c r="AE163" s="29"/>
       <c r="AF163" s="1"/>
-      <c r="AG163" s="1"/>
+      <c r="AG163" s="29"/>
       <c r="AH163" s="1"/>
       <c r="AI163" s="1"/>
     </row>
@@ -9573,7 +9594,7 @@
       <c r="AD164" s="3"/>
       <c r="AE164" s="30"/>
       <c r="AF164" s="3"/>
-      <c r="AG164" s="3"/>
+      <c r="AG164" s="30"/>
       <c r="AH164" s="3"/>
       <c r="AI164" s="3"/>
     </row>
@@ -9616,7 +9637,7 @@
       <c r="AD165" s="3"/>
       <c r="AE165" s="30"/>
       <c r="AF165" s="3"/>
-      <c r="AG165" s="3"/>
+      <c r="AG165" s="30"/>
       <c r="AH165" s="3"/>
       <c r="AI165" s="3"/>
     </row>
@@ -9657,7 +9678,7 @@
       <c r="AD166" s="1"/>
       <c r="AE166" s="29"/>
       <c r="AF166" s="1"/>
-      <c r="AG166" s="1"/>
+      <c r="AG166" s="29"/>
       <c r="AH166" s="1"/>
       <c r="AI166" s="1"/>
     </row>
@@ -9698,7 +9719,7 @@
       <c r="AD167" s="1"/>
       <c r="AE167" s="29"/>
       <c r="AF167" s="1"/>
-      <c r="AG167" s="1"/>
+      <c r="AG167" s="29"/>
       <c r="AH167" s="1"/>
       <c r="AI167" s="1"/>
     </row>
@@ -9739,7 +9760,7 @@
       <c r="AD168" s="1"/>
       <c r="AE168" s="29"/>
       <c r="AF168" s="1"/>
-      <c r="AG168" s="1"/>
+      <c r="AG168" s="29"/>
       <c r="AH168" s="1"/>
       <c r="AI168" s="1"/>
     </row>
@@ -9780,7 +9801,7 @@
       <c r="AD169" s="1"/>
       <c r="AE169" s="29"/>
       <c r="AF169" s="1"/>
-      <c r="AG169" s="1"/>
+      <c r="AG169" s="29"/>
       <c r="AH169" s="1"/>
       <c r="AI169" s="1"/>
     </row>
@@ -9821,7 +9842,7 @@
       <c r="AD170" s="1"/>
       <c r="AE170" s="29"/>
       <c r="AF170" s="1"/>
-      <c r="AG170" s="1"/>
+      <c r="AG170" s="29"/>
       <c r="AH170" s="1"/>
       <c r="AI170" s="1"/>
     </row>
@@ -9862,7 +9883,7 @@
       <c r="AD171" s="1"/>
       <c r="AE171" s="29"/>
       <c r="AF171" s="1"/>
-      <c r="AG171" s="1"/>
+      <c r="AG171" s="29"/>
       <c r="AH171" s="1"/>
       <c r="AI171" s="1"/>
     </row>
@@ -9905,7 +9926,7 @@
       <c r="AD172" s="1"/>
       <c r="AE172" s="29"/>
       <c r="AF172" s="1"/>
-      <c r="AG172" s="1"/>
+      <c r="AG172" s="29"/>
       <c r="AH172" s="1"/>
       <c r="AI172" s="1"/>
     </row>
@@ -9946,7 +9967,7 @@
       <c r="AD173" s="1"/>
       <c r="AE173" s="29"/>
       <c r="AF173" s="1"/>
-      <c r="AG173" s="1"/>
+      <c r="AG173" s="29"/>
       <c r="AH173" s="1"/>
       <c r="AI173" s="1"/>
     </row>
@@ -9997,7 +10018,7 @@
       <c r="AD174" s="1"/>
       <c r="AE174" s="29"/>
       <c r="AF174" s="1"/>
-      <c r="AG174" s="1"/>
+      <c r="AG174" s="29"/>
       <c r="AH174" s="1"/>
       <c r="AI174" s="1"/>
     </row>
@@ -10044,7 +10065,7 @@
       <c r="AD175" s="1"/>
       <c r="AE175" s="29"/>
       <c r="AF175" s="1"/>
-      <c r="AG175" s="1"/>
+      <c r="AG175" s="29"/>
       <c r="AH175" s="1"/>
       <c r="AI175" s="1"/>
     </row>
@@ -10095,7 +10116,7 @@
       <c r="AD176" s="1"/>
       <c r="AE176" s="29"/>
       <c r="AF176" s="1"/>
-      <c r="AG176" s="1"/>
+      <c r="AG176" s="29"/>
       <c r="AH176" s="1"/>
       <c r="AI176" s="1"/>
     </row>
@@ -10140,7 +10161,7 @@
       <c r="AD177" s="1"/>
       <c r="AE177" s="29"/>
       <c r="AF177" s="1"/>
-      <c r="AG177" s="1"/>
+      <c r="AG177" s="29"/>
       <c r="AH177" s="1"/>
       <c r="AI177" s="1"/>
     </row>
@@ -10185,7 +10206,7 @@
       <c r="AD178" s="1"/>
       <c r="AE178" s="29"/>
       <c r="AF178" s="1"/>
-      <c r="AG178" s="1"/>
+      <c r="AG178" s="29"/>
       <c r="AH178" s="1"/>
       <c r="AI178" s="1"/>
     </row>
@@ -10230,7 +10251,7 @@
       <c r="AD179" s="1"/>
       <c r="AE179" s="29"/>
       <c r="AF179" s="1"/>
-      <c r="AG179" s="1"/>
+      <c r="AG179" s="29"/>
       <c r="AH179" s="1"/>
       <c r="AI179" s="1"/>
     </row>
@@ -10277,7 +10298,7 @@
       <c r="AD180" s="1"/>
       <c r="AE180" s="29"/>
       <c r="AF180" s="1"/>
-      <c r="AG180" s="1"/>
+      <c r="AG180" s="29"/>
       <c r="AH180" s="1"/>
       <c r="AI180" s="1"/>
     </row>
@@ -10322,7 +10343,7 @@
       <c r="AD181" s="1"/>
       <c r="AE181" s="29"/>
       <c r="AF181" s="1"/>
-      <c r="AG181" s="1"/>
+      <c r="AG181" s="29"/>
       <c r="AH181" s="1"/>
       <c r="AI181" s="1"/>
     </row>
@@ -10369,7 +10390,7 @@
       <c r="AD182" s="1"/>
       <c r="AE182" s="29"/>
       <c r="AF182" s="1"/>
-      <c r="AG182" s="1"/>
+      <c r="AG182" s="29"/>
       <c r="AH182" s="1"/>
       <c r="AI182" s="1"/>
     </row>
@@ -10418,7 +10439,7 @@
       <c r="AD183" s="1"/>
       <c r="AE183" s="29"/>
       <c r="AF183" s="1"/>
-      <c r="AG183" s="1"/>
+      <c r="AG183" s="29"/>
       <c r="AH183" s="1"/>
       <c r="AI183" s="1"/>
     </row>
@@ -10467,7 +10488,7 @@
       <c r="AD184" s="1"/>
       <c r="AE184" s="29"/>
       <c r="AF184" s="1"/>
-      <c r="AG184" s="1"/>
+      <c r="AG184" s="29"/>
       <c r="AH184" s="1"/>
       <c r="AI184" s="1"/>
     </row>
@@ -10514,7 +10535,7 @@
       <c r="AD185" s="1"/>
       <c r="AE185" s="29"/>
       <c r="AF185" s="1"/>
-      <c r="AG185" s="1"/>
+      <c r="AG185" s="29"/>
       <c r="AH185" s="1"/>
       <c r="AI185" s="1"/>
     </row>
@@ -10565,7 +10586,7 @@
       <c r="AD186" s="1"/>
       <c r="AE186" s="29"/>
       <c r="AF186" s="1"/>
-      <c r="AG186" s="1"/>
+      <c r="AG186" s="29"/>
       <c r="AH186" s="1"/>
       <c r="AI186" s="1"/>
     </row>
@@ -10616,7 +10637,7 @@
       <c r="AD187" s="1"/>
       <c r="AE187" s="29"/>
       <c r="AF187" s="1"/>
-      <c r="AG187" s="1"/>
+      <c r="AG187" s="29"/>
       <c r="AH187" s="1"/>
       <c r="AI187" s="1"/>
     </row>
@@ -10669,7 +10690,7 @@
       <c r="AD188" s="1"/>
       <c r="AE188" s="29"/>
       <c r="AF188" s="1"/>
-      <c r="AG188" s="1"/>
+      <c r="AG188" s="29"/>
       <c r="AH188" s="1"/>
       <c r="AI188" s="1"/>
     </row>
@@ -10720,7 +10741,7 @@
       <c r="AD189" s="1"/>
       <c r="AE189" s="29"/>
       <c r="AF189" s="1"/>
-      <c r="AG189" s="1"/>
+      <c r="AG189" s="29"/>
       <c r="AH189" s="1"/>
       <c r="AI189" s="1"/>
     </row>
@@ -10771,7 +10792,7 @@
       <c r="AD190" s="1"/>
       <c r="AE190" s="29"/>
       <c r="AF190" s="1"/>
-      <c r="AG190" s="1"/>
+      <c r="AG190" s="29"/>
       <c r="AH190" s="1"/>
       <c r="AI190" s="1"/>
     </row>
@@ -10822,7 +10843,7 @@
       <c r="AD191" s="1"/>
       <c r="AE191" s="29"/>
       <c r="AF191" s="1"/>
-      <c r="AG191" s="1"/>
+      <c r="AG191" s="29"/>
       <c r="AH191" s="1"/>
       <c r="AI191" s="1"/>
     </row>
@@ -10867,7 +10888,7 @@
       <c r="AD192" s="1"/>
       <c r="AE192" s="29"/>
       <c r="AF192" s="1"/>
-      <c r="AG192" s="1"/>
+      <c r="AG192" s="29"/>
       <c r="AH192" s="1"/>
       <c r="AI192" s="1"/>
     </row>
@@ -10912,7 +10933,7 @@
       <c r="AD193" s="1"/>
       <c r="AE193" s="29"/>
       <c r="AF193" s="1"/>
-      <c r="AG193" s="1"/>
+      <c r="AG193" s="29"/>
       <c r="AH193" s="1"/>
       <c r="AI193" s="1"/>
     </row>
@@ -10955,7 +10976,7 @@
       <c r="AD194" s="1"/>
       <c r="AE194" s="29"/>
       <c r="AF194" s="1"/>
-      <c r="AG194" s="1"/>
+      <c r="AG194" s="29"/>
       <c r="AH194" s="1"/>
       <c r="AI194" s="1"/>
     </row>
@@ -10998,7 +11019,7 @@
       <c r="AD195" s="1"/>
       <c r="AE195" s="29"/>
       <c r="AF195" s="1"/>
-      <c r="AG195" s="1"/>
+      <c r="AG195" s="29"/>
       <c r="AH195" s="1"/>
       <c r="AI195" s="1"/>
     </row>
@@ -11041,7 +11062,7 @@
       <c r="AD196" s="1"/>
       <c r="AE196" s="29"/>
       <c r="AF196" s="1"/>
-      <c r="AG196" s="1"/>
+      <c r="AG196" s="29"/>
       <c r="AH196" s="1"/>
       <c r="AI196" s="1"/>
     </row>
@@ -11084,7 +11105,7 @@
       <c r="AD197" s="1"/>
       <c r="AE197" s="29"/>
       <c r="AF197" s="1"/>
-      <c r="AG197" s="1"/>
+      <c r="AG197" s="29"/>
       <c r="AH197" s="1"/>
       <c r="AI197" s="1"/>
     </row>
@@ -11129,7 +11150,7 @@
       <c r="AD198" s="1"/>
       <c r="AE198" s="29"/>
       <c r="AF198" s="1"/>
-      <c r="AG198" s="1"/>
+      <c r="AG198" s="29"/>
       <c r="AH198" s="1"/>
       <c r="AI198" s="1"/>
     </row>
@@ -11174,7 +11195,7 @@
       <c r="AD199" s="1"/>
       <c r="AE199" s="29"/>
       <c r="AF199" s="1"/>
-      <c r="AG199" s="1"/>
+      <c r="AG199" s="29"/>
       <c r="AH199" s="1"/>
       <c r="AI199" s="1"/>
     </row>
@@ -11217,7 +11238,7 @@
       <c r="AD200" s="1"/>
       <c r="AE200" s="29"/>
       <c r="AF200" s="1"/>
-      <c r="AG200" s="1"/>
+      <c r="AG200" s="29"/>
       <c r="AH200" s="1"/>
       <c r="AI200" s="1"/>
     </row>
@@ -11262,7 +11283,7 @@
       <c r="AD201" s="1"/>
       <c r="AE201" s="29"/>
       <c r="AF201" s="1"/>
-      <c r="AG201" s="1"/>
+      <c r="AG201" s="29"/>
       <c r="AH201" s="1"/>
       <c r="AI201" s="1"/>
     </row>
@@ -11305,7 +11326,7 @@
       <c r="AD202" s="1"/>
       <c r="AE202" s="29"/>
       <c r="AF202" s="1"/>
-      <c r="AG202" s="1"/>
+      <c r="AG202" s="29"/>
       <c r="AH202" s="1"/>
       <c r="AI202" s="1"/>
     </row>
@@ -11350,7 +11371,7 @@
       <c r="AD203" s="1"/>
       <c r="AE203" s="29"/>
       <c r="AF203" s="1"/>
-      <c r="AG203" s="1"/>
+      <c r="AG203" s="29"/>
       <c r="AH203" s="1"/>
       <c r="AI203" s="1"/>
     </row>
@@ -11393,7 +11414,7 @@
       <c r="AD204" s="1"/>
       <c r="AE204" s="29"/>
       <c r="AF204" s="1"/>
-      <c r="AG204" s="1"/>
+      <c r="AG204" s="29"/>
       <c r="AH204" s="1"/>
       <c r="AI204" s="1"/>
     </row>
@@ -11436,7 +11457,7 @@
       <c r="AD205" s="1"/>
       <c r="AE205" s="29"/>
       <c r="AF205" s="1"/>
-      <c r="AG205" s="1"/>
+      <c r="AG205" s="29"/>
       <c r="AH205" s="1"/>
       <c r="AI205" s="1"/>
     </row>
@@ -11479,7 +11500,7 @@
       <c r="AD206" s="1"/>
       <c r="AE206" s="29"/>
       <c r="AF206" s="1"/>
-      <c r="AG206" s="1"/>
+      <c r="AG206" s="29"/>
       <c r="AH206" s="1"/>
       <c r="AI206" s="1"/>
     </row>
@@ -11524,7 +11545,7 @@
       <c r="AD207" s="1"/>
       <c r="AE207" s="29"/>
       <c r="AF207" s="1"/>
-      <c r="AG207" s="1"/>
+      <c r="AG207" s="29"/>
       <c r="AH207" s="1"/>
       <c r="AI207" s="1"/>
     </row>
@@ -11567,7 +11588,7 @@
       <c r="AD208" s="1"/>
       <c r="AE208" s="29"/>
       <c r="AF208" s="1"/>
-      <c r="AG208" s="1"/>
+      <c r="AG208" s="29"/>
       <c r="AH208" s="1"/>
       <c r="AI208" s="1"/>
     </row>
@@ -11610,7 +11631,7 @@
       <c r="AD209" s="1"/>
       <c r="AE209" s="29"/>
       <c r="AF209" s="1"/>
-      <c r="AG209" s="1"/>
+      <c r="AG209" s="29"/>
       <c r="AH209" s="1"/>
       <c r="AI209" s="1"/>
     </row>
@@ -11653,7 +11674,7 @@
       <c r="AD210" s="1"/>
       <c r="AE210" s="29"/>
       <c r="AF210" s="1"/>
-      <c r="AG210" s="1"/>
+      <c r="AG210" s="29"/>
       <c r="AH210" s="1"/>
       <c r="AI210" s="1"/>
     </row>
@@ -11696,7 +11717,7 @@
       <c r="AD211" s="1"/>
       <c r="AE211" s="29"/>
       <c r="AF211" s="1"/>
-      <c r="AG211" s="1"/>
+      <c r="AG211" s="29"/>
       <c r="AH211" s="1"/>
       <c r="AI211" s="1"/>
     </row>
@@ -11739,7 +11760,7 @@
       <c r="AD212" s="1"/>
       <c r="AE212" s="29"/>
       <c r="AF212" s="1"/>
-      <c r="AG212" s="1"/>
+      <c r="AG212" s="29"/>
       <c r="AH212" s="1"/>
       <c r="AI212" s="1"/>
     </row>
@@ -11782,7 +11803,7 @@
       <c r="AD213" s="1"/>
       <c r="AE213" s="29"/>
       <c r="AF213" s="1"/>
-      <c r="AG213" s="1"/>
+      <c r="AG213" s="29"/>
       <c r="AH213" s="1"/>
       <c r="AI213" s="1"/>
     </row>
@@ -11825,7 +11846,7 @@
       <c r="AD214" s="1"/>
       <c r="AE214" s="29"/>
       <c r="AF214" s="1"/>
-      <c r="AG214" s="1"/>
+      <c r="AG214" s="29"/>
       <c r="AH214" s="1"/>
       <c r="AI214" s="1"/>
     </row>
@@ -11868,7 +11889,7 @@
       <c r="AD215" s="1"/>
       <c r="AE215" s="29"/>
       <c r="AF215" s="1"/>
-      <c r="AG215" s="1"/>
+      <c r="AG215" s="29"/>
       <c r="AH215" s="1"/>
       <c r="AI215" s="1"/>
     </row>
@@ -11915,7 +11936,7 @@
       <c r="AD216" s="1"/>
       <c r="AE216" s="29"/>
       <c r="AF216" s="1"/>
-      <c r="AG216" s="1"/>
+      <c r="AG216" s="29"/>
       <c r="AH216" s="1"/>
       <c r="AI216" s="1"/>
     </row>
@@ -11962,7 +11983,7 @@
       <c r="AD217" s="1"/>
       <c r="AE217" s="29"/>
       <c r="AF217" s="1"/>
-      <c r="AG217" s="1"/>
+      <c r="AG217" s="29"/>
       <c r="AH217" s="1"/>
       <c r="AI217" s="1"/>
     </row>
@@ -12009,7 +12030,7 @@
       <c r="AD218" s="1"/>
       <c r="AE218" s="29"/>
       <c r="AF218" s="1"/>
-      <c r="AG218" s="1"/>
+      <c r="AG218" s="29"/>
       <c r="AH218" s="1"/>
       <c r="AI218" s="1"/>
     </row>
@@ -12050,7 +12071,7 @@
       <c r="AD219" s="1"/>
       <c r="AE219" s="29"/>
       <c r="AF219" s="1"/>
-      <c r="AG219" s="1"/>
+      <c r="AG219" s="29"/>
       <c r="AH219" s="1"/>
       <c r="AI219" s="1"/>
     </row>
@@ -12091,7 +12112,7 @@
       <c r="AD220" s="1"/>
       <c r="AE220" s="29"/>
       <c r="AF220" s="1"/>
-      <c r="AG220" s="1"/>
+      <c r="AG220" s="29"/>
       <c r="AH220" s="1"/>
       <c r="AI220" s="1"/>
     </row>
@@ -12132,7 +12153,7 @@
       <c r="AD221" s="1"/>
       <c r="AE221" s="29"/>
       <c r="AF221" s="1"/>
-      <c r="AG221" s="1"/>
+      <c r="AG221" s="29"/>
       <c r="AH221" s="1"/>
       <c r="AI221" s="1"/>
     </row>
@@ -12175,7 +12196,7 @@
       <c r="AD222" s="1"/>
       <c r="AE222" s="29"/>
       <c r="AF222" s="1"/>
-      <c r="AG222" s="1"/>
+      <c r="AG222" s="29"/>
       <c r="AH222" s="1"/>
       <c r="AI222" s="1"/>
     </row>
@@ -12216,7 +12237,7 @@
       <c r="AD223" s="1"/>
       <c r="AE223" s="29"/>
       <c r="AF223" s="1"/>
-      <c r="AG223" s="1"/>
+      <c r="AG223" s="29"/>
       <c r="AH223" s="1"/>
       <c r="AI223" s="1"/>
     </row>
@@ -12257,7 +12278,7 @@
       <c r="AD224" s="1"/>
       <c r="AE224" s="29"/>
       <c r="AF224" s="1"/>
-      <c r="AG224" s="1"/>
+      <c r="AG224" s="29"/>
       <c r="AH224" s="1"/>
       <c r="AI224" s="1"/>
     </row>
@@ -12298,7 +12319,7 @@
       <c r="AD225" s="1"/>
       <c r="AE225" s="29"/>
       <c r="AF225" s="1"/>
-      <c r="AG225" s="1"/>
+      <c r="AG225" s="29"/>
       <c r="AH225" s="1"/>
       <c r="AI225" s="1"/>
     </row>
@@ -12339,7 +12360,7 @@
       <c r="AD226" s="1"/>
       <c r="AE226" s="29"/>
       <c r="AF226" s="1"/>
-      <c r="AG226" s="1"/>
+      <c r="AG226" s="29"/>
       <c r="AH226" s="1"/>
       <c r="AI226" s="1"/>
     </row>
@@ -12380,7 +12401,7 @@
       <c r="AD227" s="1"/>
       <c r="AE227" s="29"/>
       <c r="AF227" s="1"/>
-      <c r="AG227" s="1"/>
+      <c r="AG227" s="29"/>
       <c r="AH227" s="1"/>
       <c r="AI227" s="1"/>
     </row>
@@ -12421,7 +12442,7 @@
       <c r="AD228" s="1"/>
       <c r="AE228" s="29"/>
       <c r="AF228" s="1"/>
-      <c r="AG228" s="1"/>
+      <c r="AG228" s="29"/>
       <c r="AH228" s="1"/>
       <c r="AI228" s="1"/>
     </row>
@@ -12462,7 +12483,7 @@
       <c r="AD229" s="1"/>
       <c r="AE229" s="29"/>
       <c r="AF229" s="1"/>
-      <c r="AG229" s="1"/>
+      <c r="AG229" s="29"/>
       <c r="AH229" s="1"/>
       <c r="AI229" s="1"/>
     </row>
@@ -12503,7 +12524,7 @@
       <c r="AD230" s="1"/>
       <c r="AE230" s="29"/>
       <c r="AF230" s="1"/>
-      <c r="AG230" s="1"/>
+      <c r="AG230" s="29"/>
       <c r="AH230" s="1"/>
       <c r="AI230" s="1"/>
     </row>
@@ -12544,7 +12565,7 @@
       <c r="AD231" s="1"/>
       <c r="AE231" s="29"/>
       <c r="AF231" s="1"/>
-      <c r="AG231" s="1"/>
+      <c r="AG231" s="29"/>
       <c r="AH231" s="1"/>
       <c r="AI231" s="1"/>
     </row>
@@ -12585,7 +12606,7 @@
       <c r="AD232" s="1"/>
       <c r="AE232" s="29"/>
       <c r="AF232" s="1"/>
-      <c r="AG232" s="1"/>
+      <c r="AG232" s="29"/>
       <c r="AH232" s="1"/>
       <c r="AI232" s="1"/>
     </row>
@@ -12628,7 +12649,7 @@
       <c r="AD233" s="1"/>
       <c r="AE233" s="29"/>
       <c r="AF233" s="1"/>
-      <c r="AG233" s="1"/>
+      <c r="AG233" s="29"/>
       <c r="AH233" s="1"/>
       <c r="AI233" s="1"/>
     </row>
@@ -12669,7 +12690,7 @@
       <c r="AD234" s="1"/>
       <c r="AE234" s="29"/>
       <c r="AF234" s="1"/>
-      <c r="AG234" s="1"/>
+      <c r="AG234" s="29"/>
       <c r="AH234" s="1"/>
       <c r="AI234" s="1"/>
     </row>
@@ -12712,7 +12733,7 @@
       <c r="AD235" s="1"/>
       <c r="AE235" s="29"/>
       <c r="AF235" s="1"/>
-      <c r="AG235" s="1"/>
+      <c r="AG235" s="29"/>
       <c r="AH235" s="1"/>
       <c r="AI235" s="1"/>
     </row>
@@ -12753,7 +12774,7 @@
       <c r="AD236" s="1"/>
       <c r="AE236" s="29"/>
       <c r="AF236" s="1"/>
-      <c r="AG236" s="1"/>
+      <c r="AG236" s="29"/>
       <c r="AH236" s="1"/>
       <c r="AI236" s="1"/>
     </row>
@@ -12794,7 +12815,7 @@
       <c r="AD237" s="1"/>
       <c r="AE237" s="29"/>
       <c r="AF237" s="1"/>
-      <c r="AG237" s="1"/>
+      <c r="AG237" s="29"/>
       <c r="AH237" s="1"/>
       <c r="AI237" s="1"/>
     </row>
@@ -12835,7 +12856,7 @@
       <c r="AD238" s="1"/>
       <c r="AE238" s="29"/>
       <c r="AF238" s="1"/>
-      <c r="AG238" s="1"/>
+      <c r="AG238" s="29"/>
       <c r="AH238" s="1"/>
       <c r="AI238" s="1"/>
     </row>
@@ -12876,7 +12897,7 @@
       <c r="AD239" s="1"/>
       <c r="AE239" s="29"/>
       <c r="AF239" s="1"/>
-      <c r="AG239" s="1"/>
+      <c r="AG239" s="29"/>
       <c r="AH239" s="1"/>
       <c r="AI239" s="1"/>
     </row>
@@ -12917,7 +12938,7 @@
       <c r="AD240" s="1"/>
       <c r="AE240" s="29"/>
       <c r="AF240" s="1"/>
-      <c r="AG240" s="1"/>
+      <c r="AG240" s="29"/>
       <c r="AH240" s="1"/>
       <c r="AI240" s="1"/>
     </row>
@@ -12958,7 +12979,7 @@
       <c r="AD241" s="1"/>
       <c r="AE241" s="29"/>
       <c r="AF241" s="1"/>
-      <c r="AG241" s="1"/>
+      <c r="AG241" s="29"/>
       <c r="AH241" s="1"/>
       <c r="AI241" s="1"/>
     </row>
@@ -12999,7 +13020,7 @@
       <c r="AD242" s="1"/>
       <c r="AE242" s="29"/>
       <c r="AF242" s="1"/>
-      <c r="AG242" s="1"/>
+      <c r="AG242" s="29"/>
       <c r="AH242" s="1"/>
       <c r="AI242" s="1"/>
     </row>
@@ -13042,7 +13063,7 @@
       <c r="AD243" s="1"/>
       <c r="AE243" s="29"/>
       <c r="AF243" s="1"/>
-      <c r="AG243" s="1"/>
+      <c r="AG243" s="29"/>
       <c r="AH243" s="1"/>
       <c r="AI243" s="1"/>
     </row>
@@ -13085,7 +13106,7 @@
       <c r="AD244" s="1"/>
       <c r="AE244" s="29"/>
       <c r="AF244" s="1"/>
-      <c r="AG244" s="1"/>
+      <c r="AG244" s="29"/>
       <c r="AH244" s="1"/>
       <c r="AI244" s="1"/>
     </row>
@@ -13128,7 +13149,7 @@
       <c r="AD245" s="1"/>
       <c r="AE245" s="29"/>
       <c r="AF245" s="1"/>
-      <c r="AG245" s="1"/>
+      <c r="AG245" s="29"/>
       <c r="AH245" s="1"/>
       <c r="AI245" s="1"/>
     </row>
@@ -13171,7 +13192,7 @@
       <c r="AD246" s="1"/>
       <c r="AE246" s="29"/>
       <c r="AF246" s="1"/>
-      <c r="AG246" s="1"/>
+      <c r="AG246" s="29"/>
       <c r="AH246" s="1"/>
       <c r="AI246" s="1"/>
     </row>
@@ -13214,7 +13235,7 @@
       <c r="AD247" s="1"/>
       <c r="AE247" s="29"/>
       <c r="AF247" s="1"/>
-      <c r="AG247" s="1"/>
+      <c r="AG247" s="29"/>
       <c r="AH247" s="1"/>
       <c r="AI247" s="1"/>
     </row>
@@ -13257,7 +13278,7 @@
       <c r="AD248" s="1"/>
       <c r="AE248" s="29"/>
       <c r="AF248" s="1"/>
-      <c r="AG248" s="1"/>
+      <c r="AG248" s="29"/>
       <c r="AH248" s="1"/>
       <c r="AI248" s="1"/>
     </row>
@@ -13298,7 +13319,7 @@
       <c r="AD249" s="1"/>
       <c r="AE249" s="29"/>
       <c r="AF249" s="1"/>
-      <c r="AG249" s="1"/>
+      <c r="AG249" s="29"/>
       <c r="AH249" s="1"/>
       <c r="AI249" s="1"/>
     </row>
@@ -13339,7 +13360,7 @@
       <c r="AD250" s="1"/>
       <c r="AE250" s="29"/>
       <c r="AF250" s="1"/>
-      <c r="AG250" s="1"/>
+      <c r="AG250" s="29"/>
       <c r="AH250" s="1"/>
       <c r="AI250" s="1"/>
     </row>
@@ -13380,7 +13401,7 @@
       <c r="AD251" s="1"/>
       <c r="AE251" s="29"/>
       <c r="AF251" s="1"/>
-      <c r="AG251" s="1"/>
+      <c r="AG251" s="29"/>
       <c r="AH251" s="1"/>
       <c r="AI251" s="1"/>
     </row>
@@ -13421,7 +13442,7 @@
       <c r="AD252" s="1"/>
       <c r="AE252" s="29"/>
       <c r="AF252" s="1"/>
-      <c r="AG252" s="1"/>
+      <c r="AG252" s="29"/>
       <c r="AH252" s="1"/>
       <c r="AI252" s="1"/>
     </row>
@@ -13462,7 +13483,7 @@
       <c r="AD253" s="1"/>
       <c r="AE253" s="29"/>
       <c r="AF253" s="1"/>
-      <c r="AG253" s="1"/>
+      <c r="AG253" s="29"/>
       <c r="AH253" s="1"/>
       <c r="AI253" s="1"/>
     </row>
@@ -13503,7 +13524,7 @@
       <c r="AD254" s="1"/>
       <c r="AE254" s="29"/>
       <c r="AF254" s="1"/>
-      <c r="AG254" s="1"/>
+      <c r="AG254" s="29"/>
       <c r="AH254" s="1"/>
       <c r="AI254" s="1"/>
     </row>
@@ -13544,7 +13565,7 @@
       <c r="AD255" s="1"/>
       <c r="AE255" s="29"/>
       <c r="AF255" s="1"/>
-      <c r="AG255" s="1"/>
+      <c r="AG255" s="29"/>
       <c r="AH255" s="1"/>
       <c r="AI255" s="1"/>
     </row>
@@ -13583,7 +13604,7 @@
       <c r="AD256" s="1"/>
       <c r="AE256" s="29"/>
       <c r="AF256" s="1"/>
-      <c r="AG256" s="1"/>
+      <c r="AG256" s="29"/>
       <c r="AH256" s="1"/>
       <c r="AI256" s="1"/>
     </row>
@@ -13622,7 +13643,7 @@
       <c r="AD257" s="1"/>
       <c r="AE257" s="29"/>
       <c r="AF257" s="1"/>
-      <c r="AG257" s="1"/>
+      <c r="AG257" s="29"/>
       <c r="AH257" s="1"/>
       <c r="AI257" s="1"/>
     </row>
@@ -13661,7 +13682,7 @@
       <c r="AD258" s="1"/>
       <c r="AE258" s="29"/>
       <c r="AF258" s="1"/>
-      <c r="AG258" s="1"/>
+      <c r="AG258" s="29"/>
       <c r="AH258" s="1"/>
       <c r="AI258" s="1"/>
     </row>
@@ -13700,7 +13721,7 @@
       <c r="AD259" s="1"/>
       <c r="AE259" s="29"/>
       <c r="AF259" s="1"/>
-      <c r="AG259" s="1"/>
+      <c r="AG259" s="29"/>
       <c r="AH259" s="1"/>
       <c r="AI259" s="1"/>
     </row>
@@ -13739,7 +13760,7 @@
       <c r="AD260" s="1"/>
       <c r="AE260" s="29"/>
       <c r="AF260" s="1"/>
-      <c r="AG260" s="1"/>
+      <c r="AG260" s="29"/>
       <c r="AH260" s="1"/>
       <c r="AI260" s="1"/>
     </row>
@@ -13778,7 +13799,7 @@
       <c r="AD261" s="1"/>
       <c r="AE261" s="29"/>
       <c r="AF261" s="1"/>
-      <c r="AG261" s="1"/>
+      <c r="AG261" s="29"/>
       <c r="AH261" s="1"/>
       <c r="AI261" s="1"/>
     </row>
@@ -13817,7 +13838,7 @@
       <c r="AD262" s="1"/>
       <c r="AE262" s="29"/>
       <c r="AF262" s="1"/>
-      <c r="AG262" s="1"/>
+      <c r="AG262" s="29"/>
       <c r="AH262" s="1"/>
       <c r="AI262" s="1"/>
     </row>
@@ -13856,7 +13877,7 @@
       <c r="AD263" s="1"/>
       <c r="AE263" s="29"/>
       <c r="AF263" s="1"/>
-      <c r="AG263" s="1"/>
+      <c r="AG263" s="29"/>
       <c r="AH263" s="1"/>
       <c r="AI263" s="1"/>
     </row>
@@ -13895,7 +13916,7 @@
       <c r="AD264" s="1"/>
       <c r="AE264" s="29"/>
       <c r="AF264" s="1"/>
-      <c r="AG264" s="1"/>
+      <c r="AG264" s="29"/>
       <c r="AH264" s="1"/>
       <c r="AI264" s="1"/>
     </row>
@@ -13934,7 +13955,7 @@
       <c r="AD265" s="1"/>
       <c r="AE265" s="29"/>
       <c r="AF265" s="1"/>
-      <c r="AG265" s="1"/>
+      <c r="AG265" s="29"/>
       <c r="AH265" s="1"/>
       <c r="AI265" s="1"/>
     </row>
@@ -13973,7 +13994,7 @@
       <c r="AD266" s="1"/>
       <c r="AE266" s="29"/>
       <c r="AF266" s="1"/>
-      <c r="AG266" s="1"/>
+      <c r="AG266" s="29"/>
       <c r="AH266" s="1"/>
       <c r="AI266" s="1"/>
     </row>
@@ -14012,7 +14033,7 @@
       <c r="AD267" s="1"/>
       <c r="AE267" s="29"/>
       <c r="AF267" s="1"/>
-      <c r="AG267" s="1"/>
+      <c r="AG267" s="29"/>
       <c r="AH267" s="1"/>
       <c r="AI267" s="1"/>
     </row>
@@ -14051,7 +14072,7 @@
       <c r="AD268" s="1"/>
       <c r="AE268" s="29"/>
       <c r="AF268" s="1"/>
-      <c r="AG268" s="1"/>
+      <c r="AG268" s="29"/>
       <c r="AH268" s="1"/>
       <c r="AI268" s="1"/>
     </row>
@@ -14090,7 +14111,7 @@
       <c r="AD269" s="1"/>
       <c r="AE269" s="29"/>
       <c r="AF269" s="1"/>
-      <c r="AG269" s="1"/>
+      <c r="AG269" s="29"/>
       <c r="AH269" s="1"/>
       <c r="AI269" s="1"/>
     </row>
@@ -14129,7 +14150,7 @@
       <c r="AD270" s="1"/>
       <c r="AE270" s="29"/>
       <c r="AF270" s="1"/>
-      <c r="AG270" s="1"/>
+      <c r="AG270" s="29"/>
       <c r="AH270" s="1"/>
       <c r="AI270" s="1"/>
     </row>
@@ -14168,7 +14189,7 @@
       <c r="AD271" s="1"/>
       <c r="AE271" s="29"/>
       <c r="AF271" s="1"/>
-      <c r="AG271" s="1"/>
+      <c r="AG271" s="29"/>
       <c r="AH271" s="1"/>
       <c r="AI271" s="1"/>
     </row>
@@ -14207,7 +14228,7 @@
       <c r="AD272" s="1"/>
       <c r="AE272" s="29"/>
       <c r="AF272" s="1"/>
-      <c r="AG272" s="1"/>
+      <c r="AG272" s="29"/>
       <c r="AH272" s="1"/>
       <c r="AI272" s="1"/>
     </row>
@@ -14246,7 +14267,7 @@
       <c r="AD273" s="1"/>
       <c r="AE273" s="29"/>
       <c r="AF273" s="1"/>
-      <c r="AG273" s="1"/>
+      <c r="AG273" s="29"/>
       <c r="AH273" s="1"/>
       <c r="AI273" s="1"/>
     </row>
@@ -14285,7 +14306,7 @@
       <c r="AD274" s="1"/>
       <c r="AE274" s="29"/>
       <c r="AF274" s="1"/>
-      <c r="AG274" s="1"/>
+      <c r="AG274" s="29"/>
       <c r="AH274" s="1"/>
       <c r="AI274" s="1"/>
     </row>
@@ -14324,7 +14345,7 @@
       <c r="AD275" s="1"/>
       <c r="AE275" s="29"/>
       <c r="AF275" s="1"/>
-      <c r="AG275" s="1"/>
+      <c r="AG275" s="29"/>
       <c r="AH275" s="1"/>
       <c r="AI275" s="1"/>
     </row>
@@ -14363,7 +14384,7 @@
       <c r="AD276" s="1"/>
       <c r="AE276" s="29"/>
       <c r="AF276" s="1"/>
-      <c r="AG276" s="1"/>
+      <c r="AG276" s="29"/>
       <c r="AH276" s="1"/>
       <c r="AI276" s="1"/>
     </row>
@@ -14402,7 +14423,7 @@
       <c r="AD277" s="1"/>
       <c r="AE277" s="29"/>
       <c r="AF277" s="1"/>
-      <c r="AG277" s="1"/>
+      <c r="AG277" s="29"/>
       <c r="AH277" s="1"/>
       <c r="AI277" s="1"/>
     </row>
@@ -14441,7 +14462,7 @@
       <c r="AD278" s="1"/>
       <c r="AE278" s="29"/>
       <c r="AF278" s="1"/>
-      <c r="AG278" s="1"/>
+      <c r="AG278" s="29"/>
       <c r="AH278" s="1"/>
       <c r="AI278" s="1"/>
     </row>
@@ -14480,7 +14501,7 @@
       <c r="AD279" s="1"/>
       <c r="AE279" s="29"/>
       <c r="AF279" s="1"/>
-      <c r="AG279" s="1"/>
+      <c r="AG279" s="29"/>
       <c r="AH279" s="1"/>
       <c r="AI279" s="1"/>
     </row>
@@ -14519,7 +14540,7 @@
       <c r="AD280" s="1"/>
       <c r="AE280" s="29"/>
       <c r="AF280" s="1"/>
-      <c r="AG280" s="1"/>
+      <c r="AG280" s="29"/>
       <c r="AH280" s="1"/>
       <c r="AI280" s="1"/>
     </row>
@@ -14547,14 +14568,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8513D353-BD33-4F18-8682-09CF4EA59EE5}">
   <dimension ref="A2:H171"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.649999999999999"/>
   <cols>
-    <col min="1" max="1" width="12.08203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.0625" style="16" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.08203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.9140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="6.58203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.8125" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.0625" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.9375" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="6.5625" style="16" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="16"/>
   </cols>
   <sheetData>
@@ -15017,7 +15038,9 @@
       <c r="H32" s="18"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="19"/>
+      <c r="A33" s="19" t="s">
+        <v>396</v>
+      </c>
       <c r="B33" s="18"/>
       <c r="C33" s="18"/>
       <c r="D33" s="18"/>
@@ -16421,24 +16444,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B979FDD-83A3-41C6-8CB0-C39167BCC619}">
-  <dimension ref="A1:E221"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:G221"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" customWidth="1"/>
-    <col min="2" max="2" width="4.58203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.58203125" customWidth="1"/>
-    <col min="4" max="4" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.8125" customWidth="1"/>
+    <col min="2" max="2" width="4.5625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5625" customWidth="1"/>
+    <col min="4" max="4" width="29.1875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="28" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="D1" s="28" t="s">
         <v>120</v>
@@ -16786,7 +16809,7 @@
       </c>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:7">
       <c r="A33" s="26">
         <v>32</v>
       </c>
@@ -16797,789 +16820,925 @@
       </c>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:7">
       <c r="A34" s="26">
         <v>33</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="26" t="s">
         <v>333</v>
       </c>
-      <c r="E34" s="3"/>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="E34" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G34">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="26">
         <v>34</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="E35" s="3"/>
-    </row>
-    <row r="36" spans="1:5">
+        <v>386</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" s="26">
         <v>35</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="26" t="s">
-        <v>335</v>
-      </c>
-      <c r="E36" s="3"/>
-    </row>
-    <row r="37" spans="1:5">
+        <v>387</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G36">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="26">
         <v>36</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="26" t="s">
-        <v>336</v>
-      </c>
-      <c r="E37" s="3"/>
-    </row>
-    <row r="38" spans="1:5">
+        <v>334</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G37">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="26">
         <v>37</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="26" t="s">
-        <v>337</v>
-      </c>
-      <c r="E38" s="3"/>
-    </row>
-    <row r="39" spans="1:5">
+        <v>335</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G38">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="26">
         <v>38</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="26" t="s">
-        <v>338</v>
-      </c>
-      <c r="E39" s="3"/>
-    </row>
-    <row r="40" spans="1:5">
+        <v>388</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G39">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" s="26">
         <v>39</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="26" t="s">
-        <v>339</v>
-      </c>
-      <c r="E40" s="3"/>
-    </row>
-    <row r="41" spans="1:5">
+        <v>389</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G40">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="26">
         <v>40</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="26" t="s">
-        <v>340</v>
-      </c>
-      <c r="E41" s="3"/>
-    </row>
-    <row r="42" spans="1:5">
+        <v>390</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G41">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="26">
         <v>41</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="26" t="s">
-        <v>341</v>
-      </c>
-      <c r="E42" s="3"/>
-    </row>
-    <row r="43" spans="1:5">
+        <v>391</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G42">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" s="26">
         <v>42</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="26" t="s">
-        <v>342</v>
-      </c>
-      <c r="E43" s="3"/>
-    </row>
-    <row r="44" spans="1:5">
+        <v>336</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G43">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" s="26">
         <v>43</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="26" t="s">
-        <v>343</v>
-      </c>
-      <c r="E44" s="3"/>
-    </row>
-    <row r="45" spans="1:5">
+        <v>337</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G44">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="26">
         <v>44</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="26" t="s">
-        <v>344</v>
-      </c>
-      <c r="E45" s="3"/>
-    </row>
-    <row r="46" spans="1:5">
+        <v>338</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="26">
         <v>45</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="26" t="s">
-        <v>345</v>
-      </c>
-      <c r="E46" s="3"/>
-    </row>
-    <row r="47" spans="1:5">
+        <v>375</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G46">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" s="26">
         <v>46</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="26" t="s">
-        <v>346</v>
-      </c>
-      <c r="E47" s="3"/>
-    </row>
-    <row r="48" spans="1:5">
+        <v>392</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G47">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" s="26">
         <v>47</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="26" t="s">
-        <v>347</v>
-      </c>
-      <c r="E48" s="3"/>
-    </row>
-    <row r="49" spans="1:5">
+        <v>393</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G48">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="26">
         <v>48</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="26" t="s">
-        <v>348</v>
-      </c>
-      <c r="E49" s="3"/>
-    </row>
-    <row r="50" spans="1:5">
+        <v>394</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G49">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" s="26">
         <v>49</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="26" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="E50" s="3"/>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:7">
       <c r="A51" s="26">
         <v>50</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="26" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:7">
       <c r="A52" s="26">
         <v>51</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="26" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="E52" s="3"/>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:7">
       <c r="A53" s="26">
         <v>52</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="26" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:7">
       <c r="A54" s="26">
         <v>53</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="26" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:7">
       <c r="A55" s="26">
         <v>54</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="26" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:7">
       <c r="A56" s="26">
         <v>55</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="26" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:7">
       <c r="A57" s="26">
         <v>56</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="26" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:7">
       <c r="A58" s="26">
         <v>57</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="26" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:7">
       <c r="A59" s="26">
         <v>58</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="26" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:7">
       <c r="A60" s="26">
         <v>59</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="26" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:7">
       <c r="A61" s="26">
         <v>60</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="26" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:7">
       <c r="A62" s="26">
         <v>61</v>
       </c>
       <c r="B62" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="26" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:7">
       <c r="A63" s="26">
         <v>62</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="26" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:7">
       <c r="A64" s="26">
         <v>63</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="26" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:7">
       <c r="A65" s="26">
         <v>64</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="26" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:7">
       <c r="A66" s="26">
         <v>65</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="26" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:7">
       <c r="A67" s="26">
         <v>66</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="26" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:7">
       <c r="A68" s="26">
         <v>67</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="26" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="E68" s="3"/>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:7">
       <c r="A69" s="26">
         <v>68</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C69" s="3"/>
       <c r="D69" s="26" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="E69" s="3"/>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:7">
       <c r="A70" s="26">
         <v>69</v>
       </c>
       <c r="B70" s="26" t="s">
-        <v>354</v>
-      </c>
-      <c r="C70" s="3"/>
+        <v>344</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>157</v>
+      </c>
       <c r="D70" s="27" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="E70" s="3"/>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:7">
       <c r="A71" s="26">
         <v>70</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>157</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:7">
       <c r="A72" s="26">
         <v>71</v>
       </c>
       <c r="B72" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>157</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>373</v>
-      </c>
-      <c r="E72" s="3"/>
-    </row>
-    <row r="73" spans="1:5">
+        <v>363</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73" s="26">
         <v>72</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>157</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>374</v>
-      </c>
-      <c r="E73" s="3"/>
-    </row>
-    <row r="74" spans="1:5">
+        <v>364</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74" s="26">
         <v>73</v>
       </c>
       <c r="B74" s="26"/>
       <c r="C74" s="3"/>
       <c r="D74" s="26" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="E74" s="3"/>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:7">
       <c r="A75" s="26">
         <v>74</v>
       </c>
       <c r="B75" s="26"/>
       <c r="C75" s="3"/>
       <c r="D75" s="26" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="E75" s="3"/>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:7">
       <c r="A76" s="26">
         <v>75</v>
       </c>
       <c r="B76" s="26" t="s">
-        <v>354</v>
-      </c>
-      <c r="C76" s="3"/>
+        <v>344</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>157</v>
+      </c>
       <c r="D76" s="27" t="s">
-        <v>378</v>
-      </c>
-      <c r="E76" s="3"/>
-    </row>
-    <row r="77" spans="1:5">
+        <v>368</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G76">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
       <c r="A77" s="26">
         <v>76</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>354</v>
-      </c>
-      <c r="C77" s="3"/>
+        <v>344</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>157</v>
+      </c>
       <c r="D77" s="27" t="s">
-        <v>379</v>
-      </c>
-      <c r="E77" s="3"/>
-    </row>
-    <row r="78" spans="1:5">
+        <v>369</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G77">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78" s="26">
         <v>77</v>
       </c>
       <c r="B78" s="26" t="s">
-        <v>354</v>
-      </c>
-      <c r="C78" s="3"/>
+        <v>344</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>157</v>
+      </c>
       <c r="D78" s="27" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="E78" s="3"/>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:7">
       <c r="A79" s="26">
         <v>78</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>354</v>
-      </c>
-      <c r="C79" s="3"/>
+        <v>344</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>157</v>
+      </c>
       <c r="D79" s="27" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="E79" s="3"/>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:7">
       <c r="A80" s="26">
         <v>79</v>
       </c>
       <c r="B80" s="26" t="s">
-        <v>354</v>
-      </c>
-      <c r="C80" s="3"/>
+        <v>344</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>157</v>
+      </c>
       <c r="D80" s="27" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="E80" s="3"/>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:7">
       <c r="A81" s="26">
         <v>80</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="26" t="s">
-        <v>383</v>
-      </c>
-      <c r="E81" s="3"/>
-    </row>
-    <row r="82" spans="1:5">
+        <v>373</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G81">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
       <c r="A82" s="26">
         <v>81</v>
       </c>
       <c r="B82" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="26" t="s">
-        <v>384</v>
-      </c>
-      <c r="E82" s="3"/>
-    </row>
-    <row r="83" spans="1:5">
+        <v>374</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G82">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
       <c r="A83" s="26">
         <v>82</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C83" s="3"/>
-      <c r="D83" s="41" t="s">
-        <v>385</v>
+      <c r="D83" s="26" t="s">
+        <v>375</v>
       </c>
       <c r="E83" s="3"/>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:7">
       <c r="A84" s="26">
         <v>83</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="26" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="E84" s="3"/>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:7">
       <c r="A85" s="26">
         <v>84</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="26" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E85" s="3"/>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:7">
       <c r="A86" s="26">
         <v>85</v>
       </c>
       <c r="B86" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="26" t="s">
-        <v>388</v>
-      </c>
-      <c r="E86" s="3"/>
-    </row>
-    <row r="87" spans="1:5">
+        <v>378</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G86">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
       <c r="A87" s="26">
         <v>86</v>
       </c>
       <c r="B87" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C87" s="3"/>
       <c r="D87" s="26" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E87" s="3"/>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:7">
       <c r="A88" s="26">
         <v>87</v>
       </c>
       <c r="B88" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C88" s="3"/>
       <c r="D88" s="26" t="s">
-        <v>390</v>
-      </c>
-      <c r="E88" s="3"/>
-    </row>
-    <row r="89" spans="1:5">
+        <v>379</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G88">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
       <c r="A89" s="26">
         <v>88</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>354</v>
-      </c>
-      <c r="C89" s="3"/>
+        <v>344</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>157</v>
+      </c>
       <c r="D89" s="27" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="E89" s="3"/>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:7">
       <c r="A90" s="26">
         <v>89</v>
       </c>
       <c r="B90" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="26" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="E90" s="3"/>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:7">
       <c r="A91" s="26">
         <v>90</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C91" s="3"/>
-      <c r="D91" s="41" t="s">
-        <v>393</v>
+      <c r="D91" s="26" t="s">
+        <v>382</v>
       </c>
       <c r="E91" s="3"/>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:7">
       <c r="A92" s="26">
         <v>91</v>
       </c>
       <c r="B92" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C92" s="3"/>
-      <c r="D92" s="41" t="s">
-        <v>394</v>
+      <c r="D92" s="26" t="s">
+        <v>383</v>
       </c>
       <c r="E92" s="3"/>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:7">
       <c r="A93" s="26">
         <v>92</v>
       </c>
       <c r="B93" s="26" t="s">
-        <v>354</v>
-      </c>
-      <c r="C93" s="3"/>
+        <v>344</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>157</v>
+      </c>
       <c r="D93" s="27" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="E93" s="3"/>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:7">
       <c r="A94" s="26">
         <v>93</v>
       </c>
@@ -17588,7 +17747,7 @@
       <c r="D94" s="26"/>
       <c r="E94" s="3"/>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:7">
       <c r="A95" s="26">
         <v>94</v>
       </c>
@@ -17597,7 +17756,7 @@
       <c r="D95" s="26"/>
       <c r="E95" s="3"/>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:7">
       <c r="A96" s="26">
         <v>95</v>
       </c>
@@ -18734,7 +18893,7 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E221 C2:C221" xr:uid="{BB1BFAF5-92CA-4009-8ED1-905216C51CB6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C221 E2:E221" xr:uid="{BB1BFAF5-92CA-4009-8ED1-905216C51CB6}">
       <formula1>"〇,×,△"</formula1>
     </dataValidation>
   </dataValidations>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678919BE-119C-47B5-9116-AB61A93A5AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FCE08C-A0A8-4621-9025-54894C86EDC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="397">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -15041,12 +15041,24 @@
       <c r="A33" s="19" t="s">
         <v>396</v>
       </c>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
+      <c r="B33" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>157</v>
+      </c>
       <c r="H33" s="18"/>
     </row>
     <row r="34" spans="1:8">
@@ -16444,7 +16456,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B979FDD-83A3-41C6-8CB0-C39167BCC619}">
-  <dimension ref="A1:G221"/>
+  <dimension ref="A1:E221"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="1" width="3.8125" customWidth="1"/>
@@ -16809,7 +16821,7 @@
       </c>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:5">
       <c r="A33" s="26">
         <v>32</v>
       </c>
@@ -16820,7 +16832,7 @@
       </c>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:5">
       <c r="A34" s="26">
         <v>33</v>
       </c>
@@ -16834,11 +16846,8 @@
       <c r="E34" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G34">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" s="26">
         <v>34</v>
       </c>
@@ -16852,11 +16861,8 @@
       <c r="E35" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" s="26">
         <v>35</v>
       </c>
@@ -16870,11 +16876,8 @@
       <c r="E36" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G36">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" s="26">
         <v>36</v>
       </c>
@@ -16888,11 +16891,8 @@
       <c r="E37" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G37">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" s="26">
         <v>37</v>
       </c>
@@ -16906,11 +16906,8 @@
       <c r="E38" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G38">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" s="26">
         <v>38</v>
       </c>
@@ -16924,11 +16921,8 @@
       <c r="E39" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G39">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" s="26">
         <v>39</v>
       </c>
@@ -16942,11 +16936,8 @@
       <c r="E40" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G40">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" s="26">
         <v>40</v>
       </c>
@@ -16960,11 +16951,8 @@
       <c r="E41" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G41">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" s="26">
         <v>41</v>
       </c>
@@ -16978,11 +16966,8 @@
       <c r="E42" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G42">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" s="26">
         <v>42</v>
       </c>
@@ -16996,11 +16981,8 @@
       <c r="E43" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G43">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" s="26">
         <v>43</v>
       </c>
@@ -17014,11 +16996,8 @@
       <c r="E44" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G44">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" s="26">
         <v>44</v>
       </c>
@@ -17032,11 +17011,8 @@
       <c r="E45" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G45">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" s="26">
         <v>45</v>
       </c>
@@ -17050,11 +17026,8 @@
       <c r="E46" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G46">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" s="26">
         <v>46</v>
       </c>
@@ -17068,11 +17041,8 @@
       <c r="E47" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G47">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" s="26">
         <v>47</v>
       </c>
@@ -17086,11 +17056,8 @@
       <c r="E48" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G48">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" s="26">
         <v>48</v>
       </c>
@@ -17104,11 +17071,8 @@
       <c r="E49" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G49">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" s="26">
         <v>49</v>
       </c>
@@ -17121,7 +17085,7 @@
       </c>
       <c r="E50" s="3"/>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:5">
       <c r="A51" s="26">
         <v>50</v>
       </c>
@@ -17134,7 +17098,7 @@
       </c>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:5">
       <c r="A52" s="26">
         <v>51</v>
       </c>
@@ -17147,7 +17111,7 @@
       </c>
       <c r="E52" s="3"/>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:5">
       <c r="A53" s="26">
         <v>52</v>
       </c>
@@ -17160,7 +17124,7 @@
       </c>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:5">
       <c r="A54" s="26">
         <v>53</v>
       </c>
@@ -17173,7 +17137,7 @@
       </c>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:5">
       <c r="A55" s="26">
         <v>54</v>
       </c>
@@ -17186,7 +17150,7 @@
       </c>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:5">
       <c r="A56" s="26">
         <v>55</v>
       </c>
@@ -17199,7 +17163,7 @@
       </c>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:5">
       <c r="A57" s="26">
         <v>56</v>
       </c>
@@ -17212,7 +17176,7 @@
       </c>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:5">
       <c r="A58" s="26">
         <v>57</v>
       </c>
@@ -17225,7 +17189,7 @@
       </c>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:5">
       <c r="A59" s="26">
         <v>58</v>
       </c>
@@ -17238,7 +17202,7 @@
       </c>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:5">
       <c r="A60" s="26">
         <v>59</v>
       </c>
@@ -17251,7 +17215,7 @@
       </c>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:5">
       <c r="A61" s="26">
         <v>60</v>
       </c>
@@ -17264,7 +17228,7 @@
       </c>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:5">
       <c r="A62" s="26">
         <v>61</v>
       </c>
@@ -17277,7 +17241,7 @@
       </c>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:5">
       <c r="A63" s="26">
         <v>62</v>
       </c>
@@ -17290,7 +17254,7 @@
       </c>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:5">
       <c r="A64" s="26">
         <v>63</v>
       </c>
@@ -17303,7 +17267,7 @@
       </c>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:5">
       <c r="A65" s="26">
         <v>64</v>
       </c>
@@ -17316,7 +17280,7 @@
       </c>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:5">
       <c r="A66" s="26">
         <v>65</v>
       </c>
@@ -17329,7 +17293,7 @@
       </c>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:5">
       <c r="A67" s="26">
         <v>66</v>
       </c>
@@ -17342,7 +17306,7 @@
       </c>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:5">
       <c r="A68" s="26">
         <v>67</v>
       </c>
@@ -17355,7 +17319,7 @@
       </c>
       <c r="E68" s="3"/>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:5">
       <c r="A69" s="26">
         <v>68</v>
       </c>
@@ -17368,7 +17332,7 @@
       </c>
       <c r="E69" s="3"/>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:5">
       <c r="A70" s="26">
         <v>69</v>
       </c>
@@ -17383,7 +17347,7 @@
       </c>
       <c r="E70" s="3"/>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:5">
       <c r="A71" s="26">
         <v>70</v>
       </c>
@@ -17398,7 +17362,7 @@
       </c>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:5">
       <c r="A72" s="26">
         <v>71</v>
       </c>
@@ -17414,11 +17378,8 @@
       <c r="E72" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73" s="26">
         <v>72</v>
       </c>
@@ -17434,11 +17395,8 @@
       <c r="E73" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G73">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74" s="26">
         <v>73</v>
       </c>
@@ -17449,7 +17407,7 @@
       </c>
       <c r="E74" s="3"/>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:5">
       <c r="A75" s="26">
         <v>74</v>
       </c>
@@ -17460,7 +17418,7 @@
       </c>
       <c r="E75" s="3"/>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:5">
       <c r="A76" s="26">
         <v>75</v>
       </c>
@@ -17476,11 +17434,8 @@
       <c r="E76" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G76">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77" s="26">
         <v>76</v>
       </c>
@@ -17496,11 +17451,8 @@
       <c r="E77" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G77">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78" s="26">
         <v>77</v>
       </c>
@@ -17515,7 +17467,7 @@
       </c>
       <c r="E78" s="3"/>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:5">
       <c r="A79" s="26">
         <v>78</v>
       </c>
@@ -17530,7 +17482,7 @@
       </c>
       <c r="E79" s="3"/>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:5">
       <c r="A80" s="26">
         <v>79</v>
       </c>
@@ -17545,7 +17497,7 @@
       </c>
       <c r="E80" s="3"/>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:5">
       <c r="A81" s="26">
         <v>80</v>
       </c>
@@ -17559,11 +17511,8 @@
       <c r="E81" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G81">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" s="26">
         <v>81</v>
       </c>
@@ -17577,11 +17526,8 @@
       <c r="E82" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G82">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83" s="26">
         <v>82</v>
       </c>
@@ -17594,7 +17540,7 @@
       </c>
       <c r="E83" s="3"/>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:5">
       <c r="A84" s="26">
         <v>83</v>
       </c>
@@ -17607,7 +17553,7 @@
       </c>
       <c r="E84" s="3"/>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:5">
       <c r="A85" s="26">
         <v>84</v>
       </c>
@@ -17620,7 +17566,7 @@
       </c>
       <c r="E85" s="3"/>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:5">
       <c r="A86" s="26">
         <v>85</v>
       </c>
@@ -17634,11 +17580,8 @@
       <c r="E86" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G86">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87" s="26">
         <v>86</v>
       </c>
@@ -17651,7 +17594,7 @@
       </c>
       <c r="E87" s="3"/>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:5">
       <c r="A88" s="26">
         <v>87</v>
       </c>
@@ -17665,11 +17608,8 @@
       <c r="E88" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G88">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89" s="26">
         <v>88</v>
       </c>
@@ -17684,7 +17624,7 @@
       </c>
       <c r="E89" s="3"/>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:5">
       <c r="A90" s="26">
         <v>89</v>
       </c>
@@ -17697,7 +17637,7 @@
       </c>
       <c r="E90" s="3"/>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:5">
       <c r="A91" s="26">
         <v>90</v>
       </c>
@@ -17710,7 +17650,7 @@
       </c>
       <c r="E91" s="3"/>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:5">
       <c r="A92" s="26">
         <v>91</v>
       </c>
@@ -17723,7 +17663,7 @@
       </c>
       <c r="E92" s="3"/>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:5">
       <c r="A93" s="26">
         <v>92</v>
       </c>
@@ -17738,7 +17678,7 @@
       </c>
       <c r="E93" s="3"/>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:5">
       <c r="A94" s="26">
         <v>93</v>
       </c>
@@ -17747,7 +17687,7 @@
       <c r="D94" s="26"/>
       <c r="E94" s="3"/>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:5">
       <c r="A95" s="26">
         <v>94</v>
       </c>
@@ -17756,7 +17696,7 @@
       <c r="D95" s="26"/>
       <c r="E95" s="3"/>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:5">
       <c r="A96" s="26">
         <v>95</v>
       </c>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FCE08C-A0A8-4621-9025-54894C86EDC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46011A17-2E46-4E4A-AA49-D22DC2C3A6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="398">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -1890,6 +1890,13 @@
     <t>関西弁１</t>
     <rPh sb="0" eb="3">
       <t>カンサイベン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>犬２</t>
+    <rPh sb="0" eb="1">
+      <t>イヌ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -15062,7 +15069,9 @@
       <c r="H33" s="18"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="19"/>
+      <c r="A34" s="19" t="s">
+        <v>397</v>
+      </c>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
       <c r="D34" s="18"/>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46011A17-2E46-4E4A-AA49-D22DC2C3A6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530DA990-C862-4EB3-8402-693E2ED13379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="リスト" sheetId="1" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="401">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -1895,6 +1895,27 @@
   </si>
   <si>
     <t>犬２</t>
+    <rPh sb="0" eb="1">
+      <t>イヌ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>犬３</t>
+    <rPh sb="0" eb="1">
+      <t>イヌ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>犬２</t>
+    <rPh sb="0" eb="1">
+      <t>イヌ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>犬３</t>
     <rPh sb="0" eb="1">
       <t>イヌ</t>
     </rPh>
@@ -2625,7 +2646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI280"/>
+  <dimension ref="A1:AK280"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="1" width="3.4375" bestFit="1" customWidth="1"/>
@@ -2633,10 +2654,10 @@
     <col min="3" max="3" width="33.75" bestFit="1" customWidth="1"/>
     <col min="4" max="9" width="3.5625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="2.5625" bestFit="1" customWidth="1"/>
-    <col min="11" max="35" width="3.5625" bestFit="1" customWidth="1"/>
+    <col min="11" max="37" width="3.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="22.9">
+    <row r="1" spans="1:37" ht="22.9">
       <c r="A1" s="34"/>
       <c r="B1" s="38" t="s">
         <v>273</v>
@@ -2668,7 +2689,7 @@
       <c r="W1" s="37"/>
       <c r="X1" s="37"/>
     </row>
-    <row r="2" spans="1:35" ht="22.9">
+    <row r="2" spans="1:37" ht="22.9">
       <c r="A2" s="35"/>
       <c r="B2" s="39"/>
       <c r="C2" s="32"/>
@@ -2714,8 +2735,10 @@
       <c r="AG2" s="5"/>
       <c r="AH2" s="5"/>
       <c r="AI2" s="5"/>
-    </row>
-    <row r="3" spans="1:35" s="13" customFormat="1" ht="106.9" thickBot="1">
+      <c r="AJ2" s="5"/>
+      <c r="AK2" s="5"/>
+    </row>
+    <row r="3" spans="1:37" s="13" customFormat="1" ht="106.9" thickBot="1">
       <c r="A3" s="36"/>
       <c r="B3" s="40"/>
       <c r="C3" s="33"/>
@@ -2809,10 +2832,16 @@
       <c r="AG3" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="AH3" s="11"/>
-      <c r="AI3" s="11"/>
-    </row>
-    <row r="4" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1" thickTop="1">
+      <c r="AH3" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="AI3" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="AJ3" s="11"/>
+      <c r="AK3" s="11"/>
+    </row>
+    <row r="4" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -2864,8 +2893,10 @@
       <c r="AG4" s="29"/>
       <c r="AH4" s="1"/>
       <c r="AI4" s="1"/>
-    </row>
-    <row r="5" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="1"/>
+    </row>
+    <row r="5" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -2919,8 +2950,10 @@
       <c r="AG5" s="29"/>
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
-    </row>
-    <row r="6" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ5" s="1"/>
+      <c r="AK5" s="1"/>
+    </row>
+    <row r="6" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -2964,8 +2997,10 @@
       <c r="AG6" s="29"/>
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
-    </row>
-    <row r="7" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ6" s="1"/>
+      <c r="AK6" s="1"/>
+    </row>
+    <row r="7" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -3005,8 +3040,10 @@
       <c r="AG7" s="29"/>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
-    </row>
-    <row r="8" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="1"/>
+    </row>
+    <row r="8" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -3048,8 +3085,10 @@
       <c r="AG8" s="29"/>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
-    </row>
-    <row r="9" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="1"/>
+    </row>
+    <row r="9" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -3089,8 +3128,10 @@
       <c r="AG9" s="29"/>
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
-    </row>
-    <row r="10" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+    </row>
+    <row r="10" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -3130,8 +3171,10 @@
       <c r="AG10" s="29"/>
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
-    </row>
-    <row r="11" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ10" s="1"/>
+      <c r="AK10" s="1"/>
+    </row>
+    <row r="11" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -3175,8 +3218,10 @@
       <c r="AG11" s="29"/>
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
-    </row>
-    <row r="12" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ11" s="1"/>
+      <c r="AK11" s="1"/>
+    </row>
+    <row r="12" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -3216,8 +3261,10 @@
       <c r="AG12" s="29"/>
       <c r="AH12" s="1"/>
       <c r="AI12" s="1"/>
-    </row>
-    <row r="13" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ12" s="1"/>
+      <c r="AK12" s="1"/>
+    </row>
+    <row r="13" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -3257,8 +3304,10 @@
       <c r="AG13" s="29"/>
       <c r="AH13" s="1"/>
       <c r="AI13" s="1"/>
-    </row>
-    <row r="14" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ13" s="1"/>
+      <c r="AK13" s="1"/>
+    </row>
+    <row r="14" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -3298,8 +3347,10 @@
       <c r="AG14" s="29"/>
       <c r="AH14" s="1"/>
       <c r="AI14" s="1"/>
-    </row>
-    <row r="15" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ14" s="1"/>
+      <c r="AK14" s="1"/>
+    </row>
+    <row r="15" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -3339,8 +3390,10 @@
       <c r="AG15" s="29"/>
       <c r="AH15" s="1"/>
       <c r="AI15" s="1"/>
-    </row>
-    <row r="16" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ15" s="1"/>
+      <c r="AK15" s="1"/>
+    </row>
+    <row r="16" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -3380,8 +3433,10 @@
       <c r="AG16" s="29"/>
       <c r="AH16" s="1"/>
       <c r="AI16" s="1"/>
-    </row>
-    <row r="17" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ16" s="1"/>
+      <c r="AK16" s="1"/>
+    </row>
+    <row r="17" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -3421,8 +3476,10 @@
       <c r="AG17" s="29"/>
       <c r="AH17" s="1"/>
       <c r="AI17" s="1"/>
-    </row>
-    <row r="18" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ17" s="1"/>
+      <c r="AK17" s="1"/>
+    </row>
+    <row r="18" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -3464,8 +3521,10 @@
       <c r="AG18" s="29"/>
       <c r="AH18" s="1"/>
       <c r="AI18" s="1"/>
-    </row>
-    <row r="19" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ18" s="1"/>
+      <c r="AK18" s="1"/>
+    </row>
+    <row r="19" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -3505,8 +3564,10 @@
       <c r="AG19" s="29"/>
       <c r="AH19" s="1"/>
       <c r="AI19" s="1"/>
-    </row>
-    <row r="20" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ19" s="1"/>
+      <c r="AK19" s="1"/>
+    </row>
+    <row r="20" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -3546,8 +3607,10 @@
       <c r="AG20" s="29"/>
       <c r="AH20" s="1"/>
       <c r="AI20" s="1"/>
-    </row>
-    <row r="21" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ20" s="1"/>
+      <c r="AK20" s="1"/>
+    </row>
+    <row r="21" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -3587,8 +3650,10 @@
       <c r="AG21" s="29"/>
       <c r="AH21" s="1"/>
       <c r="AI21" s="1"/>
-    </row>
-    <row r="22" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ21" s="1"/>
+      <c r="AK21" s="1"/>
+    </row>
+    <row r="22" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -3630,8 +3695,10 @@
       <c r="AG22" s="29"/>
       <c r="AH22" s="1"/>
       <c r="AI22" s="1"/>
-    </row>
-    <row r="23" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ22" s="1"/>
+      <c r="AK22" s="1"/>
+    </row>
+    <row r="23" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -3671,8 +3738,10 @@
       <c r="AG23" s="29"/>
       <c r="AH23" s="1"/>
       <c r="AI23" s="1"/>
-    </row>
-    <row r="24" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ23" s="1"/>
+      <c r="AK23" s="1"/>
+    </row>
+    <row r="24" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -3714,8 +3783,10 @@
       <c r="AG24" s="29"/>
       <c r="AH24" s="1"/>
       <c r="AI24" s="1"/>
-    </row>
-    <row r="25" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ24" s="1"/>
+      <c r="AK24" s="1"/>
+    </row>
+    <row r="25" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -3757,8 +3828,10 @@
       <c r="AG25" s="29"/>
       <c r="AH25" s="1"/>
       <c r="AI25" s="1"/>
-    </row>
-    <row r="26" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ25" s="1"/>
+      <c r="AK25" s="1"/>
+    </row>
+    <row r="26" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -3798,8 +3871,10 @@
       <c r="AG26" s="29"/>
       <c r="AH26" s="1"/>
       <c r="AI26" s="1"/>
-    </row>
-    <row r="27" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ26" s="1"/>
+      <c r="AK26" s="1"/>
+    </row>
+    <row r="27" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -3841,8 +3916,10 @@
       <c r="AG27" s="29"/>
       <c r="AH27" s="1"/>
       <c r="AI27" s="1"/>
-    </row>
-    <row r="28" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ27" s="1"/>
+      <c r="AK27" s="1"/>
+    </row>
+    <row r="28" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -3882,8 +3959,10 @@
       <c r="AG28" s="29"/>
       <c r="AH28" s="1"/>
       <c r="AI28" s="1"/>
-    </row>
-    <row r="29" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ28" s="1"/>
+      <c r="AK28" s="1"/>
+    </row>
+    <row r="29" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -3923,8 +4002,10 @@
       <c r="AG29" s="29"/>
       <c r="AH29" s="1"/>
       <c r="AI29" s="1"/>
-    </row>
-    <row r="30" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ29" s="1"/>
+      <c r="AK29" s="1"/>
+    </row>
+    <row r="30" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -3966,8 +4047,10 @@
       <c r="AG30" s="29"/>
       <c r="AH30" s="1"/>
       <c r="AI30" s="1"/>
-    </row>
-    <row r="31" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ30" s="1"/>
+      <c r="AK30" s="1"/>
+    </row>
+    <row r="31" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -4013,8 +4096,10 @@
       <c r="AG31" s="29"/>
       <c r="AH31" s="1"/>
       <c r="AI31" s="1"/>
-    </row>
-    <row r="32" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ31" s="1"/>
+      <c r="AK31" s="1"/>
+    </row>
+    <row r="32" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -4056,8 +4141,10 @@
       <c r="AG32" s="29"/>
       <c r="AH32" s="1"/>
       <c r="AI32" s="1"/>
-    </row>
-    <row r="33" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ32" s="1"/>
+      <c r="AK32" s="1"/>
+    </row>
+    <row r="33" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -4097,8 +4184,10 @@
       <c r="AG33" s="29"/>
       <c r="AH33" s="1"/>
       <c r="AI33" s="1"/>
-    </row>
-    <row r="34" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ33" s="1"/>
+      <c r="AK33" s="1"/>
+    </row>
+    <row r="34" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -4138,8 +4227,10 @@
       <c r="AG34" s="29"/>
       <c r="AH34" s="1"/>
       <c r="AI34" s="1"/>
-    </row>
-    <row r="35" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ34" s="1"/>
+      <c r="AK34" s="1"/>
+    </row>
+    <row r="35" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -4179,8 +4270,10 @@
       <c r="AG35" s="29"/>
       <c r="AH35" s="1"/>
       <c r="AI35" s="1"/>
-    </row>
-    <row r="36" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ35" s="1"/>
+      <c r="AK35" s="1"/>
+    </row>
+    <row r="36" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -4220,8 +4313,10 @@
       <c r="AG36" s="29"/>
       <c r="AH36" s="1"/>
       <c r="AI36" s="1"/>
-    </row>
-    <row r="37" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ36" s="1"/>
+      <c r="AK36" s="1"/>
+    </row>
+    <row r="37" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -4261,8 +4356,10 @@
       <c r="AG37" s="29"/>
       <c r="AH37" s="1"/>
       <c r="AI37" s="1"/>
-    </row>
-    <row r="38" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ37" s="1"/>
+      <c r="AK37" s="1"/>
+    </row>
+    <row r="38" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -4302,8 +4399,10 @@
       <c r="AG38" s="29"/>
       <c r="AH38" s="1"/>
       <c r="AI38" s="1"/>
-    </row>
-    <row r="39" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ38" s="1"/>
+      <c r="AK38" s="1"/>
+    </row>
+    <row r="39" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -4345,8 +4444,10 @@
       <c r="AG39" s="29"/>
       <c r="AH39" s="1"/>
       <c r="AI39" s="1"/>
-    </row>
-    <row r="40" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ39" s="1"/>
+      <c r="AK39" s="1"/>
+    </row>
+    <row r="40" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -4388,8 +4489,10 @@
       <c r="AG40" s="29"/>
       <c r="AH40" s="1"/>
       <c r="AI40" s="1"/>
-    </row>
-    <row r="41" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ40" s="1"/>
+      <c r="AK40" s="1"/>
+    </row>
+    <row r="41" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -4431,8 +4534,10 @@
       <c r="AG41" s="29"/>
       <c r="AH41" s="1"/>
       <c r="AI41" s="1"/>
-    </row>
-    <row r="42" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ41" s="1"/>
+      <c r="AK41" s="1"/>
+    </row>
+    <row r="42" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -4472,8 +4577,10 @@
       <c r="AG42" s="29"/>
       <c r="AH42" s="1"/>
       <c r="AI42" s="1"/>
-    </row>
-    <row r="43" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ42" s="1"/>
+      <c r="AK42" s="1"/>
+    </row>
+    <row r="43" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -4515,8 +4622,10 @@
       <c r="AG43" s="29"/>
       <c r="AH43" s="1"/>
       <c r="AI43" s="1"/>
-    </row>
-    <row r="44" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ43" s="1"/>
+      <c r="AK43" s="1"/>
+    </row>
+    <row r="44" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -4556,8 +4665,10 @@
       <c r="AG44" s="29"/>
       <c r="AH44" s="1"/>
       <c r="AI44" s="1"/>
-    </row>
-    <row r="45" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ44" s="1"/>
+      <c r="AK44" s="1"/>
+    </row>
+    <row r="45" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -4597,8 +4708,10 @@
       <c r="AG45" s="29"/>
       <c r="AH45" s="1"/>
       <c r="AI45" s="1"/>
-    </row>
-    <row r="46" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ45" s="1"/>
+      <c r="AK45" s="1"/>
+    </row>
+    <row r="46" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -4638,8 +4751,10 @@
       <c r="AG46" s="29"/>
       <c r="AH46" s="1"/>
       <c r="AI46" s="1"/>
-    </row>
-    <row r="47" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ46" s="1"/>
+      <c r="AK46" s="1"/>
+    </row>
+    <row r="47" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -4679,8 +4794,10 @@
       <c r="AG47" s="29"/>
       <c r="AH47" s="1"/>
       <c r="AI47" s="1"/>
-    </row>
-    <row r="48" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ47" s="1"/>
+      <c r="AK47" s="1"/>
+    </row>
+    <row r="48" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -4722,8 +4839,10 @@
       <c r="AG48" s="29"/>
       <c r="AH48" s="1"/>
       <c r="AI48" s="1"/>
-    </row>
-    <row r="49" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ48" s="1"/>
+      <c r="AK48" s="1"/>
+    </row>
+    <row r="49" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -4763,8 +4882,10 @@
       <c r="AG49" s="29"/>
       <c r="AH49" s="1"/>
       <c r="AI49" s="1"/>
-    </row>
-    <row r="50" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ49" s="1"/>
+      <c r="AK49" s="1"/>
+    </row>
+    <row r="50" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -4806,8 +4927,10 @@
       <c r="AG50" s="29"/>
       <c r="AH50" s="1"/>
       <c r="AI50" s="1"/>
-    </row>
-    <row r="51" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ50" s="1"/>
+      <c r="AK50" s="1"/>
+    </row>
+    <row r="51" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -4847,8 +4970,10 @@
       <c r="AG51" s="29"/>
       <c r="AH51" s="1"/>
       <c r="AI51" s="1"/>
-    </row>
-    <row r="52" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ51" s="1"/>
+      <c r="AK51" s="1"/>
+    </row>
+    <row r="52" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -4888,8 +5013,10 @@
       <c r="AG52" s="29"/>
       <c r="AH52" s="1"/>
       <c r="AI52" s="1"/>
-    </row>
-    <row r="53" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ52" s="1"/>
+      <c r="AK52" s="1"/>
+    </row>
+    <row r="53" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -4929,8 +5056,10 @@
       <c r="AG53" s="29"/>
       <c r="AH53" s="1"/>
       <c r="AI53" s="1"/>
-    </row>
-    <row r="54" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ53" s="1"/>
+      <c r="AK53" s="1"/>
+    </row>
+    <row r="54" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A54" s="3">
         <v>51</v>
       </c>
@@ -4972,8 +5101,10 @@
       <c r="AG54" s="29"/>
       <c r="AH54" s="1"/>
       <c r="AI54" s="1"/>
-    </row>
-    <row r="55" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ54" s="1"/>
+      <c r="AK54" s="1"/>
+    </row>
+    <row r="55" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -5015,8 +5146,10 @@
       <c r="AG55" s="29"/>
       <c r="AH55" s="1"/>
       <c r="AI55" s="1"/>
-    </row>
-    <row r="56" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ55" s="1"/>
+      <c r="AK55" s="1"/>
+    </row>
+    <row r="56" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -5056,8 +5189,10 @@
       <c r="AG56" s="29"/>
       <c r="AH56" s="1"/>
       <c r="AI56" s="1"/>
-    </row>
-    <row r="57" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ56" s="1"/>
+      <c r="AK56" s="1"/>
+    </row>
+    <row r="57" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -5097,8 +5232,10 @@
       <c r="AG57" s="29"/>
       <c r="AH57" s="1"/>
       <c r="AI57" s="1"/>
-    </row>
-    <row r="58" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ57" s="1"/>
+      <c r="AK57" s="1"/>
+    </row>
+    <row r="58" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -5138,8 +5275,10 @@
       <c r="AG58" s="29"/>
       <c r="AH58" s="1"/>
       <c r="AI58" s="1"/>
-    </row>
-    <row r="59" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ58" s="1"/>
+      <c r="AK58" s="1"/>
+    </row>
+    <row r="59" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -5179,8 +5318,10 @@
       <c r="AG59" s="29"/>
       <c r="AH59" s="1"/>
       <c r="AI59" s="1"/>
-    </row>
-    <row r="60" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ59" s="1"/>
+      <c r="AK59" s="1"/>
+    </row>
+    <row r="60" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -5220,8 +5361,10 @@
       <c r="AG60" s="29"/>
       <c r="AH60" s="1"/>
       <c r="AI60" s="1"/>
-    </row>
-    <row r="61" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ60" s="1"/>
+      <c r="AK60" s="1"/>
+    </row>
+    <row r="61" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -5261,8 +5404,10 @@
       <c r="AG61" s="29"/>
       <c r="AH61" s="1"/>
       <c r="AI61" s="1"/>
-    </row>
-    <row r="62" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ61" s="1"/>
+      <c r="AK61" s="1"/>
+    </row>
+    <row r="62" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -5302,8 +5447,10 @@
       <c r="AG62" s="29"/>
       <c r="AH62" s="1"/>
       <c r="AI62" s="1"/>
-    </row>
-    <row r="63" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ62" s="1"/>
+      <c r="AK62" s="1"/>
+    </row>
+    <row r="63" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A63" s="3">
         <v>60</v>
       </c>
@@ -5345,8 +5492,10 @@
       <c r="AG63" s="29"/>
       <c r="AH63" s="1"/>
       <c r="AI63" s="1"/>
-    </row>
-    <row r="64" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ63" s="1"/>
+      <c r="AK63" s="1"/>
+    </row>
+    <row r="64" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A64" s="3">
         <v>61</v>
       </c>
@@ -5390,8 +5539,10 @@
       <c r="AG64" s="29"/>
       <c r="AH64" s="1"/>
       <c r="AI64" s="1"/>
-    </row>
-    <row r="65" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ64" s="1"/>
+      <c r="AK64" s="1"/>
+    </row>
+    <row r="65" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A65" s="3">
         <v>62</v>
       </c>
@@ -5433,8 +5584,10 @@
       <c r="AG65" s="29"/>
       <c r="AH65" s="1"/>
       <c r="AI65" s="1"/>
-    </row>
-    <row r="66" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ65" s="1"/>
+      <c r="AK65" s="1"/>
+    </row>
+    <row r="66" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A66" s="3">
         <v>63</v>
       </c>
@@ -5474,8 +5627,10 @@
       <c r="AG66" s="29"/>
       <c r="AH66" s="1"/>
       <c r="AI66" s="1"/>
-    </row>
-    <row r="67" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ66" s="1"/>
+      <c r="AK66" s="1"/>
+    </row>
+    <row r="67" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A67" s="3">
         <v>64</v>
       </c>
@@ -5519,8 +5674,10 @@
       <c r="AG67" s="29"/>
       <c r="AH67" s="1"/>
       <c r="AI67" s="1"/>
-    </row>
-    <row r="68" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ67" s="1"/>
+      <c r="AK67" s="1"/>
+    </row>
+    <row r="68" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A68" s="3">
         <v>65</v>
       </c>
@@ -5562,8 +5719,10 @@
       <c r="AG68" s="29"/>
       <c r="AH68" s="1"/>
       <c r="AI68" s="1"/>
-    </row>
-    <row r="69" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ68" s="1"/>
+      <c r="AK68" s="1"/>
+    </row>
+    <row r="69" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A69" s="3">
         <v>66</v>
       </c>
@@ -5607,8 +5766,10 @@
       <c r="AG69" s="29"/>
       <c r="AH69" s="1"/>
       <c r="AI69" s="1"/>
-    </row>
-    <row r="70" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ69" s="1"/>
+      <c r="AK69" s="1"/>
+    </row>
+    <row r="70" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A70" s="3">
         <v>67</v>
       </c>
@@ -5650,8 +5811,10 @@
       <c r="AG70" s="29"/>
       <c r="AH70" s="1"/>
       <c r="AI70" s="1"/>
-    </row>
-    <row r="71" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ70" s="1"/>
+      <c r="AK70" s="1"/>
+    </row>
+    <row r="71" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A71" s="3">
         <v>68</v>
       </c>
@@ -5693,8 +5856,10 @@
       <c r="AG71" s="29"/>
       <c r="AH71" s="1"/>
       <c r="AI71" s="1"/>
-    </row>
-    <row r="72" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ71" s="1"/>
+      <c r="AK71" s="1"/>
+    </row>
+    <row r="72" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A72" s="3">
         <v>69</v>
       </c>
@@ -5734,8 +5899,10 @@
       <c r="AG72" s="29"/>
       <c r="AH72" s="1"/>
       <c r="AI72" s="1"/>
-    </row>
-    <row r="73" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ72" s="1"/>
+      <c r="AK72" s="1"/>
+    </row>
+    <row r="73" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A73" s="3">
         <v>70</v>
       </c>
@@ -5775,8 +5942,10 @@
       <c r="AG73" s="29"/>
       <c r="AH73" s="1"/>
       <c r="AI73" s="1"/>
-    </row>
-    <row r="74" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ73" s="1"/>
+      <c r="AK73" s="1"/>
+    </row>
+    <row r="74" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A74" s="3">
         <v>71</v>
       </c>
@@ -5816,8 +5985,10 @@
       <c r="AG74" s="29"/>
       <c r="AH74" s="1"/>
       <c r="AI74" s="1"/>
-    </row>
-    <row r="75" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ74" s="1"/>
+      <c r="AK74" s="1"/>
+    </row>
+    <row r="75" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A75" s="3">
         <v>72</v>
       </c>
@@ -5857,8 +6028,10 @@
       <c r="AG75" s="29"/>
       <c r="AH75" s="1"/>
       <c r="AI75" s="1"/>
-    </row>
-    <row r="76" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ75" s="1"/>
+      <c r="AK75" s="1"/>
+    </row>
+    <row r="76" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A76" s="3">
         <v>73</v>
       </c>
@@ -5902,8 +6075,10 @@
       <c r="AG76" s="29"/>
       <c r="AH76" s="1"/>
       <c r="AI76" s="1"/>
-    </row>
-    <row r="77" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ76" s="1"/>
+      <c r="AK76" s="1"/>
+    </row>
+    <row r="77" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A77" s="3">
         <v>74</v>
       </c>
@@ -5945,8 +6120,10 @@
       <c r="AG77" s="29"/>
       <c r="AH77" s="1"/>
       <c r="AI77" s="1"/>
-    </row>
-    <row r="78" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ77" s="1"/>
+      <c r="AK77" s="1"/>
+    </row>
+    <row r="78" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A78" s="3">
         <v>75</v>
       </c>
@@ -5988,8 +6165,10 @@
       <c r="AG78" s="29"/>
       <c r="AH78" s="1"/>
       <c r="AI78" s="1"/>
-    </row>
-    <row r="79" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ78" s="1"/>
+      <c r="AK78" s="1"/>
+    </row>
+    <row r="79" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A79" s="3">
         <v>76</v>
       </c>
@@ -6031,8 +6210,10 @@
       <c r="AG79" s="29"/>
       <c r="AH79" s="1"/>
       <c r="AI79" s="1"/>
-    </row>
-    <row r="80" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ79" s="1"/>
+      <c r="AK79" s="1"/>
+    </row>
+    <row r="80" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A80" s="3">
         <v>77</v>
       </c>
@@ -6074,8 +6255,10 @@
       <c r="AG80" s="29"/>
       <c r="AH80" s="1"/>
       <c r="AI80" s="1"/>
-    </row>
-    <row r="81" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ80" s="1"/>
+      <c r="AK80" s="1"/>
+    </row>
+    <row r="81" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A81" s="3">
         <v>78</v>
       </c>
@@ -6119,8 +6302,10 @@
       <c r="AG81" s="29"/>
       <c r="AH81" s="1"/>
       <c r="AI81" s="1"/>
-    </row>
-    <row r="82" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ81" s="1"/>
+      <c r="AK81" s="1"/>
+    </row>
+    <row r="82" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A82" s="3">
         <v>79</v>
       </c>
@@ -6164,8 +6349,10 @@
       <c r="AG82" s="29"/>
       <c r="AH82" s="1"/>
       <c r="AI82" s="1"/>
-    </row>
-    <row r="83" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ82" s="1"/>
+      <c r="AK82" s="1"/>
+    </row>
+    <row r="83" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A83" s="3">
         <v>80</v>
       </c>
@@ -6209,8 +6396,10 @@
       <c r="AG83" s="29"/>
       <c r="AH83" s="1"/>
       <c r="AI83" s="1"/>
-    </row>
-    <row r="84" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ83" s="1"/>
+      <c r="AK83" s="1"/>
+    </row>
+    <row r="84" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A84" s="3">
         <v>81</v>
       </c>
@@ -6252,8 +6441,10 @@
       <c r="AG84" s="29"/>
       <c r="AH84" s="1"/>
       <c r="AI84" s="1"/>
-    </row>
-    <row r="85" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ84" s="1"/>
+      <c r="AK84" s="1"/>
+    </row>
+    <row r="85" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A85" s="3">
         <v>82</v>
       </c>
@@ -6293,8 +6484,10 @@
       <c r="AG85" s="29"/>
       <c r="AH85" s="1"/>
       <c r="AI85" s="1"/>
-    </row>
-    <row r="86" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ85" s="1"/>
+      <c r="AK85" s="1"/>
+    </row>
+    <row r="86" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A86" s="3">
         <v>83</v>
       </c>
@@ -6334,8 +6527,10 @@
       <c r="AG86" s="29"/>
       <c r="AH86" s="1"/>
       <c r="AI86" s="1"/>
-    </row>
-    <row r="87" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ86" s="1"/>
+      <c r="AK86" s="1"/>
+    </row>
+    <row r="87" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A87" s="3">
         <v>84</v>
       </c>
@@ -6375,8 +6570,10 @@
       <c r="AG87" s="29"/>
       <c r="AH87" s="1"/>
       <c r="AI87" s="1"/>
-    </row>
-    <row r="88" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ87" s="1"/>
+      <c r="AK87" s="1"/>
+    </row>
+    <row r="88" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A88" s="3">
         <v>85</v>
       </c>
@@ -6418,8 +6615,10 @@
       <c r="AG88" s="29"/>
       <c r="AH88" s="1"/>
       <c r="AI88" s="1"/>
-    </row>
-    <row r="89" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ88" s="1"/>
+      <c r="AK88" s="1"/>
+    </row>
+    <row r="89" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A89" s="3">
         <v>86</v>
       </c>
@@ -6459,8 +6658,10 @@
       <c r="AG89" s="29"/>
       <c r="AH89" s="1"/>
       <c r="AI89" s="1"/>
-    </row>
-    <row r="90" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ89" s="1"/>
+      <c r="AK89" s="1"/>
+    </row>
+    <row r="90" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A90" s="3">
         <v>87</v>
       </c>
@@ -6500,8 +6701,10 @@
       <c r="AG90" s="29"/>
       <c r="AH90" s="1"/>
       <c r="AI90" s="1"/>
-    </row>
-    <row r="91" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ90" s="1"/>
+      <c r="AK90" s="1"/>
+    </row>
+    <row r="91" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A91" s="3">
         <v>88</v>
       </c>
@@ -6543,8 +6746,10 @@
       <c r="AG91" s="29"/>
       <c r="AH91" s="1"/>
       <c r="AI91" s="1"/>
-    </row>
-    <row r="92" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ91" s="1"/>
+      <c r="AK91" s="1"/>
+    </row>
+    <row r="92" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A92" s="3">
         <v>89</v>
       </c>
@@ -6586,8 +6791,10 @@
       <c r="AG92" s="29"/>
       <c r="AH92" s="1"/>
       <c r="AI92" s="1"/>
-    </row>
-    <row r="93" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ92" s="1"/>
+      <c r="AK92" s="1"/>
+    </row>
+    <row r="93" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A93" s="3">
         <v>90</v>
       </c>
@@ -6627,8 +6834,10 @@
       <c r="AG93" s="29"/>
       <c r="AH93" s="1"/>
       <c r="AI93" s="1"/>
-    </row>
-    <row r="94" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ93" s="1"/>
+      <c r="AK93" s="1"/>
+    </row>
+    <row r="94" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A94" s="3">
         <v>91</v>
       </c>
@@ -6668,8 +6877,10 @@
       <c r="AG94" s="29"/>
       <c r="AH94" s="1"/>
       <c r="AI94" s="1"/>
-    </row>
-    <row r="95" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ94" s="1"/>
+      <c r="AK94" s="1"/>
+    </row>
+    <row r="95" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A95" s="3">
         <v>92</v>
       </c>
@@ -6709,8 +6920,10 @@
       <c r="AG95" s="29"/>
       <c r="AH95" s="1"/>
       <c r="AI95" s="1"/>
-    </row>
-    <row r="96" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ95" s="1"/>
+      <c r="AK95" s="1"/>
+    </row>
+    <row r="96" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A96" s="3">
         <v>93</v>
       </c>
@@ -6750,8 +6963,10 @@
       <c r="AG96" s="29"/>
       <c r="AH96" s="1"/>
       <c r="AI96" s="1"/>
-    </row>
-    <row r="97" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ96" s="1"/>
+      <c r="AK96" s="1"/>
+    </row>
+    <row r="97" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A97" s="3">
         <v>94</v>
       </c>
@@ -6791,8 +7006,10 @@
       <c r="AG97" s="29"/>
       <c r="AH97" s="1"/>
       <c r="AI97" s="1"/>
-    </row>
-    <row r="98" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ97" s="1"/>
+      <c r="AK97" s="1"/>
+    </row>
+    <row r="98" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A98" s="3">
         <v>95</v>
       </c>
@@ -6834,8 +7051,10 @@
       <c r="AG98" s="29"/>
       <c r="AH98" s="1"/>
       <c r="AI98" s="1"/>
-    </row>
-    <row r="99" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ98" s="1"/>
+      <c r="AK98" s="1"/>
+    </row>
+    <row r="99" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A99" s="3">
         <v>96</v>
       </c>
@@ -6875,8 +7094,10 @@
       <c r="AG99" s="29"/>
       <c r="AH99" s="1"/>
       <c r="AI99" s="1"/>
-    </row>
-    <row r="100" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ99" s="1"/>
+      <c r="AK99" s="1"/>
+    </row>
+    <row r="100" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A100" s="3">
         <v>97</v>
       </c>
@@ -6916,8 +7137,10 @@
       <c r="AG100" s="29"/>
       <c r="AH100" s="1"/>
       <c r="AI100" s="1"/>
-    </row>
-    <row r="101" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ100" s="1"/>
+      <c r="AK100" s="1"/>
+    </row>
+    <row r="101" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A101" s="3">
         <v>98</v>
       </c>
@@ -6957,8 +7180,10 @@
       <c r="AG101" s="29"/>
       <c r="AH101" s="1"/>
       <c r="AI101" s="1"/>
-    </row>
-    <row r="102" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ101" s="1"/>
+      <c r="AK101" s="1"/>
+    </row>
+    <row r="102" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A102" s="3">
         <v>99</v>
       </c>
@@ -6998,8 +7223,10 @@
       <c r="AG102" s="29"/>
       <c r="AH102" s="1"/>
       <c r="AI102" s="1"/>
-    </row>
-    <row r="103" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ102" s="1"/>
+      <c r="AK102" s="1"/>
+    </row>
+    <row r="103" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A103" s="3">
         <v>100</v>
       </c>
@@ -7039,8 +7266,10 @@
       <c r="AG103" s="29"/>
       <c r="AH103" s="1"/>
       <c r="AI103" s="1"/>
-    </row>
-    <row r="104" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ103" s="1"/>
+      <c r="AK103" s="1"/>
+    </row>
+    <row r="104" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A104" s="3">
         <v>101</v>
       </c>
@@ -7080,8 +7309,10 @@
       <c r="AG104" s="29"/>
       <c r="AH104" s="1"/>
       <c r="AI104" s="1"/>
-    </row>
-    <row r="105" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ104" s="1"/>
+      <c r="AK104" s="1"/>
+    </row>
+    <row r="105" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A105" s="3">
         <v>102</v>
       </c>
@@ -7123,8 +7354,10 @@
       <c r="AG105" s="29"/>
       <c r="AH105" s="1"/>
       <c r="AI105" s="1"/>
-    </row>
-    <row r="106" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ105" s="1"/>
+      <c r="AK105" s="1"/>
+    </row>
+    <row r="106" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A106" s="3">
         <v>103</v>
       </c>
@@ -7164,8 +7397,10 @@
       <c r="AG106" s="29"/>
       <c r="AH106" s="1"/>
       <c r="AI106" s="1"/>
-    </row>
-    <row r="107" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ106" s="1"/>
+      <c r="AK106" s="1"/>
+    </row>
+    <row r="107" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A107" s="3">
         <v>104</v>
       </c>
@@ -7207,8 +7442,10 @@
       <c r="AG107" s="29"/>
       <c r="AH107" s="1"/>
       <c r="AI107" s="1"/>
-    </row>
-    <row r="108" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ107" s="1"/>
+      <c r="AK107" s="1"/>
+    </row>
+    <row r="108" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A108" s="3">
         <v>105</v>
       </c>
@@ -7248,8 +7485,10 @@
       <c r="AG108" s="29"/>
       <c r="AH108" s="1"/>
       <c r="AI108" s="1"/>
-    </row>
-    <row r="109" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ108" s="1"/>
+      <c r="AK108" s="1"/>
+    </row>
+    <row r="109" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A109" s="3">
         <v>106</v>
       </c>
@@ -7291,8 +7530,10 @@
       <c r="AG109" s="29"/>
       <c r="AH109" s="1"/>
       <c r="AI109" s="1"/>
-    </row>
-    <row r="110" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ109" s="1"/>
+      <c r="AK109" s="1"/>
+    </row>
+    <row r="110" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A110" s="3">
         <v>107</v>
       </c>
@@ -7332,8 +7573,10 @@
       <c r="AG110" s="29"/>
       <c r="AH110" s="1"/>
       <c r="AI110" s="1"/>
-    </row>
-    <row r="111" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ110" s="1"/>
+      <c r="AK110" s="1"/>
+    </row>
+    <row r="111" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A111" s="3">
         <v>108</v>
       </c>
@@ -7373,8 +7616,10 @@
       <c r="AG111" s="29"/>
       <c r="AH111" s="1"/>
       <c r="AI111" s="1"/>
-    </row>
-    <row r="112" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ111" s="1"/>
+      <c r="AK111" s="1"/>
+    </row>
+    <row r="112" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A112" s="3">
         <v>109</v>
       </c>
@@ -7420,8 +7665,10 @@
       <c r="AG112" s="29"/>
       <c r="AH112" s="1"/>
       <c r="AI112" s="1"/>
-    </row>
-    <row r="113" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ112" s="1"/>
+      <c r="AK112" s="1"/>
+    </row>
+    <row r="113" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A113" s="3">
         <v>110</v>
       </c>
@@ -7463,8 +7710,10 @@
       <c r="AG113" s="29"/>
       <c r="AH113" s="1"/>
       <c r="AI113" s="1"/>
-    </row>
-    <row r="114" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ113" s="1"/>
+      <c r="AK113" s="1"/>
+    </row>
+    <row r="114" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A114" s="3">
         <v>111</v>
       </c>
@@ -7504,8 +7753,10 @@
       <c r="AG114" s="29"/>
       <c r="AH114" s="1"/>
       <c r="AI114" s="1"/>
-    </row>
-    <row r="115" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ114" s="1"/>
+      <c r="AK114" s="1"/>
+    </row>
+    <row r="115" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A115" s="3">
         <v>112</v>
       </c>
@@ -7547,8 +7798,10 @@
       <c r="AG115" s="29"/>
       <c r="AH115" s="1"/>
       <c r="AI115" s="1"/>
-    </row>
-    <row r="116" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ115" s="1"/>
+      <c r="AK115" s="1"/>
+    </row>
+    <row r="116" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A116" s="3">
         <v>113</v>
       </c>
@@ -7588,8 +7841,10 @@
       <c r="AG116" s="29"/>
       <c r="AH116" s="1"/>
       <c r="AI116" s="1"/>
-    </row>
-    <row r="117" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ116" s="1"/>
+      <c r="AK116" s="1"/>
+    </row>
+    <row r="117" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A117" s="3">
         <v>114</v>
       </c>
@@ -7629,8 +7884,10 @@
       <c r="AG117" s="29"/>
       <c r="AH117" s="1"/>
       <c r="AI117" s="1"/>
-    </row>
-    <row r="118" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ117" s="1"/>
+      <c r="AK117" s="1"/>
+    </row>
+    <row r="118" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A118" s="3">
         <v>115</v>
       </c>
@@ -7670,8 +7927,10 @@
       <c r="AG118" s="29"/>
       <c r="AH118" s="1"/>
       <c r="AI118" s="1"/>
-    </row>
-    <row r="119" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ118" s="1"/>
+      <c r="AK118" s="1"/>
+    </row>
+    <row r="119" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A119" s="3">
         <v>116</v>
       </c>
@@ -7711,8 +7970,10 @@
       <c r="AG119" s="29"/>
       <c r="AH119" s="1"/>
       <c r="AI119" s="1"/>
-    </row>
-    <row r="120" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ119" s="1"/>
+      <c r="AK119" s="1"/>
+    </row>
+    <row r="120" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A120" s="3">
         <v>117</v>
       </c>
@@ -7752,8 +8013,10 @@
       <c r="AG120" s="29"/>
       <c r="AH120" s="1"/>
       <c r="AI120" s="1"/>
-    </row>
-    <row r="121" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ120" s="1"/>
+      <c r="AK120" s="1"/>
+    </row>
+    <row r="121" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A121" s="3">
         <v>118</v>
       </c>
@@ -7793,8 +8056,10 @@
       <c r="AG121" s="29"/>
       <c r="AH121" s="1"/>
       <c r="AI121" s="1"/>
-    </row>
-    <row r="122" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ121" s="1"/>
+      <c r="AK121" s="1"/>
+    </row>
+    <row r="122" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A122" s="3">
         <v>119</v>
       </c>
@@ -7834,8 +8099,10 @@
       <c r="AG122" s="29"/>
       <c r="AH122" s="1"/>
       <c r="AI122" s="1"/>
-    </row>
-    <row r="123" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ122" s="1"/>
+      <c r="AK122" s="1"/>
+    </row>
+    <row r="123" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A123" s="3">
         <v>120</v>
       </c>
@@ -7875,8 +8142,10 @@
       <c r="AG123" s="29"/>
       <c r="AH123" s="1"/>
       <c r="AI123" s="1"/>
-    </row>
-    <row r="124" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ123" s="1"/>
+      <c r="AK123" s="1"/>
+    </row>
+    <row r="124" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A124" s="3">
         <v>121</v>
       </c>
@@ -7916,8 +8185,10 @@
       <c r="AG124" s="29"/>
       <c r="AH124" s="1"/>
       <c r="AI124" s="1"/>
-    </row>
-    <row r="125" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ124" s="1"/>
+      <c r="AK124" s="1"/>
+    </row>
+    <row r="125" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A125" s="3">
         <v>122</v>
       </c>
@@ -7957,8 +8228,10 @@
       <c r="AG125" s="29"/>
       <c r="AH125" s="1"/>
       <c r="AI125" s="1"/>
-    </row>
-    <row r="126" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ125" s="1"/>
+      <c r="AK125" s="1"/>
+    </row>
+    <row r="126" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A126" s="3">
         <v>123</v>
       </c>
@@ -8000,8 +8273,10 @@
       <c r="AG126" s="29"/>
       <c r="AH126" s="1"/>
       <c r="AI126" s="1"/>
-    </row>
-    <row r="127" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ126" s="1"/>
+      <c r="AK126" s="1"/>
+    </row>
+    <row r="127" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A127" s="3">
         <v>124</v>
       </c>
@@ -8041,8 +8316,10 @@
       <c r="AG127" s="29"/>
       <c r="AH127" s="1"/>
       <c r="AI127" s="1"/>
-    </row>
-    <row r="128" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ127" s="1"/>
+      <c r="AK127" s="1"/>
+    </row>
+    <row r="128" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A128" s="3">
         <v>125</v>
       </c>
@@ -8086,8 +8363,10 @@
       <c r="AG128" s="29"/>
       <c r="AH128" s="1"/>
       <c r="AI128" s="1"/>
-    </row>
-    <row r="129" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ128" s="1"/>
+      <c r="AK128" s="1"/>
+    </row>
+    <row r="129" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A129" s="3">
         <v>126</v>
       </c>
@@ -8129,8 +8408,10 @@
       <c r="AG129" s="29"/>
       <c r="AH129" s="1"/>
       <c r="AI129" s="1"/>
-    </row>
-    <row r="130" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ129" s="1"/>
+      <c r="AK129" s="1"/>
+    </row>
+    <row r="130" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A130" s="3">
         <v>127</v>
       </c>
@@ -8174,8 +8455,10 @@
       <c r="AG130" s="29"/>
       <c r="AH130" s="1"/>
       <c r="AI130" s="1"/>
-    </row>
-    <row r="131" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ130" s="1"/>
+      <c r="AK130" s="1"/>
+    </row>
+    <row r="131" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A131" s="3">
         <v>128</v>
       </c>
@@ -8217,8 +8500,10 @@
       <c r="AG131" s="29"/>
       <c r="AH131" s="1"/>
       <c r="AI131" s="1"/>
-    </row>
-    <row r="132" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ131" s="1"/>
+      <c r="AK131" s="1"/>
+    </row>
+    <row r="132" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A132" s="3">
         <v>129</v>
       </c>
@@ -8258,8 +8543,10 @@
       <c r="AG132" s="29"/>
       <c r="AH132" s="1"/>
       <c r="AI132" s="1"/>
-    </row>
-    <row r="133" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ132" s="1"/>
+      <c r="AK132" s="1"/>
+    </row>
+    <row r="133" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A133" s="3">
         <v>130</v>
       </c>
@@ -8299,8 +8586,10 @@
       <c r="AG133" s="29"/>
       <c r="AH133" s="1"/>
       <c r="AI133" s="1"/>
-    </row>
-    <row r="134" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ133" s="1"/>
+      <c r="AK133" s="1"/>
+    </row>
+    <row r="134" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A134" s="3">
         <v>131</v>
       </c>
@@ -8340,8 +8629,10 @@
       <c r="AG134" s="29"/>
       <c r="AH134" s="1"/>
       <c r="AI134" s="1"/>
-    </row>
-    <row r="135" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ134" s="1"/>
+      <c r="AK134" s="1"/>
+    </row>
+    <row r="135" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A135" s="3">
         <v>132</v>
       </c>
@@ -8381,8 +8672,10 @@
       <c r="AG135" s="29"/>
       <c r="AH135" s="1"/>
       <c r="AI135" s="1"/>
-    </row>
-    <row r="136" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ135" s="1"/>
+      <c r="AK135" s="1"/>
+    </row>
+    <row r="136" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A136" s="3">
         <v>133</v>
       </c>
@@ -8422,8 +8715,10 @@
       <c r="AG136" s="29"/>
       <c r="AH136" s="1"/>
       <c r="AI136" s="1"/>
-    </row>
-    <row r="137" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ136" s="1"/>
+      <c r="AK136" s="1"/>
+    </row>
+    <row r="137" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A137" s="3">
         <v>134</v>
       </c>
@@ -8463,8 +8758,10 @@
       <c r="AG137" s="29"/>
       <c r="AH137" s="1"/>
       <c r="AI137" s="1"/>
-    </row>
-    <row r="138" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ137" s="1"/>
+      <c r="AK137" s="1"/>
+    </row>
+    <row r="138" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A138" s="3">
         <v>135</v>
       </c>
@@ -8504,8 +8801,10 @@
       <c r="AG138" s="29"/>
       <c r="AH138" s="1"/>
       <c r="AI138" s="1"/>
-    </row>
-    <row r="139" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ138" s="1"/>
+      <c r="AK138" s="1"/>
+    </row>
+    <row r="139" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A139" s="3">
         <v>136</v>
       </c>
@@ -8545,8 +8844,10 @@
       <c r="AG139" s="29"/>
       <c r="AH139" s="1"/>
       <c r="AI139" s="1"/>
-    </row>
-    <row r="140" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ139" s="1"/>
+      <c r="AK139" s="1"/>
+    </row>
+    <row r="140" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A140" s="3">
         <v>137</v>
       </c>
@@ -8586,8 +8887,10 @@
       <c r="AG140" s="29"/>
       <c r="AH140" s="1"/>
       <c r="AI140" s="1"/>
-    </row>
-    <row r="141" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ140" s="1"/>
+      <c r="AK140" s="1"/>
+    </row>
+    <row r="141" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A141" s="3">
         <v>138</v>
       </c>
@@ -8627,8 +8930,10 @@
       <c r="AG141" s="29"/>
       <c r="AH141" s="1"/>
       <c r="AI141" s="1"/>
-    </row>
-    <row r="142" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ141" s="1"/>
+      <c r="AK141" s="1"/>
+    </row>
+    <row r="142" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A142" s="3">
         <v>139</v>
       </c>
@@ -8668,8 +8973,10 @@
       <c r="AG142" s="29"/>
       <c r="AH142" s="1"/>
       <c r="AI142" s="1"/>
-    </row>
-    <row r="143" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ142" s="1"/>
+      <c r="AK142" s="1"/>
+    </row>
+    <row r="143" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A143" s="3">
         <v>140</v>
       </c>
@@ -8709,8 +9016,10 @@
       <c r="AG143" s="29"/>
       <c r="AH143" s="1"/>
       <c r="AI143" s="1"/>
-    </row>
-    <row r="144" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ143" s="1"/>
+      <c r="AK143" s="1"/>
+    </row>
+    <row r="144" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A144" s="3">
         <v>141</v>
       </c>
@@ -8750,8 +9059,10 @@
       <c r="AG144" s="29"/>
       <c r="AH144" s="1"/>
       <c r="AI144" s="1"/>
-    </row>
-    <row r="145" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ144" s="1"/>
+      <c r="AK144" s="1"/>
+    </row>
+    <row r="145" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A145" s="3">
         <v>142</v>
       </c>
@@ -8791,8 +9102,10 @@
       <c r="AG145" s="29"/>
       <c r="AH145" s="1"/>
       <c r="AI145" s="1"/>
-    </row>
-    <row r="146" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ145" s="1"/>
+      <c r="AK145" s="1"/>
+    </row>
+    <row r="146" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A146" s="3">
         <v>143</v>
       </c>
@@ -8832,8 +9145,10 @@
       <c r="AG146" s="29"/>
       <c r="AH146" s="1"/>
       <c r="AI146" s="1"/>
-    </row>
-    <row r="147" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ146" s="1"/>
+      <c r="AK146" s="1"/>
+    </row>
+    <row r="147" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A147" s="3">
         <v>144</v>
       </c>
@@ -8873,8 +9188,10 @@
       <c r="AG147" s="29"/>
       <c r="AH147" s="1"/>
       <c r="AI147" s="1"/>
-    </row>
-    <row r="148" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ147" s="1"/>
+      <c r="AK147" s="1"/>
+    </row>
+    <row r="148" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A148" s="3">
         <v>145</v>
       </c>
@@ -8916,8 +9233,10 @@
       <c r="AG148" s="29"/>
       <c r="AH148" s="1"/>
       <c r="AI148" s="1"/>
-    </row>
-    <row r="149" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ148" s="1"/>
+      <c r="AK148" s="1"/>
+    </row>
+    <row r="149" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A149" s="3">
         <v>146</v>
       </c>
@@ -8957,8 +9276,10 @@
       <c r="AG149" s="29"/>
       <c r="AH149" s="1"/>
       <c r="AI149" s="1"/>
-    </row>
-    <row r="150" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ149" s="1"/>
+      <c r="AK149" s="1"/>
+    </row>
+    <row r="150" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A150" s="3">
         <v>147</v>
       </c>
@@ -8998,8 +9319,10 @@
       <c r="AG150" s="29"/>
       <c r="AH150" s="1"/>
       <c r="AI150" s="1"/>
-    </row>
-    <row r="151" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ150" s="1"/>
+      <c r="AK150" s="1"/>
+    </row>
+    <row r="151" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A151" s="3">
         <v>148</v>
       </c>
@@ -9039,8 +9362,10 @@
       <c r="AG151" s="29"/>
       <c r="AH151" s="1"/>
       <c r="AI151" s="1"/>
-    </row>
-    <row r="152" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ151" s="1"/>
+      <c r="AK151" s="1"/>
+    </row>
+    <row r="152" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A152" s="3">
         <v>149</v>
       </c>
@@ -9080,8 +9405,10 @@
       <c r="AG152" s="29"/>
       <c r="AH152" s="1"/>
       <c r="AI152" s="1"/>
-    </row>
-    <row r="153" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ152" s="1"/>
+      <c r="AK152" s="1"/>
+    </row>
+    <row r="153" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A153" s="3">
         <v>150</v>
       </c>
@@ -9123,8 +9450,10 @@
       <c r="AG153" s="29"/>
       <c r="AH153" s="1"/>
       <c r="AI153" s="1"/>
-    </row>
-    <row r="154" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ153" s="1"/>
+      <c r="AK153" s="1"/>
+    </row>
+    <row r="154" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A154" s="3">
         <v>151</v>
       </c>
@@ -9166,8 +9495,10 @@
       <c r="AG154" s="29"/>
       <c r="AH154" s="1"/>
       <c r="AI154" s="1"/>
-    </row>
-    <row r="155" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ154" s="1"/>
+      <c r="AK154" s="1"/>
+    </row>
+    <row r="155" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A155" s="3">
         <v>152</v>
       </c>
@@ -9211,8 +9542,10 @@
       <c r="AG155" s="29"/>
       <c r="AH155" s="1"/>
       <c r="AI155" s="1"/>
-    </row>
-    <row r="156" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ155" s="1"/>
+      <c r="AK155" s="1"/>
+    </row>
+    <row r="156" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A156" s="3">
         <v>153</v>
       </c>
@@ -9254,8 +9587,10 @@
       <c r="AG156" s="29"/>
       <c r="AH156" s="1"/>
       <c r="AI156" s="1"/>
-    </row>
-    <row r="157" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ156" s="1"/>
+      <c r="AK156" s="1"/>
+    </row>
+    <row r="157" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A157" s="3">
         <v>154</v>
       </c>
@@ -9297,8 +9632,10 @@
       <c r="AG157" s="29"/>
       <c r="AH157" s="1"/>
       <c r="AI157" s="1"/>
-    </row>
-    <row r="158" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ157" s="1"/>
+      <c r="AK157" s="1"/>
+    </row>
+    <row r="158" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A158" s="3">
         <v>155</v>
       </c>
@@ -9342,8 +9679,10 @@
       <c r="AG158" s="29"/>
       <c r="AH158" s="1"/>
       <c r="AI158" s="1"/>
-    </row>
-    <row r="159" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ158" s="1"/>
+      <c r="AK158" s="1"/>
+    </row>
+    <row r="159" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A159" s="3">
         <v>156</v>
       </c>
@@ -9385,8 +9724,10 @@
       <c r="AG159" s="29"/>
       <c r="AH159" s="1"/>
       <c r="AI159" s="1"/>
-    </row>
-    <row r="160" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ159" s="1"/>
+      <c r="AK159" s="1"/>
+    </row>
+    <row r="160" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A160" s="3">
         <v>157</v>
       </c>
@@ -9430,8 +9771,10 @@
       <c r="AG160" s="29"/>
       <c r="AH160" s="1"/>
       <c r="AI160" s="1"/>
-    </row>
-    <row r="161" spans="1:35" ht="15" customHeight="1">
+      <c r="AJ160" s="1"/>
+      <c r="AK160" s="1"/>
+    </row>
+    <row r="161" spans="1:37" ht="15" customHeight="1">
       <c r="A161" s="3">
         <v>158</v>
       </c>
@@ -9473,8 +9816,10 @@
       <c r="AG161" s="29"/>
       <c r="AH161" s="1"/>
       <c r="AI161" s="1"/>
-    </row>
-    <row r="162" spans="1:35" ht="15" customHeight="1">
+      <c r="AJ161" s="1"/>
+      <c r="AK161" s="1"/>
+    </row>
+    <row r="162" spans="1:37" ht="15" customHeight="1">
       <c r="A162" s="3">
         <v>159</v>
       </c>
@@ -9516,8 +9861,10 @@
       <c r="AG162" s="29"/>
       <c r="AH162" s="1"/>
       <c r="AI162" s="1"/>
-    </row>
-    <row r="163" spans="1:35" ht="15" customHeight="1">
+      <c r="AJ162" s="1"/>
+      <c r="AK162" s="1"/>
+    </row>
+    <row r="163" spans="1:37" ht="15" customHeight="1">
       <c r="A163" s="3">
         <v>160</v>
       </c>
@@ -9561,8 +9908,10 @@
       <c r="AG163" s="29"/>
       <c r="AH163" s="1"/>
       <c r="AI163" s="1"/>
-    </row>
-    <row r="164" spans="1:35" ht="15" customHeight="1">
+      <c r="AJ163" s="1"/>
+      <c r="AK163" s="1"/>
+    </row>
+    <row r="164" spans="1:37" ht="15" customHeight="1">
       <c r="A164" s="3">
         <v>161</v>
       </c>
@@ -9604,8 +9953,10 @@
       <c r="AG164" s="30"/>
       <c r="AH164" s="3"/>
       <c r="AI164" s="3"/>
-    </row>
-    <row r="165" spans="1:35" ht="15" customHeight="1">
+      <c r="AJ164" s="3"/>
+      <c r="AK164" s="3"/>
+    </row>
+    <row r="165" spans="1:37" ht="15" customHeight="1">
       <c r="A165" s="3">
         <v>162</v>
       </c>
@@ -9647,8 +9998,10 @@
       <c r="AG165" s="30"/>
       <c r="AH165" s="3"/>
       <c r="AI165" s="3"/>
-    </row>
-    <row r="166" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ165" s="3"/>
+      <c r="AK165" s="3"/>
+    </row>
+    <row r="166" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A166" s="3">
         <v>163</v>
       </c>
@@ -9688,8 +10041,10 @@
       <c r="AG166" s="29"/>
       <c r="AH166" s="1"/>
       <c r="AI166" s="1"/>
-    </row>
-    <row r="167" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ166" s="1"/>
+      <c r="AK166" s="1"/>
+    </row>
+    <row r="167" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A167" s="3">
         <v>164</v>
       </c>
@@ -9729,8 +10084,10 @@
       <c r="AG167" s="29"/>
       <c r="AH167" s="1"/>
       <c r="AI167" s="1"/>
-    </row>
-    <row r="168" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ167" s="1"/>
+      <c r="AK167" s="1"/>
+    </row>
+    <row r="168" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A168" s="3">
         <v>165</v>
       </c>
@@ -9770,8 +10127,10 @@
       <c r="AG168" s="29"/>
       <c r="AH168" s="1"/>
       <c r="AI168" s="1"/>
-    </row>
-    <row r="169" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ168" s="1"/>
+      <c r="AK168" s="1"/>
+    </row>
+    <row r="169" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A169" s="3">
         <v>166</v>
       </c>
@@ -9811,8 +10170,10 @@
       <c r="AG169" s="29"/>
       <c r="AH169" s="1"/>
       <c r="AI169" s="1"/>
-    </row>
-    <row r="170" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ169" s="1"/>
+      <c r="AK169" s="1"/>
+    </row>
+    <row r="170" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A170" s="3">
         <v>167</v>
       </c>
@@ -9852,8 +10213,10 @@
       <c r="AG170" s="29"/>
       <c r="AH170" s="1"/>
       <c r="AI170" s="1"/>
-    </row>
-    <row r="171" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ170" s="1"/>
+      <c r="AK170" s="1"/>
+    </row>
+    <row r="171" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A171" s="3">
         <v>168</v>
       </c>
@@ -9893,8 +10256,10 @@
       <c r="AG171" s="29"/>
       <c r="AH171" s="1"/>
       <c r="AI171" s="1"/>
-    </row>
-    <row r="172" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ171" s="1"/>
+      <c r="AK171" s="1"/>
+    </row>
+    <row r="172" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A172" s="3">
         <v>169</v>
       </c>
@@ -9936,8 +10301,10 @@
       <c r="AG172" s="29"/>
       <c r="AH172" s="1"/>
       <c r="AI172" s="1"/>
-    </row>
-    <row r="173" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ172" s="1"/>
+      <c r="AK172" s="1"/>
+    </row>
+    <row r="173" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A173" s="3">
         <v>170</v>
       </c>
@@ -9977,8 +10344,10 @@
       <c r="AG173" s="29"/>
       <c r="AH173" s="1"/>
       <c r="AI173" s="1"/>
-    </row>
-    <row r="174" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ173" s="1"/>
+      <c r="AK173" s="1"/>
+    </row>
+    <row r="174" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A174" s="3">
         <v>171</v>
       </c>
@@ -10028,8 +10397,10 @@
       <c r="AG174" s="29"/>
       <c r="AH174" s="1"/>
       <c r="AI174" s="1"/>
-    </row>
-    <row r="175" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ174" s="1"/>
+      <c r="AK174" s="1"/>
+    </row>
+    <row r="175" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A175" s="3">
         <v>172</v>
       </c>
@@ -10075,8 +10446,10 @@
       <c r="AG175" s="29"/>
       <c r="AH175" s="1"/>
       <c r="AI175" s="1"/>
-    </row>
-    <row r="176" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ175" s="1"/>
+      <c r="AK175" s="1"/>
+    </row>
+    <row r="176" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A176" s="3">
         <v>173</v>
       </c>
@@ -10126,8 +10499,10 @@
       <c r="AG176" s="29"/>
       <c r="AH176" s="1"/>
       <c r="AI176" s="1"/>
-    </row>
-    <row r="177" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ176" s="1"/>
+      <c r="AK176" s="1"/>
+    </row>
+    <row r="177" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A177" s="3">
         <v>174</v>
       </c>
@@ -10171,8 +10546,10 @@
       <c r="AG177" s="29"/>
       <c r="AH177" s="1"/>
       <c r="AI177" s="1"/>
-    </row>
-    <row r="178" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ177" s="1"/>
+      <c r="AK177" s="1"/>
+    </row>
+    <row r="178" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A178" s="3">
         <v>175</v>
       </c>
@@ -10216,8 +10593,10 @@
       <c r="AG178" s="29"/>
       <c r="AH178" s="1"/>
       <c r="AI178" s="1"/>
-    </row>
-    <row r="179" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ178" s="1"/>
+      <c r="AK178" s="1"/>
+    </row>
+    <row r="179" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A179" s="3">
         <v>176</v>
       </c>
@@ -10261,8 +10640,10 @@
       <c r="AG179" s="29"/>
       <c r="AH179" s="1"/>
       <c r="AI179" s="1"/>
-    </row>
-    <row r="180" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ179" s="1"/>
+      <c r="AK179" s="1"/>
+    </row>
+    <row r="180" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A180" s="3">
         <v>177</v>
       </c>
@@ -10308,8 +10689,10 @@
       <c r="AG180" s="29"/>
       <c r="AH180" s="1"/>
       <c r="AI180" s="1"/>
-    </row>
-    <row r="181" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ180" s="1"/>
+      <c r="AK180" s="1"/>
+    </row>
+    <row r="181" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A181" s="3">
         <v>178</v>
       </c>
@@ -10353,8 +10736,10 @@
       <c r="AG181" s="29"/>
       <c r="AH181" s="1"/>
       <c r="AI181" s="1"/>
-    </row>
-    <row r="182" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ181" s="1"/>
+      <c r="AK181" s="1"/>
+    </row>
+    <row r="182" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A182" s="3">
         <v>179</v>
       </c>
@@ -10400,8 +10785,10 @@
       <c r="AG182" s="29"/>
       <c r="AH182" s="1"/>
       <c r="AI182" s="1"/>
-    </row>
-    <row r="183" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ182" s="1"/>
+      <c r="AK182" s="1"/>
+    </row>
+    <row r="183" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A183" s="3">
         <v>180</v>
       </c>
@@ -10449,8 +10836,10 @@
       <c r="AG183" s="29"/>
       <c r="AH183" s="1"/>
       <c r="AI183" s="1"/>
-    </row>
-    <row r="184" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ183" s="1"/>
+      <c r="AK183" s="1"/>
+    </row>
+    <row r="184" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A184" s="3">
         <v>181</v>
       </c>
@@ -10498,8 +10887,10 @@
       <c r="AG184" s="29"/>
       <c r="AH184" s="1"/>
       <c r="AI184" s="1"/>
-    </row>
-    <row r="185" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ184" s="1"/>
+      <c r="AK184" s="1"/>
+    </row>
+    <row r="185" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A185" s="3">
         <v>182</v>
       </c>
@@ -10545,8 +10936,10 @@
       <c r="AG185" s="29"/>
       <c r="AH185" s="1"/>
       <c r="AI185" s="1"/>
-    </row>
-    <row r="186" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ185" s="1"/>
+      <c r="AK185" s="1"/>
+    </row>
+    <row r="186" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A186" s="3">
         <v>183</v>
       </c>
@@ -10596,8 +10989,10 @@
       <c r="AG186" s="29"/>
       <c r="AH186" s="1"/>
       <c r="AI186" s="1"/>
-    </row>
-    <row r="187" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ186" s="1"/>
+      <c r="AK186" s="1"/>
+    </row>
+    <row r="187" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A187" s="3">
         <v>184</v>
       </c>
@@ -10647,8 +11042,10 @@
       <c r="AG187" s="29"/>
       <c r="AH187" s="1"/>
       <c r="AI187" s="1"/>
-    </row>
-    <row r="188" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ187" s="1"/>
+      <c r="AK187" s="1"/>
+    </row>
+    <row r="188" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A188" s="3">
         <v>185</v>
       </c>
@@ -10700,8 +11097,10 @@
       <c r="AG188" s="29"/>
       <c r="AH188" s="1"/>
       <c r="AI188" s="1"/>
-    </row>
-    <row r="189" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ188" s="1"/>
+      <c r="AK188" s="1"/>
+    </row>
+    <row r="189" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A189" s="3">
         <v>186</v>
       </c>
@@ -10751,8 +11150,10 @@
       <c r="AG189" s="29"/>
       <c r="AH189" s="1"/>
       <c r="AI189" s="1"/>
-    </row>
-    <row r="190" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ189" s="1"/>
+      <c r="AK189" s="1"/>
+    </row>
+    <row r="190" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A190" s="3">
         <v>187</v>
       </c>
@@ -10802,8 +11203,10 @@
       <c r="AG190" s="29"/>
       <c r="AH190" s="1"/>
       <c r="AI190" s="1"/>
-    </row>
-    <row r="191" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ190" s="1"/>
+      <c r="AK190" s="1"/>
+    </row>
+    <row r="191" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A191" s="3">
         <v>188</v>
       </c>
@@ -10853,8 +11256,10 @@
       <c r="AG191" s="29"/>
       <c r="AH191" s="1"/>
       <c r="AI191" s="1"/>
-    </row>
-    <row r="192" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ191" s="1"/>
+      <c r="AK191" s="1"/>
+    </row>
+    <row r="192" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A192" s="3">
         <v>189</v>
       </c>
@@ -10898,8 +11303,10 @@
       <c r="AG192" s="29"/>
       <c r="AH192" s="1"/>
       <c r="AI192" s="1"/>
-    </row>
-    <row r="193" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ192" s="1"/>
+      <c r="AK192" s="1"/>
+    </row>
+    <row r="193" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A193" s="3">
         <v>190</v>
       </c>
@@ -10943,8 +11350,10 @@
       <c r="AG193" s="29"/>
       <c r="AH193" s="1"/>
       <c r="AI193" s="1"/>
-    </row>
-    <row r="194" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ193" s="1"/>
+      <c r="AK193" s="1"/>
+    </row>
+    <row r="194" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A194" s="3">
         <v>191</v>
       </c>
@@ -10986,8 +11395,10 @@
       <c r="AG194" s="29"/>
       <c r="AH194" s="1"/>
       <c r="AI194" s="1"/>
-    </row>
-    <row r="195" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ194" s="1"/>
+      <c r="AK194" s="1"/>
+    </row>
+    <row r="195" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A195" s="3">
         <v>192</v>
       </c>
@@ -11029,8 +11440,10 @@
       <c r="AG195" s="29"/>
       <c r="AH195" s="1"/>
       <c r="AI195" s="1"/>
-    </row>
-    <row r="196" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ195" s="1"/>
+      <c r="AK195" s="1"/>
+    </row>
+    <row r="196" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A196" s="3">
         <v>193</v>
       </c>
@@ -11072,8 +11485,10 @@
       <c r="AG196" s="29"/>
       <c r="AH196" s="1"/>
       <c r="AI196" s="1"/>
-    </row>
-    <row r="197" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ196" s="1"/>
+      <c r="AK196" s="1"/>
+    </row>
+    <row r="197" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A197" s="3">
         <v>194</v>
       </c>
@@ -11115,8 +11530,10 @@
       <c r="AG197" s="29"/>
       <c r="AH197" s="1"/>
       <c r="AI197" s="1"/>
-    </row>
-    <row r="198" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ197" s="1"/>
+      <c r="AK197" s="1"/>
+    </row>
+    <row r="198" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A198" s="3">
         <v>195</v>
       </c>
@@ -11160,8 +11577,10 @@
       <c r="AG198" s="29"/>
       <c r="AH198" s="1"/>
       <c r="AI198" s="1"/>
-    </row>
-    <row r="199" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ198" s="1"/>
+      <c r="AK198" s="1"/>
+    </row>
+    <row r="199" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A199" s="3">
         <v>196</v>
       </c>
@@ -11205,8 +11624,10 @@
       <c r="AG199" s="29"/>
       <c r="AH199" s="1"/>
       <c r="AI199" s="1"/>
-    </row>
-    <row r="200" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ199" s="1"/>
+      <c r="AK199" s="1"/>
+    </row>
+    <row r="200" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A200" s="3">
         <v>197</v>
       </c>
@@ -11248,8 +11669,10 @@
       <c r="AG200" s="29"/>
       <c r="AH200" s="1"/>
       <c r="AI200" s="1"/>
-    </row>
-    <row r="201" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ200" s="1"/>
+      <c r="AK200" s="1"/>
+    </row>
+    <row r="201" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A201" s="3">
         <v>198</v>
       </c>
@@ -11293,8 +11716,10 @@
       <c r="AG201" s="29"/>
       <c r="AH201" s="1"/>
       <c r="AI201" s="1"/>
-    </row>
-    <row r="202" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ201" s="1"/>
+      <c r="AK201" s="1"/>
+    </row>
+    <row r="202" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A202" s="3">
         <v>199</v>
       </c>
@@ -11336,8 +11761,10 @@
       <c r="AG202" s="29"/>
       <c r="AH202" s="1"/>
       <c r="AI202" s="1"/>
-    </row>
-    <row r="203" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ202" s="1"/>
+      <c r="AK202" s="1"/>
+    </row>
+    <row r="203" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A203" s="3">
         <v>200</v>
       </c>
@@ -11381,8 +11808,10 @@
       <c r="AG203" s="29"/>
       <c r="AH203" s="1"/>
       <c r="AI203" s="1"/>
-    </row>
-    <row r="204" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ203" s="1"/>
+      <c r="AK203" s="1"/>
+    </row>
+    <row r="204" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A204" s="3">
         <v>201</v>
       </c>
@@ -11424,8 +11853,10 @@
       <c r="AG204" s="29"/>
       <c r="AH204" s="1"/>
       <c r="AI204" s="1"/>
-    </row>
-    <row r="205" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ204" s="1"/>
+      <c r="AK204" s="1"/>
+    </row>
+    <row r="205" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A205" s="3">
         <v>202</v>
       </c>
@@ -11467,8 +11898,10 @@
       <c r="AG205" s="29"/>
       <c r="AH205" s="1"/>
       <c r="AI205" s="1"/>
-    </row>
-    <row r="206" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ205" s="1"/>
+      <c r="AK205" s="1"/>
+    </row>
+    <row r="206" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A206" s="3">
         <v>203</v>
       </c>
@@ -11510,8 +11943,10 @@
       <c r="AG206" s="29"/>
       <c r="AH206" s="1"/>
       <c r="AI206" s="1"/>
-    </row>
-    <row r="207" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ206" s="1"/>
+      <c r="AK206" s="1"/>
+    </row>
+    <row r="207" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A207" s="3">
         <v>204</v>
       </c>
@@ -11555,8 +11990,10 @@
       <c r="AG207" s="29"/>
       <c r="AH207" s="1"/>
       <c r="AI207" s="1"/>
-    </row>
-    <row r="208" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ207" s="1"/>
+      <c r="AK207" s="1"/>
+    </row>
+    <row r="208" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A208" s="3">
         <v>205</v>
       </c>
@@ -11598,8 +12035,10 @@
       <c r="AG208" s="29"/>
       <c r="AH208" s="1"/>
       <c r="AI208" s="1"/>
-    </row>
-    <row r="209" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ208" s="1"/>
+      <c r="AK208" s="1"/>
+    </row>
+    <row r="209" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A209" s="3">
         <v>206</v>
       </c>
@@ -11641,8 +12080,10 @@
       <c r="AG209" s="29"/>
       <c r="AH209" s="1"/>
       <c r="AI209" s="1"/>
-    </row>
-    <row r="210" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ209" s="1"/>
+      <c r="AK209" s="1"/>
+    </row>
+    <row r="210" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A210" s="3">
         <v>207</v>
       </c>
@@ -11684,8 +12125,10 @@
       <c r="AG210" s="29"/>
       <c r="AH210" s="1"/>
       <c r="AI210" s="1"/>
-    </row>
-    <row r="211" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ210" s="1"/>
+      <c r="AK210" s="1"/>
+    </row>
+    <row r="211" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A211" s="3">
         <v>208</v>
       </c>
@@ -11727,8 +12170,10 @@
       <c r="AG211" s="29"/>
       <c r="AH211" s="1"/>
       <c r="AI211" s="1"/>
-    </row>
-    <row r="212" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ211" s="1"/>
+      <c r="AK211" s="1"/>
+    </row>
+    <row r="212" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A212" s="3">
         <v>209</v>
       </c>
@@ -11770,8 +12215,10 @@
       <c r="AG212" s="29"/>
       <c r="AH212" s="1"/>
       <c r="AI212" s="1"/>
-    </row>
-    <row r="213" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ212" s="1"/>
+      <c r="AK212" s="1"/>
+    </row>
+    <row r="213" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A213" s="3">
         <v>210</v>
       </c>
@@ -11813,8 +12260,10 @@
       <c r="AG213" s="29"/>
       <c r="AH213" s="1"/>
       <c r="AI213" s="1"/>
-    </row>
-    <row r="214" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ213" s="1"/>
+      <c r="AK213" s="1"/>
+    </row>
+    <row r="214" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A214" s="3">
         <v>211</v>
       </c>
@@ -11856,8 +12305,10 @@
       <c r="AG214" s="29"/>
       <c r="AH214" s="1"/>
       <c r="AI214" s="1"/>
-    </row>
-    <row r="215" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ214" s="1"/>
+      <c r="AK214" s="1"/>
+    </row>
+    <row r="215" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A215" s="3">
         <v>212</v>
       </c>
@@ -11899,8 +12350,10 @@
       <c r="AG215" s="29"/>
       <c r="AH215" s="1"/>
       <c r="AI215" s="1"/>
-    </row>
-    <row r="216" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ215" s="1"/>
+      <c r="AK215" s="1"/>
+    </row>
+    <row r="216" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A216" s="3">
         <v>213</v>
       </c>
@@ -11946,8 +12399,10 @@
       <c r="AG216" s="29"/>
       <c r="AH216" s="1"/>
       <c r="AI216" s="1"/>
-    </row>
-    <row r="217" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ216" s="1"/>
+      <c r="AK216" s="1"/>
+    </row>
+    <row r="217" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A217" s="3">
         <v>214</v>
       </c>
@@ -11993,8 +12448,10 @@
       <c r="AG217" s="29"/>
       <c r="AH217" s="1"/>
       <c r="AI217" s="1"/>
-    </row>
-    <row r="218" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ217" s="1"/>
+      <c r="AK217" s="1"/>
+    </row>
+    <row r="218" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A218" s="3">
         <v>215</v>
       </c>
@@ -12040,8 +12497,10 @@
       <c r="AG218" s="29"/>
       <c r="AH218" s="1"/>
       <c r="AI218" s="1"/>
-    </row>
-    <row r="219" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ218" s="1"/>
+      <c r="AK218" s="1"/>
+    </row>
+    <row r="219" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A219" s="3">
         <v>216</v>
       </c>
@@ -12081,8 +12540,10 @@
       <c r="AG219" s="29"/>
       <c r="AH219" s="1"/>
       <c r="AI219" s="1"/>
-    </row>
-    <row r="220" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ219" s="1"/>
+      <c r="AK219" s="1"/>
+    </row>
+    <row r="220" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A220" s="3">
         <v>217</v>
       </c>
@@ -12122,8 +12583,10 @@
       <c r="AG220" s="29"/>
       <c r="AH220" s="1"/>
       <c r="AI220" s="1"/>
-    </row>
-    <row r="221" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ220" s="1"/>
+      <c r="AK220" s="1"/>
+    </row>
+    <row r="221" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A221" s="3">
         <v>218</v>
       </c>
@@ -12163,8 +12626,10 @@
       <c r="AG221" s="29"/>
       <c r="AH221" s="1"/>
       <c r="AI221" s="1"/>
-    </row>
-    <row r="222" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ221" s="1"/>
+      <c r="AK221" s="1"/>
+    </row>
+    <row r="222" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A222" s="3">
         <v>219</v>
       </c>
@@ -12206,8 +12671,10 @@
       <c r="AG222" s="29"/>
       <c r="AH222" s="1"/>
       <c r="AI222" s="1"/>
-    </row>
-    <row r="223" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ222" s="1"/>
+      <c r="AK222" s="1"/>
+    </row>
+    <row r="223" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A223" s="3">
         <v>220</v>
       </c>
@@ -12247,8 +12714,10 @@
       <c r="AG223" s="29"/>
       <c r="AH223" s="1"/>
       <c r="AI223" s="1"/>
-    </row>
-    <row r="224" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ223" s="1"/>
+      <c r="AK223" s="1"/>
+    </row>
+    <row r="224" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A224" s="3">
         <v>221</v>
       </c>
@@ -12288,8 +12757,10 @@
       <c r="AG224" s="29"/>
       <c r="AH224" s="1"/>
       <c r="AI224" s="1"/>
-    </row>
-    <row r="225" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ224" s="1"/>
+      <c r="AK224" s="1"/>
+    </row>
+    <row r="225" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A225" s="3">
         <v>222</v>
       </c>
@@ -12329,8 +12800,10 @@
       <c r="AG225" s="29"/>
       <c r="AH225" s="1"/>
       <c r="AI225" s="1"/>
-    </row>
-    <row r="226" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ225" s="1"/>
+      <c r="AK225" s="1"/>
+    </row>
+    <row r="226" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A226" s="3">
         <v>223</v>
       </c>
@@ -12370,8 +12843,10 @@
       <c r="AG226" s="29"/>
       <c r="AH226" s="1"/>
       <c r="AI226" s="1"/>
-    </row>
-    <row r="227" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ226" s="1"/>
+      <c r="AK226" s="1"/>
+    </row>
+    <row r="227" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A227" s="3">
         <v>224</v>
       </c>
@@ -12411,8 +12886,10 @@
       <c r="AG227" s="29"/>
       <c r="AH227" s="1"/>
       <c r="AI227" s="1"/>
-    </row>
-    <row r="228" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ227" s="1"/>
+      <c r="AK227" s="1"/>
+    </row>
+    <row r="228" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A228" s="3">
         <v>225</v>
       </c>
@@ -12452,8 +12929,10 @@
       <c r="AG228" s="29"/>
       <c r="AH228" s="1"/>
       <c r="AI228" s="1"/>
-    </row>
-    <row r="229" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ228" s="1"/>
+      <c r="AK228" s="1"/>
+    </row>
+    <row r="229" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A229" s="3">
         <v>226</v>
       </c>
@@ -12493,8 +12972,10 @@
       <c r="AG229" s="29"/>
       <c r="AH229" s="1"/>
       <c r="AI229" s="1"/>
-    </row>
-    <row r="230" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="AJ229" s="1"/>
+      <c r="AK229" s="1"/>
+    </row>
+    <row r="230" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A230" s="3">
         <v>227</v>
       </c>
@@ -12534,8 +13015,10 @@
       <c r="AG230" s="29"/>
       <c r="AH230" s="1"/>
       <c r="AI230" s="1"/>
-    </row>
-    <row r="231" spans="1:35">
+      <c r="AJ230" s="1"/>
+      <c r="AK230" s="1"/>
+    </row>
+    <row r="231" spans="1:37">
       <c r="A231" s="3">
         <v>228</v>
       </c>
@@ -12575,8 +13058,10 @@
       <c r="AG231" s="29"/>
       <c r="AH231" s="1"/>
       <c r="AI231" s="1"/>
-    </row>
-    <row r="232" spans="1:35">
+      <c r="AJ231" s="1"/>
+      <c r="AK231" s="1"/>
+    </row>
+    <row r="232" spans="1:37">
       <c r="A232" s="3">
         <v>229</v>
       </c>
@@ -12616,8 +13101,10 @@
       <c r="AG232" s="29"/>
       <c r="AH232" s="1"/>
       <c r="AI232" s="1"/>
-    </row>
-    <row r="233" spans="1:35">
+      <c r="AJ232" s="1"/>
+      <c r="AK232" s="1"/>
+    </row>
+    <row r="233" spans="1:37">
       <c r="A233" s="3">
         <v>230</v>
       </c>
@@ -12659,8 +13146,10 @@
       <c r="AG233" s="29"/>
       <c r="AH233" s="1"/>
       <c r="AI233" s="1"/>
-    </row>
-    <row r="234" spans="1:35">
+      <c r="AJ233" s="1"/>
+      <c r="AK233" s="1"/>
+    </row>
+    <row r="234" spans="1:37">
       <c r="A234" s="3">
         <v>231</v>
       </c>
@@ -12700,8 +13189,10 @@
       <c r="AG234" s="29"/>
       <c r="AH234" s="1"/>
       <c r="AI234" s="1"/>
-    </row>
-    <row r="235" spans="1:35">
+      <c r="AJ234" s="1"/>
+      <c r="AK234" s="1"/>
+    </row>
+    <row r="235" spans="1:37">
       <c r="A235" s="3">
         <v>232</v>
       </c>
@@ -12743,8 +13234,10 @@
       <c r="AG235" s="29"/>
       <c r="AH235" s="1"/>
       <c r="AI235" s="1"/>
-    </row>
-    <row r="236" spans="1:35">
+      <c r="AJ235" s="1"/>
+      <c r="AK235" s="1"/>
+    </row>
+    <row r="236" spans="1:37">
       <c r="A236" s="3">
         <v>233</v>
       </c>
@@ -12784,8 +13277,10 @@
       <c r="AG236" s="29"/>
       <c r="AH236" s="1"/>
       <c r="AI236" s="1"/>
-    </row>
-    <row r="237" spans="1:35">
+      <c r="AJ236" s="1"/>
+      <c r="AK236" s="1"/>
+    </row>
+    <row r="237" spans="1:37">
       <c r="A237" s="3">
         <v>234</v>
       </c>
@@ -12825,8 +13320,10 @@
       <c r="AG237" s="29"/>
       <c r="AH237" s="1"/>
       <c r="AI237" s="1"/>
-    </row>
-    <row r="238" spans="1:35">
+      <c r="AJ237" s="1"/>
+      <c r="AK237" s="1"/>
+    </row>
+    <row r="238" spans="1:37">
       <c r="A238" s="3">
         <v>235</v>
       </c>
@@ -12866,8 +13363,10 @@
       <c r="AG238" s="29"/>
       <c r="AH238" s="1"/>
       <c r="AI238" s="1"/>
-    </row>
-    <row r="239" spans="1:35">
+      <c r="AJ238" s="1"/>
+      <c r="AK238" s="1"/>
+    </row>
+    <row r="239" spans="1:37">
       <c r="A239" s="3">
         <v>236</v>
       </c>
@@ -12907,8 +13406,10 @@
       <c r="AG239" s="29"/>
       <c r="AH239" s="1"/>
       <c r="AI239" s="1"/>
-    </row>
-    <row r="240" spans="1:35">
+      <c r="AJ239" s="1"/>
+      <c r="AK239" s="1"/>
+    </row>
+    <row r="240" spans="1:37">
       <c r="A240" s="3">
         <v>237</v>
       </c>
@@ -12948,8 +13449,10 @@
       <c r="AG240" s="29"/>
       <c r="AH240" s="1"/>
       <c r="AI240" s="1"/>
-    </row>
-    <row r="241" spans="1:35">
+      <c r="AJ240" s="1"/>
+      <c r="AK240" s="1"/>
+    </row>
+    <row r="241" spans="1:37">
       <c r="A241" s="3">
         <v>238</v>
       </c>
@@ -12989,8 +13492,10 @@
       <c r="AG241" s="29"/>
       <c r="AH241" s="1"/>
       <c r="AI241" s="1"/>
-    </row>
-    <row r="242" spans="1:35">
+      <c r="AJ241" s="1"/>
+      <c r="AK241" s="1"/>
+    </row>
+    <row r="242" spans="1:37">
       <c r="A242" s="3">
         <v>239</v>
       </c>
@@ -13030,8 +13535,10 @@
       <c r="AG242" s="29"/>
       <c r="AH242" s="1"/>
       <c r="AI242" s="1"/>
-    </row>
-    <row r="243" spans="1:35">
+      <c r="AJ242" s="1"/>
+      <c r="AK242" s="1"/>
+    </row>
+    <row r="243" spans="1:37">
       <c r="A243" s="3">
         <v>240</v>
       </c>
@@ -13073,8 +13580,10 @@
       <c r="AG243" s="29"/>
       <c r="AH243" s="1"/>
       <c r="AI243" s="1"/>
-    </row>
-    <row r="244" spans="1:35">
+      <c r="AJ243" s="1"/>
+      <c r="AK243" s="1"/>
+    </row>
+    <row r="244" spans="1:37">
       <c r="A244" s="3">
         <v>241</v>
       </c>
@@ -13116,8 +13625,10 @@
       <c r="AG244" s="29"/>
       <c r="AH244" s="1"/>
       <c r="AI244" s="1"/>
-    </row>
-    <row r="245" spans="1:35">
+      <c r="AJ244" s="1"/>
+      <c r="AK244" s="1"/>
+    </row>
+    <row r="245" spans="1:37">
       <c r="A245" s="3">
         <v>242</v>
       </c>
@@ -13159,8 +13670,10 @@
       <c r="AG245" s="29"/>
       <c r="AH245" s="1"/>
       <c r="AI245" s="1"/>
-    </row>
-    <row r="246" spans="1:35">
+      <c r="AJ245" s="1"/>
+      <c r="AK245" s="1"/>
+    </row>
+    <row r="246" spans="1:37">
       <c r="A246" s="3">
         <v>243</v>
       </c>
@@ -13202,8 +13715,10 @@
       <c r="AG246" s="29"/>
       <c r="AH246" s="1"/>
       <c r="AI246" s="1"/>
-    </row>
-    <row r="247" spans="1:35">
+      <c r="AJ246" s="1"/>
+      <c r="AK246" s="1"/>
+    </row>
+    <row r="247" spans="1:37">
       <c r="A247" s="3">
         <v>244</v>
       </c>
@@ -13245,8 +13760,10 @@
       <c r="AG247" s="29"/>
       <c r="AH247" s="1"/>
       <c r="AI247" s="1"/>
-    </row>
-    <row r="248" spans="1:35">
+      <c r="AJ247" s="1"/>
+      <c r="AK247" s="1"/>
+    </row>
+    <row r="248" spans="1:37">
       <c r="A248" s="3">
         <v>245</v>
       </c>
@@ -13288,8 +13805,10 @@
       <c r="AG248" s="29"/>
       <c r="AH248" s="1"/>
       <c r="AI248" s="1"/>
-    </row>
-    <row r="249" spans="1:35">
+      <c r="AJ248" s="1"/>
+      <c r="AK248" s="1"/>
+    </row>
+    <row r="249" spans="1:37">
       <c r="A249" s="3">
         <v>246</v>
       </c>
@@ -13329,8 +13848,10 @@
       <c r="AG249" s="29"/>
       <c r="AH249" s="1"/>
       <c r="AI249" s="1"/>
-    </row>
-    <row r="250" spans="1:35">
+      <c r="AJ249" s="1"/>
+      <c r="AK249" s="1"/>
+    </row>
+    <row r="250" spans="1:37">
       <c r="A250" s="3">
         <v>247</v>
       </c>
@@ -13370,8 +13891,10 @@
       <c r="AG250" s="29"/>
       <c r="AH250" s="1"/>
       <c r="AI250" s="1"/>
-    </row>
-    <row r="251" spans="1:35">
+      <c r="AJ250" s="1"/>
+      <c r="AK250" s="1"/>
+    </row>
+    <row r="251" spans="1:37">
       <c r="A251" s="3">
         <v>248</v>
       </c>
@@ -13411,8 +13934,10 @@
       <c r="AG251" s="29"/>
       <c r="AH251" s="1"/>
       <c r="AI251" s="1"/>
-    </row>
-    <row r="252" spans="1:35">
+      <c r="AJ251" s="1"/>
+      <c r="AK251" s="1"/>
+    </row>
+    <row r="252" spans="1:37">
       <c r="A252" s="3">
         <v>249</v>
       </c>
@@ -13452,8 +13977,10 @@
       <c r="AG252" s="29"/>
       <c r="AH252" s="1"/>
       <c r="AI252" s="1"/>
-    </row>
-    <row r="253" spans="1:35">
+      <c r="AJ252" s="1"/>
+      <c r="AK252" s="1"/>
+    </row>
+    <row r="253" spans="1:37">
       <c r="A253" s="3">
         <v>250</v>
       </c>
@@ -13493,8 +14020,10 @@
       <c r="AG253" s="29"/>
       <c r="AH253" s="1"/>
       <c r="AI253" s="1"/>
-    </row>
-    <row r="254" spans="1:35">
+      <c r="AJ253" s="1"/>
+      <c r="AK253" s="1"/>
+    </row>
+    <row r="254" spans="1:37">
       <c r="A254" s="3">
         <v>251</v>
       </c>
@@ -13534,8 +14063,10 @@
       <c r="AG254" s="29"/>
       <c r="AH254" s="1"/>
       <c r="AI254" s="1"/>
-    </row>
-    <row r="255" spans="1:35">
+      <c r="AJ254" s="1"/>
+      <c r="AK254" s="1"/>
+    </row>
+    <row r="255" spans="1:37">
       <c r="A255" s="3">
         <v>252</v>
       </c>
@@ -13575,8 +14106,10 @@
       <c r="AG255" s="29"/>
       <c r="AH255" s="1"/>
       <c r="AI255" s="1"/>
-    </row>
-    <row r="256" spans="1:35">
+      <c r="AJ255" s="1"/>
+      <c r="AK255" s="1"/>
+    </row>
+    <row r="256" spans="1:37">
       <c r="A256" s="3">
         <v>253</v>
       </c>
@@ -13614,8 +14147,10 @@
       <c r="AG256" s="29"/>
       <c r="AH256" s="1"/>
       <c r="AI256" s="1"/>
-    </row>
-    <row r="257" spans="1:35">
+      <c r="AJ256" s="1"/>
+      <c r="AK256" s="1"/>
+    </row>
+    <row r="257" spans="1:37">
       <c r="A257" s="3">
         <v>254</v>
       </c>
@@ -13653,8 +14188,10 @@
       <c r="AG257" s="29"/>
       <c r="AH257" s="1"/>
       <c r="AI257" s="1"/>
-    </row>
-    <row r="258" spans="1:35">
+      <c r="AJ257" s="1"/>
+      <c r="AK257" s="1"/>
+    </row>
+    <row r="258" spans="1:37">
       <c r="A258" s="3">
         <v>255</v>
       </c>
@@ -13692,8 +14229,10 @@
       <c r="AG258" s="29"/>
       <c r="AH258" s="1"/>
       <c r="AI258" s="1"/>
-    </row>
-    <row r="259" spans="1:35">
+      <c r="AJ258" s="1"/>
+      <c r="AK258" s="1"/>
+    </row>
+    <row r="259" spans="1:37">
       <c r="A259" s="3">
         <v>256</v>
       </c>
@@ -13731,8 +14270,10 @@
       <c r="AG259" s="29"/>
       <c r="AH259" s="1"/>
       <c r="AI259" s="1"/>
-    </row>
-    <row r="260" spans="1:35">
+      <c r="AJ259" s="1"/>
+      <c r="AK259" s="1"/>
+    </row>
+    <row r="260" spans="1:37">
       <c r="A260" s="3">
         <v>257</v>
       </c>
@@ -13770,8 +14311,10 @@
       <c r="AG260" s="29"/>
       <c r="AH260" s="1"/>
       <c r="AI260" s="1"/>
-    </row>
-    <row r="261" spans="1:35">
+      <c r="AJ260" s="1"/>
+      <c r="AK260" s="1"/>
+    </row>
+    <row r="261" spans="1:37">
       <c r="A261" s="3">
         <v>258</v>
       </c>
@@ -13809,8 +14352,10 @@
       <c r="AG261" s="29"/>
       <c r="AH261" s="1"/>
       <c r="AI261" s="1"/>
-    </row>
-    <row r="262" spans="1:35">
+      <c r="AJ261" s="1"/>
+      <c r="AK261" s="1"/>
+    </row>
+    <row r="262" spans="1:37">
       <c r="A262" s="3">
         <v>259</v>
       </c>
@@ -13848,8 +14393,10 @@
       <c r="AG262" s="29"/>
       <c r="AH262" s="1"/>
       <c r="AI262" s="1"/>
-    </row>
-    <row r="263" spans="1:35">
+      <c r="AJ262" s="1"/>
+      <c r="AK262" s="1"/>
+    </row>
+    <row r="263" spans="1:37">
       <c r="A263" s="3">
         <v>260</v>
       </c>
@@ -13887,8 +14434,10 @@
       <c r="AG263" s="29"/>
       <c r="AH263" s="1"/>
       <c r="AI263" s="1"/>
-    </row>
-    <row r="264" spans="1:35">
+      <c r="AJ263" s="1"/>
+      <c r="AK263" s="1"/>
+    </row>
+    <row r="264" spans="1:37">
       <c r="A264" s="3">
         <v>261</v>
       </c>
@@ -13926,8 +14475,10 @@
       <c r="AG264" s="29"/>
       <c r="AH264" s="1"/>
       <c r="AI264" s="1"/>
-    </row>
-    <row r="265" spans="1:35">
+      <c r="AJ264" s="1"/>
+      <c r="AK264" s="1"/>
+    </row>
+    <row r="265" spans="1:37">
       <c r="A265" s="3">
         <v>262</v>
       </c>
@@ -13965,8 +14516,10 @@
       <c r="AG265" s="29"/>
       <c r="AH265" s="1"/>
       <c r="AI265" s="1"/>
-    </row>
-    <row r="266" spans="1:35">
+      <c r="AJ265" s="1"/>
+      <c r="AK265" s="1"/>
+    </row>
+    <row r="266" spans="1:37">
       <c r="A266" s="3">
         <v>263</v>
       </c>
@@ -14004,8 +14557,10 @@
       <c r="AG266" s="29"/>
       <c r="AH266" s="1"/>
       <c r="AI266" s="1"/>
-    </row>
-    <row r="267" spans="1:35">
+      <c r="AJ266" s="1"/>
+      <c r="AK266" s="1"/>
+    </row>
+    <row r="267" spans="1:37">
       <c r="A267" s="3">
         <v>264</v>
       </c>
@@ -14043,8 +14598,10 @@
       <c r="AG267" s="29"/>
       <c r="AH267" s="1"/>
       <c r="AI267" s="1"/>
-    </row>
-    <row r="268" spans="1:35">
+      <c r="AJ267" s="1"/>
+      <c r="AK267" s="1"/>
+    </row>
+    <row r="268" spans="1:37">
       <c r="A268" s="3">
         <v>265</v>
       </c>
@@ -14082,8 +14639,10 @@
       <c r="AG268" s="29"/>
       <c r="AH268" s="1"/>
       <c r="AI268" s="1"/>
-    </row>
-    <row r="269" spans="1:35">
+      <c r="AJ268" s="1"/>
+      <c r="AK268" s="1"/>
+    </row>
+    <row r="269" spans="1:37">
       <c r="A269" s="3">
         <v>266</v>
       </c>
@@ -14121,8 +14680,10 @@
       <c r="AG269" s="29"/>
       <c r="AH269" s="1"/>
       <c r="AI269" s="1"/>
-    </row>
-    <row r="270" spans="1:35">
+      <c r="AJ269" s="1"/>
+      <c r="AK269" s="1"/>
+    </row>
+    <row r="270" spans="1:37">
       <c r="A270" s="3">
         <v>267</v>
       </c>
@@ -14160,8 +14721,10 @@
       <c r="AG270" s="29"/>
       <c r="AH270" s="1"/>
       <c r="AI270" s="1"/>
-    </row>
-    <row r="271" spans="1:35">
+      <c r="AJ270" s="1"/>
+      <c r="AK270" s="1"/>
+    </row>
+    <row r="271" spans="1:37">
       <c r="A271" s="3">
         <v>268</v>
       </c>
@@ -14199,8 +14762,10 @@
       <c r="AG271" s="29"/>
       <c r="AH271" s="1"/>
       <c r="AI271" s="1"/>
-    </row>
-    <row r="272" spans="1:35">
+      <c r="AJ271" s="1"/>
+      <c r="AK271" s="1"/>
+    </row>
+    <row r="272" spans="1:37">
       <c r="A272" s="3">
         <v>269</v>
       </c>
@@ -14238,8 +14803,10 @@
       <c r="AG272" s="29"/>
       <c r="AH272" s="1"/>
       <c r="AI272" s="1"/>
-    </row>
-    <row r="273" spans="1:35">
+      <c r="AJ272" s="1"/>
+      <c r="AK272" s="1"/>
+    </row>
+    <row r="273" spans="1:37">
       <c r="A273" s="3">
         <v>270</v>
       </c>
@@ -14277,8 +14844,10 @@
       <c r="AG273" s="29"/>
       <c r="AH273" s="1"/>
       <c r="AI273" s="1"/>
-    </row>
-    <row r="274" spans="1:35">
+      <c r="AJ273" s="1"/>
+      <c r="AK273" s="1"/>
+    </row>
+    <row r="274" spans="1:37">
       <c r="A274" s="3">
         <v>271</v>
       </c>
@@ -14316,8 +14885,10 @@
       <c r="AG274" s="29"/>
       <c r="AH274" s="1"/>
       <c r="AI274" s="1"/>
-    </row>
-    <row r="275" spans="1:35">
+      <c r="AJ274" s="1"/>
+      <c r="AK274" s="1"/>
+    </row>
+    <row r="275" spans="1:37">
       <c r="A275" s="3">
         <v>272</v>
       </c>
@@ -14355,8 +14926,10 @@
       <c r="AG275" s="29"/>
       <c r="AH275" s="1"/>
       <c r="AI275" s="1"/>
-    </row>
-    <row r="276" spans="1:35">
+      <c r="AJ275" s="1"/>
+      <c r="AK275" s="1"/>
+    </row>
+    <row r="276" spans="1:37">
       <c r="A276" s="3">
         <v>273</v>
       </c>
@@ -14394,8 +14967,10 @@
       <c r="AG276" s="29"/>
       <c r="AH276" s="1"/>
       <c r="AI276" s="1"/>
-    </row>
-    <row r="277" spans="1:35">
+      <c r="AJ276" s="1"/>
+      <c r="AK276" s="1"/>
+    </row>
+    <row r="277" spans="1:37">
       <c r="A277" s="3">
         <v>274</v>
       </c>
@@ -14433,8 +15008,10 @@
       <c r="AG277" s="29"/>
       <c r="AH277" s="1"/>
       <c r="AI277" s="1"/>
-    </row>
-    <row r="278" spans="1:35">
+      <c r="AJ277" s="1"/>
+      <c r="AK277" s="1"/>
+    </row>
+    <row r="278" spans="1:37">
       <c r="A278" s="3">
         <v>275</v>
       </c>
@@ -14472,8 +15049,10 @@
       <c r="AG278" s="29"/>
       <c r="AH278" s="1"/>
       <c r="AI278" s="1"/>
-    </row>
-    <row r="279" spans="1:35">
+      <c r="AJ278" s="1"/>
+      <c r="AK278" s="1"/>
+    </row>
+    <row r="279" spans="1:37">
       <c r="A279" s="3">
         <v>276</v>
       </c>
@@ -14511,8 +15090,10 @@
       <c r="AG279" s="29"/>
       <c r="AH279" s="1"/>
       <c r="AI279" s="1"/>
-    </row>
-    <row r="280" spans="1:35">
+      <c r="AJ279" s="1"/>
+      <c r="AK279" s="1"/>
+    </row>
+    <row r="280" spans="1:37">
       <c r="A280" s="3">
         <v>277</v>
       </c>
@@ -14550,6 +15131,8 @@
       <c r="AG280" s="29"/>
       <c r="AH280" s="1"/>
       <c r="AI280" s="1"/>
+      <c r="AJ280" s="1"/>
+      <c r="AK280" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AB280" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -14561,7 +15144,7 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E181:E280 E4:E163 F4:AI280 D4:D280 B4:B242" xr:uid="{C452CDD0-B3A9-419A-AD4E-0E5CE327C346}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E181:E280 E4:E163 F4:AK280 D4:D280 B4:B242" xr:uid="{C452CDD0-B3A9-419A-AD4E-0E5CE327C346}">
       <formula1>"〇,×,△"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E164:E180" xr:uid="{E47C5A29-770A-4FF4-AE4B-E53AB5761727}">
@@ -15081,7 +15664,9 @@
       <c r="H34" s="18"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="19"/>
+      <c r="A35" s="19" t="s">
+        <v>398</v>
+      </c>
       <c r="B35" s="18"/>
       <c r="C35" s="18"/>
       <c r="D35" s="18"/>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530DA990-C862-4EB3-8402-693E2ED13379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8D16C5-52BD-40D6-8092-8D0A605D1B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="402">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -1921,12 +1921,19 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>合格</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウカク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2006,6 +2013,15 @@
       <sz val="6"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -2155,7 +2171,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2267,6 +2283,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -14114,7 +14131,9 @@
         <v>253</v>
       </c>
       <c r="B256" s="3"/>
-      <c r="C256" s="21"/>
+      <c r="C256" s="41" t="s">
+        <v>401</v>
+      </c>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8D16C5-52BD-40D6-8092-8D0A605D1B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C3C160-2AB5-478B-B89F-23B821B01B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4430" yWindow="650" windowWidth="14770" windowHeight="9430" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="リスト" sheetId="1" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="403">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -1925,6 +1925,13 @@
     <t>合格</t>
     <rPh sb="0" eb="2">
       <t>ゴウカク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>犬1</t>
+    <rPh sb="0" eb="1">
+      <t>イヌ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2253,6 +2260,7 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2283,7 +2291,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2664,52 +2671,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK280"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="3.4375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.4375" style="24" customWidth="1"/>
+    <col min="1" max="1" width="3.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.4140625" style="24" customWidth="1"/>
     <col min="3" max="3" width="33.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="3.5625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="2.5625" bestFit="1" customWidth="1"/>
-    <col min="11" max="37" width="3.5625" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="3.58203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2.58203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="37" width="3.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="22.9">
-      <c r="A1" s="34"/>
-      <c r="B1" s="38" t="s">
+    <row r="1" spans="1:37" ht="22.5">
+      <c r="A1" s="35"/>
+      <c r="B1" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-    </row>
-    <row r="2" spans="1:37" ht="22.9">
-      <c r="A2" s="35"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="32"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+    </row>
+    <row r="2" spans="1:37" ht="22.5">
+      <c r="A2" s="36"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="33"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="e" vm="1">
         <v>#VALUE!</v>
@@ -2755,10 +2762,10 @@
       <c r="AJ2" s="5"/>
       <c r="AK2" s="5"/>
     </row>
-    <row r="3" spans="1:37" s="13" customFormat="1" ht="106.9" thickBot="1">
-      <c r="A3" s="36"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="33"/>
+    <row r="3" spans="1:37" s="13" customFormat="1" ht="109.5" thickBot="1">
+      <c r="A3" s="37"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="34"/>
       <c r="D3" s="11" t="s">
         <v>122</v>
       </c>
@@ -14131,7 +14138,7 @@
         <v>253</v>
       </c>
       <c r="B256" s="3"/>
-      <c r="C256" s="41" t="s">
+      <c r="C256" s="31" t="s">
         <v>401</v>
       </c>
       <c r="D256" s="1"/>
@@ -15177,14 +15184,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8513D353-BD33-4F18-8682-09CF4EA59EE5}">
   <dimension ref="A2:H171"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="12.0625" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08203125" style="16" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.8125" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.0625" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.9375" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="6.5625" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.08203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.9140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="6.58203125" style="16" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="16"/>
   </cols>
   <sheetData>
@@ -15392,7 +15399,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="19" t="s">
-        <v>134</v>
+        <v>402</v>
       </c>
       <c r="B16" s="18" t="s">
         <v>157</v>
@@ -15400,10 +15407,16 @@
       <c r="C16" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
+      <c r="D16" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E16" s="25"/>
+      <c r="F16" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>157</v>
+      </c>
       <c r="H16" s="18"/>
     </row>
     <row r="17" spans="1:8">
@@ -15674,7 +15687,9 @@
       <c r="A34" s="19" t="s">
         <v>397</v>
       </c>
-      <c r="B34" s="18"/>
+      <c r="B34" s="18" t="s">
+        <v>157</v>
+      </c>
       <c r="C34" s="18"/>
       <c r="D34" s="18"/>
       <c r="E34" s="18"/>
@@ -15686,7 +15701,9 @@
       <c r="A35" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="B35" s="18"/>
+      <c r="B35" s="18" t="s">
+        <v>157</v>
+      </c>
       <c r="C35" s="18"/>
       <c r="D35" s="18"/>
       <c r="E35" s="18"/>
@@ -17070,12 +17087,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B979FDD-83A3-41C6-8CB0-C39167BCC619}">
   <dimension ref="A1:E221"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="3.8125" customWidth="1"/>
-    <col min="2" max="2" width="4.5625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5625" customWidth="1"/>
-    <col min="4" max="4" width="29.1875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.83203125" customWidth="1"/>
+    <col min="2" max="2" width="4.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.58203125" customWidth="1"/>
+    <col min="4" max="4" width="29.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C3C160-2AB5-478B-B89F-23B821B01B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADDBCF8-DCDB-46C8-A0B0-FDCBC3551F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4430" yWindow="650" windowWidth="14770" windowHeight="9430" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4430" yWindow="650" windowWidth="14770" windowHeight="9430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="リスト" sheetId="1" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="403">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -2670,6 +2670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AK280"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
@@ -2865,7 +2866,7 @@
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
     </row>
-    <row r="4" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickTop="1">
+    <row r="4" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" thickTop="1">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -2920,7 +2921,7 @@
       <c r="AJ4" s="1"/>
       <c r="AK4" s="1"/>
     </row>
-    <row r="5" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="5" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -2949,9 +2950,7 @@
       <c r="P5" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="Q5" s="1" t="s">
-        <v>157</v>
-      </c>
+      <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1" t="s">
         <v>157</v>
@@ -2977,7 +2976,7 @@
       <c r="AJ5" s="1"/>
       <c r="AK5" s="1"/>
     </row>
-    <row r="6" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="6" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -3024,7 +3023,7 @@
       <c r="AJ6" s="1"/>
       <c r="AK6" s="1"/>
     </row>
-    <row r="7" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="7" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -3067,7 +3066,7 @@
       <c r="AJ7" s="1"/>
       <c r="AK7" s="1"/>
     </row>
-    <row r="8" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="8" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -3112,7 +3111,7 @@
       <c r="AJ8" s="1"/>
       <c r="AK8" s="1"/>
     </row>
-    <row r="9" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="9" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -3155,7 +3154,7 @@
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
     </row>
-    <row r="10" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="10" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -3198,7 +3197,7 @@
       <c r="AJ10" s="1"/>
       <c r="AK10" s="1"/>
     </row>
-    <row r="11" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="11" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -3245,7 +3244,7 @@
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
     </row>
-    <row r="12" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="12" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -3288,7 +3287,7 @@
       <c r="AJ12" s="1"/>
       <c r="AK12" s="1"/>
     </row>
-    <row r="13" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="13" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -3331,7 +3330,7 @@
       <c r="AJ13" s="1"/>
       <c r="AK13" s="1"/>
     </row>
-    <row r="14" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="14" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -3374,7 +3373,7 @@
       <c r="AJ14" s="1"/>
       <c r="AK14" s="1"/>
     </row>
-    <row r="15" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="15" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -3417,7 +3416,7 @@
       <c r="AJ15" s="1"/>
       <c r="AK15" s="1"/>
     </row>
-    <row r="16" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="16" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -3460,7 +3459,7 @@
       <c r="AJ16" s="1"/>
       <c r="AK16" s="1"/>
     </row>
-    <row r="17" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="17" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -3503,7 +3502,7 @@
       <c r="AJ17" s="1"/>
       <c r="AK17" s="1"/>
     </row>
-    <row r="18" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="18" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -3548,7 +3547,7 @@
       <c r="AJ18" s="1"/>
       <c r="AK18" s="1"/>
     </row>
-    <row r="19" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="19" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -3591,7 +3590,7 @@
       <c r="AJ19" s="1"/>
       <c r="AK19" s="1"/>
     </row>
-    <row r="20" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="20" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -3634,7 +3633,7 @@
       <c r="AJ20" s="1"/>
       <c r="AK20" s="1"/>
     </row>
-    <row r="21" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="21" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -3677,7 +3676,7 @@
       <c r="AJ21" s="1"/>
       <c r="AK21" s="1"/>
     </row>
-    <row r="22" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="22" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -3722,7 +3721,7 @@
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1"/>
     </row>
-    <row r="23" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="23" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -3765,7 +3764,7 @@
       <c r="AJ23" s="1"/>
       <c r="AK23" s="1"/>
     </row>
-    <row r="24" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="24" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -3810,7 +3809,7 @@
       <c r="AJ24" s="1"/>
       <c r="AK24" s="1"/>
     </row>
-    <row r="25" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="25" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -3855,7 +3854,7 @@
       <c r="AJ25" s="1"/>
       <c r="AK25" s="1"/>
     </row>
-    <row r="26" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="26" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -3943,7 +3942,7 @@
       <c r="AJ27" s="1"/>
       <c r="AK27" s="1"/>
     </row>
-    <row r="28" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="28" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -3986,7 +3985,7 @@
       <c r="AJ28" s="1"/>
       <c r="AK28" s="1"/>
     </row>
-    <row r="29" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="29" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -4029,7 +4028,7 @@
       <c r="AJ29" s="1"/>
       <c r="AK29" s="1"/>
     </row>
-    <row r="30" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="30" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -4123,7 +4122,7 @@
       <c r="AJ31" s="1"/>
       <c r="AK31" s="1"/>
     </row>
-    <row r="32" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="32" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -4168,7 +4167,7 @@
       <c r="AJ32" s="1"/>
       <c r="AK32" s="1"/>
     </row>
-    <row r="33" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="33" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -4211,7 +4210,7 @@
       <c r="AJ33" s="1"/>
       <c r="AK33" s="1"/>
     </row>
-    <row r="34" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="34" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -4254,7 +4253,7 @@
       <c r="AJ34" s="1"/>
       <c r="AK34" s="1"/>
     </row>
-    <row r="35" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="35" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -4297,7 +4296,7 @@
       <c r="AJ35" s="1"/>
       <c r="AK35" s="1"/>
     </row>
-    <row r="36" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="36" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -4340,7 +4339,7 @@
       <c r="AJ36" s="1"/>
       <c r="AK36" s="1"/>
     </row>
-    <row r="37" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="37" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -4383,7 +4382,7 @@
       <c r="AJ37" s="1"/>
       <c r="AK37" s="1"/>
     </row>
-    <row r="38" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="38" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -4426,7 +4425,7 @@
       <c r="AJ38" s="1"/>
       <c r="AK38" s="1"/>
     </row>
-    <row r="39" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="39" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -4471,7 +4470,7 @@
       <c r="AJ39" s="1"/>
       <c r="AK39" s="1"/>
     </row>
-    <row r="40" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="40" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -4516,7 +4515,7 @@
       <c r="AJ40" s="1"/>
       <c r="AK40" s="1"/>
     </row>
-    <row r="41" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="41" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -4561,7 +4560,7 @@
       <c r="AJ41" s="1"/>
       <c r="AK41" s="1"/>
     </row>
-    <row r="42" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="42" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -4604,7 +4603,7 @@
       <c r="AJ42" s="1"/>
       <c r="AK42" s="1"/>
     </row>
-    <row r="43" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="43" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -4649,7 +4648,7 @@
       <c r="AJ43" s="1"/>
       <c r="AK43" s="1"/>
     </row>
-    <row r="44" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="44" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -4692,7 +4691,7 @@
       <c r="AJ44" s="1"/>
       <c r="AK44" s="1"/>
     </row>
-    <row r="45" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="45" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -4735,7 +4734,7 @@
       <c r="AJ45" s="1"/>
       <c r="AK45" s="1"/>
     </row>
-    <row r="46" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="46" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -4778,7 +4777,7 @@
       <c r="AJ46" s="1"/>
       <c r="AK46" s="1"/>
     </row>
-    <row r="47" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="47" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -4821,7 +4820,7 @@
       <c r="AJ47" s="1"/>
       <c r="AK47" s="1"/>
     </row>
-    <row r="48" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="48" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -4866,7 +4865,7 @@
       <c r="AJ48" s="1"/>
       <c r="AK48" s="1"/>
     </row>
-    <row r="49" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="49" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -4909,7 +4908,7 @@
       <c r="AJ49" s="1"/>
       <c r="AK49" s="1"/>
     </row>
-    <row r="50" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="50" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -4954,7 +4953,7 @@
       <c r="AJ50" s="1"/>
       <c r="AK50" s="1"/>
     </row>
-    <row r="51" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="51" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -4997,7 +4996,7 @@
       <c r="AJ51" s="1"/>
       <c r="AK51" s="1"/>
     </row>
-    <row r="52" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="52" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -5040,7 +5039,7 @@
       <c r="AJ52" s="1"/>
       <c r="AK52" s="1"/>
     </row>
-    <row r="53" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="53" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -5083,7 +5082,7 @@
       <c r="AJ53" s="1"/>
       <c r="AK53" s="1"/>
     </row>
-    <row r="54" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="54" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A54" s="3">
         <v>51</v>
       </c>
@@ -5128,7 +5127,7 @@
       <c r="AJ54" s="1"/>
       <c r="AK54" s="1"/>
     </row>
-    <row r="55" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="55" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -5173,7 +5172,7 @@
       <c r="AJ55" s="1"/>
       <c r="AK55" s="1"/>
     </row>
-    <row r="56" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="56" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -5216,7 +5215,7 @@
       <c r="AJ56" s="1"/>
       <c r="AK56" s="1"/>
     </row>
-    <row r="57" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="57" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -5259,7 +5258,7 @@
       <c r="AJ57" s="1"/>
       <c r="AK57" s="1"/>
     </row>
-    <row r="58" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="58" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -5302,7 +5301,7 @@
       <c r="AJ58" s="1"/>
       <c r="AK58" s="1"/>
     </row>
-    <row r="59" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="59" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -5345,7 +5344,7 @@
       <c r="AJ59" s="1"/>
       <c r="AK59" s="1"/>
     </row>
-    <row r="60" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="60" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -5388,7 +5387,7 @@
       <c r="AJ60" s="1"/>
       <c r="AK60" s="1"/>
     </row>
-    <row r="61" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="61" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -5431,7 +5430,7 @@
       <c r="AJ61" s="1"/>
       <c r="AK61" s="1"/>
     </row>
-    <row r="62" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="62" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -5474,7 +5473,7 @@
       <c r="AJ62" s="1"/>
       <c r="AK62" s="1"/>
     </row>
-    <row r="63" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="63" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A63" s="3">
         <v>60</v>
       </c>
@@ -5566,7 +5565,7 @@
       <c r="AJ64" s="1"/>
       <c r="AK64" s="1"/>
     </row>
-    <row r="65" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="65" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A65" s="3">
         <v>62</v>
       </c>
@@ -5611,7 +5610,7 @@
       <c r="AJ65" s="1"/>
       <c r="AK65" s="1"/>
     </row>
-    <row r="66" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="66" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A66" s="3">
         <v>63</v>
       </c>
@@ -5654,7 +5653,7 @@
       <c r="AJ66" s="1"/>
       <c r="AK66" s="1"/>
     </row>
-    <row r="67" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="67" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A67" s="3">
         <v>64</v>
       </c>
@@ -5701,7 +5700,7 @@
       <c r="AJ67" s="1"/>
       <c r="AK67" s="1"/>
     </row>
-    <row r="68" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="68" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A68" s="3">
         <v>65</v>
       </c>
@@ -5793,7 +5792,7 @@
       <c r="AJ69" s="1"/>
       <c r="AK69" s="1"/>
     </row>
-    <row r="70" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="70" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A70" s="3">
         <v>67</v>
       </c>
@@ -5838,7 +5837,7 @@
       <c r="AJ70" s="1"/>
       <c r="AK70" s="1"/>
     </row>
-    <row r="71" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="71" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A71" s="3">
         <v>68</v>
       </c>
@@ -5883,7 +5882,7 @@
       <c r="AJ71" s="1"/>
       <c r="AK71" s="1"/>
     </row>
-    <row r="72" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="72" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A72" s="3">
         <v>69</v>
       </c>
@@ -5926,7 +5925,7 @@
       <c r="AJ72" s="1"/>
       <c r="AK72" s="1"/>
     </row>
-    <row r="73" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="73" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A73" s="3">
         <v>70</v>
       </c>
@@ -5969,7 +5968,7 @@
       <c r="AJ73" s="1"/>
       <c r="AK73" s="1"/>
     </row>
-    <row r="74" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="74" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A74" s="3">
         <v>71</v>
       </c>
@@ -6012,7 +6011,7 @@
       <c r="AJ74" s="1"/>
       <c r="AK74" s="1"/>
     </row>
-    <row r="75" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="75" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A75" s="3">
         <v>72</v>
       </c>
@@ -6055,7 +6054,7 @@
       <c r="AJ75" s="1"/>
       <c r="AK75" s="1"/>
     </row>
-    <row r="76" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="76" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A76" s="3">
         <v>73</v>
       </c>
@@ -6102,7 +6101,7 @@
       <c r="AJ76" s="1"/>
       <c r="AK76" s="1"/>
     </row>
-    <row r="77" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="77" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A77" s="3">
         <v>74</v>
       </c>
@@ -6147,7 +6146,7 @@
       <c r="AJ77" s="1"/>
       <c r="AK77" s="1"/>
     </row>
-    <row r="78" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="78" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A78" s="3">
         <v>75</v>
       </c>
@@ -6192,7 +6191,7 @@
       <c r="AJ78" s="1"/>
       <c r="AK78" s="1"/>
     </row>
-    <row r="79" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="79" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A79" s="3">
         <v>76</v>
       </c>
@@ -6237,7 +6236,7 @@
       <c r="AJ79" s="1"/>
       <c r="AK79" s="1"/>
     </row>
-    <row r="80" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="80" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A80" s="3">
         <v>77</v>
       </c>
@@ -6282,7 +6281,7 @@
       <c r="AJ80" s="1"/>
       <c r="AK80" s="1"/>
     </row>
-    <row r="81" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="81" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A81" s="3">
         <v>78</v>
       </c>
@@ -6376,7 +6375,7 @@
       <c r="AJ82" s="1"/>
       <c r="AK82" s="1"/>
     </row>
-    <row r="83" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="83" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A83" s="3">
         <v>80</v>
       </c>
@@ -6423,7 +6422,7 @@
       <c r="AJ83" s="1"/>
       <c r="AK83" s="1"/>
     </row>
-    <row r="84" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="84" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A84" s="3">
         <v>81</v>
       </c>
@@ -6468,7 +6467,7 @@
       <c r="AJ84" s="1"/>
       <c r="AK84" s="1"/>
     </row>
-    <row r="85" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="85" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A85" s="3">
         <v>82</v>
       </c>
@@ -6511,7 +6510,7 @@
       <c r="AJ85" s="1"/>
       <c r="AK85" s="1"/>
     </row>
-    <row r="86" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="86" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A86" s="3">
         <v>83</v>
       </c>
@@ -6554,7 +6553,7 @@
       <c r="AJ86" s="1"/>
       <c r="AK86" s="1"/>
     </row>
-    <row r="87" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="87" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A87" s="3">
         <v>84</v>
       </c>
@@ -6642,7 +6641,7 @@
       <c r="AJ88" s="1"/>
       <c r="AK88" s="1"/>
     </row>
-    <row r="89" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="89" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A89" s="3">
         <v>86</v>
       </c>
@@ -6685,7 +6684,7 @@
       <c r="AJ89" s="1"/>
       <c r="AK89" s="1"/>
     </row>
-    <row r="90" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="90" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A90" s="3">
         <v>87</v>
       </c>
@@ -6773,7 +6772,7 @@
       <c r="AJ91" s="1"/>
       <c r="AK91" s="1"/>
     </row>
-    <row r="92" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="92" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A92" s="3">
         <v>89</v>
       </c>
@@ -6818,7 +6817,7 @@
       <c r="AJ92" s="1"/>
       <c r="AK92" s="1"/>
     </row>
-    <row r="93" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="93" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A93" s="3">
         <v>90</v>
       </c>
@@ -6861,7 +6860,7 @@
       <c r="AJ93" s="1"/>
       <c r="AK93" s="1"/>
     </row>
-    <row r="94" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="94" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A94" s="3">
         <v>91</v>
       </c>
@@ -6904,7 +6903,7 @@
       <c r="AJ94" s="1"/>
       <c r="AK94" s="1"/>
     </row>
-    <row r="95" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="95" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A95" s="3">
         <v>92</v>
       </c>
@@ -6947,7 +6946,7 @@
       <c r="AJ95" s="1"/>
       <c r="AK95" s="1"/>
     </row>
-    <row r="96" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="96" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A96" s="3">
         <v>93</v>
       </c>
@@ -6990,7 +6989,7 @@
       <c r="AJ96" s="1"/>
       <c r="AK96" s="1"/>
     </row>
-    <row r="97" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="97" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A97" s="3">
         <v>94</v>
       </c>
@@ -7033,7 +7032,7 @@
       <c r="AJ97" s="1"/>
       <c r="AK97" s="1"/>
     </row>
-    <row r="98" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="98" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A98" s="3">
         <v>95</v>
       </c>
@@ -7078,7 +7077,7 @@
       <c r="AJ98" s="1"/>
       <c r="AK98" s="1"/>
     </row>
-    <row r="99" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="99" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A99" s="3">
         <v>96</v>
       </c>
@@ -7121,7 +7120,7 @@
       <c r="AJ99" s="1"/>
       <c r="AK99" s="1"/>
     </row>
-    <row r="100" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="100" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A100" s="3">
         <v>97</v>
       </c>
@@ -7164,7 +7163,7 @@
       <c r="AJ100" s="1"/>
       <c r="AK100" s="1"/>
     </row>
-    <row r="101" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="101" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A101" s="3">
         <v>98</v>
       </c>
@@ -7207,7 +7206,7 @@
       <c r="AJ101" s="1"/>
       <c r="AK101" s="1"/>
     </row>
-    <row r="102" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="102" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A102" s="3">
         <v>99</v>
       </c>
@@ -7250,7 +7249,7 @@
       <c r="AJ102" s="1"/>
       <c r="AK102" s="1"/>
     </row>
-    <row r="103" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="103" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A103" s="3">
         <v>100</v>
       </c>
@@ -7293,7 +7292,7 @@
       <c r="AJ103" s="1"/>
       <c r="AK103" s="1"/>
     </row>
-    <row r="104" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="104" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A104" s="3">
         <v>101</v>
       </c>
@@ -7336,7 +7335,7 @@
       <c r="AJ104" s="1"/>
       <c r="AK104" s="1"/>
     </row>
-    <row r="105" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="105" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A105" s="3">
         <v>102</v>
       </c>
@@ -7381,7 +7380,7 @@
       <c r="AJ105" s="1"/>
       <c r="AK105" s="1"/>
     </row>
-    <row r="106" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="106" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A106" s="3">
         <v>103</v>
       </c>
@@ -7424,7 +7423,7 @@
       <c r="AJ106" s="1"/>
       <c r="AK106" s="1"/>
     </row>
-    <row r="107" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="107" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A107" s="3">
         <v>104</v>
       </c>
@@ -7469,7 +7468,7 @@
       <c r="AJ107" s="1"/>
       <c r="AK107" s="1"/>
     </row>
-    <row r="108" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="108" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A108" s="3">
         <v>105</v>
       </c>
@@ -7512,7 +7511,7 @@
       <c r="AJ108" s="1"/>
       <c r="AK108" s="1"/>
     </row>
-    <row r="109" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="109" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A109" s="3">
         <v>106</v>
       </c>
@@ -7557,7 +7556,7 @@
       <c r="AJ109" s="1"/>
       <c r="AK109" s="1"/>
     </row>
-    <row r="110" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="110" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A110" s="3">
         <v>107</v>
       </c>
@@ -7600,7 +7599,7 @@
       <c r="AJ110" s="1"/>
       <c r="AK110" s="1"/>
     </row>
-    <row r="111" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="111" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A111" s="3">
         <v>108</v>
       </c>
@@ -7737,7 +7736,7 @@
       <c r="AJ113" s="1"/>
       <c r="AK113" s="1"/>
     </row>
-    <row r="114" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="114" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A114" s="3">
         <v>111</v>
       </c>
@@ -7780,7 +7779,7 @@
       <c r="AJ114" s="1"/>
       <c r="AK114" s="1"/>
     </row>
-    <row r="115" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="115" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A115" s="3">
         <v>112</v>
       </c>
@@ -7825,7 +7824,7 @@
       <c r="AJ115" s="1"/>
       <c r="AK115" s="1"/>
     </row>
-    <row r="116" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="116" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A116" s="3">
         <v>113</v>
       </c>
@@ -7868,7 +7867,7 @@
       <c r="AJ116" s="1"/>
       <c r="AK116" s="1"/>
     </row>
-    <row r="117" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="117" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A117" s="3">
         <v>114</v>
       </c>
@@ -7911,7 +7910,7 @@
       <c r="AJ117" s="1"/>
       <c r="AK117" s="1"/>
     </row>
-    <row r="118" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="118" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A118" s="3">
         <v>115</v>
       </c>
@@ -7954,7 +7953,7 @@
       <c r="AJ118" s="1"/>
       <c r="AK118" s="1"/>
     </row>
-    <row r="119" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="119" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A119" s="3">
         <v>116</v>
       </c>
@@ -7997,7 +7996,7 @@
       <c r="AJ119" s="1"/>
       <c r="AK119" s="1"/>
     </row>
-    <row r="120" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="120" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A120" s="3">
         <v>117</v>
       </c>
@@ -8040,7 +8039,7 @@
       <c r="AJ120" s="1"/>
       <c r="AK120" s="1"/>
     </row>
-    <row r="121" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="121" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A121" s="3">
         <v>118</v>
       </c>
@@ -8083,7 +8082,7 @@
       <c r="AJ121" s="1"/>
       <c r="AK121" s="1"/>
     </row>
-    <row r="122" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="122" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A122" s="3">
         <v>119</v>
       </c>
@@ -8126,7 +8125,7 @@
       <c r="AJ122" s="1"/>
       <c r="AK122" s="1"/>
     </row>
-    <row r="123" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="123" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A123" s="3">
         <v>120</v>
       </c>
@@ -8169,7 +8168,7 @@
       <c r="AJ123" s="1"/>
       <c r="AK123" s="1"/>
     </row>
-    <row r="124" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="124" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A124" s="3">
         <v>121</v>
       </c>
@@ -8212,7 +8211,7 @@
       <c r="AJ124" s="1"/>
       <c r="AK124" s="1"/>
     </row>
-    <row r="125" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="125" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A125" s="3">
         <v>122</v>
       </c>
@@ -8300,7 +8299,7 @@
       <c r="AJ126" s="1"/>
       <c r="AK126" s="1"/>
     </row>
-    <row r="127" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="127" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A127" s="3">
         <v>124</v>
       </c>
@@ -8390,7 +8389,7 @@
       <c r="AJ128" s="1"/>
       <c r="AK128" s="1"/>
     </row>
-    <row r="129" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="129" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A129" s="3">
         <v>126</v>
       </c>
@@ -8482,7 +8481,7 @@
       <c r="AJ130" s="1"/>
       <c r="AK130" s="1"/>
     </row>
-    <row r="131" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="131" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A131" s="3">
         <v>128</v>
       </c>
@@ -8527,7 +8526,7 @@
       <c r="AJ131" s="1"/>
       <c r="AK131" s="1"/>
     </row>
-    <row r="132" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="132" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A132" s="3">
         <v>129</v>
       </c>
@@ -8570,7 +8569,7 @@
       <c r="AJ132" s="1"/>
       <c r="AK132" s="1"/>
     </row>
-    <row r="133" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="133" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A133" s="3">
         <v>130</v>
       </c>
@@ -8613,7 +8612,7 @@
       <c r="AJ133" s="1"/>
       <c r="AK133" s="1"/>
     </row>
-    <row r="134" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="134" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A134" s="3">
         <v>131</v>
       </c>
@@ -8656,7 +8655,7 @@
       <c r="AJ134" s="1"/>
       <c r="AK134" s="1"/>
     </row>
-    <row r="135" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="135" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A135" s="3">
         <v>132</v>
       </c>
@@ -8699,7 +8698,7 @@
       <c r="AJ135" s="1"/>
       <c r="AK135" s="1"/>
     </row>
-    <row r="136" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="136" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A136" s="3">
         <v>133</v>
       </c>
@@ -8742,7 +8741,7 @@
       <c r="AJ136" s="1"/>
       <c r="AK136" s="1"/>
     </row>
-    <row r="137" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="137" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A137" s="3">
         <v>134</v>
       </c>
@@ -8785,7 +8784,7 @@
       <c r="AJ137" s="1"/>
       <c r="AK137" s="1"/>
     </row>
-    <row r="138" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="138" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A138" s="3">
         <v>135</v>
       </c>
@@ -8828,7 +8827,7 @@
       <c r="AJ138" s="1"/>
       <c r="AK138" s="1"/>
     </row>
-    <row r="139" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="139" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A139" s="3">
         <v>136</v>
       </c>
@@ -8871,7 +8870,7 @@
       <c r="AJ139" s="1"/>
       <c r="AK139" s="1"/>
     </row>
-    <row r="140" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="140" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A140" s="3">
         <v>137</v>
       </c>
@@ -8914,7 +8913,7 @@
       <c r="AJ140" s="1"/>
       <c r="AK140" s="1"/>
     </row>
-    <row r="141" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="141" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A141" s="3">
         <v>138</v>
       </c>
@@ -8957,7 +8956,7 @@
       <c r="AJ141" s="1"/>
       <c r="AK141" s="1"/>
     </row>
-    <row r="142" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="142" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A142" s="3">
         <v>139</v>
       </c>
@@ -9000,7 +8999,7 @@
       <c r="AJ142" s="1"/>
       <c r="AK142" s="1"/>
     </row>
-    <row r="143" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="143" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A143" s="3">
         <v>140</v>
       </c>
@@ -9043,7 +9042,7 @@
       <c r="AJ143" s="1"/>
       <c r="AK143" s="1"/>
     </row>
-    <row r="144" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="144" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A144" s="3">
         <v>141</v>
       </c>
@@ -9086,7 +9085,7 @@
       <c r="AJ144" s="1"/>
       <c r="AK144" s="1"/>
     </row>
-    <row r="145" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="145" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A145" s="3">
         <v>142</v>
       </c>
@@ -9129,7 +9128,7 @@
       <c r="AJ145" s="1"/>
       <c r="AK145" s="1"/>
     </row>
-    <row r="146" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="146" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A146" s="3">
         <v>143</v>
       </c>
@@ -9172,7 +9171,7 @@
       <c r="AJ146" s="1"/>
       <c r="AK146" s="1"/>
     </row>
-    <row r="147" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="147" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A147" s="3">
         <v>144</v>
       </c>
@@ -9260,7 +9259,7 @@
       <c r="AJ148" s="1"/>
       <c r="AK148" s="1"/>
     </row>
-    <row r="149" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="149" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A149" s="3">
         <v>146</v>
       </c>
@@ -9303,7 +9302,7 @@
       <c r="AJ149" s="1"/>
       <c r="AK149" s="1"/>
     </row>
-    <row r="150" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="150" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A150" s="3">
         <v>147</v>
       </c>
@@ -9346,7 +9345,7 @@
       <c r="AJ150" s="1"/>
       <c r="AK150" s="1"/>
     </row>
-    <row r="151" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="151" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A151" s="3">
         <v>148</v>
       </c>
@@ -9389,7 +9388,7 @@
       <c r="AJ151" s="1"/>
       <c r="AK151" s="1"/>
     </row>
-    <row r="152" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="152" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A152" s="3">
         <v>149</v>
       </c>
@@ -9432,7 +9431,7 @@
       <c r="AJ152" s="1"/>
       <c r="AK152" s="1"/>
     </row>
-    <row r="153" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="153" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A153" s="3">
         <v>150</v>
       </c>
@@ -9477,7 +9476,7 @@
       <c r="AJ153" s="1"/>
       <c r="AK153" s="1"/>
     </row>
-    <row r="154" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="154" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A154" s="3">
         <v>151</v>
       </c>
@@ -9569,7 +9568,7 @@
       <c r="AJ155" s="1"/>
       <c r="AK155" s="1"/>
     </row>
-    <row r="156" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="156" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A156" s="3">
         <v>153</v>
       </c>
@@ -9614,7 +9613,7 @@
       <c r="AJ156" s="1"/>
       <c r="AK156" s="1"/>
     </row>
-    <row r="157" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="157" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A157" s="3">
         <v>154</v>
       </c>
@@ -9659,7 +9658,7 @@
       <c r="AJ157" s="1"/>
       <c r="AK157" s="1"/>
     </row>
-    <row r="158" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="158" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A158" s="3">
         <v>155</v>
       </c>
@@ -9706,7 +9705,7 @@
       <c r="AJ158" s="1"/>
       <c r="AK158" s="1"/>
     </row>
-    <row r="159" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="159" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A159" s="3">
         <v>156</v>
       </c>
@@ -9751,7 +9750,7 @@
       <c r="AJ159" s="1"/>
       <c r="AK159" s="1"/>
     </row>
-    <row r="160" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="160" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A160" s="3">
         <v>157</v>
       </c>
@@ -9798,7 +9797,7 @@
       <c r="AJ160" s="1"/>
       <c r="AK160" s="1"/>
     </row>
-    <row r="161" spans="1:37" ht="15" customHeight="1">
+    <row r="161" spans="1:37" ht="15" hidden="1" customHeight="1">
       <c r="A161" s="3">
         <v>158</v>
       </c>
@@ -9843,7 +9842,7 @@
       <c r="AJ161" s="1"/>
       <c r="AK161" s="1"/>
     </row>
-    <row r="162" spans="1:37" ht="15" customHeight="1">
+    <row r="162" spans="1:37" ht="15" hidden="1" customHeight="1">
       <c r="A162" s="3">
         <v>159</v>
       </c>
@@ -9888,7 +9887,7 @@
       <c r="AJ162" s="1"/>
       <c r="AK162" s="1"/>
     </row>
-    <row r="163" spans="1:37" ht="15" customHeight="1">
+    <row r="163" spans="1:37" ht="15" hidden="1" customHeight="1">
       <c r="A163" s="3">
         <v>160</v>
       </c>
@@ -9935,7 +9934,7 @@
       <c r="AJ163" s="1"/>
       <c r="AK163" s="1"/>
     </row>
-    <row r="164" spans="1:37" ht="15" customHeight="1">
+    <row r="164" spans="1:37" ht="15" hidden="1" customHeight="1">
       <c r="A164" s="3">
         <v>161</v>
       </c>
@@ -9980,7 +9979,7 @@
       <c r="AJ164" s="3"/>
       <c r="AK164" s="3"/>
     </row>
-    <row r="165" spans="1:37" ht="15" customHeight="1">
+    <row r="165" spans="1:37" ht="15" hidden="1" customHeight="1">
       <c r="A165" s="3">
         <v>162</v>
       </c>
@@ -10025,7 +10024,7 @@
       <c r="AJ165" s="3"/>
       <c r="AK165" s="3"/>
     </row>
-    <row r="166" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="166" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A166" s="3">
         <v>163</v>
       </c>
@@ -10068,7 +10067,7 @@
       <c r="AJ166" s="1"/>
       <c r="AK166" s="1"/>
     </row>
-    <row r="167" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="167" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A167" s="3">
         <v>164</v>
       </c>
@@ -10111,7 +10110,7 @@
       <c r="AJ167" s="1"/>
       <c r="AK167" s="1"/>
     </row>
-    <row r="168" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="168" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A168" s="3">
         <v>165</v>
       </c>
@@ -10154,7 +10153,7 @@
       <c r="AJ168" s="1"/>
       <c r="AK168" s="1"/>
     </row>
-    <row r="169" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="169" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A169" s="3">
         <v>166</v>
       </c>
@@ -10197,7 +10196,7 @@
       <c r="AJ169" s="1"/>
       <c r="AK169" s="1"/>
     </row>
-    <row r="170" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="170" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A170" s="3">
         <v>167</v>
       </c>
@@ -10240,7 +10239,7 @@
       <c r="AJ170" s="1"/>
       <c r="AK170" s="1"/>
     </row>
-    <row r="171" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="171" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A171" s="3">
         <v>168</v>
       </c>
@@ -10283,7 +10282,7 @@
       <c r="AJ171" s="1"/>
       <c r="AK171" s="1"/>
     </row>
-    <row r="172" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="172" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A172" s="3">
         <v>169</v>
       </c>
@@ -10328,7 +10327,7 @@
       <c r="AJ172" s="1"/>
       <c r="AK172" s="1"/>
     </row>
-    <row r="173" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="173" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A173" s="3">
         <v>170</v>
       </c>
@@ -10424,7 +10423,7 @@
       <c r="AJ174" s="1"/>
       <c r="AK174" s="1"/>
     </row>
-    <row r="175" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="175" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A175" s="3">
         <v>172</v>
       </c>
@@ -10526,7 +10525,7 @@
       <c r="AJ176" s="1"/>
       <c r="AK176" s="1"/>
     </row>
-    <row r="177" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="177" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A177" s="3">
         <v>174</v>
       </c>
@@ -10573,7 +10572,7 @@
       <c r="AJ177" s="1"/>
       <c r="AK177" s="1"/>
     </row>
-    <row r="178" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="178" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A178" s="3">
         <v>175</v>
       </c>
@@ -10620,7 +10619,7 @@
       <c r="AJ178" s="1"/>
       <c r="AK178" s="1"/>
     </row>
-    <row r="179" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="179" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A179" s="3">
         <v>176</v>
       </c>
@@ -10667,7 +10666,7 @@
       <c r="AJ179" s="1"/>
       <c r="AK179" s="1"/>
     </row>
-    <row r="180" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="180" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A180" s="3">
         <v>177</v>
       </c>
@@ -10716,7 +10715,7 @@
       <c r="AJ180" s="1"/>
       <c r="AK180" s="1"/>
     </row>
-    <row r="181" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="181" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A181" s="3">
         <v>178</v>
       </c>
@@ -10763,7 +10762,7 @@
       <c r="AJ181" s="1"/>
       <c r="AK181" s="1"/>
     </row>
-    <row r="182" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="182" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A182" s="3">
         <v>179</v>
       </c>
@@ -10812,7 +10811,7 @@
       <c r="AJ182" s="1"/>
       <c r="AK182" s="1"/>
     </row>
-    <row r="183" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="183" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A183" s="3">
         <v>180</v>
       </c>
@@ -10863,7 +10862,7 @@
       <c r="AJ183" s="1"/>
       <c r="AK183" s="1"/>
     </row>
-    <row r="184" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="184" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A184" s="3">
         <v>181</v>
       </c>
@@ -10914,7 +10913,7 @@
       <c r="AJ184" s="1"/>
       <c r="AK184" s="1"/>
     </row>
-    <row r="185" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="185" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A185" s="3">
         <v>182</v>
       </c>
@@ -10963,7 +10962,7 @@
       <c r="AJ185" s="1"/>
       <c r="AK185" s="1"/>
     </row>
-    <row r="186" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="186" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A186" s="3">
         <v>183</v>
       </c>
@@ -11016,7 +11015,7 @@
       <c r="AJ186" s="1"/>
       <c r="AK186" s="1"/>
     </row>
-    <row r="187" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="187" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A187" s="3">
         <v>184</v>
       </c>
@@ -11069,7 +11068,7 @@
       <c r="AJ187" s="1"/>
       <c r="AK187" s="1"/>
     </row>
-    <row r="188" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="188" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A188" s="3">
         <v>185</v>
       </c>
@@ -11124,7 +11123,7 @@
       <c r="AJ188" s="1"/>
       <c r="AK188" s="1"/>
     </row>
-    <row r="189" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="189" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A189" s="3">
         <v>186</v>
       </c>
@@ -11177,7 +11176,7 @@
       <c r="AJ189" s="1"/>
       <c r="AK189" s="1"/>
     </row>
-    <row r="190" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="190" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A190" s="3">
         <v>187</v>
       </c>
@@ -11230,7 +11229,7 @@
       <c r="AJ190" s="1"/>
       <c r="AK190" s="1"/>
     </row>
-    <row r="191" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="191" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A191" s="3">
         <v>188</v>
       </c>
@@ -11283,7 +11282,7 @@
       <c r="AJ191" s="1"/>
       <c r="AK191" s="1"/>
     </row>
-    <row r="192" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="192" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A192" s="3">
         <v>189</v>
       </c>
@@ -11330,7 +11329,7 @@
       <c r="AJ192" s="1"/>
       <c r="AK192" s="1"/>
     </row>
-    <row r="193" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="193" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A193" s="3">
         <v>190</v>
       </c>
@@ -11377,7 +11376,7 @@
       <c r="AJ193" s="1"/>
       <c r="AK193" s="1"/>
     </row>
-    <row r="194" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="194" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A194" s="3">
         <v>191</v>
       </c>
@@ -11422,7 +11421,7 @@
       <c r="AJ194" s="1"/>
       <c r="AK194" s="1"/>
     </row>
-    <row r="195" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="195" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A195" s="3">
         <v>192</v>
       </c>
@@ -11467,7 +11466,7 @@
       <c r="AJ195" s="1"/>
       <c r="AK195" s="1"/>
     </row>
-    <row r="196" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="196" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A196" s="3">
         <v>193</v>
       </c>
@@ -11512,7 +11511,7 @@
       <c r="AJ196" s="1"/>
       <c r="AK196" s="1"/>
     </row>
-    <row r="197" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="197" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A197" s="3">
         <v>194</v>
       </c>
@@ -11557,7 +11556,7 @@
       <c r="AJ197" s="1"/>
       <c r="AK197" s="1"/>
     </row>
-    <row r="198" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="198" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A198" s="3">
         <v>195</v>
       </c>
@@ -11604,7 +11603,7 @@
       <c r="AJ198" s="1"/>
       <c r="AK198" s="1"/>
     </row>
-    <row r="199" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="199" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A199" s="3">
         <v>196</v>
       </c>
@@ -11651,7 +11650,7 @@
       <c r="AJ199" s="1"/>
       <c r="AK199" s="1"/>
     </row>
-    <row r="200" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="200" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A200" s="3">
         <v>197</v>
       </c>
@@ -11696,7 +11695,7 @@
       <c r="AJ200" s="1"/>
       <c r="AK200" s="1"/>
     </row>
-    <row r="201" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="201" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A201" s="3">
         <v>198</v>
       </c>
@@ -11743,7 +11742,7 @@
       <c r="AJ201" s="1"/>
       <c r="AK201" s="1"/>
     </row>
-    <row r="202" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="202" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A202" s="3">
         <v>199</v>
       </c>
@@ -11788,7 +11787,7 @@
       <c r="AJ202" s="1"/>
       <c r="AK202" s="1"/>
     </row>
-    <row r="203" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="203" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A203" s="3">
         <v>200</v>
       </c>
@@ -11835,7 +11834,7 @@
       <c r="AJ203" s="1"/>
       <c r="AK203" s="1"/>
     </row>
-    <row r="204" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="204" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A204" s="3">
         <v>201</v>
       </c>
@@ -11880,7 +11879,7 @@
       <c r="AJ204" s="1"/>
       <c r="AK204" s="1"/>
     </row>
-    <row r="205" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="205" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A205" s="3">
         <v>202</v>
       </c>
@@ -11925,7 +11924,7 @@
       <c r="AJ205" s="1"/>
       <c r="AK205" s="1"/>
     </row>
-    <row r="206" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="206" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A206" s="3">
         <v>203</v>
       </c>
@@ -11970,7 +11969,7 @@
       <c r="AJ206" s="1"/>
       <c r="AK206" s="1"/>
     </row>
-    <row r="207" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="207" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A207" s="3">
         <v>204</v>
       </c>
@@ -12017,7 +12016,7 @@
       <c r="AJ207" s="1"/>
       <c r="AK207" s="1"/>
     </row>
-    <row r="208" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="208" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A208" s="3">
         <v>205</v>
       </c>
@@ -12062,7 +12061,7 @@
       <c r="AJ208" s="1"/>
       <c r="AK208" s="1"/>
     </row>
-    <row r="209" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="209" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A209" s="3">
         <v>206</v>
       </c>
@@ -12107,7 +12106,7 @@
       <c r="AJ209" s="1"/>
       <c r="AK209" s="1"/>
     </row>
-    <row r="210" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="210" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A210" s="3">
         <v>207</v>
       </c>
@@ -12152,7 +12151,7 @@
       <c r="AJ210" s="1"/>
       <c r="AK210" s="1"/>
     </row>
-    <row r="211" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="211" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A211" s="3">
         <v>208</v>
       </c>
@@ -12197,7 +12196,7 @@
       <c r="AJ211" s="1"/>
       <c r="AK211" s="1"/>
     </row>
-    <row r="212" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="212" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A212" s="3">
         <v>209</v>
       </c>
@@ -12242,7 +12241,7 @@
       <c r="AJ212" s="1"/>
       <c r="AK212" s="1"/>
     </row>
-    <row r="213" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="213" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A213" s="3">
         <v>210</v>
       </c>
@@ -12287,7 +12286,7 @@
       <c r="AJ213" s="1"/>
       <c r="AK213" s="1"/>
     </row>
-    <row r="214" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="214" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A214" s="3">
         <v>211</v>
       </c>
@@ -12332,7 +12331,7 @@
       <c r="AJ214" s="1"/>
       <c r="AK214" s="1"/>
     </row>
-    <row r="215" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="215" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A215" s="3">
         <v>212</v>
       </c>
@@ -12377,7 +12376,7 @@
       <c r="AJ215" s="1"/>
       <c r="AK215" s="1"/>
     </row>
-    <row r="216" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="216" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A216" s="3">
         <v>213</v>
       </c>
@@ -12426,7 +12425,7 @@
       <c r="AJ216" s="1"/>
       <c r="AK216" s="1"/>
     </row>
-    <row r="217" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="217" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A217" s="3">
         <v>214</v>
       </c>
@@ -12475,7 +12474,7 @@
       <c r="AJ217" s="1"/>
       <c r="AK217" s="1"/>
     </row>
-    <row r="218" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="218" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A218" s="3">
         <v>215</v>
       </c>
@@ -12524,7 +12523,7 @@
       <c r="AJ218" s="1"/>
       <c r="AK218" s="1"/>
     </row>
-    <row r="219" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="219" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A219" s="3">
         <v>216</v>
       </c>
@@ -12567,7 +12566,7 @@
       <c r="AJ219" s="1"/>
       <c r="AK219" s="1"/>
     </row>
-    <row r="220" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="220" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A220" s="3">
         <v>217</v>
       </c>
@@ -12610,7 +12609,7 @@
       <c r="AJ220" s="1"/>
       <c r="AK220" s="1"/>
     </row>
-    <row r="221" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="221" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A221" s="3">
         <v>218</v>
       </c>
@@ -12653,7 +12652,7 @@
       <c r="AJ221" s="1"/>
       <c r="AK221" s="1"/>
     </row>
-    <row r="222" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="222" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A222" s="3">
         <v>219</v>
       </c>
@@ -12698,7 +12697,7 @@
       <c r="AJ222" s="1"/>
       <c r="AK222" s="1"/>
     </row>
-    <row r="223" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="223" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A223" s="3">
         <v>220</v>
       </c>
@@ -12741,7 +12740,7 @@
       <c r="AJ223" s="1"/>
       <c r="AK223" s="1"/>
     </row>
-    <row r="224" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="224" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A224" s="3">
         <v>221</v>
       </c>
@@ -12784,7 +12783,7 @@
       <c r="AJ224" s="1"/>
       <c r="AK224" s="1"/>
     </row>
-    <row r="225" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="225" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A225" s="3">
         <v>222</v>
       </c>
@@ -12827,7 +12826,7 @@
       <c r="AJ225" s="1"/>
       <c r="AK225" s="1"/>
     </row>
-    <row r="226" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="226" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A226" s="3">
         <v>223</v>
       </c>
@@ -12870,7 +12869,7 @@
       <c r="AJ226" s="1"/>
       <c r="AK226" s="1"/>
     </row>
-    <row r="227" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="227" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A227" s="3">
         <v>224</v>
       </c>
@@ -12913,7 +12912,7 @@
       <c r="AJ227" s="1"/>
       <c r="AK227" s="1"/>
     </row>
-    <row r="228" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="228" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A228" s="3">
         <v>225</v>
       </c>
@@ -12956,7 +12955,7 @@
       <c r="AJ228" s="1"/>
       <c r="AK228" s="1"/>
     </row>
-    <row r="229" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="229" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A229" s="3">
         <v>226</v>
       </c>
@@ -12999,7 +12998,7 @@
       <c r="AJ229" s="1"/>
       <c r="AK229" s="1"/>
     </row>
-    <row r="230" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="230" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A230" s="3">
         <v>227</v>
       </c>
@@ -13042,7 +13041,7 @@
       <c r="AJ230" s="1"/>
       <c r="AK230" s="1"/>
     </row>
-    <row r="231" spans="1:37">
+    <row r="231" spans="1:37" hidden="1">
       <c r="A231" s="3">
         <v>228</v>
       </c>
@@ -13085,7 +13084,7 @@
       <c r="AJ231" s="1"/>
       <c r="AK231" s="1"/>
     </row>
-    <row r="232" spans="1:37">
+    <row r="232" spans="1:37" hidden="1">
       <c r="A232" s="3">
         <v>229</v>
       </c>
@@ -13128,7 +13127,7 @@
       <c r="AJ232" s="1"/>
       <c r="AK232" s="1"/>
     </row>
-    <row r="233" spans="1:37">
+    <row r="233" spans="1:37" hidden="1">
       <c r="A233" s="3">
         <v>230</v>
       </c>
@@ -13173,7 +13172,7 @@
       <c r="AJ233" s="1"/>
       <c r="AK233" s="1"/>
     </row>
-    <row r="234" spans="1:37">
+    <row r="234" spans="1:37" hidden="1">
       <c r="A234" s="3">
         <v>231</v>
       </c>
@@ -13216,7 +13215,7 @@
       <c r="AJ234" s="1"/>
       <c r="AK234" s="1"/>
     </row>
-    <row r="235" spans="1:37">
+    <row r="235" spans="1:37" hidden="1">
       <c r="A235" s="3">
         <v>232</v>
       </c>
@@ -13261,7 +13260,7 @@
       <c r="AJ235" s="1"/>
       <c r="AK235" s="1"/>
     </row>
-    <row r="236" spans="1:37">
+    <row r="236" spans="1:37" hidden="1">
       <c r="A236" s="3">
         <v>233</v>
       </c>
@@ -13304,7 +13303,7 @@
       <c r="AJ236" s="1"/>
       <c r="AK236" s="1"/>
     </row>
-    <row r="237" spans="1:37">
+    <row r="237" spans="1:37" hidden="1">
       <c r="A237" s="3">
         <v>234</v>
       </c>
@@ -13347,7 +13346,7 @@
       <c r="AJ237" s="1"/>
       <c r="AK237" s="1"/>
     </row>
-    <row r="238" spans="1:37">
+    <row r="238" spans="1:37" hidden="1">
       <c r="A238" s="3">
         <v>235</v>
       </c>
@@ -13390,7 +13389,7 @@
       <c r="AJ238" s="1"/>
       <c r="AK238" s="1"/>
     </row>
-    <row r="239" spans="1:37">
+    <row r="239" spans="1:37" hidden="1">
       <c r="A239" s="3">
         <v>236</v>
       </c>
@@ -13433,7 +13432,7 @@
       <c r="AJ239" s="1"/>
       <c r="AK239" s="1"/>
     </row>
-    <row r="240" spans="1:37">
+    <row r="240" spans="1:37" hidden="1">
       <c r="A240" s="3">
         <v>237</v>
       </c>
@@ -13476,7 +13475,7 @@
       <c r="AJ240" s="1"/>
       <c r="AK240" s="1"/>
     </row>
-    <row r="241" spans="1:37">
+    <row r="241" spans="1:37" hidden="1">
       <c r="A241" s="3">
         <v>238</v>
       </c>
@@ -13519,7 +13518,7 @@
       <c r="AJ241" s="1"/>
       <c r="AK241" s="1"/>
     </row>
-    <row r="242" spans="1:37">
+    <row r="242" spans="1:37" hidden="1">
       <c r="A242" s="3">
         <v>239</v>
       </c>
@@ -13562,7 +13561,7 @@
       <c r="AJ242" s="1"/>
       <c r="AK242" s="1"/>
     </row>
-    <row r="243" spans="1:37">
+    <row r="243" spans="1:37" hidden="1">
       <c r="A243" s="3">
         <v>240</v>
       </c>
@@ -13607,7 +13606,7 @@
       <c r="AJ243" s="1"/>
       <c r="AK243" s="1"/>
     </row>
-    <row r="244" spans="1:37">
+    <row r="244" spans="1:37" hidden="1">
       <c r="A244" s="3">
         <v>241</v>
       </c>
@@ -13652,7 +13651,7 @@
       <c r="AJ244" s="1"/>
       <c r="AK244" s="1"/>
     </row>
-    <row r="245" spans="1:37">
+    <row r="245" spans="1:37" hidden="1">
       <c r="A245" s="3">
         <v>242</v>
       </c>
@@ -13697,7 +13696,7 @@
       <c r="AJ245" s="1"/>
       <c r="AK245" s="1"/>
     </row>
-    <row r="246" spans="1:37">
+    <row r="246" spans="1:37" hidden="1">
       <c r="A246" s="3">
         <v>243</v>
       </c>
@@ -13742,7 +13741,7 @@
       <c r="AJ246" s="1"/>
       <c r="AK246" s="1"/>
     </row>
-    <row r="247" spans="1:37">
+    <row r="247" spans="1:37" hidden="1">
       <c r="A247" s="3">
         <v>244</v>
       </c>
@@ -13787,7 +13786,7 @@
       <c r="AJ247" s="1"/>
       <c r="AK247" s="1"/>
     </row>
-    <row r="248" spans="1:37">
+    <row r="248" spans="1:37" hidden="1">
       <c r="A248" s="3">
         <v>245</v>
       </c>
@@ -13832,7 +13831,7 @@
       <c r="AJ248" s="1"/>
       <c r="AK248" s="1"/>
     </row>
-    <row r="249" spans="1:37">
+    <row r="249" spans="1:37" hidden="1">
       <c r="A249" s="3">
         <v>246</v>
       </c>
@@ -13875,7 +13874,7 @@
       <c r="AJ249" s="1"/>
       <c r="AK249" s="1"/>
     </row>
-    <row r="250" spans="1:37">
+    <row r="250" spans="1:37" hidden="1">
       <c r="A250" s="3">
         <v>247</v>
       </c>
@@ -13918,7 +13917,7 @@
       <c r="AJ250" s="1"/>
       <c r="AK250" s="1"/>
     </row>
-    <row r="251" spans="1:37">
+    <row r="251" spans="1:37" hidden="1">
       <c r="A251" s="3">
         <v>248</v>
       </c>
@@ -13961,7 +13960,7 @@
       <c r="AJ251" s="1"/>
       <c r="AK251" s="1"/>
     </row>
-    <row r="252" spans="1:37">
+    <row r="252" spans="1:37" hidden="1">
       <c r="A252" s="3">
         <v>249</v>
       </c>
@@ -14004,7 +14003,7 @@
       <c r="AJ252" s="1"/>
       <c r="AK252" s="1"/>
     </row>
-    <row r="253" spans="1:37">
+    <row r="253" spans="1:37" hidden="1">
       <c r="A253" s="3">
         <v>250</v>
       </c>
@@ -14047,7 +14046,7 @@
       <c r="AJ253" s="1"/>
       <c r="AK253" s="1"/>
     </row>
-    <row r="254" spans="1:37">
+    <row r="254" spans="1:37" hidden="1">
       <c r="A254" s="3">
         <v>251</v>
       </c>
@@ -14090,7 +14089,7 @@
       <c r="AJ254" s="1"/>
       <c r="AK254" s="1"/>
     </row>
-    <row r="255" spans="1:37">
+    <row r="255" spans="1:37" hidden="1">
       <c r="A255" s="3">
         <v>252</v>
       </c>
@@ -14133,7 +14132,7 @@
       <c r="AJ255" s="1"/>
       <c r="AK255" s="1"/>
     </row>
-    <row r="256" spans="1:37">
+    <row r="256" spans="1:37" hidden="1">
       <c r="A256" s="3">
         <v>253</v>
       </c>
@@ -14176,7 +14175,7 @@
       <c r="AJ256" s="1"/>
       <c r="AK256" s="1"/>
     </row>
-    <row r="257" spans="1:37">
+    <row r="257" spans="1:37" hidden="1">
       <c r="A257" s="3">
         <v>254</v>
       </c>
@@ -14217,7 +14216,7 @@
       <c r="AJ257" s="1"/>
       <c r="AK257" s="1"/>
     </row>
-    <row r="258" spans="1:37">
+    <row r="258" spans="1:37" hidden="1">
       <c r="A258" s="3">
         <v>255</v>
       </c>
@@ -14258,7 +14257,7 @@
       <c r="AJ258" s="1"/>
       <c r="AK258" s="1"/>
     </row>
-    <row r="259" spans="1:37">
+    <row r="259" spans="1:37" hidden="1">
       <c r="A259" s="3">
         <v>256</v>
       </c>
@@ -14299,7 +14298,7 @@
       <c r="AJ259" s="1"/>
       <c r="AK259" s="1"/>
     </row>
-    <row r="260" spans="1:37">
+    <row r="260" spans="1:37" hidden="1">
       <c r="A260" s="3">
         <v>257</v>
       </c>
@@ -14340,7 +14339,7 @@
       <c r="AJ260" s="1"/>
       <c r="AK260" s="1"/>
     </row>
-    <row r="261" spans="1:37">
+    <row r="261" spans="1:37" hidden="1">
       <c r="A261" s="3">
         <v>258</v>
       </c>
@@ -14381,7 +14380,7 @@
       <c r="AJ261" s="1"/>
       <c r="AK261" s="1"/>
     </row>
-    <row r="262" spans="1:37">
+    <row r="262" spans="1:37" hidden="1">
       <c r="A262" s="3">
         <v>259</v>
       </c>
@@ -14422,7 +14421,7 @@
       <c r="AJ262" s="1"/>
       <c r="AK262" s="1"/>
     </row>
-    <row r="263" spans="1:37">
+    <row r="263" spans="1:37" hidden="1">
       <c r="A263" s="3">
         <v>260</v>
       </c>
@@ -14463,7 +14462,7 @@
       <c r="AJ263" s="1"/>
       <c r="AK263" s="1"/>
     </row>
-    <row r="264" spans="1:37">
+    <row r="264" spans="1:37" hidden="1">
       <c r="A264" s="3">
         <v>261</v>
       </c>
@@ -14504,7 +14503,7 @@
       <c r="AJ264" s="1"/>
       <c r="AK264" s="1"/>
     </row>
-    <row r="265" spans="1:37">
+    <row r="265" spans="1:37" hidden="1">
       <c r="A265" s="3">
         <v>262</v>
       </c>
@@ -14545,7 +14544,7 @@
       <c r="AJ265" s="1"/>
       <c r="AK265" s="1"/>
     </row>
-    <row r="266" spans="1:37">
+    <row r="266" spans="1:37" hidden="1">
       <c r="A266" s="3">
         <v>263</v>
       </c>
@@ -14586,7 +14585,7 @@
       <c r="AJ266" s="1"/>
       <c r="AK266" s="1"/>
     </row>
-    <row r="267" spans="1:37">
+    <row r="267" spans="1:37" hidden="1">
       <c r="A267" s="3">
         <v>264</v>
       </c>
@@ -14627,7 +14626,7 @@
       <c r="AJ267" s="1"/>
       <c r="AK267" s="1"/>
     </row>
-    <row r="268" spans="1:37">
+    <row r="268" spans="1:37" hidden="1">
       <c r="A268" s="3">
         <v>265</v>
       </c>
@@ -14668,7 +14667,7 @@
       <c r="AJ268" s="1"/>
       <c r="AK268" s="1"/>
     </row>
-    <row r="269" spans="1:37">
+    <row r="269" spans="1:37" hidden="1">
       <c r="A269" s="3">
         <v>266</v>
       </c>
@@ -14709,7 +14708,7 @@
       <c r="AJ269" s="1"/>
       <c r="AK269" s="1"/>
     </row>
-    <row r="270" spans="1:37">
+    <row r="270" spans="1:37" hidden="1">
       <c r="A270" s="3">
         <v>267</v>
       </c>
@@ -14750,7 +14749,7 @@
       <c r="AJ270" s="1"/>
       <c r="AK270" s="1"/>
     </row>
-    <row r="271" spans="1:37">
+    <row r="271" spans="1:37" hidden="1">
       <c r="A271" s="3">
         <v>268</v>
       </c>
@@ -14791,7 +14790,7 @@
       <c r="AJ271" s="1"/>
       <c r="AK271" s="1"/>
     </row>
-    <row r="272" spans="1:37">
+    <row r="272" spans="1:37" hidden="1">
       <c r="A272" s="3">
         <v>269</v>
       </c>
@@ -14832,7 +14831,7 @@
       <c r="AJ272" s="1"/>
       <c r="AK272" s="1"/>
     </row>
-    <row r="273" spans="1:37">
+    <row r="273" spans="1:37" hidden="1">
       <c r="A273" s="3">
         <v>270</v>
       </c>
@@ -14873,7 +14872,7 @@
       <c r="AJ273" s="1"/>
       <c r="AK273" s="1"/>
     </row>
-    <row r="274" spans="1:37">
+    <row r="274" spans="1:37" hidden="1">
       <c r="A274" s="3">
         <v>271</v>
       </c>
@@ -14914,7 +14913,7 @@
       <c r="AJ274" s="1"/>
       <c r="AK274" s="1"/>
     </row>
-    <row r="275" spans="1:37">
+    <row r="275" spans="1:37" hidden="1">
       <c r="A275" s="3">
         <v>272</v>
       </c>
@@ -14955,7 +14954,7 @@
       <c r="AJ275" s="1"/>
       <c r="AK275" s="1"/>
     </row>
-    <row r="276" spans="1:37">
+    <row r="276" spans="1:37" hidden="1">
       <c r="A276" s="3">
         <v>273</v>
       </c>
@@ -14996,7 +14995,7 @@
       <c r="AJ276" s="1"/>
       <c r="AK276" s="1"/>
     </row>
-    <row r="277" spans="1:37">
+    <row r="277" spans="1:37" hidden="1">
       <c r="A277" s="3">
         <v>274</v>
       </c>
@@ -15037,7 +15036,7 @@
       <c r="AJ277" s="1"/>
       <c r="AK277" s="1"/>
     </row>
-    <row r="278" spans="1:37">
+    <row r="278" spans="1:37" hidden="1">
       <c r="A278" s="3">
         <v>275</v>
       </c>
@@ -15078,7 +15077,7 @@
       <c r="AJ278" s="1"/>
       <c r="AK278" s="1"/>
     </row>
-    <row r="279" spans="1:37">
+    <row r="279" spans="1:37" hidden="1">
       <c r="A279" s="3">
         <v>276</v>
       </c>
@@ -15119,7 +15118,7 @@
       <c r="AJ279" s="1"/>
       <c r="AK279" s="1"/>
     </row>
-    <row r="280" spans="1:37">
+    <row r="280" spans="1:37" hidden="1">
       <c r="A280" s="3">
         <v>277</v>
       </c>
@@ -15161,7 +15160,13 @@
       <c r="AK280" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AB280" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:AB280" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="16">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="4">
     <mergeCell ref="C1:C3"/>
     <mergeCell ref="A1:A3"/>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADDBCF8-DCDB-46C8-A0B0-FDCBC3551F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA9268A-6509-4203-9C71-60DA9F994899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4430" yWindow="650" windowWidth="14770" windowHeight="9430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="リスト" sheetId="1" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="403">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -2963,7 +2963,9 @@
         <v>157</v>
       </c>
       <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
+      <c r="Z5" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
@@ -3764,7 +3766,7 @@
       <c r="AJ23" s="1"/>
       <c r="AK23" s="1"/>
     </row>
-    <row r="24" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="24" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -3796,7 +3798,9 @@
         <v>157</v>
       </c>
       <c r="Y24" s="1"/>
-      <c r="Z24" s="1"/>
+      <c r="Z24" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
@@ -3897,7 +3901,7 @@
       <c r="AJ26" s="1"/>
       <c r="AK26" s="1"/>
     </row>
-    <row r="27" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="27" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -4073,7 +4077,7 @@
       <c r="AJ30" s="1"/>
       <c r="AK30" s="1"/>
     </row>
-    <row r="31" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="31" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -5215,7 +5219,7 @@
       <c r="AJ56" s="1"/>
       <c r="AK56" s="1"/>
     </row>
-    <row r="57" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="57" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -5245,7 +5249,9 @@
       <c r="W57" s="1"/>
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
-      <c r="Z57" s="1"/>
+      <c r="Z57" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
@@ -5518,7 +5524,7 @@
       <c r="AJ63" s="1"/>
       <c r="AK63" s="1"/>
     </row>
-    <row r="64" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="64" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A64" s="3">
         <v>61</v>
       </c>
@@ -5700,7 +5706,7 @@
       <c r="AJ67" s="1"/>
       <c r="AK67" s="1"/>
     </row>
-    <row r="68" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="68" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A68" s="3">
         <v>65</v>
       </c>
@@ -5732,7 +5738,9 @@
       <c r="W68" s="1"/>
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
-      <c r="Z68" s="1"/>
+      <c r="Z68" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA68" s="1"/>
       <c r="AB68" s="1"/>
       <c r="AC68" s="1"/>
@@ -5745,7 +5753,7 @@
       <c r="AJ68" s="1"/>
       <c r="AK68" s="1"/>
     </row>
-    <row r="69" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="69" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A69" s="3">
         <v>66</v>
       </c>
@@ -6054,7 +6062,7 @@
       <c r="AJ75" s="1"/>
       <c r="AK75" s="1"/>
     </row>
-    <row r="76" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="76" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A76" s="3">
         <v>73</v>
       </c>
@@ -6088,7 +6096,9 @@
       <c r="W76" s="1"/>
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
-      <c r="Z76" s="1"/>
+      <c r="Z76" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
@@ -6328,7 +6338,7 @@
       <c r="AJ81" s="1"/>
       <c r="AK81" s="1"/>
     </row>
-    <row r="82" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="82" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A82" s="3">
         <v>79</v>
       </c>
@@ -6596,7 +6606,7 @@
       <c r="AJ87" s="1"/>
       <c r="AK87" s="1"/>
     </row>
-    <row r="88" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="88" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A88" s="3">
         <v>85</v>
       </c>
@@ -6727,7 +6737,7 @@
       <c r="AJ90" s="1"/>
       <c r="AK90" s="1"/>
     </row>
-    <row r="91" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="91" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A91" s="3">
         <v>88</v>
       </c>
@@ -7642,7 +7652,7 @@
       <c r="AJ111" s="1"/>
       <c r="AK111" s="1"/>
     </row>
-    <row r="112" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="112" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A112" s="3">
         <v>109</v>
       </c>
@@ -7691,7 +7701,7 @@
       <c r="AJ112" s="1"/>
       <c r="AK112" s="1"/>
     </row>
-    <row r="113" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="113" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A113" s="3">
         <v>110</v>
       </c>
@@ -8254,7 +8264,7 @@
       <c r="AJ125" s="1"/>
       <c r="AK125" s="1"/>
     </row>
-    <row r="126" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="126" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A126" s="3">
         <v>123</v>
       </c>
@@ -8342,7 +8352,7 @@
       <c r="AJ127" s="1"/>
       <c r="AK127" s="1"/>
     </row>
-    <row r="128" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="128" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A128" s="3">
         <v>125</v>
       </c>
@@ -8434,7 +8444,7 @@
       <c r="AJ129" s="1"/>
       <c r="AK129" s="1"/>
     </row>
-    <row r="130" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="130" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A130" s="3">
         <v>127</v>
       </c>
@@ -9171,7 +9181,7 @@
       <c r="AJ146" s="1"/>
       <c r="AK146" s="1"/>
     </row>
-    <row r="147" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="147" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A147" s="3">
         <v>144</v>
       </c>
@@ -9201,7 +9211,9 @@
       <c r="W147" s="1"/>
       <c r="X147" s="1"/>
       <c r="Y147" s="1"/>
-      <c r="Z147" s="1"/>
+      <c r="Z147" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA147" s="1"/>
       <c r="AB147" s="1"/>
       <c r="AC147" s="1"/>
@@ -9214,7 +9226,7 @@
       <c r="AJ147" s="1"/>
       <c r="AK147" s="1"/>
     </row>
-    <row r="148" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="148" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A148" s="3">
         <v>145</v>
       </c>
@@ -9555,7 +9567,9 @@
       <c r="W155" s="1"/>
       <c r="X155" s="1"/>
       <c r="Y155" s="1"/>
-      <c r="Z155" s="1"/>
+      <c r="Z155" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA155" s="1"/>
       <c r="AB155" s="1"/>
       <c r="AC155" s="1"/>
@@ -9658,7 +9672,7 @@
       <c r="AJ157" s="1"/>
       <c r="AK157" s="1"/>
     </row>
-    <row r="158" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="158" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A158" s="3">
         <v>155</v>
       </c>
@@ -9692,7 +9706,9 @@
       <c r="W158" s="1"/>
       <c r="X158" s="1"/>
       <c r="Y158" s="1"/>
-      <c r="Z158" s="1"/>
+      <c r="Z158" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA158" s="1"/>
       <c r="AB158" s="1"/>
       <c r="AC158" s="1"/>
@@ -9705,7 +9721,7 @@
       <c r="AJ158" s="1"/>
       <c r="AK158" s="1"/>
     </row>
-    <row r="159" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="159" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A159" s="3">
         <v>156</v>
       </c>
@@ -9737,7 +9753,9 @@
       <c r="W159" s="1"/>
       <c r="X159" s="1"/>
       <c r="Y159" s="1"/>
-      <c r="Z159" s="1"/>
+      <c r="Z159" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA159" s="1"/>
       <c r="AB159" s="1"/>
       <c r="AC159" s="1"/>
@@ -9842,7 +9860,7 @@
       <c r="AJ161" s="1"/>
       <c r="AK161" s="1"/>
     </row>
-    <row r="162" spans="1:37" ht="15" hidden="1" customHeight="1">
+    <row r="162" spans="1:37" ht="15" customHeight="1">
       <c r="A162" s="3">
         <v>159</v>
       </c>
@@ -9874,7 +9892,9 @@
       <c r="W162" s="1"/>
       <c r="X162" s="1"/>
       <c r="Y162" s="1"/>
-      <c r="Z162" s="1"/>
+      <c r="Z162" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA162" s="1"/>
       <c r="AB162" s="1"/>
       <c r="AC162" s="1"/>
@@ -9887,7 +9907,7 @@
       <c r="AJ162" s="1"/>
       <c r="AK162" s="1"/>
     </row>
-    <row r="163" spans="1:37" ht="15" hidden="1" customHeight="1">
+    <row r="163" spans="1:37" ht="15" customHeight="1">
       <c r="A163" s="3">
         <v>160</v>
       </c>
@@ -9921,7 +9941,9 @@
       <c r="W163" s="1"/>
       <c r="X163" s="1"/>
       <c r="Y163" s="1"/>
-      <c r="Z163" s="1"/>
+      <c r="Z163" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA163" s="1"/>
       <c r="AB163" s="1"/>
       <c r="AC163" s="1"/>
@@ -10410,7 +10432,9 @@
       <c r="W174" s="1"/>
       <c r="X174" s="1"/>
       <c r="Y174" s="1"/>
-      <c r="Z174" s="1"/>
+      <c r="Z174" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA174" s="1"/>
       <c r="AB174" s="1"/>
       <c r="AC174" s="1"/>
@@ -10423,7 +10447,7 @@
       <c r="AJ174" s="1"/>
       <c r="AK174" s="1"/>
     </row>
-    <row r="175" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="175" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A175" s="3">
         <v>172</v>
       </c>
@@ -10459,7 +10483,9 @@
       <c r="W175" s="1"/>
       <c r="X175" s="1"/>
       <c r="Y175" s="1"/>
-      <c r="Z175" s="1"/>
+      <c r="Z175" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA175" s="1"/>
       <c r="AB175" s="1"/>
       <c r="AC175" s="1"/>
@@ -10512,7 +10538,9 @@
       <c r="W176" s="1"/>
       <c r="X176" s="1"/>
       <c r="Y176" s="1"/>
-      <c r="Z176" s="1"/>
+      <c r="Z176" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA176" s="1"/>
       <c r="AB176" s="1"/>
       <c r="AC176" s="1"/>
@@ -10811,7 +10839,7 @@
       <c r="AJ182" s="1"/>
       <c r="AK182" s="1"/>
     </row>
-    <row r="183" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="183" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A183" s="3">
         <v>180</v>
       </c>
@@ -10849,7 +10877,9 @@
         <v>157</v>
       </c>
       <c r="Y183" s="1"/>
-      <c r="Z183" s="1"/>
+      <c r="Z183" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA183" s="1"/>
       <c r="AB183" s="1"/>
       <c r="AC183" s="1"/>
@@ -10997,12 +11027,8 @@
       <c r="X186" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="Y186" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z186" s="1" t="s">
-        <v>157</v>
-      </c>
+      <c r="Y186" s="1"/>
+      <c r="Z186" s="1"/>
       <c r="AA186" s="1"/>
       <c r="AB186" s="1"/>
       <c r="AC186" s="1"/>
@@ -11050,12 +11076,8 @@
       <c r="X187" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="Y187" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z187" s="1" t="s">
-        <v>157</v>
-      </c>
+      <c r="Y187" s="1"/>
+      <c r="Z187" s="1"/>
       <c r="AA187" s="1"/>
       <c r="AB187" s="1"/>
       <c r="AC187" s="1"/>
@@ -11105,12 +11127,8 @@
       <c r="X188" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="Y188" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z188" s="1" t="s">
-        <v>157</v>
-      </c>
+      <c r="Y188" s="1"/>
+      <c r="Z188" s="1"/>
       <c r="AA188" s="1"/>
       <c r="AB188" s="1"/>
       <c r="AC188" s="1"/>
@@ -11158,12 +11176,8 @@
       <c r="X189" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="Y189" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z189" s="1" t="s">
-        <v>157</v>
-      </c>
+      <c r="Y189" s="1"/>
+      <c r="Z189" s="1"/>
       <c r="AA189" s="1"/>
       <c r="AB189" s="1"/>
       <c r="AC189" s="1"/>
@@ -11211,12 +11225,8 @@
       <c r="X190" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="Y190" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z190" s="1" t="s">
-        <v>157</v>
-      </c>
+      <c r="Y190" s="1"/>
+      <c r="Z190" s="1"/>
       <c r="AA190" s="1"/>
       <c r="AB190" s="1"/>
       <c r="AC190" s="1"/>
@@ -11264,12 +11274,8 @@
       <c r="X191" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="Y191" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z191" s="1" t="s">
-        <v>157</v>
-      </c>
+      <c r="Y191" s="1"/>
+      <c r="Z191" s="1"/>
       <c r="AA191" s="1"/>
       <c r="AB191" s="1"/>
       <c r="AC191" s="1"/>
@@ -11603,7 +11609,7 @@
       <c r="AJ198" s="1"/>
       <c r="AK198" s="1"/>
     </row>
-    <row r="199" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="199" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A199" s="3">
         <v>196</v>
       </c>
@@ -11637,7 +11643,9 @@
         <v>157</v>
       </c>
       <c r="Y199" s="1"/>
-      <c r="Z199" s="1"/>
+      <c r="Z199" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA199" s="1"/>
       <c r="AB199" s="1"/>
       <c r="AC199" s="1"/>
@@ -12286,7 +12294,7 @@
       <c r="AJ213" s="1"/>
       <c r="AK213" s="1"/>
     </row>
-    <row r="214" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="214" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A214" s="3">
         <v>211</v>
       </c>
@@ -12318,7 +12326,9 @@
       <c r="W214" s="1"/>
       <c r="X214" s="1"/>
       <c r="Y214" s="1"/>
-      <c r="Z214" s="1"/>
+      <c r="Z214" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA214" s="1"/>
       <c r="AB214" s="1"/>
       <c r="AC214" s="1"/>
@@ -12376,7 +12386,7 @@
       <c r="AJ215" s="1"/>
       <c r="AK215" s="1"/>
     </row>
-    <row r="216" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="216" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A216" s="3">
         <v>213</v>
       </c>
@@ -12412,7 +12422,9 @@
         <v>157</v>
       </c>
       <c r="Y216" s="1"/>
-      <c r="Z216" s="1"/>
+      <c r="Z216" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA216" s="1"/>
       <c r="AB216" s="1"/>
       <c r="AC216" s="1"/>
@@ -12425,7 +12437,7 @@
       <c r="AJ216" s="1"/>
       <c r="AK216" s="1"/>
     </row>
-    <row r="217" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="217" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A217" s="3">
         <v>214</v>
       </c>
@@ -12461,7 +12473,9 @@
         <v>157</v>
       </c>
       <c r="Y217" s="1"/>
-      <c r="Z217" s="1"/>
+      <c r="Z217" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA217" s="1"/>
       <c r="AB217" s="1"/>
       <c r="AC217" s="1"/>
@@ -12474,7 +12488,7 @@
       <c r="AJ217" s="1"/>
       <c r="AK217" s="1"/>
     </row>
-    <row r="218" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="218" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A218" s="3">
         <v>215</v>
       </c>
@@ -12510,7 +12524,9 @@
         <v>157</v>
       </c>
       <c r="Y218" s="1"/>
-      <c r="Z218" s="1"/>
+      <c r="Z218" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA218" s="1"/>
       <c r="AB218" s="1"/>
       <c r="AC218" s="1"/>
@@ -13127,7 +13143,7 @@
       <c r="AJ232" s="1"/>
       <c r="AK232" s="1"/>
     </row>
-    <row r="233" spans="1:37" hidden="1">
+    <row r="233" spans="1:37">
       <c r="A233" s="3">
         <v>230</v>
       </c>
@@ -13159,7 +13175,9 @@
       <c r="W233" s="1"/>
       <c r="X233" s="1"/>
       <c r="Y233" s="1"/>
-      <c r="Z233" s="1"/>
+      <c r="Z233" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA233" s="1"/>
       <c r="AB233" s="1"/>
       <c r="AC233" s="1"/>
@@ -13215,7 +13233,7 @@
       <c r="AJ234" s="1"/>
       <c r="AK234" s="1"/>
     </row>
-    <row r="235" spans="1:37" hidden="1">
+    <row r="235" spans="1:37">
       <c r="A235" s="3">
         <v>232</v>
       </c>
@@ -13247,7 +13265,9 @@
       <c r="W235" s="1"/>
       <c r="X235" s="1"/>
       <c r="Y235" s="1"/>
-      <c r="Z235" s="1"/>
+      <c r="Z235" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA235" s="1"/>
       <c r="AB235" s="1"/>
       <c r="AC235" s="1"/>
@@ -13786,7 +13806,7 @@
       <c r="AJ247" s="1"/>
       <c r="AK247" s="1"/>
     </row>
-    <row r="248" spans="1:37" hidden="1">
+    <row r="248" spans="1:37">
       <c r="A248" s="3">
         <v>245</v>
       </c>
@@ -13818,7 +13838,9 @@
         <v>157</v>
       </c>
       <c r="Y248" s="1"/>
-      <c r="Z248" s="1"/>
+      <c r="Z248" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA248" s="1"/>
       <c r="AB248" s="1"/>
       <c r="AC248" s="1"/>
@@ -14132,7 +14154,7 @@
       <c r="AJ255" s="1"/>
       <c r="AK255" s="1"/>
     </row>
-    <row r="256" spans="1:37" hidden="1">
+    <row r="256" spans="1:37">
       <c r="A256" s="3">
         <v>253</v>
       </c>
@@ -14162,7 +14184,9 @@
       <c r="W256" s="1"/>
       <c r="X256" s="1"/>
       <c r="Y256" s="1"/>
-      <c r="Z256" s="1"/>
+      <c r="Z256" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA256" s="1"/>
       <c r="AB256" s="1"/>
       <c r="AC256" s="1"/>
@@ -15161,7 +15185,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A3:AB280" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="16">
+    <filterColumn colId="25">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA9268A-6509-4203-9C71-60DA9F994899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251CDEF1-C931-41ED-AE45-8BD565FECDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4770" yWindow="0" windowWidth="14770" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="リスト" sheetId="1" r:id="rId1"/>
@@ -5571,7 +5571,7 @@
       <c r="AJ64" s="1"/>
       <c r="AK64" s="1"/>
     </row>
-    <row r="65" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="65" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A65" s="3">
         <v>62</v>
       </c>
@@ -5603,7 +5603,9 @@
         <v>157</v>
       </c>
       <c r="Y65" s="1"/>
-      <c r="Z65" s="1"/>
+      <c r="Z65" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
@@ -13265,9 +13267,7 @@
       <c r="W235" s="1"/>
       <c r="X235" s="1"/>
       <c r="Y235" s="1"/>
-      <c r="Z235" s="1" t="s">
-        <v>157</v>
-      </c>
+      <c r="Z235" s="1"/>
       <c r="AA235" s="1"/>
       <c r="AB235" s="1"/>
       <c r="AC235" s="1"/>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\副業\LINE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251CDEF1-C931-41ED-AE45-8BD565FECDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE799A4-4DD2-4970-BB56-2E010BD53034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4770" yWindow="0" windowWidth="14770" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="リスト" sheetId="1" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="407">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -1933,6 +1933,22 @@
     <rPh sb="0" eb="1">
       <t>イヌ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おかえり</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>今から帰る</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>はい</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ほ～っ</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2670,19 +2686,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AK280"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
-    <col min="1" max="1" width="3.4140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.4140625" style="24" customWidth="1"/>
+    <col min="1" max="1" width="3.4375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.4375" style="24" customWidth="1"/>
     <col min="3" max="3" width="33.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="3.58203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="2.58203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="37" width="3.58203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="3.5625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2.5625" bestFit="1" customWidth="1"/>
+    <col min="11" max="37" width="3.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="22.5">
+    <row r="1" spans="1:37" ht="22.9">
       <c r="A1" s="35"/>
       <c r="B1" s="39" t="s">
         <v>273</v>
@@ -2714,7 +2729,7 @@
       <c r="W1" s="38"/>
       <c r="X1" s="38"/>
     </row>
-    <row r="2" spans="1:37" ht="22.5">
+    <row r="2" spans="1:37" ht="22.9">
       <c r="A2" s="36"/>
       <c r="B2" s="40"/>
       <c r="C2" s="33"/>
@@ -2763,7 +2778,7 @@
       <c r="AJ2" s="5"/>
       <c r="AK2" s="5"/>
     </row>
-    <row r="3" spans="1:37" s="13" customFormat="1" ht="109.5" thickBot="1">
+    <row r="3" spans="1:37" s="13" customFormat="1" ht="106.9" thickBot="1">
       <c r="A3" s="37"/>
       <c r="B3" s="41"/>
       <c r="C3" s="34"/>
@@ -2866,7 +2881,7 @@
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
     </row>
-    <row r="4" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" thickTop="1">
+    <row r="4" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -2921,7 +2936,7 @@
       <c r="AJ4" s="1"/>
       <c r="AK4" s="1"/>
     </row>
-    <row r="5" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickTop="1">
+    <row r="5" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -2973,12 +2988,14 @@
       <c r="AE5" s="29"/>
       <c r="AF5" s="1"/>
       <c r="AG5" s="29"/>
-      <c r="AH5" s="1"/>
+      <c r="AH5" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="1"/>
     </row>
-    <row r="6" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="6" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -3020,12 +3037,14 @@
       <c r="AE6" s="29"/>
       <c r="AF6" s="1"/>
       <c r="AG6" s="29"/>
-      <c r="AH6" s="1"/>
+      <c r="AH6" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI6" s="1"/>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="1"/>
     </row>
-    <row r="7" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="7" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -3068,7 +3087,7 @@
       <c r="AJ7" s="1"/>
       <c r="AK7" s="1"/>
     </row>
-    <row r="8" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="8" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -3113,7 +3132,7 @@
       <c r="AJ8" s="1"/>
       <c r="AK8" s="1"/>
     </row>
-    <row r="9" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="9" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -3156,7 +3175,7 @@
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
     </row>
-    <row r="10" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="10" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -3199,7 +3218,7 @@
       <c r="AJ10" s="1"/>
       <c r="AK10" s="1"/>
     </row>
-    <row r="11" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="11" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -3246,7 +3265,7 @@
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
     </row>
-    <row r="12" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="12" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -3289,7 +3308,7 @@
       <c r="AJ12" s="1"/>
       <c r="AK12" s="1"/>
     </row>
-    <row r="13" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="13" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -3332,7 +3351,7 @@
       <c r="AJ13" s="1"/>
       <c r="AK13" s="1"/>
     </row>
-    <row r="14" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="14" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -3375,7 +3394,7 @@
       <c r="AJ14" s="1"/>
       <c r="AK14" s="1"/>
     </row>
-    <row r="15" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="15" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -3418,7 +3437,7 @@
       <c r="AJ15" s="1"/>
       <c r="AK15" s="1"/>
     </row>
-    <row r="16" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="16" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -3461,7 +3480,7 @@
       <c r="AJ16" s="1"/>
       <c r="AK16" s="1"/>
     </row>
-    <row r="17" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="17" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -3504,7 +3523,7 @@
       <c r="AJ17" s="1"/>
       <c r="AK17" s="1"/>
     </row>
-    <row r="18" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="18" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -3549,7 +3568,7 @@
       <c r="AJ18" s="1"/>
       <c r="AK18" s="1"/>
     </row>
-    <row r="19" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="19" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -3592,7 +3611,7 @@
       <c r="AJ19" s="1"/>
       <c r="AK19" s="1"/>
     </row>
-    <row r="20" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="20" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -3635,7 +3654,7 @@
       <c r="AJ20" s="1"/>
       <c r="AK20" s="1"/>
     </row>
-    <row r="21" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="21" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -3673,12 +3692,14 @@
       <c r="AE21" s="29"/>
       <c r="AF21" s="1"/>
       <c r="AG21" s="29"/>
-      <c r="AH21" s="1"/>
+      <c r="AH21" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
       <c r="AK21" s="1"/>
     </row>
-    <row r="22" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="22" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -3723,7 +3744,7 @@
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1"/>
     </row>
-    <row r="23" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="23" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -3813,7 +3834,7 @@
       <c r="AJ24" s="1"/>
       <c r="AK24" s="1"/>
     </row>
-    <row r="25" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="25" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -3858,7 +3879,7 @@
       <c r="AJ25" s="1"/>
       <c r="AK25" s="1"/>
     </row>
-    <row r="26" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="26" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -3901,7 +3922,7 @@
       <c r="AJ26" s="1"/>
       <c r="AK26" s="1"/>
     </row>
-    <row r="27" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="27" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -3946,7 +3967,7 @@
       <c r="AJ27" s="1"/>
       <c r="AK27" s="1"/>
     </row>
-    <row r="28" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="28" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -3989,7 +4010,7 @@
       <c r="AJ28" s="1"/>
       <c r="AK28" s="1"/>
     </row>
-    <row r="29" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="29" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -4032,7 +4053,7 @@
       <c r="AJ29" s="1"/>
       <c r="AK29" s="1"/>
     </row>
-    <row r="30" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="30" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -4077,7 +4098,7 @@
       <c r="AJ30" s="1"/>
       <c r="AK30" s="1"/>
     </row>
-    <row r="31" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="31" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -4121,12 +4142,14 @@
       <c r="AE31" s="29"/>
       <c r="AF31" s="1"/>
       <c r="AG31" s="29"/>
-      <c r="AH31" s="1"/>
+      <c r="AH31" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
       <c r="AK31" s="1"/>
     </row>
-    <row r="32" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="32" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -4171,7 +4194,7 @@
       <c r="AJ32" s="1"/>
       <c r="AK32" s="1"/>
     </row>
-    <row r="33" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="33" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -4214,7 +4237,7 @@
       <c r="AJ33" s="1"/>
       <c r="AK33" s="1"/>
     </row>
-    <row r="34" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="34" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -4257,7 +4280,7 @@
       <c r="AJ34" s="1"/>
       <c r="AK34" s="1"/>
     </row>
-    <row r="35" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="35" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -4300,7 +4323,7 @@
       <c r="AJ35" s="1"/>
       <c r="AK35" s="1"/>
     </row>
-    <row r="36" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="36" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -4343,7 +4366,7 @@
       <c r="AJ36" s="1"/>
       <c r="AK36" s="1"/>
     </row>
-    <row r="37" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="37" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -4386,7 +4409,7 @@
       <c r="AJ37" s="1"/>
       <c r="AK37" s="1"/>
     </row>
-    <row r="38" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="38" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -4429,7 +4452,7 @@
       <c r="AJ38" s="1"/>
       <c r="AK38" s="1"/>
     </row>
-    <row r="39" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="39" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -4474,7 +4497,7 @@
       <c r="AJ39" s="1"/>
       <c r="AK39" s="1"/>
     </row>
-    <row r="40" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="40" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -4519,7 +4542,7 @@
       <c r="AJ40" s="1"/>
       <c r="AK40" s="1"/>
     </row>
-    <row r="41" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="41" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -4564,7 +4587,7 @@
       <c r="AJ41" s="1"/>
       <c r="AK41" s="1"/>
     </row>
-    <row r="42" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="42" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -4607,7 +4630,7 @@
       <c r="AJ42" s="1"/>
       <c r="AK42" s="1"/>
     </row>
-    <row r="43" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="43" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -4652,7 +4675,7 @@
       <c r="AJ43" s="1"/>
       <c r="AK43" s="1"/>
     </row>
-    <row r="44" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="44" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -4695,7 +4718,7 @@
       <c r="AJ44" s="1"/>
       <c r="AK44" s="1"/>
     </row>
-    <row r="45" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="45" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -4738,7 +4761,7 @@
       <c r="AJ45" s="1"/>
       <c r="AK45" s="1"/>
     </row>
-    <row r="46" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="46" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -4781,7 +4804,7 @@
       <c r="AJ46" s="1"/>
       <c r="AK46" s="1"/>
     </row>
-    <row r="47" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="47" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -4824,7 +4847,7 @@
       <c r="AJ47" s="1"/>
       <c r="AK47" s="1"/>
     </row>
-    <row r="48" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="48" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -4864,12 +4887,14 @@
       <c r="AE48" s="29"/>
       <c r="AF48" s="1"/>
       <c r="AG48" s="29"/>
-      <c r="AH48" s="1"/>
+      <c r="AH48" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI48" s="1"/>
       <c r="AJ48" s="1"/>
       <c r="AK48" s="1"/>
     </row>
-    <row r="49" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="49" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -4912,7 +4937,7 @@
       <c r="AJ49" s="1"/>
       <c r="AK49" s="1"/>
     </row>
-    <row r="50" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="50" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -4957,7 +4982,7 @@
       <c r="AJ50" s="1"/>
       <c r="AK50" s="1"/>
     </row>
-    <row r="51" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="51" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -5000,7 +5025,7 @@
       <c r="AJ51" s="1"/>
       <c r="AK51" s="1"/>
     </row>
-    <row r="52" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="52" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -5043,7 +5068,7 @@
       <c r="AJ52" s="1"/>
       <c r="AK52" s="1"/>
     </row>
-    <row r="53" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="53" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -5086,7 +5111,7 @@
       <c r="AJ53" s="1"/>
       <c r="AK53" s="1"/>
     </row>
-    <row r="54" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="54" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A54" s="3">
         <v>51</v>
       </c>
@@ -5131,7 +5156,7 @@
       <c r="AJ54" s="1"/>
       <c r="AK54" s="1"/>
     </row>
-    <row r="55" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="55" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -5176,7 +5201,7 @@
       <c r="AJ55" s="1"/>
       <c r="AK55" s="1"/>
     </row>
-    <row r="56" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="56" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -5264,7 +5289,7 @@
       <c r="AJ57" s="1"/>
       <c r="AK57" s="1"/>
     </row>
-    <row r="58" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="58" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -5307,7 +5332,7 @@
       <c r="AJ58" s="1"/>
       <c r="AK58" s="1"/>
     </row>
-    <row r="59" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="59" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -5350,7 +5375,7 @@
       <c r="AJ59" s="1"/>
       <c r="AK59" s="1"/>
     </row>
-    <row r="60" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="60" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -5393,7 +5418,7 @@
       <c r="AJ60" s="1"/>
       <c r="AK60" s="1"/>
     </row>
-    <row r="61" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="61" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -5436,7 +5461,7 @@
       <c r="AJ61" s="1"/>
       <c r="AK61" s="1"/>
     </row>
-    <row r="62" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="62" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -5479,7 +5504,7 @@
       <c r="AJ62" s="1"/>
       <c r="AK62" s="1"/>
     </row>
-    <row r="63" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="63" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A63" s="3">
         <v>60</v>
       </c>
@@ -5524,7 +5549,7 @@
       <c r="AJ63" s="1"/>
       <c r="AK63" s="1"/>
     </row>
-    <row r="64" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="64" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A64" s="3">
         <v>61</v>
       </c>
@@ -5566,7 +5591,9 @@
       <c r="AE64" s="29"/>
       <c r="AF64" s="1"/>
       <c r="AG64" s="29"/>
-      <c r="AH64" s="1"/>
+      <c r="AH64" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI64" s="1"/>
       <c r="AJ64" s="1"/>
       <c r="AK64" s="1"/>
@@ -5618,7 +5645,7 @@
       <c r="AJ65" s="1"/>
       <c r="AK65" s="1"/>
     </row>
-    <row r="66" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="66" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A66" s="3">
         <v>63</v>
       </c>
@@ -5661,7 +5688,7 @@
       <c r="AJ66" s="1"/>
       <c r="AK66" s="1"/>
     </row>
-    <row r="67" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="67" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A67" s="3">
         <v>64</v>
       </c>
@@ -5755,7 +5782,7 @@
       <c r="AJ68" s="1"/>
       <c r="AK68" s="1"/>
     </row>
-    <row r="69" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="69" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A69" s="3">
         <v>66</v>
       </c>
@@ -5802,7 +5829,7 @@
       <c r="AJ69" s="1"/>
       <c r="AK69" s="1"/>
     </row>
-    <row r="70" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="70" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A70" s="3">
         <v>67</v>
       </c>
@@ -5847,7 +5874,7 @@
       <c r="AJ70" s="1"/>
       <c r="AK70" s="1"/>
     </row>
-    <row r="71" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="71" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A71" s="3">
         <v>68</v>
       </c>
@@ -5892,7 +5919,7 @@
       <c r="AJ71" s="1"/>
       <c r="AK71" s="1"/>
     </row>
-    <row r="72" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="72" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A72" s="3">
         <v>69</v>
       </c>
@@ -5935,7 +5962,7 @@
       <c r="AJ72" s="1"/>
       <c r="AK72" s="1"/>
     </row>
-    <row r="73" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="73" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A73" s="3">
         <v>70</v>
       </c>
@@ -5978,7 +6005,7 @@
       <c r="AJ73" s="1"/>
       <c r="AK73" s="1"/>
     </row>
-    <row r="74" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="74" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A74" s="3">
         <v>71</v>
       </c>
@@ -6021,7 +6048,7 @@
       <c r="AJ74" s="1"/>
       <c r="AK74" s="1"/>
     </row>
-    <row r="75" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="75" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A75" s="3">
         <v>72</v>
       </c>
@@ -6108,12 +6135,14 @@
       <c r="AE76" s="29"/>
       <c r="AF76" s="1"/>
       <c r="AG76" s="29"/>
-      <c r="AH76" s="1"/>
+      <c r="AH76" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI76" s="1"/>
       <c r="AJ76" s="1"/>
       <c r="AK76" s="1"/>
     </row>
-    <row r="77" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="77" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A77" s="3">
         <v>74</v>
       </c>
@@ -6158,7 +6187,7 @@
       <c r="AJ77" s="1"/>
       <c r="AK77" s="1"/>
     </row>
-    <row r="78" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="78" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A78" s="3">
         <v>75</v>
       </c>
@@ -6203,7 +6232,7 @@
       <c r="AJ78" s="1"/>
       <c r="AK78" s="1"/>
     </row>
-    <row r="79" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="79" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A79" s="3">
         <v>76</v>
       </c>
@@ -6248,7 +6277,7 @@
       <c r="AJ79" s="1"/>
       <c r="AK79" s="1"/>
     </row>
-    <row r="80" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="80" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A80" s="3">
         <v>77</v>
       </c>
@@ -6293,7 +6322,7 @@
       <c r="AJ80" s="1"/>
       <c r="AK80" s="1"/>
     </row>
-    <row r="81" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="81" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A81" s="3">
         <v>78</v>
       </c>
@@ -6340,7 +6369,7 @@
       <c r="AJ81" s="1"/>
       <c r="AK81" s="1"/>
     </row>
-    <row r="82" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="82" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A82" s="3">
         <v>79</v>
       </c>
@@ -6387,7 +6416,7 @@
       <c r="AJ82" s="1"/>
       <c r="AK82" s="1"/>
     </row>
-    <row r="83" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="83" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A83" s="3">
         <v>80</v>
       </c>
@@ -6434,7 +6463,7 @@
       <c r="AJ83" s="1"/>
       <c r="AK83" s="1"/>
     </row>
-    <row r="84" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="84" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A84" s="3">
         <v>81</v>
       </c>
@@ -6479,7 +6508,7 @@
       <c r="AJ84" s="1"/>
       <c r="AK84" s="1"/>
     </row>
-    <row r="85" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="85" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A85" s="3">
         <v>82</v>
       </c>
@@ -6522,7 +6551,7 @@
       <c r="AJ85" s="1"/>
       <c r="AK85" s="1"/>
     </row>
-    <row r="86" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="86" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A86" s="3">
         <v>83</v>
       </c>
@@ -6565,7 +6594,7 @@
       <c r="AJ86" s="1"/>
       <c r="AK86" s="1"/>
     </row>
-    <row r="87" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="87" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A87" s="3">
         <v>84</v>
       </c>
@@ -6608,7 +6637,7 @@
       <c r="AJ87" s="1"/>
       <c r="AK87" s="1"/>
     </row>
-    <row r="88" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="88" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A88" s="3">
         <v>85</v>
       </c>
@@ -6648,12 +6677,14 @@
       <c r="AE88" s="29"/>
       <c r="AF88" s="1"/>
       <c r="AG88" s="29"/>
-      <c r="AH88" s="1"/>
+      <c r="AH88" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI88" s="1"/>
       <c r="AJ88" s="1"/>
       <c r="AK88" s="1"/>
     </row>
-    <row r="89" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="89" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A89" s="3">
         <v>86</v>
       </c>
@@ -6696,7 +6727,7 @@
       <c r="AJ89" s="1"/>
       <c r="AK89" s="1"/>
     </row>
-    <row r="90" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="90" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A90" s="3">
         <v>87</v>
       </c>
@@ -6739,7 +6770,7 @@
       <c r="AJ90" s="1"/>
       <c r="AK90" s="1"/>
     </row>
-    <row r="91" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="91" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A91" s="3">
         <v>88</v>
       </c>
@@ -6784,7 +6815,7 @@
       <c r="AJ91" s="1"/>
       <c r="AK91" s="1"/>
     </row>
-    <row r="92" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="92" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A92" s="3">
         <v>89</v>
       </c>
@@ -6829,7 +6860,7 @@
       <c r="AJ92" s="1"/>
       <c r="AK92" s="1"/>
     </row>
-    <row r="93" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="93" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A93" s="3">
         <v>90</v>
       </c>
@@ -6872,7 +6903,7 @@
       <c r="AJ93" s="1"/>
       <c r="AK93" s="1"/>
     </row>
-    <row r="94" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="94" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A94" s="3">
         <v>91</v>
       </c>
@@ -6915,7 +6946,7 @@
       <c r="AJ94" s="1"/>
       <c r="AK94" s="1"/>
     </row>
-    <row r="95" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="95" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A95" s="3">
         <v>92</v>
       </c>
@@ -6958,7 +6989,7 @@
       <c r="AJ95" s="1"/>
       <c r="AK95" s="1"/>
     </row>
-    <row r="96" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="96" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A96" s="3">
         <v>93</v>
       </c>
@@ -7001,7 +7032,7 @@
       <c r="AJ96" s="1"/>
       <c r="AK96" s="1"/>
     </row>
-    <row r="97" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="97" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A97" s="3">
         <v>94</v>
       </c>
@@ -7044,7 +7075,7 @@
       <c r="AJ97" s="1"/>
       <c r="AK97" s="1"/>
     </row>
-    <row r="98" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="98" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A98" s="3">
         <v>95</v>
       </c>
@@ -7089,7 +7120,7 @@
       <c r="AJ98" s="1"/>
       <c r="AK98" s="1"/>
     </row>
-    <row r="99" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="99" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A99" s="3">
         <v>96</v>
       </c>
@@ -7132,7 +7163,7 @@
       <c r="AJ99" s="1"/>
       <c r="AK99" s="1"/>
     </row>
-    <row r="100" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="100" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A100" s="3">
         <v>97</v>
       </c>
@@ -7175,7 +7206,7 @@
       <c r="AJ100" s="1"/>
       <c r="AK100" s="1"/>
     </row>
-    <row r="101" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="101" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A101" s="3">
         <v>98</v>
       </c>
@@ -7218,7 +7249,7 @@
       <c r="AJ101" s="1"/>
       <c r="AK101" s="1"/>
     </row>
-    <row r="102" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="102" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A102" s="3">
         <v>99</v>
       </c>
@@ -7261,7 +7292,7 @@
       <c r="AJ102" s="1"/>
       <c r="AK102" s="1"/>
     </row>
-    <row r="103" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="103" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A103" s="3">
         <v>100</v>
       </c>
@@ -7304,7 +7335,7 @@
       <c r="AJ103" s="1"/>
       <c r="AK103" s="1"/>
     </row>
-    <row r="104" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="104" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A104" s="3">
         <v>101</v>
       </c>
@@ -7347,7 +7378,7 @@
       <c r="AJ104" s="1"/>
       <c r="AK104" s="1"/>
     </row>
-    <row r="105" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="105" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A105" s="3">
         <v>102</v>
       </c>
@@ -7392,7 +7423,7 @@
       <c r="AJ105" s="1"/>
       <c r="AK105" s="1"/>
     </row>
-    <row r="106" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="106" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A106" s="3">
         <v>103</v>
       </c>
@@ -7435,7 +7466,7 @@
       <c r="AJ106" s="1"/>
       <c r="AK106" s="1"/>
     </row>
-    <row r="107" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="107" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A107" s="3">
         <v>104</v>
       </c>
@@ -7480,7 +7511,7 @@
       <c r="AJ107" s="1"/>
       <c r="AK107" s="1"/>
     </row>
-    <row r="108" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="108" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A108" s="3">
         <v>105</v>
       </c>
@@ -7523,7 +7554,7 @@
       <c r="AJ108" s="1"/>
       <c r="AK108" s="1"/>
     </row>
-    <row r="109" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="109" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A109" s="3">
         <v>106</v>
       </c>
@@ -7568,7 +7599,7 @@
       <c r="AJ109" s="1"/>
       <c r="AK109" s="1"/>
     </row>
-    <row r="110" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="110" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A110" s="3">
         <v>107</v>
       </c>
@@ -7611,7 +7642,7 @@
       <c r="AJ110" s="1"/>
       <c r="AK110" s="1"/>
     </row>
-    <row r="111" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="111" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A111" s="3">
         <v>108</v>
       </c>
@@ -7654,7 +7685,7 @@
       <c r="AJ111" s="1"/>
       <c r="AK111" s="1"/>
     </row>
-    <row r="112" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="112" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A112" s="3">
         <v>109</v>
       </c>
@@ -7703,7 +7734,7 @@
       <c r="AJ112" s="1"/>
       <c r="AK112" s="1"/>
     </row>
-    <row r="113" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="113" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A113" s="3">
         <v>110</v>
       </c>
@@ -7748,7 +7779,7 @@
       <c r="AJ113" s="1"/>
       <c r="AK113" s="1"/>
     </row>
-    <row r="114" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="114" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A114" s="3">
         <v>111</v>
       </c>
@@ -7786,12 +7817,14 @@
       <c r="AE114" s="29"/>
       <c r="AF114" s="1"/>
       <c r="AG114" s="29"/>
-      <c r="AH114" s="1"/>
+      <c r="AH114" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI114" s="1"/>
       <c r="AJ114" s="1"/>
       <c r="AK114" s="1"/>
     </row>
-    <row r="115" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="115" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A115" s="3">
         <v>112</v>
       </c>
@@ -7836,7 +7869,7 @@
       <c r="AJ115" s="1"/>
       <c r="AK115" s="1"/>
     </row>
-    <row r="116" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="116" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A116" s="3">
         <v>113</v>
       </c>
@@ -7879,7 +7912,7 @@
       <c r="AJ116" s="1"/>
       <c r="AK116" s="1"/>
     </row>
-    <row r="117" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="117" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A117" s="3">
         <v>114</v>
       </c>
@@ -7922,7 +7955,7 @@
       <c r="AJ117" s="1"/>
       <c r="AK117" s="1"/>
     </row>
-    <row r="118" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="118" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A118" s="3">
         <v>115</v>
       </c>
@@ -7965,7 +7998,7 @@
       <c r="AJ118" s="1"/>
       <c r="AK118" s="1"/>
     </row>
-    <row r="119" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="119" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A119" s="3">
         <v>116</v>
       </c>
@@ -8008,7 +8041,7 @@
       <c r="AJ119" s="1"/>
       <c r="AK119" s="1"/>
     </row>
-    <row r="120" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="120" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A120" s="3">
         <v>117</v>
       </c>
@@ -8051,7 +8084,7 @@
       <c r="AJ120" s="1"/>
       <c r="AK120" s="1"/>
     </row>
-    <row r="121" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="121" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A121" s="3">
         <v>118</v>
       </c>
@@ -8094,7 +8127,7 @@
       <c r="AJ121" s="1"/>
       <c r="AK121" s="1"/>
     </row>
-    <row r="122" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="122" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A122" s="3">
         <v>119</v>
       </c>
@@ -8137,7 +8170,7 @@
       <c r="AJ122" s="1"/>
       <c r="AK122" s="1"/>
     </row>
-    <row r="123" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="123" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A123" s="3">
         <v>120</v>
       </c>
@@ -8180,7 +8213,7 @@
       <c r="AJ123" s="1"/>
       <c r="AK123" s="1"/>
     </row>
-    <row r="124" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="124" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A124" s="3">
         <v>121</v>
       </c>
@@ -8223,7 +8256,7 @@
       <c r="AJ124" s="1"/>
       <c r="AK124" s="1"/>
     </row>
-    <row r="125" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="125" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A125" s="3">
         <v>122</v>
       </c>
@@ -8266,7 +8299,7 @@
       <c r="AJ125" s="1"/>
       <c r="AK125" s="1"/>
     </row>
-    <row r="126" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="126" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A126" s="3">
         <v>123</v>
       </c>
@@ -8311,7 +8344,7 @@
       <c r="AJ126" s="1"/>
       <c r="AK126" s="1"/>
     </row>
-    <row r="127" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="127" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A127" s="3">
         <v>124</v>
       </c>
@@ -8354,7 +8387,7 @@
       <c r="AJ127" s="1"/>
       <c r="AK127" s="1"/>
     </row>
-    <row r="128" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="128" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A128" s="3">
         <v>125</v>
       </c>
@@ -8401,7 +8434,7 @@
       <c r="AJ128" s="1"/>
       <c r="AK128" s="1"/>
     </row>
-    <row r="129" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="129" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A129" s="3">
         <v>126</v>
       </c>
@@ -8446,7 +8479,7 @@
       <c r="AJ129" s="1"/>
       <c r="AK129" s="1"/>
     </row>
-    <row r="130" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="130" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A130" s="3">
         <v>127</v>
       </c>
@@ -8488,12 +8521,14 @@
       <c r="AE130" s="29"/>
       <c r="AF130" s="1"/>
       <c r="AG130" s="29"/>
-      <c r="AH130" s="1"/>
+      <c r="AH130" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI130" s="1"/>
       <c r="AJ130" s="1"/>
       <c r="AK130" s="1"/>
     </row>
-    <row r="131" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="131" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A131" s="3">
         <v>128</v>
       </c>
@@ -8538,7 +8573,7 @@
       <c r="AJ131" s="1"/>
       <c r="AK131" s="1"/>
     </row>
-    <row r="132" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="132" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A132" s="3">
         <v>129</v>
       </c>
@@ -8576,12 +8611,14 @@
       <c r="AE132" s="29"/>
       <c r="AF132" s="1"/>
       <c r="AG132" s="29"/>
-      <c r="AH132" s="1"/>
+      <c r="AH132" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI132" s="1"/>
       <c r="AJ132" s="1"/>
       <c r="AK132" s="1"/>
     </row>
-    <row r="133" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="133" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A133" s="3">
         <v>130</v>
       </c>
@@ -8624,7 +8661,7 @@
       <c r="AJ133" s="1"/>
       <c r="AK133" s="1"/>
     </row>
-    <row r="134" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="134" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A134" s="3">
         <v>131</v>
       </c>
@@ -8667,7 +8704,7 @@
       <c r="AJ134" s="1"/>
       <c r="AK134" s="1"/>
     </row>
-    <row r="135" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="135" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A135" s="3">
         <v>132</v>
       </c>
@@ -8710,7 +8747,7 @@
       <c r="AJ135" s="1"/>
       <c r="AK135" s="1"/>
     </row>
-    <row r="136" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="136" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A136" s="3">
         <v>133</v>
       </c>
@@ -8748,12 +8785,14 @@
       <c r="AE136" s="29"/>
       <c r="AF136" s="1"/>
       <c r="AG136" s="29"/>
-      <c r="AH136" s="1"/>
+      <c r="AH136" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI136" s="1"/>
       <c r="AJ136" s="1"/>
       <c r="AK136" s="1"/>
     </row>
-    <row r="137" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="137" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A137" s="3">
         <v>134</v>
       </c>
@@ -8796,7 +8835,7 @@
       <c r="AJ137" s="1"/>
       <c r="AK137" s="1"/>
     </row>
-    <row r="138" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="138" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A138" s="3">
         <v>135</v>
       </c>
@@ -8834,12 +8873,14 @@
       <c r="AE138" s="29"/>
       <c r="AF138" s="1"/>
       <c r="AG138" s="29"/>
-      <c r="AH138" s="1"/>
+      <c r="AH138" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI138" s="1"/>
       <c r="AJ138" s="1"/>
       <c r="AK138" s="1"/>
     </row>
-    <row r="139" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="139" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A139" s="3">
         <v>136</v>
       </c>
@@ -8882,7 +8923,7 @@
       <c r="AJ139" s="1"/>
       <c r="AK139" s="1"/>
     </row>
-    <row r="140" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="140" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A140" s="3">
         <v>137</v>
       </c>
@@ -8925,7 +8966,7 @@
       <c r="AJ140" s="1"/>
       <c r="AK140" s="1"/>
     </row>
-    <row r="141" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="141" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A141" s="3">
         <v>138</v>
       </c>
@@ -8968,7 +9009,7 @@
       <c r="AJ141" s="1"/>
       <c r="AK141" s="1"/>
     </row>
-    <row r="142" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="142" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A142" s="3">
         <v>139</v>
       </c>
@@ -9011,7 +9052,7 @@
       <c r="AJ142" s="1"/>
       <c r="AK142" s="1"/>
     </row>
-    <row r="143" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="143" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A143" s="3">
         <v>140</v>
       </c>
@@ -9054,7 +9095,7 @@
       <c r="AJ143" s="1"/>
       <c r="AK143" s="1"/>
     </row>
-    <row r="144" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="144" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A144" s="3">
         <v>141</v>
       </c>
@@ -9097,7 +9138,7 @@
       <c r="AJ144" s="1"/>
       <c r="AK144" s="1"/>
     </row>
-    <row r="145" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="145" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A145" s="3">
         <v>142</v>
       </c>
@@ -9140,7 +9181,7 @@
       <c r="AJ145" s="1"/>
       <c r="AK145" s="1"/>
     </row>
-    <row r="146" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="146" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A146" s="3">
         <v>143</v>
       </c>
@@ -9223,12 +9264,14 @@
       <c r="AE147" s="29"/>
       <c r="AF147" s="1"/>
       <c r="AG147" s="29"/>
-      <c r="AH147" s="1"/>
+      <c r="AH147" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI147" s="1"/>
       <c r="AJ147" s="1"/>
       <c r="AK147" s="1"/>
     </row>
-    <row r="148" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="148" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A148" s="3">
         <v>145</v>
       </c>
@@ -9273,7 +9316,7 @@
       <c r="AJ148" s="1"/>
       <c r="AK148" s="1"/>
     </row>
-    <row r="149" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="149" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A149" s="3">
         <v>146</v>
       </c>
@@ -9316,7 +9359,7 @@
       <c r="AJ149" s="1"/>
       <c r="AK149" s="1"/>
     </row>
-    <row r="150" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="150" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A150" s="3">
         <v>147</v>
       </c>
@@ -9354,12 +9397,14 @@
       <c r="AE150" s="29"/>
       <c r="AF150" s="1"/>
       <c r="AG150" s="29"/>
-      <c r="AH150" s="1"/>
+      <c r="AH150" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI150" s="1"/>
       <c r="AJ150" s="1"/>
       <c r="AK150" s="1"/>
     </row>
-    <row r="151" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="151" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A151" s="3">
         <v>148</v>
       </c>
@@ -9402,7 +9447,7 @@
       <c r="AJ151" s="1"/>
       <c r="AK151" s="1"/>
     </row>
-    <row r="152" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="152" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A152" s="3">
         <v>149</v>
       </c>
@@ -9445,7 +9490,7 @@
       <c r="AJ152" s="1"/>
       <c r="AK152" s="1"/>
     </row>
-    <row r="153" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="153" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A153" s="3">
         <v>150</v>
       </c>
@@ -9485,12 +9530,14 @@
       <c r="AE153" s="29"/>
       <c r="AF153" s="1"/>
       <c r="AG153" s="29"/>
-      <c r="AH153" s="1"/>
+      <c r="AH153" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI153" s="1"/>
       <c r="AJ153" s="1"/>
       <c r="AK153" s="1"/>
     </row>
-    <row r="154" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="154" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A154" s="3">
         <v>151</v>
       </c>
@@ -9584,7 +9631,7 @@
       <c r="AJ155" s="1"/>
       <c r="AK155" s="1"/>
     </row>
-    <row r="156" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="156" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A156" s="3">
         <v>153</v>
       </c>
@@ -9629,7 +9676,7 @@
       <c r="AJ156" s="1"/>
       <c r="AK156" s="1"/>
     </row>
-    <row r="157" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="157" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A157" s="3">
         <v>154</v>
       </c>
@@ -9718,7 +9765,9 @@
       <c r="AE158" s="29"/>
       <c r="AF158" s="1"/>
       <c r="AG158" s="29"/>
-      <c r="AH158" s="1"/>
+      <c r="AH158" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI158" s="1"/>
       <c r="AJ158" s="1"/>
       <c r="AK158" s="1"/>
@@ -9765,12 +9814,14 @@
       <c r="AE159" s="29"/>
       <c r="AF159" s="1"/>
       <c r="AG159" s="29"/>
-      <c r="AH159" s="1"/>
+      <c r="AH159" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI159" s="1"/>
       <c r="AJ159" s="1"/>
       <c r="AK159" s="1"/>
     </row>
-    <row r="160" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="160" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A160" s="3">
         <v>157</v>
       </c>
@@ -9817,7 +9868,7 @@
       <c r="AJ160" s="1"/>
       <c r="AK160" s="1"/>
     </row>
-    <row r="161" spans="1:37" ht="15" hidden="1" customHeight="1">
+    <row r="161" spans="1:37" ht="15" customHeight="1">
       <c r="A161" s="3">
         <v>158</v>
       </c>
@@ -9904,7 +9955,9 @@
       <c r="AE162" s="29"/>
       <c r="AF162" s="1"/>
       <c r="AG162" s="29"/>
-      <c r="AH162" s="1"/>
+      <c r="AH162" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI162" s="1"/>
       <c r="AJ162" s="1"/>
       <c r="AK162" s="1"/>
@@ -9958,7 +10011,7 @@
       <c r="AJ163" s="1"/>
       <c r="AK163" s="1"/>
     </row>
-    <row r="164" spans="1:37" ht="15" hidden="1" customHeight="1">
+    <row r="164" spans="1:37" ht="15" customHeight="1">
       <c r="A164" s="3">
         <v>161</v>
       </c>
@@ -10003,7 +10056,7 @@
       <c r="AJ164" s="3"/>
       <c r="AK164" s="3"/>
     </row>
-    <row r="165" spans="1:37" ht="15" hidden="1" customHeight="1">
+    <row r="165" spans="1:37" ht="15" customHeight="1">
       <c r="A165" s="3">
         <v>162</v>
       </c>
@@ -10048,7 +10101,7 @@
       <c r="AJ165" s="3"/>
       <c r="AK165" s="3"/>
     </row>
-    <row r="166" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="166" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A166" s="3">
         <v>163</v>
       </c>
@@ -10091,7 +10144,7 @@
       <c r="AJ166" s="1"/>
       <c r="AK166" s="1"/>
     </row>
-    <row r="167" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="167" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A167" s="3">
         <v>164</v>
       </c>
@@ -10134,7 +10187,7 @@
       <c r="AJ167" s="1"/>
       <c r="AK167" s="1"/>
     </row>
-    <row r="168" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="168" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A168" s="3">
         <v>165</v>
       </c>
@@ -10177,7 +10230,7 @@
       <c r="AJ168" s="1"/>
       <c r="AK168" s="1"/>
     </row>
-    <row r="169" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="169" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A169" s="3">
         <v>166</v>
       </c>
@@ -10220,7 +10273,7 @@
       <c r="AJ169" s="1"/>
       <c r="AK169" s="1"/>
     </row>
-    <row r="170" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="170" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A170" s="3">
         <v>167</v>
       </c>
@@ -10263,7 +10316,7 @@
       <c r="AJ170" s="1"/>
       <c r="AK170" s="1"/>
     </row>
-    <row r="171" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="171" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A171" s="3">
         <v>168</v>
       </c>
@@ -10306,7 +10359,7 @@
       <c r="AJ171" s="1"/>
       <c r="AK171" s="1"/>
     </row>
-    <row r="172" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="172" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A172" s="3">
         <v>169</v>
       </c>
@@ -10351,7 +10404,7 @@
       <c r="AJ172" s="1"/>
       <c r="AK172" s="1"/>
     </row>
-    <row r="173" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="173" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A173" s="3">
         <v>170</v>
       </c>
@@ -10444,7 +10497,9 @@
       <c r="AE174" s="29"/>
       <c r="AF174" s="1"/>
       <c r="AG174" s="29"/>
-      <c r="AH174" s="1"/>
+      <c r="AH174" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI174" s="1"/>
       <c r="AJ174" s="1"/>
       <c r="AK174" s="1"/>
@@ -10495,7 +10550,9 @@
       <c r="AE175" s="29"/>
       <c r="AF175" s="1"/>
       <c r="AG175" s="29"/>
-      <c r="AH175" s="1"/>
+      <c r="AH175" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI175" s="1"/>
       <c r="AJ175" s="1"/>
       <c r="AK175" s="1"/>
@@ -10550,12 +10607,14 @@
       <c r="AE176" s="29"/>
       <c r="AF176" s="1"/>
       <c r="AG176" s="29"/>
-      <c r="AH176" s="1"/>
+      <c r="AH176" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI176" s="1"/>
       <c r="AJ176" s="1"/>
       <c r="AK176" s="1"/>
     </row>
-    <row r="177" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="177" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A177" s="3">
         <v>174</v>
       </c>
@@ -10602,7 +10661,7 @@
       <c r="AJ177" s="1"/>
       <c r="AK177" s="1"/>
     </row>
-    <row r="178" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="178" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A178" s="3">
         <v>175</v>
       </c>
@@ -10644,12 +10703,14 @@
       <c r="AE178" s="29"/>
       <c r="AF178" s="1"/>
       <c r="AG178" s="29"/>
-      <c r="AH178" s="1"/>
+      <c r="AH178" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI178" s="1"/>
       <c r="AJ178" s="1"/>
       <c r="AK178" s="1"/>
     </row>
-    <row r="179" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="179" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A179" s="3">
         <v>176</v>
       </c>
@@ -10691,12 +10752,14 @@
       <c r="AE179" s="29"/>
       <c r="AF179" s="1"/>
       <c r="AG179" s="29"/>
-      <c r="AH179" s="1"/>
+      <c r="AH179" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI179" s="1"/>
       <c r="AJ179" s="1"/>
       <c r="AK179" s="1"/>
     </row>
-    <row r="180" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="180" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A180" s="3">
         <v>177</v>
       </c>
@@ -10740,12 +10803,14 @@
       <c r="AE180" s="29"/>
       <c r="AF180" s="1"/>
       <c r="AG180" s="29"/>
-      <c r="AH180" s="1"/>
+      <c r="AH180" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI180" s="1"/>
       <c r="AJ180" s="1"/>
       <c r="AK180" s="1"/>
     </row>
-    <row r="181" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="181" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A181" s="3">
         <v>178</v>
       </c>
@@ -10787,12 +10852,14 @@
       <c r="AE181" s="29"/>
       <c r="AF181" s="1"/>
       <c r="AG181" s="29"/>
-      <c r="AH181" s="1"/>
+      <c r="AH181" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI181" s="1"/>
       <c r="AJ181" s="1"/>
       <c r="AK181" s="1"/>
     </row>
-    <row r="182" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="182" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A182" s="3">
         <v>179</v>
       </c>
@@ -10836,7 +10903,9 @@
       <c r="AE182" s="29"/>
       <c r="AF182" s="1"/>
       <c r="AG182" s="29"/>
-      <c r="AH182" s="1"/>
+      <c r="AH182" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI182" s="1"/>
       <c r="AJ182" s="1"/>
       <c r="AK182" s="1"/>
@@ -10889,12 +10958,14 @@
       <c r="AE183" s="29"/>
       <c r="AF183" s="1"/>
       <c r="AG183" s="29"/>
-      <c r="AH183" s="1"/>
+      <c r="AH183" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI183" s="1"/>
       <c r="AJ183" s="1"/>
       <c r="AK183" s="1"/>
     </row>
-    <row r="184" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="184" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A184" s="3">
         <v>181</v>
       </c>
@@ -10940,12 +11011,14 @@
       <c r="AE184" s="29"/>
       <c r="AF184" s="1"/>
       <c r="AG184" s="29"/>
-      <c r="AH184" s="1"/>
+      <c r="AH184" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI184" s="1"/>
       <c r="AJ184" s="1"/>
       <c r="AK184" s="1"/>
     </row>
-    <row r="185" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="185" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A185" s="3">
         <v>182</v>
       </c>
@@ -10989,12 +11062,14 @@
       <c r="AE185" s="29"/>
       <c r="AF185" s="1"/>
       <c r="AG185" s="29"/>
-      <c r="AH185" s="1"/>
+      <c r="AH185" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI185" s="1"/>
       <c r="AJ185" s="1"/>
       <c r="AK185" s="1"/>
     </row>
-    <row r="186" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="186" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A186" s="3">
         <v>183</v>
       </c>
@@ -11043,7 +11118,7 @@
       <c r="AJ186" s="1"/>
       <c r="AK186" s="1"/>
     </row>
-    <row r="187" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="187" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A187" s="3">
         <v>184</v>
       </c>
@@ -11092,7 +11167,7 @@
       <c r="AJ187" s="1"/>
       <c r="AK187" s="1"/>
     </row>
-    <row r="188" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="188" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A188" s="3">
         <v>185</v>
       </c>
@@ -11143,7 +11218,7 @@
       <c r="AJ188" s="1"/>
       <c r="AK188" s="1"/>
     </row>
-    <row r="189" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="189" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A189" s="3">
         <v>186</v>
       </c>
@@ -11192,7 +11267,7 @@
       <c r="AJ189" s="1"/>
       <c r="AK189" s="1"/>
     </row>
-    <row r="190" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="190" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A190" s="3">
         <v>187</v>
       </c>
@@ -11241,7 +11316,7 @@
       <c r="AJ190" s="1"/>
       <c r="AK190" s="1"/>
     </row>
-    <row r="191" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="191" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A191" s="3">
         <v>188</v>
       </c>
@@ -11290,7 +11365,7 @@
       <c r="AJ191" s="1"/>
       <c r="AK191" s="1"/>
     </row>
-    <row r="192" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="192" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A192" s="3">
         <v>189</v>
       </c>
@@ -11332,12 +11407,14 @@
       <c r="AE192" s="29"/>
       <c r="AF192" s="1"/>
       <c r="AG192" s="29"/>
-      <c r="AH192" s="1"/>
+      <c r="AH192" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI192" s="1"/>
       <c r="AJ192" s="1"/>
       <c r="AK192" s="1"/>
     </row>
-    <row r="193" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="193" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A193" s="3">
         <v>190</v>
       </c>
@@ -11384,7 +11461,7 @@
       <c r="AJ193" s="1"/>
       <c r="AK193" s="1"/>
     </row>
-    <row r="194" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="194" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A194" s="3">
         <v>191</v>
       </c>
@@ -11429,7 +11506,7 @@
       <c r="AJ194" s="1"/>
       <c r="AK194" s="1"/>
     </row>
-    <row r="195" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="195" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A195" s="3">
         <v>192</v>
       </c>
@@ -11474,7 +11551,7 @@
       <c r="AJ195" s="1"/>
       <c r="AK195" s="1"/>
     </row>
-    <row r="196" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="196" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A196" s="3">
         <v>193</v>
       </c>
@@ -11519,7 +11596,7 @@
       <c r="AJ196" s="1"/>
       <c r="AK196" s="1"/>
     </row>
-    <row r="197" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="197" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A197" s="3">
         <v>194</v>
       </c>
@@ -11564,7 +11641,7 @@
       <c r="AJ197" s="1"/>
       <c r="AK197" s="1"/>
     </row>
-    <row r="198" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="198" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A198" s="3">
         <v>195</v>
       </c>
@@ -11660,7 +11737,7 @@
       <c r="AJ199" s="1"/>
       <c r="AK199" s="1"/>
     </row>
-    <row r="200" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="200" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A200" s="3">
         <v>197</v>
       </c>
@@ -11705,7 +11782,7 @@
       <c r="AJ200" s="1"/>
       <c r="AK200" s="1"/>
     </row>
-    <row r="201" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="201" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A201" s="3">
         <v>198</v>
       </c>
@@ -11752,7 +11829,7 @@
       <c r="AJ201" s="1"/>
       <c r="AK201" s="1"/>
     </row>
-    <row r="202" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="202" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A202" s="3">
         <v>199</v>
       </c>
@@ -11797,7 +11874,7 @@
       <c r="AJ202" s="1"/>
       <c r="AK202" s="1"/>
     </row>
-    <row r="203" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="203" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A203" s="3">
         <v>200</v>
       </c>
@@ -11844,7 +11921,7 @@
       <c r="AJ203" s="1"/>
       <c r="AK203" s="1"/>
     </row>
-    <row r="204" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="204" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A204" s="3">
         <v>201</v>
       </c>
@@ -11889,7 +11966,7 @@
       <c r="AJ204" s="1"/>
       <c r="AK204" s="1"/>
     </row>
-    <row r="205" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="205" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A205" s="3">
         <v>202</v>
       </c>
@@ -11934,7 +12011,7 @@
       <c r="AJ205" s="1"/>
       <c r="AK205" s="1"/>
     </row>
-    <row r="206" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="206" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A206" s="3">
         <v>203</v>
       </c>
@@ -11979,7 +12056,7 @@
       <c r="AJ206" s="1"/>
       <c r="AK206" s="1"/>
     </row>
-    <row r="207" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="207" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A207" s="3">
         <v>204</v>
       </c>
@@ -12026,7 +12103,7 @@
       <c r="AJ207" s="1"/>
       <c r="AK207" s="1"/>
     </row>
-    <row r="208" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="208" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A208" s="3">
         <v>205</v>
       </c>
@@ -12071,7 +12148,7 @@
       <c r="AJ208" s="1"/>
       <c r="AK208" s="1"/>
     </row>
-    <row r="209" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="209" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A209" s="3">
         <v>206</v>
       </c>
@@ -12111,12 +12188,14 @@
       <c r="AE209" s="29"/>
       <c r="AF209" s="1"/>
       <c r="AG209" s="29"/>
-      <c r="AH209" s="1"/>
+      <c r="AH209" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI209" s="1"/>
       <c r="AJ209" s="1"/>
       <c r="AK209" s="1"/>
     </row>
-    <row r="210" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="210" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A210" s="3">
         <v>207</v>
       </c>
@@ -12161,7 +12240,7 @@
       <c r="AJ210" s="1"/>
       <c r="AK210" s="1"/>
     </row>
-    <row r="211" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="211" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A211" s="3">
         <v>208</v>
       </c>
@@ -12206,7 +12285,7 @@
       <c r="AJ211" s="1"/>
       <c r="AK211" s="1"/>
     </row>
-    <row r="212" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="212" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A212" s="3">
         <v>209</v>
       </c>
@@ -12251,7 +12330,7 @@
       <c r="AJ212" s="1"/>
       <c r="AK212" s="1"/>
     </row>
-    <row r="213" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="213" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A213" s="3">
         <v>210</v>
       </c>
@@ -12343,7 +12422,7 @@
       <c r="AJ214" s="1"/>
       <c r="AK214" s="1"/>
     </row>
-    <row r="215" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="215" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A215" s="3">
         <v>212</v>
       </c>
@@ -12383,7 +12462,9 @@
       <c r="AE215" s="29"/>
       <c r="AF215" s="1"/>
       <c r="AG215" s="29"/>
-      <c r="AH215" s="1"/>
+      <c r="AH215" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI215" s="1"/>
       <c r="AJ215" s="1"/>
       <c r="AK215" s="1"/>
@@ -12536,12 +12617,14 @@
       <c r="AE218" s="29"/>
       <c r="AF218" s="1"/>
       <c r="AG218" s="29"/>
-      <c r="AH218" s="1"/>
+      <c r="AH218" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI218" s="1"/>
       <c r="AJ218" s="1"/>
       <c r="AK218" s="1"/>
     </row>
-    <row r="219" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="219" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A219" s="3">
         <v>216</v>
       </c>
@@ -12584,7 +12667,7 @@
       <c r="AJ219" s="1"/>
       <c r="AK219" s="1"/>
     </row>
-    <row r="220" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="220" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A220" s="3">
         <v>217</v>
       </c>
@@ -12627,7 +12710,7 @@
       <c r="AJ220" s="1"/>
       <c r="AK220" s="1"/>
     </row>
-    <row r="221" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="221" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A221" s="3">
         <v>218</v>
       </c>
@@ -12670,7 +12753,7 @@
       <c r="AJ221" s="1"/>
       <c r="AK221" s="1"/>
     </row>
-    <row r="222" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="222" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A222" s="3">
         <v>219</v>
       </c>
@@ -12715,7 +12798,7 @@
       <c r="AJ222" s="1"/>
       <c r="AK222" s="1"/>
     </row>
-    <row r="223" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="223" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A223" s="3">
         <v>220</v>
       </c>
@@ -12758,7 +12841,7 @@
       <c r="AJ223" s="1"/>
       <c r="AK223" s="1"/>
     </row>
-    <row r="224" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="224" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A224" s="3">
         <v>221</v>
       </c>
@@ -12801,7 +12884,7 @@
       <c r="AJ224" s="1"/>
       <c r="AK224" s="1"/>
     </row>
-    <row r="225" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="225" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A225" s="3">
         <v>222</v>
       </c>
@@ -12844,7 +12927,7 @@
       <c r="AJ225" s="1"/>
       <c r="AK225" s="1"/>
     </row>
-    <row r="226" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="226" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A226" s="3">
         <v>223</v>
       </c>
@@ -12887,7 +12970,7 @@
       <c r="AJ226" s="1"/>
       <c r="AK226" s="1"/>
     </row>
-    <row r="227" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="227" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A227" s="3">
         <v>224</v>
       </c>
@@ -12930,7 +13013,7 @@
       <c r="AJ227" s="1"/>
       <c r="AK227" s="1"/>
     </row>
-    <row r="228" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="228" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A228" s="3">
         <v>225</v>
       </c>
@@ -12973,7 +13056,7 @@
       <c r="AJ228" s="1"/>
       <c r="AK228" s="1"/>
     </row>
-    <row r="229" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="229" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A229" s="3">
         <v>226</v>
       </c>
@@ -13016,7 +13099,7 @@
       <c r="AJ229" s="1"/>
       <c r="AK229" s="1"/>
     </row>
-    <row r="230" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="230" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A230" s="3">
         <v>227</v>
       </c>
@@ -13059,7 +13142,7 @@
       <c r="AJ230" s="1"/>
       <c r="AK230" s="1"/>
     </row>
-    <row r="231" spans="1:37" hidden="1">
+    <row r="231" spans="1:37">
       <c r="A231" s="3">
         <v>228</v>
       </c>
@@ -13102,7 +13185,7 @@
       <c r="AJ231" s="1"/>
       <c r="AK231" s="1"/>
     </row>
-    <row r="232" spans="1:37" hidden="1">
+    <row r="232" spans="1:37">
       <c r="A232" s="3">
         <v>229</v>
       </c>
@@ -13192,7 +13275,7 @@
       <c r="AJ233" s="1"/>
       <c r="AK233" s="1"/>
     </row>
-    <row r="234" spans="1:37" hidden="1">
+    <row r="234" spans="1:37">
       <c r="A234" s="3">
         <v>231</v>
       </c>
@@ -13275,12 +13358,14 @@
       <c r="AE235" s="29"/>
       <c r="AF235" s="1"/>
       <c r="AG235" s="29"/>
-      <c r="AH235" s="1"/>
+      <c r="AH235" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI235" s="1"/>
       <c r="AJ235" s="1"/>
       <c r="AK235" s="1"/>
     </row>
-    <row r="236" spans="1:37" hidden="1">
+    <row r="236" spans="1:37">
       <c r="A236" s="3">
         <v>233</v>
       </c>
@@ -13323,7 +13408,7 @@
       <c r="AJ236" s="1"/>
       <c r="AK236" s="1"/>
     </row>
-    <row r="237" spans="1:37" hidden="1">
+    <row r="237" spans="1:37">
       <c r="A237" s="3">
         <v>234</v>
       </c>
@@ -13366,7 +13451,7 @@
       <c r="AJ237" s="1"/>
       <c r="AK237" s="1"/>
     </row>
-    <row r="238" spans="1:37" hidden="1">
+    <row r="238" spans="1:37">
       <c r="A238" s="3">
         <v>235</v>
       </c>
@@ -13409,7 +13494,7 @@
       <c r="AJ238" s="1"/>
       <c r="AK238" s="1"/>
     </row>
-    <row r="239" spans="1:37" hidden="1">
+    <row r="239" spans="1:37">
       <c r="A239" s="3">
         <v>236</v>
       </c>
@@ -13452,7 +13537,7 @@
       <c r="AJ239" s="1"/>
       <c r="AK239" s="1"/>
     </row>
-    <row r="240" spans="1:37" hidden="1">
+    <row r="240" spans="1:37">
       <c r="A240" s="3">
         <v>237</v>
       </c>
@@ -13495,7 +13580,7 @@
       <c r="AJ240" s="1"/>
       <c r="AK240" s="1"/>
     </row>
-    <row r="241" spans="1:37" hidden="1">
+    <row r="241" spans="1:37">
       <c r="A241" s="3">
         <v>238</v>
       </c>
@@ -13538,7 +13623,7 @@
       <c r="AJ241" s="1"/>
       <c r="AK241" s="1"/>
     </row>
-    <row r="242" spans="1:37" hidden="1">
+    <row r="242" spans="1:37">
       <c r="A242" s="3">
         <v>239</v>
       </c>
@@ -13581,7 +13666,7 @@
       <c r="AJ242" s="1"/>
       <c r="AK242" s="1"/>
     </row>
-    <row r="243" spans="1:37" hidden="1">
+    <row r="243" spans="1:37">
       <c r="A243" s="3">
         <v>240</v>
       </c>
@@ -13626,7 +13711,7 @@
       <c r="AJ243" s="1"/>
       <c r="AK243" s="1"/>
     </row>
-    <row r="244" spans="1:37" hidden="1">
+    <row r="244" spans="1:37">
       <c r="A244" s="3">
         <v>241</v>
       </c>
@@ -13671,7 +13756,7 @@
       <c r="AJ244" s="1"/>
       <c r="AK244" s="1"/>
     </row>
-    <row r="245" spans="1:37" hidden="1">
+    <row r="245" spans="1:37">
       <c r="A245" s="3">
         <v>242</v>
       </c>
@@ -13716,7 +13801,7 @@
       <c r="AJ245" s="1"/>
       <c r="AK245" s="1"/>
     </row>
-    <row r="246" spans="1:37" hidden="1">
+    <row r="246" spans="1:37">
       <c r="A246" s="3">
         <v>243</v>
       </c>
@@ -13761,7 +13846,7 @@
       <c r="AJ246" s="1"/>
       <c r="AK246" s="1"/>
     </row>
-    <row r="247" spans="1:37" hidden="1">
+    <row r="247" spans="1:37">
       <c r="A247" s="3">
         <v>244</v>
       </c>
@@ -13853,7 +13938,7 @@
       <c r="AJ248" s="1"/>
       <c r="AK248" s="1"/>
     </row>
-    <row r="249" spans="1:37" hidden="1">
+    <row r="249" spans="1:37">
       <c r="A249" s="3">
         <v>246</v>
       </c>
@@ -13896,7 +13981,7 @@
       <c r="AJ249" s="1"/>
       <c r="AK249" s="1"/>
     </row>
-    <row r="250" spans="1:37" hidden="1">
+    <row r="250" spans="1:37">
       <c r="A250" s="3">
         <v>247</v>
       </c>
@@ -13939,7 +14024,7 @@
       <c r="AJ250" s="1"/>
       <c r="AK250" s="1"/>
     </row>
-    <row r="251" spans="1:37" hidden="1">
+    <row r="251" spans="1:37">
       <c r="A251" s="3">
         <v>248</v>
       </c>
@@ -13982,7 +14067,7 @@
       <c r="AJ251" s="1"/>
       <c r="AK251" s="1"/>
     </row>
-    <row r="252" spans="1:37" hidden="1">
+    <row r="252" spans="1:37">
       <c r="A252" s="3">
         <v>249</v>
       </c>
@@ -14025,7 +14110,7 @@
       <c r="AJ252" s="1"/>
       <c r="AK252" s="1"/>
     </row>
-    <row r="253" spans="1:37" hidden="1">
+    <row r="253" spans="1:37">
       <c r="A253" s="3">
         <v>250</v>
       </c>
@@ -14068,7 +14153,7 @@
       <c r="AJ253" s="1"/>
       <c r="AK253" s="1"/>
     </row>
-    <row r="254" spans="1:37" hidden="1">
+    <row r="254" spans="1:37">
       <c r="A254" s="3">
         <v>251</v>
       </c>
@@ -14111,7 +14196,7 @@
       <c r="AJ254" s="1"/>
       <c r="AK254" s="1"/>
     </row>
-    <row r="255" spans="1:37" hidden="1">
+    <row r="255" spans="1:37">
       <c r="A255" s="3">
         <v>252</v>
       </c>
@@ -14194,17 +14279,21 @@
       <c r="AE256" s="29"/>
       <c r="AF256" s="1"/>
       <c r="AG256" s="29"/>
-      <c r="AH256" s="1"/>
+      <c r="AH256" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI256" s="1"/>
       <c r="AJ256" s="1"/>
       <c r="AK256" s="1"/>
     </row>
-    <row r="257" spans="1:37" hidden="1">
+    <row r="257" spans="1:37">
       <c r="A257" s="3">
         <v>254</v>
       </c>
       <c r="B257" s="3"/>
-      <c r="C257" s="21"/>
+      <c r="C257" s="21" t="s">
+        <v>403</v>
+      </c>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
@@ -14235,17 +14324,21 @@
       <c r="AE257" s="29"/>
       <c r="AF257" s="1"/>
       <c r="AG257" s="29"/>
-      <c r="AH257" s="1"/>
+      <c r="AH257" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI257" s="1"/>
       <c r="AJ257" s="1"/>
       <c r="AK257" s="1"/>
     </row>
-    <row r="258" spans="1:37" hidden="1">
+    <row r="258" spans="1:37">
       <c r="A258" s="3">
         <v>255</v>
       </c>
       <c r="B258" s="3"/>
-      <c r="C258" s="21"/>
+      <c r="C258" s="21" t="s">
+        <v>404</v>
+      </c>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
       <c r="F258" s="1"/>
@@ -14276,17 +14369,21 @@
       <c r="AE258" s="29"/>
       <c r="AF258" s="1"/>
       <c r="AG258" s="29"/>
-      <c r="AH258" s="1"/>
+      <c r="AH258" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI258" s="1"/>
       <c r="AJ258" s="1"/>
       <c r="AK258" s="1"/>
     </row>
-    <row r="259" spans="1:37" hidden="1">
+    <row r="259" spans="1:37">
       <c r="A259" s="3">
         <v>256</v>
       </c>
       <c r="B259" s="3"/>
-      <c r="C259" s="21"/>
+      <c r="C259" s="21" t="s">
+        <v>405</v>
+      </c>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
       <c r="F259" s="1"/>
@@ -14317,17 +14414,21 @@
       <c r="AE259" s="29"/>
       <c r="AF259" s="1"/>
       <c r="AG259" s="29"/>
-      <c r="AH259" s="1"/>
+      <c r="AH259" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI259" s="1"/>
       <c r="AJ259" s="1"/>
       <c r="AK259" s="1"/>
     </row>
-    <row r="260" spans="1:37" hidden="1">
+    <row r="260" spans="1:37">
       <c r="A260" s="3">
         <v>257</v>
       </c>
       <c r="B260" s="3"/>
-      <c r="C260" s="21"/>
+      <c r="C260" s="21" t="s">
+        <v>406</v>
+      </c>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
       <c r="F260" s="1"/>
@@ -14358,12 +14459,14 @@
       <c r="AE260" s="29"/>
       <c r="AF260" s="1"/>
       <c r="AG260" s="29"/>
-      <c r="AH260" s="1"/>
+      <c r="AH260" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="AI260" s="1"/>
       <c r="AJ260" s="1"/>
       <c r="AK260" s="1"/>
     </row>
-    <row r="261" spans="1:37" hidden="1">
+    <row r="261" spans="1:37">
       <c r="A261" s="3">
         <v>258</v>
       </c>
@@ -14404,7 +14507,7 @@
       <c r="AJ261" s="1"/>
       <c r="AK261" s="1"/>
     </row>
-    <row r="262" spans="1:37" hidden="1">
+    <row r="262" spans="1:37">
       <c r="A262" s="3">
         <v>259</v>
       </c>
@@ -14445,7 +14548,7 @@
       <c r="AJ262" s="1"/>
       <c r="AK262" s="1"/>
     </row>
-    <row r="263" spans="1:37" hidden="1">
+    <row r="263" spans="1:37">
       <c r="A263" s="3">
         <v>260</v>
       </c>
@@ -14486,7 +14589,7 @@
       <c r="AJ263" s="1"/>
       <c r="AK263" s="1"/>
     </row>
-    <row r="264" spans="1:37" hidden="1">
+    <row r="264" spans="1:37">
       <c r="A264" s="3">
         <v>261</v>
       </c>
@@ -14527,7 +14630,7 @@
       <c r="AJ264" s="1"/>
       <c r="AK264" s="1"/>
     </row>
-    <row r="265" spans="1:37" hidden="1">
+    <row r="265" spans="1:37">
       <c r="A265" s="3">
         <v>262</v>
       </c>
@@ -14568,7 +14671,7 @@
       <c r="AJ265" s="1"/>
       <c r="AK265" s="1"/>
     </row>
-    <row r="266" spans="1:37" hidden="1">
+    <row r="266" spans="1:37">
       <c r="A266" s="3">
         <v>263</v>
       </c>
@@ -14609,7 +14712,7 @@
       <c r="AJ266" s="1"/>
       <c r="AK266" s="1"/>
     </row>
-    <row r="267" spans="1:37" hidden="1">
+    <row r="267" spans="1:37">
       <c r="A267" s="3">
         <v>264</v>
       </c>
@@ -14650,7 +14753,7 @@
       <c r="AJ267" s="1"/>
       <c r="AK267" s="1"/>
     </row>
-    <row r="268" spans="1:37" hidden="1">
+    <row r="268" spans="1:37">
       <c r="A268" s="3">
         <v>265</v>
       </c>
@@ -14691,7 +14794,7 @@
       <c r="AJ268" s="1"/>
       <c r="AK268" s="1"/>
     </row>
-    <row r="269" spans="1:37" hidden="1">
+    <row r="269" spans="1:37">
       <c r="A269" s="3">
         <v>266</v>
       </c>
@@ -14732,7 +14835,7 @@
       <c r="AJ269" s="1"/>
       <c r="AK269" s="1"/>
     </row>
-    <row r="270" spans="1:37" hidden="1">
+    <row r="270" spans="1:37">
       <c r="A270" s="3">
         <v>267</v>
       </c>
@@ -14773,7 +14876,7 @@
       <c r="AJ270" s="1"/>
       <c r="AK270" s="1"/>
     </row>
-    <row r="271" spans="1:37" hidden="1">
+    <row r="271" spans="1:37">
       <c r="A271" s="3">
         <v>268</v>
       </c>
@@ -14814,7 +14917,7 @@
       <c r="AJ271" s="1"/>
       <c r="AK271" s="1"/>
     </row>
-    <row r="272" spans="1:37" hidden="1">
+    <row r="272" spans="1:37">
       <c r="A272" s="3">
         <v>269</v>
       </c>
@@ -14855,7 +14958,7 @@
       <c r="AJ272" s="1"/>
       <c r="AK272" s="1"/>
     </row>
-    <row r="273" spans="1:37" hidden="1">
+    <row r="273" spans="1:37">
       <c r="A273" s="3">
         <v>270</v>
       </c>
@@ -14896,7 +14999,7 @@
       <c r="AJ273" s="1"/>
       <c r="AK273" s="1"/>
     </row>
-    <row r="274" spans="1:37" hidden="1">
+    <row r="274" spans="1:37">
       <c r="A274" s="3">
         <v>271</v>
       </c>
@@ -14937,7 +15040,7 @@
       <c r="AJ274" s="1"/>
       <c r="AK274" s="1"/>
     </row>
-    <row r="275" spans="1:37" hidden="1">
+    <row r="275" spans="1:37">
       <c r="A275" s="3">
         <v>272</v>
       </c>
@@ -14978,7 +15081,7 @@
       <c r="AJ275" s="1"/>
       <c r="AK275" s="1"/>
     </row>
-    <row r="276" spans="1:37" hidden="1">
+    <row r="276" spans="1:37">
       <c r="A276" s="3">
         <v>273</v>
       </c>
@@ -15019,7 +15122,7 @@
       <c r="AJ276" s="1"/>
       <c r="AK276" s="1"/>
     </row>
-    <row r="277" spans="1:37" hidden="1">
+    <row r="277" spans="1:37">
       <c r="A277" s="3">
         <v>274</v>
       </c>
@@ -15060,7 +15163,7 @@
       <c r="AJ277" s="1"/>
       <c r="AK277" s="1"/>
     </row>
-    <row r="278" spans="1:37" hidden="1">
+    <row r="278" spans="1:37">
       <c r="A278" s="3">
         <v>275</v>
       </c>
@@ -15101,7 +15204,7 @@
       <c r="AJ278" s="1"/>
       <c r="AK278" s="1"/>
     </row>
-    <row r="279" spans="1:37" hidden="1">
+    <row r="279" spans="1:37">
       <c r="A279" s="3">
         <v>276</v>
       </c>
@@ -15142,7 +15245,7 @@
       <c r="AJ279" s="1"/>
       <c r="AK279" s="1"/>
     </row>
-    <row r="280" spans="1:37" hidden="1">
+    <row r="280" spans="1:37">
       <c r="A280" s="3">
         <v>277</v>
       </c>
@@ -15184,13 +15287,7 @@
       <c r="AK280" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AB280" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="25">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A3:AB280" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="4">
     <mergeCell ref="C1:C3"/>
     <mergeCell ref="A1:A3"/>
@@ -15213,14 +15310,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8513D353-BD33-4F18-8682-09CF4EA59EE5}">
   <dimension ref="A2:H171"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.649999999999999"/>
   <cols>
-    <col min="1" max="1" width="12.08203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.0625" style="16" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.08203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.9140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="6.58203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.8125" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.0625" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.9375" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="6.5625" style="16" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="16"/>
   </cols>
   <sheetData>
@@ -17116,12 +17213,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B979FDD-83A3-41C6-8CB0-C39167BCC619}">
   <dimension ref="A1:E221"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" customWidth="1"/>
-    <col min="2" max="2" width="4.58203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.58203125" customWidth="1"/>
-    <col min="4" max="4" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.8125" customWidth="1"/>
+    <col min="2" max="2" width="4.5625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5625" customWidth="1"/>
+    <col min="4" max="4" width="29.1875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE799A4-4DD2-4970-BB56-2E010BD53034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00707E4D-BA90-46B3-A75F-E1513C15AF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">リスト!$A$3:$AB$280</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">進捗表!$A$2:$H$35</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -110,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="408">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -320,9 +321,6 @@
   </si>
   <si>
     <t>どうしたん</t>
-  </si>
-  <si>
-    <t>ほー　ふーん</t>
   </si>
   <si>
     <t>ほっとするわ</t>
@@ -1949,6 +1947,14 @@
   </si>
   <si>
     <t>ほ～っ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ふくろう</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ほー</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2686,6 +2692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AK280"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
@@ -2700,13 +2707,13 @@
     <row r="1" spans="1:37" ht="22.9">
       <c r="A1" s="35"/>
       <c r="B1" s="39" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C1" s="32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E1" s="38"/>
       <c r="F1" s="38"/>
@@ -2783,102 +2790,104 @@
       <c r="B3" s="41"/>
       <c r="C3" s="34"/>
       <c r="D3" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="J3" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="K3" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="L3" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="M3" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="N3" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="O3" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="P3" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="Q3" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="R3" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="R3" s="11" t="s">
+      <c r="S3" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="S3" s="11" t="s">
+      <c r="T3" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="T3" s="11" t="s">
+      <c r="U3" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="V3" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="U3" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>138</v>
-      </c>
       <c r="W3" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="X3" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Y3" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="Z3" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="Z3" s="11" t="s">
-        <v>268</v>
-      </c>
       <c r="AA3" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="AB3" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="AB3" s="11" t="s">
+      <c r="AC3" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="AC3" s="11" t="s">
-        <v>287</v>
-      </c>
       <c r="AD3" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AE3" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AF3" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG3" s="11" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AH3" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="AI3" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="AI3" s="11" t="s">
-        <v>400</v>
-      </c>
-      <c r="AJ3" s="11"/>
+      <c r="AJ3" s="11" t="s">
+        <v>406</v>
+      </c>
       <c r="AK3" s="11"/>
     </row>
     <row r="4" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickTop="1">
@@ -2886,19 +2895,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2908,19 +2917,19 @@
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
@@ -2941,19 +2950,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -2963,23 +2972,23 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
@@ -2989,7 +2998,7 @@
       <c r="AF5" s="1"/>
       <c r="AG5" s="29"/>
       <c r="AH5" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
@@ -3001,14 +3010,14 @@
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -3026,7 +3035,7 @@
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
@@ -3038,7 +3047,7 @@
       <c r="AF6" s="1"/>
       <c r="AG6" s="29"/>
       <c r="AH6" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI6" s="1"/>
       <c r="AJ6" s="1"/>
@@ -3116,7 +3125,7 @@
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
@@ -3224,14 +3233,14 @@
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -3249,7 +3258,7 @@
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
@@ -3552,7 +3561,7 @@
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
@@ -3693,7 +3702,7 @@
       <c r="AF21" s="1"/>
       <c r="AG21" s="29"/>
       <c r="AH21" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
@@ -3712,7 +3721,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -3816,11 +3825,11 @@
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
       <c r="X24" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
@@ -3863,7 +3872,7 @@
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
       <c r="X25" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
@@ -3928,7 +3937,7 @@
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -3944,7 +3953,7 @@
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
@@ -4082,7 +4091,7 @@
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
@@ -4104,16 +4113,16 @@
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -4124,7 +4133,7 @@
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
@@ -4143,7 +4152,7 @@
       <c r="AF31" s="1"/>
       <c r="AG31" s="29"/>
       <c r="AH31" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
@@ -4160,7 +4169,7 @@
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -4481,7 +4490,7 @@
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
       <c r="X39" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
@@ -4526,7 +4535,7 @@
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
       <c r="X40" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
@@ -4571,7 +4580,7 @@
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
       <c r="X41" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4659,7 +4668,7 @@
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
       <c r="X43" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4681,7 +4690,7 @@
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -4876,7 +4885,7 @@
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
       <c r="X48" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -4888,7 +4897,7 @@
       <c r="AF48" s="1"/>
       <c r="AG48" s="29"/>
       <c r="AH48" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI48" s="1"/>
       <c r="AJ48" s="1"/>
@@ -4966,7 +4975,7 @@
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
       <c r="X50" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
@@ -5140,7 +5149,7 @@
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
       <c r="X54" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
@@ -5185,7 +5194,7 @@
       <c r="V55" s="1"/>
       <c r="W55" s="1"/>
       <c r="X55" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
@@ -5275,7 +5284,7 @@
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
       <c r="Z57" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
@@ -5515,7 +5524,7 @@
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -5555,7 +5564,7 @@
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -5571,7 +5580,7 @@
       <c r="O64" s="1"/>
       <c r="P64" s="1"/>
       <c r="Q64" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
@@ -5580,7 +5589,7 @@
       <c r="V64" s="1"/>
       <c r="W64" s="1"/>
       <c r="X64" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
@@ -5592,7 +5601,7 @@
       <c r="AF64" s="1"/>
       <c r="AG64" s="29"/>
       <c r="AH64" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI64" s="1"/>
       <c r="AJ64" s="1"/>
@@ -5627,11 +5636,11 @@
       <c r="V65" s="1"/>
       <c r="W65" s="1"/>
       <c r="X65" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y65" s="1"/>
       <c r="Z65" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
@@ -5699,7 +5708,7 @@
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -5719,7 +5728,7 @@
       <c r="V67" s="1"/>
       <c r="W67" s="1"/>
       <c r="X67" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
@@ -5746,7 +5755,7 @@
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -5768,7 +5777,7 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
       <c r="Z68" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA68" s="1"/>
       <c r="AB68" s="1"/>
@@ -5788,7 +5797,7 @@
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -5804,7 +5813,7 @@
       <c r="O69" s="1"/>
       <c r="P69" s="1"/>
       <c r="Q69" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
@@ -5813,7 +5822,7 @@
       <c r="V69" s="1"/>
       <c r="W69" s="1"/>
       <c r="X69" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
@@ -5840,7 +5849,7 @@
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -5885,7 +5894,7 @@
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
@@ -6097,12 +6106,12 @@
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
@@ -6117,7 +6126,7 @@
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
       <c r="S76" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
@@ -6126,7 +6135,7 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
       <c r="Z76" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
@@ -6136,7 +6145,7 @@
       <c r="AF76" s="1"/>
       <c r="AG76" s="29"/>
       <c r="AH76" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI76" s="1"/>
       <c r="AJ76" s="1"/>
@@ -6148,7 +6157,7 @@
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -6166,7 +6175,7 @@
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
       <c r="S77" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T77" s="1"/>
       <c r="U77" s="1"/>
@@ -6193,7 +6202,7 @@
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -6211,7 +6220,7 @@
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
       <c r="S78" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
@@ -6238,7 +6247,7 @@
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
@@ -6256,7 +6265,7 @@
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
       <c r="S79" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T79" s="1"/>
       <c r="U79" s="1"/>
@@ -6283,7 +6292,7 @@
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -6301,7 +6310,7 @@
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
       <c r="S80" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T80" s="1"/>
       <c r="U80" s="1"/>
@@ -6328,12 +6337,12 @@
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
@@ -6348,7 +6357,7 @@
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
       <c r="S81" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T81" s="1"/>
       <c r="U81" s="1"/>
@@ -6375,7 +6384,7 @@
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -6391,11 +6400,11 @@
       <c r="O82" s="1"/>
       <c r="P82" s="1"/>
       <c r="Q82" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R82" s="1"/>
       <c r="S82" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T82" s="1"/>
       <c r="U82" s="1"/>
@@ -6416,13 +6425,13 @@
       <c r="AJ82" s="1"/>
       <c r="AK82" s="1"/>
     </row>
-    <row r="83" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="83" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A83" s="3">
         <v>80</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -6440,10 +6449,10 @@
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
       <c r="S83" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
@@ -6469,7 +6478,7 @@
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -6487,7 +6496,7 @@
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
       <c r="S84" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T84" s="1"/>
       <c r="U84" s="1"/>
@@ -6514,7 +6523,7 @@
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -6557,7 +6566,7 @@
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
@@ -6600,7 +6609,7 @@
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
@@ -6643,7 +6652,7 @@
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
@@ -6659,7 +6668,7 @@
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
@@ -6678,7 +6687,7 @@
       <c r="AF88" s="1"/>
       <c r="AG88" s="29"/>
       <c r="AH88" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI88" s="1"/>
       <c r="AJ88" s="1"/>
@@ -6690,7 +6699,7 @@
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
@@ -6733,7 +6742,7 @@
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
@@ -6776,7 +6785,7 @@
       </c>
       <c r="B91" s="1"/>
       <c r="C91" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
@@ -6792,7 +6801,7 @@
       <c r="O91" s="1"/>
       <c r="P91" s="1"/>
       <c r="Q91" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
@@ -6821,12 +6830,12 @@
       </c>
       <c r="B92" s="1"/>
       <c r="C92" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
@@ -6866,7 +6875,7 @@
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
@@ -7088,7 +7097,7 @@
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
@@ -7255,7 +7264,7 @@
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="4" t="s">
-        <v>70</v>
+        <v>407</v>
       </c>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
@@ -7298,7 +7307,7 @@
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
@@ -7341,7 +7350,7 @@
       </c>
       <c r="B104" s="1"/>
       <c r="C104" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
@@ -7384,7 +7393,7 @@
       </c>
       <c r="B105" s="1"/>
       <c r="C105" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
@@ -7407,7 +7416,7 @@
       <c r="V105" s="1"/>
       <c r="W105" s="1"/>
       <c r="X105" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
@@ -7429,7 +7438,7 @@
       </c>
       <c r="B106" s="1"/>
       <c r="C106" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
@@ -7472,7 +7481,7 @@
       </c>
       <c r="B107" s="1"/>
       <c r="C107" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
@@ -7495,7 +7504,7 @@
       <c r="V107" s="1"/>
       <c r="W107" s="1"/>
       <c r="X107" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
@@ -7517,7 +7526,7 @@
       </c>
       <c r="B108" s="1"/>
       <c r="C108" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
@@ -7560,7 +7569,7 @@
       </c>
       <c r="B109" s="1"/>
       <c r="C109" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
@@ -7583,7 +7592,7 @@
       <c r="V109" s="1"/>
       <c r="W109" s="1"/>
       <c r="X109" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
@@ -7605,7 +7614,7 @@
       </c>
       <c r="B110" s="1"/>
       <c r="C110" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
@@ -7648,7 +7657,7 @@
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
@@ -7691,12 +7700,12 @@
       </c>
       <c r="B112" s="1"/>
       <c r="C112" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
       <c r="F112" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G112" s="1"/>
       <c r="H112" s="1"/>
@@ -7709,7 +7718,7 @@
       <c r="O112" s="1"/>
       <c r="P112" s="1"/>
       <c r="Q112" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R112" s="1"/>
       <c r="S112" s="1"/>
@@ -7718,7 +7727,7 @@
       <c r="V112" s="1"/>
       <c r="W112" s="1"/>
       <c r="X112" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
@@ -7740,7 +7749,7 @@
       </c>
       <c r="B113" s="1"/>
       <c r="C113" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
@@ -7756,7 +7765,7 @@
       <c r="O113" s="1"/>
       <c r="P113" s="1"/>
       <c r="Q113" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R113" s="1"/>
       <c r="S113" s="1"/>
@@ -7818,7 +7827,7 @@
       <c r="AF114" s="1"/>
       <c r="AG114" s="29"/>
       <c r="AH114" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI114" s="1"/>
       <c r="AJ114" s="1"/>
@@ -7830,12 +7839,12 @@
       </c>
       <c r="B115" s="1"/>
       <c r="C115" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="1"/>
@@ -7875,7 +7884,7 @@
       </c>
       <c r="B116" s="1"/>
       <c r="C116" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
@@ -7918,7 +7927,7 @@
       </c>
       <c r="B117" s="1"/>
       <c r="C117" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
@@ -7961,7 +7970,7 @@
       </c>
       <c r="B118" s="1"/>
       <c r="C118" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
@@ -8004,7 +8013,7 @@
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
@@ -8047,7 +8056,7 @@
       </c>
       <c r="B120" s="1"/>
       <c r="C120" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
@@ -8090,7 +8099,7 @@
       </c>
       <c r="B121" s="1"/>
       <c r="C121" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
@@ -8133,7 +8142,7 @@
       </c>
       <c r="B122" s="1"/>
       <c r="C122" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
@@ -8176,7 +8185,7 @@
       </c>
       <c r="B123" s="1"/>
       <c r="C123" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
@@ -8219,7 +8228,7 @@
       </c>
       <c r="B124" s="1"/>
       <c r="C124" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
@@ -8262,7 +8271,7 @@
       </c>
       <c r="B125" s="1"/>
       <c r="C125" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
@@ -8305,7 +8314,7 @@
       </c>
       <c r="B126" s="1"/>
       <c r="C126" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
@@ -8321,7 +8330,7 @@
       <c r="O126" s="1"/>
       <c r="P126" s="1"/>
       <c r="Q126" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R126" s="1"/>
       <c r="S126" s="1"/>
@@ -8350,7 +8359,7 @@
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
@@ -8393,7 +8402,7 @@
       </c>
       <c r="B128" s="1"/>
       <c r="C128" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
@@ -8409,7 +8418,7 @@
       <c r="O128" s="1"/>
       <c r="P128" s="1"/>
       <c r="Q128" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R128" s="1"/>
       <c r="S128" s="1"/>
@@ -8418,7 +8427,7 @@
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
       <c r="X128" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
@@ -8440,7 +8449,7 @@
       </c>
       <c r="B129" s="1"/>
       <c r="C129" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
@@ -8458,7 +8467,7 @@
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
       <c r="S129" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T129" s="1"/>
       <c r="U129" s="1"/>
@@ -8485,7 +8494,7 @@
       </c>
       <c r="B130" s="1"/>
       <c r="C130" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
@@ -8501,7 +8510,7 @@
       <c r="O130" s="1"/>
       <c r="P130" s="1"/>
       <c r="Q130" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
@@ -8510,7 +8519,7 @@
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
       <c r="X130" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
@@ -8522,7 +8531,7 @@
       <c r="AF130" s="1"/>
       <c r="AG130" s="29"/>
       <c r="AH130" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI130" s="1"/>
       <c r="AJ130" s="1"/>
@@ -8534,7 +8543,7 @@
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
@@ -8557,7 +8566,7 @@
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
       <c r="X131" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
@@ -8579,7 +8588,7 @@
       </c>
       <c r="B132" s="1"/>
       <c r="C132" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
@@ -8612,7 +8621,7 @@
       <c r="AF132" s="1"/>
       <c r="AG132" s="29"/>
       <c r="AH132" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI132" s="1"/>
       <c r="AJ132" s="1"/>
@@ -8624,7 +8633,7 @@
       </c>
       <c r="B133" s="1"/>
       <c r="C133" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
@@ -8667,7 +8676,7 @@
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
@@ -8710,7 +8719,7 @@
       </c>
       <c r="B135" s="1"/>
       <c r="C135" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
@@ -8753,7 +8762,7 @@
       </c>
       <c r="B136" s="1"/>
       <c r="C136" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
@@ -8786,7 +8795,7 @@
       <c r="AF136" s="1"/>
       <c r="AG136" s="29"/>
       <c r="AH136" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI136" s="1"/>
       <c r="AJ136" s="1"/>
@@ -8798,7 +8807,7 @@
       </c>
       <c r="B137" s="1"/>
       <c r="C137" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
@@ -8841,7 +8850,7 @@
       </c>
       <c r="B138" s="1"/>
       <c r="C138" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -8874,7 +8883,7 @@
       <c r="AF138" s="1"/>
       <c r="AG138" s="29"/>
       <c r="AH138" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI138" s="1"/>
       <c r="AJ138" s="1"/>
@@ -8886,7 +8895,7 @@
       </c>
       <c r="B139" s="1"/>
       <c r="C139" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
@@ -8929,7 +8938,7 @@
       </c>
       <c r="B140" s="1"/>
       <c r="C140" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
@@ -8972,7 +8981,7 @@
       </c>
       <c r="B141" s="1"/>
       <c r="C141" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
@@ -9015,7 +9024,7 @@
       </c>
       <c r="B142" s="1"/>
       <c r="C142" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
@@ -9058,7 +9067,7 @@
       </c>
       <c r="B143" s="1"/>
       <c r="C143" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
@@ -9101,7 +9110,7 @@
       </c>
       <c r="B144" s="1"/>
       <c r="C144" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
@@ -9144,7 +9153,7 @@
       </c>
       <c r="B145" s="1"/>
       <c r="C145" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
@@ -9187,7 +9196,7 @@
       </c>
       <c r="B146" s="1"/>
       <c r="C146" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
@@ -9230,7 +9239,7 @@
       </c>
       <c r="B147" s="1"/>
       <c r="C147" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
@@ -9255,7 +9264,7 @@
       <c r="X147" s="1"/>
       <c r="Y147" s="1"/>
       <c r="Z147" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA147" s="1"/>
       <c r="AB147" s="1"/>
@@ -9265,7 +9274,7 @@
       <c r="AF147" s="1"/>
       <c r="AG147" s="29"/>
       <c r="AH147" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI147" s="1"/>
       <c r="AJ147" s="1"/>
@@ -9277,7 +9286,7 @@
       </c>
       <c r="B148" s="1"/>
       <c r="C148" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
@@ -9293,7 +9302,7 @@
       <c r="O148" s="1"/>
       <c r="P148" s="1"/>
       <c r="Q148" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
@@ -9322,7 +9331,7 @@
       </c>
       <c r="B149" s="1"/>
       <c r="C149" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
@@ -9365,7 +9374,7 @@
       </c>
       <c r="B150" s="1"/>
       <c r="C150" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
@@ -9398,7 +9407,7 @@
       <c r="AF150" s="1"/>
       <c r="AG150" s="29"/>
       <c r="AH150" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI150" s="1"/>
       <c r="AJ150" s="1"/>
@@ -9410,7 +9419,7 @@
       </c>
       <c r="B151" s="1"/>
       <c r="C151" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
@@ -9453,7 +9462,7 @@
       </c>
       <c r="B152" s="1"/>
       <c r="C152" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
@@ -9496,11 +9505,11 @@
       </c>
       <c r="B153" s="1"/>
       <c r="C153" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D153" s="1"/>
       <c r="E153" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F153" s="1"/>
       <c r="G153" s="1"/>
@@ -9531,7 +9540,7 @@
       <c r="AF153" s="1"/>
       <c r="AG153" s="29"/>
       <c r="AH153" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI153" s="1"/>
       <c r="AJ153" s="1"/>
@@ -9543,11 +9552,11 @@
       </c>
       <c r="B154" s="1"/>
       <c r="C154" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D154" s="1"/>
       <c r="E154" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F154" s="1"/>
       <c r="G154" s="1"/>
@@ -9588,11 +9597,11 @@
       </c>
       <c r="B155" s="1"/>
       <c r="C155" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D155" s="1"/>
       <c r="E155" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
@@ -9606,7 +9615,7 @@
       <c r="O155" s="1"/>
       <c r="P155" s="1"/>
       <c r="Q155" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R155" s="1"/>
       <c r="S155" s="1"/>
@@ -9617,7 +9626,7 @@
       <c r="X155" s="1"/>
       <c r="Y155" s="1"/>
       <c r="Z155" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA155" s="1"/>
       <c r="AB155" s="1"/>
@@ -9637,11 +9646,11 @@
       </c>
       <c r="B156" s="1"/>
       <c r="C156" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D156" s="1"/>
       <c r="E156" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
@@ -9682,11 +9691,11 @@
       </c>
       <c r="B157" s="1"/>
       <c r="C157" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D157" s="1"/>
       <c r="E157" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F157" s="1"/>
       <c r="G157" s="1"/>
@@ -9727,14 +9736,14 @@
       </c>
       <c r="B158" s="1"/>
       <c r="C158" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D158" s="1"/>
       <c r="E158" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
@@ -9756,7 +9765,7 @@
       <c r="X158" s="1"/>
       <c r="Y158" s="1"/>
       <c r="Z158" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA158" s="1"/>
       <c r="AB158" s="1"/>
@@ -9766,7 +9775,7 @@
       <c r="AF158" s="1"/>
       <c r="AG158" s="29"/>
       <c r="AH158" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI158" s="1"/>
       <c r="AJ158" s="1"/>
@@ -9778,11 +9787,11 @@
       </c>
       <c r="B159" s="1"/>
       <c r="C159" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D159" s="1"/>
       <c r="E159" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="1"/>
@@ -9805,7 +9814,7 @@
       <c r="X159" s="1"/>
       <c r="Y159" s="1"/>
       <c r="Z159" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA159" s="1"/>
       <c r="AB159" s="1"/>
@@ -9815,7 +9824,7 @@
       <c r="AF159" s="1"/>
       <c r="AG159" s="29"/>
       <c r="AH159" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI159" s="1"/>
       <c r="AJ159" s="1"/>
@@ -9827,11 +9836,11 @@
       </c>
       <c r="B160" s="1"/>
       <c r="C160" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D160" s="1"/>
       <c r="E160" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F160" s="1"/>
       <c r="G160" s="1"/>
@@ -9847,7 +9856,7 @@
       <c r="Q160" s="1"/>
       <c r="R160" s="1"/>
       <c r="S160" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T160" s="1"/>
       <c r="U160" s="1"/>
@@ -9874,11 +9883,11 @@
       </c>
       <c r="B161" s="1"/>
       <c r="C161" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D161" s="1"/>
       <c r="E161" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F161" s="1"/>
       <c r="G161" s="1"/>
@@ -9919,11 +9928,11 @@
       </c>
       <c r="B162" s="1"/>
       <c r="C162" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D162" s="1"/>
       <c r="E162" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F162" s="1"/>
       <c r="G162" s="1"/>
@@ -9946,7 +9955,7 @@
       <c r="X162" s="1"/>
       <c r="Y162" s="1"/>
       <c r="Z162" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA162" s="1"/>
       <c r="AB162" s="1"/>
@@ -9956,7 +9965,7 @@
       <c r="AF162" s="1"/>
       <c r="AG162" s="29"/>
       <c r="AH162" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI162" s="1"/>
       <c r="AJ162" s="1"/>
@@ -9968,11 +9977,11 @@
       </c>
       <c r="B163" s="1"/>
       <c r="C163" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D163" s="1"/>
       <c r="E163" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F163" s="1"/>
       <c r="G163" s="1"/>
@@ -9985,7 +9994,7 @@
       <c r="N163" s="1"/>
       <c r="O163" s="1"/>
       <c r="P163" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
@@ -9997,7 +10006,7 @@
       <c r="X163" s="1"/>
       <c r="Y163" s="1"/>
       <c r="Z163" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA163" s="1"/>
       <c r="AB163" s="1"/>
@@ -10017,7 +10026,7 @@
       </c>
       <c r="B164" s="1"/>
       <c r="C164" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D164" s="3"/>
       <c r="E164" s="8"/>
@@ -10032,7 +10041,7 @@
       <c r="N164" s="3"/>
       <c r="O164" s="3"/>
       <c r="P164" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q164" s="3"/>
       <c r="R164" s="3"/>
@@ -10062,7 +10071,7 @@
       </c>
       <c r="B165" s="1"/>
       <c r="C165" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D165" s="3"/>
       <c r="E165" s="8"/>
@@ -10080,7 +10089,7 @@
       <c r="Q165" s="3"/>
       <c r="R165" s="3"/>
       <c r="S165" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T165" s="1"/>
       <c r="U165" s="1"/>
@@ -10107,7 +10116,7 @@
       </c>
       <c r="B166" s="1"/>
       <c r="C166" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D166" s="1"/>
       <c r="E166" s="8"/>
@@ -10150,7 +10159,7 @@
       </c>
       <c r="B167" s="1"/>
       <c r="C167" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D167" s="1"/>
       <c r="E167" s="8"/>
@@ -10193,7 +10202,7 @@
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D168" s="1"/>
       <c r="E168" s="8"/>
@@ -10236,7 +10245,7 @@
       </c>
       <c r="B169" s="1"/>
       <c r="C169" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D169" s="1"/>
       <c r="E169" s="8"/>
@@ -10279,7 +10288,7 @@
       </c>
       <c r="B170" s="1"/>
       <c r="C170" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D170" s="1"/>
       <c r="E170" s="8"/>
@@ -10322,7 +10331,7 @@
       </c>
       <c r="B171" s="1"/>
       <c r="C171" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D171" s="1"/>
       <c r="E171" s="8"/>
@@ -10365,7 +10374,7 @@
       </c>
       <c r="B172" s="1"/>
       <c r="C172" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D172" s="1"/>
       <c r="E172" s="8"/>
@@ -10380,7 +10389,7 @@
       <c r="N172" s="1"/>
       <c r="O172" s="1"/>
       <c r="P172" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
@@ -10410,7 +10419,7 @@
       </c>
       <c r="B173" s="1"/>
       <c r="C173" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D173" s="1"/>
       <c r="E173" s="8"/>
@@ -10452,15 +10461,15 @@
         <v>171</v>
       </c>
       <c r="B174" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D174" s="1"/>
       <c r="E174" s="8"/>
       <c r="F174" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G174" s="1"/>
       <c r="H174" s="1"/>
@@ -10472,14 +10481,14 @@
       <c r="N174" s="1"/>
       <c r="O174" s="1"/>
       <c r="P174" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q174" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R174" s="1"/>
       <c r="S174" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T174" s="1"/>
       <c r="U174" s="1"/>
@@ -10488,7 +10497,7 @@
       <c r="X174" s="1"/>
       <c r="Y174" s="1"/>
       <c r="Z174" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA174" s="1"/>
       <c r="AB174" s="1"/>
@@ -10498,7 +10507,7 @@
       <c r="AF174" s="1"/>
       <c r="AG174" s="29"/>
       <c r="AH174" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI174" s="1"/>
       <c r="AJ174" s="1"/>
@@ -10509,15 +10518,15 @@
         <v>172</v>
       </c>
       <c r="B175" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D175" s="1"/>
       <c r="E175" s="8"/>
       <c r="F175" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G175" s="1"/>
       <c r="H175" s="1"/>
@@ -10532,7 +10541,7 @@
       <c r="Q175" s="1"/>
       <c r="R175" s="1"/>
       <c r="S175" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T175" s="1"/>
       <c r="U175" s="1"/>
@@ -10541,7 +10550,7 @@
       <c r="X175" s="1"/>
       <c r="Y175" s="1"/>
       <c r="Z175" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA175" s="1"/>
       <c r="AB175" s="1"/>
@@ -10551,7 +10560,7 @@
       <c r="AF175" s="1"/>
       <c r="AG175" s="29"/>
       <c r="AH175" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI175" s="1"/>
       <c r="AJ175" s="1"/>
@@ -10562,15 +10571,15 @@
         <v>173</v>
       </c>
       <c r="B176" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D176" s="1"/>
       <c r="E176" s="8"/>
       <c r="F176" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
@@ -10582,14 +10591,14 @@
       <c r="N176" s="1"/>
       <c r="O176" s="1"/>
       <c r="P176" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q176" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R176" s="1"/>
       <c r="S176" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T176" s="1"/>
       <c r="U176" s="1"/>
@@ -10598,7 +10607,7 @@
       <c r="X176" s="1"/>
       <c r="Y176" s="1"/>
       <c r="Z176" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA176" s="1"/>
       <c r="AB176" s="1"/>
@@ -10608,7 +10617,7 @@
       <c r="AF176" s="1"/>
       <c r="AG176" s="29"/>
       <c r="AH176" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI176" s="1"/>
       <c r="AJ176" s="1"/>
@@ -10619,10 +10628,10 @@
         <v>174</v>
       </c>
       <c r="B177" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D177" s="1"/>
       <c r="E177" s="8"/>
@@ -10640,7 +10649,7 @@
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
       <c r="S177" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T177" s="1"/>
       <c r="U177" s="1"/>
@@ -10666,10 +10675,10 @@
         <v>175</v>
       </c>
       <c r="B178" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D178" s="1"/>
       <c r="E178" s="8"/>
@@ -10687,7 +10696,7 @@
       <c r="Q178" s="1"/>
       <c r="R178" s="1"/>
       <c r="S178" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T178" s="1"/>
       <c r="U178" s="1"/>
@@ -10704,7 +10713,7 @@
       <c r="AF178" s="1"/>
       <c r="AG178" s="29"/>
       <c r="AH178" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI178" s="1"/>
       <c r="AJ178" s="1"/>
@@ -10715,10 +10724,10 @@
         <v>176</v>
       </c>
       <c r="B179" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D179" s="1"/>
       <c r="E179" s="8"/>
@@ -10736,7 +10745,7 @@
       <c r="Q179" s="1"/>
       <c r="R179" s="1"/>
       <c r="S179" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T179" s="1"/>
       <c r="U179" s="1"/>
@@ -10753,7 +10762,7 @@
       <c r="AF179" s="1"/>
       <c r="AG179" s="29"/>
       <c r="AH179" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI179" s="1"/>
       <c r="AJ179" s="1"/>
@@ -10764,10 +10773,10 @@
         <v>177</v>
       </c>
       <c r="B180" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D180" s="1"/>
       <c r="E180" s="8"/>
@@ -10782,12 +10791,12 @@
       <c r="N180" s="1"/>
       <c r="O180" s="1"/>
       <c r="P180" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q180" s="1"/>
       <c r="R180" s="1"/>
       <c r="S180" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T180" s="1"/>
       <c r="U180" s="1"/>
@@ -10804,7 +10813,7 @@
       <c r="AF180" s="1"/>
       <c r="AG180" s="29"/>
       <c r="AH180" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI180" s="1"/>
       <c r="AJ180" s="1"/>
@@ -10815,10 +10824,10 @@
         <v>178</v>
       </c>
       <c r="B181" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D181" s="1"/>
       <c r="E181" s="1"/>
@@ -10836,7 +10845,7 @@
       <c r="Q181" s="1"/>
       <c r="R181" s="1"/>
       <c r="S181" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T181" s="1"/>
       <c r="U181" s="1"/>
@@ -10853,7 +10862,7 @@
       <c r="AF181" s="1"/>
       <c r="AG181" s="29"/>
       <c r="AH181" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI181" s="1"/>
       <c r="AJ181" s="1"/>
@@ -10864,10 +10873,10 @@
         <v>179</v>
       </c>
       <c r="B182" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
@@ -10885,14 +10894,14 @@
       <c r="Q182" s="1"/>
       <c r="R182" s="1"/>
       <c r="S182" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T182" s="1"/>
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
       <c r="W182" s="1"/>
       <c r="X182" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
@@ -10904,7 +10913,7 @@
       <c r="AF182" s="1"/>
       <c r="AG182" s="29"/>
       <c r="AH182" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI182" s="1"/>
       <c r="AJ182" s="1"/>
@@ -10915,10 +10924,10 @@
         <v>180</v>
       </c>
       <c r="B183" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
@@ -10933,23 +10942,23 @@
       <c r="N183" s="1"/>
       <c r="O183" s="1"/>
       <c r="P183" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q183" s="1"/>
       <c r="R183" s="1"/>
       <c r="S183" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T183" s="1"/>
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
       <c r="W183" s="1"/>
       <c r="X183" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y183" s="1"/>
       <c r="Z183" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA183" s="1"/>
       <c r="AB183" s="1"/>
@@ -10959,7 +10968,7 @@
       <c r="AF183" s="1"/>
       <c r="AG183" s="29"/>
       <c r="AH183" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI183" s="1"/>
       <c r="AJ183" s="1"/>
@@ -10970,10 +10979,10 @@
         <v>181</v>
       </c>
       <c r="B184" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
@@ -10988,19 +10997,19 @@
       <c r="N184" s="1"/>
       <c r="O184" s="1"/>
       <c r="P184" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q184" s="1"/>
       <c r="R184" s="1"/>
       <c r="S184" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T184" s="1"/>
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
       <c r="W184" s="1"/>
       <c r="X184" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
@@ -11012,7 +11021,7 @@
       <c r="AF184" s="1"/>
       <c r="AG184" s="29"/>
       <c r="AH184" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI184" s="1"/>
       <c r="AJ184" s="1"/>
@@ -11023,10 +11032,10 @@
         <v>182</v>
       </c>
       <c r="B185" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D185" s="1"/>
       <c r="E185" s="1"/>
@@ -11041,12 +11050,12 @@
       <c r="N185" s="1"/>
       <c r="O185" s="1"/>
       <c r="P185" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q185" s="1"/>
       <c r="R185" s="1"/>
       <c r="S185" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T185" s="1"/>
       <c r="U185" s="1"/>
@@ -11063,7 +11072,7 @@
       <c r="AF185" s="1"/>
       <c r="AG185" s="29"/>
       <c r="AH185" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI185" s="1"/>
       <c r="AJ185" s="1"/>
@@ -11075,7 +11084,7 @@
       </c>
       <c r="B186" s="1"/>
       <c r="C186" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D186" s="1"/>
       <c r="E186" s="1"/>
@@ -11096,13 +11105,13 @@
       <c r="T186" s="1"/>
       <c r="U186" s="1"/>
       <c r="V186" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="W186" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X186" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
@@ -11124,7 +11133,7 @@
       </c>
       <c r="B187" s="1"/>
       <c r="C187" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
@@ -11145,13 +11154,13 @@
       <c r="T187" s="1"/>
       <c r="U187" s="1"/>
       <c r="V187" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="W187" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X187" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
@@ -11173,7 +11182,7 @@
       </c>
       <c r="B188" s="1"/>
       <c r="C188" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
@@ -11188,7 +11197,7 @@
       <c r="N188" s="1"/>
       <c r="O188" s="1"/>
       <c r="P188" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
@@ -11196,13 +11205,13 @@
       <c r="T188" s="1"/>
       <c r="U188" s="1"/>
       <c r="V188" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="W188" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X188" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y188" s="1"/>
       <c r="Z188" s="1"/>
@@ -11224,7 +11233,7 @@
       </c>
       <c r="B189" s="1"/>
       <c r="C189" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
@@ -11245,13 +11254,13 @@
       <c r="T189" s="1"/>
       <c r="U189" s="1"/>
       <c r="V189" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="W189" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X189" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
@@ -11273,7 +11282,7 @@
       </c>
       <c r="B190" s="1"/>
       <c r="C190" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
@@ -11294,13 +11303,13 @@
       <c r="T190" s="1"/>
       <c r="U190" s="1"/>
       <c r="V190" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="W190" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X190" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y190" s="1"/>
       <c r="Z190" s="1"/>
@@ -11322,7 +11331,7 @@
       </c>
       <c r="B191" s="1"/>
       <c r="C191" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
@@ -11343,13 +11352,13 @@
       <c r="T191" s="1"/>
       <c r="U191" s="1"/>
       <c r="V191" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="W191" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X191" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y191" s="1"/>
       <c r="Z191" s="1"/>
@@ -11365,13 +11374,13 @@
       <c r="AJ191" s="1"/>
       <c r="AK191" s="1"/>
     </row>
-    <row r="192" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="192" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A192" s="3">
         <v>189</v>
       </c>
       <c r="B192" s="1"/>
       <c r="C192" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
@@ -11389,10 +11398,10 @@
       <c r="Q192" s="1"/>
       <c r="R192" s="1"/>
       <c r="S192" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T192" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
@@ -11408,19 +11417,19 @@
       <c r="AF192" s="1"/>
       <c r="AG192" s="29"/>
       <c r="AH192" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI192" s="1"/>
       <c r="AJ192" s="1"/>
       <c r="AK192" s="1"/>
     </row>
-    <row r="193" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="193" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A193" s="3">
         <v>190</v>
       </c>
       <c r="B193" s="1"/>
       <c r="C193" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
@@ -11435,13 +11444,13 @@
       <c r="N193" s="1"/>
       <c r="O193" s="1"/>
       <c r="P193" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
       <c r="S193" s="1"/>
       <c r="T193" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
@@ -11461,13 +11470,13 @@
       <c r="AJ193" s="1"/>
       <c r="AK193" s="1"/>
     </row>
-    <row r="194" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="194" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A194" s="3">
         <v>191</v>
       </c>
       <c r="B194" s="1"/>
       <c r="C194" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
@@ -11486,7 +11495,7 @@
       <c r="R194" s="1"/>
       <c r="S194" s="1"/>
       <c r="T194" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
@@ -11506,13 +11515,13 @@
       <c r="AJ194" s="1"/>
       <c r="AK194" s="1"/>
     </row>
-    <row r="195" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="195" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A195" s="3">
         <v>192</v>
       </c>
       <c r="B195" s="1"/>
       <c r="C195" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
@@ -11531,7 +11540,7 @@
       <c r="R195" s="1"/>
       <c r="S195" s="1"/>
       <c r="T195" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
@@ -11551,13 +11560,13 @@
       <c r="AJ195" s="1"/>
       <c r="AK195" s="1"/>
     </row>
-    <row r="196" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="196" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A196" s="3">
         <v>193</v>
       </c>
       <c r="B196" s="1"/>
       <c r="C196" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
@@ -11576,7 +11585,7 @@
       <c r="R196" s="1"/>
       <c r="S196" s="1"/>
       <c r="T196" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
@@ -11596,13 +11605,13 @@
       <c r="AJ196" s="1"/>
       <c r="AK196" s="1"/>
     </row>
-    <row r="197" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="197" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A197" s="3">
         <v>194</v>
       </c>
       <c r="B197" s="1"/>
       <c r="C197" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
@@ -11621,7 +11630,7 @@
       <c r="R197" s="1"/>
       <c r="S197" s="1"/>
       <c r="T197" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
@@ -11641,13 +11650,13 @@
       <c r="AJ197" s="1"/>
       <c r="AK197" s="1"/>
     </row>
-    <row r="198" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="198" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A198" s="3">
         <v>195</v>
       </c>
       <c r="B198" s="1"/>
       <c r="C198" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
@@ -11666,13 +11675,13 @@
       <c r="R198" s="1"/>
       <c r="S198" s="1"/>
       <c r="T198" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
       <c r="W198" s="1"/>
       <c r="X198" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
@@ -11688,13 +11697,13 @@
       <c r="AJ198" s="1"/>
       <c r="AK198" s="1"/>
     </row>
-    <row r="199" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="199" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A199" s="3">
         <v>196</v>
       </c>
       <c r="B199" s="1"/>
       <c r="C199" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
@@ -11713,17 +11722,17 @@
       <c r="R199" s="1"/>
       <c r="S199" s="1"/>
       <c r="T199" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
       <c r="W199" s="1"/>
       <c r="X199" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y199" s="1"/>
       <c r="Z199" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA199" s="1"/>
       <c r="AB199" s="1"/>
@@ -11737,13 +11746,13 @@
       <c r="AJ199" s="1"/>
       <c r="AK199" s="1"/>
     </row>
-    <row r="200" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="200" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A200" s="3">
         <v>197</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
@@ -11762,7 +11771,7 @@
       <c r="R200" s="1"/>
       <c r="S200" s="1"/>
       <c r="T200" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
@@ -11782,13 +11791,13 @@
       <c r="AJ200" s="1"/>
       <c r="AK200" s="1"/>
     </row>
-    <row r="201" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="201" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A201" s="3">
         <v>198</v>
       </c>
       <c r="B201" s="1"/>
       <c r="C201" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
@@ -11807,13 +11816,13 @@
       <c r="R201" s="1"/>
       <c r="S201" s="1"/>
       <c r="T201" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U201" s="1"/>
       <c r="V201" s="1"/>
       <c r="W201" s="1"/>
       <c r="X201" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
@@ -11829,13 +11838,13 @@
       <c r="AJ201" s="1"/>
       <c r="AK201" s="1"/>
     </row>
-    <row r="202" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="202" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A202" s="3">
         <v>199</v>
       </c>
       <c r="B202" s="1"/>
       <c r="C202" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
@@ -11854,7 +11863,7 @@
       <c r="R202" s="1"/>
       <c r="S202" s="1"/>
       <c r="T202" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U202" s="1"/>
       <c r="V202" s="1"/>
@@ -11874,13 +11883,13 @@
       <c r="AJ202" s="1"/>
       <c r="AK202" s="1"/>
     </row>
-    <row r="203" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="203" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A203" s="3">
         <v>200</v>
       </c>
       <c r="B203" s="1"/>
       <c r="C203" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
@@ -11895,13 +11904,13 @@
       <c r="N203" s="1"/>
       <c r="O203" s="1"/>
       <c r="P203" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q203" s="1"/>
       <c r="R203" s="1"/>
       <c r="S203" s="1"/>
       <c r="T203" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U203" s="1"/>
       <c r="V203" s="1"/>
@@ -11921,13 +11930,13 @@
       <c r="AJ203" s="1"/>
       <c r="AK203" s="1"/>
     </row>
-    <row r="204" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="204" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A204" s="3">
         <v>201</v>
       </c>
       <c r="B204" s="1"/>
       <c r="C204" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
@@ -11946,7 +11955,7 @@
       <c r="R204" s="1"/>
       <c r="S204" s="1"/>
       <c r="T204" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U204" s="1"/>
       <c r="V204" s="1"/>
@@ -11966,13 +11975,13 @@
       <c r="AJ204" s="1"/>
       <c r="AK204" s="1"/>
     </row>
-    <row r="205" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="205" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A205" s="3">
         <v>202</v>
       </c>
       <c r="B205" s="1"/>
       <c r="C205" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
@@ -11991,7 +12000,7 @@
       <c r="R205" s="1"/>
       <c r="S205" s="1"/>
       <c r="T205" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U205" s="1"/>
       <c r="V205" s="1"/>
@@ -12011,13 +12020,13 @@
       <c r="AJ205" s="1"/>
       <c r="AK205" s="1"/>
     </row>
-    <row r="206" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="206" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A206" s="3">
         <v>203</v>
       </c>
       <c r="B206" s="1"/>
       <c r="C206" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
@@ -12036,7 +12045,7 @@
       <c r="R206" s="1"/>
       <c r="S206" s="1"/>
       <c r="T206" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U206" s="1"/>
       <c r="V206" s="1"/>
@@ -12056,13 +12065,13 @@
       <c r="AJ206" s="1"/>
       <c r="AK206" s="1"/>
     </row>
-    <row r="207" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="207" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A207" s="3">
         <v>204</v>
       </c>
       <c r="B207" s="1"/>
       <c r="C207" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
@@ -12077,13 +12086,13 @@
       <c r="N207" s="1"/>
       <c r="O207" s="1"/>
       <c r="P207" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q207" s="1"/>
       <c r="R207" s="1"/>
       <c r="S207" s="1"/>
       <c r="T207" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U207" s="1"/>
       <c r="V207" s="1"/>
@@ -12103,13 +12112,13 @@
       <c r="AJ207" s="1"/>
       <c r="AK207" s="1"/>
     </row>
-    <row r="208" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="208" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A208" s="3">
         <v>205</v>
       </c>
       <c r="B208" s="1"/>
       <c r="C208" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
@@ -12128,7 +12137,7 @@
       <c r="R208" s="1"/>
       <c r="S208" s="1"/>
       <c r="T208" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U208" s="1"/>
       <c r="V208" s="1"/>
@@ -12148,13 +12157,13 @@
       <c r="AJ208" s="1"/>
       <c r="AK208" s="1"/>
     </row>
-    <row r="209" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="209" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A209" s="3">
         <v>206</v>
       </c>
       <c r="B209" s="1"/>
       <c r="C209" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
@@ -12173,7 +12182,7 @@
       <c r="R209" s="1"/>
       <c r="S209" s="1"/>
       <c r="T209" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U209" s="1"/>
       <c r="V209" s="1"/>
@@ -12189,19 +12198,19 @@
       <c r="AF209" s="1"/>
       <c r="AG209" s="29"/>
       <c r="AH209" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI209" s="1"/>
       <c r="AJ209" s="1"/>
       <c r="AK209" s="1"/>
     </row>
-    <row r="210" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="210" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A210" s="3">
         <v>207</v>
       </c>
       <c r="B210" s="1"/>
       <c r="C210" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
@@ -12220,7 +12229,7 @@
       <c r="R210" s="1"/>
       <c r="S210" s="1"/>
       <c r="T210" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U210" s="1"/>
       <c r="V210" s="1"/>
@@ -12240,13 +12249,13 @@
       <c r="AJ210" s="1"/>
       <c r="AK210" s="1"/>
     </row>
-    <row r="211" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="211" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A211" s="3">
         <v>208</v>
       </c>
       <c r="B211" s="1"/>
       <c r="C211" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
@@ -12265,7 +12274,7 @@
       <c r="R211" s="1"/>
       <c r="S211" s="1"/>
       <c r="T211" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
@@ -12285,13 +12294,13 @@
       <c r="AJ211" s="1"/>
       <c r="AK211" s="1"/>
     </row>
-    <row r="212" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="212" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A212" s="3">
         <v>209</v>
       </c>
       <c r="B212" s="1"/>
       <c r="C212" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
@@ -12310,7 +12319,7 @@
       <c r="R212" s="1"/>
       <c r="S212" s="1"/>
       <c r="T212" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
@@ -12330,13 +12339,13 @@
       <c r="AJ212" s="1"/>
       <c r="AK212" s="1"/>
     </row>
-    <row r="213" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="213" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A213" s="3">
         <v>210</v>
       </c>
       <c r="B213" s="1"/>
       <c r="C213" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
@@ -12355,7 +12364,7 @@
       <c r="R213" s="1"/>
       <c r="S213" s="1"/>
       <c r="T213" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
@@ -12375,13 +12384,13 @@
       <c r="AJ213" s="1"/>
       <c r="AK213" s="1"/>
     </row>
-    <row r="214" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="214" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A214" s="3">
         <v>211</v>
       </c>
       <c r="B214" s="1"/>
       <c r="C214" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
@@ -12400,7 +12409,7 @@
       <c r="R214" s="1"/>
       <c r="S214" s="1"/>
       <c r="T214" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U214" s="1"/>
       <c r="V214" s="1"/>
@@ -12408,7 +12417,7 @@
       <c r="X214" s="1"/>
       <c r="Y214" s="1"/>
       <c r="Z214" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA214" s="1"/>
       <c r="AB214" s="1"/>
@@ -12428,7 +12437,7 @@
       </c>
       <c r="B215" s="1"/>
       <c r="C215" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
@@ -12443,7 +12452,7 @@
       <c r="N215" s="1"/>
       <c r="O215" s="1"/>
       <c r="P215" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q215" s="1"/>
       <c r="R215" s="1"/>
@@ -12463,21 +12472,21 @@
       <c r="AF215" s="1"/>
       <c r="AG215" s="29"/>
       <c r="AH215" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI215" s="1"/>
       <c r="AJ215" s="1"/>
       <c r="AK215" s="1"/>
     </row>
-    <row r="216" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="216" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A216" s="3">
         <v>213</v>
       </c>
       <c r="B216" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
@@ -12496,17 +12505,17 @@
       <c r="R216" s="1"/>
       <c r="S216" s="1"/>
       <c r="T216" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U216" s="1"/>
       <c r="V216" s="1"/>
       <c r="W216" s="1"/>
       <c r="X216" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y216" s="1"/>
       <c r="Z216" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA216" s="1"/>
       <c r="AB216" s="1"/>
@@ -12520,15 +12529,15 @@
       <c r="AJ216" s="1"/>
       <c r="AK216" s="1"/>
     </row>
-    <row r="217" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="217" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A217" s="3">
         <v>214</v>
       </c>
       <c r="B217" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
@@ -12547,17 +12556,17 @@
       <c r="R217" s="1"/>
       <c r="S217" s="1"/>
       <c r="T217" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U217" s="1"/>
       <c r="V217" s="1"/>
       <c r="W217" s="1"/>
       <c r="X217" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y217" s="1"/>
       <c r="Z217" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA217" s="1"/>
       <c r="AB217" s="1"/>
@@ -12571,15 +12580,15 @@
       <c r="AJ217" s="1"/>
       <c r="AK217" s="1"/>
     </row>
-    <row r="218" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="218" spans="1:37" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A218" s="3">
         <v>215</v>
       </c>
       <c r="B218" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
@@ -12598,17 +12607,17 @@
       <c r="R218" s="1"/>
       <c r="S218" s="1"/>
       <c r="T218" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U218" s="1"/>
       <c r="V218" s="1"/>
       <c r="W218" s="1"/>
       <c r="X218" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y218" s="1"/>
       <c r="Z218" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA218" s="1"/>
       <c r="AB218" s="1"/>
@@ -12618,7 +12627,7 @@
       <c r="AF218" s="1"/>
       <c r="AG218" s="29"/>
       <c r="AH218" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI218" s="1"/>
       <c r="AJ218" s="1"/>
@@ -12630,7 +12639,7 @@
       </c>
       <c r="B219" s="1"/>
       <c r="C219" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
@@ -12673,7 +12682,7 @@
       </c>
       <c r="B220" s="1"/>
       <c r="C220" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
@@ -12716,7 +12725,7 @@
       </c>
       <c r="B221" s="1"/>
       <c r="C221" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
@@ -12758,10 +12767,10 @@
         <v>219</v>
       </c>
       <c r="B222" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
@@ -12804,7 +12813,7 @@
       </c>
       <c r="B223" s="1"/>
       <c r="C223" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
@@ -12847,7 +12856,7 @@
       </c>
       <c r="B224" s="1"/>
       <c r="C224" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
@@ -12890,7 +12899,7 @@
       </c>
       <c r="B225" s="1"/>
       <c r="C225" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
@@ -12933,7 +12942,7 @@
       </c>
       <c r="B226" s="1"/>
       <c r="C226" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
@@ -12976,7 +12985,7 @@
       </c>
       <c r="B227" s="1"/>
       <c r="C227" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
@@ -13019,7 +13028,7 @@
       </c>
       <c r="B228" s="1"/>
       <c r="C228" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
@@ -13062,7 +13071,7 @@
       </c>
       <c r="B229" s="1"/>
       <c r="C229" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
@@ -13105,7 +13114,7 @@
       </c>
       <c r="B230" s="1"/>
       <c r="C230" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
@@ -13148,7 +13157,7 @@
       </c>
       <c r="B231" s="1"/>
       <c r="C231" s="21" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
@@ -13191,7 +13200,7 @@
       </c>
       <c r="B232" s="1"/>
       <c r="C232" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
@@ -13233,10 +13242,10 @@
         <v>230</v>
       </c>
       <c r="B233" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C233" s="22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
@@ -13261,7 +13270,7 @@
       <c r="X233" s="1"/>
       <c r="Y233" s="1"/>
       <c r="Z233" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA233" s="1"/>
       <c r="AB233" s="1"/>
@@ -13281,7 +13290,7 @@
       </c>
       <c r="B234" s="1"/>
       <c r="C234" s="21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
@@ -13324,7 +13333,7 @@
       </c>
       <c r="B235" s="1"/>
       <c r="C235" s="21" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
@@ -13342,7 +13351,7 @@
       <c r="Q235" s="1"/>
       <c r="R235" s="1"/>
       <c r="S235" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T235" s="1"/>
       <c r="U235" s="1"/>
@@ -13359,7 +13368,7 @@
       <c r="AF235" s="1"/>
       <c r="AG235" s="29"/>
       <c r="AH235" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI235" s="1"/>
       <c r="AJ235" s="1"/>
@@ -13371,7 +13380,7 @@
       </c>
       <c r="B236" s="1"/>
       <c r="C236" s="21" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
@@ -13414,7 +13423,7 @@
       </c>
       <c r="B237" s="1"/>
       <c r="C237" s="21" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
@@ -13457,7 +13466,7 @@
       </c>
       <c r="B238" s="1"/>
       <c r="C238" s="21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
@@ -13500,7 +13509,7 @@
       </c>
       <c r="B239" s="1"/>
       <c r="C239" s="21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
@@ -13543,7 +13552,7 @@
       </c>
       <c r="B240" s="1"/>
       <c r="C240" s="21" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
@@ -13586,7 +13595,7 @@
       </c>
       <c r="B241" s="1"/>
       <c r="C241" s="21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
@@ -13629,7 +13638,7 @@
       </c>
       <c r="B242" s="1"/>
       <c r="C242" s="21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
@@ -13672,7 +13681,7 @@
       </c>
       <c r="B243" s="3"/>
       <c r="C243" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
@@ -13690,7 +13699,7 @@
       <c r="Q243" s="1"/>
       <c r="R243" s="1"/>
       <c r="S243" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T243" s="1"/>
       <c r="U243" s="1"/>
@@ -13717,7 +13726,7 @@
       </c>
       <c r="B244" s="3"/>
       <c r="C244" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
@@ -13735,7 +13744,7 @@
       <c r="Q244" s="1"/>
       <c r="R244" s="1"/>
       <c r="S244" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T244" s="1"/>
       <c r="U244" s="1"/>
@@ -13762,7 +13771,7 @@
       </c>
       <c r="B245" s="3"/>
       <c r="C245" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
@@ -13780,7 +13789,7 @@
       <c r="Q245" s="1"/>
       <c r="R245" s="1"/>
       <c r="S245" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T245" s="1"/>
       <c r="U245" s="1"/>
@@ -13807,7 +13816,7 @@
       </c>
       <c r="B246" s="3"/>
       <c r="C246" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
@@ -13830,7 +13839,7 @@
       <c r="V246" s="1"/>
       <c r="W246" s="1"/>
       <c r="X246" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y246" s="1"/>
       <c r="Z246" s="1"/>
@@ -13852,7 +13861,7 @@
       </c>
       <c r="B247" s="3"/>
       <c r="C247" s="21" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
@@ -13875,7 +13884,7 @@
       <c r="V247" s="1"/>
       <c r="W247" s="1"/>
       <c r="X247" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y247" s="1"/>
       <c r="Z247" s="1"/>
@@ -13897,7 +13906,7 @@
       </c>
       <c r="B248" s="3"/>
       <c r="C248" s="21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
@@ -13920,11 +13929,11 @@
       <c r="V248" s="1"/>
       <c r="W248" s="1"/>
       <c r="X248" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y248" s="1"/>
       <c r="Z248" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA248" s="1"/>
       <c r="AB248" s="1"/>
@@ -13944,7 +13953,7 @@
       </c>
       <c r="B249" s="3"/>
       <c r="C249" s="21" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
@@ -13987,7 +13996,7 @@
       </c>
       <c r="B250" s="3"/>
       <c r="C250" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
@@ -14030,7 +14039,7 @@
       </c>
       <c r="B251" s="3"/>
       <c r="C251" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
@@ -14073,7 +14082,7 @@
       </c>
       <c r="B252" s="3"/>
       <c r="C252" s="21" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
@@ -14116,7 +14125,7 @@
       </c>
       <c r="B253" s="3"/>
       <c r="C253" s="21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
@@ -14159,7 +14168,7 @@
       </c>
       <c r="B254" s="3"/>
       <c r="C254" s="21" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
@@ -14202,7 +14211,7 @@
       </c>
       <c r="B255" s="3"/>
       <c r="C255" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
@@ -14245,7 +14254,7 @@
       </c>
       <c r="B256" s="3"/>
       <c r="C256" s="31" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
@@ -14270,7 +14279,7 @@
       <c r="X256" s="1"/>
       <c r="Y256" s="1"/>
       <c r="Z256" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA256" s="1"/>
       <c r="AB256" s="1"/>
@@ -14280,7 +14289,7 @@
       <c r="AF256" s="1"/>
       <c r="AG256" s="29"/>
       <c r="AH256" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI256" s="1"/>
       <c r="AJ256" s="1"/>
@@ -14292,7 +14301,7 @@
       </c>
       <c r="B257" s="3"/>
       <c r="C257" s="21" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
@@ -14325,7 +14334,7 @@
       <c r="AF257" s="1"/>
       <c r="AG257" s="29"/>
       <c r="AH257" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI257" s="1"/>
       <c r="AJ257" s="1"/>
@@ -14337,7 +14346,7 @@
       </c>
       <c r="B258" s="3"/>
       <c r="C258" s="21" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
@@ -14370,7 +14379,7 @@
       <c r="AF258" s="1"/>
       <c r="AG258" s="29"/>
       <c r="AH258" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI258" s="1"/>
       <c r="AJ258" s="1"/>
@@ -14382,7 +14391,7 @@
       </c>
       <c r="B259" s="3"/>
       <c r="C259" s="21" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
@@ -14415,7 +14424,7 @@
       <c r="AF259" s="1"/>
       <c r="AG259" s="29"/>
       <c r="AH259" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI259" s="1"/>
       <c r="AJ259" s="1"/>
@@ -14427,7 +14436,7 @@
       </c>
       <c r="B260" s="3"/>
       <c r="C260" s="21" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
@@ -14460,7 +14469,7 @@
       <c r="AF260" s="1"/>
       <c r="AG260" s="29"/>
       <c r="AH260" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AI260" s="1"/>
       <c r="AJ260" s="1"/>
@@ -15287,7 +15296,11 @@
       <c r="AK280" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AB280" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:AB280" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="19">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="4">
     <mergeCell ref="C1:C3"/>
     <mergeCell ref="A1:A3"/>
@@ -15324,30 +15337,30 @@
     <row r="2" spans="1:8">
       <c r="A2" s="14"/>
       <c r="B2" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="D2" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="E2" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="F2" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="H2" s="15" t="s">
         <v>236</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -15359,31 +15372,33 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="H4" s="18"/>
+        <v>156</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -15395,10 +15410,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -15409,10 +15424,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -15423,7 +15438,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
@@ -15435,7 +15450,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
@@ -15447,7 +15462,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -15459,10 +15474,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
@@ -15473,7 +15488,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -15485,7 +15500,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -15497,7 +15512,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -15509,13 +15524,13 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
@@ -15525,29 +15540,31 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="19" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E16" s="25"/>
       <c r="F16" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="H16" s="18"/>
+        <v>156</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
@@ -15559,79 +15576,83 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="19" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="H18" s="18"/>
+        <v>156</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="H20" s="18"/>
+        <v>156</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -15643,7 +15664,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -15655,7 +15676,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -15667,31 +15688,29 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D24" s="25"/>
       <c r="E24" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>157</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="H24" s="18"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -15703,19 +15722,29 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
+        <v>267</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="E26" s="25"/>
+      <c r="F26" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>156</v>
+      </c>
       <c r="H26" s="18"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -15727,7 +15756,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -15739,7 +15768,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
@@ -15751,7 +15780,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="19" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B30" s="18"/>
       <c r="C30" s="18"/>
@@ -15763,7 +15792,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="19" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
@@ -15775,7 +15804,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="19" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
@@ -15787,48 +15816,56 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="19" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H33" s="18"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="19" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
+        <v>156</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="25"/>
+      <c r="E34" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>156</v>
+      </c>
       <c r="H34" s="18"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="19" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C35" s="18"/>
       <c r="D35" s="18"/>
@@ -17198,6 +17235,7 @@
       <c r="H171" s="18"/>
     </row>
   </sheetData>
+  <autoFilter ref="A2:H35" xr:uid="{8513D353-BD33-4F18-8682-09CF4EA59EE5}"/>
   <phoneticPr fontId="2"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:H171" xr:uid="{4997AC82-12EC-4AE6-8FAD-17E499A10CEB}">
@@ -17223,16 +17261,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="28" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E1" s="28"/>
     </row>
@@ -17243,7 +17281,7 @@
       <c r="B2" s="26"/>
       <c r="C2" s="3"/>
       <c r="D2" s="26" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -17254,7 +17292,7 @@
       <c r="B3" s="26"/>
       <c r="C3" s="3"/>
       <c r="D3" s="26" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E3" s="3"/>
     </row>
@@ -17265,7 +17303,7 @@
       <c r="B4" s="26"/>
       <c r="C4" s="3"/>
       <c r="D4" s="26" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E4" s="3"/>
     </row>
@@ -17276,7 +17314,7 @@
       <c r="B5" s="26"/>
       <c r="C5" s="3"/>
       <c r="D5" s="26" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E5" s="3"/>
     </row>
@@ -17287,7 +17325,7 @@
       <c r="B6" s="26"/>
       <c r="C6" s="3"/>
       <c r="D6" s="26" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E6" s="3"/>
     </row>
@@ -17298,7 +17336,7 @@
       <c r="B7" s="26"/>
       <c r="C7" s="3"/>
       <c r="D7" s="26" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E7" s="3"/>
     </row>
@@ -17309,7 +17347,7 @@
       <c r="B8" s="26"/>
       <c r="C8" s="3"/>
       <c r="D8" s="26" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -17320,7 +17358,7 @@
       <c r="B9" s="26"/>
       <c r="C9" s="3"/>
       <c r="D9" s="26" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E9" s="3"/>
     </row>
@@ -17331,7 +17369,7 @@
       <c r="B10" s="26"/>
       <c r="C10" s="3"/>
       <c r="D10" s="26" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E10" s="3"/>
     </row>
@@ -17342,7 +17380,7 @@
       <c r="B11" s="26"/>
       <c r="C11" s="3"/>
       <c r="D11" s="26" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E11" s="3"/>
     </row>
@@ -17353,7 +17391,7 @@
       <c r="B12" s="26"/>
       <c r="C12" s="3"/>
       <c r="D12" s="26" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E12" s="3"/>
     </row>
@@ -17364,7 +17402,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="3"/>
       <c r="D13" s="26" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E13" s="3"/>
     </row>
@@ -17375,7 +17413,7 @@
       <c r="B14" s="26"/>
       <c r="C14" s="3"/>
       <c r="D14" s="26" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E14" s="3"/>
     </row>
@@ -17386,7 +17424,7 @@
       <c r="B15" s="26"/>
       <c r="C15" s="3"/>
       <c r="D15" s="26" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E15" s="3"/>
     </row>
@@ -17397,7 +17435,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="3"/>
       <c r="D16" s="26" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E16" s="3"/>
     </row>
@@ -17408,7 +17446,7 @@
       <c r="B17" s="26"/>
       <c r="C17" s="3"/>
       <c r="D17" s="26" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E17" s="3"/>
     </row>
@@ -17419,7 +17457,7 @@
       <c r="B18" s="26"/>
       <c r="C18" s="3"/>
       <c r="D18" s="26" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E18" s="3"/>
     </row>
@@ -17430,7 +17468,7 @@
       <c r="B19" s="26"/>
       <c r="C19" s="3"/>
       <c r="D19" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E19" s="3"/>
     </row>
@@ -17441,7 +17479,7 @@
       <c r="B20" s="26"/>
       <c r="C20" s="3"/>
       <c r="D20" s="26" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E20" s="3"/>
     </row>
@@ -17452,7 +17490,7 @@
       <c r="B21" s="26"/>
       <c r="C21" s="3"/>
       <c r="D21" s="26" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E21" s="3"/>
     </row>
@@ -17463,7 +17501,7 @@
       <c r="B22" s="26"/>
       <c r="C22" s="3"/>
       <c r="D22" s="26" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E22" s="3"/>
     </row>
@@ -17474,7 +17512,7 @@
       <c r="B23" s="26"/>
       <c r="C23" s="3"/>
       <c r="D23" s="26" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E23" s="3"/>
     </row>
@@ -17485,7 +17523,7 @@
       <c r="B24" s="26"/>
       <c r="C24" s="3"/>
       <c r="D24" s="26" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E24" s="3"/>
     </row>
@@ -17496,7 +17534,7 @@
       <c r="B25" s="26"/>
       <c r="C25" s="3"/>
       <c r="D25" s="26" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E25" s="3"/>
     </row>
@@ -17507,7 +17545,7 @@
       <c r="B26" s="26"/>
       <c r="C26" s="3"/>
       <c r="D26" s="26" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E26" s="3"/>
     </row>
@@ -17518,7 +17556,7 @@
       <c r="B27" s="26"/>
       <c r="C27" s="3"/>
       <c r="D27" s="26" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E27" s="3"/>
     </row>
@@ -17529,7 +17567,7 @@
       <c r="B28" s="26"/>
       <c r="C28" s="3"/>
       <c r="D28" s="26" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E28" s="3"/>
     </row>
@@ -17540,7 +17578,7 @@
       <c r="B29" s="26"/>
       <c r="C29" s="3"/>
       <c r="D29" s="26" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E29" s="3"/>
     </row>
@@ -17551,7 +17589,7 @@
       <c r="B30" s="26"/>
       <c r="C30" s="3"/>
       <c r="D30" s="26" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E30" s="3"/>
     </row>
@@ -17562,7 +17600,7 @@
       <c r="B31" s="26"/>
       <c r="C31" s="3"/>
       <c r="D31" s="26" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E31" s="3"/>
     </row>
@@ -17573,7 +17611,7 @@
       <c r="B32" s="26"/>
       <c r="C32" s="3"/>
       <c r="D32" s="26" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E32" s="3"/>
     </row>
@@ -17584,7 +17622,7 @@
       <c r="B33" s="26"/>
       <c r="C33" s="3"/>
       <c r="D33" s="26" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E33" s="3"/>
     </row>
@@ -17593,14 +17631,14 @@
         <v>33</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="26" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -17608,14 +17646,14 @@
         <v>34</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="26" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -17623,14 +17661,14 @@
         <v>35</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="26" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -17638,14 +17676,14 @@
         <v>36</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="26" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -17653,14 +17691,14 @@
         <v>37</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="26" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -17668,14 +17706,14 @@
         <v>38</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="26" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -17683,14 +17721,14 @@
         <v>39</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="26" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -17698,14 +17736,14 @@
         <v>40</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="26" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -17713,14 +17751,14 @@
         <v>41</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="26" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -17728,14 +17766,14 @@
         <v>42</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="26" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -17743,14 +17781,14 @@
         <v>43</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="26" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -17758,14 +17796,14 @@
         <v>44</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="26" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -17773,14 +17811,14 @@
         <v>45</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="26" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -17788,14 +17826,14 @@
         <v>46</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -17803,14 +17841,14 @@
         <v>47</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="26" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -17818,14 +17856,14 @@
         <v>48</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="26" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -17833,11 +17871,11 @@
         <v>49</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="26" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E50" s="3"/>
     </row>
@@ -17846,11 +17884,11 @@
         <v>50</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="26" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E51" s="3"/>
     </row>
@@ -17859,11 +17897,11 @@
         <v>51</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="26" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E52" s="3"/>
     </row>
@@ -17872,11 +17910,11 @@
         <v>52</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="26" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E53" s="3"/>
     </row>
@@ -17885,11 +17923,11 @@
         <v>53</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="26" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E54" s="3"/>
     </row>
@@ -17898,11 +17936,11 @@
         <v>54</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="26" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E55" s="3"/>
     </row>
@@ -17911,11 +17949,11 @@
         <v>55</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="26" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E56" s="3"/>
     </row>
@@ -17924,11 +17962,11 @@
         <v>56</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="26" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E57" s="3"/>
     </row>
@@ -17937,11 +17975,11 @@
         <v>57</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="26" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E58" s="3"/>
     </row>
@@ -17950,11 +17988,11 @@
         <v>58</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="26" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E59" s="3"/>
     </row>
@@ -17963,11 +18001,11 @@
         <v>59</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="26" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E60" s="3"/>
     </row>
@@ -17976,11 +18014,11 @@
         <v>60</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="26" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E61" s="3"/>
     </row>
@@ -17989,11 +18027,11 @@
         <v>61</v>
       </c>
       <c r="B62" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="26" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E62" s="3"/>
     </row>
@@ -18002,11 +18040,11 @@
         <v>62</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="26" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E63" s="3"/>
     </row>
@@ -18015,11 +18053,11 @@
         <v>63</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="26" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E64" s="3"/>
     </row>
@@ -18028,11 +18066,11 @@
         <v>64</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="26" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E65" s="3"/>
     </row>
@@ -18041,11 +18079,11 @@
         <v>65</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="26" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E66" s="3"/>
     </row>
@@ -18054,11 +18092,11 @@
         <v>66</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="26" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E67" s="3"/>
     </row>
@@ -18067,11 +18105,11 @@
         <v>67</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="26" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E68" s="3"/>
     </row>
@@ -18080,11 +18118,11 @@
         <v>68</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C69" s="3"/>
       <c r="D69" s="26" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E69" s="3"/>
     </row>
@@ -18093,13 +18131,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D70" s="27" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E70" s="3"/>
     </row>
@@ -18108,13 +18146,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E71" s="3"/>
     </row>
@@ -18123,16 +18161,16 @@
         <v>71</v>
       </c>
       <c r="B72" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -18140,16 +18178,16 @@
         <v>72</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -18159,7 +18197,7 @@
       <c r="B74" s="26"/>
       <c r="C74" s="3"/>
       <c r="D74" s="26" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E74" s="3"/>
     </row>
@@ -18170,7 +18208,7 @@
       <c r="B75" s="26"/>
       <c r="C75" s="3"/>
       <c r="D75" s="26" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E75" s="3"/>
     </row>
@@ -18179,16 +18217,16 @@
         <v>75</v>
       </c>
       <c r="B76" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D76" s="27" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -18196,16 +18234,16 @@
         <v>76</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D77" s="27" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -18213,13 +18251,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D78" s="27" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E78" s="3"/>
     </row>
@@ -18228,13 +18266,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E79" s="3"/>
     </row>
@@ -18243,13 +18281,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E80" s="3"/>
     </row>
@@ -18258,14 +18296,14 @@
         <v>80</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="26" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -18273,14 +18311,14 @@
         <v>81</v>
       </c>
       <c r="B82" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="26" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -18288,11 +18326,11 @@
         <v>82</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C83" s="3"/>
       <c r="D83" s="26" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E83" s="3"/>
     </row>
@@ -18301,11 +18339,11 @@
         <v>83</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="26" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E84" s="3"/>
     </row>
@@ -18314,11 +18352,11 @@
         <v>84</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="26" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E85" s="3"/>
     </row>
@@ -18327,14 +18365,14 @@
         <v>85</v>
       </c>
       <c r="B86" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="26" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -18342,11 +18380,11 @@
         <v>86</v>
       </c>
       <c r="B87" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C87" s="3"/>
       <c r="D87" s="26" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E87" s="3"/>
     </row>
@@ -18355,14 +18393,14 @@
         <v>87</v>
       </c>
       <c r="B88" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C88" s="3"/>
       <c r="D88" s="26" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -18370,13 +18408,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D89" s="27" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E89" s="3"/>
     </row>
@@ -18385,11 +18423,11 @@
         <v>89</v>
       </c>
       <c r="B90" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="26" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E90" s="3"/>
     </row>
@@ -18398,11 +18436,11 @@
         <v>90</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C91" s="3"/>
       <c r="D91" s="26" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E91" s="3"/>
     </row>
@@ -18411,11 +18449,11 @@
         <v>91</v>
       </c>
       <c r="B92" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="26" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E92" s="3"/>
     </row>
@@ -18424,13 +18462,13 @@
         <v>92</v>
       </c>
       <c r="B93" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E93" s="3"/>
     </row>

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00707E4D-BA90-46B3-A75F-E1513C15AF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68451A0-46C1-44C5-B898-55EADB80803D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="リスト" sheetId="1" r:id="rId1"/>
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="409">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -1955,6 +1955,13 @@
   </si>
   <si>
     <t>ほー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>困ったな</t>
+    <rPh sb="0" eb="1">
+      <t>コマ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2200,7 +2207,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2313,6 +2320,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2701,7 +2715,9 @@
     <col min="3" max="3" width="33.75" bestFit="1" customWidth="1"/>
     <col min="4" max="9" width="3.5625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="2.5625" bestFit="1" customWidth="1"/>
-    <col min="11" max="37" width="3.5625" bestFit="1" customWidth="1"/>
+    <col min="11" max="19" width="3.5625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.5625" style="44" bestFit="1" customWidth="1"/>
+    <col min="21" max="37" width="3.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="22.9">
@@ -2730,7 +2746,7 @@
       <c r="Q1" s="38"/>
       <c r="R1" s="38"/>
       <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
+      <c r="T1" s="42"/>
       <c r="U1" s="38"/>
       <c r="V1" s="38"/>
       <c r="W1" s="38"/>
@@ -2924,7 +2940,9 @@
       <c r="S4" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T4" s="1"/>
+      <c r="T4" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
@@ -2979,7 +2997,9 @@
       <c r="S5" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T5" s="1"/>
+      <c r="T5" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
@@ -3030,7 +3050,9 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
+      <c r="T6" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
@@ -3077,7 +3099,9 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
+      <c r="T7" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
@@ -3120,7 +3144,9 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
+      <c r="T8" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
@@ -3165,7 +3191,9 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
+      <c r="T9" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
@@ -3208,7 +3236,7 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
+      <c r="T10" s="43"/>
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
@@ -3253,7 +3281,9 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
+      <c r="T11" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
@@ -3298,7 +3328,7 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
+      <c r="T12" s="43"/>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
@@ -3341,7 +3371,7 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
+      <c r="T13" s="43"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
@@ -3384,7 +3414,7 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
+      <c r="T14" s="43"/>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
@@ -3427,7 +3457,7 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
+      <c r="T15" s="43"/>
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
@@ -3470,7 +3500,7 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
+      <c r="T16" s="43"/>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
@@ -3513,7 +3543,7 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
+      <c r="T17" s="43"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
@@ -3556,7 +3586,7 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
+      <c r="T18" s="43"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
@@ -3601,7 +3631,7 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
+      <c r="T19" s="43"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
@@ -3644,7 +3674,9 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
+      <c r="T20" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
@@ -3687,7 +3719,7 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
+      <c r="T21" s="43"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
@@ -3734,7 +3766,7 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
+      <c r="T22" s="43"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
@@ -3777,7 +3809,7 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
+      <c r="T23" s="43"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
@@ -3820,7 +3852,9 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
+      <c r="T24" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
@@ -3867,7 +3901,9 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
+      <c r="T25" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
@@ -3912,7 +3948,7 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
+      <c r="T26" s="43"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
@@ -3957,7 +3993,7 @@
       </c>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
+      <c r="T27" s="43"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
@@ -4000,7 +4036,7 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
+      <c r="T28" s="43"/>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
@@ -4043,7 +4079,7 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
+      <c r="T29" s="43"/>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
@@ -4086,7 +4122,7 @@
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
+      <c r="T30" s="43"/>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
@@ -4137,7 +4173,7 @@
       </c>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
+      <c r="T31" s="43"/>
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
@@ -4184,7 +4220,7 @@
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
+      <c r="T32" s="43"/>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
@@ -4227,7 +4263,9 @@
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
+      <c r="T33" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
@@ -4270,7 +4308,7 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
+      <c r="T34" s="43"/>
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
@@ -4313,7 +4351,7 @@
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
+      <c r="T35" s="43"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
@@ -4356,7 +4394,9 @@
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
+      <c r="T36" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
@@ -4399,7 +4439,7 @@
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
+      <c r="T37" s="43"/>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
@@ -4442,7 +4482,7 @@
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
+      <c r="T38" s="43"/>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
@@ -4485,7 +4525,9 @@
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
+      <c r="T39" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
@@ -4530,7 +4572,7 @@
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
-      <c r="T40" s="1"/>
+      <c r="T40" s="43"/>
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
@@ -4575,7 +4617,7 @@
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
+      <c r="T41" s="43"/>
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
@@ -4620,7 +4662,7 @@
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
+      <c r="T42" s="43"/>
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
@@ -4663,7 +4705,7 @@
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
+      <c r="T43" s="43"/>
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
@@ -4708,7 +4750,9 @@
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
+      <c r="T44" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
@@ -4751,7 +4795,7 @@
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
-      <c r="T45" s="1"/>
+      <c r="T45" s="43"/>
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
@@ -4794,7 +4838,7 @@
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
+      <c r="T46" s="43"/>
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
       <c r="W46" s="1"/>
@@ -4837,7 +4881,7 @@
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
-      <c r="T47" s="1"/>
+      <c r="T47" s="43"/>
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
       <c r="W47" s="1"/>
@@ -4880,7 +4924,9 @@
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
-      <c r="T48" s="1"/>
+      <c r="T48" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
@@ -4927,7 +4973,7 @@
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
-      <c r="T49" s="1"/>
+      <c r="T49" s="43"/>
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
       <c r="W49" s="1"/>
@@ -4970,7 +5016,7 @@
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
-      <c r="T50" s="1"/>
+      <c r="T50" s="43"/>
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
@@ -5015,7 +5061,7 @@
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
-      <c r="T51" s="1"/>
+      <c r="T51" s="43"/>
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
       <c r="W51" s="1"/>
@@ -5058,7 +5104,7 @@
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
-      <c r="T52" s="1"/>
+      <c r="T52" s="43"/>
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
       <c r="W52" s="1"/>
@@ -5101,7 +5147,7 @@
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
-      <c r="T53" s="1"/>
+      <c r="T53" s="43"/>
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
       <c r="W53" s="1"/>
@@ -5144,7 +5190,7 @@
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
-      <c r="T54" s="1"/>
+      <c r="T54" s="43"/>
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
@@ -5189,7 +5235,9 @@
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
-      <c r="T55" s="1"/>
+      <c r="T55" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
       <c r="W55" s="1"/>
@@ -5234,7 +5282,9 @@
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
-      <c r="T56" s="1"/>
+      <c r="T56" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
       <c r="W56" s="1"/>
@@ -5277,7 +5327,7 @@
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
       <c r="S57" s="1"/>
-      <c r="T57" s="1"/>
+      <c r="T57" s="43"/>
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
       <c r="W57" s="1"/>
@@ -5322,7 +5372,7 @@
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
       <c r="S58" s="1"/>
-      <c r="T58" s="1"/>
+      <c r="T58" s="43"/>
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
       <c r="W58" s="1"/>
@@ -5365,7 +5415,7 @@
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
-      <c r="T59" s="1"/>
+      <c r="T59" s="43"/>
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
       <c r="W59" s="1"/>
@@ -5408,7 +5458,7 @@
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
       <c r="S60" s="1"/>
-      <c r="T60" s="1"/>
+      <c r="T60" s="43"/>
       <c r="U60" s="1"/>
       <c r="V60" s="1"/>
       <c r="W60" s="1"/>
@@ -5451,7 +5501,7 @@
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
-      <c r="T61" s="1"/>
+      <c r="T61" s="43"/>
       <c r="U61" s="1"/>
       <c r="V61" s="1"/>
       <c r="W61" s="1"/>
@@ -5494,7 +5544,7 @@
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
-      <c r="T62" s="1"/>
+      <c r="T62" s="43"/>
       <c r="U62" s="1"/>
       <c r="V62" s="1"/>
       <c r="W62" s="1"/>
@@ -5539,7 +5589,7 @@
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
       <c r="S63" s="1"/>
-      <c r="T63" s="1"/>
+      <c r="T63" s="43"/>
       <c r="U63" s="1"/>
       <c r="V63" s="1"/>
       <c r="W63" s="1"/>
@@ -5584,7 +5634,9 @@
       </c>
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
-      <c r="T64" s="1"/>
+      <c r="T64" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
       <c r="W64" s="1"/>
@@ -5631,7 +5683,9 @@
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
       <c r="S65" s="1"/>
-      <c r="T65" s="1"/>
+      <c r="T65" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U65" s="1"/>
       <c r="V65" s="1"/>
       <c r="W65" s="1"/>
@@ -5678,7 +5732,9 @@
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
       <c r="S66" s="1"/>
-      <c r="T66" s="1"/>
+      <c r="T66" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U66" s="1"/>
       <c r="V66" s="1"/>
       <c r="W66" s="1"/>
@@ -5723,7 +5779,7 @@
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
       <c r="S67" s="1"/>
-      <c r="T67" s="1"/>
+      <c r="T67" s="43"/>
       <c r="U67" s="1"/>
       <c r="V67" s="1"/>
       <c r="W67" s="1"/>
@@ -5770,7 +5826,7 @@
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
       <c r="S68" s="1"/>
-      <c r="T68" s="1"/>
+      <c r="T68" s="43"/>
       <c r="U68" s="1"/>
       <c r="V68" s="1"/>
       <c r="W68" s="1"/>
@@ -5817,7 +5873,9 @@
       </c>
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
-      <c r="T69" s="1"/>
+      <c r="T69" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
       <c r="W69" s="1"/>
@@ -5864,7 +5922,7 @@
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
-      <c r="T70" s="1"/>
+      <c r="T70" s="43"/>
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
       <c r="W70" s="1"/>
@@ -5909,7 +5967,7 @@
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
       <c r="S71" s="1"/>
-      <c r="T71" s="1"/>
+      <c r="T71" s="43"/>
       <c r="U71" s="1"/>
       <c r="V71" s="1"/>
       <c r="W71" s="1"/>
@@ -5952,7 +6010,7 @@
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
       <c r="S72" s="1"/>
-      <c r="T72" s="1"/>
+      <c r="T72" s="43"/>
       <c r="U72" s="1"/>
       <c r="V72" s="1"/>
       <c r="W72" s="1"/>
@@ -5995,7 +6053,7 @@
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
-      <c r="T73" s="1"/>
+      <c r="T73" s="43"/>
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
       <c r="W73" s="1"/>
@@ -6038,7 +6096,7 @@
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>
-      <c r="T74" s="1"/>
+      <c r="T74" s="43"/>
       <c r="U74" s="1"/>
       <c r="V74" s="1"/>
       <c r="W74" s="1"/>
@@ -6081,7 +6139,7 @@
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
       <c r="S75" s="1"/>
-      <c r="T75" s="1"/>
+      <c r="T75" s="43"/>
       <c r="U75" s="1"/>
       <c r="V75" s="1"/>
       <c r="W75" s="1"/>
@@ -6128,7 +6186,7 @@
       <c r="S76" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T76" s="1"/>
+      <c r="T76" s="43"/>
       <c r="U76" s="1"/>
       <c r="V76" s="1"/>
       <c r="W76" s="1"/>
@@ -6177,7 +6235,9 @@
       <c r="S77" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T77" s="1"/>
+      <c r="T77" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U77" s="1"/>
       <c r="V77" s="1"/>
       <c r="W77" s="1"/>
@@ -6222,7 +6282,7 @@
       <c r="S78" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T78" s="1"/>
+      <c r="T78" s="43"/>
       <c r="U78" s="1"/>
       <c r="V78" s="1"/>
       <c r="W78" s="1"/>
@@ -6267,7 +6327,7 @@
       <c r="S79" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T79" s="1"/>
+      <c r="T79" s="43"/>
       <c r="U79" s="1"/>
       <c r="V79" s="1"/>
       <c r="W79" s="1"/>
@@ -6312,7 +6372,7 @@
       <c r="S80" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T80" s="1"/>
+      <c r="T80" s="43"/>
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
       <c r="W80" s="1"/>
@@ -6359,7 +6419,7 @@
       <c r="S81" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T81" s="1"/>
+      <c r="T81" s="43"/>
       <c r="U81" s="1"/>
       <c r="V81" s="1"/>
       <c r="W81" s="1"/>
@@ -6406,7 +6466,7 @@
       <c r="S82" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T82" s="1"/>
+      <c r="T82" s="43"/>
       <c r="U82" s="1"/>
       <c r="V82" s="1"/>
       <c r="W82" s="1"/>
@@ -6498,7 +6558,7 @@
       <c r="S84" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T84" s="1"/>
+      <c r="T84" s="43"/>
       <c r="U84" s="1"/>
       <c r="V84" s="1"/>
       <c r="W84" s="1"/>
@@ -6541,7 +6601,7 @@
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
-      <c r="T85" s="1"/>
+      <c r="T85" s="43"/>
       <c r="U85" s="1"/>
       <c r="V85" s="1"/>
       <c r="W85" s="1"/>
@@ -6584,7 +6644,7 @@
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
-      <c r="T86" s="1"/>
+      <c r="T86" s="43"/>
       <c r="U86" s="1"/>
       <c r="V86" s="1"/>
       <c r="W86" s="1"/>
@@ -6627,7 +6687,7 @@
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
-      <c r="T87" s="1"/>
+      <c r="T87" s="43"/>
       <c r="U87" s="1"/>
       <c r="V87" s="1"/>
       <c r="W87" s="1"/>
@@ -6672,7 +6732,7 @@
       </c>
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
-      <c r="T88" s="1"/>
+      <c r="T88" s="43"/>
       <c r="U88" s="1"/>
       <c r="V88" s="1"/>
       <c r="W88" s="1"/>
@@ -6717,7 +6777,7 @@
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
-      <c r="T89" s="1"/>
+      <c r="T89" s="43"/>
       <c r="U89" s="1"/>
       <c r="V89" s="1"/>
       <c r="W89" s="1"/>
@@ -6760,7 +6820,7 @@
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
-      <c r="T90" s="1"/>
+      <c r="T90" s="43"/>
       <c r="U90" s="1"/>
       <c r="V90" s="1"/>
       <c r="W90" s="1"/>
@@ -6805,7 +6865,9 @@
       </c>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
-      <c r="T91" s="1"/>
+      <c r="T91" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U91" s="1"/>
       <c r="V91" s="1"/>
       <c r="W91" s="1"/>
@@ -6850,7 +6912,7 @@
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
-      <c r="T92" s="1"/>
+      <c r="T92" s="43"/>
       <c r="U92" s="1"/>
       <c r="V92" s="1"/>
       <c r="W92" s="1"/>
@@ -6893,7 +6955,7 @@
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
-      <c r="T93" s="1"/>
+      <c r="T93" s="43"/>
       <c r="U93" s="1"/>
       <c r="V93" s="1"/>
       <c r="W93" s="1"/>
@@ -6936,7 +6998,7 @@
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
-      <c r="T94" s="1"/>
+      <c r="T94" s="43"/>
       <c r="U94" s="1"/>
       <c r="V94" s="1"/>
       <c r="W94" s="1"/>
@@ -6979,7 +7041,7 @@
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
-      <c r="T95" s="1"/>
+      <c r="T95" s="43"/>
       <c r="U95" s="1"/>
       <c r="V95" s="1"/>
       <c r="W95" s="1"/>
@@ -7022,7 +7084,7 @@
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
-      <c r="T96" s="1"/>
+      <c r="T96" s="43"/>
       <c r="U96" s="1"/>
       <c r="V96" s="1"/>
       <c r="W96" s="1"/>
@@ -7065,7 +7127,7 @@
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
       <c r="S97" s="1"/>
-      <c r="T97" s="1"/>
+      <c r="T97" s="43"/>
       <c r="U97" s="1"/>
       <c r="V97" s="1"/>
       <c r="W97" s="1"/>
@@ -7110,7 +7172,9 @@
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
       <c r="S98" s="1"/>
-      <c r="T98" s="1"/>
+      <c r="T98" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U98" s="1"/>
       <c r="V98" s="1"/>
       <c r="W98" s="1"/>
@@ -7153,7 +7217,7 @@
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
       <c r="S99" s="1"/>
-      <c r="T99" s="1"/>
+      <c r="T99" s="43"/>
       <c r="U99" s="1"/>
       <c r="V99" s="1"/>
       <c r="W99" s="1"/>
@@ -7196,7 +7260,7 @@
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
       <c r="S100" s="1"/>
-      <c r="T100" s="1"/>
+      <c r="T100" s="43"/>
       <c r="U100" s="1"/>
       <c r="V100" s="1"/>
       <c r="W100" s="1"/>
@@ -7239,7 +7303,7 @@
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
       <c r="S101" s="1"/>
-      <c r="T101" s="1"/>
+      <c r="T101" s="43"/>
       <c r="U101" s="1"/>
       <c r="V101" s="1"/>
       <c r="W101" s="1"/>
@@ -7282,7 +7346,7 @@
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
       <c r="S102" s="1"/>
-      <c r="T102" s="1"/>
+      <c r="T102" s="43"/>
       <c r="U102" s="1"/>
       <c r="V102" s="1"/>
       <c r="W102" s="1"/>
@@ -7325,7 +7389,7 @@
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
       <c r="S103" s="1"/>
-      <c r="T103" s="1"/>
+      <c r="T103" s="43"/>
       <c r="U103" s="1"/>
       <c r="V103" s="1"/>
       <c r="W103" s="1"/>
@@ -7368,7 +7432,7 @@
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
       <c r="S104" s="1"/>
-      <c r="T104" s="1"/>
+      <c r="T104" s="43"/>
       <c r="U104" s="1"/>
       <c r="V104" s="1"/>
       <c r="W104" s="1"/>
@@ -7411,7 +7475,9 @@
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
       <c r="S105" s="1"/>
-      <c r="T105" s="1"/>
+      <c r="T105" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
       <c r="W105" s="1"/>
@@ -7456,7 +7522,7 @@
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
       <c r="S106" s="1"/>
-      <c r="T106" s="1"/>
+      <c r="T106" s="43"/>
       <c r="U106" s="1"/>
       <c r="V106" s="1"/>
       <c r="W106" s="1"/>
@@ -7499,7 +7565,7 @@
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
       <c r="S107" s="1"/>
-      <c r="T107" s="1"/>
+      <c r="T107" s="43"/>
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
       <c r="W107" s="1"/>
@@ -7544,7 +7610,7 @@
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
       <c r="S108" s="1"/>
-      <c r="T108" s="1"/>
+      <c r="T108" s="43"/>
       <c r="U108" s="1"/>
       <c r="V108" s="1"/>
       <c r="W108" s="1"/>
@@ -7587,7 +7653,7 @@
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
       <c r="S109" s="1"/>
-      <c r="T109" s="1"/>
+      <c r="T109" s="43"/>
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
       <c r="W109" s="1"/>
@@ -7632,7 +7698,7 @@
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
       <c r="S110" s="1"/>
-      <c r="T110" s="1"/>
+      <c r="T110" s="43"/>
       <c r="U110" s="1"/>
       <c r="V110" s="1"/>
       <c r="W110" s="1"/>
@@ -7675,7 +7741,7 @@
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
       <c r="S111" s="1"/>
-      <c r="T111" s="1"/>
+      <c r="T111" s="43"/>
       <c r="U111" s="1"/>
       <c r="V111" s="1"/>
       <c r="W111" s="1"/>
@@ -7722,7 +7788,9 @@
       </c>
       <c r="R112" s="1"/>
       <c r="S112" s="1"/>
-      <c r="T112" s="1"/>
+      <c r="T112" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
       <c r="W112" s="1"/>
@@ -7769,7 +7837,7 @@
       </c>
       <c r="R113" s="1"/>
       <c r="S113" s="1"/>
-      <c r="T113" s="1"/>
+      <c r="T113" s="43"/>
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
       <c r="W113" s="1"/>
@@ -7812,7 +7880,7 @@
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
       <c r="S114" s="1"/>
-      <c r="T114" s="1"/>
+      <c r="T114" s="43"/>
       <c r="U114" s="1"/>
       <c r="V114" s="1"/>
       <c r="W114" s="1"/>
@@ -7859,7 +7927,7 @@
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
       <c r="S115" s="1"/>
-      <c r="T115" s="1"/>
+      <c r="T115" s="43"/>
       <c r="U115" s="1"/>
       <c r="V115" s="1"/>
       <c r="W115" s="1"/>
@@ -7902,7 +7970,7 @@
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
       <c r="S116" s="1"/>
-      <c r="T116" s="1"/>
+      <c r="T116" s="43"/>
       <c r="U116" s="1"/>
       <c r="V116" s="1"/>
       <c r="W116" s="1"/>
@@ -7945,7 +8013,7 @@
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
       <c r="S117" s="1"/>
-      <c r="T117" s="1"/>
+      <c r="T117" s="43"/>
       <c r="U117" s="1"/>
       <c r="V117" s="1"/>
       <c r="W117" s="1"/>
@@ -7988,7 +8056,7 @@
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
       <c r="S118" s="1"/>
-      <c r="T118" s="1"/>
+      <c r="T118" s="43"/>
       <c r="U118" s="1"/>
       <c r="V118" s="1"/>
       <c r="W118" s="1"/>
@@ -8031,7 +8099,7 @@
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
       <c r="S119" s="1"/>
-      <c r="T119" s="1"/>
+      <c r="T119" s="43"/>
       <c r="U119" s="1"/>
       <c r="V119" s="1"/>
       <c r="W119" s="1"/>
@@ -8074,7 +8142,9 @@
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
       <c r="S120" s="1"/>
-      <c r="T120" s="1"/>
+      <c r="T120" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U120" s="1"/>
       <c r="V120" s="1"/>
       <c r="W120" s="1"/>
@@ -8117,7 +8187,7 @@
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
       <c r="S121" s="1"/>
-      <c r="T121" s="1"/>
+      <c r="T121" s="43"/>
       <c r="U121" s="1"/>
       <c r="V121" s="1"/>
       <c r="W121" s="1"/>
@@ -8160,7 +8230,7 @@
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
       <c r="S122" s="1"/>
-      <c r="T122" s="1"/>
+      <c r="T122" s="43"/>
       <c r="U122" s="1"/>
       <c r="V122" s="1"/>
       <c r="W122" s="1"/>
@@ -8203,7 +8273,7 @@
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
       <c r="S123" s="1"/>
-      <c r="T123" s="1"/>
+      <c r="T123" s="43"/>
       <c r="U123" s="1"/>
       <c r="V123" s="1"/>
       <c r="W123" s="1"/>
@@ -8246,7 +8316,7 @@
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
       <c r="S124" s="1"/>
-      <c r="T124" s="1"/>
+      <c r="T124" s="43"/>
       <c r="U124" s="1"/>
       <c r="V124" s="1"/>
       <c r="W124" s="1"/>
@@ -8289,7 +8359,7 @@
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
       <c r="S125" s="1"/>
-      <c r="T125" s="1"/>
+      <c r="T125" s="43"/>
       <c r="U125" s="1"/>
       <c r="V125" s="1"/>
       <c r="W125" s="1"/>
@@ -8334,7 +8404,9 @@
       </c>
       <c r="R126" s="1"/>
       <c r="S126" s="1"/>
-      <c r="T126" s="1"/>
+      <c r="T126" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U126" s="1"/>
       <c r="V126" s="1"/>
       <c r="W126" s="1"/>
@@ -8377,7 +8449,7 @@
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
       <c r="S127" s="1"/>
-      <c r="T127" s="1"/>
+      <c r="T127" s="43"/>
       <c r="U127" s="1"/>
       <c r="V127" s="1"/>
       <c r="W127" s="1"/>
@@ -8422,7 +8494,7 @@
       </c>
       <c r="R128" s="1"/>
       <c r="S128" s="1"/>
-      <c r="T128" s="1"/>
+      <c r="T128" s="43"/>
       <c r="U128" s="1"/>
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
@@ -8469,7 +8541,7 @@
       <c r="S129" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T129" s="1"/>
+      <c r="T129" s="43"/>
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
       <c r="W129" s="1"/>
@@ -8514,7 +8586,9 @@
       </c>
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
-      <c r="T130" s="1"/>
+      <c r="T130" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U130" s="1"/>
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
@@ -8537,7 +8611,7 @@
       <c r="AJ130" s="1"/>
       <c r="AK130" s="1"/>
     </row>
-    <row r="131" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="131" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1">
       <c r="A131" s="3">
         <v>128</v>
       </c>
@@ -8561,7 +8635,7 @@
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
       <c r="S131" s="1"/>
-      <c r="T131" s="1"/>
+      <c r="T131" s="43"/>
       <c r="U131" s="1"/>
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
@@ -8606,7 +8680,9 @@
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
       <c r="S132" s="1"/>
-      <c r="T132" s="1"/>
+      <c r="T132" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U132" s="1"/>
       <c r="V132" s="1"/>
       <c r="W132" s="1"/>
@@ -8651,7 +8727,7 @@
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
-      <c r="T133" s="1"/>
+      <c r="T133" s="43"/>
       <c r="U133" s="1"/>
       <c r="V133" s="1"/>
       <c r="W133" s="1"/>
@@ -8694,7 +8770,7 @@
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
       <c r="S134" s="1"/>
-      <c r="T134" s="1"/>
+      <c r="T134" s="43"/>
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
       <c r="W134" s="1"/>
@@ -8737,7 +8813,7 @@
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
       <c r="S135" s="1"/>
-      <c r="T135" s="1"/>
+      <c r="T135" s="43"/>
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
       <c r="W135" s="1"/>
@@ -8780,7 +8856,7 @@
       <c r="Q136" s="1"/>
       <c r="R136" s="1"/>
       <c r="S136" s="1"/>
-      <c r="T136" s="1"/>
+      <c r="T136" s="43"/>
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
       <c r="W136" s="1"/>
@@ -8825,7 +8901,7 @@
       <c r="Q137" s="1"/>
       <c r="R137" s="1"/>
       <c r="S137" s="1"/>
-      <c r="T137" s="1"/>
+      <c r="T137" s="43"/>
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
       <c r="W137" s="1"/>
@@ -8868,7 +8944,9 @@
       <c r="Q138" s="1"/>
       <c r="R138" s="1"/>
       <c r="S138" s="1"/>
-      <c r="T138" s="1"/>
+      <c r="T138" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U138" s="1"/>
       <c r="V138" s="1"/>
       <c r="W138" s="1"/>
@@ -8913,7 +8991,7 @@
       <c r="Q139" s="1"/>
       <c r="R139" s="1"/>
       <c r="S139" s="1"/>
-      <c r="T139" s="1"/>
+      <c r="T139" s="43"/>
       <c r="U139" s="1"/>
       <c r="V139" s="1"/>
       <c r="W139" s="1"/>
@@ -8956,7 +9034,7 @@
       <c r="Q140" s="1"/>
       <c r="R140" s="1"/>
       <c r="S140" s="1"/>
-      <c r="T140" s="1"/>
+      <c r="T140" s="43"/>
       <c r="U140" s="1"/>
       <c r="V140" s="1"/>
       <c r="W140" s="1"/>
@@ -8999,7 +9077,7 @@
       <c r="Q141" s="1"/>
       <c r="R141" s="1"/>
       <c r="S141" s="1"/>
-      <c r="T141" s="1"/>
+      <c r="T141" s="43"/>
       <c r="U141" s="1"/>
       <c r="V141" s="1"/>
       <c r="W141" s="1"/>
@@ -9042,7 +9120,9 @@
       <c r="Q142" s="1"/>
       <c r="R142" s="1"/>
       <c r="S142" s="1"/>
-      <c r="T142" s="1"/>
+      <c r="T142" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U142" s="1"/>
       <c r="V142" s="1"/>
       <c r="W142" s="1"/>
@@ -9085,7 +9165,7 @@
       <c r="Q143" s="1"/>
       <c r="R143" s="1"/>
       <c r="S143" s="1"/>
-      <c r="T143" s="1"/>
+      <c r="T143" s="43"/>
       <c r="U143" s="1"/>
       <c r="V143" s="1"/>
       <c r="W143" s="1"/>
@@ -9128,7 +9208,7 @@
       <c r="Q144" s="1"/>
       <c r="R144" s="1"/>
       <c r="S144" s="1"/>
-      <c r="T144" s="1"/>
+      <c r="T144" s="43"/>
       <c r="U144" s="1"/>
       <c r="V144" s="1"/>
       <c r="W144" s="1"/>
@@ -9171,7 +9251,7 @@
       <c r="Q145" s="1"/>
       <c r="R145" s="1"/>
       <c r="S145" s="1"/>
-      <c r="T145" s="1"/>
+      <c r="T145" s="43"/>
       <c r="U145" s="1"/>
       <c r="V145" s="1"/>
       <c r="W145" s="1"/>
@@ -9214,7 +9294,7 @@
       <c r="Q146" s="1"/>
       <c r="R146" s="1"/>
       <c r="S146" s="1"/>
-      <c r="T146" s="1"/>
+      <c r="T146" s="43"/>
       <c r="U146" s="1"/>
       <c r="V146" s="1"/>
       <c r="W146" s="1"/>
@@ -9257,7 +9337,7 @@
       <c r="Q147" s="1"/>
       <c r="R147" s="1"/>
       <c r="S147" s="1"/>
-      <c r="T147" s="1"/>
+      <c r="T147" s="43"/>
       <c r="U147" s="1"/>
       <c r="V147" s="1"/>
       <c r="W147" s="1"/>
@@ -9306,7 +9386,7 @@
       </c>
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
-      <c r="T148" s="1"/>
+      <c r="T148" s="43"/>
       <c r="U148" s="1"/>
       <c r="V148" s="1"/>
       <c r="W148" s="1"/>
@@ -9349,7 +9429,7 @@
       <c r="Q149" s="1"/>
       <c r="R149" s="1"/>
       <c r="S149" s="1"/>
-      <c r="T149" s="1"/>
+      <c r="T149" s="43"/>
       <c r="U149" s="1"/>
       <c r="V149" s="1"/>
       <c r="W149" s="1"/>
@@ -9392,7 +9472,7 @@
       <c r="Q150" s="1"/>
       <c r="R150" s="1"/>
       <c r="S150" s="1"/>
-      <c r="T150" s="1"/>
+      <c r="T150" s="43"/>
       <c r="U150" s="1"/>
       <c r="V150" s="1"/>
       <c r="W150" s="1"/>
@@ -9437,7 +9517,7 @@
       <c r="Q151" s="1"/>
       <c r="R151" s="1"/>
       <c r="S151" s="1"/>
-      <c r="T151" s="1"/>
+      <c r="T151" s="43"/>
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
@@ -9480,7 +9560,7 @@
       <c r="Q152" s="1"/>
       <c r="R152" s="1"/>
       <c r="S152" s="1"/>
-      <c r="T152" s="1"/>
+      <c r="T152" s="43"/>
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
@@ -9525,7 +9605,9 @@
       <c r="Q153" s="1"/>
       <c r="R153" s="1"/>
       <c r="S153" s="1"/>
-      <c r="T153" s="1"/>
+      <c r="T153" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
       <c r="W153" s="1"/>
@@ -9572,7 +9654,7 @@
       <c r="Q154" s="1"/>
       <c r="R154" s="1"/>
       <c r="S154" s="1"/>
-      <c r="T154" s="1"/>
+      <c r="T154" s="43"/>
       <c r="U154" s="1"/>
       <c r="V154" s="1"/>
       <c r="W154" s="1"/>
@@ -9619,7 +9701,7 @@
       </c>
       <c r="R155" s="1"/>
       <c r="S155" s="1"/>
-      <c r="T155" s="1"/>
+      <c r="T155" s="43"/>
       <c r="U155" s="1"/>
       <c r="V155" s="1"/>
       <c r="W155" s="1"/>
@@ -9666,7 +9748,7 @@
       <c r="Q156" s="1"/>
       <c r="R156" s="1"/>
       <c r="S156" s="1"/>
-      <c r="T156" s="1"/>
+      <c r="T156" s="43"/>
       <c r="U156" s="1"/>
       <c r="V156" s="1"/>
       <c r="W156" s="1"/>
@@ -9711,7 +9793,7 @@
       <c r="Q157" s="1"/>
       <c r="R157" s="1"/>
       <c r="S157" s="1"/>
-      <c r="T157" s="1"/>
+      <c r="T157" s="43"/>
       <c r="U157" s="1"/>
       <c r="V157" s="1"/>
       <c r="W157" s="1"/>
@@ -9758,7 +9840,9 @@
       <c r="Q158" s="1"/>
       <c r="R158" s="1"/>
       <c r="S158" s="1"/>
-      <c r="T158" s="1"/>
+      <c r="T158" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U158" s="1"/>
       <c r="V158" s="1"/>
       <c r="W158" s="1"/>
@@ -9807,7 +9891,7 @@
       <c r="Q159" s="1"/>
       <c r="R159" s="1"/>
       <c r="S159" s="1"/>
-      <c r="T159" s="1"/>
+      <c r="T159" s="43"/>
       <c r="U159" s="1"/>
       <c r="V159" s="1"/>
       <c r="W159" s="1"/>
@@ -9858,7 +9942,7 @@
       <c r="S160" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T160" s="1"/>
+      <c r="T160" s="43"/>
       <c r="U160" s="1"/>
       <c r="V160" s="1"/>
       <c r="W160" s="1"/>
@@ -9903,7 +9987,7 @@
       <c r="Q161" s="1"/>
       <c r="R161" s="1"/>
       <c r="S161" s="1"/>
-      <c r="T161" s="1"/>
+      <c r="T161" s="43"/>
       <c r="U161" s="1"/>
       <c r="V161" s="1"/>
       <c r="W161" s="1"/>
@@ -9948,7 +10032,7 @@
       <c r="Q162" s="1"/>
       <c r="R162" s="1"/>
       <c r="S162" s="1"/>
-      <c r="T162" s="1"/>
+      <c r="T162" s="43"/>
       <c r="U162" s="1"/>
       <c r="V162" s="1"/>
       <c r="W162" s="1"/>
@@ -9999,7 +10083,7 @@
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
       <c r="S163" s="1"/>
-      <c r="T163" s="1"/>
+      <c r="T163" s="43"/>
       <c r="U163" s="1"/>
       <c r="V163" s="1"/>
       <c r="W163" s="1"/>
@@ -10046,7 +10130,7 @@
       <c r="Q164" s="3"/>
       <c r="R164" s="3"/>
       <c r="S164" s="1"/>
-      <c r="T164" s="1"/>
+      <c r="T164" s="43"/>
       <c r="U164" s="1"/>
       <c r="V164" s="3"/>
       <c r="W164" s="3"/>
@@ -10091,7 +10175,9 @@
       <c r="S165" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T165" s="1"/>
+      <c r="T165" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U165" s="1"/>
       <c r="V165" s="3"/>
       <c r="W165" s="3"/>
@@ -10134,7 +10220,7 @@
       <c r="Q166" s="1"/>
       <c r="R166" s="1"/>
       <c r="S166" s="1"/>
-      <c r="T166" s="1"/>
+      <c r="T166" s="43"/>
       <c r="U166" s="1"/>
       <c r="V166" s="1"/>
       <c r="W166" s="1"/>
@@ -10177,7 +10263,7 @@
       <c r="Q167" s="1"/>
       <c r="R167" s="1"/>
       <c r="S167" s="1"/>
-      <c r="T167" s="1"/>
+      <c r="T167" s="43"/>
       <c r="U167" s="1"/>
       <c r="V167" s="1"/>
       <c r="W167" s="1"/>
@@ -10220,7 +10306,7 @@
       <c r="Q168" s="1"/>
       <c r="R168" s="1"/>
       <c r="S168" s="1"/>
-      <c r="T168" s="1"/>
+      <c r="T168" s="43"/>
       <c r="U168" s="1"/>
       <c r="V168" s="1"/>
       <c r="W168" s="1"/>
@@ -10263,7 +10349,7 @@
       <c r="Q169" s="1"/>
       <c r="R169" s="1"/>
       <c r="S169" s="1"/>
-      <c r="T169" s="1"/>
+      <c r="T169" s="43"/>
       <c r="U169" s="1"/>
       <c r="V169" s="1"/>
       <c r="W169" s="1"/>
@@ -10306,7 +10392,7 @@
       <c r="Q170" s="1"/>
       <c r="R170" s="1"/>
       <c r="S170" s="1"/>
-      <c r="T170" s="1"/>
+      <c r="T170" s="43"/>
       <c r="U170" s="1"/>
       <c r="V170" s="1"/>
       <c r="W170" s="1"/>
@@ -10349,7 +10435,7 @@
       <c r="Q171" s="1"/>
       <c r="R171" s="1"/>
       <c r="S171" s="1"/>
-      <c r="T171" s="1"/>
+      <c r="T171" s="43"/>
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
       <c r="W171" s="1"/>
@@ -10394,7 +10480,7 @@
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
       <c r="S172" s="1"/>
-      <c r="T172" s="1"/>
+      <c r="T172" s="43"/>
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
       <c r="W172" s="1"/>
@@ -10437,7 +10523,7 @@
       <c r="Q173" s="1"/>
       <c r="R173" s="1"/>
       <c r="S173" s="1"/>
-      <c r="T173" s="1"/>
+      <c r="T173" s="43"/>
       <c r="U173" s="1"/>
       <c r="V173" s="1"/>
       <c r="W173" s="1"/>
@@ -10490,7 +10576,9 @@
       <c r="S174" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T174" s="1"/>
+      <c r="T174" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
       <c r="W174" s="1"/>
@@ -10543,7 +10631,9 @@
       <c r="S175" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T175" s="1"/>
+      <c r="T175" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
       <c r="W175" s="1"/>
@@ -10600,7 +10690,9 @@
       <c r="S176" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T176" s="1"/>
+      <c r="T176" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
       <c r="W176" s="1"/>
@@ -10651,7 +10743,9 @@
       <c r="S177" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T177" s="1"/>
+      <c r="T177" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
       <c r="W177" s="1"/>
@@ -10698,7 +10792,7 @@
       <c r="S178" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T178" s="1"/>
+      <c r="T178" s="43"/>
       <c r="U178" s="1"/>
       <c r="V178" s="1"/>
       <c r="W178" s="1"/>
@@ -10747,7 +10841,7 @@
       <c r="S179" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T179" s="1"/>
+      <c r="T179" s="43"/>
       <c r="U179" s="1"/>
       <c r="V179" s="1"/>
       <c r="W179" s="1"/>
@@ -10798,7 +10892,7 @@
       <c r="S180" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T180" s="1"/>
+      <c r="T180" s="43"/>
       <c r="U180" s="1"/>
       <c r="V180" s="1"/>
       <c r="W180" s="1"/>
@@ -10847,7 +10941,7 @@
       <c r="S181" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T181" s="1"/>
+      <c r="T181" s="43"/>
       <c r="U181" s="1"/>
       <c r="V181" s="1"/>
       <c r="W181" s="1"/>
@@ -10896,7 +10990,7 @@
       <c r="S182" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T182" s="1"/>
+      <c r="T182" s="43"/>
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
       <c r="W182" s="1"/>
@@ -10949,7 +11043,7 @@
       <c r="S183" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T183" s="1"/>
+      <c r="T183" s="43"/>
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
       <c r="W183" s="1"/>
@@ -11004,7 +11098,7 @@
       <c r="S184" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T184" s="1"/>
+      <c r="T184" s="43"/>
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
       <c r="W184" s="1"/>
@@ -11057,7 +11151,7 @@
       <c r="S185" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T185" s="1"/>
+      <c r="T185" s="43"/>
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
       <c r="W185" s="1"/>
@@ -11102,7 +11196,7 @@
       <c r="Q186" s="1"/>
       <c r="R186" s="1"/>
       <c r="S186" s="1"/>
-      <c r="T186" s="1"/>
+      <c r="T186" s="43"/>
       <c r="U186" s="1"/>
       <c r="V186" s="1" t="s">
         <v>156</v>
@@ -11151,7 +11245,7 @@
       <c r="Q187" s="1"/>
       <c r="R187" s="1"/>
       <c r="S187" s="1"/>
-      <c r="T187" s="1"/>
+      <c r="T187" s="43"/>
       <c r="U187" s="1"/>
       <c r="V187" s="1" t="s">
         <v>156</v>
@@ -11202,7 +11296,7 @@
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
       <c r="S188" s="1"/>
-      <c r="T188" s="1"/>
+      <c r="T188" s="43"/>
       <c r="U188" s="1"/>
       <c r="V188" s="1" t="s">
         <v>156</v>
@@ -11251,7 +11345,7 @@
       <c r="Q189" s="1"/>
       <c r="R189" s="1"/>
       <c r="S189" s="1"/>
-      <c r="T189" s="1"/>
+      <c r="T189" s="43"/>
       <c r="U189" s="1"/>
       <c r="V189" s="1" t="s">
         <v>156</v>
@@ -11300,7 +11394,7 @@
       <c r="Q190" s="1"/>
       <c r="R190" s="1"/>
       <c r="S190" s="1"/>
-      <c r="T190" s="1"/>
+      <c r="T190" s="43"/>
       <c r="U190" s="1"/>
       <c r="V190" s="1" t="s">
         <v>156</v>
@@ -11349,7 +11443,7 @@
       <c r="Q191" s="1"/>
       <c r="R191" s="1"/>
       <c r="S191" s="1"/>
-      <c r="T191" s="1"/>
+      <c r="T191" s="43"/>
       <c r="U191" s="1"/>
       <c r="V191" s="1" t="s">
         <v>156</v>
@@ -12457,7 +12551,7 @@
       <c r="Q215" s="1"/>
       <c r="R215" s="1"/>
       <c r="S215" s="1"/>
-      <c r="T215" s="1"/>
+      <c r="T215" s="43"/>
       <c r="U215" s="1"/>
       <c r="V215" s="1"/>
       <c r="W215" s="1"/>
@@ -12657,7 +12751,7 @@
       <c r="Q219" s="1"/>
       <c r="R219" s="1"/>
       <c r="S219" s="1"/>
-      <c r="T219" s="1"/>
+      <c r="T219" s="43"/>
       <c r="U219" s="1"/>
       <c r="V219" s="1"/>
       <c r="W219" s="1"/>
@@ -12700,7 +12794,7 @@
       <c r="Q220" s="1"/>
       <c r="R220" s="1"/>
       <c r="S220" s="1"/>
-      <c r="T220" s="1"/>
+      <c r="T220" s="43"/>
       <c r="U220" s="1"/>
       <c r="V220" s="1"/>
       <c r="W220" s="1"/>
@@ -12743,7 +12837,7 @@
       <c r="Q221" s="1"/>
       <c r="R221" s="1"/>
       <c r="S221" s="1"/>
-      <c r="T221" s="1"/>
+      <c r="T221" s="43"/>
       <c r="U221" s="1"/>
       <c r="V221" s="1"/>
       <c r="W221" s="1"/>
@@ -12788,7 +12882,7 @@
       <c r="Q222" s="1"/>
       <c r="R222" s="1"/>
       <c r="S222" s="1"/>
-      <c r="T222" s="1"/>
+      <c r="T222" s="43"/>
       <c r="U222" s="1"/>
       <c r="V222" s="1"/>
       <c r="W222" s="1"/>
@@ -12831,7 +12925,7 @@
       <c r="Q223" s="1"/>
       <c r="R223" s="1"/>
       <c r="S223" s="1"/>
-      <c r="T223" s="1"/>
+      <c r="T223" s="43"/>
       <c r="U223" s="1"/>
       <c r="V223" s="1"/>
       <c r="W223" s="1"/>
@@ -12874,7 +12968,7 @@
       <c r="Q224" s="1"/>
       <c r="R224" s="1"/>
       <c r="S224" s="1"/>
-      <c r="T224" s="1"/>
+      <c r="T224" s="43"/>
       <c r="U224" s="1"/>
       <c r="V224" s="1"/>
       <c r="W224" s="1"/>
@@ -12917,7 +13011,7 @@
       <c r="Q225" s="1"/>
       <c r="R225" s="1"/>
       <c r="S225" s="1"/>
-      <c r="T225" s="1"/>
+      <c r="T225" s="43"/>
       <c r="U225" s="1"/>
       <c r="V225" s="1"/>
       <c r="W225" s="1"/>
@@ -12960,7 +13054,7 @@
       <c r="Q226" s="1"/>
       <c r="R226" s="1"/>
       <c r="S226" s="1"/>
-      <c r="T226" s="1"/>
+      <c r="T226" s="43"/>
       <c r="U226" s="1"/>
       <c r="V226" s="1"/>
       <c r="W226" s="1"/>
@@ -13003,7 +13097,7 @@
       <c r="Q227" s="1"/>
       <c r="R227" s="1"/>
       <c r="S227" s="1"/>
-      <c r="T227" s="1"/>
+      <c r="T227" s="43"/>
       <c r="U227" s="1"/>
       <c r="V227" s="1"/>
       <c r="W227" s="1"/>
@@ -13046,7 +13140,7 @@
       <c r="Q228" s="1"/>
       <c r="R228" s="1"/>
       <c r="S228" s="1"/>
-      <c r="T228" s="1"/>
+      <c r="T228" s="43"/>
       <c r="U228" s="1"/>
       <c r="V228" s="1"/>
       <c r="W228" s="1"/>
@@ -13089,7 +13183,7 @@
       <c r="Q229" s="1"/>
       <c r="R229" s="1"/>
       <c r="S229" s="1"/>
-      <c r="T229" s="1"/>
+      <c r="T229" s="43"/>
       <c r="U229" s="1"/>
       <c r="V229" s="1"/>
       <c r="W229" s="1"/>
@@ -13132,7 +13226,7 @@
       <c r="Q230" s="1"/>
       <c r="R230" s="1"/>
       <c r="S230" s="1"/>
-      <c r="T230" s="1"/>
+      <c r="T230" s="43"/>
       <c r="U230" s="1"/>
       <c r="V230" s="1"/>
       <c r="W230" s="1"/>
@@ -13175,7 +13269,7 @@
       <c r="Q231" s="1"/>
       <c r="R231" s="1"/>
       <c r="S231" s="1"/>
-      <c r="T231" s="1"/>
+      <c r="T231" s="43"/>
       <c r="U231" s="1"/>
       <c r="V231" s="1"/>
       <c r="W231" s="1"/>
@@ -13218,7 +13312,7 @@
       <c r="Q232" s="1"/>
       <c r="R232" s="1"/>
       <c r="S232" s="1"/>
-      <c r="T232" s="1"/>
+      <c r="T232" s="43"/>
       <c r="U232" s="1"/>
       <c r="V232" s="1"/>
       <c r="W232" s="1"/>
@@ -13263,7 +13357,7 @@
       <c r="Q233" s="1"/>
       <c r="R233" s="1"/>
       <c r="S233" s="1"/>
-      <c r="T233" s="1"/>
+      <c r="T233" s="43"/>
       <c r="U233" s="1"/>
       <c r="V233" s="1"/>
       <c r="W233" s="1"/>
@@ -13308,7 +13402,7 @@
       <c r="Q234" s="1"/>
       <c r="R234" s="1"/>
       <c r="S234" s="1"/>
-      <c r="T234" s="1"/>
+      <c r="T234" s="43"/>
       <c r="U234" s="1"/>
       <c r="V234" s="1"/>
       <c r="W234" s="1"/>
@@ -13353,7 +13447,7 @@
       <c r="S235" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T235" s="1"/>
+      <c r="T235" s="43"/>
       <c r="U235" s="1"/>
       <c r="V235" s="1"/>
       <c r="W235" s="1"/>
@@ -13398,7 +13492,7 @@
       <c r="Q236" s="1"/>
       <c r="R236" s="1"/>
       <c r="S236" s="1"/>
-      <c r="T236" s="1"/>
+      <c r="T236" s="43"/>
       <c r="U236" s="1"/>
       <c r="V236" s="1"/>
       <c r="W236" s="1"/>
@@ -13441,7 +13535,7 @@
       <c r="Q237" s="1"/>
       <c r="R237" s="1"/>
       <c r="S237" s="1"/>
-      <c r="T237" s="1"/>
+      <c r="T237" s="43"/>
       <c r="U237" s="1"/>
       <c r="V237" s="1"/>
       <c r="W237" s="1"/>
@@ -13484,7 +13578,7 @@
       <c r="Q238" s="1"/>
       <c r="R238" s="1"/>
       <c r="S238" s="1"/>
-      <c r="T238" s="1"/>
+      <c r="T238" s="43"/>
       <c r="U238" s="1"/>
       <c r="V238" s="1"/>
       <c r="W238" s="1"/>
@@ -13527,7 +13621,7 @@
       <c r="Q239" s="1"/>
       <c r="R239" s="1"/>
       <c r="S239" s="1"/>
-      <c r="T239" s="1"/>
+      <c r="T239" s="43"/>
       <c r="U239" s="1"/>
       <c r="V239" s="1"/>
       <c r="W239" s="1"/>
@@ -13570,7 +13664,7 @@
       <c r="Q240" s="1"/>
       <c r="R240" s="1"/>
       <c r="S240" s="1"/>
-      <c r="T240" s="1"/>
+      <c r="T240" s="43"/>
       <c r="U240" s="1"/>
       <c r="V240" s="1"/>
       <c r="W240" s="1"/>
@@ -13613,7 +13707,7 @@
       <c r="Q241" s="1"/>
       <c r="R241" s="1"/>
       <c r="S241" s="1"/>
-      <c r="T241" s="1"/>
+      <c r="T241" s="43"/>
       <c r="U241" s="1"/>
       <c r="V241" s="1"/>
       <c r="W241" s="1"/>
@@ -13656,7 +13750,7 @@
       <c r="Q242" s="1"/>
       <c r="R242" s="1"/>
       <c r="S242" s="1"/>
-      <c r="T242" s="1"/>
+      <c r="T242" s="43"/>
       <c r="U242" s="1"/>
       <c r="V242" s="1"/>
       <c r="W242" s="1"/>
@@ -13701,7 +13795,7 @@
       <c r="S243" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T243" s="1"/>
+      <c r="T243" s="43"/>
       <c r="U243" s="1"/>
       <c r="V243" s="1"/>
       <c r="W243" s="1"/>
@@ -13746,7 +13840,7 @@
       <c r="S244" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T244" s="1"/>
+      <c r="T244" s="43"/>
       <c r="U244" s="1"/>
       <c r="V244" s="1"/>
       <c r="W244" s="1"/>
@@ -13791,7 +13885,7 @@
       <c r="S245" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T245" s="1"/>
+      <c r="T245" s="43"/>
       <c r="U245" s="1"/>
       <c r="V245" s="1"/>
       <c r="W245" s="1"/>
@@ -13834,7 +13928,7 @@
       <c r="Q246" s="1"/>
       <c r="R246" s="1"/>
       <c r="S246" s="1"/>
-      <c r="T246" s="1"/>
+      <c r="T246" s="43"/>
       <c r="U246" s="1"/>
       <c r="V246" s="1"/>
       <c r="W246" s="1"/>
@@ -13879,7 +13973,7 @@
       <c r="Q247" s="1"/>
       <c r="R247" s="1"/>
       <c r="S247" s="1"/>
-      <c r="T247" s="1"/>
+      <c r="T247" s="43"/>
       <c r="U247" s="1"/>
       <c r="V247" s="1"/>
       <c r="W247" s="1"/>
@@ -13924,7 +14018,7 @@
       <c r="Q248" s="1"/>
       <c r="R248" s="1"/>
       <c r="S248" s="1"/>
-      <c r="T248" s="1"/>
+      <c r="T248" s="43"/>
       <c r="U248" s="1"/>
       <c r="V248" s="1"/>
       <c r="W248" s="1"/>
@@ -13971,7 +14065,7 @@
       <c r="Q249" s="1"/>
       <c r="R249" s="1"/>
       <c r="S249" s="1"/>
-      <c r="T249" s="1"/>
+      <c r="T249" s="43"/>
       <c r="U249" s="1"/>
       <c r="V249" s="1"/>
       <c r="W249" s="1"/>
@@ -14014,7 +14108,7 @@
       <c r="Q250" s="1"/>
       <c r="R250" s="1"/>
       <c r="S250" s="1"/>
-      <c r="T250" s="1"/>
+      <c r="T250" s="43"/>
       <c r="U250" s="1"/>
       <c r="V250" s="1"/>
       <c r="W250" s="1"/>
@@ -14057,7 +14151,7 @@
       <c r="Q251" s="1"/>
       <c r="R251" s="1"/>
       <c r="S251" s="1"/>
-      <c r="T251" s="1"/>
+      <c r="T251" s="43"/>
       <c r="U251" s="1"/>
       <c r="V251" s="1"/>
       <c r="W251" s="1"/>
@@ -14100,7 +14194,7 @@
       <c r="Q252" s="1"/>
       <c r="R252" s="1"/>
       <c r="S252" s="1"/>
-      <c r="T252" s="1"/>
+      <c r="T252" s="43"/>
       <c r="U252" s="1"/>
       <c r="V252" s="1"/>
       <c r="W252" s="1"/>
@@ -14143,7 +14237,7 @@
       <c r="Q253" s="1"/>
       <c r="R253" s="1"/>
       <c r="S253" s="1"/>
-      <c r="T253" s="1"/>
+      <c r="T253" s="43"/>
       <c r="U253" s="1"/>
       <c r="V253" s="1"/>
       <c r="W253" s="1"/>
@@ -14186,7 +14280,7 @@
       <c r="Q254" s="1"/>
       <c r="R254" s="1"/>
       <c r="S254" s="1"/>
-      <c r="T254" s="1"/>
+      <c r="T254" s="43"/>
       <c r="U254" s="1"/>
       <c r="V254" s="1"/>
       <c r="W254" s="1"/>
@@ -14229,7 +14323,7 @@
       <c r="Q255" s="1"/>
       <c r="R255" s="1"/>
       <c r="S255" s="1"/>
-      <c r="T255" s="1"/>
+      <c r="T255" s="43"/>
       <c r="U255" s="1"/>
       <c r="V255" s="1"/>
       <c r="W255" s="1"/>
@@ -14272,7 +14366,7 @@
       <c r="Q256" s="1"/>
       <c r="R256" s="1"/>
       <c r="S256" s="1"/>
-      <c r="T256" s="1"/>
+      <c r="T256" s="43"/>
       <c r="U256" s="1"/>
       <c r="V256" s="1"/>
       <c r="W256" s="1"/>
@@ -14319,7 +14413,7 @@
       <c r="Q257" s="1"/>
       <c r="R257" s="1"/>
       <c r="S257" s="1"/>
-      <c r="T257" s="1"/>
+      <c r="T257" s="43"/>
       <c r="U257" s="1"/>
       <c r="V257" s="1"/>
       <c r="W257" s="1"/>
@@ -14364,7 +14458,7 @@
       <c r="Q258" s="1"/>
       <c r="R258" s="1"/>
       <c r="S258" s="1"/>
-      <c r="T258" s="1"/>
+      <c r="T258" s="43"/>
       <c r="U258" s="1"/>
       <c r="V258" s="1"/>
       <c r="W258" s="1"/>
@@ -14409,7 +14503,7 @@
       <c r="Q259" s="1"/>
       <c r="R259" s="1"/>
       <c r="S259" s="1"/>
-      <c r="T259" s="1"/>
+      <c r="T259" s="43"/>
       <c r="U259" s="1"/>
       <c r="V259" s="1"/>
       <c r="W259" s="1"/>
@@ -14454,7 +14548,7 @@
       <c r="Q260" s="1"/>
       <c r="R260" s="1"/>
       <c r="S260" s="1"/>
-      <c r="T260" s="1"/>
+      <c r="T260" s="43"/>
       <c r="U260" s="1"/>
       <c r="V260" s="1"/>
       <c r="W260" s="1"/>
@@ -14480,7 +14574,9 @@
         <v>258</v>
       </c>
       <c r="B261" s="3"/>
-      <c r="C261" s="21"/>
+      <c r="C261" s="21" t="s">
+        <v>408</v>
+      </c>
       <c r="D261" s="1"/>
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
@@ -14497,7 +14593,9 @@
       <c r="Q261" s="1"/>
       <c r="R261" s="1"/>
       <c r="S261" s="1"/>
-      <c r="T261" s="1"/>
+      <c r="T261" s="43" t="s">
+        <v>156</v>
+      </c>
       <c r="U261" s="1"/>
       <c r="V261" s="1"/>
       <c r="W261" s="1"/>
@@ -14538,7 +14636,7 @@
       <c r="Q262" s="1"/>
       <c r="R262" s="1"/>
       <c r="S262" s="1"/>
-      <c r="T262" s="1"/>
+      <c r="T262" s="43"/>
       <c r="U262" s="1"/>
       <c r="V262" s="1"/>
       <c r="W262" s="1"/>
@@ -14579,7 +14677,7 @@
       <c r="Q263" s="1"/>
       <c r="R263" s="1"/>
       <c r="S263" s="1"/>
-      <c r="T263" s="1"/>
+      <c r="T263" s="43"/>
       <c r="U263" s="1"/>
       <c r="V263" s="1"/>
       <c r="W263" s="1"/>
@@ -14620,7 +14718,7 @@
       <c r="Q264" s="1"/>
       <c r="R264" s="1"/>
       <c r="S264" s="1"/>
-      <c r="T264" s="1"/>
+      <c r="T264" s="43"/>
       <c r="U264" s="1"/>
       <c r="V264" s="1"/>
       <c r="W264" s="1"/>
@@ -14661,7 +14759,7 @@
       <c r="Q265" s="1"/>
       <c r="R265" s="1"/>
       <c r="S265" s="1"/>
-      <c r="T265" s="1"/>
+      <c r="T265" s="43"/>
       <c r="U265" s="1"/>
       <c r="V265" s="1"/>
       <c r="W265" s="1"/>
@@ -14702,7 +14800,7 @@
       <c r="Q266" s="1"/>
       <c r="R266" s="1"/>
       <c r="S266" s="1"/>
-      <c r="T266" s="1"/>
+      <c r="T266" s="43"/>
       <c r="U266" s="1"/>
       <c r="V266" s="1"/>
       <c r="W266" s="1"/>
@@ -14743,7 +14841,7 @@
       <c r="Q267" s="1"/>
       <c r="R267" s="1"/>
       <c r="S267" s="1"/>
-      <c r="T267" s="1"/>
+      <c r="T267" s="43"/>
       <c r="U267" s="1"/>
       <c r="V267" s="1"/>
       <c r="W267" s="1"/>
@@ -14784,7 +14882,7 @@
       <c r="Q268" s="1"/>
       <c r="R268" s="1"/>
       <c r="S268" s="1"/>
-      <c r="T268" s="1"/>
+      <c r="T268" s="43"/>
       <c r="U268" s="1"/>
       <c r="V268" s="1"/>
       <c r="W268" s="1"/>
@@ -14825,7 +14923,7 @@
       <c r="Q269" s="1"/>
       <c r="R269" s="1"/>
       <c r="S269" s="1"/>
-      <c r="T269" s="1"/>
+      <c r="T269" s="43"/>
       <c r="U269" s="1"/>
       <c r="V269" s="1"/>
       <c r="W269" s="1"/>
@@ -14866,7 +14964,7 @@
       <c r="Q270" s="1"/>
       <c r="R270" s="1"/>
       <c r="S270" s="1"/>
-      <c r="T270" s="1"/>
+      <c r="T270" s="43"/>
       <c r="U270" s="1"/>
       <c r="V270" s="1"/>
       <c r="W270" s="1"/>
@@ -14907,7 +15005,7 @@
       <c r="Q271" s="1"/>
       <c r="R271" s="1"/>
       <c r="S271" s="1"/>
-      <c r="T271" s="1"/>
+      <c r="T271" s="43"/>
       <c r="U271" s="1"/>
       <c r="V271" s="1"/>
       <c r="W271" s="1"/>
@@ -14948,7 +15046,7 @@
       <c r="Q272" s="1"/>
       <c r="R272" s="1"/>
       <c r="S272" s="1"/>
-      <c r="T272" s="1"/>
+      <c r="T272" s="43"/>
       <c r="U272" s="1"/>
       <c r="V272" s="1"/>
       <c r="W272" s="1"/>
@@ -14989,7 +15087,7 @@
       <c r="Q273" s="1"/>
       <c r="R273" s="1"/>
       <c r="S273" s="1"/>
-      <c r="T273" s="1"/>
+      <c r="T273" s="43"/>
       <c r="U273" s="1"/>
       <c r="V273" s="1"/>
       <c r="W273" s="1"/>
@@ -15030,7 +15128,7 @@
       <c r="Q274" s="1"/>
       <c r="R274" s="1"/>
       <c r="S274" s="1"/>
-      <c r="T274" s="1"/>
+      <c r="T274" s="43"/>
       <c r="U274" s="1"/>
       <c r="V274" s="1"/>
       <c r="W274" s="1"/>
@@ -15071,7 +15169,7 @@
       <c r="Q275" s="1"/>
       <c r="R275" s="1"/>
       <c r="S275" s="1"/>
-      <c r="T275" s="1"/>
+      <c r="T275" s="43"/>
       <c r="U275" s="1"/>
       <c r="V275" s="1"/>
       <c r="W275" s="1"/>
@@ -15112,7 +15210,7 @@
       <c r="Q276" s="1"/>
       <c r="R276" s="1"/>
       <c r="S276" s="1"/>
-      <c r="T276" s="1"/>
+      <c r="T276" s="43"/>
       <c r="U276" s="1"/>
       <c r="V276" s="1"/>
       <c r="W276" s="1"/>
@@ -15153,7 +15251,7 @@
       <c r="Q277" s="1"/>
       <c r="R277" s="1"/>
       <c r="S277" s="1"/>
-      <c r="T277" s="1"/>
+      <c r="T277" s="43"/>
       <c r="U277" s="1"/>
       <c r="V277" s="1"/>
       <c r="W277" s="1"/>
@@ -15194,7 +15292,7 @@
       <c r="Q278" s="1"/>
       <c r="R278" s="1"/>
       <c r="S278" s="1"/>
-      <c r="T278" s="1"/>
+      <c r="T278" s="43"/>
       <c r="U278" s="1"/>
       <c r="V278" s="1"/>
       <c r="W278" s="1"/>
@@ -15235,7 +15333,7 @@
       <c r="Q279" s="1"/>
       <c r="R279" s="1"/>
       <c r="S279" s="1"/>
-      <c r="T279" s="1"/>
+      <c r="T279" s="43"/>
       <c r="U279" s="1"/>
       <c r="V279" s="1"/>
       <c r="W279" s="1"/>
@@ -15276,7 +15374,7 @@
       <c r="Q280" s="1"/>
       <c r="R280" s="1"/>
       <c r="S280" s="1"/>
-      <c r="T280" s="1"/>
+      <c r="T280" s="43"/>
       <c r="U280" s="1"/>
       <c r="V280" s="1"/>
       <c r="W280" s="1"/>
@@ -15740,7 +15838,9 @@
       <c r="G26" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="H26" s="18"/>
+      <c r="H26" s="18" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="19" t="s">
@@ -15836,7 +15936,9 @@
       <c r="G33" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="H33" s="18"/>
+      <c r="H33" s="18" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="19" t="s">

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68451A0-46C1-44C5-B898-55EADB80803D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8404C8EF-681A-4EBE-B398-E1F74BC84491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="409">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -2207,7 +2207,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2311,6 +2311,9 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
@@ -2320,13 +2323,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2715,14 +2711,12 @@
     <col min="3" max="3" width="33.75" bestFit="1" customWidth="1"/>
     <col min="4" max="9" width="3.5625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="2.5625" bestFit="1" customWidth="1"/>
-    <col min="11" max="19" width="3.5625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.5625" style="44" bestFit="1" customWidth="1"/>
-    <col min="21" max="37" width="3.5625" bestFit="1" customWidth="1"/>
+    <col min="11" max="37" width="3.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="22.9">
       <c r="A1" s="35"/>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="40" t="s">
         <v>272</v>
       </c>
       <c r="C1" s="32" t="s">
@@ -2746,7 +2740,7 @@
       <c r="Q1" s="38"/>
       <c r="R1" s="38"/>
       <c r="S1" s="38"/>
-      <c r="T1" s="42"/>
+      <c r="T1" s="39"/>
       <c r="U1" s="38"/>
       <c r="V1" s="38"/>
       <c r="W1" s="38"/>
@@ -2754,7 +2748,7 @@
     </row>
     <row r="2" spans="1:37" ht="22.9">
       <c r="A2" s="36"/>
-      <c r="B2" s="40"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="33"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="e" vm="1">
@@ -2803,7 +2797,7 @@
     </row>
     <row r="3" spans="1:37" s="13" customFormat="1" ht="106.9" thickBot="1">
       <c r="A3" s="37"/>
-      <c r="B3" s="41"/>
+      <c r="B3" s="42"/>
       <c r="C3" s="34"/>
       <c r="D3" s="11" t="s">
         <v>121</v>
@@ -2940,7 +2934,7 @@
       <c r="S4" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T4" s="43" t="s">
+      <c r="T4" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U4" s="1"/>
@@ -2997,7 +2991,7 @@
       <c r="S5" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T5" s="43" t="s">
+      <c r="T5" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U5" s="1"/>
@@ -3050,7 +3044,7 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
-      <c r="T6" s="43" t="s">
+      <c r="T6" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U6" s="1"/>
@@ -3099,7 +3093,7 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
-      <c r="T7" s="43" t="s">
+      <c r="T7" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U7" s="1"/>
@@ -3144,7 +3138,7 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
-      <c r="T8" s="43" t="s">
+      <c r="T8" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U8" s="1"/>
@@ -3191,7 +3185,7 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="43" t="s">
+      <c r="T9" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U9" s="1"/>
@@ -3236,7 +3230,7 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
-      <c r="T10" s="43"/>
+      <c r="T10" s="1"/>
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
@@ -3281,7 +3275,7 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
-      <c r="T11" s="43" t="s">
+      <c r="T11" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U11" s="1"/>
@@ -3328,7 +3322,7 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
-      <c r="T12" s="43"/>
+      <c r="T12" s="1"/>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
@@ -3371,7 +3365,7 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
-      <c r="T13" s="43"/>
+      <c r="T13" s="1"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
@@ -3414,7 +3408,7 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
-      <c r="T14" s="43"/>
+      <c r="T14" s="1"/>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
@@ -3457,7 +3451,7 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
-      <c r="T15" s="43"/>
+      <c r="T15" s="1"/>
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
@@ -3500,7 +3494,7 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
-      <c r="T16" s="43"/>
+      <c r="T16" s="1"/>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
@@ -3543,7 +3537,7 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-      <c r="T17" s="43"/>
+      <c r="T17" s="1"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
@@ -3586,7 +3580,7 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
-      <c r="T18" s="43"/>
+      <c r="T18" s="1"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
@@ -3631,7 +3625,7 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-      <c r="T19" s="43"/>
+      <c r="T19" s="1"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
@@ -3674,7 +3668,7 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
-      <c r="T20" s="43" t="s">
+      <c r="T20" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U20" s="1"/>
@@ -3719,7 +3713,7 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
-      <c r="T21" s="43"/>
+      <c r="T21" s="1"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
@@ -3766,7 +3760,7 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
-      <c r="T22" s="43"/>
+      <c r="T22" s="1"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
@@ -3809,7 +3803,7 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-      <c r="T23" s="43"/>
+      <c r="T23" s="1"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
@@ -3852,7 +3846,7 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
-      <c r="T24" s="43" t="s">
+      <c r="T24" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U24" s="1"/>
@@ -3901,7 +3895,7 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
-      <c r="T25" s="43" t="s">
+      <c r="T25" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U25" s="1"/>
@@ -3948,7 +3942,7 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
-      <c r="T26" s="43"/>
+      <c r="T26" s="1"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
@@ -3993,7 +3987,7 @@
       </c>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
-      <c r="T27" s="43"/>
+      <c r="T27" s="1"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
@@ -4036,7 +4030,7 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
-      <c r="T28" s="43"/>
+      <c r="T28" s="1"/>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
@@ -4079,7 +4073,7 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
-      <c r="T29" s="43"/>
+      <c r="T29" s="1"/>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
@@ -4122,7 +4116,7 @@
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
-      <c r="T30" s="43"/>
+      <c r="T30" s="1"/>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
@@ -4173,7 +4167,7 @@
       </c>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
-      <c r="T31" s="43"/>
+      <c r="T31" s="1"/>
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
@@ -4220,7 +4214,7 @@
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
-      <c r="T32" s="43"/>
+      <c r="T32" s="1"/>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
@@ -4263,7 +4257,7 @@
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
-      <c r="T33" s="43" t="s">
+      <c r="T33" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U33" s="1"/>
@@ -4308,7 +4302,7 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
-      <c r="T34" s="43"/>
+      <c r="T34" s="1"/>
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
@@ -4351,7 +4345,7 @@
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
-      <c r="T35" s="43"/>
+      <c r="T35" s="1"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
@@ -4394,7 +4388,7 @@
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
-      <c r="T36" s="43" t="s">
+      <c r="T36" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U36" s="1"/>
@@ -4439,7 +4433,7 @@
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
-      <c r="T37" s="43"/>
+      <c r="T37" s="1"/>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
@@ -4482,7 +4476,7 @@
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
-      <c r="T38" s="43"/>
+      <c r="T38" s="1"/>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
@@ -4525,7 +4519,7 @@
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
-      <c r="T39" s="43" t="s">
+      <c r="T39" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U39" s="1"/>
@@ -4572,7 +4566,7 @@
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
-      <c r="T40" s="43"/>
+      <c r="T40" s="1"/>
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
@@ -4617,7 +4611,7 @@
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
-      <c r="T41" s="43"/>
+      <c r="T41" s="1"/>
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
@@ -4662,7 +4656,7 @@
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
-      <c r="T42" s="43"/>
+      <c r="T42" s="1"/>
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
@@ -4705,7 +4699,7 @@
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
-      <c r="T43" s="43"/>
+      <c r="T43" s="1"/>
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
@@ -4750,7 +4744,7 @@
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
-      <c r="T44" s="43" t="s">
+      <c r="T44" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U44" s="1"/>
@@ -4795,7 +4789,7 @@
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
-      <c r="T45" s="43"/>
+      <c r="T45" s="1"/>
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
@@ -4838,7 +4832,7 @@
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
-      <c r="T46" s="43"/>
+      <c r="T46" s="1"/>
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
       <c r="W46" s="1"/>
@@ -4881,7 +4875,7 @@
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
-      <c r="T47" s="43"/>
+      <c r="T47" s="1"/>
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
       <c r="W47" s="1"/>
@@ -4924,7 +4918,7 @@
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
-      <c r="T48" s="43" t="s">
+      <c r="T48" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U48" s="1"/>
@@ -4973,7 +4967,7 @@
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
-      <c r="T49" s="43"/>
+      <c r="T49" s="1"/>
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
       <c r="W49" s="1"/>
@@ -5016,7 +5010,7 @@
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
-      <c r="T50" s="43"/>
+      <c r="T50" s="1"/>
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
@@ -5061,7 +5055,7 @@
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
-      <c r="T51" s="43"/>
+      <c r="T51" s="1"/>
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
       <c r="W51" s="1"/>
@@ -5104,7 +5098,7 @@
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
-      <c r="T52" s="43"/>
+      <c r="T52" s="1"/>
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
       <c r="W52" s="1"/>
@@ -5147,7 +5141,7 @@
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
-      <c r="T53" s="43"/>
+      <c r="T53" s="1"/>
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
       <c r="W53" s="1"/>
@@ -5190,7 +5184,7 @@
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
-      <c r="T54" s="43"/>
+      <c r="T54" s="1"/>
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
@@ -5235,7 +5229,7 @@
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
-      <c r="T55" s="43" t="s">
+      <c r="T55" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U55" s="1"/>
@@ -5282,7 +5276,7 @@
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
-      <c r="T56" s="43" t="s">
+      <c r="T56" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U56" s="1"/>
@@ -5327,7 +5321,7 @@
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
       <c r="S57" s="1"/>
-      <c r="T57" s="43"/>
+      <c r="T57" s="1"/>
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
       <c r="W57" s="1"/>
@@ -5372,7 +5366,7 @@
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
       <c r="S58" s="1"/>
-      <c r="T58" s="43"/>
+      <c r="T58" s="1"/>
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
       <c r="W58" s="1"/>
@@ -5415,7 +5409,7 @@
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
-      <c r="T59" s="43"/>
+      <c r="T59" s="1"/>
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
       <c r="W59" s="1"/>
@@ -5458,7 +5452,7 @@
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
       <c r="S60" s="1"/>
-      <c r="T60" s="43"/>
+      <c r="T60" s="1"/>
       <c r="U60" s="1"/>
       <c r="V60" s="1"/>
       <c r="W60" s="1"/>
@@ -5501,7 +5495,7 @@
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
-      <c r="T61" s="43"/>
+      <c r="T61" s="1"/>
       <c r="U61" s="1"/>
       <c r="V61" s="1"/>
       <c r="W61" s="1"/>
@@ -5544,7 +5538,7 @@
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
-      <c r="T62" s="43"/>
+      <c r="T62" s="1"/>
       <c r="U62" s="1"/>
       <c r="V62" s="1"/>
       <c r="W62" s="1"/>
@@ -5589,7 +5583,7 @@
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
       <c r="S63" s="1"/>
-      <c r="T63" s="43"/>
+      <c r="T63" s="1"/>
       <c r="U63" s="1"/>
       <c r="V63" s="1"/>
       <c r="W63" s="1"/>
@@ -5634,7 +5628,7 @@
       </c>
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
-      <c r="T64" s="43" t="s">
+      <c r="T64" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U64" s="1"/>
@@ -5683,7 +5677,7 @@
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
       <c r="S65" s="1"/>
-      <c r="T65" s="43" t="s">
+      <c r="T65" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U65" s="1"/>
@@ -5732,7 +5726,7 @@
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
       <c r="S66" s="1"/>
-      <c r="T66" s="43" t="s">
+      <c r="T66" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U66" s="1"/>
@@ -5779,7 +5773,7 @@
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
       <c r="S67" s="1"/>
-      <c r="T67" s="43"/>
+      <c r="T67" s="1"/>
       <c r="U67" s="1"/>
       <c r="V67" s="1"/>
       <c r="W67" s="1"/>
@@ -5826,7 +5820,7 @@
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
       <c r="S68" s="1"/>
-      <c r="T68" s="43"/>
+      <c r="T68" s="1"/>
       <c r="U68" s="1"/>
       <c r="V68" s="1"/>
       <c r="W68" s="1"/>
@@ -5873,7 +5867,7 @@
       </c>
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
-      <c r="T69" s="43" t="s">
+      <c r="T69" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U69" s="1"/>
@@ -5922,7 +5916,7 @@
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
-      <c r="T70" s="43"/>
+      <c r="T70" s="1"/>
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
       <c r="W70" s="1"/>
@@ -5967,7 +5961,7 @@
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
       <c r="S71" s="1"/>
-      <c r="T71" s="43"/>
+      <c r="T71" s="1"/>
       <c r="U71" s="1"/>
       <c r="V71" s="1"/>
       <c r="W71" s="1"/>
@@ -6010,7 +6004,7 @@
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
       <c r="S72" s="1"/>
-      <c r="T72" s="43"/>
+      <c r="T72" s="1"/>
       <c r="U72" s="1"/>
       <c r="V72" s="1"/>
       <c r="W72" s="1"/>
@@ -6053,7 +6047,7 @@
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
-      <c r="T73" s="43"/>
+      <c r="T73" s="1"/>
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
       <c r="W73" s="1"/>
@@ -6096,7 +6090,7 @@
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>
-      <c r="T74" s="43"/>
+      <c r="T74" s="1"/>
       <c r="U74" s="1"/>
       <c r="V74" s="1"/>
       <c r="W74" s="1"/>
@@ -6139,7 +6133,7 @@
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
       <c r="S75" s="1"/>
-      <c r="T75" s="43"/>
+      <c r="T75" s="1"/>
       <c r="U75" s="1"/>
       <c r="V75" s="1"/>
       <c r="W75" s="1"/>
@@ -6186,7 +6180,7 @@
       <c r="S76" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T76" s="43"/>
+      <c r="T76" s="1"/>
       <c r="U76" s="1"/>
       <c r="V76" s="1"/>
       <c r="W76" s="1"/>
@@ -6235,7 +6229,7 @@
       <c r="S77" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T77" s="43" t="s">
+      <c r="T77" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U77" s="1"/>
@@ -6282,7 +6276,7 @@
       <c r="S78" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T78" s="43"/>
+      <c r="T78" s="1"/>
       <c r="U78" s="1"/>
       <c r="V78" s="1"/>
       <c r="W78" s="1"/>
@@ -6327,7 +6321,7 @@
       <c r="S79" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T79" s="43"/>
+      <c r="T79" s="1"/>
       <c r="U79" s="1"/>
       <c r="V79" s="1"/>
       <c r="W79" s="1"/>
@@ -6372,7 +6366,7 @@
       <c r="S80" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T80" s="43"/>
+      <c r="T80" s="1"/>
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
       <c r="W80" s="1"/>
@@ -6419,7 +6413,7 @@
       <c r="S81" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T81" s="43"/>
+      <c r="T81" s="1"/>
       <c r="U81" s="1"/>
       <c r="V81" s="1"/>
       <c r="W81" s="1"/>
@@ -6466,7 +6460,7 @@
       <c r="S82" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T82" s="43"/>
+      <c r="T82" s="1"/>
       <c r="U82" s="1"/>
       <c r="V82" s="1"/>
       <c r="W82" s="1"/>
@@ -6558,7 +6552,7 @@
       <c r="S84" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T84" s="43"/>
+      <c r="T84" s="1"/>
       <c r="U84" s="1"/>
       <c r="V84" s="1"/>
       <c r="W84" s="1"/>
@@ -6601,7 +6595,7 @@
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
-      <c r="T85" s="43"/>
+      <c r="T85" s="1"/>
       <c r="U85" s="1"/>
       <c r="V85" s="1"/>
       <c r="W85" s="1"/>
@@ -6644,7 +6638,7 @@
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
-      <c r="T86" s="43"/>
+      <c r="T86" s="1"/>
       <c r="U86" s="1"/>
       <c r="V86" s="1"/>
       <c r="W86" s="1"/>
@@ -6687,7 +6681,7 @@
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
-      <c r="T87" s="43"/>
+      <c r="T87" s="1"/>
       <c r="U87" s="1"/>
       <c r="V87" s="1"/>
       <c r="W87" s="1"/>
@@ -6732,7 +6726,7 @@
       </c>
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
-      <c r="T88" s="43"/>
+      <c r="T88" s="1"/>
       <c r="U88" s="1"/>
       <c r="V88" s="1"/>
       <c r="W88" s="1"/>
@@ -6777,7 +6771,7 @@
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
-      <c r="T89" s="43"/>
+      <c r="T89" s="1"/>
       <c r="U89" s="1"/>
       <c r="V89" s="1"/>
       <c r="W89" s="1"/>
@@ -6820,7 +6814,7 @@
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
-      <c r="T90" s="43"/>
+      <c r="T90" s="1"/>
       <c r="U90" s="1"/>
       <c r="V90" s="1"/>
       <c r="W90" s="1"/>
@@ -6865,7 +6859,7 @@
       </c>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
-      <c r="T91" s="43" t="s">
+      <c r="T91" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U91" s="1"/>
@@ -6912,7 +6906,7 @@
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
-      <c r="T92" s="43"/>
+      <c r="T92" s="1"/>
       <c r="U92" s="1"/>
       <c r="V92" s="1"/>
       <c r="W92" s="1"/>
@@ -6955,7 +6949,7 @@
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
-      <c r="T93" s="43"/>
+      <c r="T93" s="1"/>
       <c r="U93" s="1"/>
       <c r="V93" s="1"/>
       <c r="W93" s="1"/>
@@ -6998,7 +6992,7 @@
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
-      <c r="T94" s="43"/>
+      <c r="T94" s="1"/>
       <c r="U94" s="1"/>
       <c r="V94" s="1"/>
       <c r="W94" s="1"/>
@@ -7041,7 +7035,7 @@
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
-      <c r="T95" s="43"/>
+      <c r="T95" s="1"/>
       <c r="U95" s="1"/>
       <c r="V95" s="1"/>
       <c r="W95" s="1"/>
@@ -7084,7 +7078,7 @@
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
-      <c r="T96" s="43"/>
+      <c r="T96" s="1"/>
       <c r="U96" s="1"/>
       <c r="V96" s="1"/>
       <c r="W96" s="1"/>
@@ -7127,7 +7121,7 @@
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
       <c r="S97" s="1"/>
-      <c r="T97" s="43"/>
+      <c r="T97" s="1"/>
       <c r="U97" s="1"/>
       <c r="V97" s="1"/>
       <c r="W97" s="1"/>
@@ -7172,7 +7166,7 @@
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
       <c r="S98" s="1"/>
-      <c r="T98" s="43" t="s">
+      <c r="T98" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U98" s="1"/>
@@ -7217,7 +7211,7 @@
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
       <c r="S99" s="1"/>
-      <c r="T99" s="43"/>
+      <c r="T99" s="1"/>
       <c r="U99" s="1"/>
       <c r="V99" s="1"/>
       <c r="W99" s="1"/>
@@ -7260,7 +7254,7 @@
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
       <c r="S100" s="1"/>
-      <c r="T100" s="43"/>
+      <c r="T100" s="1"/>
       <c r="U100" s="1"/>
       <c r="V100" s="1"/>
       <c r="W100" s="1"/>
@@ -7303,7 +7297,7 @@
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
       <c r="S101" s="1"/>
-      <c r="T101" s="43"/>
+      <c r="T101" s="1"/>
       <c r="U101" s="1"/>
       <c r="V101" s="1"/>
       <c r="W101" s="1"/>
@@ -7346,7 +7340,7 @@
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
       <c r="S102" s="1"/>
-      <c r="T102" s="43"/>
+      <c r="T102" s="1"/>
       <c r="U102" s="1"/>
       <c r="V102" s="1"/>
       <c r="W102" s="1"/>
@@ -7389,7 +7383,7 @@
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
       <c r="S103" s="1"/>
-      <c r="T103" s="43"/>
+      <c r="T103" s="1"/>
       <c r="U103" s="1"/>
       <c r="V103" s="1"/>
       <c r="W103" s="1"/>
@@ -7432,7 +7426,7 @@
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
       <c r="S104" s="1"/>
-      <c r="T104" s="43"/>
+      <c r="T104" s="1"/>
       <c r="U104" s="1"/>
       <c r="V104" s="1"/>
       <c r="W104" s="1"/>
@@ -7475,7 +7469,7 @@
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
       <c r="S105" s="1"/>
-      <c r="T105" s="43" t="s">
+      <c r="T105" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U105" s="1"/>
@@ -7522,7 +7516,7 @@
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
       <c r="S106" s="1"/>
-      <c r="T106" s="43"/>
+      <c r="T106" s="1"/>
       <c r="U106" s="1"/>
       <c r="V106" s="1"/>
       <c r="W106" s="1"/>
@@ -7565,7 +7559,7 @@
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
       <c r="S107" s="1"/>
-      <c r="T107" s="43"/>
+      <c r="T107" s="1"/>
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
       <c r="W107" s="1"/>
@@ -7610,7 +7604,7 @@
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
       <c r="S108" s="1"/>
-      <c r="T108" s="43"/>
+      <c r="T108" s="1"/>
       <c r="U108" s="1"/>
       <c r="V108" s="1"/>
       <c r="W108" s="1"/>
@@ -7653,7 +7647,7 @@
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
       <c r="S109" s="1"/>
-      <c r="T109" s="43"/>
+      <c r="T109" s="1"/>
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
       <c r="W109" s="1"/>
@@ -7698,7 +7692,7 @@
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
       <c r="S110" s="1"/>
-      <c r="T110" s="43"/>
+      <c r="T110" s="1"/>
       <c r="U110" s="1"/>
       <c r="V110" s="1"/>
       <c r="W110" s="1"/>
@@ -7741,7 +7735,7 @@
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
       <c r="S111" s="1"/>
-      <c r="T111" s="43"/>
+      <c r="T111" s="1"/>
       <c r="U111" s="1"/>
       <c r="V111" s="1"/>
       <c r="W111" s="1"/>
@@ -7788,7 +7782,7 @@
       </c>
       <c r="R112" s="1"/>
       <c r="S112" s="1"/>
-      <c r="T112" s="43" t="s">
+      <c r="T112" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U112" s="1"/>
@@ -7837,7 +7831,7 @@
       </c>
       <c r="R113" s="1"/>
       <c r="S113" s="1"/>
-      <c r="T113" s="43"/>
+      <c r="T113" s="1"/>
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
       <c r="W113" s="1"/>
@@ -7880,7 +7874,7 @@
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
       <c r="S114" s="1"/>
-      <c r="T114" s="43"/>
+      <c r="T114" s="1"/>
       <c r="U114" s="1"/>
       <c r="V114" s="1"/>
       <c r="W114" s="1"/>
@@ -7927,7 +7921,7 @@
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
       <c r="S115" s="1"/>
-      <c r="T115" s="43"/>
+      <c r="T115" s="1"/>
       <c r="U115" s="1"/>
       <c r="V115" s="1"/>
       <c r="W115" s="1"/>
@@ -7970,7 +7964,7 @@
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
       <c r="S116" s="1"/>
-      <c r="T116" s="43"/>
+      <c r="T116" s="1"/>
       <c r="U116" s="1"/>
       <c r="V116" s="1"/>
       <c r="W116" s="1"/>
@@ -8013,7 +8007,7 @@
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
       <c r="S117" s="1"/>
-      <c r="T117" s="43"/>
+      <c r="T117" s="1"/>
       <c r="U117" s="1"/>
       <c r="V117" s="1"/>
       <c r="W117" s="1"/>
@@ -8056,7 +8050,7 @@
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
       <c r="S118" s="1"/>
-      <c r="T118" s="43"/>
+      <c r="T118" s="1"/>
       <c r="U118" s="1"/>
       <c r="V118" s="1"/>
       <c r="W118" s="1"/>
@@ -8099,7 +8093,7 @@
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
       <c r="S119" s="1"/>
-      <c r="T119" s="43"/>
+      <c r="T119" s="1"/>
       <c r="U119" s="1"/>
       <c r="V119" s="1"/>
       <c r="W119" s="1"/>
@@ -8142,7 +8136,7 @@
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
       <c r="S120" s="1"/>
-      <c r="T120" s="43" t="s">
+      <c r="T120" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U120" s="1"/>
@@ -8187,7 +8181,7 @@
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
       <c r="S121" s="1"/>
-      <c r="T121" s="43"/>
+      <c r="T121" s="1"/>
       <c r="U121" s="1"/>
       <c r="V121" s="1"/>
       <c r="W121" s="1"/>
@@ -8230,7 +8224,7 @@
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
       <c r="S122" s="1"/>
-      <c r="T122" s="43"/>
+      <c r="T122" s="1"/>
       <c r="U122" s="1"/>
       <c r="V122" s="1"/>
       <c r="W122" s="1"/>
@@ -8273,7 +8267,7 @@
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
       <c r="S123" s="1"/>
-      <c r="T123" s="43"/>
+      <c r="T123" s="1"/>
       <c r="U123" s="1"/>
       <c r="V123" s="1"/>
       <c r="W123" s="1"/>
@@ -8316,7 +8310,7 @@
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
       <c r="S124" s="1"/>
-      <c r="T124" s="43"/>
+      <c r="T124" s="1"/>
       <c r="U124" s="1"/>
       <c r="V124" s="1"/>
       <c r="W124" s="1"/>
@@ -8359,7 +8353,7 @@
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
       <c r="S125" s="1"/>
-      <c r="T125" s="43"/>
+      <c r="T125" s="1"/>
       <c r="U125" s="1"/>
       <c r="V125" s="1"/>
       <c r="W125" s="1"/>
@@ -8404,7 +8398,7 @@
       </c>
       <c r="R126" s="1"/>
       <c r="S126" s="1"/>
-      <c r="T126" s="43" t="s">
+      <c r="T126" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U126" s="1"/>
@@ -8449,7 +8443,7 @@
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
       <c r="S127" s="1"/>
-      <c r="T127" s="43"/>
+      <c r="T127" s="1"/>
       <c r="U127" s="1"/>
       <c r="V127" s="1"/>
       <c r="W127" s="1"/>
@@ -8494,7 +8488,7 @@
       </c>
       <c r="R128" s="1"/>
       <c r="S128" s="1"/>
-      <c r="T128" s="43"/>
+      <c r="T128" s="1"/>
       <c r="U128" s="1"/>
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
@@ -8541,7 +8535,7 @@
       <c r="S129" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T129" s="43"/>
+      <c r="T129" s="1"/>
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
       <c r="W129" s="1"/>
@@ -8586,7 +8580,7 @@
       </c>
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
-      <c r="T130" s="43" t="s">
+      <c r="T130" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U130" s="1"/>
@@ -8635,7 +8629,7 @@
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
       <c r="S131" s="1"/>
-      <c r="T131" s="43"/>
+      <c r="T131" s="1"/>
       <c r="U131" s="1"/>
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
@@ -8680,7 +8674,7 @@
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
       <c r="S132" s="1"/>
-      <c r="T132" s="43" t="s">
+      <c r="T132" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U132" s="1"/>
@@ -8727,7 +8721,7 @@
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
-      <c r="T133" s="43"/>
+      <c r="T133" s="1"/>
       <c r="U133" s="1"/>
       <c r="V133" s="1"/>
       <c r="W133" s="1"/>
@@ -8770,7 +8764,7 @@
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
       <c r="S134" s="1"/>
-      <c r="T134" s="43"/>
+      <c r="T134" s="1"/>
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
       <c r="W134" s="1"/>
@@ -8813,7 +8807,7 @@
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
       <c r="S135" s="1"/>
-      <c r="T135" s="43"/>
+      <c r="T135" s="1"/>
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
       <c r="W135" s="1"/>
@@ -8856,7 +8850,7 @@
       <c r="Q136" s="1"/>
       <c r="R136" s="1"/>
       <c r="S136" s="1"/>
-      <c r="T136" s="43"/>
+      <c r="T136" s="1"/>
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
       <c r="W136" s="1"/>
@@ -8901,7 +8895,7 @@
       <c r="Q137" s="1"/>
       <c r="R137" s="1"/>
       <c r="S137" s="1"/>
-      <c r="T137" s="43"/>
+      <c r="T137" s="1"/>
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
       <c r="W137" s="1"/>
@@ -8944,7 +8938,7 @@
       <c r="Q138" s="1"/>
       <c r="R138" s="1"/>
       <c r="S138" s="1"/>
-      <c r="T138" s="43" t="s">
+      <c r="T138" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U138" s="1"/>
@@ -8991,7 +8985,7 @@
       <c r="Q139" s="1"/>
       <c r="R139" s="1"/>
       <c r="S139" s="1"/>
-      <c r="T139" s="43"/>
+      <c r="T139" s="1"/>
       <c r="U139" s="1"/>
       <c r="V139" s="1"/>
       <c r="W139" s="1"/>
@@ -9034,7 +9028,7 @@
       <c r="Q140" s="1"/>
       <c r="R140" s="1"/>
       <c r="S140" s="1"/>
-      <c r="T140" s="43"/>
+      <c r="T140" s="1"/>
       <c r="U140" s="1"/>
       <c r="V140" s="1"/>
       <c r="W140" s="1"/>
@@ -9077,7 +9071,7 @@
       <c r="Q141" s="1"/>
       <c r="R141" s="1"/>
       <c r="S141" s="1"/>
-      <c r="T141" s="43"/>
+      <c r="T141" s="1"/>
       <c r="U141" s="1"/>
       <c r="V141" s="1"/>
       <c r="W141" s="1"/>
@@ -9120,7 +9114,7 @@
       <c r="Q142" s="1"/>
       <c r="R142" s="1"/>
       <c r="S142" s="1"/>
-      <c r="T142" s="43" t="s">
+      <c r="T142" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U142" s="1"/>
@@ -9165,7 +9159,7 @@
       <c r="Q143" s="1"/>
       <c r="R143" s="1"/>
       <c r="S143" s="1"/>
-      <c r="T143" s="43"/>
+      <c r="T143" s="1"/>
       <c r="U143" s="1"/>
       <c r="V143" s="1"/>
       <c r="W143" s="1"/>
@@ -9208,7 +9202,7 @@
       <c r="Q144" s="1"/>
       <c r="R144" s="1"/>
       <c r="S144" s="1"/>
-      <c r="T144" s="43"/>
+      <c r="T144" s="1"/>
       <c r="U144" s="1"/>
       <c r="V144" s="1"/>
       <c r="W144" s="1"/>
@@ -9251,7 +9245,7 @@
       <c r="Q145" s="1"/>
       <c r="R145" s="1"/>
       <c r="S145" s="1"/>
-      <c r="T145" s="43"/>
+      <c r="T145" s="1"/>
       <c r="U145" s="1"/>
       <c r="V145" s="1"/>
       <c r="W145" s="1"/>
@@ -9294,7 +9288,7 @@
       <c r="Q146" s="1"/>
       <c r="R146" s="1"/>
       <c r="S146" s="1"/>
-      <c r="T146" s="43"/>
+      <c r="T146" s="1"/>
       <c r="U146" s="1"/>
       <c r="V146" s="1"/>
       <c r="W146" s="1"/>
@@ -9337,7 +9331,7 @@
       <c r="Q147" s="1"/>
       <c r="R147" s="1"/>
       <c r="S147" s="1"/>
-      <c r="T147" s="43"/>
+      <c r="T147" s="1"/>
       <c r="U147" s="1"/>
       <c r="V147" s="1"/>
       <c r="W147" s="1"/>
@@ -9386,7 +9380,7 @@
       </c>
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
-      <c r="T148" s="43"/>
+      <c r="T148" s="1"/>
       <c r="U148" s="1"/>
       <c r="V148" s="1"/>
       <c r="W148" s="1"/>
@@ -9429,7 +9423,7 @@
       <c r="Q149" s="1"/>
       <c r="R149" s="1"/>
       <c r="S149" s="1"/>
-      <c r="T149" s="43"/>
+      <c r="T149" s="1"/>
       <c r="U149" s="1"/>
       <c r="V149" s="1"/>
       <c r="W149" s="1"/>
@@ -9472,7 +9466,7 @@
       <c r="Q150" s="1"/>
       <c r="R150" s="1"/>
       <c r="S150" s="1"/>
-      <c r="T150" s="43"/>
+      <c r="T150" s="1"/>
       <c r="U150" s="1"/>
       <c r="V150" s="1"/>
       <c r="W150" s="1"/>
@@ -9517,7 +9511,7 @@
       <c r="Q151" s="1"/>
       <c r="R151" s="1"/>
       <c r="S151" s="1"/>
-      <c r="T151" s="43"/>
+      <c r="T151" s="1"/>
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
@@ -9560,7 +9554,7 @@
       <c r="Q152" s="1"/>
       <c r="R152" s="1"/>
       <c r="S152" s="1"/>
-      <c r="T152" s="43"/>
+      <c r="T152" s="1"/>
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
@@ -9605,7 +9599,7 @@
       <c r="Q153" s="1"/>
       <c r="R153" s="1"/>
       <c r="S153" s="1"/>
-      <c r="T153" s="43" t="s">
+      <c r="T153" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U153" s="1"/>
@@ -9654,7 +9648,7 @@
       <c r="Q154" s="1"/>
       <c r="R154" s="1"/>
       <c r="S154" s="1"/>
-      <c r="T154" s="43"/>
+      <c r="T154" s="1"/>
       <c r="U154" s="1"/>
       <c r="V154" s="1"/>
       <c r="W154" s="1"/>
@@ -9701,7 +9695,7 @@
       </c>
       <c r="R155" s="1"/>
       <c r="S155" s="1"/>
-      <c r="T155" s="43"/>
+      <c r="T155" s="1"/>
       <c r="U155" s="1"/>
       <c r="V155" s="1"/>
       <c r="W155" s="1"/>
@@ -9748,7 +9742,7 @@
       <c r="Q156" s="1"/>
       <c r="R156" s="1"/>
       <c r="S156" s="1"/>
-      <c r="T156" s="43"/>
+      <c r="T156" s="1"/>
       <c r="U156" s="1"/>
       <c r="V156" s="1"/>
       <c r="W156" s="1"/>
@@ -9793,7 +9787,7 @@
       <c r="Q157" s="1"/>
       <c r="R157" s="1"/>
       <c r="S157" s="1"/>
-      <c r="T157" s="43"/>
+      <c r="T157" s="1"/>
       <c r="U157" s="1"/>
       <c r="V157" s="1"/>
       <c r="W157" s="1"/>
@@ -9840,7 +9834,7 @@
       <c r="Q158" s="1"/>
       <c r="R158" s="1"/>
       <c r="S158" s="1"/>
-      <c r="T158" s="43" t="s">
+      <c r="T158" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U158" s="1"/>
@@ -9891,7 +9885,7 @@
       <c r="Q159" s="1"/>
       <c r="R159" s="1"/>
       <c r="S159" s="1"/>
-      <c r="T159" s="43"/>
+      <c r="T159" s="1"/>
       <c r="U159" s="1"/>
       <c r="V159" s="1"/>
       <c r="W159" s="1"/>
@@ -9942,7 +9936,7 @@
       <c r="S160" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T160" s="43"/>
+      <c r="T160" s="1"/>
       <c r="U160" s="1"/>
       <c r="V160" s="1"/>
       <c r="W160" s="1"/>
@@ -9987,7 +9981,7 @@
       <c r="Q161" s="1"/>
       <c r="R161" s="1"/>
       <c r="S161" s="1"/>
-      <c r="T161" s="43"/>
+      <c r="T161" s="1"/>
       <c r="U161" s="1"/>
       <c r="V161" s="1"/>
       <c r="W161" s="1"/>
@@ -10032,7 +10026,7 @@
       <c r="Q162" s="1"/>
       <c r="R162" s="1"/>
       <c r="S162" s="1"/>
-      <c r="T162" s="43"/>
+      <c r="T162" s="1"/>
       <c r="U162" s="1"/>
       <c r="V162" s="1"/>
       <c r="W162" s="1"/>
@@ -10083,7 +10077,7 @@
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
       <c r="S163" s="1"/>
-      <c r="T163" s="43"/>
+      <c r="T163" s="1"/>
       <c r="U163" s="1"/>
       <c r="V163" s="1"/>
       <c r="W163" s="1"/>
@@ -10130,7 +10124,7 @@
       <c r="Q164" s="3"/>
       <c r="R164" s="3"/>
       <c r="S164" s="1"/>
-      <c r="T164" s="43"/>
+      <c r="T164" s="1"/>
       <c r="U164" s="1"/>
       <c r="V164" s="3"/>
       <c r="W164" s="3"/>
@@ -10175,7 +10169,7 @@
       <c r="S165" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T165" s="43" t="s">
+      <c r="T165" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U165" s="1"/>
@@ -10220,7 +10214,7 @@
       <c r="Q166" s="1"/>
       <c r="R166" s="1"/>
       <c r="S166" s="1"/>
-      <c r="T166" s="43"/>
+      <c r="T166" s="1"/>
       <c r="U166" s="1"/>
       <c r="V166" s="1"/>
       <c r="W166" s="1"/>
@@ -10263,7 +10257,7 @@
       <c r="Q167" s="1"/>
       <c r="R167" s="1"/>
       <c r="S167" s="1"/>
-      <c r="T167" s="43"/>
+      <c r="T167" s="1"/>
       <c r="U167" s="1"/>
       <c r="V167" s="1"/>
       <c r="W167" s="1"/>
@@ -10306,7 +10300,7 @@
       <c r="Q168" s="1"/>
       <c r="R168" s="1"/>
       <c r="S168" s="1"/>
-      <c r="T168" s="43"/>
+      <c r="T168" s="1"/>
       <c r="U168" s="1"/>
       <c r="V168" s="1"/>
       <c r="W168" s="1"/>
@@ -10349,7 +10343,7 @@
       <c r="Q169" s="1"/>
       <c r="R169" s="1"/>
       <c r="S169" s="1"/>
-      <c r="T169" s="43"/>
+      <c r="T169" s="1"/>
       <c r="U169" s="1"/>
       <c r="V169" s="1"/>
       <c r="W169" s="1"/>
@@ -10392,7 +10386,7 @@
       <c r="Q170" s="1"/>
       <c r="R170" s="1"/>
       <c r="S170" s="1"/>
-      <c r="T170" s="43"/>
+      <c r="T170" s="1"/>
       <c r="U170" s="1"/>
       <c r="V170" s="1"/>
       <c r="W170" s="1"/>
@@ -10435,7 +10429,7 @@
       <c r="Q171" s="1"/>
       <c r="R171" s="1"/>
       <c r="S171" s="1"/>
-      <c r="T171" s="43"/>
+      <c r="T171" s="1"/>
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
       <c r="W171" s="1"/>
@@ -10480,7 +10474,7 @@
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
       <c r="S172" s="1"/>
-      <c r="T172" s="43"/>
+      <c r="T172" s="1"/>
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
       <c r="W172" s="1"/>
@@ -10523,7 +10517,7 @@
       <c r="Q173" s="1"/>
       <c r="R173" s="1"/>
       <c r="S173" s="1"/>
-      <c r="T173" s="43"/>
+      <c r="T173" s="1"/>
       <c r="U173" s="1"/>
       <c r="V173" s="1"/>
       <c r="W173" s="1"/>
@@ -10576,7 +10570,7 @@
       <c r="S174" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T174" s="43" t="s">
+      <c r="T174" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U174" s="1"/>
@@ -10631,7 +10625,7 @@
       <c r="S175" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T175" s="43" t="s">
+      <c r="T175" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U175" s="1"/>
@@ -10690,7 +10684,7 @@
       <c r="S176" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T176" s="43" t="s">
+      <c r="T176" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U176" s="1"/>
@@ -10743,7 +10737,7 @@
       <c r="S177" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T177" s="43" t="s">
+      <c r="T177" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U177" s="1"/>
@@ -10792,7 +10786,7 @@
       <c r="S178" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T178" s="43"/>
+      <c r="T178" s="1"/>
       <c r="U178" s="1"/>
       <c r="V178" s="1"/>
       <c r="W178" s="1"/>
@@ -10841,7 +10835,7 @@
       <c r="S179" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T179" s="43"/>
+      <c r="T179" s="1"/>
       <c r="U179" s="1"/>
       <c r="V179" s="1"/>
       <c r="W179" s="1"/>
@@ -10892,7 +10886,7 @@
       <c r="S180" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T180" s="43"/>
+      <c r="T180" s="1"/>
       <c r="U180" s="1"/>
       <c r="V180" s="1"/>
       <c r="W180" s="1"/>
@@ -10941,7 +10935,7 @@
       <c r="S181" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T181" s="43"/>
+      <c r="T181" s="1"/>
       <c r="U181" s="1"/>
       <c r="V181" s="1"/>
       <c r="W181" s="1"/>
@@ -10990,7 +10984,7 @@
       <c r="S182" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T182" s="43"/>
+      <c r="T182" s="1"/>
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
       <c r="W182" s="1"/>
@@ -11043,7 +11037,7 @@
       <c r="S183" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T183" s="43"/>
+      <c r="T183" s="1"/>
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
       <c r="W183" s="1"/>
@@ -11098,7 +11092,7 @@
       <c r="S184" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T184" s="43"/>
+      <c r="T184" s="1"/>
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
       <c r="W184" s="1"/>
@@ -11151,7 +11145,7 @@
       <c r="S185" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T185" s="43"/>
+      <c r="T185" s="1"/>
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
       <c r="W185" s="1"/>
@@ -11196,7 +11190,7 @@
       <c r="Q186" s="1"/>
       <c r="R186" s="1"/>
       <c r="S186" s="1"/>
-      <c r="T186" s="43"/>
+      <c r="T186" s="1"/>
       <c r="U186" s="1"/>
       <c r="V186" s="1" t="s">
         <v>156</v>
@@ -11245,7 +11239,7 @@
       <c r="Q187" s="1"/>
       <c r="R187" s="1"/>
       <c r="S187" s="1"/>
-      <c r="T187" s="43"/>
+      <c r="T187" s="1"/>
       <c r="U187" s="1"/>
       <c r="V187" s="1" t="s">
         <v>156</v>
@@ -11296,7 +11290,7 @@
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
       <c r="S188" s="1"/>
-      <c r="T188" s="43"/>
+      <c r="T188" s="1"/>
       <c r="U188" s="1"/>
       <c r="V188" s="1" t="s">
         <v>156</v>
@@ -11345,7 +11339,7 @@
       <c r="Q189" s="1"/>
       <c r="R189" s="1"/>
       <c r="S189" s="1"/>
-      <c r="T189" s="43"/>
+      <c r="T189" s="1"/>
       <c r="U189" s="1"/>
       <c r="V189" s="1" t="s">
         <v>156</v>
@@ -11394,7 +11388,7 @@
       <c r="Q190" s="1"/>
       <c r="R190" s="1"/>
       <c r="S190" s="1"/>
-      <c r="T190" s="43"/>
+      <c r="T190" s="1"/>
       <c r="U190" s="1"/>
       <c r="V190" s="1" t="s">
         <v>156</v>
@@ -11443,7 +11437,7 @@
       <c r="Q191" s="1"/>
       <c r="R191" s="1"/>
       <c r="S191" s="1"/>
-      <c r="T191" s="43"/>
+      <c r="T191" s="1"/>
       <c r="U191" s="1"/>
       <c r="V191" s="1" t="s">
         <v>156</v>
@@ -12551,7 +12545,7 @@
       <c r="Q215" s="1"/>
       <c r="R215" s="1"/>
       <c r="S215" s="1"/>
-      <c r="T215" s="43"/>
+      <c r="T215" s="1"/>
       <c r="U215" s="1"/>
       <c r="V215" s="1"/>
       <c r="W215" s="1"/>
@@ -12751,7 +12745,7 @@
       <c r="Q219" s="1"/>
       <c r="R219" s="1"/>
       <c r="S219" s="1"/>
-      <c r="T219" s="43"/>
+      <c r="T219" s="1"/>
       <c r="U219" s="1"/>
       <c r="V219" s="1"/>
       <c r="W219" s="1"/>
@@ -12794,7 +12788,7 @@
       <c r="Q220" s="1"/>
       <c r="R220" s="1"/>
       <c r="S220" s="1"/>
-      <c r="T220" s="43"/>
+      <c r="T220" s="1"/>
       <c r="U220" s="1"/>
       <c r="V220" s="1"/>
       <c r="W220" s="1"/>
@@ -12837,7 +12831,7 @@
       <c r="Q221" s="1"/>
       <c r="R221" s="1"/>
       <c r="S221" s="1"/>
-      <c r="T221" s="43"/>
+      <c r="T221" s="1"/>
       <c r="U221" s="1"/>
       <c r="V221" s="1"/>
       <c r="W221" s="1"/>
@@ -12882,7 +12876,7 @@
       <c r="Q222" s="1"/>
       <c r="R222" s="1"/>
       <c r="S222" s="1"/>
-      <c r="T222" s="43"/>
+      <c r="T222" s="1"/>
       <c r="U222" s="1"/>
       <c r="V222" s="1"/>
       <c r="W222" s="1"/>
@@ -12925,7 +12919,7 @@
       <c r="Q223" s="1"/>
       <c r="R223" s="1"/>
       <c r="S223" s="1"/>
-      <c r="T223" s="43"/>
+      <c r="T223" s="1"/>
       <c r="U223" s="1"/>
       <c r="V223" s="1"/>
       <c r="W223" s="1"/>
@@ -12968,7 +12962,7 @@
       <c r="Q224" s="1"/>
       <c r="R224" s="1"/>
       <c r="S224" s="1"/>
-      <c r="T224" s="43"/>
+      <c r="T224" s="1"/>
       <c r="U224" s="1"/>
       <c r="V224" s="1"/>
       <c r="W224" s="1"/>
@@ -13011,7 +13005,7 @@
       <c r="Q225" s="1"/>
       <c r="R225" s="1"/>
       <c r="S225" s="1"/>
-      <c r="T225" s="43"/>
+      <c r="T225" s="1"/>
       <c r="U225" s="1"/>
       <c r="V225" s="1"/>
       <c r="W225" s="1"/>
@@ -13054,7 +13048,7 @@
       <c r="Q226" s="1"/>
       <c r="R226" s="1"/>
       <c r="S226" s="1"/>
-      <c r="T226" s="43"/>
+      <c r="T226" s="1"/>
       <c r="U226" s="1"/>
       <c r="V226" s="1"/>
       <c r="W226" s="1"/>
@@ -13097,7 +13091,7 @@
       <c r="Q227" s="1"/>
       <c r="R227" s="1"/>
       <c r="S227" s="1"/>
-      <c r="T227" s="43"/>
+      <c r="T227" s="1"/>
       <c r="U227" s="1"/>
       <c r="V227" s="1"/>
       <c r="W227" s="1"/>
@@ -13140,7 +13134,7 @@
       <c r="Q228" s="1"/>
       <c r="R228" s="1"/>
       <c r="S228" s="1"/>
-      <c r="T228" s="43"/>
+      <c r="T228" s="1"/>
       <c r="U228" s="1"/>
       <c r="V228" s="1"/>
       <c r="W228" s="1"/>
@@ -13183,7 +13177,7 @@
       <c r="Q229" s="1"/>
       <c r="R229" s="1"/>
       <c r="S229" s="1"/>
-      <c r="T229" s="43"/>
+      <c r="T229" s="1"/>
       <c r="U229" s="1"/>
       <c r="V229" s="1"/>
       <c r="W229" s="1"/>
@@ -13226,7 +13220,7 @@
       <c r="Q230" s="1"/>
       <c r="R230" s="1"/>
       <c r="S230" s="1"/>
-      <c r="T230" s="43"/>
+      <c r="T230" s="1"/>
       <c r="U230" s="1"/>
       <c r="V230" s="1"/>
       <c r="W230" s="1"/>
@@ -13269,7 +13263,7 @@
       <c r="Q231" s="1"/>
       <c r="R231" s="1"/>
       <c r="S231" s="1"/>
-      <c r="T231" s="43"/>
+      <c r="T231" s="1"/>
       <c r="U231" s="1"/>
       <c r="V231" s="1"/>
       <c r="W231" s="1"/>
@@ -13312,7 +13306,7 @@
       <c r="Q232" s="1"/>
       <c r="R232" s="1"/>
       <c r="S232" s="1"/>
-      <c r="T232" s="43"/>
+      <c r="T232" s="1"/>
       <c r="U232" s="1"/>
       <c r="V232" s="1"/>
       <c r="W232" s="1"/>
@@ -13357,7 +13351,7 @@
       <c r="Q233" s="1"/>
       <c r="R233" s="1"/>
       <c r="S233" s="1"/>
-      <c r="T233" s="43"/>
+      <c r="T233" s="1"/>
       <c r="U233" s="1"/>
       <c r="V233" s="1"/>
       <c r="W233" s="1"/>
@@ -13402,7 +13396,7 @@
       <c r="Q234" s="1"/>
       <c r="R234" s="1"/>
       <c r="S234" s="1"/>
-      <c r="T234" s="43"/>
+      <c r="T234" s="1"/>
       <c r="U234" s="1"/>
       <c r="V234" s="1"/>
       <c r="W234" s="1"/>
@@ -13447,7 +13441,7 @@
       <c r="S235" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T235" s="43"/>
+      <c r="T235" s="1"/>
       <c r="U235" s="1"/>
       <c r="V235" s="1"/>
       <c r="W235" s="1"/>
@@ -13492,7 +13486,7 @@
       <c r="Q236" s="1"/>
       <c r="R236" s="1"/>
       <c r="S236" s="1"/>
-      <c r="T236" s="43"/>
+      <c r="T236" s="1"/>
       <c r="U236" s="1"/>
       <c r="V236" s="1"/>
       <c r="W236" s="1"/>
@@ -13535,7 +13529,7 @@
       <c r="Q237" s="1"/>
       <c r="R237" s="1"/>
       <c r="S237" s="1"/>
-      <c r="T237" s="43"/>
+      <c r="T237" s="1"/>
       <c r="U237" s="1"/>
       <c r="V237" s="1"/>
       <c r="W237" s="1"/>
@@ -13578,7 +13572,7 @@
       <c r="Q238" s="1"/>
       <c r="R238" s="1"/>
       <c r="S238" s="1"/>
-      <c r="T238" s="43"/>
+      <c r="T238" s="1"/>
       <c r="U238" s="1"/>
       <c r="V238" s="1"/>
       <c r="W238" s="1"/>
@@ -13621,7 +13615,7 @@
       <c r="Q239" s="1"/>
       <c r="R239" s="1"/>
       <c r="S239" s="1"/>
-      <c r="T239" s="43"/>
+      <c r="T239" s="1"/>
       <c r="U239" s="1"/>
       <c r="V239" s="1"/>
       <c r="W239" s="1"/>
@@ -13664,7 +13658,7 @@
       <c r="Q240" s="1"/>
       <c r="R240" s="1"/>
       <c r="S240" s="1"/>
-      <c r="T240" s="43"/>
+      <c r="T240" s="1"/>
       <c r="U240" s="1"/>
       <c r="V240" s="1"/>
       <c r="W240" s="1"/>
@@ -13707,7 +13701,7 @@
       <c r="Q241" s="1"/>
       <c r="R241" s="1"/>
       <c r="S241" s="1"/>
-      <c r="T241" s="43"/>
+      <c r="T241" s="1"/>
       <c r="U241" s="1"/>
       <c r="V241" s="1"/>
       <c r="W241" s="1"/>
@@ -13750,7 +13744,7 @@
       <c r="Q242" s="1"/>
       <c r="R242" s="1"/>
       <c r="S242" s="1"/>
-      <c r="T242" s="43"/>
+      <c r="T242" s="1"/>
       <c r="U242" s="1"/>
       <c r="V242" s="1"/>
       <c r="W242" s="1"/>
@@ -13795,7 +13789,7 @@
       <c r="S243" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T243" s="43"/>
+      <c r="T243" s="1"/>
       <c r="U243" s="1"/>
       <c r="V243" s="1"/>
       <c r="W243" s="1"/>
@@ -13840,7 +13834,7 @@
       <c r="S244" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T244" s="43"/>
+      <c r="T244" s="1"/>
       <c r="U244" s="1"/>
       <c r="V244" s="1"/>
       <c r="W244" s="1"/>
@@ -13885,7 +13879,7 @@
       <c r="S245" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T245" s="43"/>
+      <c r="T245" s="1"/>
       <c r="U245" s="1"/>
       <c r="V245" s="1"/>
       <c r="W245" s="1"/>
@@ -13928,7 +13922,7 @@
       <c r="Q246" s="1"/>
       <c r="R246" s="1"/>
       <c r="S246" s="1"/>
-      <c r="T246" s="43"/>
+      <c r="T246" s="1"/>
       <c r="U246" s="1"/>
       <c r="V246" s="1"/>
       <c r="W246" s="1"/>
@@ -13973,7 +13967,7 @@
       <c r="Q247" s="1"/>
       <c r="R247" s="1"/>
       <c r="S247" s="1"/>
-      <c r="T247" s="43"/>
+      <c r="T247" s="1"/>
       <c r="U247" s="1"/>
       <c r="V247" s="1"/>
       <c r="W247" s="1"/>
@@ -14018,7 +14012,7 @@
       <c r="Q248" s="1"/>
       <c r="R248" s="1"/>
       <c r="S248" s="1"/>
-      <c r="T248" s="43"/>
+      <c r="T248" s="1"/>
       <c r="U248" s="1"/>
       <c r="V248" s="1"/>
       <c r="W248" s="1"/>
@@ -14065,7 +14059,7 @@
       <c r="Q249" s="1"/>
       <c r="R249" s="1"/>
       <c r="S249" s="1"/>
-      <c r="T249" s="43"/>
+      <c r="T249" s="1"/>
       <c r="U249" s="1"/>
       <c r="V249" s="1"/>
       <c r="W249" s="1"/>
@@ -14108,7 +14102,7 @@
       <c r="Q250" s="1"/>
       <c r="R250" s="1"/>
       <c r="S250" s="1"/>
-      <c r="T250" s="43"/>
+      <c r="T250" s="1"/>
       <c r="U250" s="1"/>
       <c r="V250" s="1"/>
       <c r="W250" s="1"/>
@@ -14151,7 +14145,7 @@
       <c r="Q251" s="1"/>
       <c r="R251" s="1"/>
       <c r="S251" s="1"/>
-      <c r="T251" s="43"/>
+      <c r="T251" s="1"/>
       <c r="U251" s="1"/>
       <c r="V251" s="1"/>
       <c r="W251" s="1"/>
@@ -14194,7 +14188,7 @@
       <c r="Q252" s="1"/>
       <c r="R252" s="1"/>
       <c r="S252" s="1"/>
-      <c r="T252" s="43"/>
+      <c r="T252" s="1"/>
       <c r="U252" s="1"/>
       <c r="V252" s="1"/>
       <c r="W252" s="1"/>
@@ -14237,7 +14231,7 @@
       <c r="Q253" s="1"/>
       <c r="R253" s="1"/>
       <c r="S253" s="1"/>
-      <c r="T253" s="43"/>
+      <c r="T253" s="1"/>
       <c r="U253" s="1"/>
       <c r="V253" s="1"/>
       <c r="W253" s="1"/>
@@ -14280,7 +14274,7 @@
       <c r="Q254" s="1"/>
       <c r="R254" s="1"/>
       <c r="S254" s="1"/>
-      <c r="T254" s="43"/>
+      <c r="T254" s="1"/>
       <c r="U254" s="1"/>
       <c r="V254" s="1"/>
       <c r="W254" s="1"/>
@@ -14323,7 +14317,7 @@
       <c r="Q255" s="1"/>
       <c r="R255" s="1"/>
       <c r="S255" s="1"/>
-      <c r="T255" s="43"/>
+      <c r="T255" s="1"/>
       <c r="U255" s="1"/>
       <c r="V255" s="1"/>
       <c r="W255" s="1"/>
@@ -14366,7 +14360,7 @@
       <c r="Q256" s="1"/>
       <c r="R256" s="1"/>
       <c r="S256" s="1"/>
-      <c r="T256" s="43"/>
+      <c r="T256" s="1"/>
       <c r="U256" s="1"/>
       <c r="V256" s="1"/>
       <c r="W256" s="1"/>
@@ -14413,7 +14407,7 @@
       <c r="Q257" s="1"/>
       <c r="R257" s="1"/>
       <c r="S257" s="1"/>
-      <c r="T257" s="43"/>
+      <c r="T257" s="1"/>
       <c r="U257" s="1"/>
       <c r="V257" s="1"/>
       <c r="W257" s="1"/>
@@ -14458,7 +14452,7 @@
       <c r="Q258" s="1"/>
       <c r="R258" s="1"/>
       <c r="S258" s="1"/>
-      <c r="T258" s="43"/>
+      <c r="T258" s="1"/>
       <c r="U258" s="1"/>
       <c r="V258" s="1"/>
       <c r="W258" s="1"/>
@@ -14503,7 +14497,7 @@
       <c r="Q259" s="1"/>
       <c r="R259" s="1"/>
       <c r="S259" s="1"/>
-      <c r="T259" s="43"/>
+      <c r="T259" s="1"/>
       <c r="U259" s="1"/>
       <c r="V259" s="1"/>
       <c r="W259" s="1"/>
@@ -14548,7 +14542,7 @@
       <c r="Q260" s="1"/>
       <c r="R260" s="1"/>
       <c r="S260" s="1"/>
-      <c r="T260" s="43"/>
+      <c r="T260" s="1"/>
       <c r="U260" s="1"/>
       <c r="V260" s="1"/>
       <c r="W260" s="1"/>
@@ -14593,7 +14587,7 @@
       <c r="Q261" s="1"/>
       <c r="R261" s="1"/>
       <c r="S261" s="1"/>
-      <c r="T261" s="43" t="s">
+      <c r="T261" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U261" s="1"/>
@@ -14636,7 +14630,7 @@
       <c r="Q262" s="1"/>
       <c r="R262" s="1"/>
       <c r="S262" s="1"/>
-      <c r="T262" s="43"/>
+      <c r="T262" s="1"/>
       <c r="U262" s="1"/>
       <c r="V262" s="1"/>
       <c r="W262" s="1"/>
@@ -14677,7 +14671,7 @@
       <c r="Q263" s="1"/>
       <c r="R263" s="1"/>
       <c r="S263" s="1"/>
-      <c r="T263" s="43"/>
+      <c r="T263" s="1"/>
       <c r="U263" s="1"/>
       <c r="V263" s="1"/>
       <c r="W263" s="1"/>
@@ -14718,7 +14712,7 @@
       <c r="Q264" s="1"/>
       <c r="R264" s="1"/>
       <c r="S264" s="1"/>
-      <c r="T264" s="43"/>
+      <c r="T264" s="1"/>
       <c r="U264" s="1"/>
       <c r="V264" s="1"/>
       <c r="W264" s="1"/>
@@ -14759,7 +14753,7 @@
       <c r="Q265" s="1"/>
       <c r="R265" s="1"/>
       <c r="S265" s="1"/>
-      <c r="T265" s="43"/>
+      <c r="T265" s="1"/>
       <c r="U265" s="1"/>
       <c r="V265" s="1"/>
       <c r="W265" s="1"/>
@@ -14800,7 +14794,7 @@
       <c r="Q266" s="1"/>
       <c r="R266" s="1"/>
       <c r="S266" s="1"/>
-      <c r="T266" s="43"/>
+      <c r="T266" s="1"/>
       <c r="U266" s="1"/>
       <c r="V266" s="1"/>
       <c r="W266" s="1"/>
@@ -14841,7 +14835,7 @@
       <c r="Q267" s="1"/>
       <c r="R267" s="1"/>
       <c r="S267" s="1"/>
-      <c r="T267" s="43"/>
+      <c r="T267" s="1"/>
       <c r="U267" s="1"/>
       <c r="V267" s="1"/>
       <c r="W267" s="1"/>
@@ -14882,7 +14876,7 @@
       <c r="Q268" s="1"/>
       <c r="R268" s="1"/>
       <c r="S268" s="1"/>
-      <c r="T268" s="43"/>
+      <c r="T268" s="1"/>
       <c r="U268" s="1"/>
       <c r="V268" s="1"/>
       <c r="W268" s="1"/>
@@ -14923,7 +14917,7 @@
       <c r="Q269" s="1"/>
       <c r="R269" s="1"/>
       <c r="S269" s="1"/>
-      <c r="T269" s="43"/>
+      <c r="T269" s="1"/>
       <c r="U269" s="1"/>
       <c r="V269" s="1"/>
       <c r="W269" s="1"/>
@@ -14964,7 +14958,7 @@
       <c r="Q270" s="1"/>
       <c r="R270" s="1"/>
       <c r="S270" s="1"/>
-      <c r="T270" s="43"/>
+      <c r="T270" s="1"/>
       <c r="U270" s="1"/>
       <c r="V270" s="1"/>
       <c r="W270" s="1"/>
@@ -15005,7 +14999,7 @@
       <c r="Q271" s="1"/>
       <c r="R271" s="1"/>
       <c r="S271" s="1"/>
-      <c r="T271" s="43"/>
+      <c r="T271" s="1"/>
       <c r="U271" s="1"/>
       <c r="V271" s="1"/>
       <c r="W271" s="1"/>
@@ -15046,7 +15040,7 @@
       <c r="Q272" s="1"/>
       <c r="R272" s="1"/>
       <c r="S272" s="1"/>
-      <c r="T272" s="43"/>
+      <c r="T272" s="1"/>
       <c r="U272" s="1"/>
       <c r="V272" s="1"/>
       <c r="W272" s="1"/>
@@ -15087,7 +15081,7 @@
       <c r="Q273" s="1"/>
       <c r="R273" s="1"/>
       <c r="S273" s="1"/>
-      <c r="T273" s="43"/>
+      <c r="T273" s="1"/>
       <c r="U273" s="1"/>
       <c r="V273" s="1"/>
       <c r="W273" s="1"/>
@@ -15128,7 +15122,7 @@
       <c r="Q274" s="1"/>
       <c r="R274" s="1"/>
       <c r="S274" s="1"/>
-      <c r="T274" s="43"/>
+      <c r="T274" s="1"/>
       <c r="U274" s="1"/>
       <c r="V274" s="1"/>
       <c r="W274" s="1"/>
@@ -15169,7 +15163,7 @@
       <c r="Q275" s="1"/>
       <c r="R275" s="1"/>
       <c r="S275" s="1"/>
-      <c r="T275" s="43"/>
+      <c r="T275" s="1"/>
       <c r="U275" s="1"/>
       <c r="V275" s="1"/>
       <c r="W275" s="1"/>
@@ -15210,7 +15204,7 @@
       <c r="Q276" s="1"/>
       <c r="R276" s="1"/>
       <c r="S276" s="1"/>
-      <c r="T276" s="43"/>
+      <c r="T276" s="1"/>
       <c r="U276" s="1"/>
       <c r="V276" s="1"/>
       <c r="W276" s="1"/>
@@ -15251,7 +15245,7 @@
       <c r="Q277" s="1"/>
       <c r="R277" s="1"/>
       <c r="S277" s="1"/>
-      <c r="T277" s="43"/>
+      <c r="T277" s="1"/>
       <c r="U277" s="1"/>
       <c r="V277" s="1"/>
       <c r="W277" s="1"/>
@@ -15292,7 +15286,7 @@
       <c r="Q278" s="1"/>
       <c r="R278" s="1"/>
       <c r="S278" s="1"/>
-      <c r="T278" s="43"/>
+      <c r="T278" s="1"/>
       <c r="U278" s="1"/>
       <c r="V278" s="1"/>
       <c r="W278" s="1"/>
@@ -15333,7 +15327,7 @@
       <c r="Q279" s="1"/>
       <c r="R279" s="1"/>
       <c r="S279" s="1"/>
-      <c r="T279" s="43"/>
+      <c r="T279" s="1"/>
       <c r="U279" s="1"/>
       <c r="V279" s="1"/>
       <c r="W279" s="1"/>
@@ -15374,7 +15368,7 @@
       <c r="Q280" s="1"/>
       <c r="R280" s="1"/>
       <c r="S280" s="1"/>
-      <c r="T280" s="43"/>
+      <c r="T280" s="1"/>
       <c r="U280" s="1"/>
       <c r="V280" s="1"/>
       <c r="W280" s="1"/>
@@ -15960,7 +15954,9 @@
       <c r="G34" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="H34" s="18"/>
+      <c r="H34" s="18" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="19" t="s">

--- a/LINE/シリーズごとのリスト.xlsx
+++ b/LINE/シリーズごとのリスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\LINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8404C8EF-681A-4EBE-B398-E1F74BC84491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{986619D4-276E-48C7-A676-45AA66F8D4CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="6">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -89,8 +89,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="6">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -106,12 +113,15 @@
     <bk>
       <rc t="1" v="4"/>
     </bk>
+    <bk>
+      <rc t="1" v="5"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="415">
   <si>
     <t>なんでやねん</t>
   </si>
@@ -257,9 +267,6 @@
     <t>敬楽しみにしております</t>
   </si>
   <si>
-    <t>敬申し訳ありません</t>
-  </si>
-  <si>
     <t>敬承知しました</t>
   </si>
   <si>
@@ -270,9 +277,6 @@
   </si>
   <si>
     <t>今日も一日お疲れ様でした</t>
-  </si>
-  <si>
-    <t>うん　うん</t>
   </si>
   <si>
     <t>キラリン</t>
@@ -1962,6 +1966,49 @@
     <rPh sb="0" eb="1">
       <t>コマ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敬申し訳ありません</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>うん　うん</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>なるほど</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>慌てた顔（言葉なし）</t>
+    <rPh sb="0" eb="1">
+      <t>アワ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コトバ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>表情だけ</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>そうだね</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ぐっ！</t>
+  </si>
+  <si>
+    <t>ふくろう１</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2388,7 +2435,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -2407,6 +2454,10 @@
   </rv>
   <rv s="0">
     <v>4</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>5</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -2428,6 +2479,7 @@
   <rel r:id="rId3"/>
   <rel r:id="rId4"/>
   <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
 </richValueRels>
 </file>
 
@@ -2717,13 +2769,13 @@
     <row r="1" spans="1:37" ht="22.9">
       <c r="A1" s="35"/>
       <c r="B1" s="40" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C1" s="32" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E1" s="38"/>
       <c r="F1" s="38"/>
@@ -2792,7 +2844,9 @@
       <c r="AG2" s="5"/>
       <c r="AH2" s="5"/>
       <c r="AI2" s="5"/>
-      <c r="AJ2" s="5"/>
+      <c r="AJ2" s="5" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
       <c r="AK2" s="5"/>
     </row>
     <row r="3" spans="1:37" s="13" customFormat="1" ht="106.9" thickBot="1">
@@ -2800,103 +2854,103 @@
       <c r="B3" s="42"/>
       <c r="C3" s="34"/>
       <c r="D3" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="F3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="J3" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="K3" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="L3" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="M3" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="N3" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="O3" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="P3" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="Q3" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="R3" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="S3" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="R3" s="11" t="s">
+      <c r="T3" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="S3" s="11" t="s">
+      <c r="U3" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="V3" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="T3" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="U3" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>137</v>
-      </c>
       <c r="W3" s="11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="X3" s="11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AA3" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="AB3" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="AC3" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="AB3" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="AC3" s="11" t="s">
-        <v>286</v>
-      </c>
       <c r="AD3" s="11" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AE3" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="AF3" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="AF3" s="11" t="s">
-        <v>295</v>
-      </c>
       <c r="AG3" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AH3" s="11" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AI3" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AJ3" s="11" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AK3" s="11"/>
     </row>
@@ -2905,19 +2959,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2927,21 +2981,21 @@
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
@@ -2954,7 +3008,9 @@
       <c r="AG4" s="29"/>
       <c r="AH4" s="1"/>
       <c r="AI4" s="1"/>
-      <c r="AJ4" s="1"/>
+      <c r="AJ4" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK4" s="1"/>
     </row>
     <row r="5" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -2962,19 +3018,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -2984,25 +3040,25 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
@@ -3012,10 +3068,12 @@
       <c r="AF5" s="1"/>
       <c r="AG5" s="29"/>
       <c r="AH5" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI5" s="1"/>
-      <c r="AJ5" s="1"/>
+      <c r="AJ5" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK5" s="1"/>
     </row>
     <row r="6" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -3024,14 +3082,14 @@
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -3045,13 +3103,13 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
@@ -3063,10 +3121,12 @@
       <c r="AF6" s="1"/>
       <c r="AG6" s="29"/>
       <c r="AH6" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI6" s="1"/>
-      <c r="AJ6" s="1"/>
+      <c r="AJ6" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK6" s="1"/>
     </row>
     <row r="7" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -3094,7 +3154,7 @@
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
@@ -3139,13 +3199,13 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
@@ -3186,7 +3246,7 @@
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
@@ -3255,14 +3315,14 @@
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -3276,13 +3336,13 @@
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
@@ -3585,7 +3645,7 @@
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
@@ -3669,7 +3729,7 @@
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
@@ -3728,10 +3788,12 @@
       <c r="AF21" s="1"/>
       <c r="AG21" s="29"/>
       <c r="AH21" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI21" s="1"/>
-      <c r="AJ21" s="1"/>
+      <c r="AJ21" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK21" s="1"/>
     </row>
     <row r="22" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -3747,7 +3809,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -3847,17 +3909,17 @@
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
       <c r="X24" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
@@ -3896,13 +3958,13 @@
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
       <c r="X25" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
@@ -3967,7 +4029,7 @@
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -3983,7 +4045,7 @@
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
@@ -4121,7 +4183,7 @@
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
@@ -4134,7 +4196,9 @@
       <c r="AG30" s="29"/>
       <c r="AH30" s="1"/>
       <c r="AI30" s="1"/>
-      <c r="AJ30" s="1"/>
+      <c r="AJ30" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK30" s="1"/>
     </row>
     <row r="31" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -4143,16 +4207,16 @@
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -4163,7 +4227,7 @@
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
@@ -4182,10 +4246,12 @@
       <c r="AF31" s="1"/>
       <c r="AG31" s="29"/>
       <c r="AH31" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI31" s="1"/>
-      <c r="AJ31" s="1"/>
+      <c r="AJ31" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK31" s="1"/>
     </row>
     <row r="32" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -4199,7 +4265,7 @@
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -4258,7 +4324,7 @@
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
@@ -4389,7 +4455,7 @@
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
@@ -4492,7 +4558,9 @@
       <c r="AG38" s="29"/>
       <c r="AH38" s="1"/>
       <c r="AI38" s="1"/>
-      <c r="AJ38" s="1"/>
+      <c r="AJ38" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK38" s="1"/>
     </row>
     <row r="39" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -4520,13 +4588,13 @@
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
       <c r="T39" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
       <c r="X39" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
@@ -4571,7 +4639,7 @@
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
       <c r="X40" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
@@ -4616,7 +4684,7 @@
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
       <c r="X41" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4704,7 +4772,7 @@
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
       <c r="X43" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4717,7 +4785,9 @@
       <c r="AG43" s="29"/>
       <c r="AH43" s="1"/>
       <c r="AI43" s="1"/>
-      <c r="AJ43" s="1"/>
+      <c r="AJ43" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK43" s="1"/>
     </row>
     <row r="44" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -4726,7 +4796,7 @@
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -4745,7 +4815,7 @@
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
@@ -4919,13 +4989,13 @@
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
       <c r="T48" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
       <c r="X48" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -4937,10 +5007,12 @@
       <c r="AF48" s="1"/>
       <c r="AG48" s="29"/>
       <c r="AH48" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI48" s="1"/>
-      <c r="AJ48" s="1"/>
+      <c r="AJ48" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK48" s="1"/>
     </row>
     <row r="49" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -5015,7 +5087,7 @@
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
       <c r="X50" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
@@ -5189,7 +5261,7 @@
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
       <c r="X54" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
@@ -5230,13 +5302,13 @@
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
       <c r="T55" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
       <c r="W55" s="1"/>
       <c r="X55" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
@@ -5277,7 +5349,7 @@
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
       <c r="T56" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
@@ -5328,7 +5400,7 @@
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
       <c r="Z57" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
@@ -5339,7 +5411,9 @@
       <c r="AG57" s="29"/>
       <c r="AH57" s="1"/>
       <c r="AI57" s="1"/>
-      <c r="AJ57" s="1"/>
+      <c r="AJ57" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK57" s="1"/>
     </row>
     <row r="58" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -5391,7 +5465,7 @@
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="4" t="s">
-        <v>48</v>
+        <v>407</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -5425,7 +5499,9 @@
       <c r="AG59" s="29"/>
       <c r="AH59" s="1"/>
       <c r="AI59" s="1"/>
-      <c r="AJ59" s="1"/>
+      <c r="AJ59" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK59" s="1"/>
     </row>
     <row r="60" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -5434,7 +5510,7 @@
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -5477,7 +5553,7 @@
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -5520,7 +5596,7 @@
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -5563,12 +5639,12 @@
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -5608,7 +5684,7 @@
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -5624,18 +5700,18 @@
       <c r="O64" s="1"/>
       <c r="P64" s="1"/>
       <c r="Q64" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
       <c r="T64" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
       <c r="W64" s="1"/>
       <c r="X64" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
@@ -5647,7 +5723,7 @@
       <c r="AF64" s="1"/>
       <c r="AG64" s="29"/>
       <c r="AH64" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI64" s="1"/>
       <c r="AJ64" s="1"/>
@@ -5659,7 +5735,7 @@
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="4" t="s">
-        <v>53</v>
+        <v>408</v>
       </c>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -5678,17 +5754,17 @@
       <c r="R65" s="1"/>
       <c r="S65" s="1"/>
       <c r="T65" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U65" s="1"/>
       <c r="V65" s="1"/>
       <c r="W65" s="1"/>
       <c r="X65" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y65" s="1"/>
       <c r="Z65" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
@@ -5699,7 +5775,9 @@
       <c r="AG65" s="29"/>
       <c r="AH65" s="1"/>
       <c r="AI65" s="1"/>
-      <c r="AJ65" s="1"/>
+      <c r="AJ65" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK65" s="1"/>
     </row>
     <row r="66" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -5708,7 +5786,7 @@
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -5727,7 +5805,7 @@
       <c r="R66" s="1"/>
       <c r="S66" s="1"/>
       <c r="T66" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U66" s="1"/>
       <c r="V66" s="1"/>
@@ -5753,12 +5831,12 @@
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -5778,7 +5856,7 @@
       <c r="V67" s="1"/>
       <c r="W67" s="1"/>
       <c r="X67" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
@@ -5800,12 +5878,12 @@
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -5827,7 +5905,7 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
       <c r="Z68" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA68" s="1"/>
       <c r="AB68" s="1"/>
@@ -5847,7 +5925,7 @@
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -5863,18 +5941,18 @@
       <c r="O69" s="1"/>
       <c r="P69" s="1"/>
       <c r="Q69" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
       <c r="T69" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
       <c r="W69" s="1"/>
       <c r="X69" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
@@ -5896,12 +5974,12 @@
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -5941,12 +6019,12 @@
       </c>
       <c r="B71" s="1"/>
       <c r="C71" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
@@ -5986,7 +6064,7 @@
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -6029,7 +6107,7 @@
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -6072,7 +6150,7 @@
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -6115,7 +6193,7 @@
       </c>
       <c r="B75" s="1"/>
       <c r="C75" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -6158,12 +6236,12 @@
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
@@ -6178,7 +6256,7 @@
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
       <c r="S76" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
@@ -6187,7 +6265,7 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
       <c r="Z76" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
@@ -6197,10 +6275,12 @@
       <c r="AF76" s="1"/>
       <c r="AG76" s="29"/>
       <c r="AH76" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI76" s="1"/>
-      <c r="AJ76" s="1"/>
+      <c r="AJ76" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK76" s="1"/>
     </row>
     <row r="77" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -6209,7 +6289,7 @@
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -6227,10 +6307,10 @@
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
       <c r="S77" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U77" s="1"/>
       <c r="V77" s="1"/>
@@ -6256,7 +6336,7 @@
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -6274,7 +6354,7 @@
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
       <c r="S78" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
@@ -6301,7 +6381,7 @@
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
@@ -6319,7 +6399,7 @@
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
       <c r="S79" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T79" s="1"/>
       <c r="U79" s="1"/>
@@ -6346,7 +6426,7 @@
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -6364,7 +6444,7 @@
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
       <c r="S80" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T80" s="1"/>
       <c r="U80" s="1"/>
@@ -6391,12 +6471,12 @@
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
@@ -6411,7 +6491,7 @@
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
       <c r="S81" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T81" s="1"/>
       <c r="U81" s="1"/>
@@ -6438,7 +6518,7 @@
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -6454,11 +6534,11 @@
       <c r="O82" s="1"/>
       <c r="P82" s="1"/>
       <c r="Q82" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R82" s="1"/>
       <c r="S82" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T82" s="1"/>
       <c r="U82" s="1"/>
@@ -6485,7 +6565,7 @@
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -6503,10 +6583,10 @@
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
       <c r="S83" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
@@ -6532,7 +6612,7 @@
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -6550,7 +6630,7 @@
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
       <c r="S84" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T84" s="1"/>
       <c r="U84" s="1"/>
@@ -6577,7 +6657,7 @@
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -6620,7 +6700,7 @@
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
@@ -6663,7 +6743,7 @@
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
@@ -6706,7 +6786,7 @@
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
@@ -6722,7 +6802,7 @@
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
@@ -6741,10 +6821,12 @@
       <c r="AF88" s="1"/>
       <c r="AG88" s="29"/>
       <c r="AH88" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI88" s="1"/>
-      <c r="AJ88" s="1"/>
+      <c r="AJ88" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK88" s="1"/>
     </row>
     <row r="89" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -6753,7 +6835,7 @@
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
@@ -6796,7 +6878,7 @@
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
@@ -6839,7 +6921,7 @@
       </c>
       <c r="B91" s="1"/>
       <c r="C91" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
@@ -6855,12 +6937,12 @@
       <c r="O91" s="1"/>
       <c r="P91" s="1"/>
       <c r="Q91" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
       <c r="T91" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U91" s="1"/>
       <c r="V91" s="1"/>
@@ -6886,12 +6968,12 @@
       </c>
       <c r="B92" s="1"/>
       <c r="C92" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
@@ -6931,7 +7013,7 @@
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
@@ -6965,7 +7047,9 @@
       <c r="AG93" s="29"/>
       <c r="AH93" s="1"/>
       <c r="AI93" s="1"/>
-      <c r="AJ93" s="1"/>
+      <c r="AJ93" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK93" s="1"/>
     </row>
     <row r="94" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -6974,7 +7058,7 @@
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
@@ -7017,7 +7101,7 @@
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
@@ -7060,7 +7144,7 @@
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
@@ -7103,7 +7187,7 @@
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
@@ -7146,14 +7230,14 @@
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
@@ -7167,7 +7251,7 @@
       <c r="R98" s="1"/>
       <c r="S98" s="1"/>
       <c r="T98" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U98" s="1"/>
       <c r="V98" s="1"/>
@@ -7236,7 +7320,7 @@
       </c>
       <c r="B100" s="1"/>
       <c r="C100" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
@@ -7279,7 +7363,7 @@
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
@@ -7313,7 +7397,9 @@
       <c r="AG101" s="29"/>
       <c r="AH101" s="1"/>
       <c r="AI101" s="1"/>
-      <c r="AJ101" s="1"/>
+      <c r="AJ101" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK101" s="1"/>
     </row>
     <row r="102" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -7322,7 +7408,7 @@
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
@@ -7365,7 +7451,7 @@
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
@@ -7408,7 +7494,7 @@
       </c>
       <c r="B104" s="1"/>
       <c r="C104" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
@@ -7451,7 +7537,7 @@
       </c>
       <c r="B105" s="1"/>
       <c r="C105" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
@@ -7470,13 +7556,13 @@
       <c r="R105" s="1"/>
       <c r="S105" s="1"/>
       <c r="T105" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
       <c r="W105" s="1"/>
       <c r="X105" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
@@ -7498,7 +7584,7 @@
       </c>
       <c r="B106" s="1"/>
       <c r="C106" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
@@ -7541,7 +7627,7 @@
       </c>
       <c r="B107" s="1"/>
       <c r="C107" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
@@ -7564,7 +7650,7 @@
       <c r="V107" s="1"/>
       <c r="W107" s="1"/>
       <c r="X107" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
@@ -7586,7 +7672,7 @@
       </c>
       <c r="B108" s="1"/>
       <c r="C108" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
@@ -7629,7 +7715,7 @@
       </c>
       <c r="B109" s="1"/>
       <c r="C109" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
@@ -7652,7 +7738,7 @@
       <c r="V109" s="1"/>
       <c r="W109" s="1"/>
       <c r="X109" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
@@ -7674,7 +7760,7 @@
       </c>
       <c r="B110" s="1"/>
       <c r="C110" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
@@ -7717,7 +7803,7 @@
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
@@ -7760,12 +7846,12 @@
       </c>
       <c r="B112" s="1"/>
       <c r="C112" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
       <c r="F112" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G112" s="1"/>
       <c r="H112" s="1"/>
@@ -7778,18 +7864,18 @@
       <c r="O112" s="1"/>
       <c r="P112" s="1"/>
       <c r="Q112" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R112" s="1"/>
       <c r="S112" s="1"/>
       <c r="T112" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
       <c r="W112" s="1"/>
       <c r="X112" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
@@ -7811,7 +7897,7 @@
       </c>
       <c r="B113" s="1"/>
       <c r="C113" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
@@ -7827,7 +7913,7 @@
       <c r="O113" s="1"/>
       <c r="P113" s="1"/>
       <c r="Q113" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R113" s="1"/>
       <c r="S113" s="1"/>
@@ -7889,7 +7975,7 @@
       <c r="AF114" s="1"/>
       <c r="AG114" s="29"/>
       <c r="AH114" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI114" s="1"/>
       <c r="AJ114" s="1"/>
@@ -7901,12 +7987,12 @@
       </c>
       <c r="B115" s="1"/>
       <c r="C115" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="1"/>
@@ -7946,7 +8032,7 @@
       </c>
       <c r="B116" s="1"/>
       <c r="C116" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
@@ -7989,7 +8075,7 @@
       </c>
       <c r="B117" s="1"/>
       <c r="C117" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
@@ -8032,7 +8118,7 @@
       </c>
       <c r="B118" s="1"/>
       <c r="C118" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
@@ -8075,7 +8161,7 @@
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
@@ -8118,7 +8204,7 @@
       </c>
       <c r="B120" s="1"/>
       <c r="C120" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
@@ -8137,7 +8223,7 @@
       <c r="R120" s="1"/>
       <c r="S120" s="1"/>
       <c r="T120" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U120" s="1"/>
       <c r="V120" s="1"/>
@@ -8154,7 +8240,9 @@
       <c r="AG120" s="29"/>
       <c r="AH120" s="1"/>
       <c r="AI120" s="1"/>
-      <c r="AJ120" s="1"/>
+      <c r="AJ120" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK120" s="1"/>
     </row>
     <row r="121" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -8163,7 +8251,7 @@
       </c>
       <c r="B121" s="1"/>
       <c r="C121" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
@@ -8206,7 +8294,7 @@
       </c>
       <c r="B122" s="1"/>
       <c r="C122" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
@@ -8249,7 +8337,7 @@
       </c>
       <c r="B123" s="1"/>
       <c r="C123" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
@@ -8292,7 +8380,7 @@
       </c>
       <c r="B124" s="1"/>
       <c r="C124" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
@@ -8335,7 +8423,7 @@
       </c>
       <c r="B125" s="1"/>
       <c r="C125" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
@@ -8378,7 +8466,7 @@
       </c>
       <c r="B126" s="1"/>
       <c r="C126" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
@@ -8394,12 +8482,12 @@
       <c r="O126" s="1"/>
       <c r="P126" s="1"/>
       <c r="Q126" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R126" s="1"/>
       <c r="S126" s="1"/>
       <c r="T126" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U126" s="1"/>
       <c r="V126" s="1"/>
@@ -8416,7 +8504,9 @@
       <c r="AG126" s="29"/>
       <c r="AH126" s="1"/>
       <c r="AI126" s="1"/>
-      <c r="AJ126" s="1"/>
+      <c r="AJ126" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK126" s="1"/>
     </row>
     <row r="127" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -8425,7 +8515,7 @@
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
@@ -8468,7 +8558,7 @@
       </c>
       <c r="B128" s="1"/>
       <c r="C128" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
@@ -8484,7 +8574,7 @@
       <c r="O128" s="1"/>
       <c r="P128" s="1"/>
       <c r="Q128" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R128" s="1"/>
       <c r="S128" s="1"/>
@@ -8493,7 +8583,7 @@
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
       <c r="X128" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
@@ -8515,7 +8605,7 @@
       </c>
       <c r="B129" s="1"/>
       <c r="C129" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
@@ -8533,7 +8623,7 @@
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
       <c r="S129" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T129" s="1"/>
       <c r="U129" s="1"/>
@@ -8560,7 +8650,7 @@
       </c>
       <c r="B130" s="1"/>
       <c r="C130" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
@@ -8576,18 +8666,18 @@
       <c r="O130" s="1"/>
       <c r="P130" s="1"/>
       <c r="Q130" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
       <c r="T130" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U130" s="1"/>
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
       <c r="X130" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
@@ -8599,7 +8689,7 @@
       <c r="AF130" s="1"/>
       <c r="AG130" s="29"/>
       <c r="AH130" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI130" s="1"/>
       <c r="AJ130" s="1"/>
@@ -8611,7 +8701,7 @@
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
@@ -8634,7 +8724,7 @@
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
       <c r="X131" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
@@ -8656,7 +8746,7 @@
       </c>
       <c r="B132" s="1"/>
       <c r="C132" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
@@ -8675,7 +8765,7 @@
       <c r="R132" s="1"/>
       <c r="S132" s="1"/>
       <c r="T132" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U132" s="1"/>
       <c r="V132" s="1"/>
@@ -8691,7 +8781,7 @@
       <c r="AF132" s="1"/>
       <c r="AG132" s="29"/>
       <c r="AH132" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI132" s="1"/>
       <c r="AJ132" s="1"/>
@@ -8703,7 +8793,7 @@
       </c>
       <c r="B133" s="1"/>
       <c r="C133" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
@@ -8746,7 +8836,7 @@
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
@@ -8789,7 +8879,7 @@
       </c>
       <c r="B135" s="1"/>
       <c r="C135" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
@@ -8832,7 +8922,7 @@
       </c>
       <c r="B136" s="1"/>
       <c r="C136" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
@@ -8865,7 +8955,7 @@
       <c r="AF136" s="1"/>
       <c r="AG136" s="29"/>
       <c r="AH136" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI136" s="1"/>
       <c r="AJ136" s="1"/>
@@ -8877,7 +8967,7 @@
       </c>
       <c r="B137" s="1"/>
       <c r="C137" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
@@ -8920,7 +9010,7 @@
       </c>
       <c r="B138" s="1"/>
       <c r="C138" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -8939,7 +9029,7 @@
       <c r="R138" s="1"/>
       <c r="S138" s="1"/>
       <c r="T138" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U138" s="1"/>
       <c r="V138" s="1"/>
@@ -8955,7 +9045,7 @@
       <c r="AF138" s="1"/>
       <c r="AG138" s="29"/>
       <c r="AH138" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI138" s="1"/>
       <c r="AJ138" s="1"/>
@@ -8967,7 +9057,7 @@
       </c>
       <c r="B139" s="1"/>
       <c r="C139" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
@@ -9010,7 +9100,7 @@
       </c>
       <c r="B140" s="1"/>
       <c r="C140" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
@@ -9053,7 +9143,7 @@
       </c>
       <c r="B141" s="1"/>
       <c r="C141" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
@@ -9096,7 +9186,7 @@
       </c>
       <c r="B142" s="1"/>
       <c r="C142" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
@@ -9115,7 +9205,7 @@
       <c r="R142" s="1"/>
       <c r="S142" s="1"/>
       <c r="T142" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U142" s="1"/>
       <c r="V142" s="1"/>
@@ -9141,7 +9231,7 @@
       </c>
       <c r="B143" s="1"/>
       <c r="C143" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
@@ -9184,7 +9274,7 @@
       </c>
       <c r="B144" s="1"/>
       <c r="C144" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
@@ -9227,7 +9317,7 @@
       </c>
       <c r="B145" s="1"/>
       <c r="C145" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
@@ -9270,7 +9360,7 @@
       </c>
       <c r="B146" s="1"/>
       <c r="C146" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
@@ -9313,7 +9403,7 @@
       </c>
       <c r="B147" s="1"/>
       <c r="C147" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
@@ -9338,7 +9428,7 @@
       <c r="X147" s="1"/>
       <c r="Y147" s="1"/>
       <c r="Z147" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA147" s="1"/>
       <c r="AB147" s="1"/>
@@ -9348,10 +9438,12 @@
       <c r="AF147" s="1"/>
       <c r="AG147" s="29"/>
       <c r="AH147" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI147" s="1"/>
-      <c r="AJ147" s="1"/>
+      <c r="AJ147" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK147" s="1"/>
     </row>
     <row r="148" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -9360,7 +9452,7 @@
       </c>
       <c r="B148" s="1"/>
       <c r="C148" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
@@ -9376,7 +9468,7 @@
       <c r="O148" s="1"/>
       <c r="P148" s="1"/>
       <c r="Q148" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
@@ -9405,7 +9497,7 @@
       </c>
       <c r="B149" s="1"/>
       <c r="C149" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
@@ -9448,7 +9540,7 @@
       </c>
       <c r="B150" s="1"/>
       <c r="C150" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
@@ -9481,7 +9573,7 @@
       <c r="AF150" s="1"/>
       <c r="AG150" s="29"/>
       <c r="AH150" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI150" s="1"/>
       <c r="AJ150" s="1"/>
@@ -9493,7 +9585,7 @@
       </c>
       <c r="B151" s="1"/>
       <c r="C151" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
@@ -9536,7 +9628,7 @@
       </c>
       <c r="B152" s="1"/>
       <c r="C152" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
@@ -9579,11 +9671,11 @@
       </c>
       <c r="B153" s="1"/>
       <c r="C153" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D153" s="1"/>
       <c r="E153" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F153" s="1"/>
       <c r="G153" s="1"/>
@@ -9600,7 +9692,7 @@
       <c r="R153" s="1"/>
       <c r="S153" s="1"/>
       <c r="T153" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
@@ -9616,7 +9708,7 @@
       <c r="AF153" s="1"/>
       <c r="AG153" s="29"/>
       <c r="AH153" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI153" s="1"/>
       <c r="AJ153" s="1"/>
@@ -9628,11 +9720,11 @@
       </c>
       <c r="B154" s="1"/>
       <c r="C154" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D154" s="1"/>
       <c r="E154" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F154" s="1"/>
       <c r="G154" s="1"/>
@@ -9673,11 +9765,11 @@
       </c>
       <c r="B155" s="1"/>
       <c r="C155" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D155" s="1"/>
       <c r="E155" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
@@ -9691,7 +9783,7 @@
       <c r="O155" s="1"/>
       <c r="P155" s="1"/>
       <c r="Q155" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R155" s="1"/>
       <c r="S155" s="1"/>
@@ -9702,7 +9794,7 @@
       <c r="X155" s="1"/>
       <c r="Y155" s="1"/>
       <c r="Z155" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA155" s="1"/>
       <c r="AB155" s="1"/>
@@ -9722,11 +9814,11 @@
       </c>
       <c r="B156" s="1"/>
       <c r="C156" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D156" s="1"/>
       <c r="E156" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
@@ -9767,11 +9859,11 @@
       </c>
       <c r="B157" s="1"/>
       <c r="C157" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D157" s="1"/>
       <c r="E157" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F157" s="1"/>
       <c r="G157" s="1"/>
@@ -9812,14 +9904,14 @@
       </c>
       <c r="B158" s="1"/>
       <c r="C158" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D158" s="1"/>
       <c r="E158" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
@@ -9835,7 +9927,7 @@
       <c r="R158" s="1"/>
       <c r="S158" s="1"/>
       <c r="T158" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U158" s="1"/>
       <c r="V158" s="1"/>
@@ -9843,7 +9935,7 @@
       <c r="X158" s="1"/>
       <c r="Y158" s="1"/>
       <c r="Z158" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA158" s="1"/>
       <c r="AB158" s="1"/>
@@ -9853,7 +9945,7 @@
       <c r="AF158" s="1"/>
       <c r="AG158" s="29"/>
       <c r="AH158" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI158" s="1"/>
       <c r="AJ158" s="1"/>
@@ -9865,11 +9957,11 @@
       </c>
       <c r="B159" s="1"/>
       <c r="C159" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D159" s="1"/>
       <c r="E159" s="10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="1"/>
@@ -9892,7 +9984,7 @@
       <c r="X159" s="1"/>
       <c r="Y159" s="1"/>
       <c r="Z159" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA159" s="1"/>
       <c r="AB159" s="1"/>
@@ -9902,10 +9994,12 @@
       <c r="AF159" s="1"/>
       <c r="AG159" s="29"/>
       <c r="AH159" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI159" s="1"/>
-      <c r="AJ159" s="1"/>
+      <c r="AJ159" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK159" s="1"/>
     </row>
     <row r="160" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -9914,11 +10008,11 @@
       </c>
       <c r="B160" s="1"/>
       <c r="C160" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D160" s="1"/>
       <c r="E160" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F160" s="1"/>
       <c r="G160" s="1"/>
@@ -9934,7 +10028,7 @@
       <c r="Q160" s="1"/>
       <c r="R160" s="1"/>
       <c r="S160" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T160" s="1"/>
       <c r="U160" s="1"/>
@@ -9961,11 +10055,11 @@
       </c>
       <c r="B161" s="1"/>
       <c r="C161" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D161" s="1"/>
       <c r="E161" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F161" s="1"/>
       <c r="G161" s="1"/>
@@ -10006,11 +10100,11 @@
       </c>
       <c r="B162" s="1"/>
       <c r="C162" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D162" s="1"/>
       <c r="E162" s="10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F162" s="1"/>
       <c r="G162" s="1"/>
@@ -10033,7 +10127,7 @@
       <c r="X162" s="1"/>
       <c r="Y162" s="1"/>
       <c r="Z162" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA162" s="1"/>
       <c r="AB162" s="1"/>
@@ -10043,7 +10137,7 @@
       <c r="AF162" s="1"/>
       <c r="AG162" s="29"/>
       <c r="AH162" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI162" s="1"/>
       <c r="AJ162" s="1"/>
@@ -10055,11 +10149,11 @@
       </c>
       <c r="B163" s="1"/>
       <c r="C163" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D163" s="1"/>
       <c r="E163" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F163" s="1"/>
       <c r="G163" s="1"/>
@@ -10072,7 +10166,7 @@
       <c r="N163" s="1"/>
       <c r="O163" s="1"/>
       <c r="P163" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
@@ -10084,7 +10178,7 @@
       <c r="X163" s="1"/>
       <c r="Y163" s="1"/>
       <c r="Z163" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA163" s="1"/>
       <c r="AB163" s="1"/>
@@ -10104,7 +10198,7 @@
       </c>
       <c r="B164" s="1"/>
       <c r="C164" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D164" s="3"/>
       <c r="E164" s="8"/>
@@ -10119,7 +10213,7 @@
       <c r="N164" s="3"/>
       <c r="O164" s="3"/>
       <c r="P164" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q164" s="3"/>
       <c r="R164" s="3"/>
@@ -10149,7 +10243,7 @@
       </c>
       <c r="B165" s="1"/>
       <c r="C165" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D165" s="3"/>
       <c r="E165" s="8"/>
@@ -10167,10 +10261,10 @@
       <c r="Q165" s="3"/>
       <c r="R165" s="3"/>
       <c r="S165" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T165" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U165" s="1"/>
       <c r="V165" s="3"/>
@@ -10196,7 +10290,7 @@
       </c>
       <c r="B166" s="1"/>
       <c r="C166" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D166" s="1"/>
       <c r="E166" s="8"/>
@@ -10239,7 +10333,7 @@
       </c>
       <c r="B167" s="1"/>
       <c r="C167" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D167" s="1"/>
       <c r="E167" s="8"/>
@@ -10282,7 +10376,7 @@
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D168" s="1"/>
       <c r="E168" s="8"/>
@@ -10325,7 +10419,7 @@
       </c>
       <c r="B169" s="1"/>
       <c r="C169" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D169" s="1"/>
       <c r="E169" s="8"/>
@@ -10368,7 +10462,7 @@
       </c>
       <c r="B170" s="1"/>
       <c r="C170" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D170" s="1"/>
       <c r="E170" s="8"/>
@@ -10411,7 +10505,7 @@
       </c>
       <c r="B171" s="1"/>
       <c r="C171" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D171" s="1"/>
       <c r="E171" s="8"/>
@@ -10454,7 +10548,7 @@
       </c>
       <c r="B172" s="1"/>
       <c r="C172" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D172" s="1"/>
       <c r="E172" s="8"/>
@@ -10469,7 +10563,7 @@
       <c r="N172" s="1"/>
       <c r="O172" s="1"/>
       <c r="P172" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
@@ -10490,7 +10584,9 @@
       <c r="AG172" s="29"/>
       <c r="AH172" s="1"/>
       <c r="AI172" s="1"/>
-      <c r="AJ172" s="1"/>
+      <c r="AJ172" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK172" s="1"/>
     </row>
     <row r="173" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -10499,7 +10595,7 @@
       </c>
       <c r="B173" s="1"/>
       <c r="C173" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D173" s="1"/>
       <c r="E173" s="8"/>
@@ -10541,15 +10637,15 @@
         <v>171</v>
       </c>
       <c r="B174" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D174" s="1"/>
       <c r="E174" s="8"/>
       <c r="F174" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G174" s="1"/>
       <c r="H174" s="1"/>
@@ -10561,17 +10657,17 @@
       <c r="N174" s="1"/>
       <c r="O174" s="1"/>
       <c r="P174" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q174" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R174" s="1"/>
       <c r="S174" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T174" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
@@ -10579,7 +10675,7 @@
       <c r="X174" s="1"/>
       <c r="Y174" s="1"/>
       <c r="Z174" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA174" s="1"/>
       <c r="AB174" s="1"/>
@@ -10589,10 +10685,12 @@
       <c r="AF174" s="1"/>
       <c r="AG174" s="29"/>
       <c r="AH174" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI174" s="1"/>
-      <c r="AJ174" s="1"/>
+      <c r="AJ174" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK174" s="1"/>
     </row>
     <row r="175" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -10600,15 +10698,15 @@
         <v>172</v>
       </c>
       <c r="B175" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D175" s="1"/>
       <c r="E175" s="8"/>
       <c r="F175" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G175" s="1"/>
       <c r="H175" s="1"/>
@@ -10623,10 +10721,10 @@
       <c r="Q175" s="1"/>
       <c r="R175" s="1"/>
       <c r="S175" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T175" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
@@ -10634,7 +10732,7 @@
       <c r="X175" s="1"/>
       <c r="Y175" s="1"/>
       <c r="Z175" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA175" s="1"/>
       <c r="AB175" s="1"/>
@@ -10644,7 +10742,7 @@
       <c r="AF175" s="1"/>
       <c r="AG175" s="29"/>
       <c r="AH175" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI175" s="1"/>
       <c r="AJ175" s="1"/>
@@ -10655,15 +10753,15 @@
         <v>173</v>
       </c>
       <c r="B176" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D176" s="1"/>
       <c r="E176" s="8"/>
       <c r="F176" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
@@ -10675,17 +10773,17 @@
       <c r="N176" s="1"/>
       <c r="O176" s="1"/>
       <c r="P176" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q176" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R176" s="1"/>
       <c r="S176" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T176" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
@@ -10693,7 +10791,7 @@
       <c r="X176" s="1"/>
       <c r="Y176" s="1"/>
       <c r="Z176" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA176" s="1"/>
       <c r="AB176" s="1"/>
@@ -10703,10 +10801,12 @@
       <c r="AF176" s="1"/>
       <c r="AG176" s="29"/>
       <c r="AH176" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI176" s="1"/>
-      <c r="AJ176" s="1"/>
+      <c r="AJ176" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK176" s="1"/>
     </row>
     <row r="177" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -10714,10 +10814,10 @@
         <v>174</v>
       </c>
       <c r="B177" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D177" s="1"/>
       <c r="E177" s="8"/>
@@ -10735,10 +10835,10 @@
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
       <c r="S177" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T177" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
@@ -10755,7 +10855,9 @@
       <c r="AG177" s="29"/>
       <c r="AH177" s="1"/>
       <c r="AI177" s="1"/>
-      <c r="AJ177" s="1"/>
+      <c r="AJ177" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK177" s="1"/>
     </row>
     <row r="178" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -10763,10 +10865,10 @@
         <v>175</v>
       </c>
       <c r="B178" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D178" s="1"/>
       <c r="E178" s="8"/>
@@ -10784,7 +10886,7 @@
       <c r="Q178" s="1"/>
       <c r="R178" s="1"/>
       <c r="S178" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T178" s="1"/>
       <c r="U178" s="1"/>
@@ -10801,10 +10903,12 @@
       <c r="AF178" s="1"/>
       <c r="AG178" s="29"/>
       <c r="AH178" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI178" s="1"/>
-      <c r="AJ178" s="1"/>
+      <c r="AJ178" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK178" s="1"/>
     </row>
     <row r="179" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -10812,10 +10916,10 @@
         <v>176</v>
       </c>
       <c r="B179" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D179" s="1"/>
       <c r="E179" s="8"/>
@@ -10833,7 +10937,7 @@
       <c r="Q179" s="1"/>
       <c r="R179" s="1"/>
       <c r="S179" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T179" s="1"/>
       <c r="U179" s="1"/>
@@ -10850,10 +10954,12 @@
       <c r="AF179" s="1"/>
       <c r="AG179" s="29"/>
       <c r="AH179" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI179" s="1"/>
-      <c r="AJ179" s="1"/>
+      <c r="AJ179" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK179" s="1"/>
     </row>
     <row r="180" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -10861,10 +10967,10 @@
         <v>177</v>
       </c>
       <c r="B180" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D180" s="1"/>
       <c r="E180" s="8"/>
@@ -10879,12 +10985,12 @@
       <c r="N180" s="1"/>
       <c r="O180" s="1"/>
       <c r="P180" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q180" s="1"/>
       <c r="R180" s="1"/>
       <c r="S180" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T180" s="1"/>
       <c r="U180" s="1"/>
@@ -10901,10 +11007,12 @@
       <c r="AF180" s="1"/>
       <c r="AG180" s="29"/>
       <c r="AH180" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI180" s="1"/>
-      <c r="AJ180" s="1"/>
+      <c r="AJ180" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK180" s="1"/>
     </row>
     <row r="181" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -10912,10 +11020,10 @@
         <v>178</v>
       </c>
       <c r="B181" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D181" s="1"/>
       <c r="E181" s="1"/>
@@ -10933,7 +11041,7 @@
       <c r="Q181" s="1"/>
       <c r="R181" s="1"/>
       <c r="S181" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T181" s="1"/>
       <c r="U181" s="1"/>
@@ -10950,10 +11058,12 @@
       <c r="AF181" s="1"/>
       <c r="AG181" s="29"/>
       <c r="AH181" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI181" s="1"/>
-      <c r="AJ181" s="1"/>
+      <c r="AJ181" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK181" s="1"/>
     </row>
     <row r="182" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -10961,10 +11071,10 @@
         <v>179</v>
       </c>
       <c r="B182" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
@@ -10982,14 +11092,14 @@
       <c r="Q182" s="1"/>
       <c r="R182" s="1"/>
       <c r="S182" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T182" s="1"/>
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
       <c r="W182" s="1"/>
       <c r="X182" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
@@ -11001,10 +11111,12 @@
       <c r="AF182" s="1"/>
       <c r="AG182" s="29"/>
       <c r="AH182" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI182" s="1"/>
-      <c r="AJ182" s="1"/>
+      <c r="AJ182" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK182" s="1"/>
     </row>
     <row r="183" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -11012,10 +11124,10 @@
         <v>180</v>
       </c>
       <c r="B183" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
@@ -11030,23 +11142,23 @@
       <c r="N183" s="1"/>
       <c r="O183" s="1"/>
       <c r="P183" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q183" s="1"/>
       <c r="R183" s="1"/>
       <c r="S183" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T183" s="1"/>
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
       <c r="W183" s="1"/>
       <c r="X183" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y183" s="1"/>
       <c r="Z183" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA183" s="1"/>
       <c r="AB183" s="1"/>
@@ -11056,10 +11168,12 @@
       <c r="AF183" s="1"/>
       <c r="AG183" s="29"/>
       <c r="AH183" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI183" s="1"/>
-      <c r="AJ183" s="1"/>
+      <c r="AJ183" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK183" s="1"/>
     </row>
     <row r="184" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -11067,10 +11181,10 @@
         <v>181</v>
       </c>
       <c r="B184" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
@@ -11085,19 +11199,19 @@
       <c r="N184" s="1"/>
       <c r="O184" s="1"/>
       <c r="P184" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q184" s="1"/>
       <c r="R184" s="1"/>
       <c r="S184" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T184" s="1"/>
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
       <c r="W184" s="1"/>
       <c r="X184" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
@@ -11109,10 +11223,12 @@
       <c r="AF184" s="1"/>
       <c r="AG184" s="29"/>
       <c r="AH184" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI184" s="1"/>
-      <c r="AJ184" s="1"/>
+      <c r="AJ184" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK184" s="1"/>
     </row>
     <row r="185" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -11120,10 +11236,10 @@
         <v>182</v>
       </c>
       <c r="B185" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D185" s="1"/>
       <c r="E185" s="1"/>
@@ -11138,12 +11254,12 @@
       <c r="N185" s="1"/>
       <c r="O185" s="1"/>
       <c r="P185" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q185" s="1"/>
       <c r="R185" s="1"/>
       <c r="S185" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T185" s="1"/>
       <c r="U185" s="1"/>
@@ -11160,7 +11276,7 @@
       <c r="AF185" s="1"/>
       <c r="AG185" s="29"/>
       <c r="AH185" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI185" s="1"/>
       <c r="AJ185" s="1"/>
@@ -11172,7 +11288,7 @@
       </c>
       <c r="B186" s="1"/>
       <c r="C186" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D186" s="1"/>
       <c r="E186" s="1"/>
@@ -11193,13 +11309,13 @@
       <c r="T186" s="1"/>
       <c r="U186" s="1"/>
       <c r="V186" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="W186" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="X186" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
@@ -11221,7 +11337,7 @@
       </c>
       <c r="B187" s="1"/>
       <c r="C187" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
@@ -11242,13 +11358,13 @@
       <c r="T187" s="1"/>
       <c r="U187" s="1"/>
       <c r="V187" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="W187" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="X187" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
@@ -11270,7 +11386,7 @@
       </c>
       <c r="B188" s="1"/>
       <c r="C188" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
@@ -11285,7 +11401,7 @@
       <c r="N188" s="1"/>
       <c r="O188" s="1"/>
       <c r="P188" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
@@ -11293,13 +11409,13 @@
       <c r="T188" s="1"/>
       <c r="U188" s="1"/>
       <c r="V188" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="W188" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="X188" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y188" s="1"/>
       <c r="Z188" s="1"/>
@@ -11321,7 +11437,7 @@
       </c>
       <c r="B189" s="1"/>
       <c r="C189" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
@@ -11342,13 +11458,13 @@
       <c r="T189" s="1"/>
       <c r="U189" s="1"/>
       <c r="V189" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="W189" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="X189" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
@@ -11370,7 +11486,7 @@
       </c>
       <c r="B190" s="1"/>
       <c r="C190" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
@@ -11391,13 +11507,13 @@
       <c r="T190" s="1"/>
       <c r="U190" s="1"/>
       <c r="V190" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="W190" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="X190" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y190" s="1"/>
       <c r="Z190" s="1"/>
@@ -11419,7 +11535,7 @@
       </c>
       <c r="B191" s="1"/>
       <c r="C191" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
@@ -11440,13 +11556,13 @@
       <c r="T191" s="1"/>
       <c r="U191" s="1"/>
       <c r="V191" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="W191" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="X191" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y191" s="1"/>
       <c r="Z191" s="1"/>
@@ -11468,7 +11584,7 @@
       </c>
       <c r="B192" s="1"/>
       <c r="C192" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
@@ -11486,10 +11602,10 @@
       <c r="Q192" s="1"/>
       <c r="R192" s="1"/>
       <c r="S192" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T192" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
@@ -11505,7 +11621,7 @@
       <c r="AF192" s="1"/>
       <c r="AG192" s="29"/>
       <c r="AH192" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI192" s="1"/>
       <c r="AJ192" s="1"/>
@@ -11517,7 +11633,7 @@
       </c>
       <c r="B193" s="1"/>
       <c r="C193" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
@@ -11532,13 +11648,13 @@
       <c r="N193" s="1"/>
       <c r="O193" s="1"/>
       <c r="P193" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
       <c r="S193" s="1"/>
       <c r="T193" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
@@ -11564,7 +11680,7 @@
       </c>
       <c r="B194" s="1"/>
       <c r="C194" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
@@ -11583,7 +11699,7 @@
       <c r="R194" s="1"/>
       <c r="S194" s="1"/>
       <c r="T194" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
@@ -11609,7 +11725,7 @@
       </c>
       <c r="B195" s="1"/>
       <c r="C195" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
@@ -11628,7 +11744,7 @@
       <c r="R195" s="1"/>
       <c r="S195" s="1"/>
       <c r="T195" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
@@ -11654,7 +11770,7 @@
       </c>
       <c r="B196" s="1"/>
       <c r="C196" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
@@ -11673,7 +11789,7 @@
       <c r="R196" s="1"/>
       <c r="S196" s="1"/>
       <c r="T196" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
@@ -11699,7 +11815,7 @@
       </c>
       <c r="B197" s="1"/>
       <c r="C197" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
@@ -11718,7 +11834,7 @@
       <c r="R197" s="1"/>
       <c r="S197" s="1"/>
       <c r="T197" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
@@ -11744,7 +11860,7 @@
       </c>
       <c r="B198" s="1"/>
       <c r="C198" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
@@ -11763,13 +11879,13 @@
       <c r="R198" s="1"/>
       <c r="S198" s="1"/>
       <c r="T198" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
       <c r="W198" s="1"/>
       <c r="X198" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
@@ -11791,7 +11907,7 @@
       </c>
       <c r="B199" s="1"/>
       <c r="C199" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
@@ -11810,17 +11926,17 @@
       <c r="R199" s="1"/>
       <c r="S199" s="1"/>
       <c r="T199" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
       <c r="W199" s="1"/>
       <c r="X199" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y199" s="1"/>
       <c r="Z199" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA199" s="1"/>
       <c r="AB199" s="1"/>
@@ -11840,7 +11956,7 @@
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
@@ -11859,7 +11975,7 @@
       <c r="R200" s="1"/>
       <c r="S200" s="1"/>
       <c r="T200" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
@@ -11885,7 +12001,7 @@
       </c>
       <c r="B201" s="1"/>
       <c r="C201" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
@@ -11904,13 +12020,13 @@
       <c r="R201" s="1"/>
       <c r="S201" s="1"/>
       <c r="T201" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U201" s="1"/>
       <c r="V201" s="1"/>
       <c r="W201" s="1"/>
       <c r="X201" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
@@ -11932,7 +12048,7 @@
       </c>
       <c r="B202" s="1"/>
       <c r="C202" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
@@ -11951,7 +12067,7 @@
       <c r="R202" s="1"/>
       <c r="S202" s="1"/>
       <c r="T202" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U202" s="1"/>
       <c r="V202" s="1"/>
@@ -11977,7 +12093,7 @@
       </c>
       <c r="B203" s="1"/>
       <c r="C203" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
@@ -11992,13 +12108,13 @@
       <c r="N203" s="1"/>
       <c r="O203" s="1"/>
       <c r="P203" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q203" s="1"/>
       <c r="R203" s="1"/>
       <c r="S203" s="1"/>
       <c r="T203" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U203" s="1"/>
       <c r="V203" s="1"/>
@@ -12024,7 +12140,7 @@
       </c>
       <c r="B204" s="1"/>
       <c r="C204" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
@@ -12043,7 +12159,7 @@
       <c r="R204" s="1"/>
       <c r="S204" s="1"/>
       <c r="T204" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U204" s="1"/>
       <c r="V204" s="1"/>
@@ -12069,7 +12185,7 @@
       </c>
       <c r="B205" s="1"/>
       <c r="C205" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
@@ -12088,7 +12204,7 @@
       <c r="R205" s="1"/>
       <c r="S205" s="1"/>
       <c r="T205" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U205" s="1"/>
       <c r="V205" s="1"/>
@@ -12114,7 +12230,7 @@
       </c>
       <c r="B206" s="1"/>
       <c r="C206" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
@@ -12133,7 +12249,7 @@
       <c r="R206" s="1"/>
       <c r="S206" s="1"/>
       <c r="T206" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U206" s="1"/>
       <c r="V206" s="1"/>
@@ -12159,7 +12275,7 @@
       </c>
       <c r="B207" s="1"/>
       <c r="C207" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
@@ -12174,13 +12290,13 @@
       <c r="N207" s="1"/>
       <c r="O207" s="1"/>
       <c r="P207" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q207" s="1"/>
       <c r="R207" s="1"/>
       <c r="S207" s="1"/>
       <c r="T207" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U207" s="1"/>
       <c r="V207" s="1"/>
@@ -12206,7 +12322,7 @@
       </c>
       <c r="B208" s="1"/>
       <c r="C208" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
@@ -12225,7 +12341,7 @@
       <c r="R208" s="1"/>
       <c r="S208" s="1"/>
       <c r="T208" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U208" s="1"/>
       <c r="V208" s="1"/>
@@ -12251,7 +12367,7 @@
       </c>
       <c r="B209" s="1"/>
       <c r="C209" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
@@ -12270,7 +12386,7 @@
       <c r="R209" s="1"/>
       <c r="S209" s="1"/>
       <c r="T209" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U209" s="1"/>
       <c r="V209" s="1"/>
@@ -12286,7 +12402,7 @@
       <c r="AF209" s="1"/>
       <c r="AG209" s="29"/>
       <c r="AH209" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI209" s="1"/>
       <c r="AJ209" s="1"/>
@@ -12298,7 +12414,7 @@
       </c>
       <c r="B210" s="1"/>
       <c r="C210" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
@@ -12317,7 +12433,7 @@
       <c r="R210" s="1"/>
       <c r="S210" s="1"/>
       <c r="T210" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U210" s="1"/>
       <c r="V210" s="1"/>
@@ -12343,7 +12459,7 @@
       </c>
       <c r="B211" s="1"/>
       <c r="C211" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
@@ -12362,7 +12478,7 @@
       <c r="R211" s="1"/>
       <c r="S211" s="1"/>
       <c r="T211" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
@@ -12388,7 +12504,7 @@
       </c>
       <c r="B212" s="1"/>
       <c r="C212" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
@@ -12407,7 +12523,7 @@
       <c r="R212" s="1"/>
       <c r="S212" s="1"/>
       <c r="T212" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
@@ -12433,7 +12549,7 @@
       </c>
       <c r="B213" s="1"/>
       <c r="C213" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
@@ -12452,7 +12568,7 @@
       <c r="R213" s="1"/>
       <c r="S213" s="1"/>
       <c r="T213" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
@@ -12478,7 +12594,7 @@
       </c>
       <c r="B214" s="1"/>
       <c r="C214" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
@@ -12497,7 +12613,7 @@
       <c r="R214" s="1"/>
       <c r="S214" s="1"/>
       <c r="T214" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U214" s="1"/>
       <c r="V214" s="1"/>
@@ -12505,7 +12621,7 @@
       <c r="X214" s="1"/>
       <c r="Y214" s="1"/>
       <c r="Z214" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA214" s="1"/>
       <c r="AB214" s="1"/>
@@ -12525,7 +12641,7 @@
       </c>
       <c r="B215" s="1"/>
       <c r="C215" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
@@ -12540,7 +12656,7 @@
       <c r="N215" s="1"/>
       <c r="O215" s="1"/>
       <c r="P215" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q215" s="1"/>
       <c r="R215" s="1"/>
@@ -12560,7 +12676,7 @@
       <c r="AF215" s="1"/>
       <c r="AG215" s="29"/>
       <c r="AH215" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI215" s="1"/>
       <c r="AJ215" s="1"/>
@@ -12571,10 +12687,10 @@
         <v>213</v>
       </c>
       <c r="B216" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
@@ -12593,17 +12709,17 @@
       <c r="R216" s="1"/>
       <c r="S216" s="1"/>
       <c r="T216" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U216" s="1"/>
       <c r="V216" s="1"/>
       <c r="W216" s="1"/>
       <c r="X216" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y216" s="1"/>
       <c r="Z216" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA216" s="1"/>
       <c r="AB216" s="1"/>
@@ -12622,10 +12738,10 @@
         <v>214</v>
       </c>
       <c r="B217" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
@@ -12644,17 +12760,17 @@
       <c r="R217" s="1"/>
       <c r="S217" s="1"/>
       <c r="T217" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U217" s="1"/>
       <c r="V217" s="1"/>
       <c r="W217" s="1"/>
       <c r="X217" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y217" s="1"/>
       <c r="Z217" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA217" s="1"/>
       <c r="AB217" s="1"/>
@@ -12673,10 +12789,10 @@
         <v>215</v>
       </c>
       <c r="B218" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
@@ -12695,17 +12811,17 @@
       <c r="R218" s="1"/>
       <c r="S218" s="1"/>
       <c r="T218" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U218" s="1"/>
       <c r="V218" s="1"/>
       <c r="W218" s="1"/>
       <c r="X218" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y218" s="1"/>
       <c r="Z218" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA218" s="1"/>
       <c r="AB218" s="1"/>
@@ -12715,7 +12831,7 @@
       <c r="AF218" s="1"/>
       <c r="AG218" s="29"/>
       <c r="AH218" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI218" s="1"/>
       <c r="AJ218" s="1"/>
@@ -12727,7 +12843,7 @@
       </c>
       <c r="B219" s="1"/>
       <c r="C219" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
@@ -12770,7 +12886,7 @@
       </c>
       <c r="B220" s="1"/>
       <c r="C220" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
@@ -12813,7 +12929,7 @@
       </c>
       <c r="B221" s="1"/>
       <c r="C221" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
@@ -12855,10 +12971,10 @@
         <v>219</v>
       </c>
       <c r="B222" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
@@ -12901,7 +13017,7 @@
       </c>
       <c r="B223" s="1"/>
       <c r="C223" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
@@ -12944,7 +13060,7 @@
       </c>
       <c r="B224" s="1"/>
       <c r="C224" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
@@ -12987,7 +13103,7 @@
       </c>
       <c r="B225" s="1"/>
       <c r="C225" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
@@ -13030,7 +13146,7 @@
       </c>
       <c r="B226" s="1"/>
       <c r="C226" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
@@ -13073,7 +13189,7 @@
       </c>
       <c r="B227" s="1"/>
       <c r="C227" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
@@ -13116,7 +13232,7 @@
       </c>
       <c r="B228" s="1"/>
       <c r="C228" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
@@ -13150,7 +13266,9 @@
       <c r="AG228" s="29"/>
       <c r="AH228" s="1"/>
       <c r="AI228" s="1"/>
-      <c r="AJ228" s="1"/>
+      <c r="AJ228" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK228" s="1"/>
     </row>
     <row r="229" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1">
@@ -13159,7 +13277,7 @@
       </c>
       <c r="B229" s="1"/>
       <c r="C229" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
@@ -13202,7 +13320,7 @@
       </c>
       <c r="B230" s="1"/>
       <c r="C230" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
@@ -13245,7 +13363,7 @@
       </c>
       <c r="B231" s="1"/>
       <c r="C231" s="21" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
@@ -13279,7 +13397,9 @@
       <c r="AG231" s="29"/>
       <c r="AH231" s="1"/>
       <c r="AI231" s="1"/>
-      <c r="AJ231" s="1"/>
+      <c r="AJ231" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK231" s="1"/>
     </row>
     <row r="232" spans="1:37">
@@ -13288,7 +13408,7 @@
       </c>
       <c r="B232" s="1"/>
       <c r="C232" s="21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
@@ -13330,10 +13450,10 @@
         <v>230</v>
       </c>
       <c r="B233" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C233" s="22" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
@@ -13358,7 +13478,7 @@
       <c r="X233" s="1"/>
       <c r="Y233" s="1"/>
       <c r="Z233" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA233" s="1"/>
       <c r="AB233" s="1"/>
@@ -13378,7 +13498,7 @@
       </c>
       <c r="B234" s="1"/>
       <c r="C234" s="21" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
@@ -13421,7 +13541,7 @@
       </c>
       <c r="B235" s="1"/>
       <c r="C235" s="21" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
@@ -13439,7 +13559,7 @@
       <c r="Q235" s="1"/>
       <c r="R235" s="1"/>
       <c r="S235" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T235" s="1"/>
       <c r="U235" s="1"/>
@@ -13456,7 +13576,7 @@
       <c r="AF235" s="1"/>
       <c r="AG235" s="29"/>
       <c r="AH235" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI235" s="1"/>
       <c r="AJ235" s="1"/>
@@ -13468,7 +13588,7 @@
       </c>
       <c r="B236" s="1"/>
       <c r="C236" s="21" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
@@ -13511,7 +13631,7 @@
       </c>
       <c r="B237" s="1"/>
       <c r="C237" s="21" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
@@ -13554,7 +13674,7 @@
       </c>
       <c r="B238" s="1"/>
       <c r="C238" s="21" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
@@ -13597,7 +13717,7 @@
       </c>
       <c r="B239" s="1"/>
       <c r="C239" s="21" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
@@ -13640,7 +13760,7 @@
       </c>
       <c r="B240" s="1"/>
       <c r="C240" s="21" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
@@ -13683,7 +13803,7 @@
       </c>
       <c r="B241" s="1"/>
       <c r="C241" s="21" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
@@ -13726,7 +13846,7 @@
       </c>
       <c r="B242" s="1"/>
       <c r="C242" s="21" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
@@ -13769,7 +13889,7 @@
       </c>
       <c r="B243" s="3"/>
       <c r="C243" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
@@ -13787,7 +13907,7 @@
       <c r="Q243" s="1"/>
       <c r="R243" s="1"/>
       <c r="S243" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T243" s="1"/>
       <c r="U243" s="1"/>
@@ -13805,7 +13925,9 @@
       <c r="AG243" s="29"/>
       <c r="AH243" s="1"/>
       <c r="AI243" s="1"/>
-      <c r="AJ243" s="1"/>
+      <c r="AJ243" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK243" s="1"/>
     </row>
     <row r="244" spans="1:37">
@@ -13814,7 +13936,7 @@
       </c>
       <c r="B244" s="3"/>
       <c r="C244" s="21" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
@@ -13832,7 +13954,7 @@
       <c r="Q244" s="1"/>
       <c r="R244" s="1"/>
       <c r="S244" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T244" s="1"/>
       <c r="U244" s="1"/>
@@ -13859,7 +13981,7 @@
       </c>
       <c r="B245" s="3"/>
       <c r="C245" s="21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
@@ -13877,7 +13999,7 @@
       <c r="Q245" s="1"/>
       <c r="R245" s="1"/>
       <c r="S245" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T245" s="1"/>
       <c r="U245" s="1"/>
@@ -13904,7 +14026,7 @@
       </c>
       <c r="B246" s="3"/>
       <c r="C246" s="21" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
@@ -13927,7 +14049,7 @@
       <c r="V246" s="1"/>
       <c r="W246" s="1"/>
       <c r="X246" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y246" s="1"/>
       <c r="Z246" s="1"/>
@@ -13949,7 +14071,7 @@
       </c>
       <c r="B247" s="3"/>
       <c r="C247" s="21" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
@@ -13972,7 +14094,7 @@
       <c r="V247" s="1"/>
       <c r="W247" s="1"/>
       <c r="X247" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y247" s="1"/>
       <c r="Z247" s="1"/>
@@ -13985,7 +14107,9 @@
       <c r="AG247" s="29"/>
       <c r="AH247" s="1"/>
       <c r="AI247" s="1"/>
-      <c r="AJ247" s="1"/>
+      <c r="AJ247" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK247" s="1"/>
     </row>
     <row r="248" spans="1:37">
@@ -13994,7 +14118,7 @@
       </c>
       <c r="B248" s="3"/>
       <c r="C248" s="21" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
@@ -14017,11 +14141,11 @@
       <c r="V248" s="1"/>
       <c r="W248" s="1"/>
       <c r="X248" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y248" s="1"/>
       <c r="Z248" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA248" s="1"/>
       <c r="AB248" s="1"/>
@@ -14041,7 +14165,7 @@
       </c>
       <c r="B249" s="3"/>
       <c r="C249" s="21" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
@@ -14084,7 +14208,7 @@
       </c>
       <c r="B250" s="3"/>
       <c r="C250" s="21" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
@@ -14127,7 +14251,7 @@
       </c>
       <c r="B251" s="3"/>
       <c r="C251" s="21" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
@@ -14170,7 +14294,7 @@
       </c>
       <c r="B252" s="3"/>
       <c r="C252" s="21" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
@@ -14213,7 +14337,7 @@
       </c>
       <c r="B253" s="3"/>
       <c r="C253" s="21" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
@@ -14256,7 +14380,7 @@
       </c>
       <c r="B254" s="3"/>
       <c r="C254" s="21" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
@@ -14299,7 +14423,7 @@
       </c>
       <c r="B255" s="3"/>
       <c r="C255" s="21" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
@@ -14342,7 +14466,7 @@
       </c>
       <c r="B256" s="3"/>
       <c r="C256" s="31" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
@@ -14367,7 +14491,7 @@
       <c r="X256" s="1"/>
       <c r="Y256" s="1"/>
       <c r="Z256" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA256" s="1"/>
       <c r="AB256" s="1"/>
@@ -14377,7 +14501,7 @@
       <c r="AF256" s="1"/>
       <c r="AG256" s="29"/>
       <c r="AH256" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI256" s="1"/>
       <c r="AJ256" s="1"/>
@@ -14389,7 +14513,7 @@
       </c>
       <c r="B257" s="3"/>
       <c r="C257" s="21" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
@@ -14422,7 +14546,7 @@
       <c r="AF257" s="1"/>
       <c r="AG257" s="29"/>
       <c r="AH257" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI257" s="1"/>
       <c r="AJ257" s="1"/>
@@ -14434,7 +14558,7 @@
       </c>
       <c r="B258" s="3"/>
       <c r="C258" s="21" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
@@ -14467,10 +14591,12 @@
       <c r="AF258" s="1"/>
       <c r="AG258" s="29"/>
       <c r="AH258" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI258" s="1"/>
-      <c r="AJ258" s="1"/>
+      <c r="AJ258" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK258" s="1"/>
     </row>
     <row r="259" spans="1:37">
@@ -14479,7 +14605,7 @@
       </c>
       <c r="B259" s="3"/>
       <c r="C259" s="21" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
@@ -14512,7 +14638,7 @@
       <c r="AF259" s="1"/>
       <c r="AG259" s="29"/>
       <c r="AH259" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI259" s="1"/>
       <c r="AJ259" s="1"/>
@@ -14524,7 +14650,7 @@
       </c>
       <c r="B260" s="3"/>
       <c r="C260" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
@@ -14557,7 +14683,7 @@
       <c r="AF260" s="1"/>
       <c r="AG260" s="29"/>
       <c r="AH260" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AI260" s="1"/>
       <c r="AJ260" s="1"/>
@@ -14569,7 +14695,7 @@
       </c>
       <c r="B261" s="3"/>
       <c r="C261" s="21" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D261" s="1"/>
       <c r="E261" s="1"/>
@@ -14588,7 +14714,7 @@
       <c r="R261" s="1"/>
       <c r="S261" s="1"/>
       <c r="T261" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U261" s="1"/>
       <c r="V261" s="1"/>
@@ -14613,7 +14739,9 @@
         <v>259</v>
       </c>
       <c r="B262" s="3"/>
-      <c r="C262" s="21"/>
+      <c r="C262" s="22" t="s">
+        <v>409</v>
+      </c>
       <c r="D262" s="1"/>
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
@@ -14646,7 +14774,9 @@
       <c r="AG262" s="29"/>
       <c r="AH262" s="1"/>
       <c r="AI262" s="1"/>
-      <c r="AJ262" s="1"/>
+      <c r="AJ262" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK262" s="1"/>
     </row>
     <row r="263" spans="1:37">
@@ -14654,7 +14784,9 @@
         <v>260</v>
       </c>
       <c r="B263" s="3"/>
-      <c r="C263" s="21"/>
+      <c r="C263" s="22" t="s">
+        <v>410</v>
+      </c>
       <c r="D263" s="1"/>
       <c r="E263" s="1"/>
       <c r="F263" s="1"/>
@@ -14695,7 +14827,9 @@
         <v>261</v>
       </c>
       <c r="B264" s="3"/>
-      <c r="C264" s="21"/>
+      <c r="C264" s="22" t="s">
+        <v>411</v>
+      </c>
       <c r="D264" s="1"/>
       <c r="E264" s="1"/>
       <c r="F264" s="1"/>
@@ -14728,7 +14862,9 @@
       <c r="AG264" s="29"/>
       <c r="AH264" s="1"/>
       <c r="AI264" s="1"/>
-      <c r="AJ264" s="1"/>
+      <c r="AJ264" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK264" s="1"/>
     </row>
     <row r="265" spans="1:37">
@@ -14736,7 +14872,9 @@
         <v>262</v>
       </c>
       <c r="B265" s="3"/>
-      <c r="C265" s="21"/>
+      <c r="C265" s="21" t="s">
+        <v>413</v>
+      </c>
       <c r="D265" s="1"/>
       <c r="E265" s="1"/>
       <c r="F265" s="1"/>
@@ -14769,7 +14907,9 @@
       <c r="AG265" s="29"/>
       <c r="AH265" s="1"/>
       <c r="AI265" s="1"/>
-      <c r="AJ265" s="1"/>
+      <c r="AJ265" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK265" s="1"/>
     </row>
     <row r="266" spans="1:37">
@@ -14777,7 +14917,9 @@
         <v>263</v>
       </c>
       <c r="B266" s="3"/>
-      <c r="C266" s="21"/>
+      <c r="C266" s="21" t="s">
+        <v>412</v>
+      </c>
       <c r="D266" s="1"/>
       <c r="E266" s="1"/>
       <c r="F266" s="1"/>
@@ -14810,7 +14952,9 @@
       <c r="AG266" s="29"/>
       <c r="AH266" s="1"/>
       <c r="AI266" s="1"/>
-      <c r="AJ266" s="1"/>
+      <c r="AJ266" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="AK266" s="1"/>
     </row>
     <row r="267" spans="1:37">
@@ -15429,30 +15573,30 @@
     <row r="2" spans="1:8">
       <c r="A2" s="14"/>
       <c r="B2" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="D2" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="E2" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="F2" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="G2" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="H2" s="15" t="s">
         <v>234</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -15464,33 +15608,33 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="19" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="19" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -15502,10 +15646,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -15516,10 +15660,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="19" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -15530,7 +15674,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="19" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
@@ -15542,7 +15686,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="20" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
@@ -15554,7 +15698,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -15566,10 +15710,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="19" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
@@ -15580,7 +15724,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -15592,7 +15736,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="19" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -15604,7 +15748,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="19" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -15616,13 +15760,13 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
@@ -15632,31 +15776,31 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="19" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E16" s="25"/>
       <c r="F16" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="19" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
@@ -15668,83 +15812,83 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="19" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="19" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="19" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="19" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -15756,7 +15900,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="19" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -15768,7 +15912,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="19" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -15780,29 +15924,29 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="19" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D24" s="25"/>
       <c r="E24" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H24" s="18"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="19" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -15814,31 +15958,31 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="19" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E26" s="25"/>
       <c r="F26" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -15850,7 +15994,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="19" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -15862,7 +16006,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="19" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
@@ -15874,7 +16018,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="19" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B30" s="18"/>
       <c r="C30" s="18"/>
@@ -15886,7 +16030,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="19" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
@@ -15898,7 +16042,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="19" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
@@ -15910,60 +16054,60 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="19" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="19" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D34" s="25"/>
       <c r="E34" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="19" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C35" s="18"/>
       <c r="D35" s="18"/>
@@ -15973,12 +16117,22 @@
       <c r="H35" s="18"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="19"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
+      <c r="A36" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="D36" s="25"/>
+      <c r="E36" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>154</v>
+      </c>
       <c r="G36" s="18"/>
       <c r="H36" s="18"/>
     </row>
@@ -17359,16 +17513,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="28" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E1" s="28"/>
     </row>
@@ -17379,7 +17533,7 @@
       <c r="B2" s="26"/>
       <c r="C2" s="3"/>
       <c r="D2" s="26" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -17390,7 +17544,7 @@
       <c r="B3" s="26"/>
       <c r="C3" s="3"/>
       <c r="D3" s="26" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E3" s="3"/>
     </row>
@@ -17401,7 +17555,7 @@
       <c r="B4" s="26"/>
       <c r="C4" s="3"/>
       <c r="D4" s="26" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E4" s="3"/>
     </row>
@@ -17412,7 +17566,7 @@
       <c r="B5" s="26"/>
       <c r="C5" s="3"/>
       <c r="D5" s="26" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E5" s="3"/>
     </row>
@@ -17423,7 +17577,7 @@
       <c r="B6" s="26"/>
       <c r="C6" s="3"/>
       <c r="D6" s="26" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E6" s="3"/>
     </row>
@@ -17434,7 +17588,7 @@
       <c r="B7" s="26"/>
       <c r="C7" s="3"/>
       <c r="D7" s="26" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E7" s="3"/>
     </row>
@@ -17445,7 +17599,7 @@
       <c r="B8" s="26"/>
       <c r="C8" s="3"/>
       <c r="D8" s="26" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -17456,7 +17610,7 @@
       <c r="B9" s="26"/>
       <c r="C9" s="3"/>
       <c r="D9" s="26" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E9" s="3"/>
     </row>
@@ -17467,7 +17621,7 @@
       <c r="B10" s="26"/>
       <c r="C10" s="3"/>
       <c r="D10" s="26" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E10" s="3"/>
     </row>
@@ -17478,7 +17632,7 @@
       <c r="B11" s="26"/>
       <c r="C11" s="3"/>
       <c r="D11" s="26" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E11" s="3"/>
     </row>
@@ -17489,7 +17643,7 @@
       <c r="B12" s="26"/>
       <c r="C12" s="3"/>
       <c r="D12" s="26" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E12" s="3"/>
     </row>
@@ -17500,7 +17654,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="3"/>
       <c r="D13" s="26" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E13" s="3"/>
     </row>
@@ -17511,7 +17665,7 @@
       <c r="B14" s="26"/>
       <c r="C14" s="3"/>
       <c r="D14" s="26" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E14" s="3"/>
     </row>
@@ -17522,7 +17676,7 @@
       <c r="B15" s="26"/>
       <c r="C15" s="3"/>
       <c r="D15" s="26" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E15" s="3"/>
     </row>
@@ -17533,7 +17687,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="3"/>
       <c r="D16" s="26" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E16" s="3"/>
     </row>
@@ -17544,7 +17698,7 @@
       <c r="B17" s="26"/>
       <c r="C17" s="3"/>
       <c r="D17" s="26" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E17" s="3"/>
     </row>
@@ -17555,7 +17709,7 @@
       <c r="B18" s="26"/>
       <c r="C18" s="3"/>
       <c r="D18" s="26" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E18" s="3"/>
     </row>
@@ -17566,7 +17720,7 @@
       <c r="B19" s="26"/>
       <c r="C19" s="3"/>
       <c r="D19" s="26" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E19" s="3"/>
     </row>
@@ -17577,7 +17731,7 @@
       <c r="B20" s="26"/>
       <c r="C20" s="3"/>
       <c r="D20" s="26" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E20" s="3"/>
     </row>
@@ -17588,7 +17742,7 @@
       <c r="B21" s="26"/>
       <c r="C21" s="3"/>
       <c r="D21" s="26" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E21" s="3"/>
     </row>
@@ -17599,7 +17753,7 @@
       <c r="B22" s="26"/>
       <c r="C22" s="3"/>
       <c r="D22" s="26" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E22" s="3"/>
     </row>
@@ -17610,7 +17764,7 @@
       <c r="B23" s="26"/>
       <c r="C23" s="3"/>
       <c r="D23" s="26" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E23" s="3"/>
     </row>
@@ -17621,7 +17775,7 @@
       <c r="B24" s="26"/>
       <c r="C24" s="3"/>
       <c r="D24" s="26" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E24" s="3"/>
     </row>
@@ -17632,7 +17786,7 @@
       <c r="B25" s="26"/>
       <c r="C25" s="3"/>
       <c r="D25" s="26" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E25" s="3"/>
     </row>
@@ -17643,7 +17797,7 @@
       <c r="B26" s="26"/>
       <c r="C26" s="3"/>
       <c r="D26" s="26" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E26" s="3"/>
     </row>
@@ -17654,7 +17808,7 @@
       <c r="B27" s="26"/>
       <c r="C27" s="3"/>
       <c r="D27" s="26" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E27" s="3"/>
     </row>
@@ -17665,7 +17819,7 @@
       <c r="B28" s="26"/>
       <c r="C28" s="3"/>
       <c r="D28" s="26" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E28" s="3"/>
     </row>
@@ -17676,7 +17830,7 @@
       <c r="B29" s="26"/>
       <c r="C29" s="3"/>
       <c r="D29" s="26" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E29" s="3"/>
     </row>
@@ -17687,7 +17841,7 @@
       <c r="B30" s="26"/>
       <c r="C30" s="3"/>
       <c r="D30" s="26" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E30" s="3"/>
     </row>
@@ -17698,7 +17852,7 @@
       <c r="B31" s="26"/>
       <c r="C31" s="3"/>
       <c r="D31" s="26" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E31" s="3"/>
     </row>
@@ -17709,7 +17863,7 @@
       <c r="B32" s="26"/>
       <c r="C32" s="3"/>
       <c r="D32" s="26" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E32" s="3"/>
     </row>
@@ -17720,7 +17874,7 @@
       <c r="B33" s="26"/>
       <c r="C33" s="3"/>
       <c r="D33" s="26" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E33" s="3"/>
     </row>
@@ -17729,14 +17883,14 @@
         <v>33</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="26" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -17744,14 +17898,14 @@
         <v>34</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="26" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -17759,14 +17913,14 @@
         <v>35</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="26" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -17774,14 +17928,14 @@
         <v>36</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="26" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -17789,14 +17943,14 @@
         <v>37</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="26" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -17804,14 +17958,14 @@
         <v>38</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="26" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -17819,14 +17973,14 @@
         <v>39</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="26" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -17834,14 +17988,14 @@
         <v>40</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="26" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -17849,14 +18003,14 @@
         <v>41</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="26" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -17864,14 +18018,14 @@
         <v>42</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="26" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -17879,14 +18033,14 @@
         <v>43</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="26" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -17894,14 +18048,14 @@
         <v>44</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="26" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -17909,14 +18063,14 @@
         <v>45</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="26" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -17924,14 +18078,14 @@
         <v>46</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="26" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -17939,14 +18093,14 @@
         <v>47</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="26" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -17954,14 +18108,14 @@
         <v>48</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="26" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -17969,11 +18123,11 @@
         <v>49</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="26" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E50" s="3"/>
     </row>
@@ -17982,11 +18136,11 @@
         <v>50</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="26" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E51" s="3"/>
     </row>
@@ -17995,11 +18149,11 @@
         <v>51</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="26" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E52" s="3"/>
     </row>
@@ -18008,11 +18162,11 @@
         <v>52</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="26" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E53" s="3"/>
     </row>
@@ -18021,11 +18175,11 @@
         <v>53</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="26" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E54" s="3"/>
     </row>
@@ -18034,11 +18188,11 @@
         <v>54</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="26" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E55" s="3"/>
     </row>
@@ -18047,11 +18201,11 @@
         <v>55</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="26" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E56" s="3"/>
     </row>
@@ -18060,11 +18214,11 @@
         <v>56</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="26" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E57" s="3"/>
     </row>
@@ -18073,11 +18227,11 @@
         <v>57</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="26" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E58" s="3"/>
     </row>
@@ -18086,11 +18240,11 @@
         <v>58</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="26" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E59" s="3"/>
     </row>
@@ -18099,11 +18253,11 @@
         <v>59</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="26" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E60" s="3"/>
     </row>
@@ -18112,11 +18266,11 @@
         <v>60</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="26" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E61" s="3"/>
     </row>
@@ -18125,11 +18279,11 @@
         <v>61</v>
       </c>
       <c r="B62" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="26" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E62" s="3"/>
     </row>
@@ -18138,11 +18292,11 @@
         <v>62</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="26" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E63" s="3"/>
     </row>
@@ -18151,11 +18305,11 @@
         <v>63</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="26" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E64" s="3"/>
     </row>
@@ -18164,11 +18318,11 @@
         <v>64</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="26" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E65" s="3"/>
     </row>
@@ -18177,11 +18331,11 @@
         <v>65</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="26" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E66" s="3"/>
     </row>
@@ -18190,11 +18344,11 @@
         <v>66</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="26" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E67" s="3"/>
     </row>
@@ -18203,11 +18357,11 @@
         <v>67</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="26" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E68" s="3"/>
     </row>
@@ -18216,11 +18370,11 @@
         <v>68</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C69" s="3"/>
       <c r="D69" s="26" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E69" s="3"/>
     </row>
@@ -18229,13 +18383,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D70" s="27" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E70" s="3"/>
     </row>
@@ -18244,13 +18398,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E71" s="3"/>
     </row>
@@ -18259,16 +18413,16 @@
         <v>71</v>
       </c>
       <c r="B72" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -18276,16 +18430,16 @@
         <v>72</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -18295,7 +18449,7 @@
       <c r="B74" s="26"/>
       <c r="C74" s="3"/>
       <c r="D74" s="26" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E74" s="3"/>
     </row>
@@ -18306,7 +18460,7 @@
       <c r="B75" s="26"/>
       <c r="C75" s="3"/>
       <c r="D75" s="26" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E75" s="3"/>
     </row>
@@ -18315,16 +18469,16 @@
         <v>75</v>
       </c>
       <c r="B76" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D76" s="27" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -18332,16 +18486,16 @@
         <v>76</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D77" s="27" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -18349,13 +18503,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D78" s="27" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E78" s="3"/>
     </row>
@@ -18364,13 +18518,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E79" s="3"/>
     </row>
@@ -18379,13 +18533,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E80" s="3"/>
     </row>
@@ -18394,14 +18548,14 @@
         <v>80</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="26" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -18409,14 +18563,14 @@
         <v>81</v>
       </c>
       <c r="B82" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="26" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -18424,11 +18578,11 @@
         <v>82</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C83" s="3"/>
       <c r="D83" s="26" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E83" s="3"/>
     </row>
@@ -18437,11 +18591,11 @@
         <v>83</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="26" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E84" s="3"/>
     </row>
@@ -18450,11 +18604,11 @@
         <v>84</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="26" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E85" s="3"/>
     </row>
@@ -18463,14 +18617,14 @@
         <v>85</v>
       </c>
       <c r="B86" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="26" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -18478,11 +18632,11 @@
         <v>86</v>
       </c>
       <c r="B87" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C87" s="3"/>
       <c r="D87" s="26" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E87" s="3"/>
     </row>
@@ -18491,14 +18645,14 @@
         <v>87</v>
       </c>
       <c r="B88" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C88" s="3"/>
       <c r="D88" s="26" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -18506,13 +18660,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D89" s="27" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E89" s="3"/>
     </row>
@@ -18521,11 +18675,11 @@
         <v>89</v>
       </c>
       <c r="B90" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="26" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E90" s="3"/>
     </row>
@@ -18534,11 +18688,11 @@
         <v>90</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C91" s="3"/>
       <c r="D91" s="26" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E91" s="3"/>
     </row>
@@ -18547,11 +18701,11 @@
         <v>91</v>
       </c>
       <c r="B92" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="26" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E92" s="3"/>
     </row>
@@ -18560,13 +18714,13 @@
         <v>92</v>
       </c>
       <c r="B93" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
    